--- a/exports/Resumen_Evidencias_OPS.xlsx
+++ b/exports/Resumen_Evidencias_OPS.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tiendas" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Actividades" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Resumen" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Tiendas" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Actividades" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Resumen'!$A$9:$H$15</definedName>
@@ -231,14 +231,14 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="10"/>
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -262,7 +262,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -292,8 +292,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -320,8 +320,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:bodyPr/>
+              <a:p>
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -344,7 +344,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>9</col>
@@ -359,9 +359,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>

--- a/exports/Resumen_Evidencias_OPS.xlsx
+++ b/exports/Resumen_Evidencias_OPS.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Resumen" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Tiendas" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Actividades" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tiendas" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Actividades" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Resumen'!$A$9:$H$15</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Resumen'!$A$1:$Q$21</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Resumen'!$A$1:$H$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Tiendas'!$A$4:$I$76</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Tiendas'!$1:$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Actividades'!$A$4:$G$11</definedName>
@@ -27,7 +27,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -70,8 +70,14 @@
       <color rgb="001E3932"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Aptos"/>
+      <b val="1"/>
+      <color rgb="00922F24"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -98,6 +104,11 @@
         <fgColor rgb="00F6F8F7"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F9E6E3"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -116,7 +127,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -127,19 +138,28 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="3" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="164" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -228,146 +248,6 @@
     </indexedColors>
   </colors>
 </styleSheet>
-</file>
-
-<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="10"/>
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>Avance por DM</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <barChart>
-        <barDir val="bar"/>
-        <grouping val="clustered"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'Resumen'!G9</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'Resumen'!$B$10:$B$15</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Resumen'!$G$10:$G$15</f>
-            </numRef>
-          </val>
-        </ser>
-        <gapWidth val="150"/>
-        <axId val="10"/>
-        <axId val="100"/>
-      </barChart>
-      <catAx>
-        <axId val="10"/>
-        <scaling>
-          <orientation val="minMax"/>
-          <max val="1"/>
-          <min val="0"/>
-        </scaling>
-        <axPos val="l"/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>% avance</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
-        <numFmt formatCode="0%" sourceLinked="0"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="100"/>
-        <lblOffset val="100"/>
-      </catAx>
-      <valAx>
-        <axId val="100"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorGridlines/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>DM</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="10"/>
-      </valAx>
-    </plotArea>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-</chartSpace>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>9</col>
-      <colOff>0</colOff>
-      <row>4</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="4968000" cy="2592000"/>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="1" name="Chart 1"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -656,6 +536,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00006241"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -690,17 +571,17 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Avance regional</t>
+          <t>Realizadas</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>DM</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Tiendas</t>
+          <t>% Avance</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -710,17 +591,17 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4">
+      <c r="A6" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>504</v>
+      </c>
+      <c r="E6" s="5">
         <f>IFERROR(SUM(D10:D15)/SUM(E10:E15),0)</f>
         <v/>
       </c>
-      <c r="C6" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="E6" s="5" t="n">
-        <v>72</v>
-      </c>
-      <c r="G6" s="5" t="n">
+      <c r="G6" s="4" t="n">
         <v>502</v>
       </c>
     </row>
@@ -771,7 +652,7 @@
       <c r="A10" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>Enrique Cesar</t>
         </is>
@@ -788,42 +669,42 @@
       <c r="F10" s="7" t="n">
         <v>68</v>
       </c>
-      <c r="G10" s="8">
+      <c r="G10" s="9">
         <f>IFERROR(D10/E10,0)</f>
         <v/>
       </c>
-      <c r="H10" s="7" t="inlineStr">
+      <c r="H10" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
       </c>
     </row>
     <row r="11" ht="21" customHeight="1">
-      <c r="A11" s="9" t="n">
+      <c r="A11" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="B11" s="9" t="inlineStr">
+      <c r="B11" s="12" t="inlineStr">
         <is>
           <t>Nancy Carolina</t>
         </is>
       </c>
-      <c r="C11" s="9" t="n">
+      <c r="C11" s="11" t="n">
         <v>12</v>
       </c>
-      <c r="D11" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" s="9" t="n">
+      <c r="D11" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="11" t="n">
         <v>84</v>
       </c>
-      <c r="F11" s="9" t="n">
+      <c r="F11" s="11" t="n">
         <v>84</v>
       </c>
-      <c r="G11" s="10">
+      <c r="G11" s="13">
         <f>IFERROR(D11/E11,0)</f>
         <v/>
       </c>
-      <c r="H11" s="9" t="inlineStr">
+      <c r="H11" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -833,7 +714,7 @@
       <c r="A12" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="B12" s="8" t="inlineStr">
         <is>
           <t>Vanessa Carreño</t>
         </is>
@@ -850,42 +731,42 @@
       <c r="F12" s="7" t="n">
         <v>91</v>
       </c>
-      <c r="G12" s="8">
+      <c r="G12" s="9">
         <f>IFERROR(D12/E12,0)</f>
         <v/>
       </c>
-      <c r="H12" s="7" t="inlineStr">
+      <c r="H12" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
       </c>
     </row>
     <row r="13" ht="21" customHeight="1">
-      <c r="A13" s="9" t="n">
+      <c r="A13" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="B13" s="9" t="inlineStr">
+      <c r="B13" s="12" t="inlineStr">
         <is>
           <t>Veronica Garcia</t>
         </is>
       </c>
-      <c r="C13" s="9" t="n">
+      <c r="C13" s="11" t="n">
         <v>11</v>
       </c>
-      <c r="D13" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" s="9" t="n">
+      <c r="D13" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="11" t="n">
         <v>77</v>
       </c>
-      <c r="F13" s="9" t="n">
+      <c r="F13" s="11" t="n">
         <v>77</v>
       </c>
-      <c r="G13" s="10">
+      <c r="G13" s="13">
         <f>IFERROR(D13/E13,0)</f>
         <v/>
       </c>
-      <c r="H13" s="9" t="inlineStr">
+      <c r="H13" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -895,7 +776,7 @@
       <c r="A14" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B14" s="8" t="inlineStr">
         <is>
           <t>Yazmin Chabela</t>
         </is>
@@ -912,42 +793,42 @@
       <c r="F14" s="7" t="n">
         <v>91</v>
       </c>
-      <c r="G14" s="8">
+      <c r="G14" s="9">
         <f>IFERROR(D14/E14,0)</f>
         <v/>
       </c>
-      <c r="H14" s="7" t="inlineStr">
+      <c r="H14" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
       </c>
     </row>
     <row r="15" ht="21" customHeight="1">
-      <c r="A15" s="9" t="n">
+      <c r="A15" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="B15" s="9" t="inlineStr">
+      <c r="B15" s="12" t="inlineStr">
         <is>
           <t>Yazmin Garcia</t>
         </is>
       </c>
-      <c r="C15" s="9" t="n">
+      <c r="C15" s="11" t="n">
         <v>13</v>
       </c>
-      <c r="D15" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" s="9" t="n">
+      <c r="D15" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="11" t="n">
         <v>91</v>
       </c>
-      <c r="F15" s="9" t="n">
+      <c r="F15" s="11" t="n">
         <v>91</v>
       </c>
-      <c r="G15" s="10">
+      <c r="G15" s="13">
         <f>IFERROR(D15/E15,0)</f>
         <v/>
       </c>
-      <c r="H15" s="9" t="inlineStr">
+      <c r="H15" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -978,13 +859,13 @@
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToWidth="1"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="001E3932"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -1065,38 +946,38 @@
       </c>
     </row>
     <row r="5" ht="21" customHeight="1">
-      <c r="A5" s="9" t="n">
+      <c r="A5" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="11" t="inlineStr">
+      <c r="B5" s="14" t="inlineStr">
         <is>
           <t>38401</t>
         </is>
       </c>
-      <c r="C5" s="9" t="inlineStr">
+      <c r="C5" s="12" t="inlineStr">
         <is>
           <t>Coacalco</t>
         </is>
       </c>
-      <c r="D5" s="9" t="inlineStr">
+      <c r="D5" s="12" t="inlineStr">
         <is>
           <t>Enrique Cesar Flores</t>
         </is>
       </c>
-      <c r="E5" s="9" t="n">
+      <c r="E5" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="F5" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="G5" s="9" t="n">
+      <c r="F5" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="G5" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="H5" s="10">
+      <c r="H5" s="13">
         <f>IFERROR(E5/F5,0)</f>
         <v/>
       </c>
-      <c r="I5" s="9" t="inlineStr">
+      <c r="I5" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -1106,17 +987,17 @@
       <c r="A6" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="12" t="inlineStr">
+      <c r="B6" s="15" t="inlineStr">
         <is>
           <t>38456</t>
         </is>
       </c>
-      <c r="C6" s="7" t="inlineStr">
+      <c r="C6" s="8" t="inlineStr">
         <is>
           <t>Plaza las Flores</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="D6" s="8" t="inlineStr">
         <is>
           <t>Enrique Cesar Flores</t>
         </is>
@@ -1130,49 +1011,49 @@
       <c r="G6" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="H6" s="8">
+      <c r="H6" s="9">
         <f>IFERROR(E6/F6,0)</f>
         <v/>
       </c>
-      <c r="I6" s="7" t="inlineStr">
+      <c r="I6" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
       </c>
     </row>
     <row r="7" ht="21" customHeight="1">
-      <c r="A7" s="9" t="n">
+      <c r="A7" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="11" t="inlineStr">
+      <c r="B7" s="14" t="inlineStr">
         <is>
           <t>38186</t>
         </is>
       </c>
-      <c r="C7" s="9" t="inlineStr">
+      <c r="C7" s="12" t="inlineStr">
         <is>
           <t>Arboledas</t>
         </is>
       </c>
-      <c r="D7" s="9" t="inlineStr">
+      <c r="D7" s="12" t="inlineStr">
         <is>
           <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
-      <c r="E7" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="G7" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="H7" s="10">
+      <c r="E7" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="G7" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="H7" s="13">
         <f>IFERROR(E7/F7,0)</f>
         <v/>
       </c>
-      <c r="I7" s="9" t="inlineStr">
+      <c r="I7" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -1182,17 +1063,17 @@
       <c r="A8" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="12" t="inlineStr">
+      <c r="B8" s="15" t="inlineStr">
         <is>
           <t>43194</t>
         </is>
       </c>
-      <c r="C8" s="7" t="inlineStr">
+      <c r="C8" s="8" t="inlineStr">
         <is>
           <t>Atana Lindavista</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="D8" s="8" t="inlineStr">
         <is>
           <t>Vanessa Carreño Rios</t>
         </is>
@@ -1206,49 +1087,49 @@
       <c r="G8" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="H8" s="8">
+      <c r="H8" s="9">
         <f>IFERROR(E8/F8,0)</f>
         <v/>
       </c>
-      <c r="I8" s="7" t="inlineStr">
+      <c r="I8" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
       </c>
     </row>
     <row r="9" ht="21" customHeight="1">
-      <c r="A9" s="9" t="n">
+      <c r="A9" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="11" t="inlineStr">
+      <c r="B9" s="14" t="inlineStr">
         <is>
           <t>43043</t>
         </is>
       </c>
-      <c r="C9" s="9" t="inlineStr">
+      <c r="C9" s="12" t="inlineStr">
         <is>
           <t>Atizapan</t>
         </is>
       </c>
-      <c r="D9" s="9" t="inlineStr">
+      <c r="D9" s="12" t="inlineStr">
         <is>
           <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
-      <c r="E9" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="G9" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="H9" s="10">
+      <c r="E9" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="G9" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="H9" s="13">
         <f>IFERROR(E9/F9,0)</f>
         <v/>
       </c>
-      <c r="I9" s="9" t="inlineStr">
+      <c r="I9" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -1258,17 +1139,17 @@
       <c r="A10" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="12" t="inlineStr">
+      <c r="B10" s="15" t="inlineStr">
         <is>
           <t>38149</t>
         </is>
       </c>
-      <c r="C10" s="7" t="inlineStr">
+      <c r="C10" s="8" t="inlineStr">
         <is>
           <t>Bellavista</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="D10" s="8" t="inlineStr">
         <is>
           <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
@@ -1282,49 +1163,49 @@
       <c r="G10" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="H10" s="8">
+      <c r="H10" s="9">
         <f>IFERROR(E10/F10,0)</f>
         <v/>
       </c>
-      <c r="I10" s="7" t="inlineStr">
+      <c r="I10" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
       </c>
     </row>
     <row r="11" ht="21" customHeight="1">
-      <c r="A11" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="B11" s="11" t="inlineStr">
+      <c r="A11" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="14" t="inlineStr">
         <is>
           <t>38930</t>
         </is>
       </c>
-      <c r="C11" s="9" t="inlineStr">
+      <c r="C11" s="12" t="inlineStr">
         <is>
           <t>Blvd. Aeropuerto dt</t>
         </is>
       </c>
-      <c r="D11" s="9" t="inlineStr">
+      <c r="D11" s="12" t="inlineStr">
         <is>
           <t>Veronica Garcia Ortega</t>
         </is>
       </c>
-      <c r="E11" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="G11" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="H11" s="10">
+      <c r="E11" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="G11" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="H11" s="13">
         <f>IFERROR(E11/F11,0)</f>
         <v/>
       </c>
-      <c r="I11" s="9" t="inlineStr">
+      <c r="I11" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -1334,17 +1215,17 @@
       <c r="A12" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="12" t="inlineStr">
+      <c r="B12" s="15" t="inlineStr">
         <is>
           <t>38529</t>
         </is>
       </c>
-      <c r="C12" s="7" t="inlineStr">
+      <c r="C12" s="8" t="inlineStr">
         <is>
           <t>Bosques de Aragon</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="D12" s="8" t="inlineStr">
         <is>
           <t>Veronica Garcia Ortega</t>
         </is>
@@ -1358,49 +1239,49 @@
       <c r="G12" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="H12" s="8">
+      <c r="H12" s="9">
         <f>IFERROR(E12/F12,0)</f>
         <v/>
       </c>
-      <c r="I12" s="7" t="inlineStr">
+      <c r="I12" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
       </c>
     </row>
     <row r="13" ht="21" customHeight="1">
-      <c r="A13" s="9" t="n">
+      <c r="A13" s="11" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="11" t="inlineStr">
+      <c r="B13" s="14" t="inlineStr">
         <is>
           <t>38527</t>
         </is>
       </c>
-      <c r="C13" s="9" t="inlineStr">
+      <c r="C13" s="12" t="inlineStr">
         <is>
           <t>Camarones</t>
         </is>
       </c>
-      <c r="D13" s="9" t="inlineStr">
+      <c r="D13" s="12" t="inlineStr">
         <is>
           <t>Vanessa Carreño Rios</t>
         </is>
       </c>
-      <c r="E13" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="G13" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="H13" s="10">
+      <c r="E13" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="G13" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="H13" s="13">
         <f>IFERROR(E13/F13,0)</f>
         <v/>
       </c>
-      <c r="I13" s="9" t="inlineStr">
+      <c r="I13" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -1410,17 +1291,17 @@
       <c r="A14" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="12" t="inlineStr">
+      <c r="B14" s="15" t="inlineStr">
         <is>
           <t>38837</t>
         </is>
       </c>
-      <c r="C14" s="7" t="inlineStr">
+      <c r="C14" s="8" t="inlineStr">
         <is>
           <t>Centenario Azcapotzalco</t>
         </is>
       </c>
-      <c r="D14" s="7" t="inlineStr">
+      <c r="D14" s="8" t="inlineStr">
         <is>
           <t>Vanessa Carreño Rios</t>
         </is>
@@ -1434,49 +1315,49 @@
       <c r="G14" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="H14" s="8">
+      <c r="H14" s="9">
         <f>IFERROR(E14/F14,0)</f>
         <v/>
       </c>
-      <c r="I14" s="7" t="inlineStr">
+      <c r="I14" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
       </c>
     </row>
     <row r="15" ht="21" customHeight="1">
-      <c r="A15" s="9" t="n">
+      <c r="A15" s="11" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="11" t="inlineStr">
+      <c r="B15" s="14" t="inlineStr">
         <is>
           <t>38394</t>
         </is>
       </c>
-      <c r="C15" s="9" t="inlineStr">
+      <c r="C15" s="12" t="inlineStr">
         <is>
           <t>Centro Comercial Lomas Verdes</t>
         </is>
       </c>
-      <c r="D15" s="9" t="inlineStr">
+      <c r="D15" s="12" t="inlineStr">
         <is>
           <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
-      <c r="E15" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="G15" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="H15" s="10">
+      <c r="E15" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="G15" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="H15" s="13">
         <f>IFERROR(E15/F15,0)</f>
         <v/>
       </c>
-      <c r="I15" s="9" t="inlineStr">
+      <c r="I15" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -1486,17 +1367,17 @@
       <c r="A16" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="12" t="inlineStr">
+      <c r="B16" s="15" t="inlineStr">
         <is>
           <t>38695</t>
         </is>
       </c>
-      <c r="C16" s="7" t="inlineStr">
+      <c r="C16" s="8" t="inlineStr">
         <is>
           <t>Cetram 4 Caminos</t>
         </is>
       </c>
-      <c r="D16" s="7" t="inlineStr">
+      <c r="D16" s="8" t="inlineStr">
         <is>
           <t>Yazmin Chabela Guadarrama</t>
         </is>
@@ -1510,49 +1391,49 @@
       <c r="G16" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="H16" s="8">
+      <c r="H16" s="9">
         <f>IFERROR(E16/F16,0)</f>
         <v/>
       </c>
-      <c r="I16" s="7" t="inlineStr">
+      <c r="I16" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
       </c>
     </row>
     <row r="17" ht="21" customHeight="1">
-      <c r="A17" s="9" t="n">
+      <c r="A17" s="11" t="n">
         <v>13</v>
       </c>
-      <c r="B17" s="11" t="inlineStr">
+      <c r="B17" s="14" t="inlineStr">
         <is>
           <t>38535</t>
         </is>
       </c>
-      <c r="C17" s="9" t="inlineStr">
+      <c r="C17" s="12" t="inlineStr">
         <is>
           <t>City Center Esmeralda</t>
         </is>
       </c>
-      <c r="D17" s="9" t="inlineStr">
+      <c r="D17" s="12" t="inlineStr">
         <is>
           <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
-      <c r="E17" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="G17" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="H17" s="10">
+      <c r="E17" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="G17" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="H17" s="13">
         <f>IFERROR(E17/F17,0)</f>
         <v/>
       </c>
-      <c r="I17" s="9" t="inlineStr">
+      <c r="I17" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -1562,17 +1443,17 @@
       <c r="A18" s="7" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="12" t="inlineStr">
+      <c r="B18" s="15" t="inlineStr">
         <is>
           <t>38604</t>
         </is>
       </c>
-      <c r="C18" s="7" t="inlineStr">
+      <c r="C18" s="8" t="inlineStr">
         <is>
           <t>Cosmopol</t>
         </is>
       </c>
-      <c r="D18" s="7" t="inlineStr">
+      <c r="D18" s="8" t="inlineStr">
         <is>
           <t>Enrique Cesar Flores</t>
         </is>
@@ -1586,49 +1467,49 @@
       <c r="G18" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="H18" s="8">
+      <c r="H18" s="9">
         <f>IFERROR(E18/F18,0)</f>
         <v/>
       </c>
-      <c r="I18" s="7" t="inlineStr">
+      <c r="I18" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
       </c>
     </row>
     <row r="19" ht="21" customHeight="1">
-      <c r="A19" s="9" t="n">
+      <c r="A19" s="11" t="n">
         <v>15</v>
       </c>
-      <c r="B19" s="11" t="inlineStr">
+      <c r="B19" s="14" t="inlineStr">
         <is>
           <t>43193</t>
         </is>
       </c>
-      <c r="C19" s="9" t="inlineStr">
+      <c r="C19" s="12" t="inlineStr">
         <is>
           <t>Cosmopol N1</t>
         </is>
       </c>
-      <c r="D19" s="9" t="inlineStr">
+      <c r="D19" s="12" t="inlineStr">
         <is>
           <t>Enrique Cesar Flores</t>
         </is>
       </c>
-      <c r="E19" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="G19" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="H19" s="10">
+      <c r="E19" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="G19" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="H19" s="13">
         <f>IFERROR(E19/F19,0)</f>
         <v/>
       </c>
-      <c r="I19" s="9" t="inlineStr">
+      <c r="I19" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -1638,17 +1519,17 @@
       <c r="A20" s="7" t="n">
         <v>16</v>
       </c>
-      <c r="B20" s="12" t="inlineStr">
+      <c r="B20" s="15" t="inlineStr">
         <is>
           <t>38197</t>
         </is>
       </c>
-      <c r="C20" s="7" t="inlineStr">
+      <c r="C20" s="8" t="inlineStr">
         <is>
           <t>Echegaray</t>
         </is>
       </c>
-      <c r="D20" s="7" t="inlineStr">
+      <c r="D20" s="8" t="inlineStr">
         <is>
           <t>Yazmin Chabela Guadarrama</t>
         </is>
@@ -1662,49 +1543,49 @@
       <c r="G20" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="H20" s="8">
+      <c r="H20" s="9">
         <f>IFERROR(E20/F20,0)</f>
         <v/>
       </c>
-      <c r="I20" s="7" t="inlineStr">
+      <c r="I20" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
       </c>
     </row>
     <row r="21" ht="21" customHeight="1">
-      <c r="A21" s="9" t="n">
+      <c r="A21" s="11" t="n">
         <v>17</v>
       </c>
-      <c r="B21" s="11" t="inlineStr">
+      <c r="B21" s="14" t="inlineStr">
         <is>
           <t>38431</t>
         </is>
       </c>
-      <c r="C21" s="9" t="inlineStr">
+      <c r="C21" s="12" t="inlineStr">
         <is>
           <t>Eduardo Molina</t>
         </is>
       </c>
-      <c r="D21" s="9" t="inlineStr">
+      <c r="D21" s="12" t="inlineStr">
         <is>
           <t>Veronica Garcia Ortega</t>
         </is>
       </c>
-      <c r="E21" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="G21" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="H21" s="10">
+      <c r="E21" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="G21" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="H21" s="13">
         <f>IFERROR(E21/F21,0)</f>
         <v/>
       </c>
-      <c r="I21" s="9" t="inlineStr">
+      <c r="I21" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -1714,17 +1595,17 @@
       <c r="A22" s="7" t="n">
         <v>18</v>
       </c>
-      <c r="B22" s="12" t="inlineStr">
+      <c r="B22" s="15" t="inlineStr">
         <is>
           <t>38458</t>
         </is>
       </c>
-      <c r="C22" s="7" t="inlineStr">
+      <c r="C22" s="8" t="inlineStr">
         <is>
           <t>El Rosario</t>
         </is>
       </c>
-      <c r="D22" s="7" t="inlineStr">
+      <c r="D22" s="8" t="inlineStr">
         <is>
           <t>Yazmin Chabela Guadarrama</t>
         </is>
@@ -1738,49 +1619,49 @@
       <c r="G22" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="H22" s="8">
+      <c r="H22" s="9">
         <f>IFERROR(E22/F22,0)</f>
         <v/>
       </c>
-      <c r="I22" s="7" t="inlineStr">
+      <c r="I22" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
       </c>
     </row>
     <row r="23" ht="21" customHeight="1">
-      <c r="A23" s="9" t="n">
+      <c r="A23" s="11" t="n">
         <v>19</v>
       </c>
-      <c r="B23" s="11" t="inlineStr">
+      <c r="B23" s="14" t="inlineStr">
         <is>
           <t>38903</t>
         </is>
       </c>
-      <c r="C23" s="9" t="inlineStr">
+      <c r="C23" s="12" t="inlineStr">
         <is>
           <t>Encuentro Oceania</t>
         </is>
       </c>
-      <c r="D23" s="9" t="inlineStr">
+      <c r="D23" s="12" t="inlineStr">
         <is>
           <t>Veronica Garcia Ortega</t>
         </is>
       </c>
-      <c r="E23" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F23" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="G23" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="H23" s="10">
+      <c r="E23" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="G23" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="H23" s="13">
         <f>IFERROR(E23/F23,0)</f>
         <v/>
       </c>
-      <c r="I23" s="9" t="inlineStr">
+      <c r="I23" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -1790,17 +1671,17 @@
       <c r="A24" s="7" t="n">
         <v>20</v>
       </c>
-      <c r="B24" s="12" t="inlineStr">
+      <c r="B24" s="15" t="inlineStr">
         <is>
           <t>38995</t>
         </is>
       </c>
-      <c r="C24" s="7" t="inlineStr">
+      <c r="C24" s="8" t="inlineStr">
         <is>
           <t>Encuentro Oceania II</t>
         </is>
       </c>
-      <c r="D24" s="7" t="inlineStr">
+      <c r="D24" s="8" t="inlineStr">
         <is>
           <t>Veronica Garcia Ortega</t>
         </is>
@@ -1814,49 +1695,49 @@
       <c r="G24" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="H24" s="8">
+      <c r="H24" s="9">
         <f>IFERROR(E24/F24,0)</f>
         <v/>
       </c>
-      <c r="I24" s="7" t="inlineStr">
+      <c r="I24" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
       </c>
     </row>
     <row r="25" ht="21" customHeight="1">
-      <c r="A25" s="9" t="n">
+      <c r="A25" s="11" t="n">
         <v>21</v>
       </c>
-      <c r="B25" s="11" t="inlineStr">
+      <c r="B25" s="14" t="inlineStr">
         <is>
           <t>38507</t>
         </is>
       </c>
-      <c r="C25" s="9" t="inlineStr">
+      <c r="C25" s="12" t="inlineStr">
         <is>
           <t>Espacio Vista del Valle</t>
         </is>
       </c>
-      <c r="D25" s="9" t="inlineStr">
+      <c r="D25" s="12" t="inlineStr">
         <is>
           <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
-      <c r="E25" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="G25" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="H25" s="10">
+      <c r="E25" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="G25" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="H25" s="13">
         <f>IFERROR(E25/F25,0)</f>
         <v/>
       </c>
-      <c r="I25" s="9" t="inlineStr">
+      <c r="I25" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -1866,17 +1747,17 @@
       <c r="A26" s="7" t="n">
         <v>22</v>
       </c>
-      <c r="B26" s="12" t="inlineStr">
+      <c r="B26" s="15" t="inlineStr">
         <is>
           <t>38363</t>
         </is>
       </c>
-      <c r="C26" s="7" t="inlineStr">
+      <c r="C26" s="8" t="inlineStr">
         <is>
           <t>Galerias Atizapan</t>
         </is>
       </c>
-      <c r="D26" s="7" t="inlineStr">
+      <c r="D26" s="8" t="inlineStr">
         <is>
           <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
@@ -1890,49 +1771,49 @@
       <c r="G26" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="H26" s="8">
+      <c r="H26" s="9">
         <f>IFERROR(E26/F26,0)</f>
         <v/>
       </c>
-      <c r="I26" s="7" t="inlineStr">
+      <c r="I26" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
       </c>
     </row>
     <row r="27" ht="21" customHeight="1">
-      <c r="A27" s="9" t="n">
+      <c r="A27" s="11" t="n">
         <v>23</v>
       </c>
-      <c r="B27" s="11" t="inlineStr">
+      <c r="B27" s="14" t="inlineStr">
         <is>
           <t>38894</t>
         </is>
       </c>
-      <c r="C27" s="9" t="inlineStr">
+      <c r="C27" s="12" t="inlineStr">
         <is>
           <t>Galerias Perinorte</t>
         </is>
       </c>
-      <c r="D27" s="9" t="inlineStr">
+      <c r="D27" s="12" t="inlineStr">
         <is>
           <t>Enrique Cesar Flores</t>
         </is>
       </c>
-      <c r="E27" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F27" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="G27" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="H27" s="10">
+      <c r="E27" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="G27" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="H27" s="13">
         <f>IFERROR(E27/F27,0)</f>
         <v/>
       </c>
-      <c r="I27" s="9" t="inlineStr">
+      <c r="I27" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -1942,17 +1823,17 @@
       <c r="A28" s="7" t="n">
         <v>24</v>
       </c>
-      <c r="B28" s="12" t="inlineStr">
+      <c r="B28" s="15" t="inlineStr">
         <is>
           <t>38770</t>
         </is>
       </c>
-      <c r="C28" s="7" t="inlineStr">
+      <c r="C28" s="8" t="inlineStr">
         <is>
           <t>Gustavo Baz 29</t>
         </is>
       </c>
-      <c r="D28" s="7" t="inlineStr">
+      <c r="D28" s="8" t="inlineStr">
         <is>
           <t>Yazmin Chabela Guadarrama</t>
         </is>
@@ -1966,49 +1847,49 @@
       <c r="G28" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="H28" s="8">
+      <c r="H28" s="9">
         <f>IFERROR(E28/F28,0)</f>
         <v/>
       </c>
-      <c r="I28" s="7" t="inlineStr">
+      <c r="I28" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
       </c>
     </row>
     <row r="29" ht="21" customHeight="1">
-      <c r="A29" s="9" t="n">
+      <c r="A29" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="B29" s="11" t="inlineStr">
+      <c r="B29" s="14" t="inlineStr">
         <is>
           <t>38230</t>
         </is>
       </c>
-      <c r="C29" s="9" t="inlineStr">
+      <c r="C29" s="12" t="inlineStr">
         <is>
           <t>ITEMS Edo de Mexico</t>
         </is>
       </c>
-      <c r="D29" s="9" t="inlineStr">
+      <c r="D29" s="12" t="inlineStr">
         <is>
           <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
-      <c r="E29" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F29" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="G29" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="H29" s="10">
+      <c r="E29" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="G29" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="H29" s="13">
         <f>IFERROR(E29/F29,0)</f>
         <v/>
       </c>
-      <c r="I29" s="9" t="inlineStr">
+      <c r="I29" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -2018,17 +1899,17 @@
       <c r="A30" s="7" t="n">
         <v>26</v>
       </c>
-      <c r="B30" s="12" t="inlineStr">
+      <c r="B30" s="15" t="inlineStr">
         <is>
           <t>38333</t>
         </is>
       </c>
-      <c r="C30" s="7" t="inlineStr">
+      <c r="C30" s="8" t="inlineStr">
         <is>
           <t>Izcalli Mega</t>
         </is>
       </c>
-      <c r="D30" s="7" t="inlineStr">
+      <c r="D30" s="8" t="inlineStr">
         <is>
           <t>Enrique Cesar Flores</t>
         </is>
@@ -2042,49 +1923,49 @@
       <c r="G30" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="H30" s="8">
+      <c r="H30" s="9">
         <f>IFERROR(E30/F30,0)</f>
         <v/>
       </c>
-      <c r="I30" s="7" t="inlineStr">
+      <c r="I30" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
       </c>
     </row>
     <row r="31" ht="21" customHeight="1">
-      <c r="A31" s="9" t="n">
+      <c r="A31" s="11" t="n">
         <v>27</v>
       </c>
-      <c r="B31" s="11" t="inlineStr">
+      <c r="B31" s="14" t="inlineStr">
         <is>
           <t>38661</t>
         </is>
       </c>
-      <c r="C31" s="9" t="inlineStr">
+      <c r="C31" s="12" t="inlineStr">
         <is>
           <t>Jinetes</t>
         </is>
       </c>
-      <c r="D31" s="9" t="inlineStr">
+      <c r="D31" s="12" t="inlineStr">
         <is>
           <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
-      <c r="E31" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F31" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="G31" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="H31" s="10">
+      <c r="E31" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="G31" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="H31" s="13">
         <f>IFERROR(E31/F31,0)</f>
         <v/>
       </c>
-      <c r="I31" s="9" t="inlineStr">
+      <c r="I31" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -2094,17 +1975,17 @@
       <c r="A32" s="7" t="n">
         <v>28</v>
       </c>
-      <c r="B32" s="12" t="inlineStr">
+      <c r="B32" s="15" t="inlineStr">
         <is>
           <t>38205</t>
         </is>
       </c>
-      <c r="C32" s="7" t="inlineStr">
+      <c r="C32" s="8" t="inlineStr">
         <is>
           <t>Lindavista</t>
         </is>
       </c>
-      <c r="D32" s="7" t="inlineStr">
+      <c r="D32" s="8" t="inlineStr">
         <is>
           <t>Vanessa Carreño Rios</t>
         </is>
@@ -2118,49 +1999,49 @@
       <c r="G32" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="H32" s="8">
+      <c r="H32" s="9">
         <f>IFERROR(E32/F32,0)</f>
         <v/>
       </c>
-      <c r="I32" s="7" t="inlineStr">
+      <c r="I32" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
       </c>
     </row>
     <row r="33" ht="21" customHeight="1">
-      <c r="A33" s="9" t="n">
+      <c r="A33" s="11" t="n">
         <v>29</v>
       </c>
-      <c r="B33" s="11" t="inlineStr">
+      <c r="B33" s="14" t="inlineStr">
         <is>
           <t>38207</t>
         </is>
       </c>
-      <c r="C33" s="9" t="inlineStr">
+      <c r="C33" s="12" t="inlineStr">
         <is>
           <t>Lindavista II</t>
         </is>
       </c>
-      <c r="D33" s="9" t="inlineStr">
+      <c r="D33" s="12" t="inlineStr">
         <is>
           <t>Vanessa Carreño Rios</t>
         </is>
       </c>
-      <c r="E33" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F33" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="G33" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="H33" s="10">
+      <c r="E33" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="G33" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="H33" s="13">
         <f>IFERROR(E33/F33,0)</f>
         <v/>
       </c>
-      <c r="I33" s="9" t="inlineStr">
+      <c r="I33" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -2170,17 +2051,17 @@
       <c r="A34" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="B34" s="12" t="inlineStr">
+      <c r="B34" s="15" t="inlineStr">
         <is>
           <t>38119</t>
         </is>
       </c>
-      <c r="C34" s="7" t="inlineStr">
+      <c r="C34" s="8" t="inlineStr">
         <is>
           <t>Lomas Verdes</t>
         </is>
       </c>
-      <c r="D34" s="7" t="inlineStr">
+      <c r="D34" s="8" t="inlineStr">
         <is>
           <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
@@ -2194,49 +2075,49 @@
       <c r="G34" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="H34" s="8">
+      <c r="H34" s="9">
         <f>IFERROR(E34/F34,0)</f>
         <v/>
       </c>
-      <c r="I34" s="7" t="inlineStr">
+      <c r="I34" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
       </c>
     </row>
     <row r="35" ht="21" customHeight="1">
-      <c r="A35" s="9" t="n">
+      <c r="A35" s="11" t="n">
         <v>31</v>
       </c>
-      <c r="B35" s="11" t="inlineStr">
+      <c r="B35" s="14" t="inlineStr">
         <is>
           <t>38270</t>
         </is>
       </c>
-      <c r="C35" s="9" t="inlineStr">
+      <c r="C35" s="12" t="inlineStr">
         <is>
           <t>Lomas Verdes II</t>
         </is>
       </c>
-      <c r="D35" s="9" t="inlineStr">
+      <c r="D35" s="12" t="inlineStr">
         <is>
           <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
-      <c r="E35" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F35" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="G35" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="H35" s="10">
+      <c r="E35" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="G35" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="H35" s="13">
         <f>IFERROR(E35/F35,0)</f>
         <v/>
       </c>
-      <c r="I35" s="9" t="inlineStr">
+      <c r="I35" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -2246,17 +2127,17 @@
       <c r="A36" s="7" t="n">
         <v>32</v>
       </c>
-      <c r="B36" s="12" t="inlineStr">
+      <c r="B36" s="15" t="inlineStr">
         <is>
           <t>38368</t>
         </is>
       </c>
-      <c r="C36" s="7" t="inlineStr">
+      <c r="C36" s="8" t="inlineStr">
         <is>
           <t>Luna Park</t>
         </is>
       </c>
-      <c r="D36" s="7" t="inlineStr">
+      <c r="D36" s="8" t="inlineStr">
         <is>
           <t>Enrique Cesar Flores</t>
         </is>
@@ -2270,49 +2151,49 @@
       <c r="G36" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="H36" s="8">
+      <c r="H36" s="9">
         <f>IFERROR(E36/F36,0)</f>
         <v/>
       </c>
-      <c r="I36" s="7" t="inlineStr">
+      <c r="I36" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
       </c>
     </row>
     <row r="37" ht="21" customHeight="1">
-      <c r="A37" s="9" t="n">
+      <c r="A37" s="11" t="n">
         <v>33</v>
       </c>
-      <c r="B37" s="11" t="inlineStr">
+      <c r="B37" s="14" t="inlineStr">
         <is>
           <t>38371</t>
         </is>
       </c>
-      <c r="C37" s="9" t="inlineStr">
+      <c r="C37" s="12" t="inlineStr">
         <is>
           <t>Montevideo DT</t>
         </is>
       </c>
-      <c r="D37" s="9" t="inlineStr">
+      <c r="D37" s="12" t="inlineStr">
         <is>
           <t>Vanessa Carreño Rios</t>
         </is>
       </c>
-      <c r="E37" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F37" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="G37" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="H37" s="10">
+      <c r="E37" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="G37" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="H37" s="13">
         <f>IFERROR(E37/F37,0)</f>
         <v/>
       </c>
-      <c r="I37" s="9" t="inlineStr">
+      <c r="I37" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -2322,17 +2203,17 @@
       <c r="A38" s="7" t="n">
         <v>34</v>
       </c>
-      <c r="B38" s="12" t="inlineStr">
+      <c r="B38" s="15" t="inlineStr">
         <is>
           <t>43111</t>
         </is>
       </c>
-      <c r="C38" s="7" t="inlineStr">
+      <c r="C38" s="8" t="inlineStr">
         <is>
           <t>Montevideo Insurgentes</t>
         </is>
       </c>
-      <c r="D38" s="7" t="inlineStr">
+      <c r="D38" s="8" t="inlineStr">
         <is>
           <t>Vanessa Carreño Rios</t>
         </is>
@@ -2346,49 +2227,49 @@
       <c r="G38" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="H38" s="8">
+      <c r="H38" s="9">
         <f>IFERROR(E38/F38,0)</f>
         <v/>
       </c>
-      <c r="I38" s="7" t="inlineStr">
+      <c r="I38" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
       </c>
     </row>
     <row r="39" ht="21" customHeight="1">
-      <c r="A39" s="9" t="n">
+      <c r="A39" s="11" t="n">
         <v>35</v>
       </c>
-      <c r="B39" s="11" t="inlineStr">
+      <c r="B39" s="14" t="inlineStr">
         <is>
           <t>38674</t>
         </is>
       </c>
-      <c r="C39" s="9" t="inlineStr">
+      <c r="C39" s="12" t="inlineStr">
         <is>
           <t>Mundo E</t>
         </is>
       </c>
-      <c r="D39" s="9" t="inlineStr">
+      <c r="D39" s="12" t="inlineStr">
         <is>
           <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
-      <c r="E39" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F39" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="G39" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="H39" s="10">
+      <c r="E39" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="G39" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="H39" s="13">
         <f>IFERROR(E39/F39,0)</f>
         <v/>
       </c>
-      <c r="I39" s="9" t="inlineStr">
+      <c r="I39" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -2398,17 +2279,17 @@
       <c r="A40" s="7" t="n">
         <v>36</v>
       </c>
-      <c r="B40" s="12" t="inlineStr">
+      <c r="B40" s="15" t="inlineStr">
         <is>
           <t>38845</t>
         </is>
       </c>
-      <c r="C40" s="7" t="inlineStr">
+      <c r="C40" s="8" t="inlineStr">
         <is>
           <t>Mundo E II</t>
         </is>
       </c>
-      <c r="D40" s="7" t="inlineStr">
+      <c r="D40" s="8" t="inlineStr">
         <is>
           <t>Nancy Carolina Rodriguez Medina</t>
         </is>
@@ -2422,49 +2303,49 @@
       <c r="G40" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="H40" s="8">
+      <c r="H40" s="9">
         <f>IFERROR(E40/F40,0)</f>
         <v/>
       </c>
-      <c r="I40" s="7" t="inlineStr">
+      <c r="I40" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
       </c>
     </row>
     <row r="41" ht="21" customHeight="1">
-      <c r="A41" s="9" t="n">
+      <c r="A41" s="11" t="n">
         <v>37</v>
       </c>
-      <c r="B41" s="11" t="inlineStr">
+      <c r="B41" s="14" t="inlineStr">
         <is>
           <t>43195</t>
         </is>
       </c>
-      <c r="C41" s="9" t="inlineStr">
+      <c r="C41" s="12" t="inlineStr">
         <is>
           <t>Parque Jadin kiosko</t>
         </is>
       </c>
-      <c r="D41" s="9" t="inlineStr">
+      <c r="D41" s="12" t="inlineStr">
         <is>
           <t>Vanessa Carreño Rios</t>
         </is>
       </c>
-      <c r="E41" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F41" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="G41" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="H41" s="10">
+      <c r="E41" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="G41" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="H41" s="13">
         <f>IFERROR(E41/F41,0)</f>
         <v/>
       </c>
-      <c r="I41" s="9" t="inlineStr">
+      <c r="I41" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -2474,17 +2355,17 @@
       <c r="A42" s="7" t="n">
         <v>38</v>
       </c>
-      <c r="B42" s="12" t="inlineStr">
+      <c r="B42" s="15" t="inlineStr">
         <is>
           <t>38937</t>
         </is>
       </c>
-      <c r="C42" s="7" t="inlineStr">
+      <c r="C42" s="8" t="inlineStr">
         <is>
           <t>Parque Tepeyac Piso 1</t>
         </is>
       </c>
-      <c r="D42" s="7" t="inlineStr">
+      <c r="D42" s="8" t="inlineStr">
         <is>
           <t>Veronica Garcia Ortega</t>
         </is>
@@ -2498,49 +2379,49 @@
       <c r="G42" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="H42" s="8">
+      <c r="H42" s="9">
         <f>IFERROR(E42/F42,0)</f>
         <v/>
       </c>
-      <c r="I42" s="7" t="inlineStr">
+      <c r="I42" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
       </c>
     </row>
     <row r="43" ht="21" customHeight="1">
-      <c r="A43" s="9" t="n">
+      <c r="A43" s="11" t="n">
         <v>39</v>
       </c>
-      <c r="B43" s="11" t="inlineStr">
+      <c r="B43" s="14" t="inlineStr">
         <is>
           <t>38965</t>
         </is>
       </c>
-      <c r="C43" s="9" t="inlineStr">
+      <c r="C43" s="12" t="inlineStr">
         <is>
           <t>Parque Tepeyac Piso 2</t>
         </is>
       </c>
-      <c r="D43" s="9" t="inlineStr">
+      <c r="D43" s="12" t="inlineStr">
         <is>
           <t>Veronica Garcia Ortega</t>
         </is>
       </c>
-      <c r="E43" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F43" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="G43" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="H43" s="10">
+      <c r="E43" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="G43" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="H43" s="13">
         <f>IFERROR(E43/F43,0)</f>
         <v/>
       </c>
-      <c r="I43" s="9" t="inlineStr">
+      <c r="I43" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -2550,17 +2431,17 @@
       <c r="A44" s="7" t="n">
         <v>40</v>
       </c>
-      <c r="B44" s="12" t="inlineStr">
+      <c r="B44" s="15" t="inlineStr">
         <is>
           <t>38561</t>
         </is>
       </c>
-      <c r="C44" s="7" t="inlineStr">
+      <c r="C44" s="8" t="inlineStr">
         <is>
           <t>Parque Toreo</t>
         </is>
       </c>
-      <c r="D44" s="7" t="inlineStr">
+      <c r="D44" s="8" t="inlineStr">
         <is>
           <t>Yazmin Chabela Guadarrama</t>
         </is>
@@ -2574,49 +2455,49 @@
       <c r="G44" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="H44" s="8">
+      <c r="H44" s="9">
         <f>IFERROR(E44/F44,0)</f>
         <v/>
       </c>
-      <c r="I44" s="7" t="inlineStr">
+      <c r="I44" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
       </c>
     </row>
     <row r="45" ht="21" customHeight="1">
-      <c r="A45" s="9" t="n">
+      <c r="A45" s="11" t="n">
         <v>41</v>
       </c>
-      <c r="B45" s="11" t="inlineStr">
+      <c r="B45" s="14" t="inlineStr">
         <is>
           <t>38590</t>
         </is>
       </c>
-      <c r="C45" s="9" t="inlineStr">
+      <c r="C45" s="12" t="inlineStr">
         <is>
           <t>Parque Toreo II</t>
         </is>
       </c>
-      <c r="D45" s="9" t="inlineStr">
+      <c r="D45" s="12" t="inlineStr">
         <is>
           <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
-      <c r="E45" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F45" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="G45" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="H45" s="10">
+      <c r="E45" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="G45" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="H45" s="13">
         <f>IFERROR(E45/F45,0)</f>
         <v/>
       </c>
-      <c r="I45" s="9" t="inlineStr">
+      <c r="I45" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -2626,17 +2507,17 @@
       <c r="A46" s="7" t="n">
         <v>42</v>
       </c>
-      <c r="B46" s="12" t="inlineStr">
+      <c r="B46" s="15" t="inlineStr">
         <is>
           <t>38792</t>
         </is>
       </c>
-      <c r="C46" s="7" t="inlineStr">
+      <c r="C46" s="8" t="inlineStr">
         <is>
           <t>Pasaje Tlanepantla</t>
         </is>
       </c>
-      <c r="D46" s="7" t="inlineStr">
+      <c r="D46" s="8" t="inlineStr">
         <is>
           <t>Nancy Carolina Rodriguez Medina</t>
         </is>
@@ -2650,49 +2531,49 @@
       <c r="G46" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="H46" s="8">
+      <c r="H46" s="9">
         <f>IFERROR(E46/F46,0)</f>
         <v/>
       </c>
-      <c r="I46" s="7" t="inlineStr">
+      <c r="I46" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
       </c>
     </row>
     <row r="47" ht="21" customHeight="1">
-      <c r="A47" s="9" t="n">
+      <c r="A47" s="11" t="n">
         <v>43</v>
       </c>
-      <c r="B47" s="11" t="inlineStr">
+      <c r="B47" s="14" t="inlineStr">
         <is>
           <t>38546</t>
         </is>
       </c>
-      <c r="C47" s="9" t="inlineStr">
+      <c r="C47" s="12" t="inlineStr">
         <is>
           <t>Patio Claveria</t>
         </is>
       </c>
-      <c r="D47" s="9" t="inlineStr">
+      <c r="D47" s="12" t="inlineStr">
         <is>
           <t>Vanessa Carreño Rios</t>
         </is>
       </c>
-      <c r="E47" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F47" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="G47" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="H47" s="10">
+      <c r="E47" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="G47" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="H47" s="13">
         <f>IFERROR(E47/F47,0)</f>
         <v/>
       </c>
-      <c r="I47" s="9" t="inlineStr">
+      <c r="I47" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -2702,17 +2583,17 @@
       <c r="A48" s="7" t="n">
         <v>44</v>
       </c>
-      <c r="B48" s="12" t="inlineStr">
+      <c r="B48" s="15" t="inlineStr">
         <is>
           <t>38515</t>
         </is>
       </c>
-      <c r="C48" s="7" t="inlineStr">
+      <c r="C48" s="8" t="inlineStr">
         <is>
           <t>Patio Ecatepec</t>
         </is>
       </c>
-      <c r="D48" s="7" t="inlineStr">
+      <c r="D48" s="8" t="inlineStr">
         <is>
           <t>Enrique Cesar Flores</t>
         </is>
@@ -2726,49 +2607,49 @@
       <c r="G48" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="H48" s="8">
+      <c r="H48" s="9">
         <f>IFERROR(E48/F48,0)</f>
         <v/>
       </c>
-      <c r="I48" s="7" t="inlineStr">
+      <c r="I48" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
       </c>
     </row>
     <row r="49" ht="21" customHeight="1">
-      <c r="A49" s="9" t="n">
+      <c r="A49" s="11" t="n">
         <v>45</v>
       </c>
-      <c r="B49" s="11" t="inlineStr">
+      <c r="B49" s="14" t="inlineStr">
         <is>
           <t>38677</t>
         </is>
       </c>
-      <c r="C49" s="9" t="inlineStr">
+      <c r="C49" s="12" t="inlineStr">
         <is>
           <t>Patio la Raza</t>
         </is>
       </c>
-      <c r="D49" s="9" t="inlineStr">
+      <c r="D49" s="12" t="inlineStr">
         <is>
           <t>Vanessa Carreño Rios</t>
         </is>
       </c>
-      <c r="E49" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F49" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="G49" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="H49" s="10">
+      <c r="E49" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="G49" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="H49" s="13">
         <f>IFERROR(E49/F49,0)</f>
         <v/>
       </c>
-      <c r="I49" s="9" t="inlineStr">
+      <c r="I49" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -2778,17 +2659,17 @@
       <c r="A50" s="7" t="n">
         <v>46</v>
       </c>
-      <c r="B50" s="12" t="inlineStr">
+      <c r="B50" s="15" t="inlineStr">
         <is>
           <t>38176</t>
         </is>
       </c>
-      <c r="C50" s="7" t="inlineStr">
+      <c r="C50" s="8" t="inlineStr">
         <is>
           <t>Periferico Satélite DT</t>
         </is>
       </c>
-      <c r="D50" s="7" t="inlineStr">
+      <c r="D50" s="8" t="inlineStr">
         <is>
           <t>Yazmin Chabela Guadarrama</t>
         </is>
@@ -2802,49 +2683,49 @@
       <c r="G50" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="H50" s="8">
+      <c r="H50" s="9">
         <f>IFERROR(E50/F50,0)</f>
         <v/>
       </c>
-      <c r="I50" s="7" t="inlineStr">
+      <c r="I50" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
       </c>
     </row>
     <row r="51" ht="21" customHeight="1">
-      <c r="A51" s="9" t="n">
+      <c r="A51" s="11" t="n">
         <v>47</v>
       </c>
-      <c r="B51" s="11" t="inlineStr">
+      <c r="B51" s="14" t="inlineStr">
         <is>
           <t>38924</t>
         </is>
       </c>
-      <c r="C51" s="9" t="inlineStr">
+      <c r="C51" s="12" t="inlineStr">
         <is>
           <t>Plaza Aeropuerto</t>
         </is>
       </c>
-      <c r="D51" s="9" t="inlineStr">
+      <c r="D51" s="12" t="inlineStr">
         <is>
           <t>Veronica Garcia Ortega</t>
         </is>
       </c>
-      <c r="E51" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F51" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="G51" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="H51" s="10">
+      <c r="E51" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F51" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="G51" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="H51" s="13">
         <f>IFERROR(E51/F51,0)</f>
         <v/>
       </c>
-      <c r="I51" s="9" t="inlineStr">
+      <c r="I51" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -2854,17 +2735,17 @@
       <c r="A52" s="7" t="n">
         <v>48</v>
       </c>
-      <c r="B52" s="12" t="inlineStr">
+      <c r="B52" s="15" t="inlineStr">
         <is>
           <t>38719</t>
         </is>
       </c>
-      <c r="C52" s="7" t="inlineStr">
+      <c r="C52" s="8" t="inlineStr">
         <is>
           <t>Plaza Fortuna</t>
         </is>
       </c>
-      <c r="D52" s="7" t="inlineStr">
+      <c r="D52" s="8" t="inlineStr">
         <is>
           <t>Veronica Garcia Ortega</t>
         </is>
@@ -2878,49 +2759,49 @@
       <c r="G52" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="H52" s="8">
+      <c r="H52" s="9">
         <f>IFERROR(E52/F52,0)</f>
         <v/>
       </c>
-      <c r="I52" s="7" t="inlineStr">
+      <c r="I52" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
       </c>
     </row>
     <row r="53" ht="21" customHeight="1">
-      <c r="A53" s="9" t="n">
+      <c r="A53" s="11" t="n">
         <v>49</v>
       </c>
-      <c r="B53" s="11" t="inlineStr">
+      <c r="B53" s="14" t="inlineStr">
         <is>
           <t>38427</t>
         </is>
       </c>
-      <c r="C53" s="9" t="inlineStr">
+      <c r="C53" s="12" t="inlineStr">
         <is>
           <t>Plaza Satelite</t>
         </is>
       </c>
-      <c r="D53" s="9" t="inlineStr">
+      <c r="D53" s="12" t="inlineStr">
         <is>
           <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
-      <c r="E53" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F53" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="G53" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="H53" s="10">
+      <c r="E53" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F53" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="G53" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="H53" s="13">
         <f>IFERROR(E53/F53,0)</f>
         <v/>
       </c>
-      <c r="I53" s="9" t="inlineStr">
+      <c r="I53" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -2930,17 +2811,17 @@
       <c r="A54" s="7" t="n">
         <v>50</v>
       </c>
-      <c r="B54" s="12" t="inlineStr">
+      <c r="B54" s="15" t="inlineStr">
         <is>
           <t>38859</t>
         </is>
       </c>
-      <c r="C54" s="7" t="inlineStr">
+      <c r="C54" s="8" t="inlineStr">
         <is>
           <t>Plaza Satelite II N1</t>
         </is>
       </c>
-      <c r="D54" s="7" t="inlineStr">
+      <c r="D54" s="8" t="inlineStr">
         <is>
           <t>Yazmin Chabela Guadarrama</t>
         </is>
@@ -2954,49 +2835,49 @@
       <c r="G54" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="H54" s="8">
+      <c r="H54" s="9">
         <f>IFERROR(E54/F54,0)</f>
         <v/>
       </c>
-      <c r="I54" s="7" t="inlineStr">
+      <c r="I54" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
       </c>
     </row>
     <row r="55" ht="21" customHeight="1">
-      <c r="A55" s="9" t="n">
+      <c r="A55" s="11" t="n">
         <v>51</v>
       </c>
-      <c r="B55" s="11" t="inlineStr">
+      <c r="B55" s="14" t="inlineStr">
         <is>
           <t>38811</t>
         </is>
       </c>
-      <c r="C55" s="9" t="inlineStr">
+      <c r="C55" s="12" t="inlineStr">
         <is>
           <t>Plaza Tepeyac</t>
         </is>
       </c>
-      <c r="D55" s="9" t="inlineStr">
+      <c r="D55" s="12" t="inlineStr">
         <is>
           <t>Veronica Garcia Ortega</t>
         </is>
       </c>
-      <c r="E55" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F55" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="G55" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="H55" s="10">
+      <c r="E55" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F55" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="G55" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="H55" s="13">
         <f>IFERROR(E55/F55,0)</f>
         <v/>
       </c>
-      <c r="I55" s="9" t="inlineStr">
+      <c r="I55" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -3006,17 +2887,17 @@
       <c r="A56" s="7" t="n">
         <v>52</v>
       </c>
-      <c r="B56" s="12" t="inlineStr">
+      <c r="B56" s="15" t="inlineStr">
         <is>
           <t>43132</t>
         </is>
       </c>
-      <c r="C56" s="7" t="inlineStr">
+      <c r="C56" s="8" t="inlineStr">
         <is>
           <t>Plaza Vista Norte</t>
         </is>
       </c>
-      <c r="D56" s="7" t="inlineStr">
+      <c r="D56" s="8" t="inlineStr">
         <is>
           <t>Vanessa Carreño Rios</t>
         </is>
@@ -3030,49 +2911,49 @@
       <c r="G56" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="H56" s="8">
+      <c r="H56" s="9">
         <f>IFERROR(E56/F56,0)</f>
         <v/>
       </c>
-      <c r="I56" s="7" t="inlineStr">
+      <c r="I56" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
       </c>
     </row>
     <row r="57" ht="21" customHeight="1">
-      <c r="A57" s="9" t="n">
+      <c r="A57" s="11" t="n">
         <v>53</v>
       </c>
-      <c r="B57" s="11" t="inlineStr">
+      <c r="B57" s="14" t="inlineStr">
         <is>
           <t>38136</t>
         </is>
       </c>
-      <c r="C57" s="9" t="inlineStr">
+      <c r="C57" s="12" t="inlineStr">
         <is>
           <t>Punta Norte</t>
         </is>
       </c>
-      <c r="D57" s="9" t="inlineStr">
+      <c r="D57" s="12" t="inlineStr">
         <is>
           <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
-      <c r="E57" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F57" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="G57" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="H57" s="10">
+      <c r="E57" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F57" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="G57" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="H57" s="13">
         <f>IFERROR(E57/F57,0)</f>
         <v/>
       </c>
-      <c r="I57" s="9" t="inlineStr">
+      <c r="I57" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -3082,17 +2963,17 @@
       <c r="A58" s="7" t="n">
         <v>54</v>
       </c>
-      <c r="B58" s="12" t="inlineStr">
+      <c r="B58" s="15" t="inlineStr">
         <is>
           <t>43152</t>
         </is>
       </c>
-      <c r="C58" s="7" t="inlineStr">
+      <c r="C58" s="8" t="inlineStr">
         <is>
           <t>Samara Satélite</t>
         </is>
       </c>
-      <c r="D58" s="7" t="inlineStr">
+      <c r="D58" s="8" t="inlineStr">
         <is>
           <t>Yazmin Chabela Guadarrama</t>
         </is>
@@ -3106,49 +2987,49 @@
       <c r="G58" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="H58" s="8">
+      <c r="H58" s="9">
         <f>IFERROR(E58/F58,0)</f>
         <v/>
       </c>
-      <c r="I58" s="7" t="inlineStr">
+      <c r="I58" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
       </c>
     </row>
     <row r="59" ht="21" customHeight="1">
-      <c r="A59" s="9" t="n">
+      <c r="A59" s="11" t="n">
         <v>55</v>
       </c>
-      <c r="B59" s="11" t="inlineStr">
+      <c r="B59" s="14" t="inlineStr">
         <is>
           <t>38339</t>
         </is>
       </c>
-      <c r="C59" s="9" t="inlineStr">
+      <c r="C59" s="12" t="inlineStr">
         <is>
           <t>San Marcos</t>
         </is>
       </c>
-      <c r="D59" s="9" t="inlineStr">
+      <c r="D59" s="12" t="inlineStr">
         <is>
           <t>Enrique Cesar Flores</t>
         </is>
       </c>
-      <c r="E59" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F59" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="G59" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="H59" s="10">
+      <c r="E59" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F59" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="G59" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="H59" s="13">
         <f>IFERROR(E59/F59,0)</f>
         <v/>
       </c>
-      <c r="I59" s="9" t="inlineStr">
+      <c r="I59" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -3158,17 +3039,17 @@
       <c r="A60" s="7" t="n">
         <v>56</v>
       </c>
-      <c r="B60" s="12" t="inlineStr">
+      <c r="B60" s="15" t="inlineStr">
         <is>
           <t>38266</t>
         </is>
       </c>
-      <c r="C60" s="7" t="inlineStr">
+      <c r="C60" s="8" t="inlineStr">
         <is>
           <t>San Mateo</t>
         </is>
       </c>
-      <c r="D60" s="7" t="inlineStr">
+      <c r="D60" s="8" t="inlineStr">
         <is>
           <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
@@ -3182,49 +3063,49 @@
       <c r="G60" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="H60" s="8">
+      <c r="H60" s="9">
         <f>IFERROR(E60/F60,0)</f>
         <v/>
       </c>
-      <c r="I60" s="7" t="inlineStr">
+      <c r="I60" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
       </c>
     </row>
     <row r="61" ht="21" customHeight="1">
-      <c r="A61" s="9" t="n">
+      <c r="A61" s="11" t="n">
         <v>57</v>
       </c>
-      <c r="B61" s="11" t="inlineStr">
+      <c r="B61" s="14" t="inlineStr">
         <is>
           <t>38862</t>
         </is>
       </c>
-      <c r="C61" s="9" t="inlineStr">
+      <c r="C61" s="12" t="inlineStr">
         <is>
           <t>San Miguel Izcalli</t>
         </is>
       </c>
-      <c r="D61" s="9" t="inlineStr">
+      <c r="D61" s="12" t="inlineStr">
         <is>
           <t>Enrique Cesar Flores</t>
         </is>
       </c>
-      <c r="E61" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F61" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="G61" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="H61" s="10">
+      <c r="E61" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F61" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="G61" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="H61" s="13">
         <f>IFERROR(E61/F61,0)</f>
         <v/>
       </c>
-      <c r="I61" s="9" t="inlineStr">
+      <c r="I61" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -3234,17 +3115,17 @@
       <c r="A62" s="7" t="n">
         <v>58</v>
       </c>
-      <c r="B62" s="12" t="inlineStr">
+      <c r="B62" s="15" t="inlineStr">
         <is>
           <t>38460</t>
         </is>
       </c>
-      <c r="C62" s="7" t="inlineStr">
+      <c r="C62" s="8" t="inlineStr">
         <is>
           <t>Santa Monica</t>
         </is>
       </c>
-      <c r="D62" s="7" t="inlineStr">
+      <c r="D62" s="8" t="inlineStr">
         <is>
           <t>Nancy Carolina Rodriguez Medina</t>
         </is>
@@ -3258,49 +3139,49 @@
       <c r="G62" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="H62" s="8">
+      <c r="H62" s="9">
         <f>IFERROR(E62/F62,0)</f>
         <v/>
       </c>
-      <c r="I62" s="7" t="inlineStr">
+      <c r="I62" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
       </c>
     </row>
     <row r="63" ht="21" customHeight="1">
-      <c r="A63" s="9" t="n">
+      <c r="A63" s="11" t="n">
         <v>59</v>
       </c>
-      <c r="B63" s="11" t="inlineStr">
+      <c r="B63" s="14" t="inlineStr">
         <is>
           <t>38117</t>
         </is>
       </c>
-      <c r="C63" s="9" t="inlineStr">
+      <c r="C63" s="12" t="inlineStr">
         <is>
           <t>Satelite</t>
         </is>
       </c>
-      <c r="D63" s="9" t="inlineStr">
+      <c r="D63" s="12" t="inlineStr">
         <is>
           <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
-      <c r="E63" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F63" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="G63" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="H63" s="10">
+      <c r="E63" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F63" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="G63" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="H63" s="13">
         <f>IFERROR(E63/F63,0)</f>
         <v/>
       </c>
-      <c r="I63" s="9" t="inlineStr">
+      <c r="I63" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -3310,17 +3191,17 @@
       <c r="A64" s="7" t="n">
         <v>60</v>
       </c>
-      <c r="B64" s="12" t="inlineStr">
+      <c r="B64" s="15" t="inlineStr">
         <is>
           <t>38475</t>
         </is>
       </c>
-      <c r="C64" s="7" t="inlineStr">
+      <c r="C64" s="8" t="inlineStr">
         <is>
           <t>Satelite Centro Civico</t>
         </is>
       </c>
-      <c r="D64" s="7" t="inlineStr">
+      <c r="D64" s="8" t="inlineStr">
         <is>
           <t>Yazmin Chabela Guadarrama</t>
         </is>
@@ -3334,49 +3215,49 @@
       <c r="G64" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="H64" s="8">
+      <c r="H64" s="9">
         <f>IFERROR(E64/F64,0)</f>
         <v/>
       </c>
-      <c r="I64" s="7" t="inlineStr">
+      <c r="I64" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
       </c>
     </row>
     <row r="65" ht="21" customHeight="1">
-      <c r="A65" s="9" t="n">
+      <c r="A65" s="11" t="n">
         <v>61</v>
       </c>
-      <c r="B65" s="11" t="inlineStr">
+      <c r="B65" s="14" t="inlineStr">
         <is>
           <t>38442</t>
         </is>
       </c>
-      <c r="C65" s="9" t="inlineStr">
+      <c r="C65" s="12" t="inlineStr">
         <is>
           <t>Sor Juana</t>
         </is>
       </c>
-      <c r="D65" s="9" t="inlineStr">
+      <c r="D65" s="12" t="inlineStr">
         <is>
           <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
-      <c r="E65" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F65" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="G65" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="H65" s="10">
+      <c r="E65" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F65" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="G65" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="H65" s="13">
         <f>IFERROR(E65/F65,0)</f>
         <v/>
       </c>
-      <c r="I65" s="9" t="inlineStr">
+      <c r="I65" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -3386,17 +3267,17 @@
       <c r="A66" s="7" t="n">
         <v>62</v>
       </c>
-      <c r="B66" s="12" t="inlineStr">
+      <c r="B66" s="15" t="inlineStr">
         <is>
           <t>38925</t>
         </is>
       </c>
-      <c r="C66" s="7" t="inlineStr">
+      <c r="C66" s="8" t="inlineStr">
         <is>
           <t>Star Medica Lomas Verdes</t>
         </is>
       </c>
-      <c r="D66" s="7" t="inlineStr">
+      <c r="D66" s="8" t="inlineStr">
         <is>
           <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
@@ -3410,49 +3291,49 @@
       <c r="G66" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="H66" s="8">
+      <c r="H66" s="9">
         <f>IFERROR(E66/F66,0)</f>
         <v/>
       </c>
-      <c r="I66" s="7" t="inlineStr">
+      <c r="I66" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
       </c>
     </row>
     <row r="67" ht="21" customHeight="1">
-      <c r="A67" s="9" t="n">
+      <c r="A67" s="11" t="n">
         <v>63</v>
       </c>
-      <c r="B67" s="11" t="inlineStr">
+      <c r="B67" s="14" t="inlineStr">
         <is>
           <t>38992</t>
         </is>
       </c>
-      <c r="C67" s="9" t="inlineStr">
+      <c r="C67" s="12" t="inlineStr">
         <is>
           <t>Tapo Puerta Oriente</t>
         </is>
       </c>
-      <c r="D67" s="9" t="inlineStr">
+      <c r="D67" s="12" t="inlineStr">
         <is>
           <t>Veronica Garcia Ortega</t>
         </is>
       </c>
-      <c r="E67" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F67" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="G67" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="H67" s="10">
+      <c r="E67" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F67" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="G67" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="H67" s="13">
         <f>IFERROR(E67/F67,0)</f>
         <v/>
       </c>
-      <c r="I67" s="9" t="inlineStr">
+      <c r="I67" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -3462,17 +3343,17 @@
       <c r="A68" s="7" t="n">
         <v>64</v>
       </c>
-      <c r="B68" s="12" t="inlineStr">
+      <c r="B68" s="15" t="inlineStr">
         <is>
           <t>38606</t>
         </is>
       </c>
-      <c r="C68" s="7" t="inlineStr">
+      <c r="C68" s="8" t="inlineStr">
         <is>
           <t>TlalnepantlaCarso</t>
         </is>
       </c>
-      <c r="D68" s="7" t="inlineStr">
+      <c r="D68" s="8" t="inlineStr">
         <is>
           <t>Nancy Carolina Rodriguez Medina</t>
         </is>
@@ -3486,49 +3367,49 @@
       <c r="G68" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="H68" s="8">
+      <c r="H68" s="9">
         <f>IFERROR(E68/F68,0)</f>
         <v/>
       </c>
-      <c r="I68" s="7" t="inlineStr">
+      <c r="I68" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
       </c>
     </row>
     <row r="69" ht="21" customHeight="1">
-      <c r="A69" s="9" t="n">
+      <c r="A69" s="11" t="n">
         <v>65</v>
       </c>
-      <c r="B69" s="11" t="inlineStr">
+      <c r="B69" s="14" t="inlineStr">
         <is>
           <t>38411</t>
         </is>
       </c>
-      <c r="C69" s="9" t="inlineStr">
+      <c r="C69" s="12" t="inlineStr">
         <is>
           <t>Torres Lindavista</t>
         </is>
       </c>
-      <c r="D69" s="9" t="inlineStr">
+      <c r="D69" s="12" t="inlineStr">
         <is>
           <t>Vanessa Carreño Rios</t>
         </is>
       </c>
-      <c r="E69" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F69" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="G69" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="H69" s="10">
+      <c r="E69" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F69" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="G69" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="H69" s="13">
         <f>IFERROR(E69/F69,0)</f>
         <v/>
       </c>
-      <c r="I69" s="9" t="inlineStr">
+      <c r="I69" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -3538,17 +3419,17 @@
       <c r="A70" s="7" t="n">
         <v>66</v>
       </c>
-      <c r="B70" s="12" t="inlineStr">
+      <c r="B70" s="15" t="inlineStr">
         <is>
           <t>43130</t>
         </is>
       </c>
-      <c r="C70" s="7" t="inlineStr">
+      <c r="C70" s="8" t="inlineStr">
         <is>
           <t>Town Center Nicolás Romero</t>
         </is>
       </c>
-      <c r="D70" s="7" t="inlineStr">
+      <c r="D70" s="8" t="inlineStr">
         <is>
           <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
@@ -3562,49 +3443,49 @@
       <c r="G70" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="H70" s="8">
+      <c r="H70" s="9">
         <f>IFERROR(E70/F70,0)</f>
         <v/>
       </c>
-      <c r="I70" s="7" t="inlineStr">
+      <c r="I70" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
       </c>
     </row>
     <row r="71" ht="21" customHeight="1">
-      <c r="A71" s="9" t="n">
+      <c r="A71" s="11" t="n">
         <v>67</v>
       </c>
-      <c r="B71" s="11" t="inlineStr">
+      <c r="B71" s="14" t="inlineStr">
         <is>
           <t>38374</t>
         </is>
       </c>
-      <c r="C71" s="9" t="inlineStr">
+      <c r="C71" s="12" t="inlineStr">
         <is>
           <t>Valle Dorado</t>
         </is>
       </c>
-      <c r="D71" s="9" t="inlineStr">
+      <c r="D71" s="12" t="inlineStr">
         <is>
           <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
-      <c r="E71" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F71" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="G71" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="H71" s="10">
+      <c r="E71" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F71" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="G71" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="H71" s="13">
         <f>IFERROR(E71/F71,0)</f>
         <v/>
       </c>
-      <c r="I71" s="9" t="inlineStr">
+      <c r="I71" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -3614,17 +3495,17 @@
       <c r="A72" s="7" t="n">
         <v>68</v>
       </c>
-      <c r="B72" s="12" t="inlineStr">
+      <c r="B72" s="15" t="inlineStr">
         <is>
           <t>38651</t>
         </is>
       </c>
-      <c r="C72" s="7" t="inlineStr">
+      <c r="C72" s="8" t="inlineStr">
         <is>
           <t>Via Vallejo</t>
         </is>
       </c>
-      <c r="D72" s="7" t="inlineStr">
+      <c r="D72" s="8" t="inlineStr">
         <is>
           <t>Vanessa Carreño Rios</t>
         </is>
@@ -3638,49 +3519,49 @@
       <c r="G72" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="H72" s="8">
+      <c r="H72" s="9">
         <f>IFERROR(E72/F72,0)</f>
         <v/>
       </c>
-      <c r="I72" s="7" t="inlineStr">
+      <c r="I72" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
       </c>
     </row>
     <row r="73" ht="21" customHeight="1">
-      <c r="A73" s="9" t="n">
+      <c r="A73" s="11" t="n">
         <v>69</v>
       </c>
-      <c r="B73" s="11" t="inlineStr">
+      <c r="B73" s="14" t="inlineStr">
         <is>
           <t>38694</t>
         </is>
       </c>
-      <c r="C73" s="9" t="inlineStr">
+      <c r="C73" s="12" t="inlineStr">
         <is>
           <t>Villas de la Hacienda</t>
         </is>
       </c>
-      <c r="D73" s="9" t="inlineStr">
+      <c r="D73" s="12" t="inlineStr">
         <is>
           <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
-      <c r="E73" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F73" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="G73" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="H73" s="10">
+      <c r="E73" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F73" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="G73" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="H73" s="13">
         <f>IFERROR(E73/F73,0)</f>
         <v/>
       </c>
-      <c r="I73" s="9" t="inlineStr">
+      <c r="I73" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -3690,17 +3571,17 @@
       <c r="A74" s="7" t="n">
         <v>70</v>
       </c>
-      <c r="B74" s="12" t="inlineStr">
+      <c r="B74" s="15" t="inlineStr">
         <is>
           <t>38656</t>
         </is>
       </c>
-      <c r="C74" s="7" t="inlineStr">
+      <c r="C74" s="8" t="inlineStr">
         <is>
           <t>Viveros de la Loma</t>
         </is>
       </c>
-      <c r="D74" s="7" t="inlineStr">
+      <c r="D74" s="8" t="inlineStr">
         <is>
           <t>Yazmin Chabela Guadarrama</t>
         </is>
@@ -3714,49 +3595,49 @@
       <c r="G74" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="H74" s="8">
+      <c r="H74" s="9">
         <f>IFERROR(E74/F74,0)</f>
         <v/>
       </c>
-      <c r="I74" s="7" t="inlineStr">
+      <c r="I74" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
       </c>
     </row>
     <row r="75" ht="21" customHeight="1">
-      <c r="A75" s="9" t="n">
+      <c r="A75" s="11" t="n">
         <v>71</v>
       </c>
-      <c r="B75" s="11" t="inlineStr">
+      <c r="B75" s="14" t="inlineStr">
         <is>
           <t>38115</t>
         </is>
       </c>
-      <c r="C75" s="9" t="inlineStr">
+      <c r="C75" s="12" t="inlineStr">
         <is>
           <t>Zona Azul</t>
         </is>
       </c>
-      <c r="D75" s="9" t="inlineStr">
+      <c r="D75" s="12" t="inlineStr">
         <is>
           <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
-      <c r="E75" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F75" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="G75" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="H75" s="10">
+      <c r="E75" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F75" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="G75" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="H75" s="13">
         <f>IFERROR(E75/F75,0)</f>
         <v/>
       </c>
-      <c r="I75" s="9" t="inlineStr">
+      <c r="I75" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -3766,17 +3647,17 @@
       <c r="A76" s="7" t="n">
         <v>72</v>
       </c>
-      <c r="B76" s="12" t="inlineStr">
+      <c r="B76" s="15" t="inlineStr">
         <is>
           <t>38142</t>
         </is>
       </c>
-      <c r="C76" s="7" t="inlineStr">
+      <c r="C76" s="8" t="inlineStr">
         <is>
           <t>Zona Esmeralda</t>
         </is>
       </c>
-      <c r="D76" s="7" t="inlineStr">
+      <c r="D76" s="8" t="inlineStr">
         <is>
           <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
@@ -3790,11 +3671,11 @@
       <c r="G76" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="H76" s="8">
+      <c r="H76" s="9">
         <f>IFERROR(E76/F76,0)</f>
         <v/>
       </c>
-      <c r="I76" s="7" t="inlineStr">
+      <c r="I76" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -3823,6 +3704,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="0016845B"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -3891,28 +3773,28 @@
       </c>
     </row>
     <row r="5" ht="21" customHeight="1">
-      <c r="A5" s="9" t="n">
+      <c r="A5" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B5" s="12" t="inlineStr">
         <is>
           <t>Roll Out</t>
         </is>
       </c>
-      <c r="C5" s="9" t="n">
+      <c r="C5" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="D5" s="9" t="n">
+      <c r="D5" s="11" t="n">
         <v>71</v>
       </c>
-      <c r="E5" s="9" t="n">
+      <c r="E5" s="11" t="n">
         <v>72</v>
       </c>
-      <c r="F5" s="10">
+      <c r="F5" s="13">
         <f>IFERROR(C5/E5,0)</f>
         <v/>
       </c>
-      <c r="G5" s="9" t="inlineStr">
+      <c r="G5" s="12" t="inlineStr">
         <is>
           <t>03/09/26</t>
         </is>
@@ -3922,7 +3804,7 @@
       <c r="A6" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>Programacion Hornos Merry - Focaccia</t>
         </is>
@@ -3936,39 +3818,39 @@
       <c r="E6" s="7" t="n">
         <v>72</v>
       </c>
-      <c r="F6" s="8">
+      <c r="F6" s="9">
         <f>IFERROR(C6/E6,0)</f>
         <v/>
       </c>
-      <c r="G6" s="7" t="inlineStr">
+      <c r="G6" s="8" t="inlineStr">
         <is>
           <t>03/09/26</t>
         </is>
       </c>
     </row>
     <row r="7" ht="21" customHeight="1">
-      <c r="A7" s="9" t="n">
+      <c r="A7" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="12" t="inlineStr">
         <is>
           <t>Rack FHW</t>
         </is>
       </c>
-      <c r="C7" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="9" t="n">
+      <c r="C7" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="11" t="n">
         <v>72</v>
       </c>
-      <c r="E7" s="9" t="n">
+      <c r="E7" s="11" t="n">
         <v>72</v>
       </c>
-      <c r="F7" s="10">
+      <c r="F7" s="13">
         <f>IFERROR(C7/E7,0)</f>
         <v/>
       </c>
-      <c r="G7" s="9" t="inlineStr">
+      <c r="G7" s="12" t="inlineStr">
         <is>
           <t>06/09/26</t>
         </is>
@@ -3978,7 +3860,7 @@
       <c r="A8" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>QR - Qualtrics</t>
         </is>
@@ -3992,39 +3874,39 @@
       <c r="E8" s="7" t="n">
         <v>72</v>
       </c>
-      <c r="F8" s="8">
+      <c r="F8" s="9">
         <f>IFERROR(C8/E8,0)</f>
         <v/>
       </c>
-      <c r="G8" s="7" t="inlineStr">
+      <c r="G8" s="8" t="inlineStr">
         <is>
           <t>03/09/26</t>
         </is>
       </c>
     </row>
     <row r="9" ht="21" customHeight="1">
-      <c r="A9" s="9" t="n">
+      <c r="A9" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="9" t="inlineStr">
+      <c r="B9" s="12" t="inlineStr">
         <is>
           <t>Max &amp; Min</t>
         </is>
       </c>
-      <c r="C9" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="9" t="n">
+      <c r="C9" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="11" t="n">
         <v>72</v>
       </c>
-      <c r="E9" s="9" t="n">
+      <c r="E9" s="11" t="n">
         <v>72</v>
       </c>
-      <c r="F9" s="10">
+      <c r="F9" s="13">
         <f>IFERROR(C9/E9,0)</f>
         <v/>
       </c>
-      <c r="G9" s="9" t="inlineStr">
+      <c r="G9" s="12" t="inlineStr">
         <is>
           <t>06/09/26</t>
         </is>
@@ -4034,7 +3916,7 @@
       <c r="A10" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>Fotografia - SM</t>
         </is>
@@ -4048,39 +3930,39 @@
       <c r="E10" s="7" t="n">
         <v>72</v>
       </c>
-      <c r="F10" s="8">
+      <c r="F10" s="9">
         <f>IFERROR(C10/E10,0)</f>
         <v/>
       </c>
-      <c r="G10" s="7" t="inlineStr">
+      <c r="G10" s="8" t="inlineStr">
         <is>
           <t>06/09/26</t>
         </is>
       </c>
     </row>
     <row r="11" ht="21" customHeight="1">
-      <c r="A11" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="B11" s="9" t="inlineStr">
+      <c r="A11" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="12" t="inlineStr">
         <is>
           <t>Mandil Verde</t>
         </is>
       </c>
-      <c r="C11" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" s="9" t="n">
+      <c r="C11" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="11" t="n">
         <v>72</v>
       </c>
-      <c r="E11" s="9" t="n">
+      <c r="E11" s="11" t="n">
         <v>72</v>
       </c>
-      <c r="F11" s="10">
+      <c r="F11" s="13">
         <f>IFERROR(C11/E11,0)</f>
         <v/>
       </c>
-      <c r="G11" s="9" t="inlineStr">
+      <c r="G11" s="12" t="inlineStr">
         <is>
           <t>13/09/26</t>
         </is>

--- a/exports/Resumen_Evidencias_OPS.xlsx
+++ b/exports/Resumen_Evidencias_OPS.xlsx
@@ -130,10 +130,10 @@
   <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -564,7 +564,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Resumen ejecutivo · Región Centro Norte · Corte 28/08/2026 20:39</t>
+          <t>Centro Norte · Corte 28/08/2026 20:39</t>
         </is>
       </c>
     </row>
@@ -581,12 +581,7 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>% Avance</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>Pendientes</t>
+          <t>% Pendiente</t>
         </is>
       </c>
     </row>
@@ -598,11 +593,8 @@
         <v>504</v>
       </c>
       <c r="E6" s="5">
-        <f>IFERROR(SUM(D10:D15)/SUM(E10:E15),0)</f>
-        <v/>
-      </c>
-      <c r="G6" s="4" t="n">
-        <v>502</v>
+        <f>IFERROR((C6-A6)/C6,0)</f>
+        <v/>
       </c>
     </row>
     <row r="7"/>
@@ -836,17 +828,15 @@
     </row>
   </sheetData>
   <autoFilter ref="A9:H15"/>
-  <mergeCells count="10">
+  <mergeCells count="8">
     <mergeCell ref="A3:H3"/>
-    <mergeCell ref="E6:F7"/>
     <mergeCell ref="C6:D7"/>
-    <mergeCell ref="G6:H7"/>
     <mergeCell ref="C5:D5"/>
     <mergeCell ref="A5:B5"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="E5:F5"/>
     <mergeCell ref="A6:B7"/>
+    <mergeCell ref="E6:H7"/>
     <mergeCell ref="A1:H2"/>
+    <mergeCell ref="E5:H5"/>
   </mergeCells>
   <conditionalFormatting sqref="G10:G15">
     <cfRule type="dataBar" priority="1">
@@ -886,7 +876,7 @@
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Detalle de tiendas</t>
+          <t>Avance por tienda</t>
         </is>
       </c>
     </row>
@@ -894,7 +884,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Ordenado de mayor a menor avance · Región Centro Norte · Corte 28/08/2026 20:39</t>
+          <t>Centro Norte · Corte 28/08/2026 20:39</t>
         </is>
       </c>
     </row>
@@ -3731,7 +3721,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Lectura operativa · Región Centro Norte · Corte 28/08/2026 20:39</t>
+          <t>Centro Norte · Corte 28/08/2026 20:39</t>
         </is>
       </c>
     </row>

--- a/exports/Resumen_Evidencias_OPS.xlsx
+++ b/exports/Resumen_Evidencias_OPS.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tiendas" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Actividades" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Resumen" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Tiendas" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Actividades" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Resumen'!$A$9:$H$15</definedName>

--- a/exports/Resumen_Evidencias_OPS.xlsx
+++ b/exports/Resumen_Evidencias_OPS.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Resumen" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Tiendas" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Actividades" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tiendas" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Actividades" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Resumen'!$A$9:$H$15</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Resumen'!$A$1:$H$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Tiendas'!$A$4:$I$76</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Resumen'!$A$9:$G$15</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Resumen'!$A$1:$G$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Tiendas'!$A$4:$H$76</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Tiendas'!$1:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Actividades'!$A$4:$G$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Actividades'!$A$4:$F$11</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -540,7 +540,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -549,8 +549,7 @@
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -581,7 +580,7 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>% Pendiente</t>
+          <t>% Avance</t>
         </is>
       </c>
     </row>
@@ -593,7 +592,7 @@
         <v>504</v>
       </c>
       <c r="E6" s="5">
-        <f>IFERROR((C6-A6)/C6,0)</f>
+        <f>IFERROR(A6/C6,0)</f>
         <v/>
       </c>
     </row>
@@ -626,15 +625,10 @@
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>Pendientes</t>
+          <t>% Avance</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
-        <is>
-          <t>% Avance</t>
-        </is>
-      </c>
-      <c r="H9" s="6" t="inlineStr">
         <is>
           <t>Estado</t>
         </is>
@@ -658,14 +652,11 @@
       <c r="E10" s="7" t="n">
         <v>70</v>
       </c>
-      <c r="F10" s="7" t="n">
-        <v>68</v>
-      </c>
-      <c r="G10" s="9">
+      <c r="F10" s="9">
         <f>IFERROR(D10/E10,0)</f>
         <v/>
       </c>
-      <c r="H10" s="10" t="inlineStr">
+      <c r="G10" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -689,14 +680,11 @@
       <c r="E11" s="11" t="n">
         <v>84</v>
       </c>
-      <c r="F11" s="11" t="n">
-        <v>84</v>
-      </c>
-      <c r="G11" s="13">
+      <c r="F11" s="13">
         <f>IFERROR(D11/E11,0)</f>
         <v/>
       </c>
-      <c r="H11" s="10" t="inlineStr">
+      <c r="G11" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -720,14 +708,11 @@
       <c r="E12" s="7" t="n">
         <v>91</v>
       </c>
-      <c r="F12" s="7" t="n">
-        <v>91</v>
-      </c>
-      <c r="G12" s="9">
+      <c r="F12" s="9">
         <f>IFERROR(D12/E12,0)</f>
         <v/>
       </c>
-      <c r="H12" s="10" t="inlineStr">
+      <c r="G12" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -751,14 +736,11 @@
       <c r="E13" s="11" t="n">
         <v>77</v>
       </c>
-      <c r="F13" s="11" t="n">
-        <v>77</v>
-      </c>
-      <c r="G13" s="13">
+      <c r="F13" s="13">
         <f>IFERROR(D13/E13,0)</f>
         <v/>
       </c>
-      <c r="H13" s="10" t="inlineStr">
+      <c r="G13" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -782,14 +764,11 @@
       <c r="E14" s="7" t="n">
         <v>91</v>
       </c>
-      <c r="F14" s="7" t="n">
-        <v>91</v>
-      </c>
-      <c r="G14" s="9">
+      <c r="F14" s="9">
         <f>IFERROR(D14/E14,0)</f>
         <v/>
       </c>
-      <c r="H14" s="10" t="inlineStr">
+      <c r="G14" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -813,32 +792,29 @@
       <c r="E15" s="11" t="n">
         <v>91</v>
       </c>
-      <c r="F15" s="11" t="n">
-        <v>91</v>
-      </c>
-      <c r="G15" s="13">
+      <c r="F15" s="13">
         <f>IFERROR(D15/E15,0)</f>
         <v/>
       </c>
-      <c r="H15" s="10" t="inlineStr">
+      <c r="G15" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A9:H15"/>
+  <autoFilter ref="A9:G15"/>
   <mergeCells count="8">
-    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="E6:G7"/>
+    <mergeCell ref="A1:G2"/>
     <mergeCell ref="C6:D7"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="E5:G5"/>
     <mergeCell ref="C5:D5"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="A6:B7"/>
-    <mergeCell ref="E6:H7"/>
-    <mergeCell ref="A1:H2"/>
-    <mergeCell ref="E5:H5"/>
   </mergeCells>
-  <conditionalFormatting sqref="G10:G15">
+  <conditionalFormatting sqref="F10:F15">
     <cfRule type="dataBar" priority="1">
       <dataBar showValue="1">
         <cfvo type="num" val="0"/>
@@ -859,7 +835,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I76"/>
+  <dimension ref="A1:H76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -869,8 +845,7 @@
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -921,15 +896,10 @@
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>Pendientes</t>
+          <t>% Avance</t>
         </is>
       </c>
       <c r="H4" s="6" t="inlineStr">
-        <is>
-          <t>% Avance</t>
-        </is>
-      </c>
-      <c r="I4" s="6" t="inlineStr">
         <is>
           <t>Estado</t>
         </is>
@@ -960,14 +930,11 @@
       <c r="F5" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="G5" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="H5" s="13">
+      <c r="G5" s="13">
         <f>IFERROR(E5/F5,0)</f>
         <v/>
       </c>
-      <c r="I5" s="10" t="inlineStr">
+      <c r="H5" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -998,14 +965,11 @@
       <c r="F6" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="G6" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="H6" s="9">
+      <c r="G6" s="9">
         <f>IFERROR(E6/F6,0)</f>
         <v/>
       </c>
-      <c r="I6" s="10" t="inlineStr">
+      <c r="H6" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -1036,14 +1000,11 @@
       <c r="F7" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="G7" s="11" t="n">
-        <v>7</v>
-      </c>
-      <c r="H7" s="13">
+      <c r="G7" s="13">
         <f>IFERROR(E7/F7,0)</f>
         <v/>
       </c>
-      <c r="I7" s="10" t="inlineStr">
+      <c r="H7" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -1074,14 +1035,11 @@
       <c r="F8" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="G8" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="H8" s="9">
+      <c r="G8" s="9">
         <f>IFERROR(E8/F8,0)</f>
         <v/>
       </c>
-      <c r="I8" s="10" t="inlineStr">
+      <c r="H8" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -1112,14 +1070,11 @@
       <c r="F9" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="G9" s="11" t="n">
-        <v>7</v>
-      </c>
-      <c r="H9" s="13">
+      <c r="G9" s="13">
         <f>IFERROR(E9/F9,0)</f>
         <v/>
       </c>
-      <c r="I9" s="10" t="inlineStr">
+      <c r="H9" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -1150,14 +1105,11 @@
       <c r="F10" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="G10" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="H10" s="9">
+      <c r="G10" s="9">
         <f>IFERROR(E10/F10,0)</f>
         <v/>
       </c>
-      <c r="I10" s="10" t="inlineStr">
+      <c r="H10" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -1188,14 +1140,11 @@
       <c r="F11" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="G11" s="11" t="n">
-        <v>7</v>
-      </c>
-      <c r="H11" s="13">
+      <c r="G11" s="13">
         <f>IFERROR(E11/F11,0)</f>
         <v/>
       </c>
-      <c r="I11" s="10" t="inlineStr">
+      <c r="H11" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -1226,14 +1175,11 @@
       <c r="F12" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="G12" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="H12" s="9">
+      <c r="G12" s="9">
         <f>IFERROR(E12/F12,0)</f>
         <v/>
       </c>
-      <c r="I12" s="10" t="inlineStr">
+      <c r="H12" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -1264,14 +1210,11 @@
       <c r="F13" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="G13" s="11" t="n">
-        <v>7</v>
-      </c>
-      <c r="H13" s="13">
+      <c r="G13" s="13">
         <f>IFERROR(E13/F13,0)</f>
         <v/>
       </c>
-      <c r="I13" s="10" t="inlineStr">
+      <c r="H13" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -1302,14 +1245,11 @@
       <c r="F14" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="G14" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="H14" s="9">
+      <c r="G14" s="9">
         <f>IFERROR(E14/F14,0)</f>
         <v/>
       </c>
-      <c r="I14" s="10" t="inlineStr">
+      <c r="H14" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -1340,14 +1280,11 @@
       <c r="F15" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="G15" s="11" t="n">
-        <v>7</v>
-      </c>
-      <c r="H15" s="13">
+      <c r="G15" s="13">
         <f>IFERROR(E15/F15,0)</f>
         <v/>
       </c>
-      <c r="I15" s="10" t="inlineStr">
+      <c r="H15" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -1378,14 +1315,11 @@
       <c r="F16" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="G16" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="H16" s="9">
+      <c r="G16" s="9">
         <f>IFERROR(E16/F16,0)</f>
         <v/>
       </c>
-      <c r="I16" s="10" t="inlineStr">
+      <c r="H16" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -1416,14 +1350,11 @@
       <c r="F17" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="G17" s="11" t="n">
-        <v>7</v>
-      </c>
-      <c r="H17" s="13">
+      <c r="G17" s="13">
         <f>IFERROR(E17/F17,0)</f>
         <v/>
       </c>
-      <c r="I17" s="10" t="inlineStr">
+      <c r="H17" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -1454,14 +1385,11 @@
       <c r="F18" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="G18" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="H18" s="9">
+      <c r="G18" s="9">
         <f>IFERROR(E18/F18,0)</f>
         <v/>
       </c>
-      <c r="I18" s="10" t="inlineStr">
+      <c r="H18" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -1492,14 +1420,11 @@
       <c r="F19" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="G19" s="11" t="n">
-        <v>7</v>
-      </c>
-      <c r="H19" s="13">
+      <c r="G19" s="13">
         <f>IFERROR(E19/F19,0)</f>
         <v/>
       </c>
-      <c r="I19" s="10" t="inlineStr">
+      <c r="H19" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -1530,14 +1455,11 @@
       <c r="F20" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="G20" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="H20" s="9">
+      <c r="G20" s="9">
         <f>IFERROR(E20/F20,0)</f>
         <v/>
       </c>
-      <c r="I20" s="10" t="inlineStr">
+      <c r="H20" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -1568,14 +1490,11 @@
       <c r="F21" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="G21" s="11" t="n">
-        <v>7</v>
-      </c>
-      <c r="H21" s="13">
+      <c r="G21" s="13">
         <f>IFERROR(E21/F21,0)</f>
         <v/>
       </c>
-      <c r="I21" s="10" t="inlineStr">
+      <c r="H21" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -1606,14 +1525,11 @@
       <c r="F22" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="G22" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="H22" s="9">
+      <c r="G22" s="9">
         <f>IFERROR(E22/F22,0)</f>
         <v/>
       </c>
-      <c r="I22" s="10" t="inlineStr">
+      <c r="H22" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -1644,14 +1560,11 @@
       <c r="F23" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="G23" s="11" t="n">
-        <v>7</v>
-      </c>
-      <c r="H23" s="13">
+      <c r="G23" s="13">
         <f>IFERROR(E23/F23,0)</f>
         <v/>
       </c>
-      <c r="I23" s="10" t="inlineStr">
+      <c r="H23" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -1682,14 +1595,11 @@
       <c r="F24" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="G24" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="H24" s="9">
+      <c r="G24" s="9">
         <f>IFERROR(E24/F24,0)</f>
         <v/>
       </c>
-      <c r="I24" s="10" t="inlineStr">
+      <c r="H24" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -1720,14 +1630,11 @@
       <c r="F25" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="G25" s="11" t="n">
-        <v>7</v>
-      </c>
-      <c r="H25" s="13">
+      <c r="G25" s="13">
         <f>IFERROR(E25/F25,0)</f>
         <v/>
       </c>
-      <c r="I25" s="10" t="inlineStr">
+      <c r="H25" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -1758,14 +1665,11 @@
       <c r="F26" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="G26" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="H26" s="9">
+      <c r="G26" s="9">
         <f>IFERROR(E26/F26,0)</f>
         <v/>
       </c>
-      <c r="I26" s="10" t="inlineStr">
+      <c r="H26" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -1796,14 +1700,11 @@
       <c r="F27" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="G27" s="11" t="n">
-        <v>7</v>
-      </c>
-      <c r="H27" s="13">
+      <c r="G27" s="13">
         <f>IFERROR(E27/F27,0)</f>
         <v/>
       </c>
-      <c r="I27" s="10" t="inlineStr">
+      <c r="H27" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -1834,14 +1735,11 @@
       <c r="F28" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="G28" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="H28" s="9">
+      <c r="G28" s="9">
         <f>IFERROR(E28/F28,0)</f>
         <v/>
       </c>
-      <c r="I28" s="10" t="inlineStr">
+      <c r="H28" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -1872,14 +1770,11 @@
       <c r="F29" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="G29" s="11" t="n">
-        <v>7</v>
-      </c>
-      <c r="H29" s="13">
+      <c r="G29" s="13">
         <f>IFERROR(E29/F29,0)</f>
         <v/>
       </c>
-      <c r="I29" s="10" t="inlineStr">
+      <c r="H29" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -1910,14 +1805,11 @@
       <c r="F30" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="G30" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="H30" s="9">
+      <c r="G30" s="9">
         <f>IFERROR(E30/F30,0)</f>
         <v/>
       </c>
-      <c r="I30" s="10" t="inlineStr">
+      <c r="H30" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -1948,14 +1840,11 @@
       <c r="F31" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="G31" s="11" t="n">
-        <v>7</v>
-      </c>
-      <c r="H31" s="13">
+      <c r="G31" s="13">
         <f>IFERROR(E31/F31,0)</f>
         <v/>
       </c>
-      <c r="I31" s="10" t="inlineStr">
+      <c r="H31" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -1986,14 +1875,11 @@
       <c r="F32" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="G32" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="H32" s="9">
+      <c r="G32" s="9">
         <f>IFERROR(E32/F32,0)</f>
         <v/>
       </c>
-      <c r="I32" s="10" t="inlineStr">
+      <c r="H32" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -2024,14 +1910,11 @@
       <c r="F33" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="G33" s="11" t="n">
-        <v>7</v>
-      </c>
-      <c r="H33" s="13">
+      <c r="G33" s="13">
         <f>IFERROR(E33/F33,0)</f>
         <v/>
       </c>
-      <c r="I33" s="10" t="inlineStr">
+      <c r="H33" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -2062,14 +1945,11 @@
       <c r="F34" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="G34" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="H34" s="9">
+      <c r="G34" s="9">
         <f>IFERROR(E34/F34,0)</f>
         <v/>
       </c>
-      <c r="I34" s="10" t="inlineStr">
+      <c r="H34" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -2100,14 +1980,11 @@
       <c r="F35" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="G35" s="11" t="n">
-        <v>7</v>
-      </c>
-      <c r="H35" s="13">
+      <c r="G35" s="13">
         <f>IFERROR(E35/F35,0)</f>
         <v/>
       </c>
-      <c r="I35" s="10" t="inlineStr">
+      <c r="H35" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -2138,14 +2015,11 @@
       <c r="F36" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="G36" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="H36" s="9">
+      <c r="G36" s="9">
         <f>IFERROR(E36/F36,0)</f>
         <v/>
       </c>
-      <c r="I36" s="10" t="inlineStr">
+      <c r="H36" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -2176,14 +2050,11 @@
       <c r="F37" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="G37" s="11" t="n">
-        <v>7</v>
-      </c>
-      <c r="H37" s="13">
+      <c r="G37" s="13">
         <f>IFERROR(E37/F37,0)</f>
         <v/>
       </c>
-      <c r="I37" s="10" t="inlineStr">
+      <c r="H37" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -2214,14 +2085,11 @@
       <c r="F38" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="G38" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="H38" s="9">
+      <c r="G38" s="9">
         <f>IFERROR(E38/F38,0)</f>
         <v/>
       </c>
-      <c r="I38" s="10" t="inlineStr">
+      <c r="H38" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -2252,14 +2120,11 @@
       <c r="F39" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="G39" s="11" t="n">
-        <v>7</v>
-      </c>
-      <c r="H39" s="13">
+      <c r="G39" s="13">
         <f>IFERROR(E39/F39,0)</f>
         <v/>
       </c>
-      <c r="I39" s="10" t="inlineStr">
+      <c r="H39" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -2290,14 +2155,11 @@
       <c r="F40" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="G40" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="H40" s="9">
+      <c r="G40" s="9">
         <f>IFERROR(E40/F40,0)</f>
         <v/>
       </c>
-      <c r="I40" s="10" t="inlineStr">
+      <c r="H40" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -2328,14 +2190,11 @@
       <c r="F41" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="G41" s="11" t="n">
-        <v>7</v>
-      </c>
-      <c r="H41" s="13">
+      <c r="G41" s="13">
         <f>IFERROR(E41/F41,0)</f>
         <v/>
       </c>
-      <c r="I41" s="10" t="inlineStr">
+      <c r="H41" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -2366,14 +2225,11 @@
       <c r="F42" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="G42" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="H42" s="9">
+      <c r="G42" s="9">
         <f>IFERROR(E42/F42,0)</f>
         <v/>
       </c>
-      <c r="I42" s="10" t="inlineStr">
+      <c r="H42" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -2404,14 +2260,11 @@
       <c r="F43" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="G43" s="11" t="n">
-        <v>7</v>
-      </c>
-      <c r="H43" s="13">
+      <c r="G43" s="13">
         <f>IFERROR(E43/F43,0)</f>
         <v/>
       </c>
-      <c r="I43" s="10" t="inlineStr">
+      <c r="H43" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -2442,14 +2295,11 @@
       <c r="F44" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="G44" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="H44" s="9">
+      <c r="G44" s="9">
         <f>IFERROR(E44/F44,0)</f>
         <v/>
       </c>
-      <c r="I44" s="10" t="inlineStr">
+      <c r="H44" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -2480,14 +2330,11 @@
       <c r="F45" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="G45" s="11" t="n">
-        <v>7</v>
-      </c>
-      <c r="H45" s="13">
+      <c r="G45" s="13">
         <f>IFERROR(E45/F45,0)</f>
         <v/>
       </c>
-      <c r="I45" s="10" t="inlineStr">
+      <c r="H45" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -2518,14 +2365,11 @@
       <c r="F46" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="G46" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="H46" s="9">
+      <c r="G46" s="9">
         <f>IFERROR(E46/F46,0)</f>
         <v/>
       </c>
-      <c r="I46" s="10" t="inlineStr">
+      <c r="H46" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -2556,14 +2400,11 @@
       <c r="F47" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="G47" s="11" t="n">
-        <v>7</v>
-      </c>
-      <c r="H47" s="13">
+      <c r="G47" s="13">
         <f>IFERROR(E47/F47,0)</f>
         <v/>
       </c>
-      <c r="I47" s="10" t="inlineStr">
+      <c r="H47" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -2594,14 +2435,11 @@
       <c r="F48" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="G48" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="H48" s="9">
+      <c r="G48" s="9">
         <f>IFERROR(E48/F48,0)</f>
         <v/>
       </c>
-      <c r="I48" s="10" t="inlineStr">
+      <c r="H48" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -2632,14 +2470,11 @@
       <c r="F49" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="G49" s="11" t="n">
-        <v>7</v>
-      </c>
-      <c r="H49" s="13">
+      <c r="G49" s="13">
         <f>IFERROR(E49/F49,0)</f>
         <v/>
       </c>
-      <c r="I49" s="10" t="inlineStr">
+      <c r="H49" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -2670,14 +2505,11 @@
       <c r="F50" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="G50" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="H50" s="9">
+      <c r="G50" s="9">
         <f>IFERROR(E50/F50,0)</f>
         <v/>
       </c>
-      <c r="I50" s="10" t="inlineStr">
+      <c r="H50" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -2708,14 +2540,11 @@
       <c r="F51" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="G51" s="11" t="n">
-        <v>7</v>
-      </c>
-      <c r="H51" s="13">
+      <c r="G51" s="13">
         <f>IFERROR(E51/F51,0)</f>
         <v/>
       </c>
-      <c r="I51" s="10" t="inlineStr">
+      <c r="H51" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -2746,14 +2575,11 @@
       <c r="F52" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="G52" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="H52" s="9">
+      <c r="G52" s="9">
         <f>IFERROR(E52/F52,0)</f>
         <v/>
       </c>
-      <c r="I52" s="10" t="inlineStr">
+      <c r="H52" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -2784,14 +2610,11 @@
       <c r="F53" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="G53" s="11" t="n">
-        <v>7</v>
-      </c>
-      <c r="H53" s="13">
+      <c r="G53" s="13">
         <f>IFERROR(E53/F53,0)</f>
         <v/>
       </c>
-      <c r="I53" s="10" t="inlineStr">
+      <c r="H53" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -2822,14 +2645,11 @@
       <c r="F54" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="G54" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="H54" s="9">
+      <c r="G54" s="9">
         <f>IFERROR(E54/F54,0)</f>
         <v/>
       </c>
-      <c r="I54" s="10" t="inlineStr">
+      <c r="H54" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -2860,14 +2680,11 @@
       <c r="F55" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="G55" s="11" t="n">
-        <v>7</v>
-      </c>
-      <c r="H55" s="13">
+      <c r="G55" s="13">
         <f>IFERROR(E55/F55,0)</f>
         <v/>
       </c>
-      <c r="I55" s="10" t="inlineStr">
+      <c r="H55" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -2898,14 +2715,11 @@
       <c r="F56" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="G56" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="H56" s="9">
+      <c r="G56" s="9">
         <f>IFERROR(E56/F56,0)</f>
         <v/>
       </c>
-      <c r="I56" s="10" t="inlineStr">
+      <c r="H56" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -2936,14 +2750,11 @@
       <c r="F57" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="G57" s="11" t="n">
-        <v>7</v>
-      </c>
-      <c r="H57" s="13">
+      <c r="G57" s="13">
         <f>IFERROR(E57/F57,0)</f>
         <v/>
       </c>
-      <c r="I57" s="10" t="inlineStr">
+      <c r="H57" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -2974,14 +2785,11 @@
       <c r="F58" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="G58" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="H58" s="9">
+      <c r="G58" s="9">
         <f>IFERROR(E58/F58,0)</f>
         <v/>
       </c>
-      <c r="I58" s="10" t="inlineStr">
+      <c r="H58" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -3012,14 +2820,11 @@
       <c r="F59" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="G59" s="11" t="n">
-        <v>7</v>
-      </c>
-      <c r="H59" s="13">
+      <c r="G59" s="13">
         <f>IFERROR(E59/F59,0)</f>
         <v/>
       </c>
-      <c r="I59" s="10" t="inlineStr">
+      <c r="H59" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -3050,14 +2855,11 @@
       <c r="F60" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="G60" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="H60" s="9">
+      <c r="G60" s="9">
         <f>IFERROR(E60/F60,0)</f>
         <v/>
       </c>
-      <c r="I60" s="10" t="inlineStr">
+      <c r="H60" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -3088,14 +2890,11 @@
       <c r="F61" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="G61" s="11" t="n">
-        <v>7</v>
-      </c>
-      <c r="H61" s="13">
+      <c r="G61" s="13">
         <f>IFERROR(E61/F61,0)</f>
         <v/>
       </c>
-      <c r="I61" s="10" t="inlineStr">
+      <c r="H61" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -3126,14 +2925,11 @@
       <c r="F62" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="G62" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="H62" s="9">
+      <c r="G62" s="9">
         <f>IFERROR(E62/F62,0)</f>
         <v/>
       </c>
-      <c r="I62" s="10" t="inlineStr">
+      <c r="H62" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -3164,14 +2960,11 @@
       <c r="F63" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="G63" s="11" t="n">
-        <v>7</v>
-      </c>
-      <c r="H63" s="13">
+      <c r="G63" s="13">
         <f>IFERROR(E63/F63,0)</f>
         <v/>
       </c>
-      <c r="I63" s="10" t="inlineStr">
+      <c r="H63" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -3202,14 +2995,11 @@
       <c r="F64" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="G64" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="H64" s="9">
+      <c r="G64" s="9">
         <f>IFERROR(E64/F64,0)</f>
         <v/>
       </c>
-      <c r="I64" s="10" t="inlineStr">
+      <c r="H64" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -3240,14 +3030,11 @@
       <c r="F65" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="G65" s="11" t="n">
-        <v>7</v>
-      </c>
-      <c r="H65" s="13">
+      <c r="G65" s="13">
         <f>IFERROR(E65/F65,0)</f>
         <v/>
       </c>
-      <c r="I65" s="10" t="inlineStr">
+      <c r="H65" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -3278,14 +3065,11 @@
       <c r="F66" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="G66" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="H66" s="9">
+      <c r="G66" s="9">
         <f>IFERROR(E66/F66,0)</f>
         <v/>
       </c>
-      <c r="I66" s="10" t="inlineStr">
+      <c r="H66" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -3316,14 +3100,11 @@
       <c r="F67" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="G67" s="11" t="n">
-        <v>7</v>
-      </c>
-      <c r="H67" s="13">
+      <c r="G67" s="13">
         <f>IFERROR(E67/F67,0)</f>
         <v/>
       </c>
-      <c r="I67" s="10" t="inlineStr">
+      <c r="H67" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -3354,14 +3135,11 @@
       <c r="F68" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="G68" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="H68" s="9">
+      <c r="G68" s="9">
         <f>IFERROR(E68/F68,0)</f>
         <v/>
       </c>
-      <c r="I68" s="10" t="inlineStr">
+      <c r="H68" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -3392,14 +3170,11 @@
       <c r="F69" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="G69" s="11" t="n">
-        <v>7</v>
-      </c>
-      <c r="H69" s="13">
+      <c r="G69" s="13">
         <f>IFERROR(E69/F69,0)</f>
         <v/>
       </c>
-      <c r="I69" s="10" t="inlineStr">
+      <c r="H69" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -3430,14 +3205,11 @@
       <c r="F70" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="G70" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="H70" s="9">
+      <c r="G70" s="9">
         <f>IFERROR(E70/F70,0)</f>
         <v/>
       </c>
-      <c r="I70" s="10" t="inlineStr">
+      <c r="H70" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -3468,14 +3240,11 @@
       <c r="F71" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="G71" s="11" t="n">
-        <v>7</v>
-      </c>
-      <c r="H71" s="13">
+      <c r="G71" s="13">
         <f>IFERROR(E71/F71,0)</f>
         <v/>
       </c>
-      <c r="I71" s="10" t="inlineStr">
+      <c r="H71" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -3506,14 +3275,11 @@
       <c r="F72" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="G72" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="H72" s="9">
+      <c r="G72" s="9">
         <f>IFERROR(E72/F72,0)</f>
         <v/>
       </c>
-      <c r="I72" s="10" t="inlineStr">
+      <c r="H72" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -3544,14 +3310,11 @@
       <c r="F73" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="G73" s="11" t="n">
-        <v>7</v>
-      </c>
-      <c r="H73" s="13">
+      <c r="G73" s="13">
         <f>IFERROR(E73/F73,0)</f>
         <v/>
       </c>
-      <c r="I73" s="10" t="inlineStr">
+      <c r="H73" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -3582,14 +3345,11 @@
       <c r="F74" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="G74" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="H74" s="9">
+      <c r="G74" s="9">
         <f>IFERROR(E74/F74,0)</f>
         <v/>
       </c>
-      <c r="I74" s="10" t="inlineStr">
+      <c r="H74" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -3620,14 +3380,11 @@
       <c r="F75" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="G75" s="11" t="n">
-        <v>7</v>
-      </c>
-      <c r="H75" s="13">
+      <c r="G75" s="13">
         <f>IFERROR(E75/F75,0)</f>
         <v/>
       </c>
-      <c r="I75" s="10" t="inlineStr">
+      <c r="H75" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -3658,26 +3415,23 @@
       <c r="F76" s="7" t="n">
         <v>7</v>
       </c>
-      <c r="G76" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="H76" s="9">
+      <c r="G76" s="9">
         <f>IFERROR(E76/F76,0)</f>
         <v/>
       </c>
-      <c r="I76" s="10" t="inlineStr">
+      <c r="H76" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:I76"/>
+  <autoFilter ref="A4:H76"/>
   <mergeCells count="2">
-    <mergeCell ref="A1:I2"/>
-    <mergeCell ref="A3:I3"/>
+    <mergeCell ref="A1:H2"/>
+    <mergeCell ref="A3:H3"/>
   </mergeCells>
-  <conditionalFormatting sqref="H5:H76">
+  <conditionalFormatting sqref="G5:G76">
     <cfRule type="dataBar" priority="1">
       <dataBar showValue="1">
         <cfvo type="num" val="0"/>
@@ -3698,16 +3452,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="42" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -3743,20 +3496,15 @@
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>Pendientes</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>% Avance</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>% Avance</t>
-        </is>
-      </c>
-      <c r="G4" s="6" t="inlineStr">
         <is>
           <t>Fecha compromiso</t>
         </is>
@@ -3775,16 +3523,13 @@
         <v>1</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>71</v>
-      </c>
-      <c r="E5" s="11" t="n">
         <v>72</v>
       </c>
-      <c r="F5" s="13">
-        <f>IFERROR(C5/E5,0)</f>
-        <v/>
-      </c>
-      <c r="G5" s="12" t="inlineStr">
+      <c r="E5" s="13">
+        <f>IFERROR(C5/D5,0)</f>
+        <v/>
+      </c>
+      <c r="F5" s="12" t="inlineStr">
         <is>
           <t>03/09/26</t>
         </is>
@@ -3805,14 +3550,11 @@
       <c r="D6" s="7" t="n">
         <v>72</v>
       </c>
-      <c r="E6" s="7" t="n">
-        <v>72</v>
-      </c>
-      <c r="F6" s="9">
-        <f>IFERROR(C6/E6,0)</f>
-        <v/>
-      </c>
-      <c r="G6" s="8" t="inlineStr">
+      <c r="E6" s="9">
+        <f>IFERROR(C6/D6,0)</f>
+        <v/>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
         <is>
           <t>03/09/26</t>
         </is>
@@ -3833,14 +3575,11 @@
       <c r="D7" s="11" t="n">
         <v>72</v>
       </c>
-      <c r="E7" s="11" t="n">
-        <v>72</v>
-      </c>
-      <c r="F7" s="13">
-        <f>IFERROR(C7/E7,0)</f>
-        <v/>
-      </c>
-      <c r="G7" s="12" t="inlineStr">
+      <c r="E7" s="13">
+        <f>IFERROR(C7/D7,0)</f>
+        <v/>
+      </c>
+      <c r="F7" s="12" t="inlineStr">
         <is>
           <t>06/09/26</t>
         </is>
@@ -3859,16 +3598,13 @@
         <v>1</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>71</v>
-      </c>
-      <c r="E8" s="7" t="n">
         <v>72</v>
       </c>
-      <c r="F8" s="9">
-        <f>IFERROR(C8/E8,0)</f>
-        <v/>
-      </c>
-      <c r="G8" s="8" t="inlineStr">
+      <c r="E8" s="9">
+        <f>IFERROR(C8/D8,0)</f>
+        <v/>
+      </c>
+      <c r="F8" s="8" t="inlineStr">
         <is>
           <t>03/09/26</t>
         </is>
@@ -3889,14 +3625,11 @@
       <c r="D9" s="11" t="n">
         <v>72</v>
       </c>
-      <c r="E9" s="11" t="n">
-        <v>72</v>
-      </c>
-      <c r="F9" s="13">
-        <f>IFERROR(C9/E9,0)</f>
-        <v/>
-      </c>
-      <c r="G9" s="12" t="inlineStr">
+      <c r="E9" s="13">
+        <f>IFERROR(C9/D9,0)</f>
+        <v/>
+      </c>
+      <c r="F9" s="12" t="inlineStr">
         <is>
           <t>06/09/26</t>
         </is>
@@ -3917,14 +3650,11 @@
       <c r="D10" s="7" t="n">
         <v>72</v>
       </c>
-      <c r="E10" s="7" t="n">
-        <v>72</v>
-      </c>
-      <c r="F10" s="9">
-        <f>IFERROR(C10/E10,0)</f>
-        <v/>
-      </c>
-      <c r="G10" s="8" t="inlineStr">
+      <c r="E10" s="9">
+        <f>IFERROR(C10/D10,0)</f>
+        <v/>
+      </c>
+      <c r="F10" s="8" t="inlineStr">
         <is>
           <t>06/09/26</t>
         </is>
@@ -3945,26 +3675,23 @@
       <c r="D11" s="11" t="n">
         <v>72</v>
       </c>
-      <c r="E11" s="11" t="n">
-        <v>72</v>
-      </c>
-      <c r="F11" s="13">
-        <f>IFERROR(C11/E11,0)</f>
-        <v/>
-      </c>
-      <c r="G11" s="12" t="inlineStr">
+      <c r="E11" s="13">
+        <f>IFERROR(C11/D11,0)</f>
+        <v/>
+      </c>
+      <c r="F11" s="12" t="inlineStr">
         <is>
           <t>13/09/26</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:G11"/>
+  <autoFilter ref="A4:F11"/>
   <mergeCells count="2">
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A1:G2"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A1:F2"/>
   </mergeCells>
-  <conditionalFormatting sqref="F5:F11">
+  <conditionalFormatting sqref="E5:E11">
     <cfRule type="dataBar" priority="1">
       <dataBar showValue="1">
         <cfvo type="num" val="0"/>

--- a/exports/Resumen_Evidencias_OPS.xlsx
+++ b/exports/Resumen_Evidencias_OPS.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tiendas" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Actividades" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Resumen" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Tiendas" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Actividades" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Resumen'!$A$9:$G$15</definedName>

--- a/exports/Resumen_Evidencias_OPS.xlsx
+++ b/exports/Resumen_Evidencias_OPS.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Resumen" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Tiendas" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Actividades" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tiendas" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Actividades" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Resumen'!$A$9:$G$15</definedName>

--- a/exports/Resumen_Evidencias_OPS.xlsx
+++ b/exports/Resumen_Evidencias_OPS.xlsx
@@ -56,7 +56,7 @@
     <font>
       <name val="Aptos Display"/>
       <b val="1"/>
-      <color rgb="00006241"/>
+      <color rgb="00003B2E"/>
       <sz val="18"/>
     </font>
     <font>
@@ -86,7 +86,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00006241"/>
+        <fgColor rgb="00003B2E"/>
       </patternFill>
     </fill>
     <fill>
@@ -536,7 +536,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="00006241"/>
+    <tabColor rgb="00003B2E"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -819,7 +819,7 @@
       <dataBar showValue="1">
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="1"/>
-        <color rgb="00006241"/>
+        <color rgb="00003B2E"/>
       </dataBar>
     </cfRule>
   </conditionalFormatting>
@@ -3436,7 +3436,7 @@
       <dataBar showValue="1">
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="1"/>
-        <color rgb="00006241"/>
+        <color rgb="00003B2E"/>
       </dataBar>
     </cfRule>
   </conditionalFormatting>
@@ -3696,7 +3696,7 @@
       <dataBar showValue="1">
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="1"/>
-        <color rgb="00006241"/>
+        <color rgb="00003B2E"/>
       </dataBar>
     </cfRule>
   </conditionalFormatting>

--- a/exports/Resumen_Evidencias_OPS.xlsx
+++ b/exports/Resumen_Evidencias_OPS.xlsx
@@ -12,11 +12,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Actividades" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Resumen'!$A$9:$G$15</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Resumen'!$A$1:$G$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Tiendas'!$A$4:$H$76</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Resumen'!$A$9:$H$15</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Resumen'!$A$1:$H$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Tiendas'!$A$4:$I$76</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Tiendas'!$1:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Actividades'!$A$4:$F$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Actividades'!$A$4:$G$12</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -540,7 +540,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -548,8 +548,9 @@
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -575,7 +576,7 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Aplican</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -589,7 +590,7 @@
         <v>2</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>504</v>
+        <v>576</v>
       </c>
       <c r="E6" s="5">
         <f>IFERROR(A6/C6,0)</f>
@@ -620,15 +621,20 @@
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Aplican</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
           <t>% Avance</t>
         </is>
       </c>
-      <c r="G9" s="6" t="inlineStr">
+      <c r="H9" s="6" t="inlineStr">
         <is>
           <t>Estado</t>
         </is>
@@ -650,13 +656,16 @@
         <v>2</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>70</v>
-      </c>
-      <c r="F10" s="9">
+        <v>80</v>
+      </c>
+      <c r="F10" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="9">
         <f>IFERROR(D10/E10,0)</f>
         <v/>
       </c>
-      <c r="G10" s="10" t="inlineStr">
+      <c r="H10" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -678,13 +687,16 @@
         <v>0</v>
       </c>
       <c r="E11" s="11" t="n">
-        <v>84</v>
-      </c>
-      <c r="F11" s="13">
+        <v>96</v>
+      </c>
+      <c r="F11" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="13">
         <f>IFERROR(D11/E11,0)</f>
         <v/>
       </c>
-      <c r="G11" s="10" t="inlineStr">
+      <c r="H11" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -706,13 +718,16 @@
         <v>0</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>91</v>
-      </c>
-      <c r="F12" s="9">
+        <v>104</v>
+      </c>
+      <c r="F12" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="9">
         <f>IFERROR(D12/E12,0)</f>
         <v/>
       </c>
-      <c r="G12" s="10" t="inlineStr">
+      <c r="H12" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -734,13 +749,16 @@
         <v>0</v>
       </c>
       <c r="E13" s="11" t="n">
-        <v>77</v>
-      </c>
-      <c r="F13" s="13">
+        <v>88</v>
+      </c>
+      <c r="F13" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="13">
         <f>IFERROR(D13/E13,0)</f>
         <v/>
       </c>
-      <c r="G13" s="10" t="inlineStr">
+      <c r="H13" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -762,13 +780,16 @@
         <v>0</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>91</v>
-      </c>
-      <c r="F14" s="9">
+        <v>104</v>
+      </c>
+      <c r="F14" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="9">
         <f>IFERROR(D14/E14,0)</f>
         <v/>
       </c>
-      <c r="G14" s="10" t="inlineStr">
+      <c r="H14" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -790,31 +811,34 @@
         <v>0</v>
       </c>
       <c r="E15" s="11" t="n">
-        <v>91</v>
-      </c>
-      <c r="F15" s="13">
+        <v>104</v>
+      </c>
+      <c r="F15" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="13">
         <f>IFERROR(D15/E15,0)</f>
         <v/>
       </c>
-      <c r="G15" s="10" t="inlineStr">
+      <c r="H15" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A9:G15"/>
+  <autoFilter ref="A9:H15"/>
   <mergeCells count="8">
-    <mergeCell ref="E6:G7"/>
-    <mergeCell ref="A1:G2"/>
+    <mergeCell ref="A3:H3"/>
     <mergeCell ref="C6:D7"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="E5:G5"/>
     <mergeCell ref="C5:D5"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="A6:B7"/>
+    <mergeCell ref="E6:H7"/>
+    <mergeCell ref="A1:H2"/>
+    <mergeCell ref="E5:H5"/>
   </mergeCells>
-  <conditionalFormatting sqref="F10:F15">
+  <conditionalFormatting sqref="G10:G15">
     <cfRule type="dataBar" priority="1">
       <dataBar showValue="1">
         <cfvo type="num" val="0"/>
@@ -835,7 +859,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H76"/>
+  <dimension ref="A1:I76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -844,8 +868,9 @@
     <col width="32" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -891,15 +916,20 @@
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Aplican</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
           <t>% Avance</t>
         </is>
       </c>
-      <c r="H4" s="6" t="inlineStr">
+      <c r="I4" s="6" t="inlineStr">
         <is>
           <t>Estado</t>
         </is>
@@ -928,13 +958,16 @@
         <v>1</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>7</v>
-      </c>
-      <c r="G5" s="13">
+        <v>8</v>
+      </c>
+      <c r="G5" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="13">
         <f>IFERROR(E5/F5,0)</f>
         <v/>
       </c>
-      <c r="H5" s="10" t="inlineStr">
+      <c r="I5" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -963,13 +996,16 @@
         <v>1</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="G6" s="9">
+        <v>8</v>
+      </c>
+      <c r="G6" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="9">
         <f>IFERROR(E6/F6,0)</f>
         <v/>
       </c>
-      <c r="H6" s="10" t="inlineStr">
+      <c r="I6" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -998,13 +1034,16 @@
         <v>0</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>7</v>
-      </c>
-      <c r="G7" s="13">
+        <v>8</v>
+      </c>
+      <c r="G7" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="13">
         <f>IFERROR(E7/F7,0)</f>
         <v/>
       </c>
-      <c r="H7" s="10" t="inlineStr">
+      <c r="I7" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -1033,13 +1072,16 @@
         <v>0</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="G8" s="9">
+        <v>8</v>
+      </c>
+      <c r="G8" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="9">
         <f>IFERROR(E8/F8,0)</f>
         <v/>
       </c>
-      <c r="H8" s="10" t="inlineStr">
+      <c r="I8" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -1068,13 +1110,16 @@
         <v>0</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>7</v>
-      </c>
-      <c r="G9" s="13">
+        <v>8</v>
+      </c>
+      <c r="G9" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="13">
         <f>IFERROR(E9/F9,0)</f>
         <v/>
       </c>
-      <c r="H9" s="10" t="inlineStr">
+      <c r="I9" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -1103,13 +1148,16 @@
         <v>0</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="G10" s="9">
+        <v>8</v>
+      </c>
+      <c r="G10" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="9">
         <f>IFERROR(E10/F10,0)</f>
         <v/>
       </c>
-      <c r="H10" s="10" t="inlineStr">
+      <c r="I10" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -1138,13 +1186,16 @@
         <v>0</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>7</v>
-      </c>
-      <c r="G11" s="13">
+        <v>8</v>
+      </c>
+      <c r="G11" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="13">
         <f>IFERROR(E11/F11,0)</f>
         <v/>
       </c>
-      <c r="H11" s="10" t="inlineStr">
+      <c r="I11" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -1173,13 +1224,16 @@
         <v>0</v>
       </c>
       <c r="F12" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="G12" s="9">
+        <v>8</v>
+      </c>
+      <c r="G12" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="9">
         <f>IFERROR(E12/F12,0)</f>
         <v/>
       </c>
-      <c r="H12" s="10" t="inlineStr">
+      <c r="I12" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -1208,13 +1262,16 @@
         <v>0</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>7</v>
-      </c>
-      <c r="G13" s="13">
+        <v>8</v>
+      </c>
+      <c r="G13" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="13">
         <f>IFERROR(E13/F13,0)</f>
         <v/>
       </c>
-      <c r="H13" s="10" t="inlineStr">
+      <c r="I13" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -1243,13 +1300,16 @@
         <v>0</v>
       </c>
       <c r="F14" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="G14" s="9">
+        <v>8</v>
+      </c>
+      <c r="G14" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="9">
         <f>IFERROR(E14/F14,0)</f>
         <v/>
       </c>
-      <c r="H14" s="10" t="inlineStr">
+      <c r="I14" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -1278,13 +1338,16 @@
         <v>0</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>7</v>
-      </c>
-      <c r="G15" s="13">
+        <v>8</v>
+      </c>
+      <c r="G15" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="13">
         <f>IFERROR(E15/F15,0)</f>
         <v/>
       </c>
-      <c r="H15" s="10" t="inlineStr">
+      <c r="I15" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -1313,13 +1376,16 @@
         <v>0</v>
       </c>
       <c r="F16" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="G16" s="9">
+        <v>8</v>
+      </c>
+      <c r="G16" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="9">
         <f>IFERROR(E16/F16,0)</f>
         <v/>
       </c>
-      <c r="H16" s="10" t="inlineStr">
+      <c r="I16" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -1348,13 +1414,16 @@
         <v>0</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>7</v>
-      </c>
-      <c r="G17" s="13">
+        <v>8</v>
+      </c>
+      <c r="G17" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="13">
         <f>IFERROR(E17/F17,0)</f>
         <v/>
       </c>
-      <c r="H17" s="10" t="inlineStr">
+      <c r="I17" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -1383,13 +1452,16 @@
         <v>0</v>
       </c>
       <c r="F18" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="G18" s="9">
+        <v>8</v>
+      </c>
+      <c r="G18" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="9">
         <f>IFERROR(E18/F18,0)</f>
         <v/>
       </c>
-      <c r="H18" s="10" t="inlineStr">
+      <c r="I18" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -1418,13 +1490,16 @@
         <v>0</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>7</v>
-      </c>
-      <c r="G19" s="13">
+        <v>8</v>
+      </c>
+      <c r="G19" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="13">
         <f>IFERROR(E19/F19,0)</f>
         <v/>
       </c>
-      <c r="H19" s="10" t="inlineStr">
+      <c r="I19" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -1453,13 +1528,16 @@
         <v>0</v>
       </c>
       <c r="F20" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="G20" s="9">
+        <v>8</v>
+      </c>
+      <c r="G20" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="9">
         <f>IFERROR(E20/F20,0)</f>
         <v/>
       </c>
-      <c r="H20" s="10" t="inlineStr">
+      <c r="I20" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -1488,13 +1566,16 @@
         <v>0</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>7</v>
-      </c>
-      <c r="G21" s="13">
+        <v>8</v>
+      </c>
+      <c r="G21" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="13">
         <f>IFERROR(E21/F21,0)</f>
         <v/>
       </c>
-      <c r="H21" s="10" t="inlineStr">
+      <c r="I21" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -1523,13 +1604,16 @@
         <v>0</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="G22" s="9">
+        <v>8</v>
+      </c>
+      <c r="G22" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="9">
         <f>IFERROR(E22/F22,0)</f>
         <v/>
       </c>
-      <c r="H22" s="10" t="inlineStr">
+      <c r="I22" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -1558,13 +1642,16 @@
         <v>0</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>7</v>
-      </c>
-      <c r="G23" s="13">
+        <v>8</v>
+      </c>
+      <c r="G23" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="13">
         <f>IFERROR(E23/F23,0)</f>
         <v/>
       </c>
-      <c r="H23" s="10" t="inlineStr">
+      <c r="I23" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -1593,13 +1680,16 @@
         <v>0</v>
       </c>
       <c r="F24" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="G24" s="9">
+        <v>8</v>
+      </c>
+      <c r="G24" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="9">
         <f>IFERROR(E24/F24,0)</f>
         <v/>
       </c>
-      <c r="H24" s="10" t="inlineStr">
+      <c r="I24" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -1628,13 +1718,16 @@
         <v>0</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>7</v>
-      </c>
-      <c r="G25" s="13">
+        <v>8</v>
+      </c>
+      <c r="G25" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" s="13">
         <f>IFERROR(E25/F25,0)</f>
         <v/>
       </c>
-      <c r="H25" s="10" t="inlineStr">
+      <c r="I25" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -1663,13 +1756,16 @@
         <v>0</v>
       </c>
       <c r="F26" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="G26" s="9">
+        <v>8</v>
+      </c>
+      <c r="G26" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="9">
         <f>IFERROR(E26/F26,0)</f>
         <v/>
       </c>
-      <c r="H26" s="10" t="inlineStr">
+      <c r="I26" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -1698,13 +1794,16 @@
         <v>0</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>7</v>
-      </c>
-      <c r="G27" s="13">
+        <v>8</v>
+      </c>
+      <c r="G27" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="13">
         <f>IFERROR(E27/F27,0)</f>
         <v/>
       </c>
-      <c r="H27" s="10" t="inlineStr">
+      <c r="I27" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -1733,13 +1832,16 @@
         <v>0</v>
       </c>
       <c r="F28" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="G28" s="9">
+        <v>8</v>
+      </c>
+      <c r="G28" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" s="9">
         <f>IFERROR(E28/F28,0)</f>
         <v/>
       </c>
-      <c r="H28" s="10" t="inlineStr">
+      <c r="I28" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -1768,13 +1870,16 @@
         <v>0</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>7</v>
-      </c>
-      <c r="G29" s="13">
+        <v>8</v>
+      </c>
+      <c r="G29" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" s="13">
         <f>IFERROR(E29/F29,0)</f>
         <v/>
       </c>
-      <c r="H29" s="10" t="inlineStr">
+      <c r="I29" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -1803,13 +1908,16 @@
         <v>0</v>
       </c>
       <c r="F30" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="G30" s="9">
+        <v>8</v>
+      </c>
+      <c r="G30" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" s="9">
         <f>IFERROR(E30/F30,0)</f>
         <v/>
       </c>
-      <c r="H30" s="10" t="inlineStr">
+      <c r="I30" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -1838,13 +1946,16 @@
         <v>0</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>7</v>
-      </c>
-      <c r="G31" s="13">
+        <v>8</v>
+      </c>
+      <c r="G31" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" s="13">
         <f>IFERROR(E31/F31,0)</f>
         <v/>
       </c>
-      <c r="H31" s="10" t="inlineStr">
+      <c r="I31" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -1873,13 +1984,16 @@
         <v>0</v>
       </c>
       <c r="F32" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="G32" s="9">
+        <v>8</v>
+      </c>
+      <c r="G32" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" s="9">
         <f>IFERROR(E32/F32,0)</f>
         <v/>
       </c>
-      <c r="H32" s="10" t="inlineStr">
+      <c r="I32" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -1908,13 +2022,16 @@
         <v>0</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>7</v>
-      </c>
-      <c r="G33" s="13">
+        <v>8</v>
+      </c>
+      <c r="G33" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" s="13">
         <f>IFERROR(E33/F33,0)</f>
         <v/>
       </c>
-      <c r="H33" s="10" t="inlineStr">
+      <c r="I33" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -1943,13 +2060,16 @@
         <v>0</v>
       </c>
       <c r="F34" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="G34" s="9">
+        <v>8</v>
+      </c>
+      <c r="G34" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" s="9">
         <f>IFERROR(E34/F34,0)</f>
         <v/>
       </c>
-      <c r="H34" s="10" t="inlineStr">
+      <c r="I34" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -1978,13 +2098,16 @@
         <v>0</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>7</v>
-      </c>
-      <c r="G35" s="13">
+        <v>8</v>
+      </c>
+      <c r="G35" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" s="13">
         <f>IFERROR(E35/F35,0)</f>
         <v/>
       </c>
-      <c r="H35" s="10" t="inlineStr">
+      <c r="I35" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -2013,13 +2136,16 @@
         <v>0</v>
       </c>
       <c r="F36" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="G36" s="9">
+        <v>8</v>
+      </c>
+      <c r="G36" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" s="9">
         <f>IFERROR(E36/F36,0)</f>
         <v/>
       </c>
-      <c r="H36" s="10" t="inlineStr">
+      <c r="I36" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -2048,13 +2174,16 @@
         <v>0</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>7</v>
-      </c>
-      <c r="G37" s="13">
+        <v>8</v>
+      </c>
+      <c r="G37" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" s="13">
         <f>IFERROR(E37/F37,0)</f>
         <v/>
       </c>
-      <c r="H37" s="10" t="inlineStr">
+      <c r="I37" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -2083,13 +2212,16 @@
         <v>0</v>
       </c>
       <c r="F38" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="G38" s="9">
+        <v>8</v>
+      </c>
+      <c r="G38" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" s="9">
         <f>IFERROR(E38/F38,0)</f>
         <v/>
       </c>
-      <c r="H38" s="10" t="inlineStr">
+      <c r="I38" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -2118,13 +2250,16 @@
         <v>0</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>7</v>
-      </c>
-      <c r="G39" s="13">
+        <v>8</v>
+      </c>
+      <c r="G39" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" s="13">
         <f>IFERROR(E39/F39,0)</f>
         <v/>
       </c>
-      <c r="H39" s="10" t="inlineStr">
+      <c r="I39" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -2153,13 +2288,16 @@
         <v>0</v>
       </c>
       <c r="F40" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="G40" s="9">
+        <v>8</v>
+      </c>
+      <c r="G40" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" s="9">
         <f>IFERROR(E40/F40,0)</f>
         <v/>
       </c>
-      <c r="H40" s="10" t="inlineStr">
+      <c r="I40" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -2188,13 +2326,16 @@
         <v>0</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>7</v>
-      </c>
-      <c r="G41" s="13">
+        <v>8</v>
+      </c>
+      <c r="G41" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" s="13">
         <f>IFERROR(E41/F41,0)</f>
         <v/>
       </c>
-      <c r="H41" s="10" t="inlineStr">
+      <c r="I41" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -2223,13 +2364,16 @@
         <v>0</v>
       </c>
       <c r="F42" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="G42" s="9">
+        <v>8</v>
+      </c>
+      <c r="G42" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" s="9">
         <f>IFERROR(E42/F42,0)</f>
         <v/>
       </c>
-      <c r="H42" s="10" t="inlineStr">
+      <c r="I42" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -2258,13 +2402,16 @@
         <v>0</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>7</v>
-      </c>
-      <c r="G43" s="13">
+        <v>8</v>
+      </c>
+      <c r="G43" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" s="13">
         <f>IFERROR(E43/F43,0)</f>
         <v/>
       </c>
-      <c r="H43" s="10" t="inlineStr">
+      <c r="I43" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -2293,13 +2440,16 @@
         <v>0</v>
       </c>
       <c r="F44" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="G44" s="9">
+        <v>8</v>
+      </c>
+      <c r="G44" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" s="9">
         <f>IFERROR(E44/F44,0)</f>
         <v/>
       </c>
-      <c r="H44" s="10" t="inlineStr">
+      <c r="I44" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -2328,13 +2478,16 @@
         <v>0</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>7</v>
-      </c>
-      <c r="G45" s="13">
+        <v>8</v>
+      </c>
+      <c r="G45" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" s="13">
         <f>IFERROR(E45/F45,0)</f>
         <v/>
       </c>
-      <c r="H45" s="10" t="inlineStr">
+      <c r="I45" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -2363,13 +2516,16 @@
         <v>0</v>
       </c>
       <c r="F46" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="G46" s="9">
+        <v>8</v>
+      </c>
+      <c r="G46" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" s="9">
         <f>IFERROR(E46/F46,0)</f>
         <v/>
       </c>
-      <c r="H46" s="10" t="inlineStr">
+      <c r="I46" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -2398,13 +2554,16 @@
         <v>0</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>7</v>
-      </c>
-      <c r="G47" s="13">
+        <v>8</v>
+      </c>
+      <c r="G47" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" s="13">
         <f>IFERROR(E47/F47,0)</f>
         <v/>
       </c>
-      <c r="H47" s="10" t="inlineStr">
+      <c r="I47" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -2433,13 +2592,16 @@
         <v>0</v>
       </c>
       <c r="F48" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="G48" s="9">
+        <v>8</v>
+      </c>
+      <c r="G48" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" s="9">
         <f>IFERROR(E48/F48,0)</f>
         <v/>
       </c>
-      <c r="H48" s="10" t="inlineStr">
+      <c r="I48" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -2468,13 +2630,16 @@
         <v>0</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>7</v>
-      </c>
-      <c r="G49" s="13">
+        <v>8</v>
+      </c>
+      <c r="G49" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" s="13">
         <f>IFERROR(E49/F49,0)</f>
         <v/>
       </c>
-      <c r="H49" s="10" t="inlineStr">
+      <c r="I49" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -2503,13 +2668,16 @@
         <v>0</v>
       </c>
       <c r="F50" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="G50" s="9">
+        <v>8</v>
+      </c>
+      <c r="G50" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" s="9">
         <f>IFERROR(E50/F50,0)</f>
         <v/>
       </c>
-      <c r="H50" s="10" t="inlineStr">
+      <c r="I50" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -2538,13 +2706,16 @@
         <v>0</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>7</v>
-      </c>
-      <c r="G51" s="13">
+        <v>8</v>
+      </c>
+      <c r="G51" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" s="13">
         <f>IFERROR(E51/F51,0)</f>
         <v/>
       </c>
-      <c r="H51" s="10" t="inlineStr">
+      <c r="I51" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -2573,13 +2744,16 @@
         <v>0</v>
       </c>
       <c r="F52" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="G52" s="9">
+        <v>8</v>
+      </c>
+      <c r="G52" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" s="9">
         <f>IFERROR(E52/F52,0)</f>
         <v/>
       </c>
-      <c r="H52" s="10" t="inlineStr">
+      <c r="I52" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -2608,13 +2782,16 @@
         <v>0</v>
       </c>
       <c r="F53" s="11" t="n">
-        <v>7</v>
-      </c>
-      <c r="G53" s="13">
+        <v>8</v>
+      </c>
+      <c r="G53" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" s="13">
         <f>IFERROR(E53/F53,0)</f>
         <v/>
       </c>
-      <c r="H53" s="10" t="inlineStr">
+      <c r="I53" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -2643,13 +2820,16 @@
         <v>0</v>
       </c>
       <c r="F54" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="G54" s="9">
+        <v>8</v>
+      </c>
+      <c r="G54" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" s="9">
         <f>IFERROR(E54/F54,0)</f>
         <v/>
       </c>
-      <c r="H54" s="10" t="inlineStr">
+      <c r="I54" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -2678,13 +2858,16 @@
         <v>0</v>
       </c>
       <c r="F55" s="11" t="n">
-        <v>7</v>
-      </c>
-      <c r="G55" s="13">
+        <v>8</v>
+      </c>
+      <c r="G55" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" s="13">
         <f>IFERROR(E55/F55,0)</f>
         <v/>
       </c>
-      <c r="H55" s="10" t="inlineStr">
+      <c r="I55" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -2713,13 +2896,16 @@
         <v>0</v>
       </c>
       <c r="F56" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="G56" s="9">
+        <v>8</v>
+      </c>
+      <c r="G56" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" s="9">
         <f>IFERROR(E56/F56,0)</f>
         <v/>
       </c>
-      <c r="H56" s="10" t="inlineStr">
+      <c r="I56" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -2748,13 +2934,16 @@
         <v>0</v>
       </c>
       <c r="F57" s="11" t="n">
-        <v>7</v>
-      </c>
-      <c r="G57" s="13">
+        <v>8</v>
+      </c>
+      <c r="G57" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" s="13">
         <f>IFERROR(E57/F57,0)</f>
         <v/>
       </c>
-      <c r="H57" s="10" t="inlineStr">
+      <c r="I57" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -2783,13 +2972,16 @@
         <v>0</v>
       </c>
       <c r="F58" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="G58" s="9">
+        <v>8</v>
+      </c>
+      <c r="G58" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" s="9">
         <f>IFERROR(E58/F58,0)</f>
         <v/>
       </c>
-      <c r="H58" s="10" t="inlineStr">
+      <c r="I58" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -2818,13 +3010,16 @@
         <v>0</v>
       </c>
       <c r="F59" s="11" t="n">
-        <v>7</v>
-      </c>
-      <c r="G59" s="13">
+        <v>8</v>
+      </c>
+      <c r="G59" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H59" s="13">
         <f>IFERROR(E59/F59,0)</f>
         <v/>
       </c>
-      <c r="H59" s="10" t="inlineStr">
+      <c r="I59" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -2853,13 +3048,16 @@
         <v>0</v>
       </c>
       <c r="F60" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="G60" s="9">
+        <v>8</v>
+      </c>
+      <c r="G60" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H60" s="9">
         <f>IFERROR(E60/F60,0)</f>
         <v/>
       </c>
-      <c r="H60" s="10" t="inlineStr">
+      <c r="I60" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -2888,13 +3086,16 @@
         <v>0</v>
       </c>
       <c r="F61" s="11" t="n">
-        <v>7</v>
-      </c>
-      <c r="G61" s="13">
+        <v>8</v>
+      </c>
+      <c r="G61" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H61" s="13">
         <f>IFERROR(E61/F61,0)</f>
         <v/>
       </c>
-      <c r="H61" s="10" t="inlineStr">
+      <c r="I61" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -2923,13 +3124,16 @@
         <v>0</v>
       </c>
       <c r="F62" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="G62" s="9">
+        <v>8</v>
+      </c>
+      <c r="G62" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H62" s="9">
         <f>IFERROR(E62/F62,0)</f>
         <v/>
       </c>
-      <c r="H62" s="10" t="inlineStr">
+      <c r="I62" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -2958,13 +3162,16 @@
         <v>0</v>
       </c>
       <c r="F63" s="11" t="n">
-        <v>7</v>
-      </c>
-      <c r="G63" s="13">
+        <v>8</v>
+      </c>
+      <c r="G63" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H63" s="13">
         <f>IFERROR(E63/F63,0)</f>
         <v/>
       </c>
-      <c r="H63" s="10" t="inlineStr">
+      <c r="I63" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -2993,13 +3200,16 @@
         <v>0</v>
       </c>
       <c r="F64" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="G64" s="9">
+        <v>8</v>
+      </c>
+      <c r="G64" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H64" s="9">
         <f>IFERROR(E64/F64,0)</f>
         <v/>
       </c>
-      <c r="H64" s="10" t="inlineStr">
+      <c r="I64" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -3028,13 +3238,16 @@
         <v>0</v>
       </c>
       <c r="F65" s="11" t="n">
-        <v>7</v>
-      </c>
-      <c r="G65" s="13">
+        <v>8</v>
+      </c>
+      <c r="G65" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H65" s="13">
         <f>IFERROR(E65/F65,0)</f>
         <v/>
       </c>
-      <c r="H65" s="10" t="inlineStr">
+      <c r="I65" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -3063,13 +3276,16 @@
         <v>0</v>
       </c>
       <c r="F66" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="G66" s="9">
+        <v>8</v>
+      </c>
+      <c r="G66" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H66" s="9">
         <f>IFERROR(E66/F66,0)</f>
         <v/>
       </c>
-      <c r="H66" s="10" t="inlineStr">
+      <c r="I66" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -3098,13 +3314,16 @@
         <v>0</v>
       </c>
       <c r="F67" s="11" t="n">
-        <v>7</v>
-      </c>
-      <c r="G67" s="13">
+        <v>8</v>
+      </c>
+      <c r="G67" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H67" s="13">
         <f>IFERROR(E67/F67,0)</f>
         <v/>
       </c>
-      <c r="H67" s="10" t="inlineStr">
+      <c r="I67" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -3133,13 +3352,16 @@
         <v>0</v>
       </c>
       <c r="F68" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="G68" s="9">
+        <v>8</v>
+      </c>
+      <c r="G68" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H68" s="9">
         <f>IFERROR(E68/F68,0)</f>
         <v/>
       </c>
-      <c r="H68" s="10" t="inlineStr">
+      <c r="I68" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -3168,13 +3390,16 @@
         <v>0</v>
       </c>
       <c r="F69" s="11" t="n">
-        <v>7</v>
-      </c>
-      <c r="G69" s="13">
+        <v>8</v>
+      </c>
+      <c r="G69" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H69" s="13">
         <f>IFERROR(E69/F69,0)</f>
         <v/>
       </c>
-      <c r="H69" s="10" t="inlineStr">
+      <c r="I69" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -3203,13 +3428,16 @@
         <v>0</v>
       </c>
       <c r="F70" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="G70" s="9">
+        <v>8</v>
+      </c>
+      <c r="G70" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H70" s="9">
         <f>IFERROR(E70/F70,0)</f>
         <v/>
       </c>
-      <c r="H70" s="10" t="inlineStr">
+      <c r="I70" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -3238,13 +3466,16 @@
         <v>0</v>
       </c>
       <c r="F71" s="11" t="n">
-        <v>7</v>
-      </c>
-      <c r="G71" s="13">
+        <v>8</v>
+      </c>
+      <c r="G71" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H71" s="13">
         <f>IFERROR(E71/F71,0)</f>
         <v/>
       </c>
-      <c r="H71" s="10" t="inlineStr">
+      <c r="I71" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -3273,13 +3504,16 @@
         <v>0</v>
       </c>
       <c r="F72" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="G72" s="9">
+        <v>8</v>
+      </c>
+      <c r="G72" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H72" s="9">
         <f>IFERROR(E72/F72,0)</f>
         <v/>
       </c>
-      <c r="H72" s="10" t="inlineStr">
+      <c r="I72" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -3308,13 +3542,16 @@
         <v>0</v>
       </c>
       <c r="F73" s="11" t="n">
-        <v>7</v>
-      </c>
-      <c r="G73" s="13">
+        <v>8</v>
+      </c>
+      <c r="G73" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H73" s="13">
         <f>IFERROR(E73/F73,0)</f>
         <v/>
       </c>
-      <c r="H73" s="10" t="inlineStr">
+      <c r="I73" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -3343,13 +3580,16 @@
         <v>0</v>
       </c>
       <c r="F74" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="G74" s="9">
+        <v>8</v>
+      </c>
+      <c r="G74" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H74" s="9">
         <f>IFERROR(E74/F74,0)</f>
         <v/>
       </c>
-      <c r="H74" s="10" t="inlineStr">
+      <c r="I74" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -3378,13 +3618,16 @@
         <v>0</v>
       </c>
       <c r="F75" s="11" t="n">
-        <v>7</v>
-      </c>
-      <c r="G75" s="13">
+        <v>8</v>
+      </c>
+      <c r="G75" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H75" s="13">
         <f>IFERROR(E75/F75,0)</f>
         <v/>
       </c>
-      <c r="H75" s="10" t="inlineStr">
+      <c r="I75" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -3413,25 +3656,28 @@
         <v>0</v>
       </c>
       <c r="F76" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="G76" s="9">
+        <v>8</v>
+      </c>
+      <c r="G76" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H76" s="9">
         <f>IFERROR(E76/F76,0)</f>
         <v/>
       </c>
-      <c r="H76" s="10" t="inlineStr">
+      <c r="I76" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:H76"/>
+  <autoFilter ref="A4:I76"/>
   <mergeCells count="2">
-    <mergeCell ref="A1:H2"/>
-    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A1:I2"/>
+    <mergeCell ref="A3:I3"/>
   </mergeCells>
-  <conditionalFormatting sqref="G5:G76">
+  <conditionalFormatting sqref="H5:H76">
     <cfRule type="dataBar" priority="1">
       <dataBar showValue="1">
         <cfvo type="num" val="0"/>
@@ -3452,15 +3698,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="42" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -3496,15 +3743,20 @@
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Aplican</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
+          <t>No aplica</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
           <t>% Avance</t>
         </is>
       </c>
-      <c r="F4" s="6" t="inlineStr">
+      <c r="G4" s="6" t="inlineStr">
         <is>
           <t>Fecha compromiso</t>
         </is>
@@ -3525,11 +3777,14 @@
       <c r="D5" s="11" t="n">
         <v>72</v>
       </c>
-      <c r="E5" s="13">
+      <c r="E5" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="13">
         <f>IFERROR(C5/D5,0)</f>
         <v/>
       </c>
-      <c r="F5" s="12" t="inlineStr">
+      <c r="G5" s="12" t="inlineStr">
         <is>
           <t>03/09/26</t>
         </is>
@@ -3550,11 +3805,14 @@
       <c r="D6" s="7" t="n">
         <v>72</v>
       </c>
-      <c r="E6" s="9">
+      <c r="E6" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="9">
         <f>IFERROR(C6/D6,0)</f>
         <v/>
       </c>
-      <c r="F6" s="8" t="inlineStr">
+      <c r="G6" s="8" t="inlineStr">
         <is>
           <t>03/09/26</t>
         </is>
@@ -3575,11 +3833,14 @@
       <c r="D7" s="11" t="n">
         <v>72</v>
       </c>
-      <c r="E7" s="13">
+      <c r="E7" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="13">
         <f>IFERROR(C7/D7,0)</f>
         <v/>
       </c>
-      <c r="F7" s="12" t="inlineStr">
+      <c r="G7" s="12" t="inlineStr">
         <is>
           <t>06/09/26</t>
         </is>
@@ -3600,11 +3861,14 @@
       <c r="D8" s="7" t="n">
         <v>72</v>
       </c>
-      <c r="E8" s="9">
+      <c r="E8" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="9">
         <f>IFERROR(C8/D8,0)</f>
         <v/>
       </c>
-      <c r="F8" s="8" t="inlineStr">
+      <c r="G8" s="8" t="inlineStr">
         <is>
           <t>03/09/26</t>
         </is>
@@ -3625,11 +3889,14 @@
       <c r="D9" s="11" t="n">
         <v>72</v>
       </c>
-      <c r="E9" s="13">
+      <c r="E9" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="13">
         <f>IFERROR(C9/D9,0)</f>
         <v/>
       </c>
-      <c r="F9" s="12" t="inlineStr">
+      <c r="G9" s="12" t="inlineStr">
         <is>
           <t>06/09/26</t>
         </is>
@@ -3650,11 +3917,14 @@
       <c r="D10" s="7" t="n">
         <v>72</v>
       </c>
-      <c r="E10" s="9">
+      <c r="E10" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="9">
         <f>IFERROR(C10/D10,0)</f>
         <v/>
       </c>
-      <c r="F10" s="8" t="inlineStr">
+      <c r="G10" s="8" t="inlineStr">
         <is>
           <t>06/09/26</t>
         </is>
@@ -3675,23 +3945,54 @@
       <c r="D11" s="11" t="n">
         <v>72</v>
       </c>
-      <c r="E11" s="13">
+      <c r="E11" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="13">
         <f>IFERROR(C11/D11,0)</f>
         <v/>
       </c>
-      <c r="F11" s="12" t="inlineStr">
+      <c r="G11" s="12" t="inlineStr">
         <is>
           <t>13/09/26</t>
         </is>
       </c>
     </row>
+    <row r="12" ht="21" customHeight="1">
+      <c r="A12" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>Lay Out</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="7" t="n">
+        <v>72</v>
+      </c>
+      <c r="E12" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="9">
+        <f>IFERROR(C12/D12,0)</f>
+        <v/>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>06/09/26</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:F11"/>
+  <autoFilter ref="A4:G12"/>
   <mergeCells count="2">
-    <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A1:F2"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A1:G2"/>
   </mergeCells>
-  <conditionalFormatting sqref="E5:E11">
+  <conditionalFormatting sqref="F5:F12">
     <cfRule type="dataBar" priority="1">
       <dataBar showValue="1">
         <cfvo type="num" val="0"/>

--- a/exports/Resumen_Evidencias_OPS.xlsx
+++ b/exports/Resumen_Evidencias_OPS.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Resumen" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Tiendas" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Actividades" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tiendas" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Actividades" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Resumen'!$A$9:$H$15</definedName>
@@ -564,7 +564,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Centro Norte · Corte 28/08/2026 20:39</t>
+          <t>Centro Norte · Corte 29/08/2026 09:43</t>
         </is>
       </c>
     </row>
@@ -587,7 +587,7 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>576</v>
@@ -646,17 +646,17 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>Enrique Cesar</t>
+          <t>Veronica Garcia</t>
         </is>
       </c>
       <c r="C10" s="7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D10" s="7" t="n">
         <v>2</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="F10" s="7" t="n">
         <v>0</v>
@@ -677,17 +677,17 @@
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina</t>
+          <t>Yazmin Garcia</t>
         </is>
       </c>
       <c r="C11" s="11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E11" s="11" t="n">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="F11" s="11" t="n">
         <v>0</v>
@@ -708,17 +708,17 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño</t>
+          <t>Enrique Cesar</t>
         </is>
       </c>
       <c r="C12" s="7" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>104</v>
+        <v>80</v>
       </c>
       <c r="F12" s="7" t="n">
         <v>0</v>
@@ -739,17 +739,17 @@
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia</t>
+          <t>Nancy Carolina</t>
         </is>
       </c>
       <c r="C13" s="11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D13" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E13" s="11" t="n">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="F13" s="11" t="n">
         <v>0</v>
@@ -777,7 +777,7 @@
         <v>13</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E14" s="7" t="n">
         <v>104</v>
@@ -801,7 +801,7 @@
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Garcia</t>
+          <t>Vanessa Carreño</t>
         </is>
       </c>
       <c r="C15" s="11" t="n">
@@ -884,7 +884,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Centro Norte · Corte 28/08/2026 20:39</t>
+          <t>Centro Norte · Corte 29/08/2026 09:43</t>
         </is>
       </c>
     </row>
@@ -941,17 +941,17 @@
       </c>
       <c r="B5" s="14" t="inlineStr">
         <is>
-          <t>38401</t>
+          <t>38186</t>
         </is>
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>Coacalco</t>
+          <t>Arboledas</t>
         </is>
       </c>
       <c r="D5" s="12" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E5" s="11" t="n">
@@ -979,17 +979,17 @@
       </c>
       <c r="B6" s="15" t="inlineStr">
         <is>
-          <t>38456</t>
+          <t>38149</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>Plaza las Flores</t>
+          <t>Bellavista</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E6" s="7" t="n">
@@ -1017,21 +1017,21 @@
       </c>
       <c r="B7" s="14" t="inlineStr">
         <is>
-          <t>38186</t>
+          <t>38401</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>Arboledas</t>
+          <t>Coacalco</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E7" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" s="11" t="n">
         <v>8</v>
@@ -1055,21 +1055,21 @@
       </c>
       <c r="B8" s="15" t="inlineStr">
         <is>
-          <t>43194</t>
+          <t>38965</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>Atana Lindavista</t>
+          <t>Parque Tepeyac Piso 2</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E8" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" s="7" t="n">
         <v>8</v>
@@ -1093,21 +1093,21 @@
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>43043</t>
+          <t>38590</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>Atizapan</t>
+          <t>Parque Toreo II</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E9" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F9" s="11" t="n">
         <v>8</v>
@@ -1131,21 +1131,21 @@
       </c>
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>38149</t>
+          <t>38811</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>Bellavista</t>
+          <t>Plaza Tepeyac</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E10" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10" s="7" t="n">
         <v>8</v>
@@ -1169,21 +1169,21 @@
       </c>
       <c r="B11" s="14" t="inlineStr">
         <is>
-          <t>38930</t>
+          <t>38115</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>Blvd. Aeropuerto dt</t>
+          <t>Zona Azul</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E11" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F11" s="11" t="n">
         <v>8</v>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>38529</t>
+          <t>43194</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Bosques de Aragon</t>
+          <t>Atana Lindavista</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E12" s="7" t="n">
@@ -1245,17 +1245,17 @@
       </c>
       <c r="B13" s="14" t="inlineStr">
         <is>
-          <t>38527</t>
+          <t>43043</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>Camarones</t>
+          <t>Atizapan</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E13" s="11" t="n">
@@ -1283,17 +1283,17 @@
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>38837</t>
+          <t>38930</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Centenario Azcapotzalco</t>
+          <t>Blvd. Aeropuerto dt</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E14" s="7" t="n">
@@ -1321,17 +1321,17 @@
       </c>
       <c r="B15" s="14" t="inlineStr">
         <is>
-          <t>38394</t>
+          <t>38529</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>Centro Comercial Lomas Verdes</t>
+          <t>Bosques de Aragon</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E15" s="11" t="n">
@@ -1359,17 +1359,17 @@
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>38695</t>
+          <t>38527</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>Cetram 4 Caminos</t>
+          <t>Camarones</t>
         </is>
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E16" s="7" t="n">
@@ -1397,17 +1397,17 @@
       </c>
       <c r="B17" s="14" t="inlineStr">
         <is>
-          <t>38535</t>
+          <t>38837</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>City Center Esmeralda</t>
+          <t>Centenario Azcapotzalco</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E17" s="11" t="n">
@@ -1435,17 +1435,17 @@
       </c>
       <c r="B18" s="15" t="inlineStr">
         <is>
-          <t>38604</t>
+          <t>38394</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>Cosmopol</t>
+          <t>Centro Comercial Lomas Verdes</t>
         </is>
       </c>
       <c r="D18" s="8" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E18" s="7" t="n">
@@ -1473,17 +1473,17 @@
       </c>
       <c r="B19" s="14" t="inlineStr">
         <is>
-          <t>43193</t>
+          <t>38695</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>Cosmopol N1</t>
+          <t>Cetram 4 Caminos</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E19" s="11" t="n">
@@ -1511,17 +1511,17 @@
       </c>
       <c r="B20" s="15" t="inlineStr">
         <is>
-          <t>38197</t>
+          <t>38535</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>Echegaray</t>
+          <t>City Center Esmeralda</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E20" s="7" t="n">
@@ -1549,17 +1549,17 @@
       </c>
       <c r="B21" s="14" t="inlineStr">
         <is>
-          <t>38431</t>
+          <t>38604</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>Eduardo Molina</t>
+          <t>Cosmopol</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E21" s="11" t="n">
@@ -1587,17 +1587,17 @@
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>38458</t>
+          <t>43193</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>El Rosario</t>
+          <t>Cosmopol N1</t>
         </is>
       </c>
       <c r="D22" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E22" s="7" t="n">
@@ -1625,17 +1625,17 @@
       </c>
       <c r="B23" s="14" t="inlineStr">
         <is>
-          <t>38903</t>
+          <t>38197</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>Encuentro Oceania</t>
+          <t>Echegaray</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E23" s="11" t="n">
@@ -1663,12 +1663,12 @@
       </c>
       <c r="B24" s="15" t="inlineStr">
         <is>
-          <t>38995</t>
+          <t>38431</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>Encuentro Oceania II</t>
+          <t>Eduardo Molina</t>
         </is>
       </c>
       <c r="D24" s="8" t="inlineStr">
@@ -1701,17 +1701,17 @@
       </c>
       <c r="B25" s="14" t="inlineStr">
         <is>
-          <t>38507</t>
+          <t>38458</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>Espacio Vista del Valle</t>
+          <t>El Rosario</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E25" s="11" t="n">
@@ -1739,17 +1739,17 @@
       </c>
       <c r="B26" s="15" t="inlineStr">
         <is>
-          <t>38363</t>
+          <t>38903</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>Galerias Atizapan</t>
+          <t>Encuentro Oceania</t>
         </is>
       </c>
       <c r="D26" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E26" s="7" t="n">
@@ -1777,17 +1777,17 @@
       </c>
       <c r="B27" s="14" t="inlineStr">
         <is>
-          <t>38894</t>
+          <t>38995</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>Galerias Perinorte</t>
+          <t>Encuentro Oceania II</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E27" s="11" t="n">
@@ -1815,17 +1815,17 @@
       </c>
       <c r="B28" s="15" t="inlineStr">
         <is>
-          <t>38770</t>
+          <t>38507</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>Gustavo Baz 29</t>
+          <t>Espacio Vista del Valle</t>
         </is>
       </c>
       <c r="D28" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E28" s="7" t="n">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="B29" s="14" t="inlineStr">
         <is>
-          <t>38230</t>
+          <t>38363</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>ITEMS Edo de Mexico</t>
+          <t>Galerias Atizapan</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E29" s="11" t="n">
@@ -1891,12 +1891,12 @@
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>38333</t>
+          <t>38894</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>Izcalli Mega</t>
+          <t>Galerias Perinorte</t>
         </is>
       </c>
       <c r="D30" s="8" t="inlineStr">
@@ -1929,17 +1929,17 @@
       </c>
       <c r="B31" s="14" t="inlineStr">
         <is>
-          <t>38661</t>
+          <t>38770</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>Jinetes</t>
+          <t>Gustavo Baz 29</t>
         </is>
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E31" s="11" t="n">
@@ -1967,17 +1967,17 @@
       </c>
       <c r="B32" s="15" t="inlineStr">
         <is>
-          <t>38205</t>
+          <t>38230</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>Lindavista</t>
+          <t>ITEMS Edo de Mexico</t>
         </is>
       </c>
       <c r="D32" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E32" s="7" t="n">
@@ -2005,17 +2005,17 @@
       </c>
       <c r="B33" s="14" t="inlineStr">
         <is>
-          <t>38207</t>
+          <t>38333</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>Lindavista II</t>
+          <t>Izcalli Mega</t>
         </is>
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E33" s="11" t="n">
@@ -2043,17 +2043,17 @@
       </c>
       <c r="B34" s="15" t="inlineStr">
         <is>
-          <t>38119</t>
+          <t>38661</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>Lomas Verdes</t>
+          <t>Jinetes</t>
         </is>
       </c>
       <c r="D34" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E34" s="7" t="n">
@@ -2081,17 +2081,17 @@
       </c>
       <c r="B35" s="14" t="inlineStr">
         <is>
-          <t>38270</t>
+          <t>38205</t>
         </is>
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>Lomas Verdes II</t>
+          <t>Lindavista</t>
         </is>
       </c>
       <c r="D35" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E35" s="11" t="n">
@@ -2119,17 +2119,17 @@
       </c>
       <c r="B36" s="15" t="inlineStr">
         <is>
-          <t>38368</t>
+          <t>38207</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>Luna Park</t>
+          <t>Lindavista II</t>
         </is>
       </c>
       <c r="D36" s="8" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E36" s="7" t="n">
@@ -2157,17 +2157,17 @@
       </c>
       <c r="B37" s="14" t="inlineStr">
         <is>
-          <t>38371</t>
+          <t>38119</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>Montevideo DT</t>
+          <t>Lomas Verdes</t>
         </is>
       </c>
       <c r="D37" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E37" s="11" t="n">
@@ -2195,17 +2195,17 @@
       </c>
       <c r="B38" s="15" t="inlineStr">
         <is>
-          <t>43111</t>
+          <t>38270</t>
         </is>
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>Montevideo Insurgentes</t>
+          <t>Lomas Verdes II</t>
         </is>
       </c>
       <c r="D38" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E38" s="7" t="n">
@@ -2233,17 +2233,17 @@
       </c>
       <c r="B39" s="14" t="inlineStr">
         <is>
-          <t>38674</t>
+          <t>38368</t>
         </is>
       </c>
       <c r="C39" s="12" t="inlineStr">
         <is>
-          <t>Mundo E</t>
+          <t>Luna Park</t>
         </is>
       </c>
       <c r="D39" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E39" s="11" t="n">
@@ -2271,17 +2271,17 @@
       </c>
       <c r="B40" s="15" t="inlineStr">
         <is>
-          <t>38845</t>
+          <t>38371</t>
         </is>
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>Mundo E II</t>
+          <t>Montevideo DT</t>
         </is>
       </c>
       <c r="D40" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E40" s="7" t="n">
@@ -2309,12 +2309,12 @@
       </c>
       <c r="B41" s="14" t="inlineStr">
         <is>
-          <t>43195</t>
+          <t>43111</t>
         </is>
       </c>
       <c r="C41" s="12" t="inlineStr">
         <is>
-          <t>Parque Jadin kiosko</t>
+          <t>Montevideo Insurgentes</t>
         </is>
       </c>
       <c r="D41" s="12" t="inlineStr">
@@ -2347,17 +2347,17 @@
       </c>
       <c r="B42" s="15" t="inlineStr">
         <is>
-          <t>38937</t>
+          <t>38674</t>
         </is>
       </c>
       <c r="C42" s="8" t="inlineStr">
         <is>
-          <t>Parque Tepeyac Piso 1</t>
+          <t>Mundo E</t>
         </is>
       </c>
       <c r="D42" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E42" s="7" t="n">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="B43" s="14" t="inlineStr">
         <is>
-          <t>38965</t>
+          <t>38845</t>
         </is>
       </c>
       <c r="C43" s="12" t="inlineStr">
         <is>
-          <t>Parque Tepeyac Piso 2</t>
+          <t>Mundo E II</t>
         </is>
       </c>
       <c r="D43" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E43" s="11" t="n">
@@ -2423,17 +2423,17 @@
       </c>
       <c r="B44" s="15" t="inlineStr">
         <is>
-          <t>38561</t>
+          <t>43195</t>
         </is>
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t>Parque Toreo</t>
+          <t>Parque Jadin kiosko</t>
         </is>
       </c>
       <c r="D44" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E44" s="7" t="n">
@@ -2461,17 +2461,17 @@
       </c>
       <c r="B45" s="14" t="inlineStr">
         <is>
-          <t>38590</t>
+          <t>38937</t>
         </is>
       </c>
       <c r="C45" s="12" t="inlineStr">
         <is>
-          <t>Parque Toreo II</t>
+          <t>Parque Tepeyac Piso 1</t>
         </is>
       </c>
       <c r="D45" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E45" s="11" t="n">
@@ -2499,17 +2499,17 @@
       </c>
       <c r="B46" s="15" t="inlineStr">
         <is>
-          <t>38792</t>
+          <t>38561</t>
         </is>
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t>Pasaje Tlanepantla</t>
+          <t>Parque Toreo</t>
         </is>
       </c>
       <c r="D46" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E46" s="7" t="n">
@@ -2537,17 +2537,17 @@
       </c>
       <c r="B47" s="14" t="inlineStr">
         <is>
-          <t>38546</t>
+          <t>38792</t>
         </is>
       </c>
       <c r="C47" s="12" t="inlineStr">
         <is>
-          <t>Patio Claveria</t>
+          <t>Pasaje Tlanepantla</t>
         </is>
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E47" s="11" t="n">
@@ -2575,17 +2575,17 @@
       </c>
       <c r="B48" s="15" t="inlineStr">
         <is>
-          <t>38515</t>
+          <t>38546</t>
         </is>
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
-          <t>Patio Ecatepec</t>
+          <t>Patio Claveria</t>
         </is>
       </c>
       <c r="D48" s="8" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E48" s="7" t="n">
@@ -2613,17 +2613,17 @@
       </c>
       <c r="B49" s="14" t="inlineStr">
         <is>
-          <t>38677</t>
+          <t>38515</t>
         </is>
       </c>
       <c r="C49" s="12" t="inlineStr">
         <is>
-          <t>Patio la Raza</t>
+          <t>Patio Ecatepec</t>
         </is>
       </c>
       <c r="D49" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E49" s="11" t="n">
@@ -2651,17 +2651,17 @@
       </c>
       <c r="B50" s="15" t="inlineStr">
         <is>
-          <t>38176</t>
+          <t>38677</t>
         </is>
       </c>
       <c r="C50" s="8" t="inlineStr">
         <is>
-          <t>Periferico Satélite DT</t>
+          <t>Patio la Raza</t>
         </is>
       </c>
       <c r="D50" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E50" s="7" t="n">
@@ -2689,17 +2689,17 @@
       </c>
       <c r="B51" s="14" t="inlineStr">
         <is>
-          <t>38924</t>
+          <t>38176</t>
         </is>
       </c>
       <c r="C51" s="12" t="inlineStr">
         <is>
-          <t>Plaza Aeropuerto</t>
+          <t>Periferico Satélite DT</t>
         </is>
       </c>
       <c r="D51" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E51" s="11" t="n">
@@ -2727,12 +2727,12 @@
       </c>
       <c r="B52" s="15" t="inlineStr">
         <is>
-          <t>38719</t>
+          <t>38924</t>
         </is>
       </c>
       <c r="C52" s="8" t="inlineStr">
         <is>
-          <t>Plaza Fortuna</t>
+          <t>Plaza Aeropuerto</t>
         </is>
       </c>
       <c r="D52" s="8" t="inlineStr">
@@ -2765,17 +2765,17 @@
       </c>
       <c r="B53" s="14" t="inlineStr">
         <is>
-          <t>38427</t>
+          <t>38719</t>
         </is>
       </c>
       <c r="C53" s="12" t="inlineStr">
         <is>
-          <t>Plaza Satelite</t>
+          <t>Plaza Fortuna</t>
         </is>
       </c>
       <c r="D53" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E53" s="11" t="n">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="B54" s="15" t="inlineStr">
         <is>
-          <t>38859</t>
+          <t>38427</t>
         </is>
       </c>
       <c r="C54" s="8" t="inlineStr">
         <is>
-          <t>Plaza Satelite II N1</t>
+          <t>Plaza Satelite</t>
         </is>
       </c>
       <c r="D54" s="8" t="inlineStr">
@@ -2841,17 +2841,17 @@
       </c>
       <c r="B55" s="14" t="inlineStr">
         <is>
-          <t>38811</t>
+          <t>38859</t>
         </is>
       </c>
       <c r="C55" s="12" t="inlineStr">
         <is>
-          <t>Plaza Tepeyac</t>
+          <t>Plaza Satelite II N1</t>
         </is>
       </c>
       <c r="D55" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E55" s="11" t="n">
@@ -2917,17 +2917,17 @@
       </c>
       <c r="B57" s="14" t="inlineStr">
         <is>
-          <t>38136</t>
+          <t>38456</t>
         </is>
       </c>
       <c r="C57" s="12" t="inlineStr">
         <is>
-          <t>Punta Norte</t>
+          <t>Plaza las Flores</t>
         </is>
       </c>
       <c r="D57" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E57" s="11" t="n">
@@ -2955,17 +2955,17 @@
       </c>
       <c r="B58" s="15" t="inlineStr">
         <is>
-          <t>43152</t>
+          <t>38136</t>
         </is>
       </c>
       <c r="C58" s="8" t="inlineStr">
         <is>
-          <t>Samara Satélite</t>
+          <t>Punta Norte</t>
         </is>
       </c>
       <c r="D58" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E58" s="7" t="n">
@@ -2993,17 +2993,17 @@
       </c>
       <c r="B59" s="14" t="inlineStr">
         <is>
-          <t>38339</t>
+          <t>43152</t>
         </is>
       </c>
       <c r="C59" s="12" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Samara Satélite</t>
         </is>
       </c>
       <c r="D59" s="12" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E59" s="11" t="n">
@@ -3031,17 +3031,17 @@
       </c>
       <c r="B60" s="15" t="inlineStr">
         <is>
-          <t>38266</t>
+          <t>38339</t>
         </is>
       </c>
       <c r="C60" s="8" t="inlineStr">
         <is>
-          <t>San Mateo</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="D60" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E60" s="7" t="n">
@@ -3069,17 +3069,17 @@
       </c>
       <c r="B61" s="14" t="inlineStr">
         <is>
-          <t>38862</t>
+          <t>38266</t>
         </is>
       </c>
       <c r="C61" s="12" t="inlineStr">
         <is>
-          <t>San Miguel Izcalli</t>
+          <t>San Mateo</t>
         </is>
       </c>
       <c r="D61" s="12" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E61" s="11" t="n">
@@ -3107,17 +3107,17 @@
       </c>
       <c r="B62" s="15" t="inlineStr">
         <is>
-          <t>38460</t>
+          <t>38862</t>
         </is>
       </c>
       <c r="C62" s="8" t="inlineStr">
         <is>
-          <t>Santa Monica</t>
+          <t>San Miguel Izcalli</t>
         </is>
       </c>
       <c r="D62" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E62" s="7" t="n">
@@ -3145,17 +3145,17 @@
       </c>
       <c r="B63" s="14" t="inlineStr">
         <is>
-          <t>38117</t>
+          <t>38460</t>
         </is>
       </c>
       <c r="C63" s="12" t="inlineStr">
         <is>
-          <t>Satelite</t>
+          <t>Santa Monica</t>
         </is>
       </c>
       <c r="D63" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E63" s="11" t="n">
@@ -3183,12 +3183,12 @@
       </c>
       <c r="B64" s="15" t="inlineStr">
         <is>
-          <t>38475</t>
+          <t>38117</t>
         </is>
       </c>
       <c r="C64" s="8" t="inlineStr">
         <is>
-          <t>Satelite Centro Civico</t>
+          <t>Satelite</t>
         </is>
       </c>
       <c r="D64" s="8" t="inlineStr">
@@ -3221,17 +3221,17 @@
       </c>
       <c r="B65" s="14" t="inlineStr">
         <is>
-          <t>38442</t>
+          <t>38475</t>
         </is>
       </c>
       <c r="C65" s="12" t="inlineStr">
         <is>
-          <t>Sor Juana</t>
+          <t>Satelite Centro Civico</t>
         </is>
       </c>
       <c r="D65" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E65" s="11" t="n">
@@ -3259,17 +3259,17 @@
       </c>
       <c r="B66" s="15" t="inlineStr">
         <is>
-          <t>38925</t>
+          <t>38442</t>
         </is>
       </c>
       <c r="C66" s="8" t="inlineStr">
         <is>
-          <t>Star Medica Lomas Verdes</t>
+          <t>Sor Juana</t>
         </is>
       </c>
       <c r="D66" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E66" s="7" t="n">
@@ -3297,17 +3297,17 @@
       </c>
       <c r="B67" s="14" t="inlineStr">
         <is>
-          <t>38992</t>
+          <t>38925</t>
         </is>
       </c>
       <c r="C67" s="12" t="inlineStr">
         <is>
-          <t>Tapo Puerta Oriente</t>
+          <t>Star Medica Lomas Verdes</t>
         </is>
       </c>
       <c r="D67" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E67" s="11" t="n">
@@ -3335,17 +3335,17 @@
       </c>
       <c r="B68" s="15" t="inlineStr">
         <is>
-          <t>38606</t>
+          <t>38992</t>
         </is>
       </c>
       <c r="C68" s="8" t="inlineStr">
         <is>
-          <t>TlalnepantlaCarso</t>
+          <t>Tapo Puerta Oriente</t>
         </is>
       </c>
       <c r="D68" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E68" s="7" t="n">
@@ -3373,17 +3373,17 @@
       </c>
       <c r="B69" s="14" t="inlineStr">
         <is>
-          <t>38411</t>
+          <t>38606</t>
         </is>
       </c>
       <c r="C69" s="12" t="inlineStr">
         <is>
-          <t>Torres Lindavista</t>
+          <t>TlalnepantlaCarso</t>
         </is>
       </c>
       <c r="D69" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E69" s="11" t="n">
@@ -3411,17 +3411,17 @@
       </c>
       <c r="B70" s="15" t="inlineStr">
         <is>
-          <t>43130</t>
+          <t>38411</t>
         </is>
       </c>
       <c r="C70" s="8" t="inlineStr">
         <is>
-          <t>Town Center Nicolás Romero</t>
+          <t>Torres Lindavista</t>
         </is>
       </c>
       <c r="D70" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E70" s="7" t="n">
@@ -3449,17 +3449,17 @@
       </c>
       <c r="B71" s="14" t="inlineStr">
         <is>
-          <t>38374</t>
+          <t>43130</t>
         </is>
       </c>
       <c r="C71" s="12" t="inlineStr">
         <is>
-          <t>Valle Dorado</t>
+          <t>Town Center Nicolás Romero</t>
         </is>
       </c>
       <c r="D71" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E71" s="11" t="n">
@@ -3487,17 +3487,17 @@
       </c>
       <c r="B72" s="15" t="inlineStr">
         <is>
-          <t>38651</t>
+          <t>38374</t>
         </is>
       </c>
       <c r="C72" s="8" t="inlineStr">
         <is>
-          <t>Via Vallejo</t>
+          <t>Valle Dorado</t>
         </is>
       </c>
       <c r="D72" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E72" s="7" t="n">
@@ -3525,17 +3525,17 @@
       </c>
       <c r="B73" s="14" t="inlineStr">
         <is>
-          <t>38694</t>
+          <t>38651</t>
         </is>
       </c>
       <c r="C73" s="12" t="inlineStr">
         <is>
-          <t>Villas de la Hacienda</t>
+          <t>Via Vallejo</t>
         </is>
       </c>
       <c r="D73" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E73" s="11" t="n">
@@ -3563,17 +3563,17 @@
       </c>
       <c r="B74" s="15" t="inlineStr">
         <is>
-          <t>38656</t>
+          <t>38694</t>
         </is>
       </c>
       <c r="C74" s="8" t="inlineStr">
         <is>
-          <t>Viveros de la Loma</t>
+          <t>Villas de la Hacienda</t>
         </is>
       </c>
       <c r="D74" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E74" s="7" t="n">
@@ -3601,17 +3601,17 @@
       </c>
       <c r="B75" s="14" t="inlineStr">
         <is>
-          <t>38115</t>
+          <t>38656</t>
         </is>
       </c>
       <c r="C75" s="12" t="inlineStr">
         <is>
-          <t>Zona Azul</t>
+          <t>Viveros de la Loma</t>
         </is>
       </c>
       <c r="D75" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E75" s="11" t="n">
@@ -3721,7 +3721,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Centro Norte · Corte 28/08/2026 20:39</t>
+          <t>Centro Norte · Corte 29/08/2026 09:43</t>
         </is>
       </c>
     </row>
@@ -3800,7 +3800,7 @@
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D6" s="7" t="n">
         <v>72</v>
@@ -3828,7 +3828,7 @@
         </is>
       </c>
       <c r="C7" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D7" s="11" t="n">
         <v>72</v>
@@ -3912,7 +3912,7 @@
         </is>
       </c>
       <c r="C10" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D10" s="7" t="n">
         <v>72</v>
@@ -3940,7 +3940,7 @@
         </is>
       </c>
       <c r="C11" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D11" s="11" t="n">
         <v>72</v>
@@ -3968,7 +3968,7 @@
         </is>
       </c>
       <c r="C12" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D12" s="7" t="n">
         <v>72</v>

--- a/exports/Resumen_Evidencias_OPS.xlsx
+++ b/exports/Resumen_Evidencias_OPS.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Resumen" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Tiendas" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Actividades" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tiendas" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Actividades" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Resumen'!$A$9:$H$15</definedName>

--- a/exports/Resumen_Evidencias_OPS.xlsx
+++ b/exports/Resumen_Evidencias_OPS.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tiendas" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Actividades" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Resumen" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Tiendas" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Actividades" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Resumen'!$A$9:$H$15</definedName>
@@ -564,7 +564,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Centro Norte · Corte 29/08/2026 09:43</t>
+          <t>Centro Norte · Corte 29/08/2026 10:03</t>
         </is>
       </c>
     </row>
@@ -587,7 +587,7 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>576</v>
@@ -677,17 +677,17 @@
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Garcia</t>
+          <t>Nancy Carolina</t>
         </is>
       </c>
       <c r="C11" s="11" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D11" s="11" t="n">
         <v>2</v>
       </c>
       <c r="E11" s="11" t="n">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="F11" s="11" t="n">
         <v>0</v>
@@ -708,17 +708,17 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Enrique Cesar</t>
+          <t>Yazmin Garcia</t>
         </is>
       </c>
       <c r="C12" s="7" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>80</v>
+        <v>104</v>
       </c>
       <c r="F12" s="7" t="n">
         <v>0</v>
@@ -739,17 +739,17 @@
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina</t>
+          <t>Enrique Cesar</t>
         </is>
       </c>
       <c r="C13" s="11" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D13" s="11" t="n">
         <v>1</v>
       </c>
       <c r="E13" s="11" t="n">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="F13" s="11" t="n">
         <v>0</v>
@@ -884,7 +884,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Centro Norte · Corte 29/08/2026 09:43</t>
+          <t>Centro Norte · Corte 29/08/2026 10:03</t>
         </is>
       </c>
     </row>
@@ -1169,17 +1169,17 @@
       </c>
       <c r="B11" s="14" t="inlineStr">
         <is>
-          <t>38115</t>
+          <t>38136</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>Zona Azul</t>
+          <t>Punta Norte</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E11" s="11" t="n">
@@ -1207,21 +1207,21 @@
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>43194</t>
+          <t>38115</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Atana Lindavista</t>
+          <t>Zona Azul</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E12" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F12" s="7" t="n">
         <v>8</v>
@@ -1245,17 +1245,17 @@
       </c>
       <c r="B13" s="14" t="inlineStr">
         <is>
-          <t>43043</t>
+          <t>43194</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>Atizapan</t>
+          <t>Atana Lindavista</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E13" s="11" t="n">
@@ -1283,17 +1283,17 @@
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>38930</t>
+          <t>43043</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Blvd. Aeropuerto dt</t>
+          <t>Atizapan</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E14" s="7" t="n">
@@ -1321,12 +1321,12 @@
       </c>
       <c r="B15" s="14" t="inlineStr">
         <is>
-          <t>38529</t>
+          <t>38930</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>Bosques de Aragon</t>
+          <t>Blvd. Aeropuerto dt</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
@@ -1359,17 +1359,17 @@
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>38527</t>
+          <t>38529</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>Camarones</t>
+          <t>Bosques de Aragon</t>
         </is>
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E16" s="7" t="n">
@@ -1397,12 +1397,12 @@
       </c>
       <c r="B17" s="14" t="inlineStr">
         <is>
-          <t>38837</t>
+          <t>38527</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>Centenario Azcapotzalco</t>
+          <t>Camarones</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
@@ -1435,17 +1435,17 @@
       </c>
       <c r="B18" s="15" t="inlineStr">
         <is>
-          <t>38394</t>
+          <t>38837</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>Centro Comercial Lomas Verdes</t>
+          <t>Centenario Azcapotzalco</t>
         </is>
       </c>
       <c r="D18" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E18" s="7" t="n">
@@ -1473,17 +1473,17 @@
       </c>
       <c r="B19" s="14" t="inlineStr">
         <is>
-          <t>38695</t>
+          <t>38394</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>Cetram 4 Caminos</t>
+          <t>Centro Comercial Lomas Verdes</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E19" s="11" t="n">
@@ -1511,17 +1511,17 @@
       </c>
       <c r="B20" s="15" t="inlineStr">
         <is>
-          <t>38535</t>
+          <t>38695</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>City Center Esmeralda</t>
+          <t>Cetram 4 Caminos</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E20" s="7" t="n">
@@ -1549,17 +1549,17 @@
       </c>
       <c r="B21" s="14" t="inlineStr">
         <is>
-          <t>38604</t>
+          <t>38535</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>Cosmopol</t>
+          <t>City Center Esmeralda</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E21" s="11" t="n">
@@ -1587,12 +1587,12 @@
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>43193</t>
+          <t>38604</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>Cosmopol N1</t>
+          <t>Cosmopol</t>
         </is>
       </c>
       <c r="D22" s="8" t="inlineStr">
@@ -1625,17 +1625,17 @@
       </c>
       <c r="B23" s="14" t="inlineStr">
         <is>
-          <t>38197</t>
+          <t>43193</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>Echegaray</t>
+          <t>Cosmopol N1</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E23" s="11" t="n">
@@ -1663,17 +1663,17 @@
       </c>
       <c r="B24" s="15" t="inlineStr">
         <is>
-          <t>38431</t>
+          <t>38197</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>Eduardo Molina</t>
+          <t>Echegaray</t>
         </is>
       </c>
       <c r="D24" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E24" s="7" t="n">
@@ -1701,17 +1701,17 @@
       </c>
       <c r="B25" s="14" t="inlineStr">
         <is>
-          <t>38458</t>
+          <t>38431</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>El Rosario</t>
+          <t>Eduardo Molina</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E25" s="11" t="n">
@@ -1739,17 +1739,17 @@
       </c>
       <c r="B26" s="15" t="inlineStr">
         <is>
-          <t>38903</t>
+          <t>38458</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>Encuentro Oceania</t>
+          <t>El Rosario</t>
         </is>
       </c>
       <c r="D26" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E26" s="7" t="n">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="B27" s="14" t="inlineStr">
         <is>
-          <t>38995</t>
+          <t>38903</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>Encuentro Oceania II</t>
+          <t>Encuentro Oceania</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
@@ -1815,17 +1815,17 @@
       </c>
       <c r="B28" s="15" t="inlineStr">
         <is>
-          <t>38507</t>
+          <t>38995</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>Espacio Vista del Valle</t>
+          <t>Encuentro Oceania II</t>
         </is>
       </c>
       <c r="D28" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E28" s="7" t="n">
@@ -1853,12 +1853,12 @@
       </c>
       <c r="B29" s="14" t="inlineStr">
         <is>
-          <t>38363</t>
+          <t>38507</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>Galerias Atizapan</t>
+          <t>Espacio Vista del Valle</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr">
@@ -1891,17 +1891,17 @@
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>38894</t>
+          <t>38363</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>Galerias Perinorte</t>
+          <t>Galerias Atizapan</t>
         </is>
       </c>
       <c r="D30" s="8" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E30" s="7" t="n">
@@ -1929,17 +1929,17 @@
       </c>
       <c r="B31" s="14" t="inlineStr">
         <is>
-          <t>38770</t>
+          <t>38894</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>Gustavo Baz 29</t>
+          <t>Galerias Perinorte</t>
         </is>
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E31" s="11" t="n">
@@ -1967,17 +1967,17 @@
       </c>
       <c r="B32" s="15" t="inlineStr">
         <is>
-          <t>38230</t>
+          <t>38770</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>ITEMS Edo de Mexico</t>
+          <t>Gustavo Baz 29</t>
         </is>
       </c>
       <c r="D32" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E32" s="7" t="n">
@@ -2005,17 +2005,17 @@
       </c>
       <c r="B33" s="14" t="inlineStr">
         <is>
-          <t>38333</t>
+          <t>38230</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>Izcalli Mega</t>
+          <t>ITEMS Edo de Mexico</t>
         </is>
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E33" s="11" t="n">
@@ -2043,17 +2043,17 @@
       </c>
       <c r="B34" s="15" t="inlineStr">
         <is>
-          <t>38661</t>
+          <t>38333</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>Jinetes</t>
+          <t>Izcalli Mega</t>
         </is>
       </c>
       <c r="D34" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E34" s="7" t="n">
@@ -2081,17 +2081,17 @@
       </c>
       <c r="B35" s="14" t="inlineStr">
         <is>
-          <t>38205</t>
+          <t>38661</t>
         </is>
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>Lindavista</t>
+          <t>Jinetes</t>
         </is>
       </c>
       <c r="D35" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E35" s="11" t="n">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="B36" s="15" t="inlineStr">
         <is>
-          <t>38207</t>
+          <t>38205</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>Lindavista II</t>
+          <t>Lindavista</t>
         </is>
       </c>
       <c r="D36" s="8" t="inlineStr">
@@ -2157,17 +2157,17 @@
       </c>
       <c r="B37" s="14" t="inlineStr">
         <is>
-          <t>38119</t>
+          <t>38207</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>Lomas Verdes</t>
+          <t>Lindavista II</t>
         </is>
       </c>
       <c r="D37" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E37" s="11" t="n">
@@ -2195,12 +2195,12 @@
       </c>
       <c r="B38" s="15" t="inlineStr">
         <is>
-          <t>38270</t>
+          <t>38119</t>
         </is>
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>Lomas Verdes II</t>
+          <t>Lomas Verdes</t>
         </is>
       </c>
       <c r="D38" s="8" t="inlineStr">
@@ -2233,17 +2233,17 @@
       </c>
       <c r="B39" s="14" t="inlineStr">
         <is>
-          <t>38368</t>
+          <t>38270</t>
         </is>
       </c>
       <c r="C39" s="12" t="inlineStr">
         <is>
-          <t>Luna Park</t>
+          <t>Lomas Verdes II</t>
         </is>
       </c>
       <c r="D39" s="12" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E39" s="11" t="n">
@@ -2271,17 +2271,17 @@
       </c>
       <c r="B40" s="15" t="inlineStr">
         <is>
-          <t>38371</t>
+          <t>38368</t>
         </is>
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>Montevideo DT</t>
+          <t>Luna Park</t>
         </is>
       </c>
       <c r="D40" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E40" s="7" t="n">
@@ -2309,12 +2309,12 @@
       </c>
       <c r="B41" s="14" t="inlineStr">
         <is>
-          <t>43111</t>
+          <t>38371</t>
         </is>
       </c>
       <c r="C41" s="12" t="inlineStr">
         <is>
-          <t>Montevideo Insurgentes</t>
+          <t>Montevideo DT</t>
         </is>
       </c>
       <c r="D41" s="12" t="inlineStr">
@@ -2347,17 +2347,17 @@
       </c>
       <c r="B42" s="15" t="inlineStr">
         <is>
-          <t>38674</t>
+          <t>43111</t>
         </is>
       </c>
       <c r="C42" s="8" t="inlineStr">
         <is>
-          <t>Mundo E</t>
+          <t>Montevideo Insurgentes</t>
         </is>
       </c>
       <c r="D42" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E42" s="7" t="n">
@@ -2385,12 +2385,12 @@
       </c>
       <c r="B43" s="14" t="inlineStr">
         <is>
-          <t>38845</t>
+          <t>38674</t>
         </is>
       </c>
       <c r="C43" s="12" t="inlineStr">
         <is>
-          <t>Mundo E II</t>
+          <t>Mundo E</t>
         </is>
       </c>
       <c r="D43" s="12" t="inlineStr">
@@ -2423,17 +2423,17 @@
       </c>
       <c r="B44" s="15" t="inlineStr">
         <is>
-          <t>43195</t>
+          <t>38845</t>
         </is>
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t>Parque Jadin kiosko</t>
+          <t>Mundo E II</t>
         </is>
       </c>
       <c r="D44" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E44" s="7" t="n">
@@ -2461,17 +2461,17 @@
       </c>
       <c r="B45" s="14" t="inlineStr">
         <is>
-          <t>38937</t>
+          <t>43195</t>
         </is>
       </c>
       <c r="C45" s="12" t="inlineStr">
         <is>
-          <t>Parque Tepeyac Piso 1</t>
+          <t>Parque Jadin kiosko</t>
         </is>
       </c>
       <c r="D45" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E45" s="11" t="n">
@@ -2499,17 +2499,17 @@
       </c>
       <c r="B46" s="15" t="inlineStr">
         <is>
-          <t>38561</t>
+          <t>38937</t>
         </is>
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t>Parque Toreo</t>
+          <t>Parque Tepeyac Piso 1</t>
         </is>
       </c>
       <c r="D46" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E46" s="7" t="n">
@@ -2537,17 +2537,17 @@
       </c>
       <c r="B47" s="14" t="inlineStr">
         <is>
-          <t>38792</t>
+          <t>38561</t>
         </is>
       </c>
       <c r="C47" s="12" t="inlineStr">
         <is>
-          <t>Pasaje Tlanepantla</t>
+          <t>Parque Toreo</t>
         </is>
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E47" s="11" t="n">
@@ -2575,17 +2575,17 @@
       </c>
       <c r="B48" s="15" t="inlineStr">
         <is>
-          <t>38546</t>
+          <t>38792</t>
         </is>
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
-          <t>Patio Claveria</t>
+          <t>Pasaje Tlanepantla</t>
         </is>
       </c>
       <c r="D48" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E48" s="7" t="n">
@@ -2613,17 +2613,17 @@
       </c>
       <c r="B49" s="14" t="inlineStr">
         <is>
-          <t>38515</t>
+          <t>38546</t>
         </is>
       </c>
       <c r="C49" s="12" t="inlineStr">
         <is>
-          <t>Patio Ecatepec</t>
+          <t>Patio Claveria</t>
         </is>
       </c>
       <c r="D49" s="12" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E49" s="11" t="n">
@@ -2651,17 +2651,17 @@
       </c>
       <c r="B50" s="15" t="inlineStr">
         <is>
-          <t>38677</t>
+          <t>38515</t>
         </is>
       </c>
       <c r="C50" s="8" t="inlineStr">
         <is>
-          <t>Patio la Raza</t>
+          <t>Patio Ecatepec</t>
         </is>
       </c>
       <c r="D50" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E50" s="7" t="n">
@@ -2689,17 +2689,17 @@
       </c>
       <c r="B51" s="14" t="inlineStr">
         <is>
-          <t>38176</t>
+          <t>38677</t>
         </is>
       </c>
       <c r="C51" s="12" t="inlineStr">
         <is>
-          <t>Periferico Satélite DT</t>
+          <t>Patio la Raza</t>
         </is>
       </c>
       <c r="D51" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E51" s="11" t="n">
@@ -2727,17 +2727,17 @@
       </c>
       <c r="B52" s="15" t="inlineStr">
         <is>
-          <t>38924</t>
+          <t>38176</t>
         </is>
       </c>
       <c r="C52" s="8" t="inlineStr">
         <is>
-          <t>Plaza Aeropuerto</t>
+          <t>Periferico Satélite DT</t>
         </is>
       </c>
       <c r="D52" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E52" s="7" t="n">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="B53" s="14" t="inlineStr">
         <is>
-          <t>38719</t>
+          <t>38924</t>
         </is>
       </c>
       <c r="C53" s="12" t="inlineStr">
         <is>
-          <t>Plaza Fortuna</t>
+          <t>Plaza Aeropuerto</t>
         </is>
       </c>
       <c r="D53" s="12" t="inlineStr">
@@ -2803,17 +2803,17 @@
       </c>
       <c r="B54" s="15" t="inlineStr">
         <is>
-          <t>38427</t>
+          <t>38719</t>
         </is>
       </c>
       <c r="C54" s="8" t="inlineStr">
         <is>
-          <t>Plaza Satelite</t>
+          <t>Plaza Fortuna</t>
         </is>
       </c>
       <c r="D54" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E54" s="7" t="n">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="B55" s="14" t="inlineStr">
         <is>
-          <t>38859</t>
+          <t>38427</t>
         </is>
       </c>
       <c r="C55" s="12" t="inlineStr">
         <is>
-          <t>Plaza Satelite II N1</t>
+          <t>Plaza Satelite</t>
         </is>
       </c>
       <c r="D55" s="12" t="inlineStr">
@@ -2879,17 +2879,17 @@
       </c>
       <c r="B56" s="15" t="inlineStr">
         <is>
-          <t>43132</t>
+          <t>38859</t>
         </is>
       </c>
       <c r="C56" s="8" t="inlineStr">
         <is>
-          <t>Plaza Vista Norte</t>
+          <t>Plaza Satelite II N1</t>
         </is>
       </c>
       <c r="D56" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E56" s="7" t="n">
@@ -2917,17 +2917,17 @@
       </c>
       <c r="B57" s="14" t="inlineStr">
         <is>
-          <t>38456</t>
+          <t>43132</t>
         </is>
       </c>
       <c r="C57" s="12" t="inlineStr">
         <is>
-          <t>Plaza las Flores</t>
+          <t>Plaza Vista Norte</t>
         </is>
       </c>
       <c r="D57" s="12" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E57" s="11" t="n">
@@ -2955,17 +2955,17 @@
       </c>
       <c r="B58" s="15" t="inlineStr">
         <is>
-          <t>38136</t>
+          <t>38456</t>
         </is>
       </c>
       <c r="C58" s="8" t="inlineStr">
         <is>
-          <t>Punta Norte</t>
+          <t>Plaza las Flores</t>
         </is>
       </c>
       <c r="D58" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E58" s="7" t="n">
@@ -3721,7 +3721,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Centro Norte · Corte 29/08/2026 09:43</t>
+          <t>Centro Norte · Corte 29/08/2026 10:03</t>
         </is>
       </c>
     </row>
@@ -3856,7 +3856,7 @@
         </is>
       </c>
       <c r="C8" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D8" s="7" t="n">
         <v>72</v>

--- a/exports/Resumen_Evidencias_OPS.xlsx
+++ b/exports/Resumen_Evidencias_OPS.xlsx
@@ -564,7 +564,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Centro Norte · Corte 29/08/2026 10:03</t>
+          <t>Centro Norte · Corte 29/08/2026 12:13</t>
         </is>
       </c>
     </row>
@@ -587,7 +587,7 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>576</v>
@@ -646,17 +646,17 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia</t>
+          <t>Enrique Cesar</t>
         </is>
       </c>
       <c r="C10" s="7" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D10" s="7" t="n">
         <v>2</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="F10" s="7" t="n">
         <v>0</v>
@@ -684,7 +684,7 @@
         <v>12</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E11" s="11" t="n">
         <v>96</v>
@@ -708,14 +708,14 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Garcia</t>
+          <t>Vanessa Carreño</t>
         </is>
       </c>
       <c r="C12" s="7" t="n">
         <v>13</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E12" s="7" t="n">
         <v>104</v>
@@ -739,17 +739,17 @@
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>Enrique Cesar</t>
+          <t>Veronica Garcia</t>
         </is>
       </c>
       <c r="C13" s="11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D13" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E13" s="11" t="n">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="F13" s="11" t="n">
         <v>0</v>
@@ -777,7 +777,7 @@
         <v>13</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E14" s="7" t="n">
         <v>104</v>
@@ -801,7 +801,7 @@
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño</t>
+          <t>Yazmin Garcia</t>
         </is>
       </c>
       <c r="C15" s="11" t="n">
@@ -884,7 +884,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Centro Norte · Corte 29/08/2026 10:03</t>
+          <t>Centro Norte · Corte 29/08/2026 12:13</t>
         </is>
       </c>
     </row>
@@ -941,17 +941,17 @@
       </c>
       <c r="B5" s="14" t="inlineStr">
         <is>
-          <t>38186</t>
+          <t>38894</t>
         </is>
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>Arboledas</t>
+          <t>Galerias Perinorte</t>
         </is>
       </c>
       <c r="D5" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E5" s="11" t="n">
@@ -979,17 +979,17 @@
       </c>
       <c r="B6" s="15" t="inlineStr">
         <is>
-          <t>38149</t>
+          <t>38333</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>Bellavista</t>
+          <t>Izcalli Mega</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E6" s="7" t="n">
@@ -1017,21 +1017,21 @@
       </c>
       <c r="B7" s="14" t="inlineStr">
         <is>
-          <t>38401</t>
+          <t>38186</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>Coacalco</t>
+          <t>Arboledas</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E7" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7" s="11" t="n">
         <v>8</v>
@@ -1055,21 +1055,21 @@
       </c>
       <c r="B8" s="15" t="inlineStr">
         <is>
-          <t>38965</t>
+          <t>43194</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>Parque Tepeyac Piso 2</t>
+          <t>Atana Lindavista</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E8" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F8" s="7" t="n">
         <v>8</v>
@@ -1093,21 +1093,21 @@
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>38590</t>
+          <t>43043</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>Parque Toreo II</t>
+          <t>Atizapan</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E9" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F9" s="11" t="n">
         <v>8</v>
@@ -1131,21 +1131,21 @@
       </c>
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>38811</t>
+          <t>38149</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>Plaza Tepeyac</t>
+          <t>Bellavista</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E10" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F10" s="7" t="n">
         <v>8</v>
@@ -1169,21 +1169,21 @@
       </c>
       <c r="B11" s="14" t="inlineStr">
         <is>
-          <t>38136</t>
+          <t>38930</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>Punta Norte</t>
+          <t>Blvd. Aeropuerto dt</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E11" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F11" s="11" t="n">
         <v>8</v>
@@ -1207,21 +1207,21 @@
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>38115</t>
+          <t>38529</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Zona Azul</t>
+          <t>Bosques de Aragon</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E12" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F12" s="7" t="n">
         <v>8</v>
@@ -1245,12 +1245,12 @@
       </c>
       <c r="B13" s="14" t="inlineStr">
         <is>
-          <t>43194</t>
+          <t>38527</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>Atana Lindavista</t>
+          <t>Camarones</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
@@ -1283,17 +1283,17 @@
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>43043</t>
+          <t>38837</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Atizapan</t>
+          <t>Centenario Azcapotzalco</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E14" s="7" t="n">
@@ -1321,17 +1321,17 @@
       </c>
       <c r="B15" s="14" t="inlineStr">
         <is>
-          <t>38930</t>
+          <t>38394</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>Blvd. Aeropuerto dt</t>
+          <t>Centro Comercial Lomas Verdes</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E15" s="11" t="n">
@@ -1359,17 +1359,17 @@
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>38529</t>
+          <t>38695</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>Bosques de Aragon</t>
+          <t>Cetram 4 Caminos</t>
         </is>
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E16" s="7" t="n">
@@ -1397,17 +1397,17 @@
       </c>
       <c r="B17" s="14" t="inlineStr">
         <is>
-          <t>38527</t>
+          <t>38535</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>Camarones</t>
+          <t>City Center Esmeralda</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E17" s="11" t="n">
@@ -1435,17 +1435,17 @@
       </c>
       <c r="B18" s="15" t="inlineStr">
         <is>
-          <t>38837</t>
+          <t>38401</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>Centenario Azcapotzalco</t>
+          <t>Coacalco</t>
         </is>
       </c>
       <c r="D18" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E18" s="7" t="n">
@@ -1473,17 +1473,17 @@
       </c>
       <c r="B19" s="14" t="inlineStr">
         <is>
-          <t>38394</t>
+          <t>38604</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>Centro Comercial Lomas Verdes</t>
+          <t>Cosmopol</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E19" s="11" t="n">
@@ -1511,17 +1511,17 @@
       </c>
       <c r="B20" s="15" t="inlineStr">
         <is>
-          <t>38695</t>
+          <t>43193</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>Cetram 4 Caminos</t>
+          <t>Cosmopol N1</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E20" s="7" t="n">
@@ -1549,17 +1549,17 @@
       </c>
       <c r="B21" s="14" t="inlineStr">
         <is>
-          <t>38535</t>
+          <t>38197</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>City Center Esmeralda</t>
+          <t>Echegaray</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E21" s="11" t="n">
@@ -1587,17 +1587,17 @@
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>38604</t>
+          <t>38431</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>Cosmopol</t>
+          <t>Eduardo Molina</t>
         </is>
       </c>
       <c r="D22" s="8" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E22" s="7" t="n">
@@ -1625,17 +1625,17 @@
       </c>
       <c r="B23" s="14" t="inlineStr">
         <is>
-          <t>43193</t>
+          <t>38458</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>Cosmopol N1</t>
+          <t>El Rosario</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E23" s="11" t="n">
@@ -1663,17 +1663,17 @@
       </c>
       <c r="B24" s="15" t="inlineStr">
         <is>
-          <t>38197</t>
+          <t>38903</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>Echegaray</t>
+          <t>Encuentro Oceania</t>
         </is>
       </c>
       <c r="D24" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E24" s="7" t="n">
@@ -1701,12 +1701,12 @@
       </c>
       <c r="B25" s="14" t="inlineStr">
         <is>
-          <t>38431</t>
+          <t>38995</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>Eduardo Molina</t>
+          <t>Encuentro Oceania II</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
@@ -1739,17 +1739,17 @@
       </c>
       <c r="B26" s="15" t="inlineStr">
         <is>
-          <t>38458</t>
+          <t>38507</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>El Rosario</t>
+          <t>Espacio Vista del Valle</t>
         </is>
       </c>
       <c r="D26" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E26" s="7" t="n">
@@ -1777,17 +1777,17 @@
       </c>
       <c r="B27" s="14" t="inlineStr">
         <is>
-          <t>38903</t>
+          <t>38363</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>Encuentro Oceania</t>
+          <t>Galerias Atizapan</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E27" s="11" t="n">
@@ -1815,17 +1815,17 @@
       </c>
       <c r="B28" s="15" t="inlineStr">
         <is>
-          <t>38995</t>
+          <t>38770</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>Encuentro Oceania II</t>
+          <t>Gustavo Baz 29</t>
         </is>
       </c>
       <c r="D28" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E28" s="7" t="n">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="B29" s="14" t="inlineStr">
         <is>
-          <t>38507</t>
+          <t>38230</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>Espacio Vista del Valle</t>
+          <t>ITEMS Edo de Mexico</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E29" s="11" t="n">
@@ -1891,17 +1891,17 @@
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>38363</t>
+          <t>38661</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>Galerias Atizapan</t>
+          <t>Jinetes</t>
         </is>
       </c>
       <c r="D30" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E30" s="7" t="n">
@@ -1929,17 +1929,17 @@
       </c>
       <c r="B31" s="14" t="inlineStr">
         <is>
-          <t>38894</t>
+          <t>38205</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>Galerias Perinorte</t>
+          <t>Lindavista</t>
         </is>
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E31" s="11" t="n">
@@ -1967,17 +1967,17 @@
       </c>
       <c r="B32" s="15" t="inlineStr">
         <is>
-          <t>38770</t>
+          <t>38207</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>Gustavo Baz 29</t>
+          <t>Lindavista II</t>
         </is>
       </c>
       <c r="D32" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E32" s="7" t="n">
@@ -2005,17 +2005,17 @@
       </c>
       <c r="B33" s="14" t="inlineStr">
         <is>
-          <t>38230</t>
+          <t>38119</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>ITEMS Edo de Mexico</t>
+          <t>Lomas Verdes</t>
         </is>
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E33" s="11" t="n">
@@ -2043,17 +2043,17 @@
       </c>
       <c r="B34" s="15" t="inlineStr">
         <is>
-          <t>38333</t>
+          <t>38270</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>Izcalli Mega</t>
+          <t>Lomas Verdes II</t>
         </is>
       </c>
       <c r="D34" s="8" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E34" s="7" t="n">
@@ -2081,17 +2081,17 @@
       </c>
       <c r="B35" s="14" t="inlineStr">
         <is>
-          <t>38661</t>
+          <t>38368</t>
         </is>
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>Jinetes</t>
+          <t>Luna Park</t>
         </is>
       </c>
       <c r="D35" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E35" s="11" t="n">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="B36" s="15" t="inlineStr">
         <is>
-          <t>38205</t>
+          <t>38371</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>Lindavista</t>
+          <t>Montevideo DT</t>
         </is>
       </c>
       <c r="D36" s="8" t="inlineStr">
@@ -2157,12 +2157,12 @@
       </c>
       <c r="B37" s="14" t="inlineStr">
         <is>
-          <t>38207</t>
+          <t>43111</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>Lindavista II</t>
+          <t>Montevideo Insurgentes</t>
         </is>
       </c>
       <c r="D37" s="12" t="inlineStr">
@@ -2195,17 +2195,17 @@
       </c>
       <c r="B38" s="15" t="inlineStr">
         <is>
-          <t>38119</t>
+          <t>38674</t>
         </is>
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>Lomas Verdes</t>
+          <t>Mundo E</t>
         </is>
       </c>
       <c r="D38" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E38" s="7" t="n">
@@ -2233,17 +2233,17 @@
       </c>
       <c r="B39" s="14" t="inlineStr">
         <is>
-          <t>38270</t>
+          <t>38845</t>
         </is>
       </c>
       <c r="C39" s="12" t="inlineStr">
         <is>
-          <t>Lomas Verdes II</t>
+          <t>Mundo E II</t>
         </is>
       </c>
       <c r="D39" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E39" s="11" t="n">
@@ -2271,17 +2271,17 @@
       </c>
       <c r="B40" s="15" t="inlineStr">
         <is>
-          <t>38368</t>
+          <t>43195</t>
         </is>
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>Luna Park</t>
+          <t>Parque Jadin kiosko</t>
         </is>
       </c>
       <c r="D40" s="8" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E40" s="7" t="n">
@@ -2309,17 +2309,17 @@
       </c>
       <c r="B41" s="14" t="inlineStr">
         <is>
-          <t>38371</t>
+          <t>38937</t>
         </is>
       </c>
       <c r="C41" s="12" t="inlineStr">
         <is>
-          <t>Montevideo DT</t>
+          <t>Parque Tepeyac Piso 1</t>
         </is>
       </c>
       <c r="D41" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E41" s="11" t="n">
@@ -2347,17 +2347,17 @@
       </c>
       <c r="B42" s="15" t="inlineStr">
         <is>
-          <t>43111</t>
+          <t>38965</t>
         </is>
       </c>
       <c r="C42" s="8" t="inlineStr">
         <is>
-          <t>Montevideo Insurgentes</t>
+          <t>Parque Tepeyac Piso 2</t>
         </is>
       </c>
       <c r="D42" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E42" s="7" t="n">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="B43" s="14" t="inlineStr">
         <is>
-          <t>38674</t>
+          <t>38561</t>
         </is>
       </c>
       <c r="C43" s="12" t="inlineStr">
         <is>
-          <t>Mundo E</t>
+          <t>Parque Toreo</t>
         </is>
       </c>
       <c r="D43" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E43" s="11" t="n">
@@ -2423,17 +2423,17 @@
       </c>
       <c r="B44" s="15" t="inlineStr">
         <is>
-          <t>38845</t>
+          <t>38590</t>
         </is>
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t>Mundo E II</t>
+          <t>Parque Toreo II</t>
         </is>
       </c>
       <c r="D44" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E44" s="7" t="n">
@@ -2461,17 +2461,17 @@
       </c>
       <c r="B45" s="14" t="inlineStr">
         <is>
-          <t>43195</t>
+          <t>38792</t>
         </is>
       </c>
       <c r="C45" s="12" t="inlineStr">
         <is>
-          <t>Parque Jadin kiosko</t>
+          <t>Pasaje Tlanepantla</t>
         </is>
       </c>
       <c r="D45" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E45" s="11" t="n">
@@ -2499,17 +2499,17 @@
       </c>
       <c r="B46" s="15" t="inlineStr">
         <is>
-          <t>38937</t>
+          <t>38546</t>
         </is>
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t>Parque Tepeyac Piso 1</t>
+          <t>Patio Claveria</t>
         </is>
       </c>
       <c r="D46" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E46" s="7" t="n">
@@ -2537,17 +2537,17 @@
       </c>
       <c r="B47" s="14" t="inlineStr">
         <is>
-          <t>38561</t>
+          <t>38515</t>
         </is>
       </c>
       <c r="C47" s="12" t="inlineStr">
         <is>
-          <t>Parque Toreo</t>
+          <t>Patio Ecatepec</t>
         </is>
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E47" s="11" t="n">
@@ -2575,17 +2575,17 @@
       </c>
       <c r="B48" s="15" t="inlineStr">
         <is>
-          <t>38792</t>
+          <t>38677</t>
         </is>
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
-          <t>Pasaje Tlanepantla</t>
+          <t>Patio la Raza</t>
         </is>
       </c>
       <c r="D48" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E48" s="7" t="n">
@@ -2613,17 +2613,17 @@
       </c>
       <c r="B49" s="14" t="inlineStr">
         <is>
-          <t>38546</t>
+          <t>38176</t>
         </is>
       </c>
       <c r="C49" s="12" t="inlineStr">
         <is>
-          <t>Patio Claveria</t>
+          <t>Periferico Satélite DT</t>
         </is>
       </c>
       <c r="D49" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E49" s="11" t="n">
@@ -2651,17 +2651,17 @@
       </c>
       <c r="B50" s="15" t="inlineStr">
         <is>
-          <t>38515</t>
+          <t>38924</t>
         </is>
       </c>
       <c r="C50" s="8" t="inlineStr">
         <is>
-          <t>Patio Ecatepec</t>
+          <t>Plaza Aeropuerto</t>
         </is>
       </c>
       <c r="D50" s="8" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E50" s="7" t="n">
@@ -2689,17 +2689,17 @@
       </c>
       <c r="B51" s="14" t="inlineStr">
         <is>
-          <t>38677</t>
+          <t>38719</t>
         </is>
       </c>
       <c r="C51" s="12" t="inlineStr">
         <is>
-          <t>Patio la Raza</t>
+          <t>Plaza Fortuna</t>
         </is>
       </c>
       <c r="D51" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E51" s="11" t="n">
@@ -2727,12 +2727,12 @@
       </c>
       <c r="B52" s="15" t="inlineStr">
         <is>
-          <t>38176</t>
+          <t>38427</t>
         </is>
       </c>
       <c r="C52" s="8" t="inlineStr">
         <is>
-          <t>Periferico Satélite DT</t>
+          <t>Plaza Satelite</t>
         </is>
       </c>
       <c r="D52" s="8" t="inlineStr">
@@ -2765,17 +2765,17 @@
       </c>
       <c r="B53" s="14" t="inlineStr">
         <is>
-          <t>38924</t>
+          <t>38859</t>
         </is>
       </c>
       <c r="C53" s="12" t="inlineStr">
         <is>
-          <t>Plaza Aeropuerto</t>
+          <t>Plaza Satelite II N1</t>
         </is>
       </c>
       <c r="D53" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E53" s="11" t="n">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="B54" s="15" t="inlineStr">
         <is>
-          <t>38719</t>
+          <t>38811</t>
         </is>
       </c>
       <c r="C54" s="8" t="inlineStr">
         <is>
-          <t>Plaza Fortuna</t>
+          <t>Plaza Tepeyac</t>
         </is>
       </c>
       <c r="D54" s="8" t="inlineStr">
@@ -2841,17 +2841,17 @@
       </c>
       <c r="B55" s="14" t="inlineStr">
         <is>
-          <t>38427</t>
+          <t>43132</t>
         </is>
       </c>
       <c r="C55" s="12" t="inlineStr">
         <is>
-          <t>Plaza Satelite</t>
+          <t>Plaza Vista Norte</t>
         </is>
       </c>
       <c r="D55" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E55" s="11" t="n">
@@ -2879,17 +2879,17 @@
       </c>
       <c r="B56" s="15" t="inlineStr">
         <is>
-          <t>38859</t>
+          <t>38456</t>
         </is>
       </c>
       <c r="C56" s="8" t="inlineStr">
         <is>
-          <t>Plaza Satelite II N1</t>
+          <t>Plaza las Flores</t>
         </is>
       </c>
       <c r="D56" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E56" s="7" t="n">
@@ -2917,17 +2917,17 @@
       </c>
       <c r="B57" s="14" t="inlineStr">
         <is>
-          <t>43132</t>
+          <t>38136</t>
         </is>
       </c>
       <c r="C57" s="12" t="inlineStr">
         <is>
-          <t>Plaza Vista Norte</t>
+          <t>Punta Norte</t>
         </is>
       </c>
       <c r="D57" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E57" s="11" t="n">
@@ -2955,17 +2955,17 @@
       </c>
       <c r="B58" s="15" t="inlineStr">
         <is>
-          <t>38456</t>
+          <t>43152</t>
         </is>
       </c>
       <c r="C58" s="8" t="inlineStr">
         <is>
-          <t>Plaza las Flores</t>
+          <t>Samara Satélite</t>
         </is>
       </c>
       <c r="D58" s="8" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E58" s="7" t="n">
@@ -2993,17 +2993,17 @@
       </c>
       <c r="B59" s="14" t="inlineStr">
         <is>
-          <t>43152</t>
+          <t>38339</t>
         </is>
       </c>
       <c r="C59" s="12" t="inlineStr">
         <is>
-          <t>Samara Satélite</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="D59" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E59" s="11" t="n">
@@ -3031,17 +3031,17 @@
       </c>
       <c r="B60" s="15" t="inlineStr">
         <is>
-          <t>38339</t>
+          <t>38266</t>
         </is>
       </c>
       <c r="C60" s="8" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>San Mateo</t>
         </is>
       </c>
       <c r="D60" s="8" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E60" s="7" t="n">
@@ -3069,17 +3069,17 @@
       </c>
       <c r="B61" s="14" t="inlineStr">
         <is>
-          <t>38266</t>
+          <t>38862</t>
         </is>
       </c>
       <c r="C61" s="12" t="inlineStr">
         <is>
-          <t>San Mateo</t>
+          <t>San Miguel Izcalli</t>
         </is>
       </c>
       <c r="D61" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E61" s="11" t="n">
@@ -3107,17 +3107,17 @@
       </c>
       <c r="B62" s="15" t="inlineStr">
         <is>
-          <t>38862</t>
+          <t>38460</t>
         </is>
       </c>
       <c r="C62" s="8" t="inlineStr">
         <is>
-          <t>San Miguel Izcalli</t>
+          <t>Santa Monica</t>
         </is>
       </c>
       <c r="D62" s="8" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E62" s="7" t="n">
@@ -3145,17 +3145,17 @@
       </c>
       <c r="B63" s="14" t="inlineStr">
         <is>
-          <t>38460</t>
+          <t>38117</t>
         </is>
       </c>
       <c r="C63" s="12" t="inlineStr">
         <is>
-          <t>Santa Monica</t>
+          <t>Satelite</t>
         </is>
       </c>
       <c r="D63" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E63" s="11" t="n">
@@ -3183,12 +3183,12 @@
       </c>
       <c r="B64" s="15" t="inlineStr">
         <is>
-          <t>38117</t>
+          <t>38475</t>
         </is>
       </c>
       <c r="C64" s="8" t="inlineStr">
         <is>
-          <t>Satelite</t>
+          <t>Satelite Centro Civico</t>
         </is>
       </c>
       <c r="D64" s="8" t="inlineStr">
@@ -3221,17 +3221,17 @@
       </c>
       <c r="B65" s="14" t="inlineStr">
         <is>
-          <t>38475</t>
+          <t>38442</t>
         </is>
       </c>
       <c r="C65" s="12" t="inlineStr">
         <is>
-          <t>Satelite Centro Civico</t>
+          <t>Sor Juana</t>
         </is>
       </c>
       <c r="D65" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E65" s="11" t="n">
@@ -3259,17 +3259,17 @@
       </c>
       <c r="B66" s="15" t="inlineStr">
         <is>
-          <t>38442</t>
+          <t>38925</t>
         </is>
       </c>
       <c r="C66" s="8" t="inlineStr">
         <is>
-          <t>Sor Juana</t>
+          <t>Star Medica Lomas Verdes</t>
         </is>
       </c>
       <c r="D66" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E66" s="7" t="n">
@@ -3297,17 +3297,17 @@
       </c>
       <c r="B67" s="14" t="inlineStr">
         <is>
-          <t>38925</t>
+          <t>38992</t>
         </is>
       </c>
       <c r="C67" s="12" t="inlineStr">
         <is>
-          <t>Star Medica Lomas Verdes</t>
+          <t>Tapo Puerta Oriente</t>
         </is>
       </c>
       <c r="D67" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E67" s="11" t="n">
@@ -3335,17 +3335,17 @@
       </c>
       <c r="B68" s="15" t="inlineStr">
         <is>
-          <t>38992</t>
+          <t>38606</t>
         </is>
       </c>
       <c r="C68" s="8" t="inlineStr">
         <is>
-          <t>Tapo Puerta Oriente</t>
+          <t>TlalnepantlaCarso</t>
         </is>
       </c>
       <c r="D68" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E68" s="7" t="n">
@@ -3373,17 +3373,17 @@
       </c>
       <c r="B69" s="14" t="inlineStr">
         <is>
-          <t>38606</t>
+          <t>38411</t>
         </is>
       </c>
       <c r="C69" s="12" t="inlineStr">
         <is>
-          <t>TlalnepantlaCarso</t>
+          <t>Torres Lindavista</t>
         </is>
       </c>
       <c r="D69" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E69" s="11" t="n">
@@ -3411,17 +3411,17 @@
       </c>
       <c r="B70" s="15" t="inlineStr">
         <is>
-          <t>38411</t>
+          <t>43130</t>
         </is>
       </c>
       <c r="C70" s="8" t="inlineStr">
         <is>
-          <t>Torres Lindavista</t>
+          <t>Town Center Nicolás Romero</t>
         </is>
       </c>
       <c r="D70" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E70" s="7" t="n">
@@ -3449,17 +3449,17 @@
       </c>
       <c r="B71" s="14" t="inlineStr">
         <is>
-          <t>43130</t>
+          <t>38374</t>
         </is>
       </c>
       <c r="C71" s="12" t="inlineStr">
         <is>
-          <t>Town Center Nicolás Romero</t>
+          <t>Valle Dorado</t>
         </is>
       </c>
       <c r="D71" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E71" s="11" t="n">
@@ -3487,17 +3487,17 @@
       </c>
       <c r="B72" s="15" t="inlineStr">
         <is>
-          <t>38374</t>
+          <t>38651</t>
         </is>
       </c>
       <c r="C72" s="8" t="inlineStr">
         <is>
-          <t>Valle Dorado</t>
+          <t>Via Vallejo</t>
         </is>
       </c>
       <c r="D72" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E72" s="7" t="n">
@@ -3525,17 +3525,17 @@
       </c>
       <c r="B73" s="14" t="inlineStr">
         <is>
-          <t>38651</t>
+          <t>38694</t>
         </is>
       </c>
       <c r="C73" s="12" t="inlineStr">
         <is>
-          <t>Via Vallejo</t>
+          <t>Villas de la Hacienda</t>
         </is>
       </c>
       <c r="D73" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E73" s="11" t="n">
@@ -3563,17 +3563,17 @@
       </c>
       <c r="B74" s="15" t="inlineStr">
         <is>
-          <t>38694</t>
+          <t>38656</t>
         </is>
       </c>
       <c r="C74" s="8" t="inlineStr">
         <is>
-          <t>Villas de la Hacienda</t>
+          <t>Viveros de la Loma</t>
         </is>
       </c>
       <c r="D74" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E74" s="7" t="n">
@@ -3601,17 +3601,17 @@
       </c>
       <c r="B75" s="14" t="inlineStr">
         <is>
-          <t>38656</t>
+          <t>38115</t>
         </is>
       </c>
       <c r="C75" s="12" t="inlineStr">
         <is>
-          <t>Viveros de la Loma</t>
+          <t>Zona Azul</t>
         </is>
       </c>
       <c r="D75" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E75" s="11" t="n">
@@ -3721,7 +3721,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Centro Norte · Corte 29/08/2026 10:03</t>
+          <t>Centro Norte · Corte 29/08/2026 12:13</t>
         </is>
       </c>
     </row>
@@ -3772,7 +3772,7 @@
         </is>
       </c>
       <c r="C5" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D5" s="11" t="n">
         <v>72</v>
@@ -3800,7 +3800,7 @@
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D6" s="7" t="n">
         <v>72</v>
@@ -3828,7 +3828,7 @@
         </is>
       </c>
       <c r="C7" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D7" s="11" t="n">
         <v>72</v>
@@ -3856,7 +3856,7 @@
         </is>
       </c>
       <c r="C8" s="7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D8" s="7" t="n">
         <v>72</v>
@@ -3912,7 +3912,7 @@
         </is>
       </c>
       <c r="C10" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D10" s="7" t="n">
         <v>72</v>
@@ -3940,7 +3940,7 @@
         </is>
       </c>
       <c r="C11" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D11" s="11" t="n">
         <v>72</v>
@@ -3968,7 +3968,7 @@
         </is>
       </c>
       <c r="C12" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D12" s="7" t="n">
         <v>72</v>

--- a/exports/Resumen_Evidencias_OPS.xlsx
+++ b/exports/Resumen_Evidencias_OPS.xlsx
@@ -16,7 +16,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Resumen'!$A$1:$H$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Tiendas'!$A$4:$I$76</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Tiendas'!$1:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Actividades'!$A$4:$G$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Actividades'!$A$4:$G$13</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -590,7 +590,7 @@
         <v>2</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>576</v>
+        <v>648</v>
       </c>
       <c r="E6" s="5">
         <f>IFERROR(A6/C6,0)</f>
@@ -656,7 +656,7 @@
         <v>2</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="F10" s="7" t="n">
         <v>0</v>
@@ -687,7 +687,7 @@
         <v>0</v>
       </c>
       <c r="E11" s="11" t="n">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="F11" s="11" t="n">
         <v>0</v>
@@ -718,7 +718,7 @@
         <v>0</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="F12" s="7" t="n">
         <v>0</v>
@@ -749,7 +749,7 @@
         <v>0</v>
       </c>
       <c r="E13" s="11" t="n">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="F13" s="11" t="n">
         <v>0</v>
@@ -780,7 +780,7 @@
         <v>0</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="F14" s="7" t="n">
         <v>0</v>
@@ -811,7 +811,7 @@
         <v>0</v>
       </c>
       <c r="E15" s="11" t="n">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="F15" s="11" t="n">
         <v>0</v>
@@ -958,7 +958,7 @@
         <v>1</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G5" s="11" t="n">
         <v>0</v>
@@ -996,7 +996,7 @@
         <v>1</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G6" s="7" t="n">
         <v>0</v>
@@ -1034,7 +1034,7 @@
         <v>0</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G7" s="11" t="n">
         <v>0</v>
@@ -1072,7 +1072,7 @@
         <v>0</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G8" s="7" t="n">
         <v>0</v>
@@ -1110,7 +1110,7 @@
         <v>0</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G9" s="11" t="n">
         <v>0</v>
@@ -1148,7 +1148,7 @@
         <v>0</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G10" s="7" t="n">
         <v>0</v>
@@ -1186,7 +1186,7 @@
         <v>0</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G11" s="11" t="n">
         <v>0</v>
@@ -1224,7 +1224,7 @@
         <v>0</v>
       </c>
       <c r="F12" s="7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G12" s="7" t="n">
         <v>0</v>
@@ -1262,7 +1262,7 @@
         <v>0</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G13" s="11" t="n">
         <v>0</v>
@@ -1300,7 +1300,7 @@
         <v>0</v>
       </c>
       <c r="F14" s="7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G14" s="7" t="n">
         <v>0</v>
@@ -1338,7 +1338,7 @@
         <v>0</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G15" s="11" t="n">
         <v>0</v>
@@ -1376,7 +1376,7 @@
         <v>0</v>
       </c>
       <c r="F16" s="7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G16" s="7" t="n">
         <v>0</v>
@@ -1414,7 +1414,7 @@
         <v>0</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G17" s="11" t="n">
         <v>0</v>
@@ -1452,7 +1452,7 @@
         <v>0</v>
       </c>
       <c r="F18" s="7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G18" s="7" t="n">
         <v>0</v>
@@ -1490,7 +1490,7 @@
         <v>0</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G19" s="11" t="n">
         <v>0</v>
@@ -1528,7 +1528,7 @@
         <v>0</v>
       </c>
       <c r="F20" s="7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G20" s="7" t="n">
         <v>0</v>
@@ -1566,7 +1566,7 @@
         <v>0</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G21" s="11" t="n">
         <v>0</v>
@@ -1604,7 +1604,7 @@
         <v>0</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G22" s="7" t="n">
         <v>0</v>
@@ -1642,7 +1642,7 @@
         <v>0</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G23" s="11" t="n">
         <v>0</v>
@@ -1680,7 +1680,7 @@
         <v>0</v>
       </c>
       <c r="F24" s="7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G24" s="7" t="n">
         <v>0</v>
@@ -1718,7 +1718,7 @@
         <v>0</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G25" s="11" t="n">
         <v>0</v>
@@ -1756,7 +1756,7 @@
         <v>0</v>
       </c>
       <c r="F26" s="7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G26" s="7" t="n">
         <v>0</v>
@@ -1794,7 +1794,7 @@
         <v>0</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G27" s="11" t="n">
         <v>0</v>
@@ -1832,7 +1832,7 @@
         <v>0</v>
       </c>
       <c r="F28" s="7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G28" s="7" t="n">
         <v>0</v>
@@ -1870,7 +1870,7 @@
         <v>0</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G29" s="11" t="n">
         <v>0</v>
@@ -1908,7 +1908,7 @@
         <v>0</v>
       </c>
       <c r="F30" s="7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G30" s="7" t="n">
         <v>0</v>
@@ -1946,7 +1946,7 @@
         <v>0</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G31" s="11" t="n">
         <v>0</v>
@@ -1984,7 +1984,7 @@
         <v>0</v>
       </c>
       <c r="F32" s="7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G32" s="7" t="n">
         <v>0</v>
@@ -2022,7 +2022,7 @@
         <v>0</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G33" s="11" t="n">
         <v>0</v>
@@ -2060,7 +2060,7 @@
         <v>0</v>
       </c>
       <c r="F34" s="7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G34" s="7" t="n">
         <v>0</v>
@@ -2098,7 +2098,7 @@
         <v>0</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G35" s="11" t="n">
         <v>0</v>
@@ -2136,7 +2136,7 @@
         <v>0</v>
       </c>
       <c r="F36" s="7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G36" s="7" t="n">
         <v>0</v>
@@ -2174,7 +2174,7 @@
         <v>0</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G37" s="11" t="n">
         <v>0</v>
@@ -2212,7 +2212,7 @@
         <v>0</v>
       </c>
       <c r="F38" s="7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G38" s="7" t="n">
         <v>0</v>
@@ -2250,7 +2250,7 @@
         <v>0</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G39" s="11" t="n">
         <v>0</v>
@@ -2288,7 +2288,7 @@
         <v>0</v>
       </c>
       <c r="F40" s="7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G40" s="7" t="n">
         <v>0</v>
@@ -2326,7 +2326,7 @@
         <v>0</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G41" s="11" t="n">
         <v>0</v>
@@ -2364,7 +2364,7 @@
         <v>0</v>
       </c>
       <c r="F42" s="7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G42" s="7" t="n">
         <v>0</v>
@@ -2402,7 +2402,7 @@
         <v>0</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G43" s="11" t="n">
         <v>0</v>
@@ -2440,7 +2440,7 @@
         <v>0</v>
       </c>
       <c r="F44" s="7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G44" s="7" t="n">
         <v>0</v>
@@ -2478,7 +2478,7 @@
         <v>0</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G45" s="11" t="n">
         <v>0</v>
@@ -2516,7 +2516,7 @@
         <v>0</v>
       </c>
       <c r="F46" s="7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G46" s="7" t="n">
         <v>0</v>
@@ -2554,7 +2554,7 @@
         <v>0</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G47" s="11" t="n">
         <v>0</v>
@@ -2592,7 +2592,7 @@
         <v>0</v>
       </c>
       <c r="F48" s="7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G48" s="7" t="n">
         <v>0</v>
@@ -2630,7 +2630,7 @@
         <v>0</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G49" s="11" t="n">
         <v>0</v>
@@ -2668,7 +2668,7 @@
         <v>0</v>
       </c>
       <c r="F50" s="7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G50" s="7" t="n">
         <v>0</v>
@@ -2706,7 +2706,7 @@
         <v>0</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G51" s="11" t="n">
         <v>0</v>
@@ -2744,7 +2744,7 @@
         <v>0</v>
       </c>
       <c r="F52" s="7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G52" s="7" t="n">
         <v>0</v>
@@ -2782,7 +2782,7 @@
         <v>0</v>
       </c>
       <c r="F53" s="11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G53" s="11" t="n">
         <v>0</v>
@@ -2820,7 +2820,7 @@
         <v>0</v>
       </c>
       <c r="F54" s="7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G54" s="7" t="n">
         <v>0</v>
@@ -2858,7 +2858,7 @@
         <v>0</v>
       </c>
       <c r="F55" s="11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G55" s="11" t="n">
         <v>0</v>
@@ -2896,7 +2896,7 @@
         <v>0</v>
       </c>
       <c r="F56" s="7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G56" s="7" t="n">
         <v>0</v>
@@ -2934,7 +2934,7 @@
         <v>0</v>
       </c>
       <c r="F57" s="11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G57" s="11" t="n">
         <v>0</v>
@@ -2972,7 +2972,7 @@
         <v>0</v>
       </c>
       <c r="F58" s="7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G58" s="7" t="n">
         <v>0</v>
@@ -3010,7 +3010,7 @@
         <v>0</v>
       </c>
       <c r="F59" s="11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G59" s="11" t="n">
         <v>0</v>
@@ -3048,7 +3048,7 @@
         <v>0</v>
       </c>
       <c r="F60" s="7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G60" s="7" t="n">
         <v>0</v>
@@ -3086,7 +3086,7 @@
         <v>0</v>
       </c>
       <c r="F61" s="11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G61" s="11" t="n">
         <v>0</v>
@@ -3124,7 +3124,7 @@
         <v>0</v>
       </c>
       <c r="F62" s="7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G62" s="7" t="n">
         <v>0</v>
@@ -3162,7 +3162,7 @@
         <v>0</v>
       </c>
       <c r="F63" s="11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G63" s="11" t="n">
         <v>0</v>
@@ -3200,7 +3200,7 @@
         <v>0</v>
       </c>
       <c r="F64" s="7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G64" s="7" t="n">
         <v>0</v>
@@ -3238,7 +3238,7 @@
         <v>0</v>
       </c>
       <c r="F65" s="11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G65" s="11" t="n">
         <v>0</v>
@@ -3276,7 +3276,7 @@
         <v>0</v>
       </c>
       <c r="F66" s="7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G66" s="7" t="n">
         <v>0</v>
@@ -3314,7 +3314,7 @@
         <v>0</v>
       </c>
       <c r="F67" s="11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G67" s="11" t="n">
         <v>0</v>
@@ -3352,7 +3352,7 @@
         <v>0</v>
       </c>
       <c r="F68" s="7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G68" s="7" t="n">
         <v>0</v>
@@ -3390,7 +3390,7 @@
         <v>0</v>
       </c>
       <c r="F69" s="11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G69" s="11" t="n">
         <v>0</v>
@@ -3428,7 +3428,7 @@
         <v>0</v>
       </c>
       <c r="F70" s="7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G70" s="7" t="n">
         <v>0</v>
@@ -3466,7 +3466,7 @@
         <v>0</v>
       </c>
       <c r="F71" s="11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G71" s="11" t="n">
         <v>0</v>
@@ -3504,7 +3504,7 @@
         <v>0</v>
       </c>
       <c r="F72" s="7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G72" s="7" t="n">
         <v>0</v>
@@ -3542,7 +3542,7 @@
         <v>0</v>
       </c>
       <c r="F73" s="11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G73" s="11" t="n">
         <v>0</v>
@@ -3580,7 +3580,7 @@
         <v>0</v>
       </c>
       <c r="F74" s="7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G74" s="7" t="n">
         <v>0</v>
@@ -3618,7 +3618,7 @@
         <v>0</v>
       </c>
       <c r="F75" s="11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G75" s="11" t="n">
         <v>0</v>
@@ -3656,7 +3656,7 @@
         <v>0</v>
       </c>
       <c r="F76" s="7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G76" s="7" t="n">
         <v>0</v>
@@ -3698,7 +3698,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3986,13 +3986,41 @@
         </is>
       </c>
     </row>
+    <row r="13" ht="21" customHeight="1">
+      <c r="A13" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="12" t="inlineStr">
+        <is>
+          <t>Community Board</t>
+        </is>
+      </c>
+      <c r="C13" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" s="11" t="n">
+        <v>72</v>
+      </c>
+      <c r="E13" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="13">
+        <f>IFERROR(C13/D13,0)</f>
+        <v/>
+      </c>
+      <c r="G13" s="12" t="inlineStr">
+        <is>
+          <t>03/09/26</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:G12"/>
+  <autoFilter ref="A4:G13"/>
   <mergeCells count="2">
     <mergeCell ref="A3:G3"/>
     <mergeCell ref="A1:G2"/>
   </mergeCells>
-  <conditionalFormatting sqref="F5:F12">
+  <conditionalFormatting sqref="F5:F13">
     <cfRule type="dataBar" priority="1">
       <dataBar showValue="1">
         <cfvo type="num" val="0"/>

--- a/exports/Resumen_Evidencias_OPS.xlsx
+++ b/exports/Resumen_Evidencias_OPS.xlsx
@@ -12,11 +12,11 @@
     <sheet name="Actividades" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Resumen'!$A$9:$H$15</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Resumen'!$A$1:$H$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Tiendas'!$A$4:$I$76</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Resumen'!$A$9:$G$15</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Resumen'!$A$1:$G$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Tiendas'!$A$4:$H$76</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Tiendas'!$1:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Actividades'!$A$4:$G$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Actividades'!$A$4:$F$13</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -544,13 +544,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -576,7 +575,7 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Aplican</t>
+          <t>Pendientes</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -590,10 +589,10 @@
         <v>2</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="E6" s="5">
-        <f>IFERROR(A6/C6,0)</f>
+        <f>IFERROR(A6/(A6+C6),0)</f>
         <v/>
       </c>
     </row>
@@ -621,20 +620,15 @@
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>Aplican</t>
+          <t>Pendientes</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>No aplica</t>
+          <t>% Avance</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
-        <is>
-          <t>% Avance</t>
-        </is>
-      </c>
-      <c r="H9" s="6" t="inlineStr">
         <is>
           <t>Estado</t>
         </is>
@@ -655,17 +649,14 @@
       <c r="D10" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="E10" s="7" t="n">
-        <v>90</v>
-      </c>
-      <c r="F10" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="9">
-        <f>IFERROR(D10/E10,0)</f>
-        <v/>
-      </c>
-      <c r="H10" s="10" t="inlineStr">
+      <c r="E10" s="8" t="n">
+        <v>88</v>
+      </c>
+      <c r="F10" s="9">
+        <f>IFERROR(D10/(D10+E10),0)</f>
+        <v/>
+      </c>
+      <c r="G10" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -686,17 +677,14 @@
       <c r="D11" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="E11" s="11" t="n">
+      <c r="E11" s="12" t="n">
         <v>108</v>
       </c>
-      <c r="F11" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" s="13">
-        <f>IFERROR(D11/E11,0)</f>
-        <v/>
-      </c>
-      <c r="H11" s="10" t="inlineStr">
+      <c r="F11" s="13">
+        <f>IFERROR(D11/(D11+E11),0)</f>
+        <v/>
+      </c>
+      <c r="G11" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -717,17 +705,14 @@
       <c r="D12" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="E12" s="7" t="n">
+      <c r="E12" s="8" t="n">
         <v>117</v>
       </c>
-      <c r="F12" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" s="9">
-        <f>IFERROR(D12/E12,0)</f>
-        <v/>
-      </c>
-      <c r="H12" s="10" t="inlineStr">
+      <c r="F12" s="9">
+        <f>IFERROR(D12/(D12+E12),0)</f>
+        <v/>
+      </c>
+      <c r="G12" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -748,17 +733,14 @@
       <c r="D13" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="E13" s="11" t="n">
+      <c r="E13" s="12" t="n">
         <v>99</v>
       </c>
-      <c r="F13" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G13" s="13">
-        <f>IFERROR(D13/E13,0)</f>
-        <v/>
-      </c>
-      <c r="H13" s="10" t="inlineStr">
+      <c r="F13" s="13">
+        <f>IFERROR(D13/(D13+E13),0)</f>
+        <v/>
+      </c>
+      <c r="G13" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -779,17 +761,14 @@
       <c r="D14" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="E14" s="7" t="n">
+      <c r="E14" s="8" t="n">
         <v>117</v>
       </c>
-      <c r="F14" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" s="9">
-        <f>IFERROR(D14/E14,0)</f>
-        <v/>
-      </c>
-      <c r="H14" s="10" t="inlineStr">
+      <c r="F14" s="9">
+        <f>IFERROR(D14/(D14+E14),0)</f>
+        <v/>
+      </c>
+      <c r="G14" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -810,35 +789,32 @@
       <c r="D15" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="E15" s="11" t="n">
+      <c r="E15" s="12" t="n">
         <v>117</v>
       </c>
-      <c r="F15" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G15" s="13">
-        <f>IFERROR(D15/E15,0)</f>
-        <v/>
-      </c>
-      <c r="H15" s="10" t="inlineStr">
+      <c r="F15" s="13">
+        <f>IFERROR(D15/(D15+E15),0)</f>
+        <v/>
+      </c>
+      <c r="G15" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A9:H15"/>
+  <autoFilter ref="A9:G15"/>
   <mergeCells count="8">
-    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="E6:G7"/>
+    <mergeCell ref="A1:G2"/>
     <mergeCell ref="C6:D7"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="E5:G5"/>
     <mergeCell ref="C5:D5"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="A6:B7"/>
-    <mergeCell ref="E6:H7"/>
-    <mergeCell ref="A1:H2"/>
-    <mergeCell ref="E5:H5"/>
   </mergeCells>
-  <conditionalFormatting sqref="G10:G15">
+  <conditionalFormatting sqref="F10:F15">
     <cfRule type="dataBar" priority="1">
       <dataBar showValue="1">
         <cfvo type="num" val="0"/>
@@ -859,7 +835,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I76"/>
+  <dimension ref="A1:H76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -867,10 +843,9 @@
     <col width="30" customWidth="1" min="3" max="3"/>
     <col width="32" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -916,20 +891,15 @@
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Aplican</t>
+          <t>Pendientes</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
         <is>
-          <t>No aplica</t>
+          <t>% Avance</t>
         </is>
       </c>
       <c r="H4" s="6" t="inlineStr">
-        <is>
-          <t>% Avance</t>
-        </is>
-      </c>
-      <c r="I4" s="6" t="inlineStr">
         <is>
           <t>Estado</t>
         </is>
@@ -958,16 +928,13 @@
         <v>1</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>9</v>
-      </c>
-      <c r="G5" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" s="13">
-        <f>IFERROR(E5/F5,0)</f>
-        <v/>
-      </c>
-      <c r="I5" s="10" t="inlineStr">
+        <v>8</v>
+      </c>
+      <c r="G5" s="13">
+        <f>IFERROR(E5/(E5+F5),0)</f>
+        <v/>
+      </c>
+      <c r="H5" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -996,16 +963,13 @@
         <v>1</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>9</v>
-      </c>
-      <c r="G6" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" s="9">
-        <f>IFERROR(E6/F6,0)</f>
-        <v/>
-      </c>
-      <c r="I6" s="10" t="inlineStr">
+        <v>8</v>
+      </c>
+      <c r="G6" s="9">
+        <f>IFERROR(E6/(E6+F6),0)</f>
+        <v/>
+      </c>
+      <c r="H6" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -1036,14 +1000,11 @@
       <c r="F7" s="11" t="n">
         <v>9</v>
       </c>
-      <c r="G7" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" s="13">
-        <f>IFERROR(E7/F7,0)</f>
-        <v/>
-      </c>
-      <c r="I7" s="10" t="inlineStr">
+      <c r="G7" s="13">
+        <f>IFERROR(E7/(E7+F7),0)</f>
+        <v/>
+      </c>
+      <c r="H7" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -1074,14 +1035,11 @@
       <c r="F8" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="G8" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" s="9">
-        <f>IFERROR(E8/F8,0)</f>
-        <v/>
-      </c>
-      <c r="I8" s="10" t="inlineStr">
+      <c r="G8" s="9">
+        <f>IFERROR(E8/(E8+F8),0)</f>
+        <v/>
+      </c>
+      <c r="H8" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -1112,14 +1070,11 @@
       <c r="F9" s="11" t="n">
         <v>9</v>
       </c>
-      <c r="G9" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" s="13">
-        <f>IFERROR(E9/F9,0)</f>
-        <v/>
-      </c>
-      <c r="I9" s="10" t="inlineStr">
+      <c r="G9" s="13">
+        <f>IFERROR(E9/(E9+F9),0)</f>
+        <v/>
+      </c>
+      <c r="H9" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -1150,14 +1105,11 @@
       <c r="F10" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="G10" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" s="9">
-        <f>IFERROR(E10/F10,0)</f>
-        <v/>
-      </c>
-      <c r="I10" s="10" t="inlineStr">
+      <c r="G10" s="9">
+        <f>IFERROR(E10/(E10+F10),0)</f>
+        <v/>
+      </c>
+      <c r="H10" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -1188,14 +1140,11 @@
       <c r="F11" s="11" t="n">
         <v>9</v>
       </c>
-      <c r="G11" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" s="13">
-        <f>IFERROR(E11/F11,0)</f>
-        <v/>
-      </c>
-      <c r="I11" s="10" t="inlineStr">
+      <c r="G11" s="13">
+        <f>IFERROR(E11/(E11+F11),0)</f>
+        <v/>
+      </c>
+      <c r="H11" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -1226,14 +1175,11 @@
       <c r="F12" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="G12" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" s="9">
-        <f>IFERROR(E12/F12,0)</f>
-        <v/>
-      </c>
-      <c r="I12" s="10" t="inlineStr">
+      <c r="G12" s="9">
+        <f>IFERROR(E12/(E12+F12),0)</f>
+        <v/>
+      </c>
+      <c r="H12" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -1264,14 +1210,11 @@
       <c r="F13" s="11" t="n">
         <v>9</v>
       </c>
-      <c r="G13" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" s="13">
-        <f>IFERROR(E13/F13,0)</f>
-        <v/>
-      </c>
-      <c r="I13" s="10" t="inlineStr">
+      <c r="G13" s="13">
+        <f>IFERROR(E13/(E13+F13),0)</f>
+        <v/>
+      </c>
+      <c r="H13" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -1302,14 +1245,11 @@
       <c r="F14" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="G14" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" s="9">
-        <f>IFERROR(E14/F14,0)</f>
-        <v/>
-      </c>
-      <c r="I14" s="10" t="inlineStr">
+      <c r="G14" s="9">
+        <f>IFERROR(E14/(E14+F14),0)</f>
+        <v/>
+      </c>
+      <c r="H14" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -1340,14 +1280,11 @@
       <c r="F15" s="11" t="n">
         <v>9</v>
       </c>
-      <c r="G15" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" s="13">
-        <f>IFERROR(E15/F15,0)</f>
-        <v/>
-      </c>
-      <c r="I15" s="10" t="inlineStr">
+      <c r="G15" s="13">
+        <f>IFERROR(E15/(E15+F15),0)</f>
+        <v/>
+      </c>
+      <c r="H15" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -1378,14 +1315,11 @@
       <c r="F16" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="G16" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" s="9">
-        <f>IFERROR(E16/F16,0)</f>
-        <v/>
-      </c>
-      <c r="I16" s="10" t="inlineStr">
+      <c r="G16" s="9">
+        <f>IFERROR(E16/(E16+F16),0)</f>
+        <v/>
+      </c>
+      <c r="H16" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -1416,14 +1350,11 @@
       <c r="F17" s="11" t="n">
         <v>9</v>
       </c>
-      <c r="G17" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" s="13">
-        <f>IFERROR(E17/F17,0)</f>
-        <v/>
-      </c>
-      <c r="I17" s="10" t="inlineStr">
+      <c r="G17" s="13">
+        <f>IFERROR(E17/(E17+F17),0)</f>
+        <v/>
+      </c>
+      <c r="H17" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -1454,14 +1385,11 @@
       <c r="F18" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="G18" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" s="9">
-        <f>IFERROR(E18/F18,0)</f>
-        <v/>
-      </c>
-      <c r="I18" s="10" t="inlineStr">
+      <c r="G18" s="9">
+        <f>IFERROR(E18/(E18+F18),0)</f>
+        <v/>
+      </c>
+      <c r="H18" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -1492,14 +1420,11 @@
       <c r="F19" s="11" t="n">
         <v>9</v>
       </c>
-      <c r="G19" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" s="13">
-        <f>IFERROR(E19/F19,0)</f>
-        <v/>
-      </c>
-      <c r="I19" s="10" t="inlineStr">
+      <c r="G19" s="13">
+        <f>IFERROR(E19/(E19+F19),0)</f>
+        <v/>
+      </c>
+      <c r="H19" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -1530,14 +1455,11 @@
       <c r="F20" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="G20" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H20" s="9">
-        <f>IFERROR(E20/F20,0)</f>
-        <v/>
-      </c>
-      <c r="I20" s="10" t="inlineStr">
+      <c r="G20" s="9">
+        <f>IFERROR(E20/(E20+F20),0)</f>
+        <v/>
+      </c>
+      <c r="H20" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -1568,14 +1490,11 @@
       <c r="F21" s="11" t="n">
         <v>9</v>
       </c>
-      <c r="G21" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" s="13">
-        <f>IFERROR(E21/F21,0)</f>
-        <v/>
-      </c>
-      <c r="I21" s="10" t="inlineStr">
+      <c r="G21" s="13">
+        <f>IFERROR(E21/(E21+F21),0)</f>
+        <v/>
+      </c>
+      <c r="H21" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -1606,14 +1525,11 @@
       <c r="F22" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="G22" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H22" s="9">
-        <f>IFERROR(E22/F22,0)</f>
-        <v/>
-      </c>
-      <c r="I22" s="10" t="inlineStr">
+      <c r="G22" s="9">
+        <f>IFERROR(E22/(E22+F22),0)</f>
+        <v/>
+      </c>
+      <c r="H22" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -1644,14 +1560,11 @@
       <c r="F23" s="11" t="n">
         <v>9</v>
       </c>
-      <c r="G23" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" s="13">
-        <f>IFERROR(E23/F23,0)</f>
-        <v/>
-      </c>
-      <c r="I23" s="10" t="inlineStr">
+      <c r="G23" s="13">
+        <f>IFERROR(E23/(E23+F23),0)</f>
+        <v/>
+      </c>
+      <c r="H23" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -1682,14 +1595,11 @@
       <c r="F24" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="G24" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" s="9">
-        <f>IFERROR(E24/F24,0)</f>
-        <v/>
-      </c>
-      <c r="I24" s="10" t="inlineStr">
+      <c r="G24" s="9">
+        <f>IFERROR(E24/(E24+F24),0)</f>
+        <v/>
+      </c>
+      <c r="H24" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -1720,14 +1630,11 @@
       <c r="F25" s="11" t="n">
         <v>9</v>
       </c>
-      <c r="G25" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" s="13">
-        <f>IFERROR(E25/F25,0)</f>
-        <v/>
-      </c>
-      <c r="I25" s="10" t="inlineStr">
+      <c r="G25" s="13">
+        <f>IFERROR(E25/(E25+F25),0)</f>
+        <v/>
+      </c>
+      <c r="H25" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -1758,14 +1665,11 @@
       <c r="F26" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="G26" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" s="9">
-        <f>IFERROR(E26/F26,0)</f>
-        <v/>
-      </c>
-      <c r="I26" s="10" t="inlineStr">
+      <c r="G26" s="9">
+        <f>IFERROR(E26/(E26+F26),0)</f>
+        <v/>
+      </c>
+      <c r="H26" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -1796,14 +1700,11 @@
       <c r="F27" s="11" t="n">
         <v>9</v>
       </c>
-      <c r="G27" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" s="13">
-        <f>IFERROR(E27/F27,0)</f>
-        <v/>
-      </c>
-      <c r="I27" s="10" t="inlineStr">
+      <c r="G27" s="13">
+        <f>IFERROR(E27/(E27+F27),0)</f>
+        <v/>
+      </c>
+      <c r="H27" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -1834,14 +1735,11 @@
       <c r="F28" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="G28" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H28" s="9">
-        <f>IFERROR(E28/F28,0)</f>
-        <v/>
-      </c>
-      <c r="I28" s="10" t="inlineStr">
+      <c r="G28" s="9">
+        <f>IFERROR(E28/(E28+F28),0)</f>
+        <v/>
+      </c>
+      <c r="H28" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -1872,14 +1770,11 @@
       <c r="F29" s="11" t="n">
         <v>9</v>
       </c>
-      <c r="G29" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" s="13">
-        <f>IFERROR(E29/F29,0)</f>
-        <v/>
-      </c>
-      <c r="I29" s="10" t="inlineStr">
+      <c r="G29" s="13">
+        <f>IFERROR(E29/(E29+F29),0)</f>
+        <v/>
+      </c>
+      <c r="H29" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -1910,14 +1805,11 @@
       <c r="F30" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="G30" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" s="9">
-        <f>IFERROR(E30/F30,0)</f>
-        <v/>
-      </c>
-      <c r="I30" s="10" t="inlineStr">
+      <c r="G30" s="9">
+        <f>IFERROR(E30/(E30+F30),0)</f>
+        <v/>
+      </c>
+      <c r="H30" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -1948,14 +1840,11 @@
       <c r="F31" s="11" t="n">
         <v>9</v>
       </c>
-      <c r="G31" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H31" s="13">
-        <f>IFERROR(E31/F31,0)</f>
-        <v/>
-      </c>
-      <c r="I31" s="10" t="inlineStr">
+      <c r="G31" s="13">
+        <f>IFERROR(E31/(E31+F31),0)</f>
+        <v/>
+      </c>
+      <c r="H31" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -1986,14 +1875,11 @@
       <c r="F32" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="G32" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H32" s="9">
-        <f>IFERROR(E32/F32,0)</f>
-        <v/>
-      </c>
-      <c r="I32" s="10" t="inlineStr">
+      <c r="G32" s="9">
+        <f>IFERROR(E32/(E32+F32),0)</f>
+        <v/>
+      </c>
+      <c r="H32" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -2024,14 +1910,11 @@
       <c r="F33" s="11" t="n">
         <v>9</v>
       </c>
-      <c r="G33" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H33" s="13">
-        <f>IFERROR(E33/F33,0)</f>
-        <v/>
-      </c>
-      <c r="I33" s="10" t="inlineStr">
+      <c r="G33" s="13">
+        <f>IFERROR(E33/(E33+F33),0)</f>
+        <v/>
+      </c>
+      <c r="H33" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -2062,14 +1945,11 @@
       <c r="F34" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="G34" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H34" s="9">
-        <f>IFERROR(E34/F34,0)</f>
-        <v/>
-      </c>
-      <c r="I34" s="10" t="inlineStr">
+      <c r="G34" s="9">
+        <f>IFERROR(E34/(E34+F34),0)</f>
+        <v/>
+      </c>
+      <c r="H34" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -2100,14 +1980,11 @@
       <c r="F35" s="11" t="n">
         <v>9</v>
       </c>
-      <c r="G35" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H35" s="13">
-        <f>IFERROR(E35/F35,0)</f>
-        <v/>
-      </c>
-      <c r="I35" s="10" t="inlineStr">
+      <c r="G35" s="13">
+        <f>IFERROR(E35/(E35+F35),0)</f>
+        <v/>
+      </c>
+      <c r="H35" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -2138,14 +2015,11 @@
       <c r="F36" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="G36" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H36" s="9">
-        <f>IFERROR(E36/F36,0)</f>
-        <v/>
-      </c>
-      <c r="I36" s="10" t="inlineStr">
+      <c r="G36" s="9">
+        <f>IFERROR(E36/(E36+F36),0)</f>
+        <v/>
+      </c>
+      <c r="H36" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -2176,14 +2050,11 @@
       <c r="F37" s="11" t="n">
         <v>9</v>
       </c>
-      <c r="G37" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H37" s="13">
-        <f>IFERROR(E37/F37,0)</f>
-        <v/>
-      </c>
-      <c r="I37" s="10" t="inlineStr">
+      <c r="G37" s="13">
+        <f>IFERROR(E37/(E37+F37),0)</f>
+        <v/>
+      </c>
+      <c r="H37" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -2214,14 +2085,11 @@
       <c r="F38" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="G38" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H38" s="9">
-        <f>IFERROR(E38/F38,0)</f>
-        <v/>
-      </c>
-      <c r="I38" s="10" t="inlineStr">
+      <c r="G38" s="9">
+        <f>IFERROR(E38/(E38+F38),0)</f>
+        <v/>
+      </c>
+      <c r="H38" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -2252,14 +2120,11 @@
       <c r="F39" s="11" t="n">
         <v>9</v>
       </c>
-      <c r="G39" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H39" s="13">
-        <f>IFERROR(E39/F39,0)</f>
-        <v/>
-      </c>
-      <c r="I39" s="10" t="inlineStr">
+      <c r="G39" s="13">
+        <f>IFERROR(E39/(E39+F39),0)</f>
+        <v/>
+      </c>
+      <c r="H39" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -2290,14 +2155,11 @@
       <c r="F40" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="G40" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H40" s="9">
-        <f>IFERROR(E40/F40,0)</f>
-        <v/>
-      </c>
-      <c r="I40" s="10" t="inlineStr">
+      <c r="G40" s="9">
+        <f>IFERROR(E40/(E40+F40),0)</f>
+        <v/>
+      </c>
+      <c r="H40" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -2328,14 +2190,11 @@
       <c r="F41" s="11" t="n">
         <v>9</v>
       </c>
-      <c r="G41" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H41" s="13">
-        <f>IFERROR(E41/F41,0)</f>
-        <v/>
-      </c>
-      <c r="I41" s="10" t="inlineStr">
+      <c r="G41" s="13">
+        <f>IFERROR(E41/(E41+F41),0)</f>
+        <v/>
+      </c>
+      <c r="H41" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -2366,14 +2225,11 @@
       <c r="F42" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="G42" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H42" s="9">
-        <f>IFERROR(E42/F42,0)</f>
-        <v/>
-      </c>
-      <c r="I42" s="10" t="inlineStr">
+      <c r="G42" s="9">
+        <f>IFERROR(E42/(E42+F42),0)</f>
+        <v/>
+      </c>
+      <c r="H42" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -2404,14 +2260,11 @@
       <c r="F43" s="11" t="n">
         <v>9</v>
       </c>
-      <c r="G43" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H43" s="13">
-        <f>IFERROR(E43/F43,0)</f>
-        <v/>
-      </c>
-      <c r="I43" s="10" t="inlineStr">
+      <c r="G43" s="13">
+        <f>IFERROR(E43/(E43+F43),0)</f>
+        <v/>
+      </c>
+      <c r="H43" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -2442,14 +2295,11 @@
       <c r="F44" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="G44" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H44" s="9">
-        <f>IFERROR(E44/F44,0)</f>
-        <v/>
-      </c>
-      <c r="I44" s="10" t="inlineStr">
+      <c r="G44" s="9">
+        <f>IFERROR(E44/(E44+F44),0)</f>
+        <v/>
+      </c>
+      <c r="H44" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -2480,14 +2330,11 @@
       <c r="F45" s="11" t="n">
         <v>9</v>
       </c>
-      <c r="G45" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H45" s="13">
-        <f>IFERROR(E45/F45,0)</f>
-        <v/>
-      </c>
-      <c r="I45" s="10" t="inlineStr">
+      <c r="G45" s="13">
+        <f>IFERROR(E45/(E45+F45),0)</f>
+        <v/>
+      </c>
+      <c r="H45" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -2518,14 +2365,11 @@
       <c r="F46" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="G46" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H46" s="9">
-        <f>IFERROR(E46/F46,0)</f>
-        <v/>
-      </c>
-      <c r="I46" s="10" t="inlineStr">
+      <c r="G46" s="9">
+        <f>IFERROR(E46/(E46+F46),0)</f>
+        <v/>
+      </c>
+      <c r="H46" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -2556,14 +2400,11 @@
       <c r="F47" s="11" t="n">
         <v>9</v>
       </c>
-      <c r="G47" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H47" s="13">
-        <f>IFERROR(E47/F47,0)</f>
-        <v/>
-      </c>
-      <c r="I47" s="10" t="inlineStr">
+      <c r="G47" s="13">
+        <f>IFERROR(E47/(E47+F47),0)</f>
+        <v/>
+      </c>
+      <c r="H47" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -2594,14 +2435,11 @@
       <c r="F48" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="G48" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H48" s="9">
-        <f>IFERROR(E48/F48,0)</f>
-        <v/>
-      </c>
-      <c r="I48" s="10" t="inlineStr">
+      <c r="G48" s="9">
+        <f>IFERROR(E48/(E48+F48),0)</f>
+        <v/>
+      </c>
+      <c r="H48" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -2632,14 +2470,11 @@
       <c r="F49" s="11" t="n">
         <v>9</v>
       </c>
-      <c r="G49" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H49" s="13">
-        <f>IFERROR(E49/F49,0)</f>
-        <v/>
-      </c>
-      <c r="I49" s="10" t="inlineStr">
+      <c r="G49" s="13">
+        <f>IFERROR(E49/(E49+F49),0)</f>
+        <v/>
+      </c>
+      <c r="H49" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -2670,14 +2505,11 @@
       <c r="F50" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="G50" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H50" s="9">
-        <f>IFERROR(E50/F50,0)</f>
-        <v/>
-      </c>
-      <c r="I50" s="10" t="inlineStr">
+      <c r="G50" s="9">
+        <f>IFERROR(E50/(E50+F50),0)</f>
+        <v/>
+      </c>
+      <c r="H50" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -2708,14 +2540,11 @@
       <c r="F51" s="11" t="n">
         <v>9</v>
       </c>
-      <c r="G51" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H51" s="13">
-        <f>IFERROR(E51/F51,0)</f>
-        <v/>
-      </c>
-      <c r="I51" s="10" t="inlineStr">
+      <c r="G51" s="13">
+        <f>IFERROR(E51/(E51+F51),0)</f>
+        <v/>
+      </c>
+      <c r="H51" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -2746,14 +2575,11 @@
       <c r="F52" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="G52" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H52" s="9">
-        <f>IFERROR(E52/F52,0)</f>
-        <v/>
-      </c>
-      <c r="I52" s="10" t="inlineStr">
+      <c r="G52" s="9">
+        <f>IFERROR(E52/(E52+F52),0)</f>
+        <v/>
+      </c>
+      <c r="H52" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -2784,14 +2610,11 @@
       <c r="F53" s="11" t="n">
         <v>9</v>
       </c>
-      <c r="G53" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H53" s="13">
-        <f>IFERROR(E53/F53,0)</f>
-        <v/>
-      </c>
-      <c r="I53" s="10" t="inlineStr">
+      <c r="G53" s="13">
+        <f>IFERROR(E53/(E53+F53),0)</f>
+        <v/>
+      </c>
+      <c r="H53" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -2822,14 +2645,11 @@
       <c r="F54" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="G54" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H54" s="9">
-        <f>IFERROR(E54/F54,0)</f>
-        <v/>
-      </c>
-      <c r="I54" s="10" t="inlineStr">
+      <c r="G54" s="9">
+        <f>IFERROR(E54/(E54+F54),0)</f>
+        <v/>
+      </c>
+      <c r="H54" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -2860,14 +2680,11 @@
       <c r="F55" s="11" t="n">
         <v>9</v>
       </c>
-      <c r="G55" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H55" s="13">
-        <f>IFERROR(E55/F55,0)</f>
-        <v/>
-      </c>
-      <c r="I55" s="10" t="inlineStr">
+      <c r="G55" s="13">
+        <f>IFERROR(E55/(E55+F55),0)</f>
+        <v/>
+      </c>
+      <c r="H55" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -2898,14 +2715,11 @@
       <c r="F56" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="G56" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H56" s="9">
-        <f>IFERROR(E56/F56,0)</f>
-        <v/>
-      </c>
-      <c r="I56" s="10" t="inlineStr">
+      <c r="G56" s="9">
+        <f>IFERROR(E56/(E56+F56),0)</f>
+        <v/>
+      </c>
+      <c r="H56" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -2936,14 +2750,11 @@
       <c r="F57" s="11" t="n">
         <v>9</v>
       </c>
-      <c r="G57" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H57" s="13">
-        <f>IFERROR(E57/F57,0)</f>
-        <v/>
-      </c>
-      <c r="I57" s="10" t="inlineStr">
+      <c r="G57" s="13">
+        <f>IFERROR(E57/(E57+F57),0)</f>
+        <v/>
+      </c>
+      <c r="H57" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -2974,14 +2785,11 @@
       <c r="F58" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="G58" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H58" s="9">
-        <f>IFERROR(E58/F58,0)</f>
-        <v/>
-      </c>
-      <c r="I58" s="10" t="inlineStr">
+      <c r="G58" s="9">
+        <f>IFERROR(E58/(E58+F58),0)</f>
+        <v/>
+      </c>
+      <c r="H58" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -3012,14 +2820,11 @@
       <c r="F59" s="11" t="n">
         <v>9</v>
       </c>
-      <c r="G59" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H59" s="13">
-        <f>IFERROR(E59/F59,0)</f>
-        <v/>
-      </c>
-      <c r="I59" s="10" t="inlineStr">
+      <c r="G59" s="13">
+        <f>IFERROR(E59/(E59+F59),0)</f>
+        <v/>
+      </c>
+      <c r="H59" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -3050,14 +2855,11 @@
       <c r="F60" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="G60" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H60" s="9">
-        <f>IFERROR(E60/F60,0)</f>
-        <v/>
-      </c>
-      <c r="I60" s="10" t="inlineStr">
+      <c r="G60" s="9">
+        <f>IFERROR(E60/(E60+F60),0)</f>
+        <v/>
+      </c>
+      <c r="H60" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -3088,14 +2890,11 @@
       <c r="F61" s="11" t="n">
         <v>9</v>
       </c>
-      <c r="G61" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H61" s="13">
-        <f>IFERROR(E61/F61,0)</f>
-        <v/>
-      </c>
-      <c r="I61" s="10" t="inlineStr">
+      <c r="G61" s="13">
+        <f>IFERROR(E61/(E61+F61),0)</f>
+        <v/>
+      </c>
+      <c r="H61" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -3126,14 +2925,11 @@
       <c r="F62" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="G62" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H62" s="9">
-        <f>IFERROR(E62/F62,0)</f>
-        <v/>
-      </c>
-      <c r="I62" s="10" t="inlineStr">
+      <c r="G62" s="9">
+        <f>IFERROR(E62/(E62+F62),0)</f>
+        <v/>
+      </c>
+      <c r="H62" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -3164,14 +2960,11 @@
       <c r="F63" s="11" t="n">
         <v>9</v>
       </c>
-      <c r="G63" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H63" s="13">
-        <f>IFERROR(E63/F63,0)</f>
-        <v/>
-      </c>
-      <c r="I63" s="10" t="inlineStr">
+      <c r="G63" s="13">
+        <f>IFERROR(E63/(E63+F63),0)</f>
+        <v/>
+      </c>
+      <c r="H63" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -3202,14 +2995,11 @@
       <c r="F64" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="G64" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H64" s="9">
-        <f>IFERROR(E64/F64,0)</f>
-        <v/>
-      </c>
-      <c r="I64" s="10" t="inlineStr">
+      <c r="G64" s="9">
+        <f>IFERROR(E64/(E64+F64),0)</f>
+        <v/>
+      </c>
+      <c r="H64" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -3240,14 +3030,11 @@
       <c r="F65" s="11" t="n">
         <v>9</v>
       </c>
-      <c r="G65" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H65" s="13">
-        <f>IFERROR(E65/F65,0)</f>
-        <v/>
-      </c>
-      <c r="I65" s="10" t="inlineStr">
+      <c r="G65" s="13">
+        <f>IFERROR(E65/(E65+F65),0)</f>
+        <v/>
+      </c>
+      <c r="H65" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -3278,14 +3065,11 @@
       <c r="F66" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="G66" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H66" s="9">
-        <f>IFERROR(E66/F66,0)</f>
-        <v/>
-      </c>
-      <c r="I66" s="10" t="inlineStr">
+      <c r="G66" s="9">
+        <f>IFERROR(E66/(E66+F66),0)</f>
+        <v/>
+      </c>
+      <c r="H66" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -3316,14 +3100,11 @@
       <c r="F67" s="11" t="n">
         <v>9</v>
       </c>
-      <c r="G67" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H67" s="13">
-        <f>IFERROR(E67/F67,0)</f>
-        <v/>
-      </c>
-      <c r="I67" s="10" t="inlineStr">
+      <c r="G67" s="13">
+        <f>IFERROR(E67/(E67+F67),0)</f>
+        <v/>
+      </c>
+      <c r="H67" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -3354,14 +3135,11 @@
       <c r="F68" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="G68" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H68" s="9">
-        <f>IFERROR(E68/F68,0)</f>
-        <v/>
-      </c>
-      <c r="I68" s="10" t="inlineStr">
+      <c r="G68" s="9">
+        <f>IFERROR(E68/(E68+F68),0)</f>
+        <v/>
+      </c>
+      <c r="H68" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -3392,14 +3170,11 @@
       <c r="F69" s="11" t="n">
         <v>9</v>
       </c>
-      <c r="G69" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H69" s="13">
-        <f>IFERROR(E69/F69,0)</f>
-        <v/>
-      </c>
-      <c r="I69" s="10" t="inlineStr">
+      <c r="G69" s="13">
+        <f>IFERROR(E69/(E69+F69),0)</f>
+        <v/>
+      </c>
+      <c r="H69" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -3430,14 +3205,11 @@
       <c r="F70" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="G70" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H70" s="9">
-        <f>IFERROR(E70/F70,0)</f>
-        <v/>
-      </c>
-      <c r="I70" s="10" t="inlineStr">
+      <c r="G70" s="9">
+        <f>IFERROR(E70/(E70+F70),0)</f>
+        <v/>
+      </c>
+      <c r="H70" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -3468,14 +3240,11 @@
       <c r="F71" s="11" t="n">
         <v>9</v>
       </c>
-      <c r="G71" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H71" s="13">
-        <f>IFERROR(E71/F71,0)</f>
-        <v/>
-      </c>
-      <c r="I71" s="10" t="inlineStr">
+      <c r="G71" s="13">
+        <f>IFERROR(E71/(E71+F71),0)</f>
+        <v/>
+      </c>
+      <c r="H71" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -3506,14 +3275,11 @@
       <c r="F72" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="G72" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H72" s="9">
-        <f>IFERROR(E72/F72,0)</f>
-        <v/>
-      </c>
-      <c r="I72" s="10" t="inlineStr">
+      <c r="G72" s="9">
+        <f>IFERROR(E72/(E72+F72),0)</f>
+        <v/>
+      </c>
+      <c r="H72" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -3544,14 +3310,11 @@
       <c r="F73" s="11" t="n">
         <v>9</v>
       </c>
-      <c r="G73" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H73" s="13">
-        <f>IFERROR(E73/F73,0)</f>
-        <v/>
-      </c>
-      <c r="I73" s="10" t="inlineStr">
+      <c r="G73" s="13">
+        <f>IFERROR(E73/(E73+F73),0)</f>
+        <v/>
+      </c>
+      <c r="H73" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -3582,14 +3345,11 @@
       <c r="F74" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="G74" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H74" s="9">
-        <f>IFERROR(E74/F74,0)</f>
-        <v/>
-      </c>
-      <c r="I74" s="10" t="inlineStr">
+      <c r="G74" s="9">
+        <f>IFERROR(E74/(E74+F74),0)</f>
+        <v/>
+      </c>
+      <c r="H74" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -3620,14 +3380,11 @@
       <c r="F75" s="11" t="n">
         <v>9</v>
       </c>
-      <c r="G75" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H75" s="13">
-        <f>IFERROR(E75/F75,0)</f>
-        <v/>
-      </c>
-      <c r="I75" s="10" t="inlineStr">
+      <c r="G75" s="13">
+        <f>IFERROR(E75/(E75+F75),0)</f>
+        <v/>
+      </c>
+      <c r="H75" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
@@ -3658,26 +3415,23 @@
       <c r="F76" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="G76" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H76" s="9">
-        <f>IFERROR(E76/F76,0)</f>
-        <v/>
-      </c>
-      <c r="I76" s="10" t="inlineStr">
+      <c r="G76" s="9">
+        <f>IFERROR(E76/(E76+F76),0)</f>
+        <v/>
+      </c>
+      <c r="H76" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:I76"/>
+  <autoFilter ref="A4:H76"/>
   <mergeCells count="2">
-    <mergeCell ref="A1:I2"/>
-    <mergeCell ref="A3:I3"/>
+    <mergeCell ref="A1:H2"/>
+    <mergeCell ref="A3:H3"/>
   </mergeCells>
-  <conditionalFormatting sqref="H5:H76">
+  <conditionalFormatting sqref="G5:G76">
     <cfRule type="dataBar" priority="1">
       <dataBar showValue="1">
         <cfvo type="num" val="0"/>
@@ -3698,16 +3452,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -3743,20 +3496,15 @@
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>Aplican</t>
+          <t>Pendientes</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>No aplica</t>
+          <t>% Avance</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>% Avance</t>
-        </is>
-      </c>
-      <c r="G4" s="6" t="inlineStr">
         <is>
           <t>Fecha compromiso</t>
         </is>
@@ -3775,16 +3523,13 @@
         <v>2</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>72</v>
-      </c>
-      <c r="E5" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="13">
-        <f>IFERROR(C5/D5,0)</f>
-        <v/>
-      </c>
-      <c r="G5" s="12" t="inlineStr">
+        <v>70</v>
+      </c>
+      <c r="E5" s="13">
+        <f>IFERROR(C5/(C5+D5),0)</f>
+        <v/>
+      </c>
+      <c r="F5" s="12" t="inlineStr">
         <is>
           <t>03/09/26</t>
         </is>
@@ -3805,14 +3550,11 @@
       <c r="D6" s="7" t="n">
         <v>72</v>
       </c>
-      <c r="E6" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="9">
-        <f>IFERROR(C6/D6,0)</f>
-        <v/>
-      </c>
-      <c r="G6" s="8" t="inlineStr">
+      <c r="E6" s="9">
+        <f>IFERROR(C6/(C6+D6),0)</f>
+        <v/>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
         <is>
           <t>03/09/26</t>
         </is>
@@ -3833,14 +3575,11 @@
       <c r="D7" s="11" t="n">
         <v>72</v>
       </c>
-      <c r="E7" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="13">
-        <f>IFERROR(C7/D7,0)</f>
-        <v/>
-      </c>
-      <c r="G7" s="12" t="inlineStr">
+      <c r="E7" s="13">
+        <f>IFERROR(C7/(C7+D7),0)</f>
+        <v/>
+      </c>
+      <c r="F7" s="12" t="inlineStr">
         <is>
           <t>06/09/26</t>
         </is>
@@ -3861,14 +3600,11 @@
       <c r="D8" s="7" t="n">
         <v>72</v>
       </c>
-      <c r="E8" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="9">
-        <f>IFERROR(C8/D8,0)</f>
-        <v/>
-      </c>
-      <c r="G8" s="8" t="inlineStr">
+      <c r="E8" s="9">
+        <f>IFERROR(C8/(C8+D8),0)</f>
+        <v/>
+      </c>
+      <c r="F8" s="8" t="inlineStr">
         <is>
           <t>03/09/26</t>
         </is>
@@ -3889,14 +3625,11 @@
       <c r="D9" s="11" t="n">
         <v>72</v>
       </c>
-      <c r="E9" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="13">
-        <f>IFERROR(C9/D9,0)</f>
-        <v/>
-      </c>
-      <c r="G9" s="12" t="inlineStr">
+      <c r="E9" s="13">
+        <f>IFERROR(C9/(C9+D9),0)</f>
+        <v/>
+      </c>
+      <c r="F9" s="12" t="inlineStr">
         <is>
           <t>06/09/26</t>
         </is>
@@ -3917,14 +3650,11 @@
       <c r="D10" s="7" t="n">
         <v>72</v>
       </c>
-      <c r="E10" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="9">
-        <f>IFERROR(C10/D10,0)</f>
-        <v/>
-      </c>
-      <c r="G10" s="8" t="inlineStr">
+      <c r="E10" s="9">
+        <f>IFERROR(C10/(C10+D10),0)</f>
+        <v/>
+      </c>
+      <c r="F10" s="8" t="inlineStr">
         <is>
           <t>06/09/26</t>
         </is>
@@ -3945,14 +3675,11 @@
       <c r="D11" s="11" t="n">
         <v>72</v>
       </c>
-      <c r="E11" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" s="13">
-        <f>IFERROR(C11/D11,0)</f>
-        <v/>
-      </c>
-      <c r="G11" s="12" t="inlineStr">
+      <c r="E11" s="13">
+        <f>IFERROR(C11/(C11+D11),0)</f>
+        <v/>
+      </c>
+      <c r="F11" s="12" t="inlineStr">
         <is>
           <t>13/09/26</t>
         </is>
@@ -3973,14 +3700,11 @@
       <c r="D12" s="7" t="n">
         <v>72</v>
       </c>
-      <c r="E12" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" s="9">
-        <f>IFERROR(C12/D12,0)</f>
-        <v/>
-      </c>
-      <c r="G12" s="8" t="inlineStr">
+      <c r="E12" s="9">
+        <f>IFERROR(C12/(C12+D12),0)</f>
+        <v/>
+      </c>
+      <c r="F12" s="8" t="inlineStr">
         <is>
           <t>06/09/26</t>
         </is>
@@ -4001,26 +3725,23 @@
       <c r="D13" s="11" t="n">
         <v>72</v>
       </c>
-      <c r="E13" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" s="13">
-        <f>IFERROR(C13/D13,0)</f>
-        <v/>
-      </c>
-      <c r="G13" s="12" t="inlineStr">
+      <c r="E13" s="13">
+        <f>IFERROR(C13/(C13+D13),0)</f>
+        <v/>
+      </c>
+      <c r="F13" s="12" t="inlineStr">
         <is>
           <t>03/09/26</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:G13"/>
+  <autoFilter ref="A4:F13"/>
   <mergeCells count="2">
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A1:G2"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A1:F2"/>
   </mergeCells>
-  <conditionalFormatting sqref="F5:F13">
+  <conditionalFormatting sqref="E5:E13">
     <cfRule type="dataBar" priority="1">
       <dataBar showValue="1">
         <cfvo type="num" val="0"/>

--- a/exports/Resumen_Evidencias_OPS.xlsx
+++ b/exports/Resumen_Evidencias_OPS.xlsx
@@ -16,7 +16,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Resumen'!$A$1:$G$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Tiendas'!$A$4:$H$76</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Tiendas'!$1:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Actividades'!$A$4:$F$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Actividades'!$A$4:$F$14</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -27,7 +27,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -76,8 +76,14 @@
       <color rgb="00922F24"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Aptos"/>
+      <b val="1"/>
+      <color rgb="0080520C"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -109,6 +115,11 @@
         <fgColor rgb="00F9E6E3"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF0D5"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -127,7 +138,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -170,6 +181,9 @@
     </xf>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -563,7 +577,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Centro Norte · Corte 29/08/2026 12:13</t>
+          <t>Centro Norte · Corte 29/08/2026 14:28</t>
         </is>
       </c>
     </row>
@@ -586,10 +600,10 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>646</v>
+        <v>712</v>
       </c>
       <c r="E6" s="5">
         <f>IFERROR(A6/(A6+C6),0)</f>
@@ -647,10 +661,10 @@
         <v>10</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="F10" s="9">
         <f>IFERROR(D10/(D10+E10),0)</f>
@@ -668,17 +682,17 @@
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina</t>
+          <t>Vanessa Carreño</t>
         </is>
       </c>
       <c r="C11" s="11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E11" s="12" t="n">
-        <v>108</v>
+        <v>129</v>
       </c>
       <c r="F11" s="13">
         <f>IFERROR(D11/(D11+E11),0)</f>
@@ -696,17 +710,17 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño</t>
+          <t>Nancy Carolina</t>
         </is>
       </c>
       <c r="C12" s="7" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D12" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E12" s="8" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="F12" s="9">
         <f>IFERROR(D12/(D12+E12),0)</f>
@@ -734,7 +748,7 @@
         <v>0</v>
       </c>
       <c r="E13" s="12" t="n">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="F13" s="13">
         <f>IFERROR(D13/(D13+E13),0)</f>
@@ -762,7 +776,7 @@
         <v>0</v>
       </c>
       <c r="E14" s="8" t="n">
-        <v>117</v>
+        <v>130</v>
       </c>
       <c r="F14" s="9">
         <f>IFERROR(D14/(D14+E14),0)</f>
@@ -790,7 +804,7 @@
         <v>0</v>
       </c>
       <c r="E15" s="12" t="n">
-        <v>117</v>
+        <v>130</v>
       </c>
       <c r="F15" s="13">
         <f>IFERROR(D15/(D15+E15),0)</f>
@@ -859,7 +873,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Centro Norte · Corte 29/08/2026 12:13</t>
+          <t>Centro Norte · Corte 29/08/2026 14:28</t>
         </is>
       </c>
     </row>
@@ -911,12 +925,12 @@
       </c>
       <c r="B5" s="14" t="inlineStr">
         <is>
-          <t>38894</t>
+          <t>38862</t>
         </is>
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>Galerias Perinorte</t>
+          <t>San Miguel Izcalli</t>
         </is>
       </c>
       <c r="D5" s="12" t="inlineStr">
@@ -925,18 +939,18 @@
         </is>
       </c>
       <c r="E5" s="11" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G5" s="13">
         <f>IFERROR(E5/(E5+F5),0)</f>
         <v/>
       </c>
-      <c r="H5" s="10" t="inlineStr">
-        <is>
-          <t>Atención</t>
+      <c r="H5" s="15" t="inlineStr">
+        <is>
+          <t>Seguimiento</t>
         </is>
       </c>
     </row>
@@ -944,14 +958,14 @@
       <c r="A6" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="15" t="inlineStr">
-        <is>
-          <t>38333</t>
+      <c r="B6" s="16" t="inlineStr">
+        <is>
+          <t>38894</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>Izcalli Mega</t>
+          <t>Galerias Perinorte</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
@@ -960,7 +974,7 @@
         </is>
       </c>
       <c r="E6" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F6" s="7" t="n">
         <v>8</v>
@@ -981,21 +995,21 @@
       </c>
       <c r="B7" s="14" t="inlineStr">
         <is>
-          <t>38186</t>
+          <t>43194</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>Arboledas</t>
+          <t>Atana Lindavista</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E7" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" s="11" t="n">
         <v>9</v>
@@ -1014,23 +1028,23 @@
       <c r="A8" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="15" t="inlineStr">
-        <is>
-          <t>43194</t>
+      <c r="B8" s="16" t="inlineStr">
+        <is>
+          <t>38333</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>Atana Lindavista</t>
+          <t>Izcalli Mega</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E8" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" s="7" t="n">
         <v>9</v>
@@ -1051,24 +1065,24 @@
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>43043</t>
+          <t>38186</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>Atizapan</t>
+          <t>Arboledas</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E9" s="11" t="n">
         <v>0</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G9" s="13">
         <f>IFERROR(E9/(E9+F9),0)</f>
@@ -1084,14 +1098,14 @@
       <c r="A10" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="15" t="inlineStr">
-        <is>
-          <t>38149</t>
+      <c r="B10" s="16" t="inlineStr">
+        <is>
+          <t>43043</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>Bellavista</t>
+          <t>Atizapan</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
@@ -1103,7 +1117,7 @@
         <v>0</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G10" s="9">
         <f>IFERROR(E10/(E10+F10),0)</f>
@@ -1121,24 +1135,24 @@
       </c>
       <c r="B11" s="14" t="inlineStr">
         <is>
-          <t>38930</t>
+          <t>38149</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>Blvd. Aeropuerto dt</t>
+          <t>Bellavista</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E11" s="11" t="n">
         <v>0</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G11" s="13">
         <f>IFERROR(E11/(E11+F11),0)</f>
@@ -1154,14 +1168,14 @@
       <c r="A12" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="15" t="inlineStr">
-        <is>
-          <t>38529</t>
+      <c r="B12" s="16" t="inlineStr">
+        <is>
+          <t>38930</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Bosques de Aragon</t>
+          <t>Blvd. Aeropuerto dt</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
@@ -1173,7 +1187,7 @@
         <v>0</v>
       </c>
       <c r="F12" s="7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G12" s="9">
         <f>IFERROR(E12/(E12+F12),0)</f>
@@ -1191,24 +1205,24 @@
       </c>
       <c r="B13" s="14" t="inlineStr">
         <is>
-          <t>38527</t>
+          <t>38529</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>Camarones</t>
+          <t>Bosques de Aragon</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E13" s="11" t="n">
         <v>0</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G13" s="13">
         <f>IFERROR(E13/(E13+F13),0)</f>
@@ -1224,14 +1238,14 @@
       <c r="A14" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="15" t="inlineStr">
-        <is>
-          <t>38837</t>
+      <c r="B14" s="16" t="inlineStr">
+        <is>
+          <t>38527</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Centenario Azcapotzalco</t>
+          <t>Camarones</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr">
@@ -1243,7 +1257,7 @@
         <v>0</v>
       </c>
       <c r="F14" s="7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G14" s="9">
         <f>IFERROR(E14/(E14+F14),0)</f>
@@ -1261,24 +1275,24 @@
       </c>
       <c r="B15" s="14" t="inlineStr">
         <is>
-          <t>38394</t>
+          <t>38837</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>Centro Comercial Lomas Verdes</t>
+          <t>Centenario Azcapotzalco</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E15" s="11" t="n">
         <v>0</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G15" s="13">
         <f>IFERROR(E15/(E15+F15),0)</f>
@@ -1294,26 +1308,26 @@
       <c r="A16" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="15" t="inlineStr">
-        <is>
-          <t>38695</t>
+      <c r="B16" s="16" t="inlineStr">
+        <is>
+          <t>38394</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>Cetram 4 Caminos</t>
+          <t>Centro Comercial Lomas Verdes</t>
         </is>
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E16" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F16" s="7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G16" s="9">
         <f>IFERROR(E16/(E16+F16),0)</f>
@@ -1331,24 +1345,24 @@
       </c>
       <c r="B17" s="14" t="inlineStr">
         <is>
-          <t>38535</t>
+          <t>38695</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>City Center Esmeralda</t>
+          <t>Cetram 4 Caminos</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E17" s="11" t="n">
         <v>0</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G17" s="13">
         <f>IFERROR(E17/(E17+F17),0)</f>
@@ -1364,26 +1378,26 @@
       <c r="A18" s="7" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="15" t="inlineStr">
-        <is>
-          <t>38401</t>
+      <c r="B18" s="16" t="inlineStr">
+        <is>
+          <t>38535</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>Coacalco</t>
+          <t>City Center Esmeralda</t>
         </is>
       </c>
       <c r="D18" s="8" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E18" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F18" s="7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G18" s="9">
         <f>IFERROR(E18/(E18+F18),0)</f>
@@ -1401,12 +1415,12 @@
       </c>
       <c r="B19" s="14" t="inlineStr">
         <is>
-          <t>38604</t>
+          <t>38401</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>Cosmopol</t>
+          <t>Coacalco</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
@@ -1418,7 +1432,7 @@
         <v>0</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G19" s="13">
         <f>IFERROR(E19/(E19+F19),0)</f>
@@ -1434,14 +1448,14 @@
       <c r="A20" s="7" t="n">
         <v>16</v>
       </c>
-      <c r="B20" s="15" t="inlineStr">
-        <is>
-          <t>43193</t>
+      <c r="B20" s="16" t="inlineStr">
+        <is>
+          <t>38604</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>Cosmopol N1</t>
+          <t>Cosmopol</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr">
@@ -1453,7 +1467,7 @@
         <v>0</v>
       </c>
       <c r="F20" s="7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G20" s="9">
         <f>IFERROR(E20/(E20+F20),0)</f>
@@ -1471,24 +1485,24 @@
       </c>
       <c r="B21" s="14" t="inlineStr">
         <is>
-          <t>38197</t>
+          <t>43193</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>Echegaray</t>
+          <t>Cosmopol N1</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E21" s="11" t="n">
         <v>0</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G21" s="13">
         <f>IFERROR(E21/(E21+F21),0)</f>
@@ -1504,26 +1518,26 @@
       <c r="A22" s="7" t="n">
         <v>18</v>
       </c>
-      <c r="B22" s="15" t="inlineStr">
-        <is>
-          <t>38431</t>
+      <c r="B22" s="16" t="inlineStr">
+        <is>
+          <t>38197</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>Eduardo Molina</t>
+          <t>Echegaray</t>
         </is>
       </c>
       <c r="D22" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E22" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G22" s="9">
         <f>IFERROR(E22/(E22+F22),0)</f>
@@ -1541,24 +1555,24 @@
       </c>
       <c r="B23" s="14" t="inlineStr">
         <is>
-          <t>38458</t>
+          <t>38431</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>El Rosario</t>
+          <t>Eduardo Molina</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E23" s="11" t="n">
         <v>0</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G23" s="13">
         <f>IFERROR(E23/(E23+F23),0)</f>
@@ -1574,26 +1588,26 @@
       <c r="A24" s="7" t="n">
         <v>20</v>
       </c>
-      <c r="B24" s="15" t="inlineStr">
-        <is>
-          <t>38903</t>
+      <c r="B24" s="16" t="inlineStr">
+        <is>
+          <t>38458</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>Encuentro Oceania</t>
+          <t>El Rosario</t>
         </is>
       </c>
       <c r="D24" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E24" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F24" s="7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G24" s="9">
         <f>IFERROR(E24/(E24+F24),0)</f>
@@ -1611,12 +1625,12 @@
       </c>
       <c r="B25" s="14" t="inlineStr">
         <is>
-          <t>38995</t>
+          <t>38903</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>Encuentro Oceania II</t>
+          <t>Encuentro Oceania</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
@@ -1628,7 +1642,7 @@
         <v>0</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G25" s="13">
         <f>IFERROR(E25/(E25+F25),0)</f>
@@ -1644,26 +1658,26 @@
       <c r="A26" s="7" t="n">
         <v>22</v>
       </c>
-      <c r="B26" s="15" t="inlineStr">
-        <is>
-          <t>38507</t>
+      <c r="B26" s="16" t="inlineStr">
+        <is>
+          <t>38995</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>Espacio Vista del Valle</t>
+          <t>Encuentro Oceania II</t>
         </is>
       </c>
       <c r="D26" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E26" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F26" s="7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G26" s="9">
         <f>IFERROR(E26/(E26+F26),0)</f>
@@ -1681,12 +1695,12 @@
       </c>
       <c r="B27" s="14" t="inlineStr">
         <is>
-          <t>38363</t>
+          <t>38507</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>Galerias Atizapan</t>
+          <t>Espacio Vista del Valle</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
@@ -1698,7 +1712,7 @@
         <v>0</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G27" s="13">
         <f>IFERROR(E27/(E27+F27),0)</f>
@@ -1714,26 +1728,26 @@
       <c r="A28" s="7" t="n">
         <v>24</v>
       </c>
-      <c r="B28" s="15" t="inlineStr">
-        <is>
-          <t>38770</t>
+      <c r="B28" s="16" t="inlineStr">
+        <is>
+          <t>38363</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>Gustavo Baz 29</t>
+          <t>Galerias Atizapan</t>
         </is>
       </c>
       <c r="D28" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E28" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F28" s="7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G28" s="9">
         <f>IFERROR(E28/(E28+F28),0)</f>
@@ -1751,24 +1765,24 @@
       </c>
       <c r="B29" s="14" t="inlineStr">
         <is>
-          <t>38230</t>
+          <t>38770</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>ITEMS Edo de Mexico</t>
+          <t>Gustavo Baz 29</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E29" s="11" t="n">
         <v>0</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G29" s="13">
         <f>IFERROR(E29/(E29+F29),0)</f>
@@ -1784,14 +1798,14 @@
       <c r="A30" s="7" t="n">
         <v>26</v>
       </c>
-      <c r="B30" s="15" t="inlineStr">
-        <is>
-          <t>38661</t>
+      <c r="B30" s="16" t="inlineStr">
+        <is>
+          <t>38230</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>Jinetes</t>
+          <t>ITEMS Edo de Mexico</t>
         </is>
       </c>
       <c r="D30" s="8" t="inlineStr">
@@ -1803,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="F30" s="7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G30" s="9">
         <f>IFERROR(E30/(E30+F30),0)</f>
@@ -1821,24 +1835,24 @@
       </c>
       <c r="B31" s="14" t="inlineStr">
         <is>
-          <t>38205</t>
+          <t>38661</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>Lindavista</t>
+          <t>Jinetes</t>
         </is>
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E31" s="11" t="n">
         <v>0</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G31" s="13">
         <f>IFERROR(E31/(E31+F31),0)</f>
@@ -1854,14 +1868,14 @@
       <c r="A32" s="7" t="n">
         <v>28</v>
       </c>
-      <c r="B32" s="15" t="inlineStr">
-        <is>
-          <t>38207</t>
+      <c r="B32" s="16" t="inlineStr">
+        <is>
+          <t>38205</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>Lindavista II</t>
+          <t>Lindavista</t>
         </is>
       </c>
       <c r="D32" s="8" t="inlineStr">
@@ -1873,7 +1887,7 @@
         <v>0</v>
       </c>
       <c r="F32" s="7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G32" s="9">
         <f>IFERROR(E32/(E32+F32),0)</f>
@@ -1891,24 +1905,24 @@
       </c>
       <c r="B33" s="14" t="inlineStr">
         <is>
-          <t>38119</t>
+          <t>38207</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>Lomas Verdes</t>
+          <t>Lindavista II</t>
         </is>
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E33" s="11" t="n">
         <v>0</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G33" s="13">
         <f>IFERROR(E33/(E33+F33),0)</f>
@@ -1924,14 +1938,14 @@
       <c r="A34" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="B34" s="15" t="inlineStr">
-        <is>
-          <t>38270</t>
+      <c r="B34" s="16" t="inlineStr">
+        <is>
+          <t>38119</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>Lomas Verdes II</t>
+          <t>Lomas Verdes</t>
         </is>
       </c>
       <c r="D34" s="8" t="inlineStr">
@@ -1943,7 +1957,7 @@
         <v>0</v>
       </c>
       <c r="F34" s="7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G34" s="9">
         <f>IFERROR(E34/(E34+F34),0)</f>
@@ -1961,24 +1975,24 @@
       </c>
       <c r="B35" s="14" t="inlineStr">
         <is>
-          <t>38368</t>
+          <t>38270</t>
         </is>
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>Luna Park</t>
+          <t>Lomas Verdes II</t>
         </is>
       </c>
       <c r="D35" s="12" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E35" s="11" t="n">
         <v>0</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G35" s="13">
         <f>IFERROR(E35/(E35+F35),0)</f>
@@ -1994,26 +2008,26 @@
       <c r="A36" s="7" t="n">
         <v>32</v>
       </c>
-      <c r="B36" s="15" t="inlineStr">
-        <is>
-          <t>38371</t>
+      <c r="B36" s="16" t="inlineStr">
+        <is>
+          <t>38368</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>Montevideo DT</t>
+          <t>Luna Park</t>
         </is>
       </c>
       <c r="D36" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E36" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F36" s="7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G36" s="9">
         <f>IFERROR(E36/(E36+F36),0)</f>
@@ -2031,12 +2045,12 @@
       </c>
       <c r="B37" s="14" t="inlineStr">
         <is>
-          <t>43111</t>
+          <t>38371</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>Montevideo Insurgentes</t>
+          <t>Montevideo DT</t>
         </is>
       </c>
       <c r="D37" s="12" t="inlineStr">
@@ -2048,7 +2062,7 @@
         <v>0</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G37" s="13">
         <f>IFERROR(E37/(E37+F37),0)</f>
@@ -2064,26 +2078,26 @@
       <c r="A38" s="7" t="n">
         <v>34</v>
       </c>
-      <c r="B38" s="15" t="inlineStr">
-        <is>
-          <t>38674</t>
+      <c r="B38" s="16" t="inlineStr">
+        <is>
+          <t>43111</t>
         </is>
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>Mundo E</t>
+          <t>Montevideo Insurgentes</t>
         </is>
       </c>
       <c r="D38" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E38" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F38" s="7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G38" s="9">
         <f>IFERROR(E38/(E38+F38),0)</f>
@@ -2101,12 +2115,12 @@
       </c>
       <c r="B39" s="14" t="inlineStr">
         <is>
-          <t>38845</t>
+          <t>38674</t>
         </is>
       </c>
       <c r="C39" s="12" t="inlineStr">
         <is>
-          <t>Mundo E II</t>
+          <t>Mundo E</t>
         </is>
       </c>
       <c r="D39" s="12" t="inlineStr">
@@ -2118,7 +2132,7 @@
         <v>0</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G39" s="13">
         <f>IFERROR(E39/(E39+F39),0)</f>
@@ -2134,26 +2148,26 @@
       <c r="A40" s="7" t="n">
         <v>36</v>
       </c>
-      <c r="B40" s="15" t="inlineStr">
-        <is>
-          <t>43195</t>
+      <c r="B40" s="16" t="inlineStr">
+        <is>
+          <t>38845</t>
         </is>
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>Parque Jadin kiosko</t>
+          <t>Mundo E II</t>
         </is>
       </c>
       <c r="D40" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E40" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F40" s="7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G40" s="9">
         <f>IFERROR(E40/(E40+F40),0)</f>
@@ -2171,24 +2185,24 @@
       </c>
       <c r="B41" s="14" t="inlineStr">
         <is>
-          <t>38937</t>
+          <t>43195</t>
         </is>
       </c>
       <c r="C41" s="12" t="inlineStr">
         <is>
-          <t>Parque Tepeyac Piso 1</t>
+          <t>Parque Jadin kiosko</t>
         </is>
       </c>
       <c r="D41" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E41" s="11" t="n">
         <v>0</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G41" s="13">
         <f>IFERROR(E41/(E41+F41),0)</f>
@@ -2204,14 +2218,14 @@
       <c r="A42" s="7" t="n">
         <v>38</v>
       </c>
-      <c r="B42" s="15" t="inlineStr">
-        <is>
-          <t>38965</t>
+      <c r="B42" s="16" t="inlineStr">
+        <is>
+          <t>38937</t>
         </is>
       </c>
       <c r="C42" s="8" t="inlineStr">
         <is>
-          <t>Parque Tepeyac Piso 2</t>
+          <t>Parque Tepeyac Piso 1</t>
         </is>
       </c>
       <c r="D42" s="8" t="inlineStr">
@@ -2223,7 +2237,7 @@
         <v>0</v>
       </c>
       <c r="F42" s="7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G42" s="9">
         <f>IFERROR(E42/(E42+F42),0)</f>
@@ -2241,24 +2255,24 @@
       </c>
       <c r="B43" s="14" t="inlineStr">
         <is>
-          <t>38561</t>
+          <t>38965</t>
         </is>
       </c>
       <c r="C43" s="12" t="inlineStr">
         <is>
-          <t>Parque Toreo</t>
+          <t>Parque Tepeyac Piso 2</t>
         </is>
       </c>
       <c r="D43" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E43" s="11" t="n">
         <v>0</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G43" s="13">
         <f>IFERROR(E43/(E43+F43),0)</f>
@@ -2274,14 +2288,14 @@
       <c r="A44" s="7" t="n">
         <v>40</v>
       </c>
-      <c r="B44" s="15" t="inlineStr">
-        <is>
-          <t>38590</t>
+      <c r="B44" s="16" t="inlineStr">
+        <is>
+          <t>38561</t>
         </is>
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t>Parque Toreo II</t>
+          <t>Parque Toreo</t>
         </is>
       </c>
       <c r="D44" s="8" t="inlineStr">
@@ -2293,7 +2307,7 @@
         <v>0</v>
       </c>
       <c r="F44" s="7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G44" s="9">
         <f>IFERROR(E44/(E44+F44),0)</f>
@@ -2311,24 +2325,24 @@
       </c>
       <c r="B45" s="14" t="inlineStr">
         <is>
-          <t>38792</t>
+          <t>38590</t>
         </is>
       </c>
       <c r="C45" s="12" t="inlineStr">
         <is>
-          <t>Pasaje Tlanepantla</t>
+          <t>Parque Toreo II</t>
         </is>
       </c>
       <c r="D45" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E45" s="11" t="n">
         <v>0</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G45" s="13">
         <f>IFERROR(E45/(E45+F45),0)</f>
@@ -2344,26 +2358,26 @@
       <c r="A46" s="7" t="n">
         <v>42</v>
       </c>
-      <c r="B46" s="15" t="inlineStr">
-        <is>
-          <t>38546</t>
+      <c r="B46" s="16" t="inlineStr">
+        <is>
+          <t>38792</t>
         </is>
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t>Patio Claveria</t>
+          <t>Pasaje Tlanepantla</t>
         </is>
       </c>
       <c r="D46" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E46" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F46" s="7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G46" s="9">
         <f>IFERROR(E46/(E46+F46),0)</f>
@@ -2381,24 +2395,24 @@
       </c>
       <c r="B47" s="14" t="inlineStr">
         <is>
-          <t>38515</t>
+          <t>38546</t>
         </is>
       </c>
       <c r="C47" s="12" t="inlineStr">
         <is>
-          <t>Patio Ecatepec</t>
+          <t>Patio Claveria</t>
         </is>
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E47" s="11" t="n">
         <v>0</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G47" s="13">
         <f>IFERROR(E47/(E47+F47),0)</f>
@@ -2414,26 +2428,26 @@
       <c r="A48" s="7" t="n">
         <v>44</v>
       </c>
-      <c r="B48" s="15" t="inlineStr">
-        <is>
-          <t>38677</t>
+      <c r="B48" s="16" t="inlineStr">
+        <is>
+          <t>38515</t>
         </is>
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
-          <t>Patio la Raza</t>
+          <t>Patio Ecatepec</t>
         </is>
       </c>
       <c r="D48" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E48" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F48" s="7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G48" s="9">
         <f>IFERROR(E48/(E48+F48),0)</f>
@@ -2451,24 +2465,24 @@
       </c>
       <c r="B49" s="14" t="inlineStr">
         <is>
-          <t>38176</t>
+          <t>38677</t>
         </is>
       </c>
       <c r="C49" s="12" t="inlineStr">
         <is>
-          <t>Periferico Satélite DT</t>
+          <t>Patio la Raza</t>
         </is>
       </c>
       <c r="D49" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E49" s="11" t="n">
         <v>0</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G49" s="13">
         <f>IFERROR(E49/(E49+F49),0)</f>
@@ -2484,26 +2498,26 @@
       <c r="A50" s="7" t="n">
         <v>46</v>
       </c>
-      <c r="B50" s="15" t="inlineStr">
-        <is>
-          <t>38924</t>
+      <c r="B50" s="16" t="inlineStr">
+        <is>
+          <t>38176</t>
         </is>
       </c>
       <c r="C50" s="8" t="inlineStr">
         <is>
-          <t>Plaza Aeropuerto</t>
+          <t>Periferico Satélite DT</t>
         </is>
       </c>
       <c r="D50" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E50" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F50" s="7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G50" s="9">
         <f>IFERROR(E50/(E50+F50),0)</f>
@@ -2521,12 +2535,12 @@
       </c>
       <c r="B51" s="14" t="inlineStr">
         <is>
-          <t>38719</t>
+          <t>38924</t>
         </is>
       </c>
       <c r="C51" s="12" t="inlineStr">
         <is>
-          <t>Plaza Fortuna</t>
+          <t>Plaza Aeropuerto</t>
         </is>
       </c>
       <c r="D51" s="12" t="inlineStr">
@@ -2538,7 +2552,7 @@
         <v>0</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G51" s="13">
         <f>IFERROR(E51/(E51+F51),0)</f>
@@ -2554,26 +2568,26 @@
       <c r="A52" s="7" t="n">
         <v>48</v>
       </c>
-      <c r="B52" s="15" t="inlineStr">
-        <is>
-          <t>38427</t>
+      <c r="B52" s="16" t="inlineStr">
+        <is>
+          <t>38719</t>
         </is>
       </c>
       <c r="C52" s="8" t="inlineStr">
         <is>
-          <t>Plaza Satelite</t>
+          <t>Plaza Fortuna</t>
         </is>
       </c>
       <c r="D52" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E52" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F52" s="7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G52" s="9">
         <f>IFERROR(E52/(E52+F52),0)</f>
@@ -2591,12 +2605,12 @@
       </c>
       <c r="B53" s="14" t="inlineStr">
         <is>
-          <t>38859</t>
+          <t>38427</t>
         </is>
       </c>
       <c r="C53" s="12" t="inlineStr">
         <is>
-          <t>Plaza Satelite II N1</t>
+          <t>Plaza Satelite</t>
         </is>
       </c>
       <c r="D53" s="12" t="inlineStr">
@@ -2608,7 +2622,7 @@
         <v>0</v>
       </c>
       <c r="F53" s="11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G53" s="13">
         <f>IFERROR(E53/(E53+F53),0)</f>
@@ -2624,26 +2638,26 @@
       <c r="A54" s="7" t="n">
         <v>50</v>
       </c>
-      <c r="B54" s="15" t="inlineStr">
-        <is>
-          <t>38811</t>
+      <c r="B54" s="16" t="inlineStr">
+        <is>
+          <t>38859</t>
         </is>
       </c>
       <c r="C54" s="8" t="inlineStr">
         <is>
-          <t>Plaza Tepeyac</t>
+          <t>Plaza Satelite II N1</t>
         </is>
       </c>
       <c r="D54" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E54" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F54" s="7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G54" s="9">
         <f>IFERROR(E54/(E54+F54),0)</f>
@@ -2661,24 +2675,24 @@
       </c>
       <c r="B55" s="14" t="inlineStr">
         <is>
-          <t>43132</t>
+          <t>38811</t>
         </is>
       </c>
       <c r="C55" s="12" t="inlineStr">
         <is>
-          <t>Plaza Vista Norte</t>
+          <t>Plaza Tepeyac</t>
         </is>
       </c>
       <c r="D55" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E55" s="11" t="n">
         <v>0</v>
       </c>
       <c r="F55" s="11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G55" s="13">
         <f>IFERROR(E55/(E55+F55),0)</f>
@@ -2694,26 +2708,26 @@
       <c r="A56" s="7" t="n">
         <v>52</v>
       </c>
-      <c r="B56" s="15" t="inlineStr">
-        <is>
-          <t>38456</t>
+      <c r="B56" s="16" t="inlineStr">
+        <is>
+          <t>43132</t>
         </is>
       </c>
       <c r="C56" s="8" t="inlineStr">
         <is>
-          <t>Plaza las Flores</t>
+          <t>Plaza Vista Norte</t>
         </is>
       </c>
       <c r="D56" s="8" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E56" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F56" s="7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G56" s="9">
         <f>IFERROR(E56/(E56+F56),0)</f>
@@ -2731,24 +2745,24 @@
       </c>
       <c r="B57" s="14" t="inlineStr">
         <is>
-          <t>38136</t>
+          <t>38456</t>
         </is>
       </c>
       <c r="C57" s="12" t="inlineStr">
         <is>
-          <t>Punta Norte</t>
+          <t>Plaza las Flores</t>
         </is>
       </c>
       <c r="D57" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E57" s="11" t="n">
         <v>0</v>
       </c>
       <c r="F57" s="11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G57" s="13">
         <f>IFERROR(E57/(E57+F57),0)</f>
@@ -2764,26 +2778,26 @@
       <c r="A58" s="7" t="n">
         <v>54</v>
       </c>
-      <c r="B58" s="15" t="inlineStr">
-        <is>
-          <t>43152</t>
+      <c r="B58" s="16" t="inlineStr">
+        <is>
+          <t>38136</t>
         </is>
       </c>
       <c r="C58" s="8" t="inlineStr">
         <is>
-          <t>Samara Satélite</t>
+          <t>Punta Norte</t>
         </is>
       </c>
       <c r="D58" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E58" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F58" s="7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G58" s="9">
         <f>IFERROR(E58/(E58+F58),0)</f>
@@ -2801,24 +2815,24 @@
       </c>
       <c r="B59" s="14" t="inlineStr">
         <is>
-          <t>38339</t>
+          <t>43152</t>
         </is>
       </c>
       <c r="C59" s="12" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Samara Satélite</t>
         </is>
       </c>
       <c r="D59" s="12" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E59" s="11" t="n">
         <v>0</v>
       </c>
       <c r="F59" s="11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G59" s="13">
         <f>IFERROR(E59/(E59+F59),0)</f>
@@ -2834,26 +2848,26 @@
       <c r="A60" s="7" t="n">
         <v>56</v>
       </c>
-      <c r="B60" s="15" t="inlineStr">
-        <is>
-          <t>38266</t>
+      <c r="B60" s="16" t="inlineStr">
+        <is>
+          <t>38339</t>
         </is>
       </c>
       <c r="C60" s="8" t="inlineStr">
         <is>
-          <t>San Mateo</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="D60" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E60" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F60" s="7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G60" s="9">
         <f>IFERROR(E60/(E60+F60),0)</f>
@@ -2871,24 +2885,24 @@
       </c>
       <c r="B61" s="14" t="inlineStr">
         <is>
-          <t>38862</t>
+          <t>38266</t>
         </is>
       </c>
       <c r="C61" s="12" t="inlineStr">
         <is>
-          <t>San Miguel Izcalli</t>
+          <t>San Mateo</t>
         </is>
       </c>
       <c r="D61" s="12" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E61" s="11" t="n">
         <v>0</v>
       </c>
       <c r="F61" s="11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G61" s="13">
         <f>IFERROR(E61/(E61+F61),0)</f>
@@ -2904,7 +2918,7 @@
       <c r="A62" s="7" t="n">
         <v>58</v>
       </c>
-      <c r="B62" s="15" t="inlineStr">
+      <c r="B62" s="16" t="inlineStr">
         <is>
           <t>38460</t>
         </is>
@@ -2923,7 +2937,7 @@
         <v>0</v>
       </c>
       <c r="F62" s="7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G62" s="9">
         <f>IFERROR(E62/(E62+F62),0)</f>
@@ -2958,7 +2972,7 @@
         <v>0</v>
       </c>
       <c r="F63" s="11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G63" s="13">
         <f>IFERROR(E63/(E63+F63),0)</f>
@@ -2974,7 +2988,7 @@
       <c r="A64" s="7" t="n">
         <v>60</v>
       </c>
-      <c r="B64" s="15" t="inlineStr">
+      <c r="B64" s="16" t="inlineStr">
         <is>
           <t>38475</t>
         </is>
@@ -2993,7 +3007,7 @@
         <v>0</v>
       </c>
       <c r="F64" s="7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G64" s="9">
         <f>IFERROR(E64/(E64+F64),0)</f>
@@ -3028,7 +3042,7 @@
         <v>0</v>
       </c>
       <c r="F65" s="11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G65" s="13">
         <f>IFERROR(E65/(E65+F65),0)</f>
@@ -3044,7 +3058,7 @@
       <c r="A66" s="7" t="n">
         <v>62</v>
       </c>
-      <c r="B66" s="15" t="inlineStr">
+      <c r="B66" s="16" t="inlineStr">
         <is>
           <t>38925</t>
         </is>
@@ -3063,7 +3077,7 @@
         <v>0</v>
       </c>
       <c r="F66" s="7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G66" s="9">
         <f>IFERROR(E66/(E66+F66),0)</f>
@@ -3098,7 +3112,7 @@
         <v>0</v>
       </c>
       <c r="F67" s="11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G67" s="13">
         <f>IFERROR(E67/(E67+F67),0)</f>
@@ -3114,7 +3128,7 @@
       <c r="A68" s="7" t="n">
         <v>64</v>
       </c>
-      <c r="B68" s="15" t="inlineStr">
+      <c r="B68" s="16" t="inlineStr">
         <is>
           <t>38606</t>
         </is>
@@ -3133,7 +3147,7 @@
         <v>0</v>
       </c>
       <c r="F68" s="7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G68" s="9">
         <f>IFERROR(E68/(E68+F68),0)</f>
@@ -3168,7 +3182,7 @@
         <v>0</v>
       </c>
       <c r="F69" s="11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G69" s="13">
         <f>IFERROR(E69/(E69+F69),0)</f>
@@ -3184,7 +3198,7 @@
       <c r="A70" s="7" t="n">
         <v>66</v>
       </c>
-      <c r="B70" s="15" t="inlineStr">
+      <c r="B70" s="16" t="inlineStr">
         <is>
           <t>43130</t>
         </is>
@@ -3203,7 +3217,7 @@
         <v>0</v>
       </c>
       <c r="F70" s="7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G70" s="9">
         <f>IFERROR(E70/(E70+F70),0)</f>
@@ -3238,7 +3252,7 @@
         <v>0</v>
       </c>
       <c r="F71" s="11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G71" s="13">
         <f>IFERROR(E71/(E71+F71),0)</f>
@@ -3254,7 +3268,7 @@
       <c r="A72" s="7" t="n">
         <v>68</v>
       </c>
-      <c r="B72" s="15" t="inlineStr">
+      <c r="B72" s="16" t="inlineStr">
         <is>
           <t>38651</t>
         </is>
@@ -3273,7 +3287,7 @@
         <v>0</v>
       </c>
       <c r="F72" s="7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G72" s="9">
         <f>IFERROR(E72/(E72+F72),0)</f>
@@ -3308,7 +3322,7 @@
         <v>0</v>
       </c>
       <c r="F73" s="11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G73" s="13">
         <f>IFERROR(E73/(E73+F73),0)</f>
@@ -3324,7 +3338,7 @@
       <c r="A74" s="7" t="n">
         <v>70</v>
       </c>
-      <c r="B74" s="15" t="inlineStr">
+      <c r="B74" s="16" t="inlineStr">
         <is>
           <t>38656</t>
         </is>
@@ -3343,7 +3357,7 @@
         <v>0</v>
       </c>
       <c r="F74" s="7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G74" s="9">
         <f>IFERROR(E74/(E74+F74),0)</f>
@@ -3378,7 +3392,7 @@
         <v>0</v>
       </c>
       <c r="F75" s="11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G75" s="13">
         <f>IFERROR(E75/(E75+F75),0)</f>
@@ -3394,7 +3408,7 @@
       <c r="A76" s="7" t="n">
         <v>72</v>
       </c>
-      <c r="B76" s="15" t="inlineStr">
+      <c r="B76" s="16" t="inlineStr">
         <is>
           <t>38142</t>
         </is>
@@ -3413,7 +3427,7 @@
         <v>0</v>
       </c>
       <c r="F76" s="7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G76" s="9">
         <f>IFERROR(E76/(E76+F76),0)</f>
@@ -3452,7 +3466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3474,7 +3488,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Centro Norte · Corte 29/08/2026 12:13</t>
+          <t>Centro Norte · Corte 29/08/2026 14:28</t>
         </is>
       </c>
     </row>
@@ -3520,10 +3534,10 @@
         </is>
       </c>
       <c r="C5" s="11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E5" s="13">
         <f>IFERROR(C5/(C5+D5),0)</f>
@@ -3570,10 +3584,10 @@
         </is>
       </c>
       <c r="C7" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E7" s="13">
         <f>IFERROR(C7/(C7+D7),0)</f>
@@ -3670,10 +3684,10 @@
         </is>
       </c>
       <c r="C11" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E11" s="13">
         <f>IFERROR(C11/(C11+D11),0)</f>
@@ -3695,10 +3709,10 @@
         </is>
       </c>
       <c r="C12" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E12" s="9">
         <f>IFERROR(C12/(C12+D12),0)</f>
@@ -3735,13 +3749,38 @@
         </is>
       </c>
     </row>
+    <row r="14" ht="21" customHeight="1">
+      <c r="A14" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>Activacion PSL Sharpie</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D14" s="7" t="n">
+        <v>72</v>
+      </c>
+      <c r="E14" s="9">
+        <f>IFERROR(C14/(C14+D14),0)</f>
+        <v/>
+      </c>
+      <c r="F14" s="8" t="inlineStr">
+        <is>
+          <t>31/08/26</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:F13"/>
+  <autoFilter ref="A4:F14"/>
   <mergeCells count="2">
     <mergeCell ref="A3:F3"/>
     <mergeCell ref="A1:F2"/>
   </mergeCells>
-  <conditionalFormatting sqref="E5:E13">
+  <conditionalFormatting sqref="E5:E14">
     <cfRule type="dataBar" priority="1">
       <dataBar showValue="1">
         <cfvo type="num" val="0"/>

--- a/exports/Resumen_Evidencias_OPS.xlsx
+++ b/exports/Resumen_Evidencias_OPS.xlsx
@@ -577,7 +577,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Centro Norte · Corte 29/08/2026 14:28</t>
+          <t>Centro Norte · Corte 29/08/2026 15:22</t>
         </is>
       </c>
     </row>
@@ -600,10 +600,10 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="E6" s="5">
         <f>IFERROR(A6/(A6+C6),0)</f>
@@ -682,17 +682,17 @@
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño</t>
+          <t>Yazmin Garcia</t>
         </is>
       </c>
       <c r="C11" s="11" t="n">
         <v>13</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E11" s="12" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F11" s="13">
         <f>IFERROR(D11/(D11+E11),0)</f>
@@ -710,17 +710,17 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina</t>
+          <t>Vanessa Carreño</t>
         </is>
       </c>
       <c r="C12" s="7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E12" s="8" t="n">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="F12" s="9">
         <f>IFERROR(D12/(D12+E12),0)</f>
@@ -738,17 +738,17 @@
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia</t>
+          <t>Nancy Carolina</t>
         </is>
       </c>
       <c r="C13" s="11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D13" s="11" t="n">
         <v>0</v>
       </c>
       <c r="E13" s="12" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="F13" s="13">
         <f>IFERROR(D13/(D13+E13),0)</f>
@@ -766,17 +766,17 @@
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela</t>
+          <t>Veronica Garcia</t>
         </is>
       </c>
       <c r="C14" s="7" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D14" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E14" s="8" t="n">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="F14" s="9">
         <f>IFERROR(D14/(D14+E14),0)</f>
@@ -794,7 +794,7 @@
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Garcia</t>
+          <t>Yazmin Chabela</t>
         </is>
       </c>
       <c r="C15" s="11" t="n">
@@ -873,7 +873,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Centro Norte · Corte 29/08/2026 14:28</t>
+          <t>Centro Norte · Corte 29/08/2026 15:22</t>
         </is>
       </c>
     </row>
@@ -1065,24 +1065,24 @@
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>38186</t>
+          <t>38925</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>Arboledas</t>
+          <t>Star Medica Lomas Verdes</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E9" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G9" s="13">
         <f>IFERROR(E9/(E9+F9),0)</f>
@@ -1100,12 +1100,12 @@
       </c>
       <c r="B10" s="16" t="inlineStr">
         <is>
-          <t>43043</t>
+          <t>38142</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>Atizapan</t>
+          <t>Zona Esmeralda</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
@@ -1114,10 +1114,10 @@
         </is>
       </c>
       <c r="E10" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G10" s="9">
         <f>IFERROR(E10/(E10+F10),0)</f>
@@ -1135,17 +1135,17 @@
       </c>
       <c r="B11" s="14" t="inlineStr">
         <is>
-          <t>38149</t>
+          <t>38186</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>Bellavista</t>
+          <t>Arboledas</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E11" s="11" t="n">
@@ -1170,17 +1170,17 @@
       </c>
       <c r="B12" s="16" t="inlineStr">
         <is>
-          <t>38930</t>
+          <t>43043</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Blvd. Aeropuerto dt</t>
+          <t>Atizapan</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E12" s="7" t="n">
@@ -1205,17 +1205,17 @@
       </c>
       <c r="B13" s="14" t="inlineStr">
         <is>
-          <t>38529</t>
+          <t>38149</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>Bosques de Aragon</t>
+          <t>Bellavista</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E13" s="11" t="n">
@@ -1240,17 +1240,17 @@
       </c>
       <c r="B14" s="16" t="inlineStr">
         <is>
-          <t>38527</t>
+          <t>38930</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Camarones</t>
+          <t>Blvd. Aeropuerto dt</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E14" s="7" t="n">
@@ -1275,17 +1275,17 @@
       </c>
       <c r="B15" s="14" t="inlineStr">
         <is>
-          <t>38837</t>
+          <t>38529</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>Centenario Azcapotzalco</t>
+          <t>Bosques de Aragon</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E15" s="11" t="n">
@@ -1310,17 +1310,17 @@
       </c>
       <c r="B16" s="16" t="inlineStr">
         <is>
-          <t>38394</t>
+          <t>38527</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>Centro Comercial Lomas Verdes</t>
+          <t>Camarones</t>
         </is>
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E16" s="7" t="n">
@@ -1345,17 +1345,17 @@
       </c>
       <c r="B17" s="14" t="inlineStr">
         <is>
-          <t>38695</t>
+          <t>38837</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>Cetram 4 Caminos</t>
+          <t>Centenario Azcapotzalco</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E17" s="11" t="n">
@@ -1380,12 +1380,12 @@
       </c>
       <c r="B18" s="16" t="inlineStr">
         <is>
-          <t>38535</t>
+          <t>38394</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>City Center Esmeralda</t>
+          <t>Centro Comercial Lomas Verdes</t>
         </is>
       </c>
       <c r="D18" s="8" t="inlineStr">
@@ -1415,17 +1415,17 @@
       </c>
       <c r="B19" s="14" t="inlineStr">
         <is>
-          <t>38401</t>
+          <t>38695</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>Coacalco</t>
+          <t>Cetram 4 Caminos</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E19" s="11" t="n">
@@ -1450,17 +1450,17 @@
       </c>
       <c r="B20" s="16" t="inlineStr">
         <is>
-          <t>38604</t>
+          <t>38535</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>Cosmopol</t>
+          <t>City Center Esmeralda</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E20" s="7" t="n">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="B21" s="14" t="inlineStr">
         <is>
-          <t>43193</t>
+          <t>38401</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>Cosmopol N1</t>
+          <t>Coacalco</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
@@ -1520,17 +1520,17 @@
       </c>
       <c r="B22" s="16" t="inlineStr">
         <is>
-          <t>38197</t>
+          <t>38604</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>Echegaray</t>
+          <t>Cosmopol</t>
         </is>
       </c>
       <c r="D22" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E22" s="7" t="n">
@@ -1555,17 +1555,17 @@
       </c>
       <c r="B23" s="14" t="inlineStr">
         <is>
-          <t>38431</t>
+          <t>43193</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>Eduardo Molina</t>
+          <t>Cosmopol N1</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E23" s="11" t="n">
@@ -1590,12 +1590,12 @@
       </c>
       <c r="B24" s="16" t="inlineStr">
         <is>
-          <t>38458</t>
+          <t>38197</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>El Rosario</t>
+          <t>Echegaray</t>
         </is>
       </c>
       <c r="D24" s="8" t="inlineStr">
@@ -1625,12 +1625,12 @@
       </c>
       <c r="B25" s="14" t="inlineStr">
         <is>
-          <t>38903</t>
+          <t>38431</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>Encuentro Oceania</t>
+          <t>Eduardo Molina</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
@@ -1660,17 +1660,17 @@
       </c>
       <c r="B26" s="16" t="inlineStr">
         <is>
-          <t>38995</t>
+          <t>38458</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>Encuentro Oceania II</t>
+          <t>El Rosario</t>
         </is>
       </c>
       <c r="D26" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E26" s="7" t="n">
@@ -1695,17 +1695,17 @@
       </c>
       <c r="B27" s="14" t="inlineStr">
         <is>
-          <t>38507</t>
+          <t>38903</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>Espacio Vista del Valle</t>
+          <t>Encuentro Oceania</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E27" s="11" t="n">
@@ -1730,17 +1730,17 @@
       </c>
       <c r="B28" s="16" t="inlineStr">
         <is>
-          <t>38363</t>
+          <t>38995</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>Galerias Atizapan</t>
+          <t>Encuentro Oceania II</t>
         </is>
       </c>
       <c r="D28" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E28" s="7" t="n">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="B29" s="14" t="inlineStr">
         <is>
-          <t>38770</t>
+          <t>38507</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>Gustavo Baz 29</t>
+          <t>Espacio Vista del Valle</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E29" s="11" t="n">
@@ -1800,17 +1800,17 @@
       </c>
       <c r="B30" s="16" t="inlineStr">
         <is>
-          <t>38230</t>
+          <t>38363</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>ITEMS Edo de Mexico</t>
+          <t>Galerias Atizapan</t>
         </is>
       </c>
       <c r="D30" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E30" s="7" t="n">
@@ -1835,17 +1835,17 @@
       </c>
       <c r="B31" s="14" t="inlineStr">
         <is>
-          <t>38661</t>
+          <t>38770</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>Jinetes</t>
+          <t>Gustavo Baz 29</t>
         </is>
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E31" s="11" t="n">
@@ -1870,17 +1870,17 @@
       </c>
       <c r="B32" s="16" t="inlineStr">
         <is>
-          <t>38205</t>
+          <t>38230</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>Lindavista</t>
+          <t>ITEMS Edo de Mexico</t>
         </is>
       </c>
       <c r="D32" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E32" s="7" t="n">
@@ -1905,17 +1905,17 @@
       </c>
       <c r="B33" s="14" t="inlineStr">
         <is>
-          <t>38207</t>
+          <t>38661</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>Lindavista II</t>
+          <t>Jinetes</t>
         </is>
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E33" s="11" t="n">
@@ -1940,17 +1940,17 @@
       </c>
       <c r="B34" s="16" t="inlineStr">
         <is>
-          <t>38119</t>
+          <t>38205</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>Lomas Verdes</t>
+          <t>Lindavista</t>
         </is>
       </c>
       <c r="D34" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E34" s="7" t="n">
@@ -1975,17 +1975,17 @@
       </c>
       <c r="B35" s="14" t="inlineStr">
         <is>
-          <t>38270</t>
+          <t>38207</t>
         </is>
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>Lomas Verdes II</t>
+          <t>Lindavista II</t>
         </is>
       </c>
       <c r="D35" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E35" s="11" t="n">
@@ -2010,17 +2010,17 @@
       </c>
       <c r="B36" s="16" t="inlineStr">
         <is>
-          <t>38368</t>
+          <t>38119</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>Luna Park</t>
+          <t>Lomas Verdes</t>
         </is>
       </c>
       <c r="D36" s="8" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E36" s="7" t="n">
@@ -2045,17 +2045,17 @@
       </c>
       <c r="B37" s="14" t="inlineStr">
         <is>
-          <t>38371</t>
+          <t>38270</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>Montevideo DT</t>
+          <t>Lomas Verdes II</t>
         </is>
       </c>
       <c r="D37" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E37" s="11" t="n">
@@ -2080,17 +2080,17 @@
       </c>
       <c r="B38" s="16" t="inlineStr">
         <is>
-          <t>43111</t>
+          <t>38368</t>
         </is>
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>Montevideo Insurgentes</t>
+          <t>Luna Park</t>
         </is>
       </c>
       <c r="D38" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E38" s="7" t="n">
@@ -2115,17 +2115,17 @@
       </c>
       <c r="B39" s="14" t="inlineStr">
         <is>
-          <t>38674</t>
+          <t>38371</t>
         </is>
       </c>
       <c r="C39" s="12" t="inlineStr">
         <is>
-          <t>Mundo E</t>
+          <t>Montevideo DT</t>
         </is>
       </c>
       <c r="D39" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E39" s="11" t="n">
@@ -2150,17 +2150,17 @@
       </c>
       <c r="B40" s="16" t="inlineStr">
         <is>
-          <t>38845</t>
+          <t>43111</t>
         </is>
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>Mundo E II</t>
+          <t>Montevideo Insurgentes</t>
         </is>
       </c>
       <c r="D40" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E40" s="7" t="n">
@@ -2185,17 +2185,17 @@
       </c>
       <c r="B41" s="14" t="inlineStr">
         <is>
-          <t>43195</t>
+          <t>38674</t>
         </is>
       </c>
       <c r="C41" s="12" t="inlineStr">
         <is>
-          <t>Parque Jadin kiosko</t>
+          <t>Mundo E</t>
         </is>
       </c>
       <c r="D41" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E41" s="11" t="n">
@@ -2220,17 +2220,17 @@
       </c>
       <c r="B42" s="16" t="inlineStr">
         <is>
-          <t>38937</t>
+          <t>38845</t>
         </is>
       </c>
       <c r="C42" s="8" t="inlineStr">
         <is>
-          <t>Parque Tepeyac Piso 1</t>
+          <t>Mundo E II</t>
         </is>
       </c>
       <c r="D42" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E42" s="7" t="n">
@@ -2255,17 +2255,17 @@
       </c>
       <c r="B43" s="14" t="inlineStr">
         <is>
-          <t>38965</t>
+          <t>43195</t>
         </is>
       </c>
       <c r="C43" s="12" t="inlineStr">
         <is>
-          <t>Parque Tepeyac Piso 2</t>
+          <t>Parque Jadin kiosko</t>
         </is>
       </c>
       <c r="D43" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E43" s="11" t="n">
@@ -2290,17 +2290,17 @@
       </c>
       <c r="B44" s="16" t="inlineStr">
         <is>
-          <t>38561</t>
+          <t>38937</t>
         </is>
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t>Parque Toreo</t>
+          <t>Parque Tepeyac Piso 1</t>
         </is>
       </c>
       <c r="D44" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E44" s="7" t="n">
@@ -2325,17 +2325,17 @@
       </c>
       <c r="B45" s="14" t="inlineStr">
         <is>
-          <t>38590</t>
+          <t>38965</t>
         </is>
       </c>
       <c r="C45" s="12" t="inlineStr">
         <is>
-          <t>Parque Toreo II</t>
+          <t>Parque Tepeyac Piso 2</t>
         </is>
       </c>
       <c r="D45" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E45" s="11" t="n">
@@ -2360,17 +2360,17 @@
       </c>
       <c r="B46" s="16" t="inlineStr">
         <is>
-          <t>38792</t>
+          <t>38561</t>
         </is>
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t>Pasaje Tlanepantla</t>
+          <t>Parque Toreo</t>
         </is>
       </c>
       <c r="D46" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E46" s="7" t="n">
@@ -2395,17 +2395,17 @@
       </c>
       <c r="B47" s="14" t="inlineStr">
         <is>
-          <t>38546</t>
+          <t>38590</t>
         </is>
       </c>
       <c r="C47" s="12" t="inlineStr">
         <is>
-          <t>Patio Claveria</t>
+          <t>Parque Toreo II</t>
         </is>
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E47" s="11" t="n">
@@ -2430,17 +2430,17 @@
       </c>
       <c r="B48" s="16" t="inlineStr">
         <is>
-          <t>38515</t>
+          <t>38792</t>
         </is>
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
-          <t>Patio Ecatepec</t>
+          <t>Pasaje Tlanepantla</t>
         </is>
       </c>
       <c r="D48" s="8" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E48" s="7" t="n">
@@ -2465,12 +2465,12 @@
       </c>
       <c r="B49" s="14" t="inlineStr">
         <is>
-          <t>38677</t>
+          <t>38546</t>
         </is>
       </c>
       <c r="C49" s="12" t="inlineStr">
         <is>
-          <t>Patio la Raza</t>
+          <t>Patio Claveria</t>
         </is>
       </c>
       <c r="D49" s="12" t="inlineStr">
@@ -2500,17 +2500,17 @@
       </c>
       <c r="B50" s="16" t="inlineStr">
         <is>
-          <t>38176</t>
+          <t>38515</t>
         </is>
       </c>
       <c r="C50" s="8" t="inlineStr">
         <is>
-          <t>Periferico Satélite DT</t>
+          <t>Patio Ecatepec</t>
         </is>
       </c>
       <c r="D50" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E50" s="7" t="n">
@@ -2535,17 +2535,17 @@
       </c>
       <c r="B51" s="14" t="inlineStr">
         <is>
-          <t>38924</t>
+          <t>38677</t>
         </is>
       </c>
       <c r="C51" s="12" t="inlineStr">
         <is>
-          <t>Plaza Aeropuerto</t>
+          <t>Patio la Raza</t>
         </is>
       </c>
       <c r="D51" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E51" s="11" t="n">
@@ -2570,17 +2570,17 @@
       </c>
       <c r="B52" s="16" t="inlineStr">
         <is>
-          <t>38719</t>
+          <t>38176</t>
         </is>
       </c>
       <c r="C52" s="8" t="inlineStr">
         <is>
-          <t>Plaza Fortuna</t>
+          <t>Periferico Satélite DT</t>
         </is>
       </c>
       <c r="D52" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E52" s="7" t="n">
@@ -2605,17 +2605,17 @@
       </c>
       <c r="B53" s="14" t="inlineStr">
         <is>
-          <t>38427</t>
+          <t>38924</t>
         </is>
       </c>
       <c r="C53" s="12" t="inlineStr">
         <is>
-          <t>Plaza Satelite</t>
+          <t>Plaza Aeropuerto</t>
         </is>
       </c>
       <c r="D53" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E53" s="11" t="n">
@@ -2640,17 +2640,17 @@
       </c>
       <c r="B54" s="16" t="inlineStr">
         <is>
-          <t>38859</t>
+          <t>38719</t>
         </is>
       </c>
       <c r="C54" s="8" t="inlineStr">
         <is>
-          <t>Plaza Satelite II N1</t>
+          <t>Plaza Fortuna</t>
         </is>
       </c>
       <c r="D54" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E54" s="7" t="n">
@@ -2675,17 +2675,17 @@
       </c>
       <c r="B55" s="14" t="inlineStr">
         <is>
-          <t>38811</t>
+          <t>38427</t>
         </is>
       </c>
       <c r="C55" s="12" t="inlineStr">
         <is>
-          <t>Plaza Tepeyac</t>
+          <t>Plaza Satelite</t>
         </is>
       </c>
       <c r="D55" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E55" s="11" t="n">
@@ -2710,17 +2710,17 @@
       </c>
       <c r="B56" s="16" t="inlineStr">
         <is>
-          <t>43132</t>
+          <t>38859</t>
         </is>
       </c>
       <c r="C56" s="8" t="inlineStr">
         <is>
-          <t>Plaza Vista Norte</t>
+          <t>Plaza Satelite II N1</t>
         </is>
       </c>
       <c r="D56" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E56" s="7" t="n">
@@ -2745,17 +2745,17 @@
       </c>
       <c r="B57" s="14" t="inlineStr">
         <is>
-          <t>38456</t>
+          <t>38811</t>
         </is>
       </c>
       <c r="C57" s="12" t="inlineStr">
         <is>
-          <t>Plaza las Flores</t>
+          <t>Plaza Tepeyac</t>
         </is>
       </c>
       <c r="D57" s="12" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E57" s="11" t="n">
@@ -2780,17 +2780,17 @@
       </c>
       <c r="B58" s="16" t="inlineStr">
         <is>
-          <t>38136</t>
+          <t>43132</t>
         </is>
       </c>
       <c r="C58" s="8" t="inlineStr">
         <is>
-          <t>Punta Norte</t>
+          <t>Plaza Vista Norte</t>
         </is>
       </c>
       <c r="D58" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E58" s="7" t="n">
@@ -2815,17 +2815,17 @@
       </c>
       <c r="B59" s="14" t="inlineStr">
         <is>
-          <t>43152</t>
+          <t>38456</t>
         </is>
       </c>
       <c r="C59" s="12" t="inlineStr">
         <is>
-          <t>Samara Satélite</t>
+          <t>Plaza las Flores</t>
         </is>
       </c>
       <c r="D59" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E59" s="11" t="n">
@@ -2850,17 +2850,17 @@
       </c>
       <c r="B60" s="16" t="inlineStr">
         <is>
-          <t>38339</t>
+          <t>38136</t>
         </is>
       </c>
       <c r="C60" s="8" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Punta Norte</t>
         </is>
       </c>
       <c r="D60" s="8" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E60" s="7" t="n">
@@ -2885,17 +2885,17 @@
       </c>
       <c r="B61" s="14" t="inlineStr">
         <is>
-          <t>38266</t>
+          <t>43152</t>
         </is>
       </c>
       <c r="C61" s="12" t="inlineStr">
         <is>
-          <t>San Mateo</t>
+          <t>Samara Satélite</t>
         </is>
       </c>
       <c r="D61" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E61" s="11" t="n">
@@ -2920,17 +2920,17 @@
       </c>
       <c r="B62" s="16" t="inlineStr">
         <is>
-          <t>38460</t>
+          <t>38339</t>
         </is>
       </c>
       <c r="C62" s="8" t="inlineStr">
         <is>
-          <t>Santa Monica</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="D62" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E62" s="7" t="n">
@@ -2955,17 +2955,17 @@
       </c>
       <c r="B63" s="14" t="inlineStr">
         <is>
-          <t>38117</t>
+          <t>38266</t>
         </is>
       </c>
       <c r="C63" s="12" t="inlineStr">
         <is>
-          <t>Satelite</t>
+          <t>San Mateo</t>
         </is>
       </c>
       <c r="D63" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E63" s="11" t="n">
@@ -2990,17 +2990,17 @@
       </c>
       <c r="B64" s="16" t="inlineStr">
         <is>
-          <t>38475</t>
+          <t>38460</t>
         </is>
       </c>
       <c r="C64" s="8" t="inlineStr">
         <is>
-          <t>Satelite Centro Civico</t>
+          <t>Santa Monica</t>
         </is>
       </c>
       <c r="D64" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E64" s="7" t="n">
@@ -3025,17 +3025,17 @@
       </c>
       <c r="B65" s="14" t="inlineStr">
         <is>
-          <t>38442</t>
+          <t>38117</t>
         </is>
       </c>
       <c r="C65" s="12" t="inlineStr">
         <is>
-          <t>Sor Juana</t>
+          <t>Satelite</t>
         </is>
       </c>
       <c r="D65" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E65" s="11" t="n">
@@ -3060,17 +3060,17 @@
       </c>
       <c r="B66" s="16" t="inlineStr">
         <is>
-          <t>38925</t>
+          <t>38475</t>
         </is>
       </c>
       <c r="C66" s="8" t="inlineStr">
         <is>
-          <t>Star Medica Lomas Verdes</t>
+          <t>Satelite Centro Civico</t>
         </is>
       </c>
       <c r="D66" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E66" s="7" t="n">
@@ -3095,17 +3095,17 @@
       </c>
       <c r="B67" s="14" t="inlineStr">
         <is>
-          <t>38992</t>
+          <t>38442</t>
         </is>
       </c>
       <c r="C67" s="12" t="inlineStr">
         <is>
-          <t>Tapo Puerta Oriente</t>
+          <t>Sor Juana</t>
         </is>
       </c>
       <c r="D67" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E67" s="11" t="n">
@@ -3130,17 +3130,17 @@
       </c>
       <c r="B68" s="16" t="inlineStr">
         <is>
-          <t>38606</t>
+          <t>38992</t>
         </is>
       </c>
       <c r="C68" s="8" t="inlineStr">
         <is>
-          <t>TlalnepantlaCarso</t>
+          <t>Tapo Puerta Oriente</t>
         </is>
       </c>
       <c r="D68" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E68" s="7" t="n">
@@ -3165,17 +3165,17 @@
       </c>
       <c r="B69" s="14" t="inlineStr">
         <is>
-          <t>38411</t>
+          <t>38606</t>
         </is>
       </c>
       <c r="C69" s="12" t="inlineStr">
         <is>
-          <t>Torres Lindavista</t>
+          <t>TlalnepantlaCarso</t>
         </is>
       </c>
       <c r="D69" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E69" s="11" t="n">
@@ -3200,17 +3200,17 @@
       </c>
       <c r="B70" s="16" t="inlineStr">
         <is>
-          <t>43130</t>
+          <t>38411</t>
         </is>
       </c>
       <c r="C70" s="8" t="inlineStr">
         <is>
-          <t>Town Center Nicolás Romero</t>
+          <t>Torres Lindavista</t>
         </is>
       </c>
       <c r="D70" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E70" s="7" t="n">
@@ -3235,17 +3235,17 @@
       </c>
       <c r="B71" s="14" t="inlineStr">
         <is>
-          <t>38374</t>
+          <t>43130</t>
         </is>
       </c>
       <c r="C71" s="12" t="inlineStr">
         <is>
-          <t>Valle Dorado</t>
+          <t>Town Center Nicolás Romero</t>
         </is>
       </c>
       <c r="D71" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E71" s="11" t="n">
@@ -3270,17 +3270,17 @@
       </c>
       <c r="B72" s="16" t="inlineStr">
         <is>
-          <t>38651</t>
+          <t>38374</t>
         </is>
       </c>
       <c r="C72" s="8" t="inlineStr">
         <is>
-          <t>Via Vallejo</t>
+          <t>Valle Dorado</t>
         </is>
       </c>
       <c r="D72" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E72" s="7" t="n">
@@ -3305,17 +3305,17 @@
       </c>
       <c r="B73" s="14" t="inlineStr">
         <is>
-          <t>38694</t>
+          <t>38651</t>
         </is>
       </c>
       <c r="C73" s="12" t="inlineStr">
         <is>
-          <t>Villas de la Hacienda</t>
+          <t>Via Vallejo</t>
         </is>
       </c>
       <c r="D73" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E73" s="11" t="n">
@@ -3340,17 +3340,17 @@
       </c>
       <c r="B74" s="16" t="inlineStr">
         <is>
-          <t>38656</t>
+          <t>38694</t>
         </is>
       </c>
       <c r="C74" s="8" t="inlineStr">
         <is>
-          <t>Viveros de la Loma</t>
+          <t>Villas de la Hacienda</t>
         </is>
       </c>
       <c r="D74" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E74" s="7" t="n">
@@ -3375,17 +3375,17 @@
       </c>
       <c r="B75" s="14" t="inlineStr">
         <is>
-          <t>38115</t>
+          <t>38656</t>
         </is>
       </c>
       <c r="C75" s="12" t="inlineStr">
         <is>
-          <t>Zona Azul</t>
+          <t>Viveros de la Loma</t>
         </is>
       </c>
       <c r="D75" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E75" s="11" t="n">
@@ -3410,12 +3410,12 @@
       </c>
       <c r="B76" s="16" t="inlineStr">
         <is>
-          <t>38142</t>
+          <t>38115</t>
         </is>
       </c>
       <c r="C76" s="8" t="inlineStr">
         <is>
-          <t>Zona Esmeralda</t>
+          <t>Zona Azul</t>
         </is>
       </c>
       <c r="D76" s="8" t="inlineStr">
@@ -3488,7 +3488,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Centro Norte · Corte 29/08/2026 14:28</t>
+          <t>Centro Norte · Corte 29/08/2026 15:22</t>
         </is>
       </c>
     </row>
@@ -3759,10 +3759,10 @@
         </is>
       </c>
       <c r="C14" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E14" s="9">
         <f>IFERROR(C14/(C14+D14),0)</f>

--- a/exports/Resumen_Evidencias_OPS.xlsx
+++ b/exports/Resumen_Evidencias_OPS.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tiendas" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Actividades" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Resumen" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Tiendas" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Actividades" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Resumen'!$A$9:$G$15</definedName>
@@ -27,7 +27,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -76,14 +76,8 @@
       <color rgb="00922F24"/>
       <sz val="9"/>
     </font>
-    <font>
-      <name val="Aptos"/>
-      <b val="1"/>
-      <color rgb="0080520C"/>
-      <sz val="9"/>
-    </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -115,11 +109,6 @@
         <fgColor rgb="00F9E6E3"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF0D5"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -138,7 +127,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -181,9 +170,6 @@
     </xf>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -600,10 +586,10 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="E6" s="5">
         <f>IFERROR(A6/(A6+C6),0)</f>
@@ -661,10 +647,10 @@
         <v>10</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F10" s="9">
         <f>IFERROR(D10/(D10+E10),0)</f>
@@ -939,18 +925,18 @@
         </is>
       </c>
       <c r="E5" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G5" s="13">
         <f>IFERROR(E5/(E5+F5),0)</f>
         <v/>
       </c>
-      <c r="H5" s="15" t="inlineStr">
-        <is>
-          <t>Seguimiento</t>
+      <c r="H5" s="10" t="inlineStr">
+        <is>
+          <t>Atención</t>
         </is>
       </c>
     </row>
@@ -958,7 +944,7 @@
       <c r="A6" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="16" t="inlineStr">
+      <c r="B6" s="15" t="inlineStr">
         <is>
           <t>38894</t>
         </is>
@@ -1028,7 +1014,7 @@
       <c r="A8" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="16" t="inlineStr">
+      <c r="B8" s="15" t="inlineStr">
         <is>
           <t>38333</t>
         </is>
@@ -1098,7 +1084,7 @@
       <c r="A10" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="16" t="inlineStr">
+      <c r="B10" s="15" t="inlineStr">
         <is>
           <t>38142</t>
         </is>
@@ -1168,7 +1154,7 @@
       <c r="A12" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="16" t="inlineStr">
+      <c r="B12" s="15" t="inlineStr">
         <is>
           <t>43043</t>
         </is>
@@ -1238,7 +1224,7 @@
       <c r="A14" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="16" t="inlineStr">
+      <c r="B14" s="15" t="inlineStr">
         <is>
           <t>38930</t>
         </is>
@@ -1308,7 +1294,7 @@
       <c r="A16" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="16" t="inlineStr">
+      <c r="B16" s="15" t="inlineStr">
         <is>
           <t>38527</t>
         </is>
@@ -1378,7 +1364,7 @@
       <c r="A18" s="7" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="16" t="inlineStr">
+      <c r="B18" s="15" t="inlineStr">
         <is>
           <t>38394</t>
         </is>
@@ -1448,7 +1434,7 @@
       <c r="A20" s="7" t="n">
         <v>16</v>
       </c>
-      <c r="B20" s="16" t="inlineStr">
+      <c r="B20" s="15" t="inlineStr">
         <is>
           <t>38535</t>
         </is>
@@ -1518,7 +1504,7 @@
       <c r="A22" s="7" t="n">
         <v>18</v>
       </c>
-      <c r="B22" s="16" t="inlineStr">
+      <c r="B22" s="15" t="inlineStr">
         <is>
           <t>38604</t>
         </is>
@@ -1588,7 +1574,7 @@
       <c r="A24" s="7" t="n">
         <v>20</v>
       </c>
-      <c r="B24" s="16" t="inlineStr">
+      <c r="B24" s="15" t="inlineStr">
         <is>
           <t>38197</t>
         </is>
@@ -1658,7 +1644,7 @@
       <c r="A26" s="7" t="n">
         <v>22</v>
       </c>
-      <c r="B26" s="16" t="inlineStr">
+      <c r="B26" s="15" t="inlineStr">
         <is>
           <t>38458</t>
         </is>
@@ -1728,7 +1714,7 @@
       <c r="A28" s="7" t="n">
         <v>24</v>
       </c>
-      <c r="B28" s="16" t="inlineStr">
+      <c r="B28" s="15" t="inlineStr">
         <is>
           <t>38995</t>
         </is>
@@ -1798,7 +1784,7 @@
       <c r="A30" s="7" t="n">
         <v>26</v>
       </c>
-      <c r="B30" s="16" t="inlineStr">
+      <c r="B30" s="15" t="inlineStr">
         <is>
           <t>38363</t>
         </is>
@@ -1868,7 +1854,7 @@
       <c r="A32" s="7" t="n">
         <v>28</v>
       </c>
-      <c r="B32" s="16" t="inlineStr">
+      <c r="B32" s="15" t="inlineStr">
         <is>
           <t>38230</t>
         </is>
@@ -1938,7 +1924,7 @@
       <c r="A34" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="B34" s="16" t="inlineStr">
+      <c r="B34" s="15" t="inlineStr">
         <is>
           <t>38205</t>
         </is>
@@ -2008,7 +1994,7 @@
       <c r="A36" s="7" t="n">
         <v>32</v>
       </c>
-      <c r="B36" s="16" t="inlineStr">
+      <c r="B36" s="15" t="inlineStr">
         <is>
           <t>38119</t>
         </is>
@@ -2078,7 +2064,7 @@
       <c r="A38" s="7" t="n">
         <v>34</v>
       </c>
-      <c r="B38" s="16" t="inlineStr">
+      <c r="B38" s="15" t="inlineStr">
         <is>
           <t>38368</t>
         </is>
@@ -2148,7 +2134,7 @@
       <c r="A40" s="7" t="n">
         <v>36</v>
       </c>
-      <c r="B40" s="16" t="inlineStr">
+      <c r="B40" s="15" t="inlineStr">
         <is>
           <t>43111</t>
         </is>
@@ -2218,7 +2204,7 @@
       <c r="A42" s="7" t="n">
         <v>38</v>
       </c>
-      <c r="B42" s="16" t="inlineStr">
+      <c r="B42" s="15" t="inlineStr">
         <is>
           <t>38845</t>
         </is>
@@ -2288,7 +2274,7 @@
       <c r="A44" s="7" t="n">
         <v>40</v>
       </c>
-      <c r="B44" s="16" t="inlineStr">
+      <c r="B44" s="15" t="inlineStr">
         <is>
           <t>38937</t>
         </is>
@@ -2358,7 +2344,7 @@
       <c r="A46" s="7" t="n">
         <v>42</v>
       </c>
-      <c r="B46" s="16" t="inlineStr">
+      <c r="B46" s="15" t="inlineStr">
         <is>
           <t>38561</t>
         </is>
@@ -2428,7 +2414,7 @@
       <c r="A48" s="7" t="n">
         <v>44</v>
       </c>
-      <c r="B48" s="16" t="inlineStr">
+      <c r="B48" s="15" t="inlineStr">
         <is>
           <t>38792</t>
         </is>
@@ -2498,7 +2484,7 @@
       <c r="A50" s="7" t="n">
         <v>46</v>
       </c>
-      <c r="B50" s="16" t="inlineStr">
+      <c r="B50" s="15" t="inlineStr">
         <is>
           <t>38515</t>
         </is>
@@ -2568,7 +2554,7 @@
       <c r="A52" s="7" t="n">
         <v>48</v>
       </c>
-      <c r="B52" s="16" t="inlineStr">
+      <c r="B52" s="15" t="inlineStr">
         <is>
           <t>38176</t>
         </is>
@@ -2638,7 +2624,7 @@
       <c r="A54" s="7" t="n">
         <v>50</v>
       </c>
-      <c r="B54" s="16" t="inlineStr">
+      <c r="B54" s="15" t="inlineStr">
         <is>
           <t>38719</t>
         </is>
@@ -2708,7 +2694,7 @@
       <c r="A56" s="7" t="n">
         <v>52</v>
       </c>
-      <c r="B56" s="16" t="inlineStr">
+      <c r="B56" s="15" t="inlineStr">
         <is>
           <t>38859</t>
         </is>
@@ -2778,7 +2764,7 @@
       <c r="A58" s="7" t="n">
         <v>54</v>
       </c>
-      <c r="B58" s="16" t="inlineStr">
+      <c r="B58" s="15" t="inlineStr">
         <is>
           <t>43132</t>
         </is>
@@ -2848,7 +2834,7 @@
       <c r="A60" s="7" t="n">
         <v>56</v>
       </c>
-      <c r="B60" s="16" t="inlineStr">
+      <c r="B60" s="15" t="inlineStr">
         <is>
           <t>38136</t>
         </is>
@@ -2918,7 +2904,7 @@
       <c r="A62" s="7" t="n">
         <v>58</v>
       </c>
-      <c r="B62" s="16" t="inlineStr">
+      <c r="B62" s="15" t="inlineStr">
         <is>
           <t>38339</t>
         </is>
@@ -2988,7 +2974,7 @@
       <c r="A64" s="7" t="n">
         <v>60</v>
       </c>
-      <c r="B64" s="16" t="inlineStr">
+      <c r="B64" s="15" t="inlineStr">
         <is>
           <t>38460</t>
         </is>
@@ -3058,7 +3044,7 @@
       <c r="A66" s="7" t="n">
         <v>62</v>
       </c>
-      <c r="B66" s="16" t="inlineStr">
+      <c r="B66" s="15" t="inlineStr">
         <is>
           <t>38475</t>
         </is>
@@ -3128,7 +3114,7 @@
       <c r="A68" s="7" t="n">
         <v>64</v>
       </c>
-      <c r="B68" s="16" t="inlineStr">
+      <c r="B68" s="15" t="inlineStr">
         <is>
           <t>38992</t>
         </is>
@@ -3198,7 +3184,7 @@
       <c r="A70" s="7" t="n">
         <v>66</v>
       </c>
-      <c r="B70" s="16" t="inlineStr">
+      <c r="B70" s="15" t="inlineStr">
         <is>
           <t>38411</t>
         </is>
@@ -3268,7 +3254,7 @@
       <c r="A72" s="7" t="n">
         <v>68</v>
       </c>
-      <c r="B72" s="16" t="inlineStr">
+      <c r="B72" s="15" t="inlineStr">
         <is>
           <t>38374</t>
         </is>
@@ -3338,7 +3324,7 @@
       <c r="A74" s="7" t="n">
         <v>70</v>
       </c>
-      <c r="B74" s="16" t="inlineStr">
+      <c r="B74" s="15" t="inlineStr">
         <is>
           <t>38694</t>
         </is>
@@ -3408,7 +3394,7 @@
       <c r="A76" s="7" t="n">
         <v>72</v>
       </c>
-      <c r="B76" s="16" t="inlineStr">
+      <c r="B76" s="15" t="inlineStr">
         <is>
           <t>38115</t>
         </is>
@@ -3584,10 +3570,10 @@
         </is>
       </c>
       <c r="C7" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E7" s="13">
         <f>IFERROR(C7/(C7+D7),0)</f>

--- a/exports/Resumen_Evidencias_OPS.xlsx
+++ b/exports/Resumen_Evidencias_OPS.xlsx
@@ -563,7 +563,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Centro Norte · Corte 29/08/2026 15:22</t>
+          <t>Centro Norte · Corte 29/08/2026 15:56</t>
         </is>
       </c>
     </row>
@@ -586,10 +586,10 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="E6" s="5">
         <f>IFERROR(A6/(A6+C6),0)</f>
@@ -647,10 +647,10 @@
         <v>10</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F10" s="9">
         <f>IFERROR(D10/(D10+E10),0)</f>
@@ -675,10 +675,10 @@
         <v>13</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E11" s="12" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F11" s="13">
         <f>IFERROR(D11/(D11+E11),0)</f>
@@ -859,7 +859,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Centro Norte · Corte 29/08/2026 15:22</t>
+          <t>Centro Norte · Corte 29/08/2026 15:56</t>
         </is>
       </c>
     </row>
@@ -1016,17 +1016,17 @@
       </c>
       <c r="B8" s="15" t="inlineStr">
         <is>
-          <t>38333</t>
+          <t>38394</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>Izcalli Mega</t>
+          <t>Centro Comercial Lomas Verdes</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E8" s="7" t="n">
@@ -1051,17 +1051,17 @@
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>38925</t>
+          <t>38333</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>Star Medica Lomas Verdes</t>
+          <t>Izcalli Mega</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E9" s="11" t="n">
@@ -1086,17 +1086,17 @@
       </c>
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>38142</t>
+          <t>38456</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>Zona Esmeralda</t>
+          <t>Plaza las Flores</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E10" s="7" t="n">
@@ -1121,24 +1121,24 @@
       </c>
       <c r="B11" s="14" t="inlineStr">
         <is>
-          <t>38186</t>
+          <t>38925</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>Arboledas</t>
+          <t>Star Medica Lomas Verdes</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E11" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G11" s="13">
         <f>IFERROR(E11/(E11+F11),0)</f>
@@ -1156,12 +1156,12 @@
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>43043</t>
+          <t>38142</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Atizapan</t>
+          <t>Zona Esmeralda</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
@@ -1170,10 +1170,10 @@
         </is>
       </c>
       <c r="E12" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F12" s="7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G12" s="9">
         <f>IFERROR(E12/(E12+F12),0)</f>
@@ -1191,17 +1191,17 @@
       </c>
       <c r="B13" s="14" t="inlineStr">
         <is>
-          <t>38149</t>
+          <t>38186</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>Bellavista</t>
+          <t>Arboledas</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E13" s="11" t="n">
@@ -1226,17 +1226,17 @@
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>38930</t>
+          <t>43043</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Blvd. Aeropuerto dt</t>
+          <t>Atizapan</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E14" s="7" t="n">
@@ -1261,17 +1261,17 @@
       </c>
       <c r="B15" s="14" t="inlineStr">
         <is>
-          <t>38529</t>
+          <t>38149</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>Bosques de Aragon</t>
+          <t>Bellavista</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E15" s="11" t="n">
@@ -1296,17 +1296,17 @@
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>38527</t>
+          <t>38930</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>Camarones</t>
+          <t>Blvd. Aeropuerto dt</t>
         </is>
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E16" s="7" t="n">
@@ -1331,17 +1331,17 @@
       </c>
       <c r="B17" s="14" t="inlineStr">
         <is>
-          <t>38837</t>
+          <t>38529</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>Centenario Azcapotzalco</t>
+          <t>Bosques de Aragon</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E17" s="11" t="n">
@@ -1366,17 +1366,17 @@
       </c>
       <c r="B18" s="15" t="inlineStr">
         <is>
-          <t>38394</t>
+          <t>38527</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>Centro Comercial Lomas Verdes</t>
+          <t>Camarones</t>
         </is>
       </c>
       <c r="D18" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E18" s="7" t="n">
@@ -1401,17 +1401,17 @@
       </c>
       <c r="B19" s="14" t="inlineStr">
         <is>
-          <t>38695</t>
+          <t>38837</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>Cetram 4 Caminos</t>
+          <t>Centenario Azcapotzalco</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E19" s="11" t="n">
@@ -1436,17 +1436,17 @@
       </c>
       <c r="B20" s="15" t="inlineStr">
         <is>
-          <t>38535</t>
+          <t>38695</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>City Center Esmeralda</t>
+          <t>Cetram 4 Caminos</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E20" s="7" t="n">
@@ -1471,17 +1471,17 @@
       </c>
       <c r="B21" s="14" t="inlineStr">
         <is>
-          <t>38401</t>
+          <t>38535</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>Coacalco</t>
+          <t>City Center Esmeralda</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E21" s="11" t="n">
@@ -1506,12 +1506,12 @@
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>38604</t>
+          <t>38401</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>Cosmopol</t>
+          <t>Coacalco</t>
         </is>
       </c>
       <c r="D22" s="8" t="inlineStr">
@@ -1541,12 +1541,12 @@
       </c>
       <c r="B23" s="14" t="inlineStr">
         <is>
-          <t>43193</t>
+          <t>38604</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>Cosmopol N1</t>
+          <t>Cosmopol</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr">
@@ -1576,17 +1576,17 @@
       </c>
       <c r="B24" s="15" t="inlineStr">
         <is>
-          <t>38197</t>
+          <t>43193</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>Echegaray</t>
+          <t>Cosmopol N1</t>
         </is>
       </c>
       <c r="D24" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E24" s="7" t="n">
@@ -1611,17 +1611,17 @@
       </c>
       <c r="B25" s="14" t="inlineStr">
         <is>
-          <t>38431</t>
+          <t>38197</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>Eduardo Molina</t>
+          <t>Echegaray</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E25" s="11" t="n">
@@ -1646,17 +1646,17 @@
       </c>
       <c r="B26" s="15" t="inlineStr">
         <is>
-          <t>38458</t>
+          <t>38431</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>El Rosario</t>
+          <t>Eduardo Molina</t>
         </is>
       </c>
       <c r="D26" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E26" s="7" t="n">
@@ -1681,17 +1681,17 @@
       </c>
       <c r="B27" s="14" t="inlineStr">
         <is>
-          <t>38903</t>
+          <t>38458</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>Encuentro Oceania</t>
+          <t>El Rosario</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E27" s="11" t="n">
@@ -1716,12 +1716,12 @@
       </c>
       <c r="B28" s="15" t="inlineStr">
         <is>
-          <t>38995</t>
+          <t>38903</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>Encuentro Oceania II</t>
+          <t>Encuentro Oceania</t>
         </is>
       </c>
       <c r="D28" s="8" t="inlineStr">
@@ -1751,17 +1751,17 @@
       </c>
       <c r="B29" s="14" t="inlineStr">
         <is>
-          <t>38507</t>
+          <t>38995</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>Espacio Vista del Valle</t>
+          <t>Encuentro Oceania II</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E29" s="11" t="n">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>38363</t>
+          <t>38507</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>Galerias Atizapan</t>
+          <t>Espacio Vista del Valle</t>
         </is>
       </c>
       <c r="D30" s="8" t="inlineStr">
@@ -1821,17 +1821,17 @@
       </c>
       <c r="B31" s="14" t="inlineStr">
         <is>
-          <t>38770</t>
+          <t>38363</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>Gustavo Baz 29</t>
+          <t>Galerias Atizapan</t>
         </is>
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E31" s="11" t="n">
@@ -1856,17 +1856,17 @@
       </c>
       <c r="B32" s="15" t="inlineStr">
         <is>
-          <t>38230</t>
+          <t>38770</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>ITEMS Edo de Mexico</t>
+          <t>Gustavo Baz 29</t>
         </is>
       </c>
       <c r="D32" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E32" s="7" t="n">
@@ -1891,12 +1891,12 @@
       </c>
       <c r="B33" s="14" t="inlineStr">
         <is>
-          <t>38661</t>
+          <t>38230</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>Jinetes</t>
+          <t>ITEMS Edo de Mexico</t>
         </is>
       </c>
       <c r="D33" s="12" t="inlineStr">
@@ -1926,17 +1926,17 @@
       </c>
       <c r="B34" s="15" t="inlineStr">
         <is>
-          <t>38205</t>
+          <t>38661</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>Lindavista</t>
+          <t>Jinetes</t>
         </is>
       </c>
       <c r="D34" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E34" s="7" t="n">
@@ -1961,12 +1961,12 @@
       </c>
       <c r="B35" s="14" t="inlineStr">
         <is>
-          <t>38207</t>
+          <t>38205</t>
         </is>
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>Lindavista II</t>
+          <t>Lindavista</t>
         </is>
       </c>
       <c r="D35" s="12" t="inlineStr">
@@ -1996,17 +1996,17 @@
       </c>
       <c r="B36" s="15" t="inlineStr">
         <is>
-          <t>38119</t>
+          <t>38207</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>Lomas Verdes</t>
+          <t>Lindavista II</t>
         </is>
       </c>
       <c r="D36" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E36" s="7" t="n">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="B37" s="14" t="inlineStr">
         <is>
-          <t>38270</t>
+          <t>38119</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>Lomas Verdes II</t>
+          <t>Lomas Verdes</t>
         </is>
       </c>
       <c r="D37" s="12" t="inlineStr">
@@ -2066,17 +2066,17 @@
       </c>
       <c r="B38" s="15" t="inlineStr">
         <is>
-          <t>38368</t>
+          <t>38270</t>
         </is>
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>Luna Park</t>
+          <t>Lomas Verdes II</t>
         </is>
       </c>
       <c r="D38" s="8" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E38" s="7" t="n">
@@ -2101,17 +2101,17 @@
       </c>
       <c r="B39" s="14" t="inlineStr">
         <is>
-          <t>38371</t>
+          <t>38368</t>
         </is>
       </c>
       <c r="C39" s="12" t="inlineStr">
         <is>
-          <t>Montevideo DT</t>
+          <t>Luna Park</t>
         </is>
       </c>
       <c r="D39" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E39" s="11" t="n">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="B40" s="15" t="inlineStr">
         <is>
-          <t>43111</t>
+          <t>38371</t>
         </is>
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>Montevideo Insurgentes</t>
+          <t>Montevideo DT</t>
         </is>
       </c>
       <c r="D40" s="8" t="inlineStr">
@@ -2171,17 +2171,17 @@
       </c>
       <c r="B41" s="14" t="inlineStr">
         <is>
-          <t>38674</t>
+          <t>43111</t>
         </is>
       </c>
       <c r="C41" s="12" t="inlineStr">
         <is>
-          <t>Mundo E</t>
+          <t>Montevideo Insurgentes</t>
         </is>
       </c>
       <c r="D41" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E41" s="11" t="n">
@@ -2206,12 +2206,12 @@
       </c>
       <c r="B42" s="15" t="inlineStr">
         <is>
-          <t>38845</t>
+          <t>38674</t>
         </is>
       </c>
       <c r="C42" s="8" t="inlineStr">
         <is>
-          <t>Mundo E II</t>
+          <t>Mundo E</t>
         </is>
       </c>
       <c r="D42" s="8" t="inlineStr">
@@ -2241,17 +2241,17 @@
       </c>
       <c r="B43" s="14" t="inlineStr">
         <is>
-          <t>43195</t>
+          <t>38845</t>
         </is>
       </c>
       <c r="C43" s="12" t="inlineStr">
         <is>
-          <t>Parque Jadin kiosko</t>
+          <t>Mundo E II</t>
         </is>
       </c>
       <c r="D43" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E43" s="11" t="n">
@@ -2276,17 +2276,17 @@
       </c>
       <c r="B44" s="15" t="inlineStr">
         <is>
-          <t>38937</t>
+          <t>43195</t>
         </is>
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t>Parque Tepeyac Piso 1</t>
+          <t>Parque Jadin kiosko</t>
         </is>
       </c>
       <c r="D44" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E44" s="7" t="n">
@@ -2311,12 +2311,12 @@
       </c>
       <c r="B45" s="14" t="inlineStr">
         <is>
-          <t>38965</t>
+          <t>38937</t>
         </is>
       </c>
       <c r="C45" s="12" t="inlineStr">
         <is>
-          <t>Parque Tepeyac Piso 2</t>
+          <t>Parque Tepeyac Piso 1</t>
         </is>
       </c>
       <c r="D45" s="12" t="inlineStr">
@@ -2346,17 +2346,17 @@
       </c>
       <c r="B46" s="15" t="inlineStr">
         <is>
-          <t>38561</t>
+          <t>38965</t>
         </is>
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t>Parque Toreo</t>
+          <t>Parque Tepeyac Piso 2</t>
         </is>
       </c>
       <c r="D46" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E46" s="7" t="n">
@@ -2381,12 +2381,12 @@
       </c>
       <c r="B47" s="14" t="inlineStr">
         <is>
-          <t>38590</t>
+          <t>38561</t>
         </is>
       </c>
       <c r="C47" s="12" t="inlineStr">
         <is>
-          <t>Parque Toreo II</t>
+          <t>Parque Toreo</t>
         </is>
       </c>
       <c r="D47" s="12" t="inlineStr">
@@ -2416,17 +2416,17 @@
       </c>
       <c r="B48" s="15" t="inlineStr">
         <is>
-          <t>38792</t>
+          <t>38590</t>
         </is>
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
-          <t>Pasaje Tlanepantla</t>
+          <t>Parque Toreo II</t>
         </is>
       </c>
       <c r="D48" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E48" s="7" t="n">
@@ -2451,17 +2451,17 @@
       </c>
       <c r="B49" s="14" t="inlineStr">
         <is>
-          <t>38546</t>
+          <t>38792</t>
         </is>
       </c>
       <c r="C49" s="12" t="inlineStr">
         <is>
-          <t>Patio Claveria</t>
+          <t>Pasaje Tlanepantla</t>
         </is>
       </c>
       <c r="D49" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E49" s="11" t="n">
@@ -2486,17 +2486,17 @@
       </c>
       <c r="B50" s="15" t="inlineStr">
         <is>
-          <t>38515</t>
+          <t>38546</t>
         </is>
       </c>
       <c r="C50" s="8" t="inlineStr">
         <is>
-          <t>Patio Ecatepec</t>
+          <t>Patio Claveria</t>
         </is>
       </c>
       <c r="D50" s="8" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E50" s="7" t="n">
@@ -2521,17 +2521,17 @@
       </c>
       <c r="B51" s="14" t="inlineStr">
         <is>
-          <t>38677</t>
+          <t>38515</t>
         </is>
       </c>
       <c r="C51" s="12" t="inlineStr">
         <is>
-          <t>Patio la Raza</t>
+          <t>Patio Ecatepec</t>
         </is>
       </c>
       <c r="D51" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E51" s="11" t="n">
@@ -2556,17 +2556,17 @@
       </c>
       <c r="B52" s="15" t="inlineStr">
         <is>
-          <t>38176</t>
+          <t>38677</t>
         </is>
       </c>
       <c r="C52" s="8" t="inlineStr">
         <is>
-          <t>Periferico Satélite DT</t>
+          <t>Patio la Raza</t>
         </is>
       </c>
       <c r="D52" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E52" s="7" t="n">
@@ -2591,17 +2591,17 @@
       </c>
       <c r="B53" s="14" t="inlineStr">
         <is>
-          <t>38924</t>
+          <t>38176</t>
         </is>
       </c>
       <c r="C53" s="12" t="inlineStr">
         <is>
-          <t>Plaza Aeropuerto</t>
+          <t>Periferico Satélite DT</t>
         </is>
       </c>
       <c r="D53" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E53" s="11" t="n">
@@ -2626,12 +2626,12 @@
       </c>
       <c r="B54" s="15" t="inlineStr">
         <is>
-          <t>38719</t>
+          <t>38924</t>
         </is>
       </c>
       <c r="C54" s="8" t="inlineStr">
         <is>
-          <t>Plaza Fortuna</t>
+          <t>Plaza Aeropuerto</t>
         </is>
       </c>
       <c r="D54" s="8" t="inlineStr">
@@ -2661,17 +2661,17 @@
       </c>
       <c r="B55" s="14" t="inlineStr">
         <is>
-          <t>38427</t>
+          <t>38719</t>
         </is>
       </c>
       <c r="C55" s="12" t="inlineStr">
         <is>
-          <t>Plaza Satelite</t>
+          <t>Plaza Fortuna</t>
         </is>
       </c>
       <c r="D55" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E55" s="11" t="n">
@@ -2696,12 +2696,12 @@
       </c>
       <c r="B56" s="15" t="inlineStr">
         <is>
-          <t>38859</t>
+          <t>38427</t>
         </is>
       </c>
       <c r="C56" s="8" t="inlineStr">
         <is>
-          <t>Plaza Satelite II N1</t>
+          <t>Plaza Satelite</t>
         </is>
       </c>
       <c r="D56" s="8" t="inlineStr">
@@ -2731,17 +2731,17 @@
       </c>
       <c r="B57" s="14" t="inlineStr">
         <is>
-          <t>38811</t>
+          <t>38859</t>
         </is>
       </c>
       <c r="C57" s="12" t="inlineStr">
         <is>
-          <t>Plaza Tepeyac</t>
+          <t>Plaza Satelite II N1</t>
         </is>
       </c>
       <c r="D57" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E57" s="11" t="n">
@@ -2766,17 +2766,17 @@
       </c>
       <c r="B58" s="15" t="inlineStr">
         <is>
-          <t>43132</t>
+          <t>38811</t>
         </is>
       </c>
       <c r="C58" s="8" t="inlineStr">
         <is>
-          <t>Plaza Vista Norte</t>
+          <t>Plaza Tepeyac</t>
         </is>
       </c>
       <c r="D58" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E58" s="7" t="n">
@@ -2801,17 +2801,17 @@
       </c>
       <c r="B59" s="14" t="inlineStr">
         <is>
-          <t>38456</t>
+          <t>43132</t>
         </is>
       </c>
       <c r="C59" s="12" t="inlineStr">
         <is>
-          <t>Plaza las Flores</t>
+          <t>Plaza Vista Norte</t>
         </is>
       </c>
       <c r="D59" s="12" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E59" s="11" t="n">
@@ -3474,7 +3474,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Centro Norte · Corte 29/08/2026 15:22</t>
+          <t>Centro Norte · Corte 29/08/2026 15:56</t>
         </is>
       </c>
     </row>
@@ -3520,10 +3520,10 @@
         </is>
       </c>
       <c r="C5" s="11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E5" s="13">
         <f>IFERROR(C5/(C5+D5),0)</f>
@@ -3745,10 +3745,10 @@
         </is>
       </c>
       <c r="C14" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E14" s="9">
         <f>IFERROR(C14/(C14+D14),0)</f>

--- a/exports/Resumen_Evidencias_OPS.xlsx
+++ b/exports/Resumen_Evidencias_OPS.xlsx
@@ -563,7 +563,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Centro Norte · Corte 29/08/2026 15:56</t>
+          <t>Centro Norte · Corte 29/08/2026 22:34</t>
         </is>
       </c>
     </row>
@@ -586,10 +586,10 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="E6" s="5">
         <f>IFERROR(A6/(A6+C6),0)</f>
@@ -647,10 +647,10 @@
         <v>10</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F10" s="9">
         <f>IFERROR(D10/(D10+E10),0)</f>
@@ -859,7 +859,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Centro Norte · Corte 29/08/2026 15:56</t>
+          <t>Centro Norte · Corte 29/08/2026 22:34</t>
         </is>
       </c>
     </row>
@@ -911,12 +911,12 @@
       </c>
       <c r="B5" s="14" t="inlineStr">
         <is>
-          <t>38862</t>
+          <t>38894</t>
         </is>
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>San Miguel Izcalli</t>
+          <t>Galerias Perinorte</t>
         </is>
       </c>
       <c r="D5" s="12" t="inlineStr">
@@ -946,12 +946,12 @@
       </c>
       <c r="B6" s="15" t="inlineStr">
         <is>
-          <t>38894</t>
+          <t>38862</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>Galerias Perinorte</t>
+          <t>San Miguel Izcalli</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
@@ -960,10 +960,10 @@
         </is>
       </c>
       <c r="E6" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G6" s="9">
         <f>IFERROR(E6/(E6+F6),0)</f>
@@ -1086,12 +1086,12 @@
       </c>
       <c r="B10" s="15" t="inlineStr">
         <is>
-          <t>38456</t>
+          <t>38368</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>Plaza las Flores</t>
+          <t>Luna Park</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
@@ -1121,17 +1121,17 @@
       </c>
       <c r="B11" s="14" t="inlineStr">
         <is>
-          <t>38925</t>
+          <t>38456</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>Star Medica Lomas Verdes</t>
+          <t>Plaza las Flores</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E11" s="11" t="n">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
-          <t>38142</t>
+          <t>38925</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Zona Esmeralda</t>
+          <t>Star Medica Lomas Verdes</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
@@ -1191,24 +1191,24 @@
       </c>
       <c r="B13" s="14" t="inlineStr">
         <is>
-          <t>38186</t>
+          <t>38142</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>Arboledas</t>
+          <t>Zona Esmeralda</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E13" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G13" s="13">
         <f>IFERROR(E13/(E13+F13),0)</f>
@@ -1226,17 +1226,17 @@
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
-          <t>43043</t>
+          <t>38186</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Atizapan</t>
+          <t>Arboledas</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E14" s="7" t="n">
@@ -1261,12 +1261,12 @@
       </c>
       <c r="B15" s="14" t="inlineStr">
         <is>
-          <t>38149</t>
+          <t>43043</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>Bellavista</t>
+          <t>Atizapan</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
@@ -1296,17 +1296,17 @@
       </c>
       <c r="B16" s="15" t="inlineStr">
         <is>
-          <t>38930</t>
+          <t>38149</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>Blvd. Aeropuerto dt</t>
+          <t>Bellavista</t>
         </is>
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E16" s="7" t="n">
@@ -1331,12 +1331,12 @@
       </c>
       <c r="B17" s="14" t="inlineStr">
         <is>
-          <t>38529</t>
+          <t>38930</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>Bosques de Aragon</t>
+          <t>Blvd. Aeropuerto dt</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
@@ -1366,17 +1366,17 @@
       </c>
       <c r="B18" s="15" t="inlineStr">
         <is>
-          <t>38527</t>
+          <t>38529</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>Camarones</t>
+          <t>Bosques de Aragon</t>
         </is>
       </c>
       <c r="D18" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E18" s="7" t="n">
@@ -1401,12 +1401,12 @@
       </c>
       <c r="B19" s="14" t="inlineStr">
         <is>
-          <t>38837</t>
+          <t>38527</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>Centenario Azcapotzalco</t>
+          <t>Camarones</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
@@ -1436,17 +1436,17 @@
       </c>
       <c r="B20" s="15" t="inlineStr">
         <is>
-          <t>38695</t>
+          <t>38837</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>Cetram 4 Caminos</t>
+          <t>Centenario Azcapotzalco</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E20" s="7" t="n">
@@ -1471,17 +1471,17 @@
       </c>
       <c r="B21" s="14" t="inlineStr">
         <is>
-          <t>38535</t>
+          <t>38695</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>City Center Esmeralda</t>
+          <t>Cetram 4 Caminos</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E21" s="11" t="n">
@@ -1506,17 +1506,17 @@
       </c>
       <c r="B22" s="15" t="inlineStr">
         <is>
-          <t>38401</t>
+          <t>38535</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>Coacalco</t>
+          <t>City Center Esmeralda</t>
         </is>
       </c>
       <c r="D22" s="8" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E22" s="7" t="n">
@@ -1541,12 +1541,12 @@
       </c>
       <c r="B23" s="14" t="inlineStr">
         <is>
-          <t>38604</t>
+          <t>38401</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>Cosmopol</t>
+          <t>Coacalco</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="B24" s="15" t="inlineStr">
         <is>
-          <t>43193</t>
+          <t>38604</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>Cosmopol N1</t>
+          <t>Cosmopol</t>
         </is>
       </c>
       <c r="D24" s="8" t="inlineStr">
@@ -1611,17 +1611,17 @@
       </c>
       <c r="B25" s="14" t="inlineStr">
         <is>
-          <t>38197</t>
+          <t>43193</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>Echegaray</t>
+          <t>Cosmopol N1</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E25" s="11" t="n">
@@ -1646,17 +1646,17 @@
       </c>
       <c r="B26" s="15" t="inlineStr">
         <is>
-          <t>38431</t>
+          <t>38197</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>Eduardo Molina</t>
+          <t>Echegaray</t>
         </is>
       </c>
       <c r="D26" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E26" s="7" t="n">
@@ -1681,17 +1681,17 @@
       </c>
       <c r="B27" s="14" t="inlineStr">
         <is>
-          <t>38458</t>
+          <t>38431</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>El Rosario</t>
+          <t>Eduardo Molina</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E27" s="11" t="n">
@@ -1716,17 +1716,17 @@
       </c>
       <c r="B28" s="15" t="inlineStr">
         <is>
-          <t>38903</t>
+          <t>38458</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>Encuentro Oceania</t>
+          <t>El Rosario</t>
         </is>
       </c>
       <c r="D28" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E28" s="7" t="n">
@@ -1751,12 +1751,12 @@
       </c>
       <c r="B29" s="14" t="inlineStr">
         <is>
-          <t>38995</t>
+          <t>38903</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>Encuentro Oceania II</t>
+          <t>Encuentro Oceania</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr">
@@ -1786,17 +1786,17 @@
       </c>
       <c r="B30" s="15" t="inlineStr">
         <is>
-          <t>38507</t>
+          <t>38995</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>Espacio Vista del Valle</t>
+          <t>Encuentro Oceania II</t>
         </is>
       </c>
       <c r="D30" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E30" s="7" t="n">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="B31" s="14" t="inlineStr">
         <is>
-          <t>38363</t>
+          <t>38507</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>Galerias Atizapan</t>
+          <t>Espacio Vista del Valle</t>
         </is>
       </c>
       <c r="D31" s="12" t="inlineStr">
@@ -1856,17 +1856,17 @@
       </c>
       <c r="B32" s="15" t="inlineStr">
         <is>
-          <t>38770</t>
+          <t>38363</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>Gustavo Baz 29</t>
+          <t>Galerias Atizapan</t>
         </is>
       </c>
       <c r="D32" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E32" s="7" t="n">
@@ -1891,17 +1891,17 @@
       </c>
       <c r="B33" s="14" t="inlineStr">
         <is>
-          <t>38230</t>
+          <t>38770</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>ITEMS Edo de Mexico</t>
+          <t>Gustavo Baz 29</t>
         </is>
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E33" s="11" t="n">
@@ -1926,12 +1926,12 @@
       </c>
       <c r="B34" s="15" t="inlineStr">
         <is>
-          <t>38661</t>
+          <t>38230</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>Jinetes</t>
+          <t>ITEMS Edo de Mexico</t>
         </is>
       </c>
       <c r="D34" s="8" t="inlineStr">
@@ -1961,17 +1961,17 @@
       </c>
       <c r="B35" s="14" t="inlineStr">
         <is>
-          <t>38205</t>
+          <t>38661</t>
         </is>
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>Lindavista</t>
+          <t>Jinetes</t>
         </is>
       </c>
       <c r="D35" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E35" s="11" t="n">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="B36" s="15" t="inlineStr">
         <is>
-          <t>38207</t>
+          <t>38205</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>Lindavista II</t>
+          <t>Lindavista</t>
         </is>
       </c>
       <c r="D36" s="8" t="inlineStr">
@@ -2031,17 +2031,17 @@
       </c>
       <c r="B37" s="14" t="inlineStr">
         <is>
-          <t>38119</t>
+          <t>38207</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>Lomas Verdes</t>
+          <t>Lindavista II</t>
         </is>
       </c>
       <c r="D37" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E37" s="11" t="n">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="B38" s="15" t="inlineStr">
         <is>
-          <t>38270</t>
+          <t>38119</t>
         </is>
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>Lomas Verdes II</t>
+          <t>Lomas Verdes</t>
         </is>
       </c>
       <c r="D38" s="8" t="inlineStr">
@@ -2101,17 +2101,17 @@
       </c>
       <c r="B39" s="14" t="inlineStr">
         <is>
-          <t>38368</t>
+          <t>38270</t>
         </is>
       </c>
       <c r="C39" s="12" t="inlineStr">
         <is>
-          <t>Luna Park</t>
+          <t>Lomas Verdes II</t>
         </is>
       </c>
       <c r="D39" s="12" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E39" s="11" t="n">
@@ -3474,7 +3474,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Centro Norte · Corte 29/08/2026 15:56</t>
+          <t>Centro Norte · Corte 29/08/2026 22:34</t>
         </is>
       </c>
     </row>
@@ -3520,10 +3520,10 @@
         </is>
       </c>
       <c r="C5" s="11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E5" s="13">
         <f>IFERROR(C5/(C5+D5),0)</f>
@@ -3545,10 +3545,10 @@
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D6" s="7" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E6" s="9">
         <f>IFERROR(C6/(C6+D6),0)</f>

--- a/exports/Resumen_Evidencias_OPS.xlsx
+++ b/exports/Resumen_Evidencias_OPS.xlsx
@@ -27,7 +27,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -76,8 +76,14 @@
       <color rgb="00922F24"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Aptos"/>
+      <b val="1"/>
+      <color rgb="0080520C"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -109,6 +115,11 @@
         <fgColor rgb="00F9E6E3"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF0D5"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -127,7 +138,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -170,6 +181,9 @@
     </xf>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -563,7 +577,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Centro Norte · Corte 29/08/2026 22:34</t>
+          <t>Centro Norte · Corte 30/08/2026 13:47</t>
         </is>
       </c>
     </row>
@@ -586,10 +600,10 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>707</v>
+        <v>680</v>
       </c>
       <c r="E6" s="5">
         <f>IFERROR(A6/(A6+C6),0)</f>
@@ -647,10 +661,10 @@
         <v>10</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="F10" s="9">
         <f>IFERROR(D10/(D10+E10),0)</f>
@@ -668,17 +682,17 @@
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Garcia</t>
+          <t>Yazmin Chabela</t>
         </is>
       </c>
       <c r="C11" s="11" t="n">
         <v>13</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="E11" s="12" t="n">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="F11" s="13">
         <f>IFERROR(D11/(D11+E11),0)</f>
@@ -696,17 +710,17 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño</t>
+          <t>Yazmin Garcia</t>
         </is>
       </c>
       <c r="C12" s="7" t="n">
         <v>13</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E12" s="8" t="n">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="F12" s="9">
         <f>IFERROR(D12/(D12+E12),0)</f>
@@ -724,17 +738,17 @@
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina</t>
+          <t>Vanessa Carreño</t>
         </is>
       </c>
       <c r="C13" s="11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D13" s="11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E13" s="12" t="n">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="F13" s="13">
         <f>IFERROR(D13/(D13+E13),0)</f>
@@ -759,10 +773,10 @@
         <v>11</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E14" s="8" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F14" s="9">
         <f>IFERROR(D14/(D14+E14),0)</f>
@@ -780,17 +794,17 @@
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela</t>
+          <t>Nancy Carolina</t>
         </is>
       </c>
       <c r="C15" s="11" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D15" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E15" s="12" t="n">
-        <v>130</v>
+        <v>119</v>
       </c>
       <c r="F15" s="13">
         <f>IFERROR(D15/(D15+E15),0)</f>
@@ -859,7 +873,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Centro Norte · Corte 29/08/2026 22:34</t>
+          <t>Centro Norte · Corte 30/08/2026 13:47</t>
         </is>
       </c>
     </row>
@@ -911,32 +925,32 @@
       </c>
       <c r="B5" s="14" t="inlineStr">
         <is>
-          <t>38894</t>
+          <t>38561</t>
         </is>
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>Galerias Perinorte</t>
+          <t>Parque Toreo</t>
         </is>
       </c>
       <c r="D5" s="12" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E5" s="11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G5" s="13">
         <f>IFERROR(E5/(E5+F5),0)</f>
         <v/>
       </c>
-      <c r="H5" s="10" t="inlineStr">
-        <is>
-          <t>Atención</t>
+      <c r="H5" s="15" t="inlineStr">
+        <is>
+          <t>Seguimiento</t>
         </is>
       </c>
     </row>
@@ -944,34 +958,34 @@
       <c r="A6" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="15" t="inlineStr">
-        <is>
-          <t>38862</t>
+      <c r="B6" s="16" t="inlineStr">
+        <is>
+          <t>38695</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>San Miguel Izcalli</t>
+          <t>Cetram 4 Caminos</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E6" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G6" s="9">
         <f>IFERROR(E6/(E6+F6),0)</f>
         <v/>
       </c>
-      <c r="H6" s="10" t="inlineStr">
-        <is>
-          <t>Atención</t>
+      <c r="H6" s="15" t="inlineStr">
+        <is>
+          <t>Seguimiento</t>
         </is>
       </c>
     </row>
@@ -981,24 +995,24 @@
       </c>
       <c r="B7" s="14" t="inlineStr">
         <is>
-          <t>43194</t>
+          <t>38894</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>Atana Lindavista</t>
+          <t>Galerias Perinorte</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E7" s="11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G7" s="13">
         <f>IFERROR(E7/(E7+F7),0)</f>
@@ -1014,26 +1028,26 @@
       <c r="A8" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="15" t="inlineStr">
-        <is>
-          <t>38394</t>
+      <c r="B8" s="16" t="inlineStr">
+        <is>
+          <t>38339</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>Centro Comercial Lomas Verdes</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E8" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G8" s="9">
         <f>IFERROR(E8/(E8+F8),0)</f>
@@ -1051,12 +1065,12 @@
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>38333</t>
+          <t>38862</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>Izcalli Mega</t>
+          <t>San Miguel Izcalli</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
@@ -1065,10 +1079,10 @@
         </is>
       </c>
       <c r="E9" s="11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G9" s="13">
         <f>IFERROR(E9/(E9+F9),0)</f>
@@ -1084,19 +1098,19 @@
       <c r="A10" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="15" t="inlineStr">
-        <is>
-          <t>38368</t>
+      <c r="B10" s="16" t="inlineStr">
+        <is>
+          <t>43194</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>Luna Park</t>
+          <t>Atana Lindavista</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E10" s="7" t="n">
@@ -1121,17 +1135,17 @@
       </c>
       <c r="B11" s="14" t="inlineStr">
         <is>
-          <t>38456</t>
+          <t>38149</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>Plaza las Flores</t>
+          <t>Bellavista</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E11" s="11" t="n">
@@ -1154,19 +1168,19 @@
       <c r="A12" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="15" t="inlineStr">
-        <is>
-          <t>38925</t>
+      <c r="B12" s="16" t="inlineStr">
+        <is>
+          <t>38527</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Star Medica Lomas Verdes</t>
+          <t>Camarones</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E12" s="7" t="n">
@@ -1191,12 +1205,12 @@
       </c>
       <c r="B13" s="14" t="inlineStr">
         <is>
-          <t>38142</t>
+          <t>38394</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>Zona Esmeralda</t>
+          <t>Centro Comercial Lomas Verdes</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
@@ -1224,26 +1238,26 @@
       <c r="A14" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="15" t="inlineStr">
-        <is>
-          <t>38186</t>
+      <c r="B14" s="16" t="inlineStr">
+        <is>
+          <t>38535</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Arboledas</t>
+          <t>City Center Esmeralda</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E14" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F14" s="7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G14" s="9">
         <f>IFERROR(E14/(E14+F14),0)</f>
@@ -1261,24 +1275,24 @@
       </c>
       <c r="B15" s="14" t="inlineStr">
         <is>
-          <t>43043</t>
+          <t>38197</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>Atizapan</t>
+          <t>Echegaray</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E15" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G15" s="13">
         <f>IFERROR(E15/(E15+F15),0)</f>
@@ -1294,14 +1308,14 @@
       <c r="A16" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="15" t="inlineStr">
-        <is>
-          <t>38149</t>
+      <c r="B16" s="16" t="inlineStr">
+        <is>
+          <t>38363</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>Bellavista</t>
+          <t>Galerias Atizapan</t>
         </is>
       </c>
       <c r="D16" s="8" t="inlineStr">
@@ -1310,10 +1324,10 @@
         </is>
       </c>
       <c r="E16" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F16" s="7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G16" s="9">
         <f>IFERROR(E16/(E16+F16),0)</f>
@@ -1331,24 +1345,24 @@
       </c>
       <c r="B17" s="14" t="inlineStr">
         <is>
-          <t>38930</t>
+          <t>38333</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>Blvd. Aeropuerto dt</t>
+          <t>Izcalli Mega</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E17" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G17" s="13">
         <f>IFERROR(E17/(E17+F17),0)</f>
@@ -1364,26 +1378,26 @@
       <c r="A18" s="7" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="15" t="inlineStr">
-        <is>
-          <t>38529</t>
+      <c r="B18" s="16" t="inlineStr">
+        <is>
+          <t>38661</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>Bosques de Aragon</t>
+          <t>Jinetes</t>
         </is>
       </c>
       <c r="D18" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E18" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F18" s="7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G18" s="9">
         <f>IFERROR(E18/(E18+F18),0)</f>
@@ -1401,24 +1415,24 @@
       </c>
       <c r="B19" s="14" t="inlineStr">
         <is>
-          <t>38527</t>
+          <t>38368</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>Camarones</t>
+          <t>Luna Park</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E19" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G19" s="13">
         <f>IFERROR(E19/(E19+F19),0)</f>
@@ -1434,14 +1448,14 @@
       <c r="A20" s="7" t="n">
         <v>16</v>
       </c>
-      <c r="B20" s="15" t="inlineStr">
-        <is>
-          <t>38837</t>
+      <c r="B20" s="16" t="inlineStr">
+        <is>
+          <t>43195</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>Centenario Azcapotzalco</t>
+          <t>Parque Jadin kiosko</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr">
@@ -1450,10 +1464,10 @@
         </is>
       </c>
       <c r="E20" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F20" s="7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G20" s="9">
         <f>IFERROR(E20/(E20+F20),0)</f>
@@ -1471,24 +1485,24 @@
       </c>
       <c r="B21" s="14" t="inlineStr">
         <is>
-          <t>38695</t>
+          <t>38937</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>Cetram 4 Caminos</t>
+          <t>Parque Tepeyac Piso 1</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E21" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G21" s="13">
         <f>IFERROR(E21/(E21+F21),0)</f>
@@ -1504,26 +1518,26 @@
       <c r="A22" s="7" t="n">
         <v>18</v>
       </c>
-      <c r="B22" s="15" t="inlineStr">
-        <is>
-          <t>38535</t>
+      <c r="B22" s="16" t="inlineStr">
+        <is>
+          <t>38590</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>City Center Esmeralda</t>
+          <t>Parque Toreo II</t>
         </is>
       </c>
       <c r="D22" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E22" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G22" s="9">
         <f>IFERROR(E22/(E22+F22),0)</f>
@@ -1541,24 +1555,24 @@
       </c>
       <c r="B23" s="14" t="inlineStr">
         <is>
-          <t>38401</t>
+          <t>43132</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>Coacalco</t>
+          <t>Plaza Vista Norte</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E23" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G23" s="13">
         <f>IFERROR(E23/(E23+F23),0)</f>
@@ -1574,14 +1588,14 @@
       <c r="A24" s="7" t="n">
         <v>20</v>
       </c>
-      <c r="B24" s="15" t="inlineStr">
-        <is>
-          <t>38604</t>
+      <c r="B24" s="16" t="inlineStr">
+        <is>
+          <t>38456</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>Cosmopol</t>
+          <t>Plaza las Flores</t>
         </is>
       </c>
       <c r="D24" s="8" t="inlineStr">
@@ -1590,10 +1604,10 @@
         </is>
       </c>
       <c r="E24" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F24" s="7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G24" s="9">
         <f>IFERROR(E24/(E24+F24),0)</f>
@@ -1611,24 +1625,24 @@
       </c>
       <c r="B25" s="14" t="inlineStr">
         <is>
-          <t>43193</t>
+          <t>38266</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>Cosmopol N1</t>
+          <t>San Mateo</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E25" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G25" s="13">
         <f>IFERROR(E25/(E25+F25),0)</f>
@@ -1644,14 +1658,14 @@
       <c r="A26" s="7" t="n">
         <v>22</v>
       </c>
-      <c r="B26" s="15" t="inlineStr">
-        <is>
-          <t>38197</t>
+      <c r="B26" s="16" t="inlineStr">
+        <is>
+          <t>38117</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>Echegaray</t>
+          <t>Satelite</t>
         </is>
       </c>
       <c r="D26" s="8" t="inlineStr">
@@ -1660,10 +1674,10 @@
         </is>
       </c>
       <c r="E26" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F26" s="7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G26" s="9">
         <f>IFERROR(E26/(E26+F26),0)</f>
@@ -1681,24 +1695,24 @@
       </c>
       <c r="B27" s="14" t="inlineStr">
         <is>
-          <t>38431</t>
+          <t>38475</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>Eduardo Molina</t>
+          <t>Satelite Centro Civico</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E27" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G27" s="13">
         <f>IFERROR(E27/(E27+F27),0)</f>
@@ -1714,26 +1728,26 @@
       <c r="A28" s="7" t="n">
         <v>24</v>
       </c>
-      <c r="B28" s="15" t="inlineStr">
-        <is>
-          <t>38458</t>
+      <c r="B28" s="16" t="inlineStr">
+        <is>
+          <t>38925</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>El Rosario</t>
+          <t>Star Medica Lomas Verdes</t>
         </is>
       </c>
       <c r="D28" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E28" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F28" s="7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G28" s="9">
         <f>IFERROR(E28/(E28+F28),0)</f>
@@ -1751,24 +1765,24 @@
       </c>
       <c r="B29" s="14" t="inlineStr">
         <is>
-          <t>38903</t>
+          <t>38656</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>Encuentro Oceania</t>
+          <t>Viveros de la Loma</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E29" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G29" s="13">
         <f>IFERROR(E29/(E29+F29),0)</f>
@@ -1784,26 +1798,26 @@
       <c r="A30" s="7" t="n">
         <v>26</v>
       </c>
-      <c r="B30" s="15" t="inlineStr">
-        <is>
-          <t>38995</t>
+      <c r="B30" s="16" t="inlineStr">
+        <is>
+          <t>38142</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>Encuentro Oceania II</t>
+          <t>Zona Esmeralda</t>
         </is>
       </c>
       <c r="D30" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E30" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F30" s="7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G30" s="9">
         <f>IFERROR(E30/(E30+F30),0)</f>
@@ -1821,17 +1835,17 @@
       </c>
       <c r="B31" s="14" t="inlineStr">
         <is>
-          <t>38507</t>
+          <t>38186</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>Espacio Vista del Valle</t>
+          <t>Arboledas</t>
         </is>
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E31" s="11" t="n">
@@ -1854,14 +1868,14 @@
       <c r="A32" s="7" t="n">
         <v>28</v>
       </c>
-      <c r="B32" s="15" t="inlineStr">
-        <is>
-          <t>38363</t>
+      <c r="B32" s="16" t="inlineStr">
+        <is>
+          <t>43043</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>Galerias Atizapan</t>
+          <t>Atizapan</t>
         </is>
       </c>
       <c r="D32" s="8" t="inlineStr">
@@ -1891,17 +1905,17 @@
       </c>
       <c r="B33" s="14" t="inlineStr">
         <is>
-          <t>38770</t>
+          <t>38930</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>Gustavo Baz 29</t>
+          <t>Blvd. Aeropuerto dt</t>
         </is>
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E33" s="11" t="n">
@@ -1924,19 +1938,19 @@
       <c r="A34" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="B34" s="15" t="inlineStr">
-        <is>
-          <t>38230</t>
+      <c r="B34" s="16" t="inlineStr">
+        <is>
+          <t>38529</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>ITEMS Edo de Mexico</t>
+          <t>Bosques de Aragon</t>
         </is>
       </c>
       <c r="D34" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E34" s="7" t="n">
@@ -1961,17 +1975,17 @@
       </c>
       <c r="B35" s="14" t="inlineStr">
         <is>
-          <t>38661</t>
+          <t>38837</t>
         </is>
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>Jinetes</t>
+          <t>Centenario Azcapotzalco</t>
         </is>
       </c>
       <c r="D35" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E35" s="11" t="n">
@@ -1994,19 +2008,19 @@
       <c r="A36" s="7" t="n">
         <v>32</v>
       </c>
-      <c r="B36" s="15" t="inlineStr">
-        <is>
-          <t>38205</t>
+      <c r="B36" s="16" t="inlineStr">
+        <is>
+          <t>38401</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>Lindavista</t>
+          <t>Coacalco</t>
         </is>
       </c>
       <c r="D36" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E36" s="7" t="n">
@@ -2031,17 +2045,17 @@
       </c>
       <c r="B37" s="14" t="inlineStr">
         <is>
-          <t>38207</t>
+          <t>38604</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>Lindavista II</t>
+          <t>Cosmopol</t>
         </is>
       </c>
       <c r="D37" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E37" s="11" t="n">
@@ -2064,26 +2078,26 @@
       <c r="A38" s="7" t="n">
         <v>34</v>
       </c>
-      <c r="B38" s="15" t="inlineStr">
-        <is>
-          <t>38119</t>
+      <c r="B38" s="16" t="inlineStr">
+        <is>
+          <t>43193</t>
         </is>
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>Lomas Verdes</t>
+          <t>Cosmopol N1</t>
         </is>
       </c>
       <c r="D38" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E38" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F38" s="7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G38" s="9">
         <f>IFERROR(E38/(E38+F38),0)</f>
@@ -2101,17 +2115,17 @@
       </c>
       <c r="B39" s="14" t="inlineStr">
         <is>
-          <t>38270</t>
+          <t>38431</t>
         </is>
       </c>
       <c r="C39" s="12" t="inlineStr">
         <is>
-          <t>Lomas Verdes II</t>
+          <t>Eduardo Molina</t>
         </is>
       </c>
       <c r="D39" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E39" s="11" t="n">
@@ -2134,19 +2148,19 @@
       <c r="A40" s="7" t="n">
         <v>36</v>
       </c>
-      <c r="B40" s="15" t="inlineStr">
-        <is>
-          <t>38371</t>
+      <c r="B40" s="16" t="inlineStr">
+        <is>
+          <t>38458</t>
         </is>
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>Montevideo DT</t>
+          <t>El Rosario</t>
         </is>
       </c>
       <c r="D40" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E40" s="7" t="n">
@@ -2171,17 +2185,17 @@
       </c>
       <c r="B41" s="14" t="inlineStr">
         <is>
-          <t>43111</t>
+          <t>38903</t>
         </is>
       </c>
       <c r="C41" s="12" t="inlineStr">
         <is>
-          <t>Montevideo Insurgentes</t>
+          <t>Encuentro Oceania</t>
         </is>
       </c>
       <c r="D41" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E41" s="11" t="n">
@@ -2204,19 +2218,19 @@
       <c r="A42" s="7" t="n">
         <v>38</v>
       </c>
-      <c r="B42" s="15" t="inlineStr">
-        <is>
-          <t>38674</t>
+      <c r="B42" s="16" t="inlineStr">
+        <is>
+          <t>38995</t>
         </is>
       </c>
       <c r="C42" s="8" t="inlineStr">
         <is>
-          <t>Mundo E</t>
+          <t>Encuentro Oceania II</t>
         </is>
       </c>
       <c r="D42" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E42" s="7" t="n">
@@ -2241,17 +2255,17 @@
       </c>
       <c r="B43" s="14" t="inlineStr">
         <is>
-          <t>38845</t>
+          <t>38507</t>
         </is>
       </c>
       <c r="C43" s="12" t="inlineStr">
         <is>
-          <t>Mundo E II</t>
+          <t>Espacio Vista del Valle</t>
         </is>
       </c>
       <c r="D43" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E43" s="11" t="n">
@@ -2274,19 +2288,19 @@
       <c r="A44" s="7" t="n">
         <v>40</v>
       </c>
-      <c r="B44" s="15" t="inlineStr">
-        <is>
-          <t>43195</t>
+      <c r="B44" s="16" t="inlineStr">
+        <is>
+          <t>38770</t>
         </is>
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t>Parque Jadin kiosko</t>
+          <t>Gustavo Baz 29</t>
         </is>
       </c>
       <c r="D44" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E44" s="7" t="n">
@@ -2311,17 +2325,17 @@
       </c>
       <c r="B45" s="14" t="inlineStr">
         <is>
-          <t>38937</t>
+          <t>38230</t>
         </is>
       </c>
       <c r="C45" s="12" t="inlineStr">
         <is>
-          <t>Parque Tepeyac Piso 1</t>
+          <t>ITEMS Edo de Mexico</t>
         </is>
       </c>
       <c r="D45" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E45" s="11" t="n">
@@ -2344,19 +2358,19 @@
       <c r="A46" s="7" t="n">
         <v>42</v>
       </c>
-      <c r="B46" s="15" t="inlineStr">
-        <is>
-          <t>38965</t>
+      <c r="B46" s="16" t="inlineStr">
+        <is>
+          <t>38205</t>
         </is>
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t>Parque Tepeyac Piso 2</t>
+          <t>Lindavista</t>
         </is>
       </c>
       <c r="D46" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E46" s="7" t="n">
@@ -2381,17 +2395,17 @@
       </c>
       <c r="B47" s="14" t="inlineStr">
         <is>
-          <t>38561</t>
+          <t>38207</t>
         </is>
       </c>
       <c r="C47" s="12" t="inlineStr">
         <is>
-          <t>Parque Toreo</t>
+          <t>Lindavista II</t>
         </is>
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E47" s="11" t="n">
@@ -2414,19 +2428,19 @@
       <c r="A48" s="7" t="n">
         <v>44</v>
       </c>
-      <c r="B48" s="15" t="inlineStr">
-        <is>
-          <t>38590</t>
+      <c r="B48" s="16" t="inlineStr">
+        <is>
+          <t>38119</t>
         </is>
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
-          <t>Parque Toreo II</t>
+          <t>Lomas Verdes</t>
         </is>
       </c>
       <c r="D48" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E48" s="7" t="n">
@@ -2451,17 +2465,17 @@
       </c>
       <c r="B49" s="14" t="inlineStr">
         <is>
-          <t>38792</t>
+          <t>38270</t>
         </is>
       </c>
       <c r="C49" s="12" t="inlineStr">
         <is>
-          <t>Pasaje Tlanepantla</t>
+          <t>Lomas Verdes II</t>
         </is>
       </c>
       <c r="D49" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E49" s="11" t="n">
@@ -2484,14 +2498,14 @@
       <c r="A50" s="7" t="n">
         <v>46</v>
       </c>
-      <c r="B50" s="15" t="inlineStr">
-        <is>
-          <t>38546</t>
+      <c r="B50" s="16" t="inlineStr">
+        <is>
+          <t>38371</t>
         </is>
       </c>
       <c r="C50" s="8" t="inlineStr">
         <is>
-          <t>Patio Claveria</t>
+          <t>Montevideo DT</t>
         </is>
       </c>
       <c r="D50" s="8" t="inlineStr">
@@ -2521,17 +2535,17 @@
       </c>
       <c r="B51" s="14" t="inlineStr">
         <is>
-          <t>38515</t>
+          <t>43111</t>
         </is>
       </c>
       <c r="C51" s="12" t="inlineStr">
         <is>
-          <t>Patio Ecatepec</t>
+          <t>Montevideo Insurgentes</t>
         </is>
       </c>
       <c r="D51" s="12" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E51" s="11" t="n">
@@ -2554,19 +2568,19 @@
       <c r="A52" s="7" t="n">
         <v>48</v>
       </c>
-      <c r="B52" s="15" t="inlineStr">
-        <is>
-          <t>38677</t>
+      <c r="B52" s="16" t="inlineStr">
+        <is>
+          <t>38674</t>
         </is>
       </c>
       <c r="C52" s="8" t="inlineStr">
         <is>
-          <t>Patio la Raza</t>
+          <t>Mundo E</t>
         </is>
       </c>
       <c r="D52" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E52" s="7" t="n">
@@ -2591,17 +2605,17 @@
       </c>
       <c r="B53" s="14" t="inlineStr">
         <is>
-          <t>38176</t>
+          <t>38845</t>
         </is>
       </c>
       <c r="C53" s="12" t="inlineStr">
         <is>
-          <t>Periferico Satélite DT</t>
+          <t>Mundo E II</t>
         </is>
       </c>
       <c r="D53" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E53" s="11" t="n">
@@ -2624,14 +2638,14 @@
       <c r="A54" s="7" t="n">
         <v>50</v>
       </c>
-      <c r="B54" s="15" t="inlineStr">
-        <is>
-          <t>38924</t>
+      <c r="B54" s="16" t="inlineStr">
+        <is>
+          <t>38965</t>
         </is>
       </c>
       <c r="C54" s="8" t="inlineStr">
         <is>
-          <t>Plaza Aeropuerto</t>
+          <t>Parque Tepeyac Piso 2</t>
         </is>
       </c>
       <c r="D54" s="8" t="inlineStr">
@@ -2661,17 +2675,17 @@
       </c>
       <c r="B55" s="14" t="inlineStr">
         <is>
-          <t>38719</t>
+          <t>38792</t>
         </is>
       </c>
       <c r="C55" s="12" t="inlineStr">
         <is>
-          <t>Plaza Fortuna</t>
+          <t>Pasaje Tlanepantla</t>
         </is>
       </c>
       <c r="D55" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E55" s="11" t="n">
@@ -2694,19 +2708,19 @@
       <c r="A56" s="7" t="n">
         <v>52</v>
       </c>
-      <c r="B56" s="15" t="inlineStr">
-        <is>
-          <t>38427</t>
+      <c r="B56" s="16" t="inlineStr">
+        <is>
+          <t>38546</t>
         </is>
       </c>
       <c r="C56" s="8" t="inlineStr">
         <is>
-          <t>Plaza Satelite</t>
+          <t>Patio Claveria</t>
         </is>
       </c>
       <c r="D56" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E56" s="7" t="n">
@@ -2731,17 +2745,17 @@
       </c>
       <c r="B57" s="14" t="inlineStr">
         <is>
-          <t>38859</t>
+          <t>38515</t>
         </is>
       </c>
       <c r="C57" s="12" t="inlineStr">
         <is>
-          <t>Plaza Satelite II N1</t>
+          <t>Patio Ecatepec</t>
         </is>
       </c>
       <c r="D57" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E57" s="11" t="n">
@@ -2764,19 +2778,19 @@
       <c r="A58" s="7" t="n">
         <v>54</v>
       </c>
-      <c r="B58" s="15" t="inlineStr">
-        <is>
-          <t>38811</t>
+      <c r="B58" s="16" t="inlineStr">
+        <is>
+          <t>38677</t>
         </is>
       </c>
       <c r="C58" s="8" t="inlineStr">
         <is>
-          <t>Plaza Tepeyac</t>
+          <t>Patio la Raza</t>
         </is>
       </c>
       <c r="D58" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E58" s="7" t="n">
@@ -2801,17 +2815,17 @@
       </c>
       <c r="B59" s="14" t="inlineStr">
         <is>
-          <t>43132</t>
+          <t>38176</t>
         </is>
       </c>
       <c r="C59" s="12" t="inlineStr">
         <is>
-          <t>Plaza Vista Norte</t>
+          <t>Periferico Satélite DT</t>
         </is>
       </c>
       <c r="D59" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E59" s="11" t="n">
@@ -2834,19 +2848,19 @@
       <c r="A60" s="7" t="n">
         <v>56</v>
       </c>
-      <c r="B60" s="15" t="inlineStr">
-        <is>
-          <t>38136</t>
+      <c r="B60" s="16" t="inlineStr">
+        <is>
+          <t>38924</t>
         </is>
       </c>
       <c r="C60" s="8" t="inlineStr">
         <is>
-          <t>Punta Norte</t>
+          <t>Plaza Aeropuerto</t>
         </is>
       </c>
       <c r="D60" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E60" s="7" t="n">
@@ -2871,17 +2885,17 @@
       </c>
       <c r="B61" s="14" t="inlineStr">
         <is>
-          <t>43152</t>
+          <t>38719</t>
         </is>
       </c>
       <c r="C61" s="12" t="inlineStr">
         <is>
-          <t>Samara Satélite</t>
+          <t>Plaza Fortuna</t>
         </is>
       </c>
       <c r="D61" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E61" s="11" t="n">
@@ -2904,19 +2918,19 @@
       <c r="A62" s="7" t="n">
         <v>58</v>
       </c>
-      <c r="B62" s="15" t="inlineStr">
-        <is>
-          <t>38339</t>
+      <c r="B62" s="16" t="inlineStr">
+        <is>
+          <t>38427</t>
         </is>
       </c>
       <c r="C62" s="8" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Plaza Satelite</t>
         </is>
       </c>
       <c r="D62" s="8" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E62" s="7" t="n">
@@ -2941,17 +2955,17 @@
       </c>
       <c r="B63" s="14" t="inlineStr">
         <is>
-          <t>38266</t>
+          <t>38859</t>
         </is>
       </c>
       <c r="C63" s="12" t="inlineStr">
         <is>
-          <t>San Mateo</t>
+          <t>Plaza Satelite II N1</t>
         </is>
       </c>
       <c r="D63" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E63" s="11" t="n">
@@ -2974,19 +2988,19 @@
       <c r="A64" s="7" t="n">
         <v>60</v>
       </c>
-      <c r="B64" s="15" t="inlineStr">
-        <is>
-          <t>38460</t>
+      <c r="B64" s="16" t="inlineStr">
+        <is>
+          <t>38811</t>
         </is>
       </c>
       <c r="C64" s="8" t="inlineStr">
         <is>
-          <t>Santa Monica</t>
+          <t>Plaza Tepeyac</t>
         </is>
       </c>
       <c r="D64" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E64" s="7" t="n">
@@ -3011,17 +3025,17 @@
       </c>
       <c r="B65" s="14" t="inlineStr">
         <is>
-          <t>38117</t>
+          <t>38136</t>
         </is>
       </c>
       <c r="C65" s="12" t="inlineStr">
         <is>
-          <t>Satelite</t>
+          <t>Punta Norte</t>
         </is>
       </c>
       <c r="D65" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E65" s="11" t="n">
@@ -3044,14 +3058,14 @@
       <c r="A66" s="7" t="n">
         <v>62</v>
       </c>
-      <c r="B66" s="15" t="inlineStr">
-        <is>
-          <t>38475</t>
+      <c r="B66" s="16" t="inlineStr">
+        <is>
+          <t>43152</t>
         </is>
       </c>
       <c r="C66" s="8" t="inlineStr">
         <is>
-          <t>Satelite Centro Civico</t>
+          <t>Samara Satélite</t>
         </is>
       </c>
       <c r="D66" s="8" t="inlineStr">
@@ -3081,12 +3095,12 @@
       </c>
       <c r="B67" s="14" t="inlineStr">
         <is>
-          <t>38442</t>
+          <t>38460</t>
         </is>
       </c>
       <c r="C67" s="12" t="inlineStr">
         <is>
-          <t>Sor Juana</t>
+          <t>Santa Monica</t>
         </is>
       </c>
       <c r="D67" s="12" t="inlineStr">
@@ -3114,19 +3128,19 @@
       <c r="A68" s="7" t="n">
         <v>64</v>
       </c>
-      <c r="B68" s="15" t="inlineStr">
-        <is>
-          <t>38992</t>
+      <c r="B68" s="16" t="inlineStr">
+        <is>
+          <t>38442</t>
         </is>
       </c>
       <c r="C68" s="8" t="inlineStr">
         <is>
-          <t>Tapo Puerta Oriente</t>
+          <t>Sor Juana</t>
         </is>
       </c>
       <c r="D68" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E68" s="7" t="n">
@@ -3151,17 +3165,17 @@
       </c>
       <c r="B69" s="14" t="inlineStr">
         <is>
-          <t>38606</t>
+          <t>38992</t>
         </is>
       </c>
       <c r="C69" s="12" t="inlineStr">
         <is>
-          <t>TlalnepantlaCarso</t>
+          <t>Tapo Puerta Oriente</t>
         </is>
       </c>
       <c r="D69" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E69" s="11" t="n">
@@ -3184,19 +3198,19 @@
       <c r="A70" s="7" t="n">
         <v>66</v>
       </c>
-      <c r="B70" s="15" t="inlineStr">
-        <is>
-          <t>38411</t>
+      <c r="B70" s="16" t="inlineStr">
+        <is>
+          <t>38606</t>
         </is>
       </c>
       <c r="C70" s="8" t="inlineStr">
         <is>
-          <t>Torres Lindavista</t>
+          <t>TlalnepantlaCarso</t>
         </is>
       </c>
       <c r="D70" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E70" s="7" t="n">
@@ -3221,17 +3235,17 @@
       </c>
       <c r="B71" s="14" t="inlineStr">
         <is>
-          <t>43130</t>
+          <t>38411</t>
         </is>
       </c>
       <c r="C71" s="12" t="inlineStr">
         <is>
-          <t>Town Center Nicolás Romero</t>
+          <t>Torres Lindavista</t>
         </is>
       </c>
       <c r="D71" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E71" s="11" t="n">
@@ -3254,19 +3268,19 @@
       <c r="A72" s="7" t="n">
         <v>68</v>
       </c>
-      <c r="B72" s="15" t="inlineStr">
-        <is>
-          <t>38374</t>
+      <c r="B72" s="16" t="inlineStr">
+        <is>
+          <t>43130</t>
         </is>
       </c>
       <c r="C72" s="8" t="inlineStr">
         <is>
-          <t>Valle Dorado</t>
+          <t>Town Center Nicolás Romero</t>
         </is>
       </c>
       <c r="D72" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E72" s="7" t="n">
@@ -3291,17 +3305,17 @@
       </c>
       <c r="B73" s="14" t="inlineStr">
         <is>
-          <t>38651</t>
+          <t>38374</t>
         </is>
       </c>
       <c r="C73" s="12" t="inlineStr">
         <is>
-          <t>Via Vallejo</t>
+          <t>Valle Dorado</t>
         </is>
       </c>
       <c r="D73" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E73" s="11" t="n">
@@ -3324,19 +3338,19 @@
       <c r="A74" s="7" t="n">
         <v>70</v>
       </c>
-      <c r="B74" s="15" t="inlineStr">
-        <is>
-          <t>38694</t>
+      <c r="B74" s="16" t="inlineStr">
+        <is>
+          <t>38651</t>
         </is>
       </c>
       <c r="C74" s="8" t="inlineStr">
         <is>
-          <t>Villas de la Hacienda</t>
+          <t>Via Vallejo</t>
         </is>
       </c>
       <c r="D74" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E74" s="7" t="n">
@@ -3361,17 +3375,17 @@
       </c>
       <c r="B75" s="14" t="inlineStr">
         <is>
-          <t>38656</t>
+          <t>38694</t>
         </is>
       </c>
       <c r="C75" s="12" t="inlineStr">
         <is>
-          <t>Viveros de la Loma</t>
+          <t>Villas de la Hacienda</t>
         </is>
       </c>
       <c r="D75" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E75" s="11" t="n">
@@ -3394,7 +3408,7 @@
       <c r="A76" s="7" t="n">
         <v>72</v>
       </c>
-      <c r="B76" s="15" t="inlineStr">
+      <c r="B76" s="16" t="inlineStr">
         <is>
           <t>38115</t>
         </is>
@@ -3474,7 +3488,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Centro Norte · Corte 29/08/2026 22:34</t>
+          <t>Centro Norte · Corte 30/08/2026 13:47</t>
         </is>
       </c>
     </row>
@@ -3520,10 +3534,10 @@
         </is>
       </c>
       <c r="C5" s="11" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="E5" s="13">
         <f>IFERROR(C5/(C5+D5),0)</f>
@@ -3570,10 +3584,10 @@
         </is>
       </c>
       <c r="C7" s="11" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E7" s="13">
         <f>IFERROR(C7/(C7+D7),0)</f>
@@ -3595,10 +3609,10 @@
         </is>
       </c>
       <c r="C8" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E8" s="9">
         <f>IFERROR(C8/(C8+D8),0)</f>
@@ -3620,10 +3634,10 @@
         </is>
       </c>
       <c r="C9" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D9" s="11" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E9" s="13">
         <f>IFERROR(C9/(C9+D9),0)</f>
@@ -3670,10 +3684,10 @@
         </is>
       </c>
       <c r="C11" s="11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E11" s="13">
         <f>IFERROR(C11/(C11+D11),0)</f>
@@ -3695,10 +3709,10 @@
         </is>
       </c>
       <c r="C12" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E12" s="9">
         <f>IFERROR(C12/(C12+D12),0)</f>
@@ -3723,7 +3737,7 @@
         <v>0</v>
       </c>
       <c r="D13" s="11" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E13" s="13">
         <f>IFERROR(C13/(C13+D13),0)</f>
@@ -3745,10 +3759,10 @@
         </is>
       </c>
       <c r="C14" s="7" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="E14" s="9">
         <f>IFERROR(C14/(C14+D14),0)</f>

--- a/exports/Resumen_Evidencias_OPS.xlsx
+++ b/exports/Resumen_Evidencias_OPS.xlsx
@@ -577,7 +577,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Centro Norte · Corte 30/08/2026 13:47</t>
+          <t>Centro Norte · Corte 30/08/2026 14:58</t>
         </is>
       </c>
     </row>
@@ -600,10 +600,10 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="E6" s="5">
         <f>IFERROR(A6/(A6+C6),0)</f>
@@ -661,10 +661,10 @@
         <v>10</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F10" s="9">
         <f>IFERROR(D10/(D10+E10),0)</f>
@@ -873,7 +873,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Centro Norte · Corte 30/08/2026 13:47</t>
+          <t>Centro Norte · Corte 30/08/2026 14:58</t>
         </is>
       </c>
     </row>
@@ -1275,17 +1275,17 @@
       </c>
       <c r="B15" s="14" t="inlineStr">
         <is>
-          <t>38197</t>
+          <t>38604</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>Echegaray</t>
+          <t>Cosmopol</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E15" s="11" t="n">
@@ -1310,17 +1310,17 @@
       </c>
       <c r="B16" s="16" t="inlineStr">
         <is>
-          <t>38363</t>
+          <t>38197</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>Galerias Atizapan</t>
+          <t>Echegaray</t>
         </is>
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E16" s="7" t="n">
@@ -1345,17 +1345,17 @@
       </c>
       <c r="B17" s="14" t="inlineStr">
         <is>
-          <t>38333</t>
+          <t>38363</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>Izcalli Mega</t>
+          <t>Galerias Atizapan</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E17" s="11" t="n">
@@ -1380,17 +1380,17 @@
       </c>
       <c r="B18" s="16" t="inlineStr">
         <is>
-          <t>38661</t>
+          <t>38333</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>Jinetes</t>
+          <t>Izcalli Mega</t>
         </is>
       </c>
       <c r="D18" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E18" s="7" t="n">
@@ -1415,17 +1415,17 @@
       </c>
       <c r="B19" s="14" t="inlineStr">
         <is>
-          <t>38368</t>
+          <t>38661</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>Luna Park</t>
+          <t>Jinetes</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E19" s="11" t="n">
@@ -1450,17 +1450,17 @@
       </c>
       <c r="B20" s="16" t="inlineStr">
         <is>
-          <t>43195</t>
+          <t>38368</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>Parque Jadin kiosko</t>
+          <t>Luna Park</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E20" s="7" t="n">
@@ -1485,17 +1485,17 @@
       </c>
       <c r="B21" s="14" t="inlineStr">
         <is>
-          <t>38937</t>
+          <t>43195</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>Parque Tepeyac Piso 1</t>
+          <t>Parque Jadin kiosko</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E21" s="11" t="n">
@@ -1520,17 +1520,17 @@
       </c>
       <c r="B22" s="16" t="inlineStr">
         <is>
-          <t>38590</t>
+          <t>38937</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>Parque Toreo II</t>
+          <t>Parque Tepeyac Piso 1</t>
         </is>
       </c>
       <c r="D22" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E22" s="7" t="n">
@@ -1555,17 +1555,17 @@
       </c>
       <c r="B23" s="14" t="inlineStr">
         <is>
-          <t>43132</t>
+          <t>38590</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>Plaza Vista Norte</t>
+          <t>Parque Toreo II</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E23" s="11" t="n">
@@ -1590,17 +1590,17 @@
       </c>
       <c r="B24" s="16" t="inlineStr">
         <is>
-          <t>38456</t>
+          <t>43132</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>Plaza las Flores</t>
+          <t>Plaza Vista Norte</t>
         </is>
       </c>
       <c r="D24" s="8" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E24" s="7" t="n">
@@ -1625,17 +1625,17 @@
       </c>
       <c r="B25" s="14" t="inlineStr">
         <is>
-          <t>38266</t>
+          <t>38456</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>San Mateo</t>
+          <t>Plaza las Flores</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E25" s="11" t="n">
@@ -1660,17 +1660,17 @@
       </c>
       <c r="B26" s="16" t="inlineStr">
         <is>
-          <t>38117</t>
+          <t>38266</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>Satelite</t>
+          <t>San Mateo</t>
         </is>
       </c>
       <c r="D26" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E26" s="7" t="n">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="B27" s="14" t="inlineStr">
         <is>
-          <t>38475</t>
+          <t>38117</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>Satelite Centro Civico</t>
+          <t>Satelite</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
@@ -1730,17 +1730,17 @@
       </c>
       <c r="B28" s="16" t="inlineStr">
         <is>
-          <t>38925</t>
+          <t>38475</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>Star Medica Lomas Verdes</t>
+          <t>Satelite Centro Civico</t>
         </is>
       </c>
       <c r="D28" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E28" s="7" t="n">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="B29" s="14" t="inlineStr">
         <is>
-          <t>38656</t>
+          <t>38925</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>Viveros de la Loma</t>
+          <t>Star Medica Lomas Verdes</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E29" s="11" t="n">
@@ -1800,17 +1800,17 @@
       </c>
       <c r="B30" s="16" t="inlineStr">
         <is>
-          <t>38142</t>
+          <t>38656</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>Zona Esmeralda</t>
+          <t>Viveros de la Loma</t>
         </is>
       </c>
       <c r="D30" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E30" s="7" t="n">
@@ -1835,24 +1835,24 @@
       </c>
       <c r="B31" s="14" t="inlineStr">
         <is>
-          <t>38186</t>
+          <t>38142</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>Arboledas</t>
+          <t>Zona Esmeralda</t>
         </is>
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E31" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G31" s="13">
         <f>IFERROR(E31/(E31+F31),0)</f>
@@ -1870,17 +1870,17 @@
       </c>
       <c r="B32" s="16" t="inlineStr">
         <is>
-          <t>43043</t>
+          <t>38186</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>Atizapan</t>
+          <t>Arboledas</t>
         </is>
       </c>
       <c r="D32" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E32" s="7" t="n">
@@ -1905,17 +1905,17 @@
       </c>
       <c r="B33" s="14" t="inlineStr">
         <is>
-          <t>38930</t>
+          <t>43043</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>Blvd. Aeropuerto dt</t>
+          <t>Atizapan</t>
         </is>
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E33" s="11" t="n">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="B34" s="16" t="inlineStr">
         <is>
-          <t>38529</t>
+          <t>38930</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>Bosques de Aragon</t>
+          <t>Blvd. Aeropuerto dt</t>
         </is>
       </c>
       <c r="D34" s="8" t="inlineStr">
@@ -1975,17 +1975,17 @@
       </c>
       <c r="B35" s="14" t="inlineStr">
         <is>
-          <t>38837</t>
+          <t>38529</t>
         </is>
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>Centenario Azcapotzalco</t>
+          <t>Bosques de Aragon</t>
         </is>
       </c>
       <c r="D35" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E35" s="11" t="n">
@@ -2010,17 +2010,17 @@
       </c>
       <c r="B36" s="16" t="inlineStr">
         <is>
-          <t>38401</t>
+          <t>38837</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>Coacalco</t>
+          <t>Centenario Azcapotzalco</t>
         </is>
       </c>
       <c r="D36" s="8" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E36" s="7" t="n">
@@ -2045,12 +2045,12 @@
       </c>
       <c r="B37" s="14" t="inlineStr">
         <is>
-          <t>38604</t>
+          <t>38401</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>Cosmopol</t>
+          <t>Coacalco</t>
         </is>
       </c>
       <c r="D37" s="12" t="inlineStr">
@@ -3488,7 +3488,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Centro Norte · Corte 30/08/2026 13:47</t>
+          <t>Centro Norte · Corte 30/08/2026 14:58</t>
         </is>
       </c>
     </row>
@@ -3534,10 +3534,10 @@
         </is>
       </c>
       <c r="C5" s="11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E5" s="13">
         <f>IFERROR(C5/(C5+D5),0)</f>
@@ -3759,10 +3759,10 @@
         </is>
       </c>
       <c r="C14" s="7" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E14" s="9">
         <f>IFERROR(C14/(C14+D14),0)</f>

--- a/exports/Resumen_Evidencias_OPS.xlsx
+++ b/exports/Resumen_Evidencias_OPS.xlsx
@@ -577,7 +577,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Centro Norte · Corte 30/08/2026 14:58</t>
+          <t>Centro Norte · Corte 30/08/2026 16:21</t>
         </is>
       </c>
     </row>
@@ -600,10 +600,10 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>679</v>
+        <v>670</v>
       </c>
       <c r="E6" s="5">
         <f>IFERROR(A6/(A6+C6),0)</f>
@@ -661,10 +661,10 @@
         <v>10</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F10" s="9">
         <f>IFERROR(D10/(D10+E10),0)</f>
@@ -710,17 +710,17 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Garcia</t>
+          <t>Vanessa Carreño</t>
         </is>
       </c>
       <c r="C12" s="7" t="n">
         <v>13</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E12" s="8" t="n">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="F12" s="9">
         <f>IFERROR(D12/(D12+E12),0)</f>
@@ -738,17 +738,17 @@
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño</t>
+          <t>Yazmin Garcia</t>
         </is>
       </c>
       <c r="C13" s="11" t="n">
         <v>13</v>
       </c>
       <c r="D13" s="11" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E13" s="12" t="n">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="F13" s="13">
         <f>IFERROR(D13/(D13+E13),0)</f>
@@ -873,7 +873,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Centro Norte · Corte 30/08/2026 14:58</t>
+          <t>Centro Norte · Corte 30/08/2026 16:21</t>
         </is>
       </c>
     </row>
@@ -1100,24 +1100,24 @@
       </c>
       <c r="B10" s="16" t="inlineStr">
         <is>
-          <t>43194</t>
+          <t>38333</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>Atana Lindavista</t>
+          <t>Izcalli Mega</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E10" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G10" s="9">
         <f>IFERROR(E10/(E10+F10),0)</f>
@@ -1135,24 +1135,24 @@
       </c>
       <c r="B11" s="14" t="inlineStr">
         <is>
-          <t>38149</t>
+          <t>38368</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>Bellavista</t>
+          <t>Luna Park</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E11" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G11" s="13">
         <f>IFERROR(E11/(E11+F11),0)</f>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="B12" s="16" t="inlineStr">
         <is>
-          <t>38527</t>
+          <t>43194</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Camarones</t>
+          <t>Atana Lindavista</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
@@ -1205,12 +1205,12 @@
       </c>
       <c r="B13" s="14" t="inlineStr">
         <is>
-          <t>38394</t>
+          <t>38149</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>Centro Comercial Lomas Verdes</t>
+          <t>Bellavista</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
@@ -1240,17 +1240,17 @@
       </c>
       <c r="B14" s="16" t="inlineStr">
         <is>
-          <t>38535</t>
+          <t>38527</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>City Center Esmeralda</t>
+          <t>Camarones</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E14" s="7" t="n">
@@ -1275,17 +1275,17 @@
       </c>
       <c r="B15" s="14" t="inlineStr">
         <is>
-          <t>38604</t>
+          <t>38394</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>Cosmopol</t>
+          <t>Centro Comercial Lomas Verdes</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E15" s="11" t="n">
@@ -1310,17 +1310,17 @@
       </c>
       <c r="B16" s="16" t="inlineStr">
         <is>
-          <t>38197</t>
+          <t>38535</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>Echegaray</t>
+          <t>City Center Esmeralda</t>
         </is>
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E16" s="7" t="n">
@@ -1345,17 +1345,17 @@
       </c>
       <c r="B17" s="14" t="inlineStr">
         <is>
-          <t>38363</t>
+          <t>38604</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>Galerias Atizapan</t>
+          <t>Cosmopol</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E17" s="11" t="n">
@@ -1380,17 +1380,17 @@
       </c>
       <c r="B18" s="16" t="inlineStr">
         <is>
-          <t>38333</t>
+          <t>38197</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>Izcalli Mega</t>
+          <t>Echegaray</t>
         </is>
       </c>
       <c r="D18" s="8" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E18" s="7" t="n">
@@ -1415,17 +1415,17 @@
       </c>
       <c r="B19" s="14" t="inlineStr">
         <is>
-          <t>38661</t>
+          <t>38363</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>Jinetes</t>
+          <t>Galerias Atizapan</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E19" s="11" t="n">
@@ -1450,17 +1450,17 @@
       </c>
       <c r="B20" s="16" t="inlineStr">
         <is>
-          <t>38368</t>
+          <t>38661</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>Luna Park</t>
+          <t>Jinetes</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E20" s="7" t="n">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="B21" s="14" t="inlineStr">
         <is>
-          <t>43195</t>
+          <t>38205</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>Parque Jadin kiosko</t>
+          <t>Lindavista</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
@@ -1520,17 +1520,17 @@
       </c>
       <c r="B22" s="16" t="inlineStr">
         <is>
-          <t>38937</t>
+          <t>38119</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>Parque Tepeyac Piso 1</t>
+          <t>Lomas Verdes</t>
         </is>
       </c>
       <c r="D22" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E22" s="7" t="n">
@@ -1555,17 +1555,17 @@
       </c>
       <c r="B23" s="14" t="inlineStr">
         <is>
-          <t>38590</t>
+          <t>43111</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>Parque Toreo II</t>
+          <t>Montevideo Insurgentes</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E23" s="11" t="n">
@@ -1590,12 +1590,12 @@
       </c>
       <c r="B24" s="16" t="inlineStr">
         <is>
-          <t>43132</t>
+          <t>43195</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>Plaza Vista Norte</t>
+          <t>Parque Jadin kiosko</t>
         </is>
       </c>
       <c r="D24" s="8" t="inlineStr">
@@ -1625,17 +1625,17 @@
       </c>
       <c r="B25" s="14" t="inlineStr">
         <is>
-          <t>38456</t>
+          <t>38937</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>Plaza las Flores</t>
+          <t>Parque Tepeyac Piso 1</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E25" s="11" t="n">
@@ -1660,17 +1660,17 @@
       </c>
       <c r="B26" s="16" t="inlineStr">
         <is>
-          <t>38266</t>
+          <t>38590</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>San Mateo</t>
+          <t>Parque Toreo II</t>
         </is>
       </c>
       <c r="D26" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E26" s="7" t="n">
@@ -1695,17 +1695,17 @@
       </c>
       <c r="B27" s="14" t="inlineStr">
         <is>
-          <t>38117</t>
+          <t>38546</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>Satelite</t>
+          <t>Patio Claveria</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E27" s="11" t="n">
@@ -1730,17 +1730,17 @@
       </c>
       <c r="B28" s="16" t="inlineStr">
         <is>
-          <t>38475</t>
+          <t>38677</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>Satelite Centro Civico</t>
+          <t>Patio la Raza</t>
         </is>
       </c>
       <c r="D28" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E28" s="7" t="n">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="B29" s="14" t="inlineStr">
         <is>
-          <t>38925</t>
+          <t>43132</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>Star Medica Lomas Verdes</t>
+          <t>Plaza Vista Norte</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E29" s="11" t="n">
@@ -1800,17 +1800,17 @@
       </c>
       <c r="B30" s="16" t="inlineStr">
         <is>
-          <t>38656</t>
+          <t>38456</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>Viveros de la Loma</t>
+          <t>Plaza las Flores</t>
         </is>
       </c>
       <c r="D30" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E30" s="7" t="n">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="B31" s="14" t="inlineStr">
         <is>
-          <t>38142</t>
+          <t>38266</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>Zona Esmeralda</t>
+          <t>San Mateo</t>
         </is>
       </c>
       <c r="D31" s="12" t="inlineStr">
@@ -1870,24 +1870,24 @@
       </c>
       <c r="B32" s="16" t="inlineStr">
         <is>
-          <t>38186</t>
+          <t>38117</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>Arboledas</t>
+          <t>Satelite</t>
         </is>
       </c>
       <c r="D32" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E32" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F32" s="7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G32" s="9">
         <f>IFERROR(E32/(E32+F32),0)</f>
@@ -1905,24 +1905,24 @@
       </c>
       <c r="B33" s="14" t="inlineStr">
         <is>
-          <t>43043</t>
+          <t>38475</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>Atizapan</t>
+          <t>Satelite Centro Civico</t>
         </is>
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E33" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G33" s="13">
         <f>IFERROR(E33/(E33+F33),0)</f>
@@ -1940,24 +1940,24 @@
       </c>
       <c r="B34" s="16" t="inlineStr">
         <is>
-          <t>38930</t>
+          <t>38925</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>Blvd. Aeropuerto dt</t>
+          <t>Star Medica Lomas Verdes</t>
         </is>
       </c>
       <c r="D34" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E34" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F34" s="7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G34" s="9">
         <f>IFERROR(E34/(E34+F34),0)</f>
@@ -1975,24 +1975,24 @@
       </c>
       <c r="B35" s="14" t="inlineStr">
         <is>
-          <t>38529</t>
+          <t>38411</t>
         </is>
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>Bosques de Aragon</t>
+          <t>Torres Lindavista</t>
         </is>
       </c>
       <c r="D35" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E35" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G35" s="13">
         <f>IFERROR(E35/(E35+F35),0)</f>
@@ -2010,12 +2010,12 @@
       </c>
       <c r="B36" s="16" t="inlineStr">
         <is>
-          <t>38837</t>
+          <t>38651</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>Centenario Azcapotzalco</t>
+          <t>Via Vallejo</t>
         </is>
       </c>
       <c r="D36" s="8" t="inlineStr">
@@ -2024,10 +2024,10 @@
         </is>
       </c>
       <c r="E36" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F36" s="7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G36" s="9">
         <f>IFERROR(E36/(E36+F36),0)</f>
@@ -2045,24 +2045,24 @@
       </c>
       <c r="B37" s="14" t="inlineStr">
         <is>
-          <t>38401</t>
+          <t>38656</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>Coacalco</t>
+          <t>Viveros de la Loma</t>
         </is>
       </c>
       <c r="D37" s="12" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E37" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G37" s="13">
         <f>IFERROR(E37/(E37+F37),0)</f>
@@ -2080,21 +2080,21 @@
       </c>
       <c r="B38" s="16" t="inlineStr">
         <is>
-          <t>43193</t>
+          <t>38142</t>
         </is>
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>Cosmopol N1</t>
+          <t>Zona Esmeralda</t>
         </is>
       </c>
       <c r="D38" s="8" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E38" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F38" s="7" t="n">
         <v>9</v>
@@ -2115,17 +2115,17 @@
       </c>
       <c r="B39" s="14" t="inlineStr">
         <is>
-          <t>38431</t>
+          <t>38186</t>
         </is>
       </c>
       <c r="C39" s="12" t="inlineStr">
         <is>
-          <t>Eduardo Molina</t>
+          <t>Arboledas</t>
         </is>
       </c>
       <c r="D39" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E39" s="11" t="n">
@@ -2150,17 +2150,17 @@
       </c>
       <c r="B40" s="16" t="inlineStr">
         <is>
-          <t>38458</t>
+          <t>43043</t>
         </is>
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>El Rosario</t>
+          <t>Atizapan</t>
         </is>
       </c>
       <c r="D40" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E40" s="7" t="n">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="B41" s="14" t="inlineStr">
         <is>
-          <t>38903</t>
+          <t>38930</t>
         </is>
       </c>
       <c r="C41" s="12" t="inlineStr">
         <is>
-          <t>Encuentro Oceania</t>
+          <t>Blvd. Aeropuerto dt</t>
         </is>
       </c>
       <c r="D41" s="12" t="inlineStr">
@@ -2220,12 +2220,12 @@
       </c>
       <c r="B42" s="16" t="inlineStr">
         <is>
-          <t>38995</t>
+          <t>38529</t>
         </is>
       </c>
       <c r="C42" s="8" t="inlineStr">
         <is>
-          <t>Encuentro Oceania II</t>
+          <t>Bosques de Aragon</t>
         </is>
       </c>
       <c r="D42" s="8" t="inlineStr">
@@ -2255,17 +2255,17 @@
       </c>
       <c r="B43" s="14" t="inlineStr">
         <is>
-          <t>38507</t>
+          <t>38837</t>
         </is>
       </c>
       <c r="C43" s="12" t="inlineStr">
         <is>
-          <t>Espacio Vista del Valle</t>
+          <t>Centenario Azcapotzalco</t>
         </is>
       </c>
       <c r="D43" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E43" s="11" t="n">
@@ -2290,17 +2290,17 @@
       </c>
       <c r="B44" s="16" t="inlineStr">
         <is>
-          <t>38770</t>
+          <t>38401</t>
         </is>
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t>Gustavo Baz 29</t>
+          <t>Coacalco</t>
         </is>
       </c>
       <c r="D44" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E44" s="7" t="n">
@@ -2325,24 +2325,24 @@
       </c>
       <c r="B45" s="14" t="inlineStr">
         <is>
-          <t>38230</t>
+          <t>43193</t>
         </is>
       </c>
       <c r="C45" s="12" t="inlineStr">
         <is>
-          <t>ITEMS Edo de Mexico</t>
+          <t>Cosmopol N1</t>
         </is>
       </c>
       <c r="D45" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E45" s="11" t="n">
         <v>0</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G45" s="13">
         <f>IFERROR(E45/(E45+F45),0)</f>
@@ -2360,17 +2360,17 @@
       </c>
       <c r="B46" s="16" t="inlineStr">
         <is>
-          <t>38205</t>
+          <t>38431</t>
         </is>
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t>Lindavista</t>
+          <t>Eduardo Molina</t>
         </is>
       </c>
       <c r="D46" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E46" s="7" t="n">
@@ -2395,17 +2395,17 @@
       </c>
       <c r="B47" s="14" t="inlineStr">
         <is>
-          <t>38207</t>
+          <t>38458</t>
         </is>
       </c>
       <c r="C47" s="12" t="inlineStr">
         <is>
-          <t>Lindavista II</t>
+          <t>El Rosario</t>
         </is>
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E47" s="11" t="n">
@@ -2430,17 +2430,17 @@
       </c>
       <c r="B48" s="16" t="inlineStr">
         <is>
-          <t>38119</t>
+          <t>38903</t>
         </is>
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
-          <t>Lomas Verdes</t>
+          <t>Encuentro Oceania</t>
         </is>
       </c>
       <c r="D48" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E48" s="7" t="n">
@@ -2465,17 +2465,17 @@
       </c>
       <c r="B49" s="14" t="inlineStr">
         <is>
-          <t>38270</t>
+          <t>38995</t>
         </is>
       </c>
       <c r="C49" s="12" t="inlineStr">
         <is>
-          <t>Lomas Verdes II</t>
+          <t>Encuentro Oceania II</t>
         </is>
       </c>
       <c r="D49" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E49" s="11" t="n">
@@ -2500,17 +2500,17 @@
       </c>
       <c r="B50" s="16" t="inlineStr">
         <is>
-          <t>38371</t>
+          <t>38507</t>
         </is>
       </c>
       <c r="C50" s="8" t="inlineStr">
         <is>
-          <t>Montevideo DT</t>
+          <t>Espacio Vista del Valle</t>
         </is>
       </c>
       <c r="D50" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E50" s="7" t="n">
@@ -2535,17 +2535,17 @@
       </c>
       <c r="B51" s="14" t="inlineStr">
         <is>
-          <t>43111</t>
+          <t>38770</t>
         </is>
       </c>
       <c r="C51" s="12" t="inlineStr">
         <is>
-          <t>Montevideo Insurgentes</t>
+          <t>Gustavo Baz 29</t>
         </is>
       </c>
       <c r="D51" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E51" s="11" t="n">
@@ -2570,12 +2570,12 @@
       </c>
       <c r="B52" s="16" t="inlineStr">
         <is>
-          <t>38674</t>
+          <t>38230</t>
         </is>
       </c>
       <c r="C52" s="8" t="inlineStr">
         <is>
-          <t>Mundo E</t>
+          <t>ITEMS Edo de Mexico</t>
         </is>
       </c>
       <c r="D52" s="8" t="inlineStr">
@@ -2605,17 +2605,17 @@
       </c>
       <c r="B53" s="14" t="inlineStr">
         <is>
-          <t>38845</t>
+          <t>38207</t>
         </is>
       </c>
       <c r="C53" s="12" t="inlineStr">
         <is>
-          <t>Mundo E II</t>
+          <t>Lindavista II</t>
         </is>
       </c>
       <c r="D53" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E53" s="11" t="n">
@@ -2640,17 +2640,17 @@
       </c>
       <c r="B54" s="16" t="inlineStr">
         <is>
-          <t>38965</t>
+          <t>38270</t>
         </is>
       </c>
       <c r="C54" s="8" t="inlineStr">
         <is>
-          <t>Parque Tepeyac Piso 2</t>
+          <t>Lomas Verdes II</t>
         </is>
       </c>
       <c r="D54" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E54" s="7" t="n">
@@ -2675,17 +2675,17 @@
       </c>
       <c r="B55" s="14" t="inlineStr">
         <is>
-          <t>38792</t>
+          <t>38371</t>
         </is>
       </c>
       <c r="C55" s="12" t="inlineStr">
         <is>
-          <t>Pasaje Tlanepantla</t>
+          <t>Montevideo DT</t>
         </is>
       </c>
       <c r="D55" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E55" s="11" t="n">
@@ -2710,17 +2710,17 @@
       </c>
       <c r="B56" s="16" t="inlineStr">
         <is>
-          <t>38546</t>
+          <t>38674</t>
         </is>
       </c>
       <c r="C56" s="8" t="inlineStr">
         <is>
-          <t>Patio Claveria</t>
+          <t>Mundo E</t>
         </is>
       </c>
       <c r="D56" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E56" s="7" t="n">
@@ -2745,17 +2745,17 @@
       </c>
       <c r="B57" s="14" t="inlineStr">
         <is>
-          <t>38515</t>
+          <t>38845</t>
         </is>
       </c>
       <c r="C57" s="12" t="inlineStr">
         <is>
-          <t>Patio Ecatepec</t>
+          <t>Mundo E II</t>
         </is>
       </c>
       <c r="D57" s="12" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E57" s="11" t="n">
@@ -2780,17 +2780,17 @@
       </c>
       <c r="B58" s="16" t="inlineStr">
         <is>
-          <t>38677</t>
+          <t>38965</t>
         </is>
       </c>
       <c r="C58" s="8" t="inlineStr">
         <is>
-          <t>Patio la Raza</t>
+          <t>Parque Tepeyac Piso 2</t>
         </is>
       </c>
       <c r="D58" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E58" s="7" t="n">
@@ -2815,17 +2815,17 @@
       </c>
       <c r="B59" s="14" t="inlineStr">
         <is>
-          <t>38176</t>
+          <t>38792</t>
         </is>
       </c>
       <c r="C59" s="12" t="inlineStr">
         <is>
-          <t>Periferico Satélite DT</t>
+          <t>Pasaje Tlanepantla</t>
         </is>
       </c>
       <c r="D59" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E59" s="11" t="n">
@@ -2850,17 +2850,17 @@
       </c>
       <c r="B60" s="16" t="inlineStr">
         <is>
-          <t>38924</t>
+          <t>38515</t>
         </is>
       </c>
       <c r="C60" s="8" t="inlineStr">
         <is>
-          <t>Plaza Aeropuerto</t>
+          <t>Patio Ecatepec</t>
         </is>
       </c>
       <c r="D60" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E60" s="7" t="n">
@@ -2885,17 +2885,17 @@
       </c>
       <c r="B61" s="14" t="inlineStr">
         <is>
-          <t>38719</t>
+          <t>38176</t>
         </is>
       </c>
       <c r="C61" s="12" t="inlineStr">
         <is>
-          <t>Plaza Fortuna</t>
+          <t>Periferico Satélite DT</t>
         </is>
       </c>
       <c r="D61" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E61" s="11" t="n">
@@ -2920,17 +2920,17 @@
       </c>
       <c r="B62" s="16" t="inlineStr">
         <is>
-          <t>38427</t>
+          <t>38924</t>
         </is>
       </c>
       <c r="C62" s="8" t="inlineStr">
         <is>
-          <t>Plaza Satelite</t>
+          <t>Plaza Aeropuerto</t>
         </is>
       </c>
       <c r="D62" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E62" s="7" t="n">
@@ -2955,17 +2955,17 @@
       </c>
       <c r="B63" s="14" t="inlineStr">
         <is>
-          <t>38859</t>
+          <t>38719</t>
         </is>
       </c>
       <c r="C63" s="12" t="inlineStr">
         <is>
-          <t>Plaza Satelite II N1</t>
+          <t>Plaza Fortuna</t>
         </is>
       </c>
       <c r="D63" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E63" s="11" t="n">
@@ -2990,17 +2990,17 @@
       </c>
       <c r="B64" s="16" t="inlineStr">
         <is>
-          <t>38811</t>
+          <t>38427</t>
         </is>
       </c>
       <c r="C64" s="8" t="inlineStr">
         <is>
-          <t>Plaza Tepeyac</t>
+          <t>Plaza Satelite</t>
         </is>
       </c>
       <c r="D64" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E64" s="7" t="n">
@@ -3025,17 +3025,17 @@
       </c>
       <c r="B65" s="14" t="inlineStr">
         <is>
-          <t>38136</t>
+          <t>38859</t>
         </is>
       </c>
       <c r="C65" s="12" t="inlineStr">
         <is>
-          <t>Punta Norte</t>
+          <t>Plaza Satelite II N1</t>
         </is>
       </c>
       <c r="D65" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E65" s="11" t="n">
@@ -3060,17 +3060,17 @@
       </c>
       <c r="B66" s="16" t="inlineStr">
         <is>
-          <t>43152</t>
+          <t>38811</t>
         </is>
       </c>
       <c r="C66" s="8" t="inlineStr">
         <is>
-          <t>Samara Satélite</t>
+          <t>Plaza Tepeyac</t>
         </is>
       </c>
       <c r="D66" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E66" s="7" t="n">
@@ -3095,12 +3095,12 @@
       </c>
       <c r="B67" s="14" t="inlineStr">
         <is>
-          <t>38460</t>
+          <t>38136</t>
         </is>
       </c>
       <c r="C67" s="12" t="inlineStr">
         <is>
-          <t>Santa Monica</t>
+          <t>Punta Norte</t>
         </is>
       </c>
       <c r="D67" s="12" t="inlineStr">
@@ -3130,17 +3130,17 @@
       </c>
       <c r="B68" s="16" t="inlineStr">
         <is>
-          <t>38442</t>
+          <t>43152</t>
         </is>
       </c>
       <c r="C68" s="8" t="inlineStr">
         <is>
-          <t>Sor Juana</t>
+          <t>Samara Satélite</t>
         </is>
       </c>
       <c r="D68" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E68" s="7" t="n">
@@ -3165,17 +3165,17 @@
       </c>
       <c r="B69" s="14" t="inlineStr">
         <is>
-          <t>38992</t>
+          <t>38460</t>
         </is>
       </c>
       <c r="C69" s="12" t="inlineStr">
         <is>
-          <t>Tapo Puerta Oriente</t>
+          <t>Santa Monica</t>
         </is>
       </c>
       <c r="D69" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E69" s="11" t="n">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="B70" s="16" t="inlineStr">
         <is>
-          <t>38606</t>
+          <t>38442</t>
         </is>
       </c>
       <c r="C70" s="8" t="inlineStr">
         <is>
-          <t>TlalnepantlaCarso</t>
+          <t>Sor Juana</t>
         </is>
       </c>
       <c r="D70" s="8" t="inlineStr">
@@ -3235,17 +3235,17 @@
       </c>
       <c r="B71" s="14" t="inlineStr">
         <is>
-          <t>38411</t>
+          <t>38992</t>
         </is>
       </c>
       <c r="C71" s="12" t="inlineStr">
         <is>
-          <t>Torres Lindavista</t>
+          <t>Tapo Puerta Oriente</t>
         </is>
       </c>
       <c r="D71" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E71" s="11" t="n">
@@ -3270,17 +3270,17 @@
       </c>
       <c r="B72" s="16" t="inlineStr">
         <is>
-          <t>43130</t>
+          <t>38606</t>
         </is>
       </c>
       <c r="C72" s="8" t="inlineStr">
         <is>
-          <t>Town Center Nicolás Romero</t>
+          <t>TlalnepantlaCarso</t>
         </is>
       </c>
       <c r="D72" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E72" s="7" t="n">
@@ -3305,17 +3305,17 @@
       </c>
       <c r="B73" s="14" t="inlineStr">
         <is>
-          <t>38374</t>
+          <t>43130</t>
         </is>
       </c>
       <c r="C73" s="12" t="inlineStr">
         <is>
-          <t>Valle Dorado</t>
+          <t>Town Center Nicolás Romero</t>
         </is>
       </c>
       <c r="D73" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E73" s="11" t="n">
@@ -3340,17 +3340,17 @@
       </c>
       <c r="B74" s="16" t="inlineStr">
         <is>
-          <t>38651</t>
+          <t>38374</t>
         </is>
       </c>
       <c r="C74" s="8" t="inlineStr">
         <is>
-          <t>Via Vallejo</t>
+          <t>Valle Dorado</t>
         </is>
       </c>
       <c r="D74" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E74" s="7" t="n">
@@ -3488,7 +3488,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Centro Norte · Corte 30/08/2026 14:58</t>
+          <t>Centro Norte · Corte 30/08/2026 16:21</t>
         </is>
       </c>
     </row>
@@ -3584,10 +3584,10 @@
         </is>
       </c>
       <c r="C7" s="11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E7" s="13">
         <f>IFERROR(C7/(C7+D7),0)</f>
@@ -3759,10 +3759,10 @@
         </is>
       </c>
       <c r="C14" s="7" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="E14" s="9">
         <f>IFERROR(C14/(C14+D14),0)</f>

--- a/exports/Resumen_Evidencias_OPS.xlsx
+++ b/exports/Resumen_Evidencias_OPS.xlsx
@@ -577,7 +577,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Centro Norte · Corte 30/08/2026 16:21</t>
+          <t>Centro Norte · Corte 30/08/2026 16:26</t>
         </is>
       </c>
     </row>
@@ -873,7 +873,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Centro Norte · Corte 30/08/2026 16:21</t>
+          <t>Centro Norte · Corte 30/08/2026 16:26</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Centro Norte · Corte 30/08/2026 16:21</t>
+          <t>Centro Norte · Corte 30/08/2026 16:26</t>
         </is>
       </c>
     </row>

--- a/exports/Resumen_Evidencias_OPS.xlsx
+++ b/exports/Resumen_Evidencias_OPS.xlsx
@@ -577,7 +577,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Centro Norte · Corte 30/08/2026 16:26</t>
+          <t>Centro Norte · Corte 30/08/2026 16:36</t>
         </is>
       </c>
     </row>
@@ -600,10 +600,10 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="E6" s="5">
         <f>IFERROR(A6/(A6+C6),0)</f>
@@ -766,17 +766,17 @@
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia</t>
+          <t>Nancy Carolina</t>
         </is>
       </c>
       <c r="C14" s="7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E14" s="8" t="n">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="F14" s="9">
         <f>IFERROR(D14/(D14+E14),0)</f>
@@ -794,17 +794,17 @@
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina</t>
+          <t>Veronica Garcia</t>
         </is>
       </c>
       <c r="C15" s="11" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D15" s="11" t="n">
         <v>1</v>
       </c>
       <c r="E15" s="12" t="n">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="F15" s="13">
         <f>IFERROR(D15/(D15+E15),0)</f>
@@ -873,7 +873,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Centro Norte · Corte 30/08/2026 16:26</t>
+          <t>Centro Norte · Corte 30/08/2026 16:36</t>
         </is>
       </c>
     </row>
@@ -1975,17 +1975,17 @@
       </c>
       <c r="B35" s="14" t="inlineStr">
         <is>
-          <t>38411</t>
+          <t>38606</t>
         </is>
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>Torres Lindavista</t>
+          <t>TlalnepantlaCarso</t>
         </is>
       </c>
       <c r="D35" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E35" s="11" t="n">
@@ -2010,12 +2010,12 @@
       </c>
       <c r="B36" s="16" t="inlineStr">
         <is>
-          <t>38651</t>
+          <t>38411</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>Via Vallejo</t>
+          <t>Torres Lindavista</t>
         </is>
       </c>
       <c r="D36" s="8" t="inlineStr">
@@ -2045,17 +2045,17 @@
       </c>
       <c r="B37" s="14" t="inlineStr">
         <is>
-          <t>38656</t>
+          <t>38651</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>Viveros de la Loma</t>
+          <t>Via Vallejo</t>
         </is>
       </c>
       <c r="D37" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E37" s="11" t="n">
@@ -2080,17 +2080,17 @@
       </c>
       <c r="B38" s="16" t="inlineStr">
         <is>
-          <t>38142</t>
+          <t>38656</t>
         </is>
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>Zona Esmeralda</t>
+          <t>Viveros de la Loma</t>
         </is>
       </c>
       <c r="D38" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E38" s="7" t="n">
@@ -2115,24 +2115,24 @@
       </c>
       <c r="B39" s="14" t="inlineStr">
         <is>
-          <t>38186</t>
+          <t>38142</t>
         </is>
       </c>
       <c r="C39" s="12" t="inlineStr">
         <is>
-          <t>Arboledas</t>
+          <t>Zona Esmeralda</t>
         </is>
       </c>
       <c r="D39" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E39" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G39" s="13">
         <f>IFERROR(E39/(E39+F39),0)</f>
@@ -2150,17 +2150,17 @@
       </c>
       <c r="B40" s="16" t="inlineStr">
         <is>
-          <t>43043</t>
+          <t>38186</t>
         </is>
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>Atizapan</t>
+          <t>Arboledas</t>
         </is>
       </c>
       <c r="D40" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E40" s="7" t="n">
@@ -2185,17 +2185,17 @@
       </c>
       <c r="B41" s="14" t="inlineStr">
         <is>
-          <t>38930</t>
+          <t>43043</t>
         </is>
       </c>
       <c r="C41" s="12" t="inlineStr">
         <is>
-          <t>Blvd. Aeropuerto dt</t>
+          <t>Atizapan</t>
         </is>
       </c>
       <c r="D41" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E41" s="11" t="n">
@@ -2220,12 +2220,12 @@
       </c>
       <c r="B42" s="16" t="inlineStr">
         <is>
-          <t>38529</t>
+          <t>38930</t>
         </is>
       </c>
       <c r="C42" s="8" t="inlineStr">
         <is>
-          <t>Bosques de Aragon</t>
+          <t>Blvd. Aeropuerto dt</t>
         </is>
       </c>
       <c r="D42" s="8" t="inlineStr">
@@ -2255,17 +2255,17 @@
       </c>
       <c r="B43" s="14" t="inlineStr">
         <is>
-          <t>38837</t>
+          <t>38529</t>
         </is>
       </c>
       <c r="C43" s="12" t="inlineStr">
         <is>
-          <t>Centenario Azcapotzalco</t>
+          <t>Bosques de Aragon</t>
         </is>
       </c>
       <c r="D43" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E43" s="11" t="n">
@@ -2290,17 +2290,17 @@
       </c>
       <c r="B44" s="16" t="inlineStr">
         <is>
-          <t>38401</t>
+          <t>38837</t>
         </is>
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t>Coacalco</t>
+          <t>Centenario Azcapotzalco</t>
         </is>
       </c>
       <c r="D44" s="8" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E44" s="7" t="n">
@@ -2325,12 +2325,12 @@
       </c>
       <c r="B45" s="14" t="inlineStr">
         <is>
-          <t>43193</t>
+          <t>38401</t>
         </is>
       </c>
       <c r="C45" s="12" t="inlineStr">
         <is>
-          <t>Cosmopol N1</t>
+          <t>Coacalco</t>
         </is>
       </c>
       <c r="D45" s="12" t="inlineStr">
@@ -2342,7 +2342,7 @@
         <v>0</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G45" s="13">
         <f>IFERROR(E45/(E45+F45),0)</f>
@@ -2360,24 +2360,24 @@
       </c>
       <c r="B46" s="16" t="inlineStr">
         <is>
-          <t>38431</t>
+          <t>43193</t>
         </is>
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t>Eduardo Molina</t>
+          <t>Cosmopol N1</t>
         </is>
       </c>
       <c r="D46" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E46" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F46" s="7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G46" s="9">
         <f>IFERROR(E46/(E46+F46),0)</f>
@@ -2395,17 +2395,17 @@
       </c>
       <c r="B47" s="14" t="inlineStr">
         <is>
-          <t>38458</t>
+          <t>38431</t>
         </is>
       </c>
       <c r="C47" s="12" t="inlineStr">
         <is>
-          <t>El Rosario</t>
+          <t>Eduardo Molina</t>
         </is>
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E47" s="11" t="n">
@@ -2430,17 +2430,17 @@
       </c>
       <c r="B48" s="16" t="inlineStr">
         <is>
-          <t>38903</t>
+          <t>38458</t>
         </is>
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
-          <t>Encuentro Oceania</t>
+          <t>El Rosario</t>
         </is>
       </c>
       <c r="D48" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E48" s="7" t="n">
@@ -2465,12 +2465,12 @@
       </c>
       <c r="B49" s="14" t="inlineStr">
         <is>
-          <t>38995</t>
+          <t>38903</t>
         </is>
       </c>
       <c r="C49" s="12" t="inlineStr">
         <is>
-          <t>Encuentro Oceania II</t>
+          <t>Encuentro Oceania</t>
         </is>
       </c>
       <c r="D49" s="12" t="inlineStr">
@@ -2500,17 +2500,17 @@
       </c>
       <c r="B50" s="16" t="inlineStr">
         <is>
-          <t>38507</t>
+          <t>38995</t>
         </is>
       </c>
       <c r="C50" s="8" t="inlineStr">
         <is>
-          <t>Espacio Vista del Valle</t>
+          <t>Encuentro Oceania II</t>
         </is>
       </c>
       <c r="D50" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E50" s="7" t="n">
@@ -2535,17 +2535,17 @@
       </c>
       <c r="B51" s="14" t="inlineStr">
         <is>
-          <t>38770</t>
+          <t>38507</t>
         </is>
       </c>
       <c r="C51" s="12" t="inlineStr">
         <is>
-          <t>Gustavo Baz 29</t>
+          <t>Espacio Vista del Valle</t>
         </is>
       </c>
       <c r="D51" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E51" s="11" t="n">
@@ -2570,17 +2570,17 @@
       </c>
       <c r="B52" s="16" t="inlineStr">
         <is>
-          <t>38230</t>
+          <t>38770</t>
         </is>
       </c>
       <c r="C52" s="8" t="inlineStr">
         <is>
-          <t>ITEMS Edo de Mexico</t>
+          <t>Gustavo Baz 29</t>
         </is>
       </c>
       <c r="D52" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E52" s="7" t="n">
@@ -2605,17 +2605,17 @@
       </c>
       <c r="B53" s="14" t="inlineStr">
         <is>
-          <t>38207</t>
+          <t>38230</t>
         </is>
       </c>
       <c r="C53" s="12" t="inlineStr">
         <is>
-          <t>Lindavista II</t>
+          <t>ITEMS Edo de Mexico</t>
         </is>
       </c>
       <c r="D53" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E53" s="11" t="n">
@@ -2640,17 +2640,17 @@
       </c>
       <c r="B54" s="16" t="inlineStr">
         <is>
-          <t>38270</t>
+          <t>38207</t>
         </is>
       </c>
       <c r="C54" s="8" t="inlineStr">
         <is>
-          <t>Lomas Verdes II</t>
+          <t>Lindavista II</t>
         </is>
       </c>
       <c r="D54" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E54" s="7" t="n">
@@ -2675,17 +2675,17 @@
       </c>
       <c r="B55" s="14" t="inlineStr">
         <is>
-          <t>38371</t>
+          <t>38270</t>
         </is>
       </c>
       <c r="C55" s="12" t="inlineStr">
         <is>
-          <t>Montevideo DT</t>
+          <t>Lomas Verdes II</t>
         </is>
       </c>
       <c r="D55" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E55" s="11" t="n">
@@ -2710,17 +2710,17 @@
       </c>
       <c r="B56" s="16" t="inlineStr">
         <is>
-          <t>38674</t>
+          <t>38371</t>
         </is>
       </c>
       <c r="C56" s="8" t="inlineStr">
         <is>
-          <t>Mundo E</t>
+          <t>Montevideo DT</t>
         </is>
       </c>
       <c r="D56" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E56" s="7" t="n">
@@ -2745,12 +2745,12 @@
       </c>
       <c r="B57" s="14" t="inlineStr">
         <is>
-          <t>38845</t>
+          <t>38674</t>
         </is>
       </c>
       <c r="C57" s="12" t="inlineStr">
         <is>
-          <t>Mundo E II</t>
+          <t>Mundo E</t>
         </is>
       </c>
       <c r="D57" s="12" t="inlineStr">
@@ -2780,17 +2780,17 @@
       </c>
       <c r="B58" s="16" t="inlineStr">
         <is>
-          <t>38965</t>
+          <t>38845</t>
         </is>
       </c>
       <c r="C58" s="8" t="inlineStr">
         <is>
-          <t>Parque Tepeyac Piso 2</t>
+          <t>Mundo E II</t>
         </is>
       </c>
       <c r="D58" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E58" s="7" t="n">
@@ -2815,17 +2815,17 @@
       </c>
       <c r="B59" s="14" t="inlineStr">
         <is>
-          <t>38792</t>
+          <t>38965</t>
         </is>
       </c>
       <c r="C59" s="12" t="inlineStr">
         <is>
-          <t>Pasaje Tlanepantla</t>
+          <t>Parque Tepeyac Piso 2</t>
         </is>
       </c>
       <c r="D59" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E59" s="11" t="n">
@@ -2850,17 +2850,17 @@
       </c>
       <c r="B60" s="16" t="inlineStr">
         <is>
-          <t>38515</t>
+          <t>38792</t>
         </is>
       </c>
       <c r="C60" s="8" t="inlineStr">
         <is>
-          <t>Patio Ecatepec</t>
+          <t>Pasaje Tlanepantla</t>
         </is>
       </c>
       <c r="D60" s="8" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E60" s="7" t="n">
@@ -2885,17 +2885,17 @@
       </c>
       <c r="B61" s="14" t="inlineStr">
         <is>
-          <t>38176</t>
+          <t>38515</t>
         </is>
       </c>
       <c r="C61" s="12" t="inlineStr">
         <is>
-          <t>Periferico Satélite DT</t>
+          <t>Patio Ecatepec</t>
         </is>
       </c>
       <c r="D61" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E61" s="11" t="n">
@@ -2920,17 +2920,17 @@
       </c>
       <c r="B62" s="16" t="inlineStr">
         <is>
-          <t>38924</t>
+          <t>38176</t>
         </is>
       </c>
       <c r="C62" s="8" t="inlineStr">
         <is>
-          <t>Plaza Aeropuerto</t>
+          <t>Periferico Satélite DT</t>
         </is>
       </c>
       <c r="D62" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E62" s="7" t="n">
@@ -2955,12 +2955,12 @@
       </c>
       <c r="B63" s="14" t="inlineStr">
         <is>
-          <t>38719</t>
+          <t>38924</t>
         </is>
       </c>
       <c r="C63" s="12" t="inlineStr">
         <is>
-          <t>Plaza Fortuna</t>
+          <t>Plaza Aeropuerto</t>
         </is>
       </c>
       <c r="D63" s="12" t="inlineStr">
@@ -2990,17 +2990,17 @@
       </c>
       <c r="B64" s="16" t="inlineStr">
         <is>
-          <t>38427</t>
+          <t>38719</t>
         </is>
       </c>
       <c r="C64" s="8" t="inlineStr">
         <is>
-          <t>Plaza Satelite</t>
+          <t>Plaza Fortuna</t>
         </is>
       </c>
       <c r="D64" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E64" s="7" t="n">
@@ -3025,12 +3025,12 @@
       </c>
       <c r="B65" s="14" t="inlineStr">
         <is>
-          <t>38859</t>
+          <t>38427</t>
         </is>
       </c>
       <c r="C65" s="12" t="inlineStr">
         <is>
-          <t>Plaza Satelite II N1</t>
+          <t>Plaza Satelite</t>
         </is>
       </c>
       <c r="D65" s="12" t="inlineStr">
@@ -3060,17 +3060,17 @@
       </c>
       <c r="B66" s="16" t="inlineStr">
         <is>
-          <t>38811</t>
+          <t>38859</t>
         </is>
       </c>
       <c r="C66" s="8" t="inlineStr">
         <is>
-          <t>Plaza Tepeyac</t>
+          <t>Plaza Satelite II N1</t>
         </is>
       </c>
       <c r="D66" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E66" s="7" t="n">
@@ -3095,17 +3095,17 @@
       </c>
       <c r="B67" s="14" t="inlineStr">
         <is>
-          <t>38136</t>
+          <t>38811</t>
         </is>
       </c>
       <c r="C67" s="12" t="inlineStr">
         <is>
-          <t>Punta Norte</t>
+          <t>Plaza Tepeyac</t>
         </is>
       </c>
       <c r="D67" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E67" s="11" t="n">
@@ -3130,17 +3130,17 @@
       </c>
       <c r="B68" s="16" t="inlineStr">
         <is>
-          <t>43152</t>
+          <t>38136</t>
         </is>
       </c>
       <c r="C68" s="8" t="inlineStr">
         <is>
-          <t>Samara Satélite</t>
+          <t>Punta Norte</t>
         </is>
       </c>
       <c r="D68" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E68" s="7" t="n">
@@ -3165,17 +3165,17 @@
       </c>
       <c r="B69" s="14" t="inlineStr">
         <is>
-          <t>38460</t>
+          <t>43152</t>
         </is>
       </c>
       <c r="C69" s="12" t="inlineStr">
         <is>
-          <t>Santa Monica</t>
+          <t>Samara Satélite</t>
         </is>
       </c>
       <c r="D69" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E69" s="11" t="n">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="B70" s="16" t="inlineStr">
         <is>
-          <t>38442</t>
+          <t>38460</t>
         </is>
       </c>
       <c r="C70" s="8" t="inlineStr">
         <is>
-          <t>Sor Juana</t>
+          <t>Santa Monica</t>
         </is>
       </c>
       <c r="D70" s="8" t="inlineStr">
@@ -3235,17 +3235,17 @@
       </c>
       <c r="B71" s="14" t="inlineStr">
         <is>
-          <t>38992</t>
+          <t>38442</t>
         </is>
       </c>
       <c r="C71" s="12" t="inlineStr">
         <is>
-          <t>Tapo Puerta Oriente</t>
+          <t>Sor Juana</t>
         </is>
       </c>
       <c r="D71" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E71" s="11" t="n">
@@ -3270,17 +3270,17 @@
       </c>
       <c r="B72" s="16" t="inlineStr">
         <is>
-          <t>38606</t>
+          <t>38992</t>
         </is>
       </c>
       <c r="C72" s="8" t="inlineStr">
         <is>
-          <t>TlalnepantlaCarso</t>
+          <t>Tapo Puerta Oriente</t>
         </is>
       </c>
       <c r="D72" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E72" s="7" t="n">
@@ -3488,7 +3488,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Centro Norte · Corte 30/08/2026 16:26</t>
+          <t>Centro Norte · Corte 30/08/2026 16:36</t>
         </is>
       </c>
     </row>
@@ -3534,10 +3534,10 @@
         </is>
       </c>
       <c r="C5" s="11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E5" s="13">
         <f>IFERROR(C5/(C5+D5),0)</f>

--- a/exports/Resumen_Evidencias_OPS.xlsx
+++ b/exports/Resumen_Evidencias_OPS.xlsx
@@ -577,7 +577,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Centro Norte · Corte 30/08/2026 16:36</t>
+          <t>Centro Norte · Corte 30/08/2026 16:39</t>
         </is>
       </c>
     </row>
@@ -600,10 +600,10 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>669</v>
+        <v>666</v>
       </c>
       <c r="E6" s="5">
         <f>IFERROR(A6/(A6+C6),0)</f>
@@ -689,10 +689,10 @@
         <v>13</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E11" s="12" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F11" s="13">
         <f>IFERROR(D11/(D11+E11),0)</f>
@@ -773,10 +773,10 @@
         <v>12</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E14" s="8" t="n">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F14" s="9">
         <f>IFERROR(D14/(D14+E14),0)</f>
@@ -801,10 +801,10 @@
         <v>11</v>
       </c>
       <c r="D15" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E15" s="12" t="n">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F15" s="13">
         <f>IFERROR(D15/(D15+E15),0)</f>
@@ -873,7 +873,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Centro Norte · Corte 30/08/2026 16:36</t>
+          <t>Centro Norte · Corte 30/08/2026 16:39</t>
         </is>
       </c>
     </row>
@@ -1170,24 +1170,24 @@
       </c>
       <c r="B12" s="16" t="inlineStr">
         <is>
-          <t>43194</t>
+          <t>38606</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Atana Lindavista</t>
+          <t>TlalnepantlaCarso</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E12" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F12" s="7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G12" s="9">
         <f>IFERROR(E12/(E12+F12),0)</f>
@@ -1205,17 +1205,17 @@
       </c>
       <c r="B13" s="14" t="inlineStr">
         <is>
-          <t>38149</t>
+          <t>43194</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>Bellavista</t>
+          <t>Atana Lindavista</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E13" s="11" t="n">
@@ -1240,17 +1240,17 @@
       </c>
       <c r="B14" s="16" t="inlineStr">
         <is>
-          <t>38527</t>
+          <t>38149</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Camarones</t>
+          <t>Bellavista</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E14" s="7" t="n">
@@ -1275,17 +1275,17 @@
       </c>
       <c r="B15" s="14" t="inlineStr">
         <is>
-          <t>38394</t>
+          <t>38527</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>Centro Comercial Lomas Verdes</t>
+          <t>Camarones</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E15" s="11" t="n">
@@ -1310,12 +1310,12 @@
       </c>
       <c r="B16" s="16" t="inlineStr">
         <is>
-          <t>38535</t>
+          <t>38394</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>City Center Esmeralda</t>
+          <t>Centro Comercial Lomas Verdes</t>
         </is>
       </c>
       <c r="D16" s="8" t="inlineStr">
@@ -1345,17 +1345,17 @@
       </c>
       <c r="B17" s="14" t="inlineStr">
         <is>
-          <t>38604</t>
+          <t>38535</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>Cosmopol</t>
+          <t>City Center Esmeralda</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E17" s="11" t="n">
@@ -1380,17 +1380,17 @@
       </c>
       <c r="B18" s="16" t="inlineStr">
         <is>
-          <t>38197</t>
+          <t>38604</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>Echegaray</t>
+          <t>Cosmopol</t>
         </is>
       </c>
       <c r="D18" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E18" s="7" t="n">
@@ -1415,17 +1415,17 @@
       </c>
       <c r="B19" s="14" t="inlineStr">
         <is>
-          <t>38363</t>
+          <t>38197</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>Galerias Atizapan</t>
+          <t>Echegaray</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E19" s="11" t="n">
@@ -1450,17 +1450,17 @@
       </c>
       <c r="B20" s="16" t="inlineStr">
         <is>
-          <t>38661</t>
+          <t>38431</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>Jinetes</t>
+          <t>Eduardo Molina</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E20" s="7" t="n">
@@ -1485,17 +1485,17 @@
       </c>
       <c r="B21" s="14" t="inlineStr">
         <is>
-          <t>38205</t>
+          <t>38363</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>Lindavista</t>
+          <t>Galerias Atizapan</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E21" s="11" t="n">
@@ -1520,17 +1520,17 @@
       </c>
       <c r="B22" s="16" t="inlineStr">
         <is>
-          <t>38119</t>
+          <t>38661</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>Lomas Verdes</t>
+          <t>Jinetes</t>
         </is>
       </c>
       <c r="D22" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E22" s="7" t="n">
@@ -1555,12 +1555,12 @@
       </c>
       <c r="B23" s="14" t="inlineStr">
         <is>
-          <t>43111</t>
+          <t>38205</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>Montevideo Insurgentes</t>
+          <t>Lindavista</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr">
@@ -1590,17 +1590,17 @@
       </c>
       <c r="B24" s="16" t="inlineStr">
         <is>
-          <t>43195</t>
+          <t>38119</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>Parque Jadin kiosko</t>
+          <t>Lomas Verdes</t>
         </is>
       </c>
       <c r="D24" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E24" s="7" t="n">
@@ -1625,17 +1625,17 @@
       </c>
       <c r="B25" s="14" t="inlineStr">
         <is>
-          <t>38937</t>
+          <t>43111</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>Parque Tepeyac Piso 1</t>
+          <t>Montevideo Insurgentes</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E25" s="11" t="n">
@@ -1660,17 +1660,17 @@
       </c>
       <c r="B26" s="16" t="inlineStr">
         <is>
-          <t>38590</t>
+          <t>43195</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>Parque Toreo II</t>
+          <t>Parque Jadin kiosko</t>
         </is>
       </c>
       <c r="D26" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E26" s="7" t="n">
@@ -1695,17 +1695,17 @@
       </c>
       <c r="B27" s="14" t="inlineStr">
         <is>
-          <t>38546</t>
+          <t>38937</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>Patio Claveria</t>
+          <t>Parque Tepeyac Piso 1</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E27" s="11" t="n">
@@ -1730,17 +1730,17 @@
       </c>
       <c r="B28" s="16" t="inlineStr">
         <is>
-          <t>38677</t>
+          <t>38590</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>Patio la Raza</t>
+          <t>Parque Toreo II</t>
         </is>
       </c>
       <c r="D28" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E28" s="7" t="n">
@@ -1765,12 +1765,12 @@
       </c>
       <c r="B29" s="14" t="inlineStr">
         <is>
-          <t>43132</t>
+          <t>38546</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>Plaza Vista Norte</t>
+          <t>Patio Claveria</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr">
@@ -1800,17 +1800,17 @@
       </c>
       <c r="B30" s="16" t="inlineStr">
         <is>
-          <t>38456</t>
+          <t>38677</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>Plaza las Flores</t>
+          <t>Patio la Raza</t>
         </is>
       </c>
       <c r="D30" s="8" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E30" s="7" t="n">
@@ -1835,17 +1835,17 @@
       </c>
       <c r="B31" s="14" t="inlineStr">
         <is>
-          <t>38266</t>
+          <t>43132</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>San Mateo</t>
+          <t>Plaza Vista Norte</t>
         </is>
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E31" s="11" t="n">
@@ -1870,17 +1870,17 @@
       </c>
       <c r="B32" s="16" t="inlineStr">
         <is>
-          <t>38117</t>
+          <t>38456</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>Satelite</t>
+          <t>Plaza las Flores</t>
         </is>
       </c>
       <c r="D32" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E32" s="7" t="n">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="B33" s="14" t="inlineStr">
         <is>
-          <t>38475</t>
+          <t>43152</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>Satelite Centro Civico</t>
+          <t>Samara Satélite</t>
         </is>
       </c>
       <c r="D33" s="12" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="B34" s="16" t="inlineStr">
         <is>
-          <t>38925</t>
+          <t>38266</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>Star Medica Lomas Verdes</t>
+          <t>San Mateo</t>
         </is>
       </c>
       <c r="D34" s="8" t="inlineStr">
@@ -1975,17 +1975,17 @@
       </c>
       <c r="B35" s="14" t="inlineStr">
         <is>
-          <t>38606</t>
+          <t>38117</t>
         </is>
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>TlalnepantlaCarso</t>
+          <t>Satelite</t>
         </is>
       </c>
       <c r="D35" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E35" s="11" t="n">
@@ -2010,17 +2010,17 @@
       </c>
       <c r="B36" s="16" t="inlineStr">
         <is>
-          <t>38411</t>
+          <t>38475</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>Torres Lindavista</t>
+          <t>Satelite Centro Civico</t>
         </is>
       </c>
       <c r="D36" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E36" s="7" t="n">
@@ -2045,17 +2045,17 @@
       </c>
       <c r="B37" s="14" t="inlineStr">
         <is>
-          <t>38651</t>
+          <t>38925</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>Via Vallejo</t>
+          <t>Star Medica Lomas Verdes</t>
         </is>
       </c>
       <c r="D37" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E37" s="11" t="n">
@@ -2080,17 +2080,17 @@
       </c>
       <c r="B38" s="16" t="inlineStr">
         <is>
-          <t>38656</t>
+          <t>38411</t>
         </is>
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>Viveros de la Loma</t>
+          <t>Torres Lindavista</t>
         </is>
       </c>
       <c r="D38" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E38" s="7" t="n">
@@ -2115,17 +2115,17 @@
       </c>
       <c r="B39" s="14" t="inlineStr">
         <is>
-          <t>38142</t>
+          <t>38651</t>
         </is>
       </c>
       <c r="C39" s="12" t="inlineStr">
         <is>
-          <t>Zona Esmeralda</t>
+          <t>Via Vallejo</t>
         </is>
       </c>
       <c r="D39" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E39" s="11" t="n">
@@ -2150,24 +2150,24 @@
       </c>
       <c r="B40" s="16" t="inlineStr">
         <is>
-          <t>38186</t>
+          <t>38656</t>
         </is>
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>Arboledas</t>
+          <t>Viveros de la Loma</t>
         </is>
       </c>
       <c r="D40" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E40" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F40" s="7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G40" s="9">
         <f>IFERROR(E40/(E40+F40),0)</f>
@@ -2185,12 +2185,12 @@
       </c>
       <c r="B41" s="14" t="inlineStr">
         <is>
-          <t>43043</t>
+          <t>38142</t>
         </is>
       </c>
       <c r="C41" s="12" t="inlineStr">
         <is>
-          <t>Atizapan</t>
+          <t>Zona Esmeralda</t>
         </is>
       </c>
       <c r="D41" s="12" t="inlineStr">
@@ -2199,10 +2199,10 @@
         </is>
       </c>
       <c r="E41" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G41" s="13">
         <f>IFERROR(E41/(E41+F41),0)</f>
@@ -2220,17 +2220,17 @@
       </c>
       <c r="B42" s="16" t="inlineStr">
         <is>
-          <t>38930</t>
+          <t>38186</t>
         </is>
       </c>
       <c r="C42" s="8" t="inlineStr">
         <is>
-          <t>Blvd. Aeropuerto dt</t>
+          <t>Arboledas</t>
         </is>
       </c>
       <c r="D42" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E42" s="7" t="n">
@@ -2255,17 +2255,17 @@
       </c>
       <c r="B43" s="14" t="inlineStr">
         <is>
-          <t>38529</t>
+          <t>43043</t>
         </is>
       </c>
       <c r="C43" s="12" t="inlineStr">
         <is>
-          <t>Bosques de Aragon</t>
+          <t>Atizapan</t>
         </is>
       </c>
       <c r="D43" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E43" s="11" t="n">
@@ -2290,17 +2290,17 @@
       </c>
       <c r="B44" s="16" t="inlineStr">
         <is>
-          <t>38837</t>
+          <t>38930</t>
         </is>
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t>Centenario Azcapotzalco</t>
+          <t>Blvd. Aeropuerto dt</t>
         </is>
       </c>
       <c r="D44" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E44" s="7" t="n">
@@ -2325,17 +2325,17 @@
       </c>
       <c r="B45" s="14" t="inlineStr">
         <is>
-          <t>38401</t>
+          <t>38529</t>
         </is>
       </c>
       <c r="C45" s="12" t="inlineStr">
         <is>
-          <t>Coacalco</t>
+          <t>Bosques de Aragon</t>
         </is>
       </c>
       <c r="D45" s="12" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E45" s="11" t="n">
@@ -2360,24 +2360,24 @@
       </c>
       <c r="B46" s="16" t="inlineStr">
         <is>
-          <t>43193</t>
+          <t>38837</t>
         </is>
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t>Cosmopol N1</t>
+          <t>Centenario Azcapotzalco</t>
         </is>
       </c>
       <c r="D46" s="8" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E46" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F46" s="7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G46" s="9">
         <f>IFERROR(E46/(E46+F46),0)</f>
@@ -2395,17 +2395,17 @@
       </c>
       <c r="B47" s="14" t="inlineStr">
         <is>
-          <t>38431</t>
+          <t>38401</t>
         </is>
       </c>
       <c r="C47" s="12" t="inlineStr">
         <is>
-          <t>Eduardo Molina</t>
+          <t>Coacalco</t>
         </is>
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E47" s="11" t="n">
@@ -2430,24 +2430,24 @@
       </c>
       <c r="B48" s="16" t="inlineStr">
         <is>
-          <t>38458</t>
+          <t>43193</t>
         </is>
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
-          <t>El Rosario</t>
+          <t>Cosmopol N1</t>
         </is>
       </c>
       <c r="D48" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E48" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F48" s="7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G48" s="9">
         <f>IFERROR(E48/(E48+F48),0)</f>
@@ -2465,17 +2465,17 @@
       </c>
       <c r="B49" s="14" t="inlineStr">
         <is>
-          <t>38903</t>
+          <t>38458</t>
         </is>
       </c>
       <c r="C49" s="12" t="inlineStr">
         <is>
-          <t>Encuentro Oceania</t>
+          <t>El Rosario</t>
         </is>
       </c>
       <c r="D49" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E49" s="11" t="n">
@@ -2500,12 +2500,12 @@
       </c>
       <c r="B50" s="16" t="inlineStr">
         <is>
-          <t>38995</t>
+          <t>38903</t>
         </is>
       </c>
       <c r="C50" s="8" t="inlineStr">
         <is>
-          <t>Encuentro Oceania II</t>
+          <t>Encuentro Oceania</t>
         </is>
       </c>
       <c r="D50" s="8" t="inlineStr">
@@ -2535,17 +2535,17 @@
       </c>
       <c r="B51" s="14" t="inlineStr">
         <is>
-          <t>38507</t>
+          <t>38995</t>
         </is>
       </c>
       <c r="C51" s="12" t="inlineStr">
         <is>
-          <t>Espacio Vista del Valle</t>
+          <t>Encuentro Oceania II</t>
         </is>
       </c>
       <c r="D51" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E51" s="11" t="n">
@@ -2570,17 +2570,17 @@
       </c>
       <c r="B52" s="16" t="inlineStr">
         <is>
-          <t>38770</t>
+          <t>38507</t>
         </is>
       </c>
       <c r="C52" s="8" t="inlineStr">
         <is>
-          <t>Gustavo Baz 29</t>
+          <t>Espacio Vista del Valle</t>
         </is>
       </c>
       <c r="D52" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E52" s="7" t="n">
@@ -2605,17 +2605,17 @@
       </c>
       <c r="B53" s="14" t="inlineStr">
         <is>
-          <t>38230</t>
+          <t>38770</t>
         </is>
       </c>
       <c r="C53" s="12" t="inlineStr">
         <is>
-          <t>ITEMS Edo de Mexico</t>
+          <t>Gustavo Baz 29</t>
         </is>
       </c>
       <c r="D53" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E53" s="11" t="n">
@@ -2640,17 +2640,17 @@
       </c>
       <c r="B54" s="16" t="inlineStr">
         <is>
-          <t>38207</t>
+          <t>38230</t>
         </is>
       </c>
       <c r="C54" s="8" t="inlineStr">
         <is>
-          <t>Lindavista II</t>
+          <t>ITEMS Edo de Mexico</t>
         </is>
       </c>
       <c r="D54" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E54" s="7" t="n">
@@ -2675,17 +2675,17 @@
       </c>
       <c r="B55" s="14" t="inlineStr">
         <is>
-          <t>38270</t>
+          <t>38207</t>
         </is>
       </c>
       <c r="C55" s="12" t="inlineStr">
         <is>
-          <t>Lomas Verdes II</t>
+          <t>Lindavista II</t>
         </is>
       </c>
       <c r="D55" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E55" s="11" t="n">
@@ -2710,17 +2710,17 @@
       </c>
       <c r="B56" s="16" t="inlineStr">
         <is>
-          <t>38371</t>
+          <t>38270</t>
         </is>
       </c>
       <c r="C56" s="8" t="inlineStr">
         <is>
-          <t>Montevideo DT</t>
+          <t>Lomas Verdes II</t>
         </is>
       </c>
       <c r="D56" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E56" s="7" t="n">
@@ -2745,17 +2745,17 @@
       </c>
       <c r="B57" s="14" t="inlineStr">
         <is>
-          <t>38674</t>
+          <t>38371</t>
         </is>
       </c>
       <c r="C57" s="12" t="inlineStr">
         <is>
-          <t>Mundo E</t>
+          <t>Montevideo DT</t>
         </is>
       </c>
       <c r="D57" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E57" s="11" t="n">
@@ -2780,12 +2780,12 @@
       </c>
       <c r="B58" s="16" t="inlineStr">
         <is>
-          <t>38845</t>
+          <t>38674</t>
         </is>
       </c>
       <c r="C58" s="8" t="inlineStr">
         <is>
-          <t>Mundo E II</t>
+          <t>Mundo E</t>
         </is>
       </c>
       <c r="D58" s="8" t="inlineStr">
@@ -2815,17 +2815,17 @@
       </c>
       <c r="B59" s="14" t="inlineStr">
         <is>
-          <t>38965</t>
+          <t>38845</t>
         </is>
       </c>
       <c r="C59" s="12" t="inlineStr">
         <is>
-          <t>Parque Tepeyac Piso 2</t>
+          <t>Mundo E II</t>
         </is>
       </c>
       <c r="D59" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E59" s="11" t="n">
@@ -2850,17 +2850,17 @@
       </c>
       <c r="B60" s="16" t="inlineStr">
         <is>
-          <t>38792</t>
+          <t>38965</t>
         </is>
       </c>
       <c r="C60" s="8" t="inlineStr">
         <is>
-          <t>Pasaje Tlanepantla</t>
+          <t>Parque Tepeyac Piso 2</t>
         </is>
       </c>
       <c r="D60" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E60" s="7" t="n">
@@ -2885,17 +2885,17 @@
       </c>
       <c r="B61" s="14" t="inlineStr">
         <is>
-          <t>38515</t>
+          <t>38792</t>
         </is>
       </c>
       <c r="C61" s="12" t="inlineStr">
         <is>
-          <t>Patio Ecatepec</t>
+          <t>Pasaje Tlanepantla</t>
         </is>
       </c>
       <c r="D61" s="12" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E61" s="11" t="n">
@@ -2920,17 +2920,17 @@
       </c>
       <c r="B62" s="16" t="inlineStr">
         <is>
-          <t>38176</t>
+          <t>38515</t>
         </is>
       </c>
       <c r="C62" s="8" t="inlineStr">
         <is>
-          <t>Periferico Satélite DT</t>
+          <t>Patio Ecatepec</t>
         </is>
       </c>
       <c r="D62" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E62" s="7" t="n">
@@ -2955,17 +2955,17 @@
       </c>
       <c r="B63" s="14" t="inlineStr">
         <is>
-          <t>38924</t>
+          <t>38176</t>
         </is>
       </c>
       <c r="C63" s="12" t="inlineStr">
         <is>
-          <t>Plaza Aeropuerto</t>
+          <t>Periferico Satélite DT</t>
         </is>
       </c>
       <c r="D63" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E63" s="11" t="n">
@@ -2990,12 +2990,12 @@
       </c>
       <c r="B64" s="16" t="inlineStr">
         <is>
-          <t>38719</t>
+          <t>38924</t>
         </is>
       </c>
       <c r="C64" s="8" t="inlineStr">
         <is>
-          <t>Plaza Fortuna</t>
+          <t>Plaza Aeropuerto</t>
         </is>
       </c>
       <c r="D64" s="8" t="inlineStr">
@@ -3025,17 +3025,17 @@
       </c>
       <c r="B65" s="14" t="inlineStr">
         <is>
-          <t>38427</t>
+          <t>38719</t>
         </is>
       </c>
       <c r="C65" s="12" t="inlineStr">
         <is>
-          <t>Plaza Satelite</t>
+          <t>Plaza Fortuna</t>
         </is>
       </c>
       <c r="D65" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E65" s="11" t="n">
@@ -3060,12 +3060,12 @@
       </c>
       <c r="B66" s="16" t="inlineStr">
         <is>
-          <t>38859</t>
+          <t>38427</t>
         </is>
       </c>
       <c r="C66" s="8" t="inlineStr">
         <is>
-          <t>Plaza Satelite II N1</t>
+          <t>Plaza Satelite</t>
         </is>
       </c>
       <c r="D66" s="8" t="inlineStr">
@@ -3095,17 +3095,17 @@
       </c>
       <c r="B67" s="14" t="inlineStr">
         <is>
-          <t>38811</t>
+          <t>38859</t>
         </is>
       </c>
       <c r="C67" s="12" t="inlineStr">
         <is>
-          <t>Plaza Tepeyac</t>
+          <t>Plaza Satelite II N1</t>
         </is>
       </c>
       <c r="D67" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E67" s="11" t="n">
@@ -3130,17 +3130,17 @@
       </c>
       <c r="B68" s="16" t="inlineStr">
         <is>
-          <t>38136</t>
+          <t>38811</t>
         </is>
       </c>
       <c r="C68" s="8" t="inlineStr">
         <is>
-          <t>Punta Norte</t>
+          <t>Plaza Tepeyac</t>
         </is>
       </c>
       <c r="D68" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E68" s="7" t="n">
@@ -3165,17 +3165,17 @@
       </c>
       <c r="B69" s="14" t="inlineStr">
         <is>
-          <t>43152</t>
+          <t>38136</t>
         </is>
       </c>
       <c r="C69" s="12" t="inlineStr">
         <is>
-          <t>Samara Satélite</t>
+          <t>Punta Norte</t>
         </is>
       </c>
       <c r="D69" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E69" s="11" t="n">
@@ -3488,7 +3488,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Centro Norte · Corte 30/08/2026 16:36</t>
+          <t>Centro Norte · Corte 30/08/2026 16:39</t>
         </is>
       </c>
     </row>
@@ -3759,10 +3759,10 @@
         </is>
       </c>
       <c r="C14" s="7" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="E14" s="9">
         <f>IFERROR(C14/(C14+D14),0)</f>

--- a/exports/Resumen_Evidencias_OPS.xlsx
+++ b/exports/Resumen_Evidencias_OPS.xlsx
@@ -577,7 +577,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Centro Norte · Corte 30/08/2026 16:39</t>
+          <t>Centro Norte · Corte 30/08/2026 16:53</t>
         </is>
       </c>
     </row>
@@ -600,10 +600,10 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="E6" s="5">
         <f>IFERROR(A6/(A6+C6),0)</f>
@@ -689,10 +689,10 @@
         <v>13</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E11" s="12" t="n">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="F11" s="13">
         <f>IFERROR(D11/(D11+E11),0)</f>
@@ -873,7 +873,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Centro Norte · Corte 30/08/2026 16:39</t>
+          <t>Centro Norte · Corte 30/08/2026 16:53</t>
         </is>
       </c>
     </row>
@@ -1520,17 +1520,17 @@
       </c>
       <c r="B22" s="16" t="inlineStr">
         <is>
-          <t>38661</t>
+          <t>38770</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>Jinetes</t>
+          <t>Gustavo Baz 29</t>
         </is>
       </c>
       <c r="D22" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E22" s="7" t="n">
@@ -1555,17 +1555,17 @@
       </c>
       <c r="B23" s="14" t="inlineStr">
         <is>
-          <t>38205</t>
+          <t>38661</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>Lindavista</t>
+          <t>Jinetes</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E23" s="11" t="n">
@@ -1590,17 +1590,17 @@
       </c>
       <c r="B24" s="16" t="inlineStr">
         <is>
-          <t>38119</t>
+          <t>38205</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>Lomas Verdes</t>
+          <t>Lindavista</t>
         </is>
       </c>
       <c r="D24" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E24" s="7" t="n">
@@ -1625,17 +1625,17 @@
       </c>
       <c r="B25" s="14" t="inlineStr">
         <is>
-          <t>43111</t>
+          <t>38119</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>Montevideo Insurgentes</t>
+          <t>Lomas Verdes</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E25" s="11" t="n">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="B26" s="16" t="inlineStr">
         <is>
-          <t>43195</t>
+          <t>43111</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>Parque Jadin kiosko</t>
+          <t>Montevideo Insurgentes</t>
         </is>
       </c>
       <c r="D26" s="8" t="inlineStr">
@@ -1695,17 +1695,17 @@
       </c>
       <c r="B27" s="14" t="inlineStr">
         <is>
-          <t>38937</t>
+          <t>43195</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>Parque Tepeyac Piso 1</t>
+          <t>Parque Jadin kiosko</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E27" s="11" t="n">
@@ -1730,17 +1730,17 @@
       </c>
       <c r="B28" s="16" t="inlineStr">
         <is>
-          <t>38590</t>
+          <t>38937</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>Parque Toreo II</t>
+          <t>Parque Tepeyac Piso 1</t>
         </is>
       </c>
       <c r="D28" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E28" s="7" t="n">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="B29" s="14" t="inlineStr">
         <is>
-          <t>38546</t>
+          <t>38590</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>Patio Claveria</t>
+          <t>Parque Toreo II</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E29" s="11" t="n">
@@ -1800,12 +1800,12 @@
       </c>
       <c r="B30" s="16" t="inlineStr">
         <is>
-          <t>38677</t>
+          <t>38546</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>Patio la Raza</t>
+          <t>Patio Claveria</t>
         </is>
       </c>
       <c r="D30" s="8" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="B31" s="14" t="inlineStr">
         <is>
-          <t>43132</t>
+          <t>38677</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>Plaza Vista Norte</t>
+          <t>Patio la Raza</t>
         </is>
       </c>
       <c r="D31" s="12" t="inlineStr">
@@ -1870,17 +1870,17 @@
       </c>
       <c r="B32" s="16" t="inlineStr">
         <is>
-          <t>38456</t>
+          <t>38427</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>Plaza las Flores</t>
+          <t>Plaza Satelite</t>
         </is>
       </c>
       <c r="D32" s="8" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E32" s="7" t="n">
@@ -1905,17 +1905,17 @@
       </c>
       <c r="B33" s="14" t="inlineStr">
         <is>
-          <t>43152</t>
+          <t>43132</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>Samara Satélite</t>
+          <t>Plaza Vista Norte</t>
         </is>
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E33" s="11" t="n">
@@ -1940,17 +1940,17 @@
       </c>
       <c r="B34" s="16" t="inlineStr">
         <is>
-          <t>38266</t>
+          <t>38456</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>San Mateo</t>
+          <t>Plaza las Flores</t>
         </is>
       </c>
       <c r="D34" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E34" s="7" t="n">
@@ -1975,12 +1975,12 @@
       </c>
       <c r="B35" s="14" t="inlineStr">
         <is>
-          <t>38117</t>
+          <t>43152</t>
         </is>
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>Satelite</t>
+          <t>Samara Satélite</t>
         </is>
       </c>
       <c r="D35" s="12" t="inlineStr">
@@ -2010,17 +2010,17 @@
       </c>
       <c r="B36" s="16" t="inlineStr">
         <is>
-          <t>38475</t>
+          <t>38266</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>Satelite Centro Civico</t>
+          <t>San Mateo</t>
         </is>
       </c>
       <c r="D36" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E36" s="7" t="n">
@@ -2045,17 +2045,17 @@
       </c>
       <c r="B37" s="14" t="inlineStr">
         <is>
-          <t>38925</t>
+          <t>38117</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>Star Medica Lomas Verdes</t>
+          <t>Satelite</t>
         </is>
       </c>
       <c r="D37" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E37" s="11" t="n">
@@ -2080,17 +2080,17 @@
       </c>
       <c r="B38" s="16" t="inlineStr">
         <is>
-          <t>38411</t>
+          <t>38475</t>
         </is>
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>Torres Lindavista</t>
+          <t>Satelite Centro Civico</t>
         </is>
       </c>
       <c r="D38" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E38" s="7" t="n">
@@ -2115,17 +2115,17 @@
       </c>
       <c r="B39" s="14" t="inlineStr">
         <is>
-          <t>38651</t>
+          <t>38925</t>
         </is>
       </c>
       <c r="C39" s="12" t="inlineStr">
         <is>
-          <t>Via Vallejo</t>
+          <t>Star Medica Lomas Verdes</t>
         </is>
       </c>
       <c r="D39" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E39" s="11" t="n">
@@ -2150,17 +2150,17 @@
       </c>
       <c r="B40" s="16" t="inlineStr">
         <is>
-          <t>38656</t>
+          <t>38411</t>
         </is>
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>Viveros de la Loma</t>
+          <t>Torres Lindavista</t>
         </is>
       </c>
       <c r="D40" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E40" s="7" t="n">
@@ -2185,17 +2185,17 @@
       </c>
       <c r="B41" s="14" t="inlineStr">
         <is>
-          <t>38142</t>
+          <t>38651</t>
         </is>
       </c>
       <c r="C41" s="12" t="inlineStr">
         <is>
-          <t>Zona Esmeralda</t>
+          <t>Via Vallejo</t>
         </is>
       </c>
       <c r="D41" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E41" s="11" t="n">
@@ -2220,24 +2220,24 @@
       </c>
       <c r="B42" s="16" t="inlineStr">
         <is>
-          <t>38186</t>
+          <t>38656</t>
         </is>
       </c>
       <c r="C42" s="8" t="inlineStr">
         <is>
-          <t>Arboledas</t>
+          <t>Viveros de la Loma</t>
         </is>
       </c>
       <c r="D42" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E42" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F42" s="7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G42" s="9">
         <f>IFERROR(E42/(E42+F42),0)</f>
@@ -2255,12 +2255,12 @@
       </c>
       <c r="B43" s="14" t="inlineStr">
         <is>
-          <t>43043</t>
+          <t>38142</t>
         </is>
       </c>
       <c r="C43" s="12" t="inlineStr">
         <is>
-          <t>Atizapan</t>
+          <t>Zona Esmeralda</t>
         </is>
       </c>
       <c r="D43" s="12" t="inlineStr">
@@ -2269,10 +2269,10 @@
         </is>
       </c>
       <c r="E43" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G43" s="13">
         <f>IFERROR(E43/(E43+F43),0)</f>
@@ -2290,17 +2290,17 @@
       </c>
       <c r="B44" s="16" t="inlineStr">
         <is>
-          <t>38930</t>
+          <t>38186</t>
         </is>
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t>Blvd. Aeropuerto dt</t>
+          <t>Arboledas</t>
         </is>
       </c>
       <c r="D44" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E44" s="7" t="n">
@@ -2325,17 +2325,17 @@
       </c>
       <c r="B45" s="14" t="inlineStr">
         <is>
-          <t>38529</t>
+          <t>43043</t>
         </is>
       </c>
       <c r="C45" s="12" t="inlineStr">
         <is>
-          <t>Bosques de Aragon</t>
+          <t>Atizapan</t>
         </is>
       </c>
       <c r="D45" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E45" s="11" t="n">
@@ -2360,17 +2360,17 @@
       </c>
       <c r="B46" s="16" t="inlineStr">
         <is>
-          <t>38837</t>
+          <t>38930</t>
         </is>
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t>Centenario Azcapotzalco</t>
+          <t>Blvd. Aeropuerto dt</t>
         </is>
       </c>
       <c r="D46" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E46" s="7" t="n">
@@ -2395,17 +2395,17 @@
       </c>
       <c r="B47" s="14" t="inlineStr">
         <is>
-          <t>38401</t>
+          <t>38529</t>
         </is>
       </c>
       <c r="C47" s="12" t="inlineStr">
         <is>
-          <t>Coacalco</t>
+          <t>Bosques de Aragon</t>
         </is>
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E47" s="11" t="n">
@@ -2430,24 +2430,24 @@
       </c>
       <c r="B48" s="16" t="inlineStr">
         <is>
-          <t>43193</t>
+          <t>38837</t>
         </is>
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
-          <t>Cosmopol N1</t>
+          <t>Centenario Azcapotzalco</t>
         </is>
       </c>
       <c r="D48" s="8" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E48" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F48" s="7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G48" s="9">
         <f>IFERROR(E48/(E48+F48),0)</f>
@@ -2465,17 +2465,17 @@
       </c>
       <c r="B49" s="14" t="inlineStr">
         <is>
-          <t>38458</t>
+          <t>38401</t>
         </is>
       </c>
       <c r="C49" s="12" t="inlineStr">
         <is>
-          <t>El Rosario</t>
+          <t>Coacalco</t>
         </is>
       </c>
       <c r="D49" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E49" s="11" t="n">
@@ -2500,24 +2500,24 @@
       </c>
       <c r="B50" s="16" t="inlineStr">
         <is>
-          <t>38903</t>
+          <t>43193</t>
         </is>
       </c>
       <c r="C50" s="8" t="inlineStr">
         <is>
-          <t>Encuentro Oceania</t>
+          <t>Cosmopol N1</t>
         </is>
       </c>
       <c r="D50" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E50" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F50" s="7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G50" s="9">
         <f>IFERROR(E50/(E50+F50),0)</f>
@@ -2535,17 +2535,17 @@
       </c>
       <c r="B51" s="14" t="inlineStr">
         <is>
-          <t>38995</t>
+          <t>38458</t>
         </is>
       </c>
       <c r="C51" s="12" t="inlineStr">
         <is>
-          <t>Encuentro Oceania II</t>
+          <t>El Rosario</t>
         </is>
       </c>
       <c r="D51" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E51" s="11" t="n">
@@ -2570,17 +2570,17 @@
       </c>
       <c r="B52" s="16" t="inlineStr">
         <is>
-          <t>38507</t>
+          <t>38903</t>
         </is>
       </c>
       <c r="C52" s="8" t="inlineStr">
         <is>
-          <t>Espacio Vista del Valle</t>
+          <t>Encuentro Oceania</t>
         </is>
       </c>
       <c r="D52" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E52" s="7" t="n">
@@ -2605,17 +2605,17 @@
       </c>
       <c r="B53" s="14" t="inlineStr">
         <is>
-          <t>38770</t>
+          <t>38995</t>
         </is>
       </c>
       <c r="C53" s="12" t="inlineStr">
         <is>
-          <t>Gustavo Baz 29</t>
+          <t>Encuentro Oceania II</t>
         </is>
       </c>
       <c r="D53" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E53" s="11" t="n">
@@ -2640,17 +2640,17 @@
       </c>
       <c r="B54" s="16" t="inlineStr">
         <is>
-          <t>38230</t>
+          <t>38507</t>
         </is>
       </c>
       <c r="C54" s="8" t="inlineStr">
         <is>
-          <t>ITEMS Edo de Mexico</t>
+          <t>Espacio Vista del Valle</t>
         </is>
       </c>
       <c r="D54" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E54" s="7" t="n">
@@ -2675,17 +2675,17 @@
       </c>
       <c r="B55" s="14" t="inlineStr">
         <is>
-          <t>38207</t>
+          <t>38230</t>
         </is>
       </c>
       <c r="C55" s="12" t="inlineStr">
         <is>
-          <t>Lindavista II</t>
+          <t>ITEMS Edo de Mexico</t>
         </is>
       </c>
       <c r="D55" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E55" s="11" t="n">
@@ -2710,17 +2710,17 @@
       </c>
       <c r="B56" s="16" t="inlineStr">
         <is>
-          <t>38270</t>
+          <t>38207</t>
         </is>
       </c>
       <c r="C56" s="8" t="inlineStr">
         <is>
-          <t>Lomas Verdes II</t>
+          <t>Lindavista II</t>
         </is>
       </c>
       <c r="D56" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E56" s="7" t="n">
@@ -2745,17 +2745,17 @@
       </c>
       <c r="B57" s="14" t="inlineStr">
         <is>
-          <t>38371</t>
+          <t>38270</t>
         </is>
       </c>
       <c r="C57" s="12" t="inlineStr">
         <is>
-          <t>Montevideo DT</t>
+          <t>Lomas Verdes II</t>
         </is>
       </c>
       <c r="D57" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E57" s="11" t="n">
@@ -2780,17 +2780,17 @@
       </c>
       <c r="B58" s="16" t="inlineStr">
         <is>
-          <t>38674</t>
+          <t>38371</t>
         </is>
       </c>
       <c r="C58" s="8" t="inlineStr">
         <is>
-          <t>Mundo E</t>
+          <t>Montevideo DT</t>
         </is>
       </c>
       <c r="D58" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E58" s="7" t="n">
@@ -2815,12 +2815,12 @@
       </c>
       <c r="B59" s="14" t="inlineStr">
         <is>
-          <t>38845</t>
+          <t>38674</t>
         </is>
       </c>
       <c r="C59" s="12" t="inlineStr">
         <is>
-          <t>Mundo E II</t>
+          <t>Mundo E</t>
         </is>
       </c>
       <c r="D59" s="12" t="inlineStr">
@@ -2850,17 +2850,17 @@
       </c>
       <c r="B60" s="16" t="inlineStr">
         <is>
-          <t>38965</t>
+          <t>38845</t>
         </is>
       </c>
       <c r="C60" s="8" t="inlineStr">
         <is>
-          <t>Parque Tepeyac Piso 2</t>
+          <t>Mundo E II</t>
         </is>
       </c>
       <c r="D60" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E60" s="7" t="n">
@@ -2885,17 +2885,17 @@
       </c>
       <c r="B61" s="14" t="inlineStr">
         <is>
-          <t>38792</t>
+          <t>38965</t>
         </is>
       </c>
       <c r="C61" s="12" t="inlineStr">
         <is>
-          <t>Pasaje Tlanepantla</t>
+          <t>Parque Tepeyac Piso 2</t>
         </is>
       </c>
       <c r="D61" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E61" s="11" t="n">
@@ -2920,17 +2920,17 @@
       </c>
       <c r="B62" s="16" t="inlineStr">
         <is>
-          <t>38515</t>
+          <t>38792</t>
         </is>
       </c>
       <c r="C62" s="8" t="inlineStr">
         <is>
-          <t>Patio Ecatepec</t>
+          <t>Pasaje Tlanepantla</t>
         </is>
       </c>
       <c r="D62" s="8" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E62" s="7" t="n">
@@ -2955,17 +2955,17 @@
       </c>
       <c r="B63" s="14" t="inlineStr">
         <is>
-          <t>38176</t>
+          <t>38515</t>
         </is>
       </c>
       <c r="C63" s="12" t="inlineStr">
         <is>
-          <t>Periferico Satélite DT</t>
+          <t>Patio Ecatepec</t>
         </is>
       </c>
       <c r="D63" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E63" s="11" t="n">
@@ -2990,17 +2990,17 @@
       </c>
       <c r="B64" s="16" t="inlineStr">
         <is>
-          <t>38924</t>
+          <t>38176</t>
         </is>
       </c>
       <c r="C64" s="8" t="inlineStr">
         <is>
-          <t>Plaza Aeropuerto</t>
+          <t>Periferico Satélite DT</t>
         </is>
       </c>
       <c r="D64" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E64" s="7" t="n">
@@ -3025,12 +3025,12 @@
       </c>
       <c r="B65" s="14" t="inlineStr">
         <is>
-          <t>38719</t>
+          <t>38924</t>
         </is>
       </c>
       <c r="C65" s="12" t="inlineStr">
         <is>
-          <t>Plaza Fortuna</t>
+          <t>Plaza Aeropuerto</t>
         </is>
       </c>
       <c r="D65" s="12" t="inlineStr">
@@ -3060,17 +3060,17 @@
       </c>
       <c r="B66" s="16" t="inlineStr">
         <is>
-          <t>38427</t>
+          <t>38719</t>
         </is>
       </c>
       <c r="C66" s="8" t="inlineStr">
         <is>
-          <t>Plaza Satelite</t>
+          <t>Plaza Fortuna</t>
         </is>
       </c>
       <c r="D66" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E66" s="7" t="n">
@@ -3488,7 +3488,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Centro Norte · Corte 30/08/2026 16:39</t>
+          <t>Centro Norte · Corte 30/08/2026 16:53</t>
         </is>
       </c>
     </row>
@@ -3759,10 +3759,10 @@
         </is>
       </c>
       <c r="C14" s="7" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E14" s="9">
         <f>IFERROR(C14/(C14+D14),0)</f>

--- a/exports/Resumen_Evidencias_OPS.xlsx
+++ b/exports/Resumen_Evidencias_OPS.xlsx
@@ -577,7 +577,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Centro Norte · Corte 30/08/2026 16:53</t>
+          <t>Centro Norte · Corte 30/08/2026 17:01</t>
         </is>
       </c>
     </row>
@@ -600,10 +600,10 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="E6" s="5">
         <f>IFERROR(A6/(A6+C6),0)</f>
@@ -689,10 +689,10 @@
         <v>13</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E11" s="12" t="n">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F11" s="13">
         <f>IFERROR(D11/(D11+E11),0)</f>
@@ -873,7 +873,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Centro Norte · Corte 30/08/2026 16:53</t>
+          <t>Centro Norte · Corte 30/08/2026 17:01</t>
         </is>
       </c>
     </row>
@@ -1485,17 +1485,17 @@
       </c>
       <c r="B21" s="14" t="inlineStr">
         <is>
-          <t>38363</t>
+          <t>38458</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>Galerias Atizapan</t>
+          <t>El Rosario</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E21" s="11" t="n">
@@ -1520,17 +1520,17 @@
       </c>
       <c r="B22" s="16" t="inlineStr">
         <is>
-          <t>38770</t>
+          <t>38363</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>Gustavo Baz 29</t>
+          <t>Galerias Atizapan</t>
         </is>
       </c>
       <c r="D22" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E22" s="7" t="n">
@@ -1555,17 +1555,17 @@
       </c>
       <c r="B23" s="14" t="inlineStr">
         <is>
-          <t>38661</t>
+          <t>38770</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>Jinetes</t>
+          <t>Gustavo Baz 29</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E23" s="11" t="n">
@@ -1590,17 +1590,17 @@
       </c>
       <c r="B24" s="16" t="inlineStr">
         <is>
-          <t>38205</t>
+          <t>38661</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>Lindavista</t>
+          <t>Jinetes</t>
         </is>
       </c>
       <c r="D24" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E24" s="7" t="n">
@@ -1625,17 +1625,17 @@
       </c>
       <c r="B25" s="14" t="inlineStr">
         <is>
-          <t>38119</t>
+          <t>38205</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>Lomas Verdes</t>
+          <t>Lindavista</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E25" s="11" t="n">
@@ -1660,17 +1660,17 @@
       </c>
       <c r="B26" s="16" t="inlineStr">
         <is>
-          <t>43111</t>
+          <t>38119</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>Montevideo Insurgentes</t>
+          <t>Lomas Verdes</t>
         </is>
       </c>
       <c r="D26" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E26" s="7" t="n">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="B27" s="14" t="inlineStr">
         <is>
-          <t>43195</t>
+          <t>43111</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>Parque Jadin kiosko</t>
+          <t>Montevideo Insurgentes</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
@@ -1730,17 +1730,17 @@
       </c>
       <c r="B28" s="16" t="inlineStr">
         <is>
-          <t>38937</t>
+          <t>43195</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>Parque Tepeyac Piso 1</t>
+          <t>Parque Jadin kiosko</t>
         </is>
       </c>
       <c r="D28" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E28" s="7" t="n">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="B29" s="14" t="inlineStr">
         <is>
-          <t>38590</t>
+          <t>38937</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>Parque Toreo II</t>
+          <t>Parque Tepeyac Piso 1</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E29" s="11" t="n">
@@ -1800,17 +1800,17 @@
       </c>
       <c r="B30" s="16" t="inlineStr">
         <is>
-          <t>38546</t>
+          <t>38590</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>Patio Claveria</t>
+          <t>Parque Toreo II</t>
         </is>
       </c>
       <c r="D30" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E30" s="7" t="n">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="B31" s="14" t="inlineStr">
         <is>
-          <t>38677</t>
+          <t>38546</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>Patio la Raza</t>
+          <t>Patio Claveria</t>
         </is>
       </c>
       <c r="D31" s="12" t="inlineStr">
@@ -1870,17 +1870,17 @@
       </c>
       <c r="B32" s="16" t="inlineStr">
         <is>
-          <t>38427</t>
+          <t>38677</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>Plaza Satelite</t>
+          <t>Patio la Raza</t>
         </is>
       </c>
       <c r="D32" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E32" s="7" t="n">
@@ -1905,17 +1905,17 @@
       </c>
       <c r="B33" s="14" t="inlineStr">
         <is>
-          <t>43132</t>
+          <t>38427</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>Plaza Vista Norte</t>
+          <t>Plaza Satelite</t>
         </is>
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E33" s="11" t="n">
@@ -1940,17 +1940,17 @@
       </c>
       <c r="B34" s="16" t="inlineStr">
         <is>
-          <t>38456</t>
+          <t>43132</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>Plaza las Flores</t>
+          <t>Plaza Vista Norte</t>
         </is>
       </c>
       <c r="D34" s="8" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E34" s="7" t="n">
@@ -1975,17 +1975,17 @@
       </c>
       <c r="B35" s="14" t="inlineStr">
         <is>
-          <t>43152</t>
+          <t>38456</t>
         </is>
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>Samara Satélite</t>
+          <t>Plaza las Flores</t>
         </is>
       </c>
       <c r="D35" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E35" s="11" t="n">
@@ -2010,17 +2010,17 @@
       </c>
       <c r="B36" s="16" t="inlineStr">
         <is>
-          <t>38266</t>
+          <t>43152</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>San Mateo</t>
+          <t>Samara Satélite</t>
         </is>
       </c>
       <c r="D36" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E36" s="7" t="n">
@@ -2045,17 +2045,17 @@
       </c>
       <c r="B37" s="14" t="inlineStr">
         <is>
-          <t>38117</t>
+          <t>38266</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>Satelite</t>
+          <t>San Mateo</t>
         </is>
       </c>
       <c r="D37" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E37" s="11" t="n">
@@ -2080,12 +2080,12 @@
       </c>
       <c r="B38" s="16" t="inlineStr">
         <is>
-          <t>38475</t>
+          <t>38117</t>
         </is>
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>Satelite Centro Civico</t>
+          <t>Satelite</t>
         </is>
       </c>
       <c r="D38" s="8" t="inlineStr">
@@ -2115,17 +2115,17 @@
       </c>
       <c r="B39" s="14" t="inlineStr">
         <is>
-          <t>38925</t>
+          <t>38475</t>
         </is>
       </c>
       <c r="C39" s="12" t="inlineStr">
         <is>
-          <t>Star Medica Lomas Verdes</t>
+          <t>Satelite Centro Civico</t>
         </is>
       </c>
       <c r="D39" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E39" s="11" t="n">
@@ -2150,17 +2150,17 @@
       </c>
       <c r="B40" s="16" t="inlineStr">
         <is>
-          <t>38411</t>
+          <t>38925</t>
         </is>
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>Torres Lindavista</t>
+          <t>Star Medica Lomas Verdes</t>
         </is>
       </c>
       <c r="D40" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E40" s="7" t="n">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="B41" s="14" t="inlineStr">
         <is>
-          <t>38651</t>
+          <t>38411</t>
         </is>
       </c>
       <c r="C41" s="12" t="inlineStr">
         <is>
-          <t>Via Vallejo</t>
+          <t>Torres Lindavista</t>
         </is>
       </c>
       <c r="D41" s="12" t="inlineStr">
@@ -2220,17 +2220,17 @@
       </c>
       <c r="B42" s="16" t="inlineStr">
         <is>
-          <t>38656</t>
+          <t>38651</t>
         </is>
       </c>
       <c r="C42" s="8" t="inlineStr">
         <is>
-          <t>Viveros de la Loma</t>
+          <t>Via Vallejo</t>
         </is>
       </c>
       <c r="D42" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E42" s="7" t="n">
@@ -2255,17 +2255,17 @@
       </c>
       <c r="B43" s="14" t="inlineStr">
         <is>
-          <t>38142</t>
+          <t>38656</t>
         </is>
       </c>
       <c r="C43" s="12" t="inlineStr">
         <is>
-          <t>Zona Esmeralda</t>
+          <t>Viveros de la Loma</t>
         </is>
       </c>
       <c r="D43" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E43" s="11" t="n">
@@ -2290,24 +2290,24 @@
       </c>
       <c r="B44" s="16" t="inlineStr">
         <is>
-          <t>38186</t>
+          <t>38142</t>
         </is>
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t>Arboledas</t>
+          <t>Zona Esmeralda</t>
         </is>
       </c>
       <c r="D44" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E44" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F44" s="7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G44" s="9">
         <f>IFERROR(E44/(E44+F44),0)</f>
@@ -2325,17 +2325,17 @@
       </c>
       <c r="B45" s="14" t="inlineStr">
         <is>
-          <t>43043</t>
+          <t>38186</t>
         </is>
       </c>
       <c r="C45" s="12" t="inlineStr">
         <is>
-          <t>Atizapan</t>
+          <t>Arboledas</t>
         </is>
       </c>
       <c r="D45" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E45" s="11" t="n">
@@ -2360,17 +2360,17 @@
       </c>
       <c r="B46" s="16" t="inlineStr">
         <is>
-          <t>38930</t>
+          <t>43043</t>
         </is>
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t>Blvd. Aeropuerto dt</t>
+          <t>Atizapan</t>
         </is>
       </c>
       <c r="D46" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E46" s="7" t="n">
@@ -2395,12 +2395,12 @@
       </c>
       <c r="B47" s="14" t="inlineStr">
         <is>
-          <t>38529</t>
+          <t>38930</t>
         </is>
       </c>
       <c r="C47" s="12" t="inlineStr">
         <is>
-          <t>Bosques de Aragon</t>
+          <t>Blvd. Aeropuerto dt</t>
         </is>
       </c>
       <c r="D47" s="12" t="inlineStr">
@@ -2430,17 +2430,17 @@
       </c>
       <c r="B48" s="16" t="inlineStr">
         <is>
-          <t>38837</t>
+          <t>38529</t>
         </is>
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
-          <t>Centenario Azcapotzalco</t>
+          <t>Bosques de Aragon</t>
         </is>
       </c>
       <c r="D48" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E48" s="7" t="n">
@@ -2465,17 +2465,17 @@
       </c>
       <c r="B49" s="14" t="inlineStr">
         <is>
-          <t>38401</t>
+          <t>38837</t>
         </is>
       </c>
       <c r="C49" s="12" t="inlineStr">
         <is>
-          <t>Coacalco</t>
+          <t>Centenario Azcapotzalco</t>
         </is>
       </c>
       <c r="D49" s="12" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E49" s="11" t="n">
@@ -2500,12 +2500,12 @@
       </c>
       <c r="B50" s="16" t="inlineStr">
         <is>
-          <t>43193</t>
+          <t>38401</t>
         </is>
       </c>
       <c r="C50" s="8" t="inlineStr">
         <is>
-          <t>Cosmopol N1</t>
+          <t>Coacalco</t>
         </is>
       </c>
       <c r="D50" s="8" t="inlineStr">
@@ -2517,7 +2517,7 @@
         <v>0</v>
       </c>
       <c r="F50" s="7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G50" s="9">
         <f>IFERROR(E50/(E50+F50),0)</f>
@@ -2535,24 +2535,24 @@
       </c>
       <c r="B51" s="14" t="inlineStr">
         <is>
-          <t>38458</t>
+          <t>43193</t>
         </is>
       </c>
       <c r="C51" s="12" t="inlineStr">
         <is>
-          <t>El Rosario</t>
+          <t>Cosmopol N1</t>
         </is>
       </c>
       <c r="D51" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E51" s="11" t="n">
         <v>0</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G51" s="13">
         <f>IFERROR(E51/(E51+F51),0)</f>
@@ -3488,7 +3488,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Centro Norte · Corte 30/08/2026 16:53</t>
+          <t>Centro Norte · Corte 30/08/2026 17:01</t>
         </is>
       </c>
     </row>
@@ -3759,10 +3759,10 @@
         </is>
       </c>
       <c r="C14" s="7" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E14" s="9">
         <f>IFERROR(C14/(C14+D14),0)</f>

--- a/exports/Resumen_Evidencias_OPS.xlsx
+++ b/exports/Resumen_Evidencias_OPS.xlsx
@@ -577,7 +577,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Centro Norte · Corte 30/08/2026 17:01</t>
+          <t>Centro Norte · Corte 30/08/2026 17:24</t>
         </is>
       </c>
     </row>
@@ -600,10 +600,10 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>663</v>
+        <v>654</v>
       </c>
       <c r="E6" s="5">
         <f>IFERROR(A6/(A6+C6),0)</f>
@@ -661,10 +661,10 @@
         <v>10</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="F10" s="9">
         <f>IFERROR(D10/(D10+E10),0)</f>
@@ -689,10 +689,10 @@
         <v>13</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E11" s="12" t="n">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F11" s="13">
         <f>IFERROR(D11/(D11+E11),0)</f>
@@ -717,10 +717,10 @@
         <v>13</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E12" s="8" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F12" s="9">
         <f>IFERROR(D12/(D12+E12),0)</f>
@@ -745,10 +745,10 @@
         <v>13</v>
       </c>
       <c r="D13" s="11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E13" s="12" t="n">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="F13" s="13">
         <f>IFERROR(D13/(D13+E13),0)</f>
@@ -773,10 +773,10 @@
         <v>12</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E14" s="8" t="n">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F14" s="9">
         <f>IFERROR(D14/(D14+E14),0)</f>
@@ -873,7 +873,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Centro Norte · Corte 30/08/2026 17:01</t>
+          <t>Centro Norte · Corte 30/08/2026 17:24</t>
         </is>
       </c>
     </row>
@@ -925,12 +925,12 @@
       </c>
       <c r="B5" s="14" t="inlineStr">
         <is>
-          <t>38561</t>
+          <t>38695</t>
         </is>
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>Parque Toreo</t>
+          <t>Cetram 4 Caminos</t>
         </is>
       </c>
       <c r="D5" s="12" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="B6" s="16" t="inlineStr">
         <is>
-          <t>38695</t>
+          <t>38561</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>Cetram 4 Caminos</t>
+          <t>Parque Toreo</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
@@ -974,10 +974,10 @@
         </is>
       </c>
       <c r="E6" s="7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G6" s="9">
         <f>IFERROR(E6/(E6+F6),0)</f>
@@ -995,12 +995,12 @@
       </c>
       <c r="B7" s="14" t="inlineStr">
         <is>
-          <t>38894</t>
+          <t>38339</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>Galerias Perinorte</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
@@ -1009,18 +1009,18 @@
         </is>
       </c>
       <c r="E7" s="11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G7" s="13">
         <f>IFERROR(E7/(E7+F7),0)</f>
         <v/>
       </c>
-      <c r="H7" s="10" t="inlineStr">
-        <is>
-          <t>Atención</t>
+      <c r="H7" s="15" t="inlineStr">
+        <is>
+          <t>Seguimiento</t>
         </is>
       </c>
     </row>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="B8" s="16" t="inlineStr">
         <is>
-          <t>38339</t>
+          <t>38894</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Galerias Perinorte</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
@@ -1065,12 +1065,12 @@
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>38862</t>
+          <t>38333</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>San Miguel Izcalli</t>
+          <t>Izcalli Mega</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
@@ -1100,12 +1100,12 @@
       </c>
       <c r="B10" s="16" t="inlineStr">
         <is>
-          <t>38333</t>
+          <t>38862</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>Izcalli Mega</t>
+          <t>San Miguel Izcalli</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
@@ -1114,10 +1114,10 @@
         </is>
       </c>
       <c r="E10" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G10" s="9">
         <f>IFERROR(E10/(E10+F10),0)</f>
@@ -1170,17 +1170,17 @@
       </c>
       <c r="B12" s="16" t="inlineStr">
         <is>
-          <t>38606</t>
+          <t>38456</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>TlalnepantlaCarso</t>
+          <t>Plaza las Flores</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E12" s="7" t="n">
@@ -1205,24 +1205,24 @@
       </c>
       <c r="B13" s="14" t="inlineStr">
         <is>
-          <t>43194</t>
+          <t>38606</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>Atana Lindavista</t>
+          <t>TlalnepantlaCarso</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E13" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G13" s="13">
         <f>IFERROR(E13/(E13+F13),0)</f>
@@ -1240,17 +1240,17 @@
       </c>
       <c r="B14" s="16" t="inlineStr">
         <is>
-          <t>38149</t>
+          <t>38186</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Bellavista</t>
+          <t>Arboledas</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E14" s="7" t="n">
@@ -1275,12 +1275,12 @@
       </c>
       <c r="B15" s="14" t="inlineStr">
         <is>
-          <t>38527</t>
+          <t>43194</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>Camarones</t>
+          <t>Atana Lindavista</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
@@ -1310,12 +1310,12 @@
       </c>
       <c r="B16" s="16" t="inlineStr">
         <is>
-          <t>38394</t>
+          <t>38149</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>Centro Comercial Lomas Verdes</t>
+          <t>Bellavista</t>
         </is>
       </c>
       <c r="D16" s="8" t="inlineStr">
@@ -1345,17 +1345,17 @@
       </c>
       <c r="B17" s="14" t="inlineStr">
         <is>
-          <t>38535</t>
+          <t>38527</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>City Center Esmeralda</t>
+          <t>Camarones</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E17" s="11" t="n">
@@ -1380,17 +1380,17 @@
       </c>
       <c r="B18" s="16" t="inlineStr">
         <is>
-          <t>38604</t>
+          <t>38394</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>Cosmopol</t>
+          <t>Centro Comercial Lomas Verdes</t>
         </is>
       </c>
       <c r="D18" s="8" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E18" s="7" t="n">
@@ -1415,17 +1415,17 @@
       </c>
       <c r="B19" s="14" t="inlineStr">
         <is>
-          <t>38197</t>
+          <t>38535</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>Echegaray</t>
+          <t>City Center Esmeralda</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E19" s="11" t="n">
@@ -1450,17 +1450,17 @@
       </c>
       <c r="B20" s="16" t="inlineStr">
         <is>
-          <t>38431</t>
+          <t>38604</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>Eduardo Molina</t>
+          <t>Cosmopol</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E20" s="7" t="n">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="B21" s="14" t="inlineStr">
         <is>
-          <t>38458</t>
+          <t>38197</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>El Rosario</t>
+          <t>Echegaray</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
@@ -1520,17 +1520,17 @@
       </c>
       <c r="B22" s="16" t="inlineStr">
         <is>
-          <t>38363</t>
+          <t>38431</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>Galerias Atizapan</t>
+          <t>Eduardo Molina</t>
         </is>
       </c>
       <c r="D22" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E22" s="7" t="n">
@@ -1555,12 +1555,12 @@
       </c>
       <c r="B23" s="14" t="inlineStr">
         <is>
-          <t>38770</t>
+          <t>38458</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>Gustavo Baz 29</t>
+          <t>El Rosario</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr">
@@ -1590,17 +1590,17 @@
       </c>
       <c r="B24" s="16" t="inlineStr">
         <is>
-          <t>38661</t>
+          <t>38363</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>Jinetes</t>
+          <t>Galerias Atizapan</t>
         </is>
       </c>
       <c r="D24" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E24" s="7" t="n">
@@ -1625,17 +1625,17 @@
       </c>
       <c r="B25" s="14" t="inlineStr">
         <is>
-          <t>38205</t>
+          <t>38770</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>Lindavista</t>
+          <t>Gustavo Baz 29</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E25" s="11" t="n">
@@ -1660,17 +1660,17 @@
       </c>
       <c r="B26" s="16" t="inlineStr">
         <is>
-          <t>38119</t>
+          <t>38661</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>Lomas Verdes</t>
+          <t>Jinetes</t>
         </is>
       </c>
       <c r="D26" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E26" s="7" t="n">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="B27" s="14" t="inlineStr">
         <is>
-          <t>43111</t>
+          <t>38205</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>Montevideo Insurgentes</t>
+          <t>Lindavista</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="B28" s="16" t="inlineStr">
         <is>
-          <t>43195</t>
+          <t>38207</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>Parque Jadin kiosko</t>
+          <t>Lindavista II</t>
         </is>
       </c>
       <c r="D28" s="8" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="B29" s="14" t="inlineStr">
         <is>
-          <t>38937</t>
+          <t>38119</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>Parque Tepeyac Piso 1</t>
+          <t>Lomas Verdes</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E29" s="11" t="n">
@@ -1800,17 +1800,17 @@
       </c>
       <c r="B30" s="16" t="inlineStr">
         <is>
-          <t>38590</t>
+          <t>43111</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>Parque Toreo II</t>
+          <t>Montevideo Insurgentes</t>
         </is>
       </c>
       <c r="D30" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E30" s="7" t="n">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="B31" s="14" t="inlineStr">
         <is>
-          <t>38546</t>
+          <t>43195</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>Patio Claveria</t>
+          <t>Parque Jadin kiosko</t>
         </is>
       </c>
       <c r="D31" s="12" t="inlineStr">
@@ -1870,17 +1870,17 @@
       </c>
       <c r="B32" s="16" t="inlineStr">
         <is>
-          <t>38677</t>
+          <t>38937</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>Patio la Raza</t>
+          <t>Parque Tepeyac Piso 1</t>
         </is>
       </c>
       <c r="D32" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E32" s="7" t="n">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="B33" s="14" t="inlineStr">
         <is>
-          <t>38427</t>
+          <t>38590</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>Plaza Satelite</t>
+          <t>Parque Toreo II</t>
         </is>
       </c>
       <c r="D33" s="12" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="B34" s="16" t="inlineStr">
         <is>
-          <t>43132</t>
+          <t>38546</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>Plaza Vista Norte</t>
+          <t>Patio Claveria</t>
         </is>
       </c>
       <c r="D34" s="8" t="inlineStr">
@@ -1975,17 +1975,17 @@
       </c>
       <c r="B35" s="14" t="inlineStr">
         <is>
-          <t>38456</t>
+          <t>38677</t>
         </is>
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>Plaza las Flores</t>
+          <t>Patio la Raza</t>
         </is>
       </c>
       <c r="D35" s="12" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E35" s="11" t="n">
@@ -2010,12 +2010,12 @@
       </c>
       <c r="B36" s="16" t="inlineStr">
         <is>
-          <t>43152</t>
+          <t>38427</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>Samara Satélite</t>
+          <t>Plaza Satelite</t>
         </is>
       </c>
       <c r="D36" s="8" t="inlineStr">
@@ -2045,17 +2045,17 @@
       </c>
       <c r="B37" s="14" t="inlineStr">
         <is>
-          <t>38266</t>
+          <t>43132</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>San Mateo</t>
+          <t>Plaza Vista Norte</t>
         </is>
       </c>
       <c r="D37" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E37" s="11" t="n">
@@ -2080,12 +2080,12 @@
       </c>
       <c r="B38" s="16" t="inlineStr">
         <is>
-          <t>38117</t>
+          <t>43152</t>
         </is>
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>Satelite</t>
+          <t>Samara Satélite</t>
         </is>
       </c>
       <c r="D38" s="8" t="inlineStr">
@@ -2115,17 +2115,17 @@
       </c>
       <c r="B39" s="14" t="inlineStr">
         <is>
-          <t>38475</t>
+          <t>38266</t>
         </is>
       </c>
       <c r="C39" s="12" t="inlineStr">
         <is>
-          <t>Satelite Centro Civico</t>
+          <t>San Mateo</t>
         </is>
       </c>
       <c r="D39" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E39" s="11" t="n">
@@ -2150,17 +2150,17 @@
       </c>
       <c r="B40" s="16" t="inlineStr">
         <is>
-          <t>38925</t>
+          <t>38117</t>
         </is>
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>Star Medica Lomas Verdes</t>
+          <t>Satelite</t>
         </is>
       </c>
       <c r="D40" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E40" s="7" t="n">
@@ -2185,17 +2185,17 @@
       </c>
       <c r="B41" s="14" t="inlineStr">
         <is>
-          <t>38411</t>
+          <t>38475</t>
         </is>
       </c>
       <c r="C41" s="12" t="inlineStr">
         <is>
-          <t>Torres Lindavista</t>
+          <t>Satelite Centro Civico</t>
         </is>
       </c>
       <c r="D41" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E41" s="11" t="n">
@@ -2220,17 +2220,17 @@
       </c>
       <c r="B42" s="16" t="inlineStr">
         <is>
-          <t>38651</t>
+          <t>38925</t>
         </is>
       </c>
       <c r="C42" s="8" t="inlineStr">
         <is>
-          <t>Via Vallejo</t>
+          <t>Star Medica Lomas Verdes</t>
         </is>
       </c>
       <c r="D42" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E42" s="7" t="n">
@@ -2255,17 +2255,17 @@
       </c>
       <c r="B43" s="14" t="inlineStr">
         <is>
-          <t>38656</t>
+          <t>38411</t>
         </is>
       </c>
       <c r="C43" s="12" t="inlineStr">
         <is>
-          <t>Viveros de la Loma</t>
+          <t>Torres Lindavista</t>
         </is>
       </c>
       <c r="D43" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E43" s="11" t="n">
@@ -2290,12 +2290,12 @@
       </c>
       <c r="B44" s="16" t="inlineStr">
         <is>
-          <t>38142</t>
+          <t>43130</t>
         </is>
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t>Zona Esmeralda</t>
+          <t>Town Center Nicolás Romero</t>
         </is>
       </c>
       <c r="D44" s="8" t="inlineStr">
@@ -2325,24 +2325,24 @@
       </c>
       <c r="B45" s="14" t="inlineStr">
         <is>
-          <t>38186</t>
+          <t>38651</t>
         </is>
       </c>
       <c r="C45" s="12" t="inlineStr">
         <is>
-          <t>Arboledas</t>
+          <t>Via Vallejo</t>
         </is>
       </c>
       <c r="D45" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E45" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G45" s="13">
         <f>IFERROR(E45/(E45+F45),0)</f>
@@ -2360,24 +2360,24 @@
       </c>
       <c r="B46" s="16" t="inlineStr">
         <is>
-          <t>43043</t>
+          <t>38694</t>
         </is>
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t>Atizapan</t>
+          <t>Villas de la Hacienda</t>
         </is>
       </c>
       <c r="D46" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E46" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F46" s="7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G46" s="9">
         <f>IFERROR(E46/(E46+F46),0)</f>
@@ -2395,24 +2395,24 @@
       </c>
       <c r="B47" s="14" t="inlineStr">
         <is>
-          <t>38930</t>
+          <t>38656</t>
         </is>
       </c>
       <c r="C47" s="12" t="inlineStr">
         <is>
-          <t>Blvd. Aeropuerto dt</t>
+          <t>Viveros de la Loma</t>
         </is>
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E47" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G47" s="13">
         <f>IFERROR(E47/(E47+F47),0)</f>
@@ -2430,24 +2430,24 @@
       </c>
       <c r="B48" s="16" t="inlineStr">
         <is>
-          <t>38529</t>
+          <t>38115</t>
         </is>
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
-          <t>Bosques de Aragon</t>
+          <t>Zona Azul</t>
         </is>
       </c>
       <c r="D48" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E48" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F48" s="7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G48" s="9">
         <f>IFERROR(E48/(E48+F48),0)</f>
@@ -2465,24 +2465,24 @@
       </c>
       <c r="B49" s="14" t="inlineStr">
         <is>
-          <t>38837</t>
+          <t>38142</t>
         </is>
       </c>
       <c r="C49" s="12" t="inlineStr">
         <is>
-          <t>Centenario Azcapotzalco</t>
+          <t>Zona Esmeralda</t>
         </is>
       </c>
       <c r="D49" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E49" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G49" s="13">
         <f>IFERROR(E49/(E49+F49),0)</f>
@@ -2500,17 +2500,17 @@
       </c>
       <c r="B50" s="16" t="inlineStr">
         <is>
-          <t>38401</t>
+          <t>43043</t>
         </is>
       </c>
       <c r="C50" s="8" t="inlineStr">
         <is>
-          <t>Coacalco</t>
+          <t>Atizapan</t>
         </is>
       </c>
       <c r="D50" s="8" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E50" s="7" t="n">
@@ -2535,24 +2535,24 @@
       </c>
       <c r="B51" s="14" t="inlineStr">
         <is>
-          <t>43193</t>
+          <t>38930</t>
         </is>
       </c>
       <c r="C51" s="12" t="inlineStr">
         <is>
-          <t>Cosmopol N1</t>
+          <t>Blvd. Aeropuerto dt</t>
         </is>
       </c>
       <c r="D51" s="12" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E51" s="11" t="n">
         <v>0</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G51" s="13">
         <f>IFERROR(E51/(E51+F51),0)</f>
@@ -2570,12 +2570,12 @@
       </c>
       <c r="B52" s="16" t="inlineStr">
         <is>
-          <t>38903</t>
+          <t>38529</t>
         </is>
       </c>
       <c r="C52" s="8" t="inlineStr">
         <is>
-          <t>Encuentro Oceania</t>
+          <t>Bosques de Aragon</t>
         </is>
       </c>
       <c r="D52" s="8" t="inlineStr">
@@ -2605,17 +2605,17 @@
       </c>
       <c r="B53" s="14" t="inlineStr">
         <is>
-          <t>38995</t>
+          <t>38837</t>
         </is>
       </c>
       <c r="C53" s="12" t="inlineStr">
         <is>
-          <t>Encuentro Oceania II</t>
+          <t>Centenario Azcapotzalco</t>
         </is>
       </c>
       <c r="D53" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E53" s="11" t="n">
@@ -2640,17 +2640,17 @@
       </c>
       <c r="B54" s="16" t="inlineStr">
         <is>
-          <t>38507</t>
+          <t>38401</t>
         </is>
       </c>
       <c r="C54" s="8" t="inlineStr">
         <is>
-          <t>Espacio Vista del Valle</t>
+          <t>Coacalco</t>
         </is>
       </c>
       <c r="D54" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E54" s="7" t="n">
@@ -2675,24 +2675,24 @@
       </c>
       <c r="B55" s="14" t="inlineStr">
         <is>
-          <t>38230</t>
+          <t>43193</t>
         </is>
       </c>
       <c r="C55" s="12" t="inlineStr">
         <is>
-          <t>ITEMS Edo de Mexico</t>
+          <t>Cosmopol N1</t>
         </is>
       </c>
       <c r="D55" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E55" s="11" t="n">
         <v>0</v>
       </c>
       <c r="F55" s="11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G55" s="13">
         <f>IFERROR(E55/(E55+F55),0)</f>
@@ -2710,17 +2710,17 @@
       </c>
       <c r="B56" s="16" t="inlineStr">
         <is>
-          <t>38207</t>
+          <t>38903</t>
         </is>
       </c>
       <c r="C56" s="8" t="inlineStr">
         <is>
-          <t>Lindavista II</t>
+          <t>Encuentro Oceania</t>
         </is>
       </c>
       <c r="D56" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E56" s="7" t="n">
@@ -2745,17 +2745,17 @@
       </c>
       <c r="B57" s="14" t="inlineStr">
         <is>
-          <t>38270</t>
+          <t>38995</t>
         </is>
       </c>
       <c r="C57" s="12" t="inlineStr">
         <is>
-          <t>Lomas Verdes II</t>
+          <t>Encuentro Oceania II</t>
         </is>
       </c>
       <c r="D57" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E57" s="11" t="n">
@@ -2780,17 +2780,17 @@
       </c>
       <c r="B58" s="16" t="inlineStr">
         <is>
-          <t>38371</t>
+          <t>38507</t>
         </is>
       </c>
       <c r="C58" s="8" t="inlineStr">
         <is>
-          <t>Montevideo DT</t>
+          <t>Espacio Vista del Valle</t>
         </is>
       </c>
       <c r="D58" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E58" s="7" t="n">
@@ -2815,12 +2815,12 @@
       </c>
       <c r="B59" s="14" t="inlineStr">
         <is>
-          <t>38674</t>
+          <t>38230</t>
         </is>
       </c>
       <c r="C59" s="12" t="inlineStr">
         <is>
-          <t>Mundo E</t>
+          <t>ITEMS Edo de Mexico</t>
         </is>
       </c>
       <c r="D59" s="12" t="inlineStr">
@@ -2850,17 +2850,17 @@
       </c>
       <c r="B60" s="16" t="inlineStr">
         <is>
-          <t>38845</t>
+          <t>38270</t>
         </is>
       </c>
       <c r="C60" s="8" t="inlineStr">
         <is>
-          <t>Mundo E II</t>
+          <t>Lomas Verdes II</t>
         </is>
       </c>
       <c r="D60" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E60" s="7" t="n">
@@ -2885,17 +2885,17 @@
       </c>
       <c r="B61" s="14" t="inlineStr">
         <is>
-          <t>38965</t>
+          <t>38371</t>
         </is>
       </c>
       <c r="C61" s="12" t="inlineStr">
         <is>
-          <t>Parque Tepeyac Piso 2</t>
+          <t>Montevideo DT</t>
         </is>
       </c>
       <c r="D61" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E61" s="11" t="n">
@@ -2920,12 +2920,12 @@
       </c>
       <c r="B62" s="16" t="inlineStr">
         <is>
-          <t>38792</t>
+          <t>38674</t>
         </is>
       </c>
       <c r="C62" s="8" t="inlineStr">
         <is>
-          <t>Pasaje Tlanepantla</t>
+          <t>Mundo E</t>
         </is>
       </c>
       <c r="D62" s="8" t="inlineStr">
@@ -2955,17 +2955,17 @@
       </c>
       <c r="B63" s="14" t="inlineStr">
         <is>
-          <t>38515</t>
+          <t>38845</t>
         </is>
       </c>
       <c r="C63" s="12" t="inlineStr">
         <is>
-          <t>Patio Ecatepec</t>
+          <t>Mundo E II</t>
         </is>
       </c>
       <c r="D63" s="12" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E63" s="11" t="n">
@@ -2990,17 +2990,17 @@
       </c>
       <c r="B64" s="16" t="inlineStr">
         <is>
-          <t>38176</t>
+          <t>38965</t>
         </is>
       </c>
       <c r="C64" s="8" t="inlineStr">
         <is>
-          <t>Periferico Satélite DT</t>
+          <t>Parque Tepeyac Piso 2</t>
         </is>
       </c>
       <c r="D64" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E64" s="7" t="n">
@@ -3025,17 +3025,17 @@
       </c>
       <c r="B65" s="14" t="inlineStr">
         <is>
-          <t>38924</t>
+          <t>38792</t>
         </is>
       </c>
       <c r="C65" s="12" t="inlineStr">
         <is>
-          <t>Plaza Aeropuerto</t>
+          <t>Pasaje Tlanepantla</t>
         </is>
       </c>
       <c r="D65" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E65" s="11" t="n">
@@ -3060,17 +3060,17 @@
       </c>
       <c r="B66" s="16" t="inlineStr">
         <is>
-          <t>38719</t>
+          <t>38515</t>
         </is>
       </c>
       <c r="C66" s="8" t="inlineStr">
         <is>
-          <t>Plaza Fortuna</t>
+          <t>Patio Ecatepec</t>
         </is>
       </c>
       <c r="D66" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E66" s="7" t="n">
@@ -3095,12 +3095,12 @@
       </c>
       <c r="B67" s="14" t="inlineStr">
         <is>
-          <t>38859</t>
+          <t>38176</t>
         </is>
       </c>
       <c r="C67" s="12" t="inlineStr">
         <is>
-          <t>Plaza Satelite II N1</t>
+          <t>Periferico Satélite DT</t>
         </is>
       </c>
       <c r="D67" s="12" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="B68" s="16" t="inlineStr">
         <is>
-          <t>38811</t>
+          <t>38924</t>
         </is>
       </c>
       <c r="C68" s="8" t="inlineStr">
         <is>
-          <t>Plaza Tepeyac</t>
+          <t>Plaza Aeropuerto</t>
         </is>
       </c>
       <c r="D68" s="8" t="inlineStr">
@@ -3165,17 +3165,17 @@
       </c>
       <c r="B69" s="14" t="inlineStr">
         <is>
-          <t>38136</t>
+          <t>38719</t>
         </is>
       </c>
       <c r="C69" s="12" t="inlineStr">
         <is>
-          <t>Punta Norte</t>
+          <t>Plaza Fortuna</t>
         </is>
       </c>
       <c r="D69" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E69" s="11" t="n">
@@ -3200,17 +3200,17 @@
       </c>
       <c r="B70" s="16" t="inlineStr">
         <is>
-          <t>38460</t>
+          <t>38859</t>
         </is>
       </c>
       <c r="C70" s="8" t="inlineStr">
         <is>
-          <t>Santa Monica</t>
+          <t>Plaza Satelite II N1</t>
         </is>
       </c>
       <c r="D70" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E70" s="7" t="n">
@@ -3235,17 +3235,17 @@
       </c>
       <c r="B71" s="14" t="inlineStr">
         <is>
-          <t>38442</t>
+          <t>38811</t>
         </is>
       </c>
       <c r="C71" s="12" t="inlineStr">
         <is>
-          <t>Sor Juana</t>
+          <t>Plaza Tepeyac</t>
         </is>
       </c>
       <c r="D71" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E71" s="11" t="n">
@@ -3270,17 +3270,17 @@
       </c>
       <c r="B72" s="16" t="inlineStr">
         <is>
-          <t>38992</t>
+          <t>38136</t>
         </is>
       </c>
       <c r="C72" s="8" t="inlineStr">
         <is>
-          <t>Tapo Puerta Oriente</t>
+          <t>Punta Norte</t>
         </is>
       </c>
       <c r="D72" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E72" s="7" t="n">
@@ -3305,17 +3305,17 @@
       </c>
       <c r="B73" s="14" t="inlineStr">
         <is>
-          <t>43130</t>
+          <t>38460</t>
         </is>
       </c>
       <c r="C73" s="12" t="inlineStr">
         <is>
-          <t>Town Center Nicolás Romero</t>
+          <t>Santa Monica</t>
         </is>
       </c>
       <c r="D73" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E73" s="11" t="n">
@@ -3340,12 +3340,12 @@
       </c>
       <c r="B74" s="16" t="inlineStr">
         <is>
-          <t>38374</t>
+          <t>38442</t>
         </is>
       </c>
       <c r="C74" s="8" t="inlineStr">
         <is>
-          <t>Valle Dorado</t>
+          <t>Sor Juana</t>
         </is>
       </c>
       <c r="D74" s="8" t="inlineStr">
@@ -3375,17 +3375,17 @@
       </c>
       <c r="B75" s="14" t="inlineStr">
         <is>
-          <t>38694</t>
+          <t>38992</t>
         </is>
       </c>
       <c r="C75" s="12" t="inlineStr">
         <is>
-          <t>Villas de la Hacienda</t>
+          <t>Tapo Puerta Oriente</t>
         </is>
       </c>
       <c r="D75" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E75" s="11" t="n">
@@ -3410,17 +3410,17 @@
       </c>
       <c r="B76" s="16" t="inlineStr">
         <is>
-          <t>38115</t>
+          <t>38374</t>
         </is>
       </c>
       <c r="C76" s="8" t="inlineStr">
         <is>
-          <t>Zona Azul</t>
+          <t>Valle Dorado</t>
         </is>
       </c>
       <c r="D76" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E76" s="7" t="n">
@@ -3488,7 +3488,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Centro Norte · Corte 30/08/2026 17:01</t>
+          <t>Centro Norte · Corte 30/08/2026 17:24</t>
         </is>
       </c>
     </row>
@@ -3709,10 +3709,10 @@
         </is>
       </c>
       <c r="C12" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E12" s="9">
         <f>IFERROR(C12/(C12+D12),0)</f>
@@ -3759,10 +3759,10 @@
         </is>
       </c>
       <c r="C14" s="7" t="n">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="E14" s="9">
         <f>IFERROR(C14/(C14+D14),0)</f>

--- a/exports/Resumen_Evidencias_OPS.xlsx
+++ b/exports/Resumen_Evidencias_OPS.xlsx
@@ -577,7 +577,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Centro Norte · Corte 30/08/2026 17:24</t>
+          <t>Centro Norte · Corte 30/08/2026 17:57</t>
         </is>
       </c>
     </row>
@@ -600,10 +600,10 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>654</v>
+        <v>649</v>
       </c>
       <c r="E6" s="5">
         <f>IFERROR(A6/(A6+C6),0)</f>
@@ -661,10 +661,10 @@
         <v>10</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="F10" s="9">
         <f>IFERROR(D10/(D10+E10),0)</f>
@@ -689,10 +689,10 @@
         <v>13</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E11" s="12" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F11" s="13">
         <f>IFERROR(D11/(D11+E11),0)</f>
@@ -873,7 +873,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Centro Norte · Corte 30/08/2026 17:24</t>
+          <t>Centro Norte · Corte 30/08/2026 17:57</t>
         </is>
       </c>
     </row>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="B8" s="16" t="inlineStr">
         <is>
-          <t>38894</t>
+          <t>38401</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>Galerias Perinorte</t>
+          <t>Coacalco</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
@@ -1065,12 +1065,12 @@
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>38333</t>
+          <t>38894</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>Izcalli Mega</t>
+          <t>Galerias Perinorte</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
@@ -1100,12 +1100,12 @@
       </c>
       <c r="B10" s="16" t="inlineStr">
         <is>
-          <t>38862</t>
+          <t>38333</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>San Miguel Izcalli</t>
+          <t>Izcalli Mega</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
@@ -1149,10 +1149,10 @@
         </is>
       </c>
       <c r="E11" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G11" s="13">
         <f>IFERROR(E11/(E11+F11),0)</f>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="B12" s="16" t="inlineStr">
         <is>
-          <t>38456</t>
+          <t>38862</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Plaza las Flores</t>
+          <t>San Miguel Izcalli</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
@@ -1184,10 +1184,10 @@
         </is>
       </c>
       <c r="E12" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F12" s="7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G12" s="9">
         <f>IFERROR(E12/(E12+F12),0)</f>
@@ -1205,17 +1205,17 @@
       </c>
       <c r="B13" s="14" t="inlineStr">
         <is>
-          <t>38606</t>
+          <t>38456</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>TlalnepantlaCarso</t>
+          <t>Plaza las Flores</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E13" s="11" t="n">
@@ -1240,12 +1240,12 @@
       </c>
       <c r="B14" s="16" t="inlineStr">
         <is>
-          <t>38186</t>
+          <t>38606</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Arboledas</t>
+          <t>TlalnepantlaCarso</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr">
@@ -1254,10 +1254,10 @@
         </is>
       </c>
       <c r="E14" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F14" s="7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G14" s="9">
         <f>IFERROR(E14/(E14+F14),0)</f>
@@ -1275,17 +1275,17 @@
       </c>
       <c r="B15" s="14" t="inlineStr">
         <is>
-          <t>43194</t>
+          <t>38186</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>Atana Lindavista</t>
+          <t>Arboledas</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E15" s="11" t="n">
@@ -1310,17 +1310,17 @@
       </c>
       <c r="B16" s="16" t="inlineStr">
         <is>
-          <t>38149</t>
+          <t>43194</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>Bellavista</t>
+          <t>Atana Lindavista</t>
         </is>
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E16" s="7" t="n">
@@ -1345,17 +1345,17 @@
       </c>
       <c r="B17" s="14" t="inlineStr">
         <is>
-          <t>38527</t>
+          <t>38149</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>Camarones</t>
+          <t>Bellavista</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E17" s="11" t="n">
@@ -1380,17 +1380,17 @@
       </c>
       <c r="B18" s="16" t="inlineStr">
         <is>
-          <t>38394</t>
+          <t>38527</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>Centro Comercial Lomas Verdes</t>
+          <t>Camarones</t>
         </is>
       </c>
       <c r="D18" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E18" s="7" t="n">
@@ -1415,12 +1415,12 @@
       </c>
       <c r="B19" s="14" t="inlineStr">
         <is>
-          <t>38535</t>
+          <t>38394</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>City Center Esmeralda</t>
+          <t>Centro Comercial Lomas Verdes</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
@@ -1450,17 +1450,17 @@
       </c>
       <c r="B20" s="16" t="inlineStr">
         <is>
-          <t>38604</t>
+          <t>38535</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>Cosmopol</t>
+          <t>City Center Esmeralda</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E20" s="7" t="n">
@@ -1485,17 +1485,17 @@
       </c>
       <c r="B21" s="14" t="inlineStr">
         <is>
-          <t>38197</t>
+          <t>38604</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>Echegaray</t>
+          <t>Cosmopol</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E21" s="11" t="n">
@@ -1520,17 +1520,17 @@
       </c>
       <c r="B22" s="16" t="inlineStr">
         <is>
-          <t>38431</t>
+          <t>38197</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>Eduardo Molina</t>
+          <t>Echegaray</t>
         </is>
       </c>
       <c r="D22" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E22" s="7" t="n">
@@ -1555,17 +1555,17 @@
       </c>
       <c r="B23" s="14" t="inlineStr">
         <is>
-          <t>38458</t>
+          <t>38431</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>El Rosario</t>
+          <t>Eduardo Molina</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E23" s="11" t="n">
@@ -1590,17 +1590,17 @@
       </c>
       <c r="B24" s="16" t="inlineStr">
         <is>
-          <t>38363</t>
+          <t>38458</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>Galerias Atizapan</t>
+          <t>El Rosario</t>
         </is>
       </c>
       <c r="D24" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E24" s="7" t="n">
@@ -1625,17 +1625,17 @@
       </c>
       <c r="B25" s="14" t="inlineStr">
         <is>
-          <t>38770</t>
+          <t>38363</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>Gustavo Baz 29</t>
+          <t>Galerias Atizapan</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E25" s="11" t="n">
@@ -1660,17 +1660,17 @@
       </c>
       <c r="B26" s="16" t="inlineStr">
         <is>
-          <t>38661</t>
+          <t>38770</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>Jinetes</t>
+          <t>Gustavo Baz 29</t>
         </is>
       </c>
       <c r="D26" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E26" s="7" t="n">
@@ -1695,17 +1695,17 @@
       </c>
       <c r="B27" s="14" t="inlineStr">
         <is>
-          <t>38205</t>
+          <t>38661</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>Lindavista</t>
+          <t>Jinetes</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E27" s="11" t="n">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="B28" s="16" t="inlineStr">
         <is>
-          <t>38207</t>
+          <t>38205</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>Lindavista II</t>
+          <t>Lindavista</t>
         </is>
       </c>
       <c r="D28" s="8" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="B29" s="14" t="inlineStr">
         <is>
-          <t>38119</t>
+          <t>38207</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>Lomas Verdes</t>
+          <t>Lindavista II</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E29" s="11" t="n">
@@ -1800,17 +1800,17 @@
       </c>
       <c r="B30" s="16" t="inlineStr">
         <is>
-          <t>43111</t>
+          <t>38119</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>Montevideo Insurgentes</t>
+          <t>Lomas Verdes</t>
         </is>
       </c>
       <c r="D30" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E30" s="7" t="n">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="B31" s="14" t="inlineStr">
         <is>
-          <t>43195</t>
+          <t>43111</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>Parque Jadin kiosko</t>
+          <t>Montevideo Insurgentes</t>
         </is>
       </c>
       <c r="D31" s="12" t="inlineStr">
@@ -1870,17 +1870,17 @@
       </c>
       <c r="B32" s="16" t="inlineStr">
         <is>
-          <t>38937</t>
+          <t>43195</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>Parque Tepeyac Piso 1</t>
+          <t>Parque Jadin kiosko</t>
         </is>
       </c>
       <c r="D32" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E32" s="7" t="n">
@@ -1905,17 +1905,17 @@
       </c>
       <c r="B33" s="14" t="inlineStr">
         <is>
-          <t>38590</t>
+          <t>38937</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>Parque Toreo II</t>
+          <t>Parque Tepeyac Piso 1</t>
         </is>
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E33" s="11" t="n">
@@ -1940,17 +1940,17 @@
       </c>
       <c r="B34" s="16" t="inlineStr">
         <is>
-          <t>38546</t>
+          <t>38590</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>Patio Claveria</t>
+          <t>Parque Toreo II</t>
         </is>
       </c>
       <c r="D34" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E34" s="7" t="n">
@@ -1975,12 +1975,12 @@
       </c>
       <c r="B35" s="14" t="inlineStr">
         <is>
-          <t>38677</t>
+          <t>38546</t>
         </is>
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>Patio la Raza</t>
+          <t>Patio Claveria</t>
         </is>
       </c>
       <c r="D35" s="12" t="inlineStr">
@@ -2010,17 +2010,17 @@
       </c>
       <c r="B36" s="16" t="inlineStr">
         <is>
-          <t>38427</t>
+          <t>38677</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>Plaza Satelite</t>
+          <t>Patio la Raza</t>
         </is>
       </c>
       <c r="D36" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E36" s="7" t="n">
@@ -2045,17 +2045,17 @@
       </c>
       <c r="B37" s="14" t="inlineStr">
         <is>
-          <t>43132</t>
+          <t>38427</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>Plaza Vista Norte</t>
+          <t>Plaza Satelite</t>
         </is>
       </c>
       <c r="D37" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E37" s="11" t="n">
@@ -2080,12 +2080,12 @@
       </c>
       <c r="B38" s="16" t="inlineStr">
         <is>
-          <t>43152</t>
+          <t>38859</t>
         </is>
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>Samara Satélite</t>
+          <t>Plaza Satelite II N1</t>
         </is>
       </c>
       <c r="D38" s="8" t="inlineStr">
@@ -2115,17 +2115,17 @@
       </c>
       <c r="B39" s="14" t="inlineStr">
         <is>
-          <t>38266</t>
+          <t>43132</t>
         </is>
       </c>
       <c r="C39" s="12" t="inlineStr">
         <is>
-          <t>San Mateo</t>
+          <t>Plaza Vista Norte</t>
         </is>
       </c>
       <c r="D39" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E39" s="11" t="n">
@@ -2150,12 +2150,12 @@
       </c>
       <c r="B40" s="16" t="inlineStr">
         <is>
-          <t>38117</t>
+          <t>43152</t>
         </is>
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>Satelite</t>
+          <t>Samara Satélite</t>
         </is>
       </c>
       <c r="D40" s="8" t="inlineStr">
@@ -2185,17 +2185,17 @@
       </c>
       <c r="B41" s="14" t="inlineStr">
         <is>
-          <t>38475</t>
+          <t>38266</t>
         </is>
       </c>
       <c r="C41" s="12" t="inlineStr">
         <is>
-          <t>Satelite Centro Civico</t>
+          <t>San Mateo</t>
         </is>
       </c>
       <c r="D41" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E41" s="11" t="n">
@@ -2220,17 +2220,17 @@
       </c>
       <c r="B42" s="16" t="inlineStr">
         <is>
-          <t>38925</t>
+          <t>38117</t>
         </is>
       </c>
       <c r="C42" s="8" t="inlineStr">
         <is>
-          <t>Star Medica Lomas Verdes</t>
+          <t>Satelite</t>
         </is>
       </c>
       <c r="D42" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E42" s="7" t="n">
@@ -2255,17 +2255,17 @@
       </c>
       <c r="B43" s="14" t="inlineStr">
         <is>
-          <t>38411</t>
+          <t>38475</t>
         </is>
       </c>
       <c r="C43" s="12" t="inlineStr">
         <is>
-          <t>Torres Lindavista</t>
+          <t>Satelite Centro Civico</t>
         </is>
       </c>
       <c r="D43" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E43" s="11" t="n">
@@ -2290,12 +2290,12 @@
       </c>
       <c r="B44" s="16" t="inlineStr">
         <is>
-          <t>43130</t>
+          <t>38925</t>
         </is>
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t>Town Center Nicolás Romero</t>
+          <t>Star Medica Lomas Verdes</t>
         </is>
       </c>
       <c r="D44" s="8" t="inlineStr">
@@ -2325,12 +2325,12 @@
       </c>
       <c r="B45" s="14" t="inlineStr">
         <is>
-          <t>38651</t>
+          <t>38411</t>
         </is>
       </c>
       <c r="C45" s="12" t="inlineStr">
         <is>
-          <t>Via Vallejo</t>
+          <t>Torres Lindavista</t>
         </is>
       </c>
       <c r="D45" s="12" t="inlineStr">
@@ -2360,17 +2360,17 @@
       </c>
       <c r="B46" s="16" t="inlineStr">
         <is>
-          <t>38694</t>
+          <t>43130</t>
         </is>
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t>Villas de la Hacienda</t>
+          <t>Town Center Nicolás Romero</t>
         </is>
       </c>
       <c r="D46" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E46" s="7" t="n">
@@ -2395,17 +2395,17 @@
       </c>
       <c r="B47" s="14" t="inlineStr">
         <is>
-          <t>38656</t>
+          <t>38651</t>
         </is>
       </c>
       <c r="C47" s="12" t="inlineStr">
         <is>
-          <t>Viveros de la Loma</t>
+          <t>Via Vallejo</t>
         </is>
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E47" s="11" t="n">
@@ -2430,17 +2430,17 @@
       </c>
       <c r="B48" s="16" t="inlineStr">
         <is>
-          <t>38115</t>
+          <t>38694</t>
         </is>
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
-          <t>Zona Azul</t>
+          <t>Villas de la Hacienda</t>
         </is>
       </c>
       <c r="D48" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E48" s="7" t="n">
@@ -2465,17 +2465,17 @@
       </c>
       <c r="B49" s="14" t="inlineStr">
         <is>
-          <t>38142</t>
+          <t>38656</t>
         </is>
       </c>
       <c r="C49" s="12" t="inlineStr">
         <is>
-          <t>Zona Esmeralda</t>
+          <t>Viveros de la Loma</t>
         </is>
       </c>
       <c r="D49" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E49" s="11" t="n">
@@ -2500,12 +2500,12 @@
       </c>
       <c r="B50" s="16" t="inlineStr">
         <is>
-          <t>43043</t>
+          <t>38115</t>
         </is>
       </c>
       <c r="C50" s="8" t="inlineStr">
         <is>
-          <t>Atizapan</t>
+          <t>Zona Azul</t>
         </is>
       </c>
       <c r="D50" s="8" t="inlineStr">
@@ -2514,10 +2514,10 @@
         </is>
       </c>
       <c r="E50" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F50" s="7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G50" s="9">
         <f>IFERROR(E50/(E50+F50),0)</f>
@@ -2535,24 +2535,24 @@
       </c>
       <c r="B51" s="14" t="inlineStr">
         <is>
-          <t>38930</t>
+          <t>38142</t>
         </is>
       </c>
       <c r="C51" s="12" t="inlineStr">
         <is>
-          <t>Blvd. Aeropuerto dt</t>
+          <t>Zona Esmeralda</t>
         </is>
       </c>
       <c r="D51" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E51" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G51" s="13">
         <f>IFERROR(E51/(E51+F51),0)</f>
@@ -2570,17 +2570,17 @@
       </c>
       <c r="B52" s="16" t="inlineStr">
         <is>
-          <t>38529</t>
+          <t>43043</t>
         </is>
       </c>
       <c r="C52" s="8" t="inlineStr">
         <is>
-          <t>Bosques de Aragon</t>
+          <t>Atizapan</t>
         </is>
       </c>
       <c r="D52" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E52" s="7" t="n">
@@ -2605,17 +2605,17 @@
       </c>
       <c r="B53" s="14" t="inlineStr">
         <is>
-          <t>38837</t>
+          <t>38930</t>
         </is>
       </c>
       <c r="C53" s="12" t="inlineStr">
         <is>
-          <t>Centenario Azcapotzalco</t>
+          <t>Blvd. Aeropuerto dt</t>
         </is>
       </c>
       <c r="D53" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E53" s="11" t="n">
@@ -2640,17 +2640,17 @@
       </c>
       <c r="B54" s="16" t="inlineStr">
         <is>
-          <t>38401</t>
+          <t>38529</t>
         </is>
       </c>
       <c r="C54" s="8" t="inlineStr">
         <is>
-          <t>Coacalco</t>
+          <t>Bosques de Aragon</t>
         </is>
       </c>
       <c r="D54" s="8" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E54" s="7" t="n">
@@ -2675,24 +2675,24 @@
       </c>
       <c r="B55" s="14" t="inlineStr">
         <is>
-          <t>43193</t>
+          <t>38837</t>
         </is>
       </c>
       <c r="C55" s="12" t="inlineStr">
         <is>
-          <t>Cosmopol N1</t>
+          <t>Centenario Azcapotzalco</t>
         </is>
       </c>
       <c r="D55" s="12" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E55" s="11" t="n">
         <v>0</v>
       </c>
       <c r="F55" s="11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G55" s="13">
         <f>IFERROR(E55/(E55+F55),0)</f>
@@ -2710,24 +2710,24 @@
       </c>
       <c r="B56" s="16" t="inlineStr">
         <is>
-          <t>38903</t>
+          <t>43193</t>
         </is>
       </c>
       <c r="C56" s="8" t="inlineStr">
         <is>
-          <t>Encuentro Oceania</t>
+          <t>Cosmopol N1</t>
         </is>
       </c>
       <c r="D56" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E56" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F56" s="7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G56" s="9">
         <f>IFERROR(E56/(E56+F56),0)</f>
@@ -2745,12 +2745,12 @@
       </c>
       <c r="B57" s="14" t="inlineStr">
         <is>
-          <t>38995</t>
+          <t>38903</t>
         </is>
       </c>
       <c r="C57" s="12" t="inlineStr">
         <is>
-          <t>Encuentro Oceania II</t>
+          <t>Encuentro Oceania</t>
         </is>
       </c>
       <c r="D57" s="12" t="inlineStr">
@@ -2780,17 +2780,17 @@
       </c>
       <c r="B58" s="16" t="inlineStr">
         <is>
-          <t>38507</t>
+          <t>38995</t>
         </is>
       </c>
       <c r="C58" s="8" t="inlineStr">
         <is>
-          <t>Espacio Vista del Valle</t>
+          <t>Encuentro Oceania II</t>
         </is>
       </c>
       <c r="D58" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E58" s="7" t="n">
@@ -2815,17 +2815,17 @@
       </c>
       <c r="B59" s="14" t="inlineStr">
         <is>
-          <t>38230</t>
+          <t>38507</t>
         </is>
       </c>
       <c r="C59" s="12" t="inlineStr">
         <is>
-          <t>ITEMS Edo de Mexico</t>
+          <t>Espacio Vista del Valle</t>
         </is>
       </c>
       <c r="D59" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E59" s="11" t="n">
@@ -2850,17 +2850,17 @@
       </c>
       <c r="B60" s="16" t="inlineStr">
         <is>
-          <t>38270</t>
+          <t>38230</t>
         </is>
       </c>
       <c r="C60" s="8" t="inlineStr">
         <is>
-          <t>Lomas Verdes II</t>
+          <t>ITEMS Edo de Mexico</t>
         </is>
       </c>
       <c r="D60" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E60" s="7" t="n">
@@ -2885,17 +2885,17 @@
       </c>
       <c r="B61" s="14" t="inlineStr">
         <is>
-          <t>38371</t>
+          <t>38270</t>
         </is>
       </c>
       <c r="C61" s="12" t="inlineStr">
         <is>
-          <t>Montevideo DT</t>
+          <t>Lomas Verdes II</t>
         </is>
       </c>
       <c r="D61" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E61" s="11" t="n">
@@ -2920,17 +2920,17 @@
       </c>
       <c r="B62" s="16" t="inlineStr">
         <is>
-          <t>38674</t>
+          <t>38371</t>
         </is>
       </c>
       <c r="C62" s="8" t="inlineStr">
         <is>
-          <t>Mundo E</t>
+          <t>Montevideo DT</t>
         </is>
       </c>
       <c r="D62" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E62" s="7" t="n">
@@ -2955,12 +2955,12 @@
       </c>
       <c r="B63" s="14" t="inlineStr">
         <is>
-          <t>38845</t>
+          <t>38674</t>
         </is>
       </c>
       <c r="C63" s="12" t="inlineStr">
         <is>
-          <t>Mundo E II</t>
+          <t>Mundo E</t>
         </is>
       </c>
       <c r="D63" s="12" t="inlineStr">
@@ -2990,17 +2990,17 @@
       </c>
       <c r="B64" s="16" t="inlineStr">
         <is>
-          <t>38965</t>
+          <t>38845</t>
         </is>
       </c>
       <c r="C64" s="8" t="inlineStr">
         <is>
-          <t>Parque Tepeyac Piso 2</t>
+          <t>Mundo E II</t>
         </is>
       </c>
       <c r="D64" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E64" s="7" t="n">
@@ -3025,17 +3025,17 @@
       </c>
       <c r="B65" s="14" t="inlineStr">
         <is>
-          <t>38792</t>
+          <t>38965</t>
         </is>
       </c>
       <c r="C65" s="12" t="inlineStr">
         <is>
-          <t>Pasaje Tlanepantla</t>
+          <t>Parque Tepeyac Piso 2</t>
         </is>
       </c>
       <c r="D65" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E65" s="11" t="n">
@@ -3060,17 +3060,17 @@
       </c>
       <c r="B66" s="16" t="inlineStr">
         <is>
-          <t>38515</t>
+          <t>38792</t>
         </is>
       </c>
       <c r="C66" s="8" t="inlineStr">
         <is>
-          <t>Patio Ecatepec</t>
+          <t>Pasaje Tlanepantla</t>
         </is>
       </c>
       <c r="D66" s="8" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E66" s="7" t="n">
@@ -3095,17 +3095,17 @@
       </c>
       <c r="B67" s="14" t="inlineStr">
         <is>
-          <t>38176</t>
+          <t>38515</t>
         </is>
       </c>
       <c r="C67" s="12" t="inlineStr">
         <is>
-          <t>Periferico Satélite DT</t>
+          <t>Patio Ecatepec</t>
         </is>
       </c>
       <c r="D67" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E67" s="11" t="n">
@@ -3130,17 +3130,17 @@
       </c>
       <c r="B68" s="16" t="inlineStr">
         <is>
-          <t>38924</t>
+          <t>38176</t>
         </is>
       </c>
       <c r="C68" s="8" t="inlineStr">
         <is>
-          <t>Plaza Aeropuerto</t>
+          <t>Periferico Satélite DT</t>
         </is>
       </c>
       <c r="D68" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E68" s="7" t="n">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="B69" s="14" t="inlineStr">
         <is>
-          <t>38719</t>
+          <t>38924</t>
         </is>
       </c>
       <c r="C69" s="12" t="inlineStr">
         <is>
-          <t>Plaza Fortuna</t>
+          <t>Plaza Aeropuerto</t>
         </is>
       </c>
       <c r="D69" s="12" t="inlineStr">
@@ -3200,17 +3200,17 @@
       </c>
       <c r="B70" s="16" t="inlineStr">
         <is>
-          <t>38859</t>
+          <t>38719</t>
         </is>
       </c>
       <c r="C70" s="8" t="inlineStr">
         <is>
-          <t>Plaza Satelite II N1</t>
+          <t>Plaza Fortuna</t>
         </is>
       </c>
       <c r="D70" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E70" s="7" t="n">
@@ -3488,7 +3488,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Centro Norte · Corte 30/08/2026 17:24</t>
+          <t>Centro Norte · Corte 30/08/2026 17:57</t>
         </is>
       </c>
     </row>
@@ -3534,10 +3534,10 @@
         </is>
       </c>
       <c r="C5" s="11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E5" s="13">
         <f>IFERROR(C5/(C5+D5),0)</f>
@@ -3634,10 +3634,10 @@
         </is>
       </c>
       <c r="C9" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D9" s="11" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E9" s="13">
         <f>IFERROR(C9/(C9+D9),0)</f>
@@ -3659,10 +3659,10 @@
         </is>
       </c>
       <c r="C10" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E10" s="9">
         <f>IFERROR(C10/(C10+D10),0)</f>
@@ -3709,10 +3709,10 @@
         </is>
       </c>
       <c r="C12" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E12" s="9">
         <f>IFERROR(C12/(C12+D12),0)</f>

--- a/exports/Resumen_Evidencias_OPS.xlsx
+++ b/exports/Resumen_Evidencias_OPS.xlsx
@@ -577,7 +577,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Centro Norte · Corte 30/08/2026 17:57</t>
+          <t>Centro Norte · Corte 30/08/2026 18:14</t>
         </is>
       </c>
     </row>
@@ -600,10 +600,10 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="E6" s="5">
         <f>IFERROR(A6/(A6+C6),0)</f>
@@ -661,10 +661,10 @@
         <v>10</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F10" s="9">
         <f>IFERROR(D10/(D10+E10),0)</f>
@@ -773,10 +773,10 @@
         <v>12</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E14" s="8" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F14" s="9">
         <f>IFERROR(D14/(D14+E14),0)</f>
@@ -873,7 +873,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Centro Norte · Corte 30/08/2026 17:57</t>
+          <t>Centro Norte · Corte 30/08/2026 18:14</t>
         </is>
       </c>
     </row>
@@ -995,12 +995,12 @@
       </c>
       <c r="B7" s="14" t="inlineStr">
         <is>
-          <t>38339</t>
+          <t>38333</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Izcalli Mega</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="B8" s="16" t="inlineStr">
         <is>
-          <t>38401</t>
+          <t>38339</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>Coacalco</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
@@ -1044,18 +1044,18 @@
         </is>
       </c>
       <c r="E8" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G8" s="9">
         <f>IFERROR(E8/(E8+F8),0)</f>
         <v/>
       </c>
-      <c r="H8" s="10" t="inlineStr">
-        <is>
-          <t>Atención</t>
+      <c r="H8" s="15" t="inlineStr">
+        <is>
+          <t>Seguimiento</t>
         </is>
       </c>
     </row>
@@ -1065,12 +1065,12 @@
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>38894</t>
+          <t>38401</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>Galerias Perinorte</t>
+          <t>Coacalco</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
@@ -1100,12 +1100,12 @@
       </c>
       <c r="B10" s="16" t="inlineStr">
         <is>
-          <t>38333</t>
+          <t>38894</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>Izcalli Mega</t>
+          <t>Galerias Perinorte</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
@@ -1205,12 +1205,12 @@
       </c>
       <c r="B13" s="14" t="inlineStr">
         <is>
-          <t>38456</t>
+          <t>38604</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>Plaza las Flores</t>
+          <t>Cosmopol</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
@@ -1240,17 +1240,17 @@
       </c>
       <c r="B14" s="16" t="inlineStr">
         <is>
-          <t>38606</t>
+          <t>38456</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>TlalnepantlaCarso</t>
+          <t>Plaza las Flores</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E14" s="7" t="n">
@@ -1275,12 +1275,12 @@
       </c>
       <c r="B15" s="14" t="inlineStr">
         <is>
-          <t>38186</t>
+          <t>38606</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>Arboledas</t>
+          <t>TlalnepantlaCarso</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
@@ -1289,10 +1289,10 @@
         </is>
       </c>
       <c r="E15" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G15" s="13">
         <f>IFERROR(E15/(E15+F15),0)</f>
@@ -1310,17 +1310,17 @@
       </c>
       <c r="B16" s="16" t="inlineStr">
         <is>
-          <t>43194</t>
+          <t>38186</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>Atana Lindavista</t>
+          <t>Arboledas</t>
         </is>
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E16" s="7" t="n">
@@ -1345,17 +1345,17 @@
       </c>
       <c r="B17" s="14" t="inlineStr">
         <is>
-          <t>38149</t>
+          <t>43194</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>Bellavista</t>
+          <t>Atana Lindavista</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E17" s="11" t="n">
@@ -1380,17 +1380,17 @@
       </c>
       <c r="B18" s="16" t="inlineStr">
         <is>
-          <t>38527</t>
+          <t>38149</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>Camarones</t>
+          <t>Bellavista</t>
         </is>
       </c>
       <c r="D18" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E18" s="7" t="n">
@@ -1415,17 +1415,17 @@
       </c>
       <c r="B19" s="14" t="inlineStr">
         <is>
-          <t>38394</t>
+          <t>38527</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>Centro Comercial Lomas Verdes</t>
+          <t>Camarones</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E19" s="11" t="n">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="B20" s="16" t="inlineStr">
         <is>
-          <t>38535</t>
+          <t>38394</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>City Center Esmeralda</t>
+          <t>Centro Comercial Lomas Verdes</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr">
@@ -1485,17 +1485,17 @@
       </c>
       <c r="B21" s="14" t="inlineStr">
         <is>
-          <t>38604</t>
+          <t>38535</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>Cosmopol</t>
+          <t>City Center Esmeralda</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E21" s="11" t="n">
@@ -2290,17 +2290,17 @@
       </c>
       <c r="B44" s="16" t="inlineStr">
         <is>
-          <t>38925</t>
+          <t>38442</t>
         </is>
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t>Star Medica Lomas Verdes</t>
+          <t>Sor Juana</t>
         </is>
       </c>
       <c r="D44" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E44" s="7" t="n">
@@ -2325,17 +2325,17 @@
       </c>
       <c r="B45" s="14" t="inlineStr">
         <is>
-          <t>38411</t>
+          <t>38925</t>
         </is>
       </c>
       <c r="C45" s="12" t="inlineStr">
         <is>
-          <t>Torres Lindavista</t>
+          <t>Star Medica Lomas Verdes</t>
         </is>
       </c>
       <c r="D45" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E45" s="11" t="n">
@@ -2360,17 +2360,17 @@
       </c>
       <c r="B46" s="16" t="inlineStr">
         <is>
-          <t>43130</t>
+          <t>38411</t>
         </is>
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t>Town Center Nicolás Romero</t>
+          <t>Torres Lindavista</t>
         </is>
       </c>
       <c r="D46" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E46" s="7" t="n">
@@ -2395,17 +2395,17 @@
       </c>
       <c r="B47" s="14" t="inlineStr">
         <is>
-          <t>38651</t>
+          <t>43130</t>
         </is>
       </c>
       <c r="C47" s="12" t="inlineStr">
         <is>
-          <t>Via Vallejo</t>
+          <t>Town Center Nicolás Romero</t>
         </is>
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E47" s="11" t="n">
@@ -2430,17 +2430,17 @@
       </c>
       <c r="B48" s="16" t="inlineStr">
         <is>
-          <t>38694</t>
+          <t>38651</t>
         </is>
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
-          <t>Villas de la Hacienda</t>
+          <t>Via Vallejo</t>
         </is>
       </c>
       <c r="D48" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E48" s="7" t="n">
@@ -2465,17 +2465,17 @@
       </c>
       <c r="B49" s="14" t="inlineStr">
         <is>
-          <t>38656</t>
+          <t>38694</t>
         </is>
       </c>
       <c r="C49" s="12" t="inlineStr">
         <is>
-          <t>Viveros de la Loma</t>
+          <t>Villas de la Hacienda</t>
         </is>
       </c>
       <c r="D49" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E49" s="11" t="n">
@@ -2500,17 +2500,17 @@
       </c>
       <c r="B50" s="16" t="inlineStr">
         <is>
-          <t>38115</t>
+          <t>38656</t>
         </is>
       </c>
       <c r="C50" s="8" t="inlineStr">
         <is>
-          <t>Zona Azul</t>
+          <t>Viveros de la Loma</t>
         </is>
       </c>
       <c r="D50" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E50" s="7" t="n">
@@ -2535,12 +2535,12 @@
       </c>
       <c r="B51" s="14" t="inlineStr">
         <is>
-          <t>38142</t>
+          <t>38115</t>
         </is>
       </c>
       <c r="C51" s="12" t="inlineStr">
         <is>
-          <t>Zona Esmeralda</t>
+          <t>Zona Azul</t>
         </is>
       </c>
       <c r="D51" s="12" t="inlineStr">
@@ -2570,12 +2570,12 @@
       </c>
       <c r="B52" s="16" t="inlineStr">
         <is>
-          <t>43043</t>
+          <t>38142</t>
         </is>
       </c>
       <c r="C52" s="8" t="inlineStr">
         <is>
-          <t>Atizapan</t>
+          <t>Zona Esmeralda</t>
         </is>
       </c>
       <c r="D52" s="8" t="inlineStr">
@@ -2584,10 +2584,10 @@
         </is>
       </c>
       <c r="E52" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F52" s="7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G52" s="9">
         <f>IFERROR(E52/(E52+F52),0)</f>
@@ -2605,17 +2605,17 @@
       </c>
       <c r="B53" s="14" t="inlineStr">
         <is>
-          <t>38930</t>
+          <t>43043</t>
         </is>
       </c>
       <c r="C53" s="12" t="inlineStr">
         <is>
-          <t>Blvd. Aeropuerto dt</t>
+          <t>Atizapan</t>
         </is>
       </c>
       <c r="D53" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E53" s="11" t="n">
@@ -2640,12 +2640,12 @@
       </c>
       <c r="B54" s="16" t="inlineStr">
         <is>
-          <t>38529</t>
+          <t>38930</t>
         </is>
       </c>
       <c r="C54" s="8" t="inlineStr">
         <is>
-          <t>Bosques de Aragon</t>
+          <t>Blvd. Aeropuerto dt</t>
         </is>
       </c>
       <c r="D54" s="8" t="inlineStr">
@@ -2675,17 +2675,17 @@
       </c>
       <c r="B55" s="14" t="inlineStr">
         <is>
-          <t>38837</t>
+          <t>38529</t>
         </is>
       </c>
       <c r="C55" s="12" t="inlineStr">
         <is>
-          <t>Centenario Azcapotzalco</t>
+          <t>Bosques de Aragon</t>
         </is>
       </c>
       <c r="D55" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E55" s="11" t="n">
@@ -2710,24 +2710,24 @@
       </c>
       <c r="B56" s="16" t="inlineStr">
         <is>
-          <t>43193</t>
+          <t>38837</t>
         </is>
       </c>
       <c r="C56" s="8" t="inlineStr">
         <is>
-          <t>Cosmopol N1</t>
+          <t>Centenario Azcapotzalco</t>
         </is>
       </c>
       <c r="D56" s="8" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E56" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F56" s="7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G56" s="9">
         <f>IFERROR(E56/(E56+F56),0)</f>
@@ -2745,24 +2745,24 @@
       </c>
       <c r="B57" s="14" t="inlineStr">
         <is>
-          <t>38903</t>
+          <t>43193</t>
         </is>
       </c>
       <c r="C57" s="12" t="inlineStr">
         <is>
-          <t>Encuentro Oceania</t>
+          <t>Cosmopol N1</t>
         </is>
       </c>
       <c r="D57" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E57" s="11" t="n">
         <v>0</v>
       </c>
       <c r="F57" s="11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G57" s="13">
         <f>IFERROR(E57/(E57+F57),0)</f>
@@ -2780,12 +2780,12 @@
       </c>
       <c r="B58" s="16" t="inlineStr">
         <is>
-          <t>38995</t>
+          <t>38903</t>
         </is>
       </c>
       <c r="C58" s="8" t="inlineStr">
         <is>
-          <t>Encuentro Oceania II</t>
+          <t>Encuentro Oceania</t>
         </is>
       </c>
       <c r="D58" s="8" t="inlineStr">
@@ -2815,17 +2815,17 @@
       </c>
       <c r="B59" s="14" t="inlineStr">
         <is>
-          <t>38507</t>
+          <t>38995</t>
         </is>
       </c>
       <c r="C59" s="12" t="inlineStr">
         <is>
-          <t>Espacio Vista del Valle</t>
+          <t>Encuentro Oceania II</t>
         </is>
       </c>
       <c r="D59" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E59" s="11" t="n">
@@ -2850,17 +2850,17 @@
       </c>
       <c r="B60" s="16" t="inlineStr">
         <is>
-          <t>38230</t>
+          <t>38507</t>
         </is>
       </c>
       <c r="C60" s="8" t="inlineStr">
         <is>
-          <t>ITEMS Edo de Mexico</t>
+          <t>Espacio Vista del Valle</t>
         </is>
       </c>
       <c r="D60" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E60" s="7" t="n">
@@ -2885,17 +2885,17 @@
       </c>
       <c r="B61" s="14" t="inlineStr">
         <is>
-          <t>38270</t>
+          <t>38230</t>
         </is>
       </c>
       <c r="C61" s="12" t="inlineStr">
         <is>
-          <t>Lomas Verdes II</t>
+          <t>ITEMS Edo de Mexico</t>
         </is>
       </c>
       <c r="D61" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E61" s="11" t="n">
@@ -2920,17 +2920,17 @@
       </c>
       <c r="B62" s="16" t="inlineStr">
         <is>
-          <t>38371</t>
+          <t>38270</t>
         </is>
       </c>
       <c r="C62" s="8" t="inlineStr">
         <is>
-          <t>Montevideo DT</t>
+          <t>Lomas Verdes II</t>
         </is>
       </c>
       <c r="D62" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E62" s="7" t="n">
@@ -2955,17 +2955,17 @@
       </c>
       <c r="B63" s="14" t="inlineStr">
         <is>
-          <t>38674</t>
+          <t>38371</t>
         </is>
       </c>
       <c r="C63" s="12" t="inlineStr">
         <is>
-          <t>Mundo E</t>
+          <t>Montevideo DT</t>
         </is>
       </c>
       <c r="D63" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E63" s="11" t="n">
@@ -2990,12 +2990,12 @@
       </c>
       <c r="B64" s="16" t="inlineStr">
         <is>
-          <t>38845</t>
+          <t>38674</t>
         </is>
       </c>
       <c r="C64" s="8" t="inlineStr">
         <is>
-          <t>Mundo E II</t>
+          <t>Mundo E</t>
         </is>
       </c>
       <c r="D64" s="8" t="inlineStr">
@@ -3025,17 +3025,17 @@
       </c>
       <c r="B65" s="14" t="inlineStr">
         <is>
-          <t>38965</t>
+          <t>38845</t>
         </is>
       </c>
       <c r="C65" s="12" t="inlineStr">
         <is>
-          <t>Parque Tepeyac Piso 2</t>
+          <t>Mundo E II</t>
         </is>
       </c>
       <c r="D65" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E65" s="11" t="n">
@@ -3060,17 +3060,17 @@
       </c>
       <c r="B66" s="16" t="inlineStr">
         <is>
-          <t>38792</t>
+          <t>38965</t>
         </is>
       </c>
       <c r="C66" s="8" t="inlineStr">
         <is>
-          <t>Pasaje Tlanepantla</t>
+          <t>Parque Tepeyac Piso 2</t>
         </is>
       </c>
       <c r="D66" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E66" s="7" t="n">
@@ -3095,17 +3095,17 @@
       </c>
       <c r="B67" s="14" t="inlineStr">
         <is>
-          <t>38515</t>
+          <t>38792</t>
         </is>
       </c>
       <c r="C67" s="12" t="inlineStr">
         <is>
-          <t>Patio Ecatepec</t>
+          <t>Pasaje Tlanepantla</t>
         </is>
       </c>
       <c r="D67" s="12" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E67" s="11" t="n">
@@ -3130,17 +3130,17 @@
       </c>
       <c r="B68" s="16" t="inlineStr">
         <is>
-          <t>38176</t>
+          <t>38515</t>
         </is>
       </c>
       <c r="C68" s="8" t="inlineStr">
         <is>
-          <t>Periferico Satélite DT</t>
+          <t>Patio Ecatepec</t>
         </is>
       </c>
       <c r="D68" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E68" s="7" t="n">
@@ -3165,17 +3165,17 @@
       </c>
       <c r="B69" s="14" t="inlineStr">
         <is>
-          <t>38924</t>
+          <t>38176</t>
         </is>
       </c>
       <c r="C69" s="12" t="inlineStr">
         <is>
-          <t>Plaza Aeropuerto</t>
+          <t>Periferico Satélite DT</t>
         </is>
       </c>
       <c r="D69" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E69" s="11" t="n">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="B70" s="16" t="inlineStr">
         <is>
-          <t>38719</t>
+          <t>38924</t>
         </is>
       </c>
       <c r="C70" s="8" t="inlineStr">
         <is>
-          <t>Plaza Fortuna</t>
+          <t>Plaza Aeropuerto</t>
         </is>
       </c>
       <c r="D70" s="8" t="inlineStr">
@@ -3235,12 +3235,12 @@
       </c>
       <c r="B71" s="14" t="inlineStr">
         <is>
-          <t>38811</t>
+          <t>38719</t>
         </is>
       </c>
       <c r="C71" s="12" t="inlineStr">
         <is>
-          <t>Plaza Tepeyac</t>
+          <t>Plaza Fortuna</t>
         </is>
       </c>
       <c r="D71" s="12" t="inlineStr">
@@ -3270,17 +3270,17 @@
       </c>
       <c r="B72" s="16" t="inlineStr">
         <is>
-          <t>38136</t>
+          <t>38811</t>
         </is>
       </c>
       <c r="C72" s="8" t="inlineStr">
         <is>
-          <t>Punta Norte</t>
+          <t>Plaza Tepeyac</t>
         </is>
       </c>
       <c r="D72" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E72" s="7" t="n">
@@ -3305,12 +3305,12 @@
       </c>
       <c r="B73" s="14" t="inlineStr">
         <is>
-          <t>38460</t>
+          <t>38136</t>
         </is>
       </c>
       <c r="C73" s="12" t="inlineStr">
         <is>
-          <t>Santa Monica</t>
+          <t>Punta Norte</t>
         </is>
       </c>
       <c r="D73" s="12" t="inlineStr">
@@ -3340,12 +3340,12 @@
       </c>
       <c r="B74" s="16" t="inlineStr">
         <is>
-          <t>38442</t>
+          <t>38460</t>
         </is>
       </c>
       <c r="C74" s="8" t="inlineStr">
         <is>
-          <t>Sor Juana</t>
+          <t>Santa Monica</t>
         </is>
       </c>
       <c r="D74" s="8" t="inlineStr">
@@ -3488,7 +3488,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Centro Norte · Corte 30/08/2026 17:57</t>
+          <t>Centro Norte · Corte 30/08/2026 18:14</t>
         </is>
       </c>
     </row>
@@ -3559,10 +3559,10 @@
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D6" s="7" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E6" s="9">
         <f>IFERROR(C6/(C6+D6),0)</f>
@@ -3684,10 +3684,10 @@
         </is>
       </c>
       <c r="C11" s="11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E11" s="13">
         <f>IFERROR(C11/(C11+D11),0)</f>
@@ -3759,10 +3759,10 @@
         </is>
       </c>
       <c r="C14" s="7" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E14" s="9">
         <f>IFERROR(C14/(C14+D14),0)</f>

--- a/exports/Resumen_Evidencias_OPS.xlsx
+++ b/exports/Resumen_Evidencias_OPS.xlsx
@@ -577,7 +577,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Centro Norte · Corte 30/08/2026 18:14</t>
+          <t>Centro Norte · Corte 30/08/2026 18:26</t>
         </is>
       </c>
     </row>
@@ -600,10 +600,10 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="E6" s="5">
         <f>IFERROR(A6/(A6+C6),0)</f>
@@ -661,10 +661,10 @@
         <v>10</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F10" s="9">
         <f>IFERROR(D10/(D10+E10),0)</f>
@@ -873,7 +873,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Centro Norte · Corte 30/08/2026 18:14</t>
+          <t>Centro Norte · Corte 30/08/2026 18:26</t>
         </is>
       </c>
     </row>
@@ -995,12 +995,12 @@
       </c>
       <c r="B7" s="14" t="inlineStr">
         <is>
-          <t>38333</t>
+          <t>38401</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>Izcalli Mega</t>
+          <t>Coacalco</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="B8" s="16" t="inlineStr">
         <is>
-          <t>38339</t>
+          <t>38333</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Izcalli Mega</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
@@ -1065,12 +1065,12 @@
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>38401</t>
+          <t>38339</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>Coacalco</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
@@ -1079,18 +1079,18 @@
         </is>
       </c>
       <c r="E9" s="11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G9" s="13">
         <f>IFERROR(E9/(E9+F9),0)</f>
         <v/>
       </c>
-      <c r="H9" s="10" t="inlineStr">
-        <is>
-          <t>Atención</t>
+      <c r="H9" s="15" t="inlineStr">
+        <is>
+          <t>Seguimiento</t>
         </is>
       </c>
     </row>
@@ -2010,17 +2010,17 @@
       </c>
       <c r="B36" s="16" t="inlineStr">
         <is>
-          <t>38677</t>
+          <t>38515</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>Patio la Raza</t>
+          <t>Patio Ecatepec</t>
         </is>
       </c>
       <c r="D36" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E36" s="7" t="n">
@@ -2045,17 +2045,17 @@
       </c>
       <c r="B37" s="14" t="inlineStr">
         <is>
-          <t>38427</t>
+          <t>38677</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>Plaza Satelite</t>
+          <t>Patio la Raza</t>
         </is>
       </c>
       <c r="D37" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E37" s="11" t="n">
@@ -2080,12 +2080,12 @@
       </c>
       <c r="B38" s="16" t="inlineStr">
         <is>
-          <t>38859</t>
+          <t>38427</t>
         </is>
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>Plaza Satelite II N1</t>
+          <t>Plaza Satelite</t>
         </is>
       </c>
       <c r="D38" s="8" t="inlineStr">
@@ -2115,17 +2115,17 @@
       </c>
       <c r="B39" s="14" t="inlineStr">
         <is>
-          <t>43132</t>
+          <t>38859</t>
         </is>
       </c>
       <c r="C39" s="12" t="inlineStr">
         <is>
-          <t>Plaza Vista Norte</t>
+          <t>Plaza Satelite II N1</t>
         </is>
       </c>
       <c r="D39" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E39" s="11" t="n">
@@ -2150,17 +2150,17 @@
       </c>
       <c r="B40" s="16" t="inlineStr">
         <is>
-          <t>43152</t>
+          <t>43132</t>
         </is>
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>Samara Satélite</t>
+          <t>Plaza Vista Norte</t>
         </is>
       </c>
       <c r="D40" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E40" s="7" t="n">
@@ -2185,17 +2185,17 @@
       </c>
       <c r="B41" s="14" t="inlineStr">
         <is>
-          <t>38266</t>
+          <t>43152</t>
         </is>
       </c>
       <c r="C41" s="12" t="inlineStr">
         <is>
-          <t>San Mateo</t>
+          <t>Samara Satélite</t>
         </is>
       </c>
       <c r="D41" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E41" s="11" t="n">
@@ -2220,17 +2220,17 @@
       </c>
       <c r="B42" s="16" t="inlineStr">
         <is>
-          <t>38117</t>
+          <t>38266</t>
         </is>
       </c>
       <c r="C42" s="8" t="inlineStr">
         <is>
-          <t>Satelite</t>
+          <t>San Mateo</t>
         </is>
       </c>
       <c r="D42" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E42" s="7" t="n">
@@ -2255,12 +2255,12 @@
       </c>
       <c r="B43" s="14" t="inlineStr">
         <is>
-          <t>38475</t>
+          <t>38117</t>
         </is>
       </c>
       <c r="C43" s="12" t="inlineStr">
         <is>
-          <t>Satelite Centro Civico</t>
+          <t>Satelite</t>
         </is>
       </c>
       <c r="D43" s="12" t="inlineStr">
@@ -2290,17 +2290,17 @@
       </c>
       <c r="B44" s="16" t="inlineStr">
         <is>
-          <t>38442</t>
+          <t>38475</t>
         </is>
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t>Sor Juana</t>
+          <t>Satelite Centro Civico</t>
         </is>
       </c>
       <c r="D44" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E44" s="7" t="n">
@@ -2325,17 +2325,17 @@
       </c>
       <c r="B45" s="14" t="inlineStr">
         <is>
-          <t>38925</t>
+          <t>38442</t>
         </is>
       </c>
       <c r="C45" s="12" t="inlineStr">
         <is>
-          <t>Star Medica Lomas Verdes</t>
+          <t>Sor Juana</t>
         </is>
       </c>
       <c r="D45" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E45" s="11" t="n">
@@ -2360,17 +2360,17 @@
       </c>
       <c r="B46" s="16" t="inlineStr">
         <is>
-          <t>38411</t>
+          <t>38925</t>
         </is>
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t>Torres Lindavista</t>
+          <t>Star Medica Lomas Verdes</t>
         </is>
       </c>
       <c r="D46" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E46" s="7" t="n">
@@ -2395,17 +2395,17 @@
       </c>
       <c r="B47" s="14" t="inlineStr">
         <is>
-          <t>43130</t>
+          <t>38411</t>
         </is>
       </c>
       <c r="C47" s="12" t="inlineStr">
         <is>
-          <t>Town Center Nicolás Romero</t>
+          <t>Torres Lindavista</t>
         </is>
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E47" s="11" t="n">
@@ -2430,17 +2430,17 @@
       </c>
       <c r="B48" s="16" t="inlineStr">
         <is>
-          <t>38651</t>
+          <t>43130</t>
         </is>
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
-          <t>Via Vallejo</t>
+          <t>Town Center Nicolás Romero</t>
         </is>
       </c>
       <c r="D48" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E48" s="7" t="n">
@@ -2465,17 +2465,17 @@
       </c>
       <c r="B49" s="14" t="inlineStr">
         <is>
-          <t>38694</t>
+          <t>38651</t>
         </is>
       </c>
       <c r="C49" s="12" t="inlineStr">
         <is>
-          <t>Villas de la Hacienda</t>
+          <t>Via Vallejo</t>
         </is>
       </c>
       <c r="D49" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E49" s="11" t="n">
@@ -2500,17 +2500,17 @@
       </c>
       <c r="B50" s="16" t="inlineStr">
         <is>
-          <t>38656</t>
+          <t>38694</t>
         </is>
       </c>
       <c r="C50" s="8" t="inlineStr">
         <is>
-          <t>Viveros de la Loma</t>
+          <t>Villas de la Hacienda</t>
         </is>
       </c>
       <c r="D50" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E50" s="7" t="n">
@@ -2535,17 +2535,17 @@
       </c>
       <c r="B51" s="14" t="inlineStr">
         <is>
-          <t>38115</t>
+          <t>38656</t>
         </is>
       </c>
       <c r="C51" s="12" t="inlineStr">
         <is>
-          <t>Zona Azul</t>
+          <t>Viveros de la Loma</t>
         </is>
       </c>
       <c r="D51" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E51" s="11" t="n">
@@ -2570,12 +2570,12 @@
       </c>
       <c r="B52" s="16" t="inlineStr">
         <is>
-          <t>38142</t>
+          <t>38115</t>
         </is>
       </c>
       <c r="C52" s="8" t="inlineStr">
         <is>
-          <t>Zona Esmeralda</t>
+          <t>Zona Azul</t>
         </is>
       </c>
       <c r="D52" s="8" t="inlineStr">
@@ -2605,12 +2605,12 @@
       </c>
       <c r="B53" s="14" t="inlineStr">
         <is>
-          <t>43043</t>
+          <t>38142</t>
         </is>
       </c>
       <c r="C53" s="12" t="inlineStr">
         <is>
-          <t>Atizapan</t>
+          <t>Zona Esmeralda</t>
         </is>
       </c>
       <c r="D53" s="12" t="inlineStr">
@@ -2619,10 +2619,10 @@
         </is>
       </c>
       <c r="E53" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F53" s="11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G53" s="13">
         <f>IFERROR(E53/(E53+F53),0)</f>
@@ -2640,17 +2640,17 @@
       </c>
       <c r="B54" s="16" t="inlineStr">
         <is>
-          <t>38930</t>
+          <t>43043</t>
         </is>
       </c>
       <c r="C54" s="8" t="inlineStr">
         <is>
-          <t>Blvd. Aeropuerto dt</t>
+          <t>Atizapan</t>
         </is>
       </c>
       <c r="D54" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E54" s="7" t="n">
@@ -2675,12 +2675,12 @@
       </c>
       <c r="B55" s="14" t="inlineStr">
         <is>
-          <t>38529</t>
+          <t>38930</t>
         </is>
       </c>
       <c r="C55" s="12" t="inlineStr">
         <is>
-          <t>Bosques de Aragon</t>
+          <t>Blvd. Aeropuerto dt</t>
         </is>
       </c>
       <c r="D55" s="12" t="inlineStr">
@@ -2710,17 +2710,17 @@
       </c>
       <c r="B56" s="16" t="inlineStr">
         <is>
-          <t>38837</t>
+          <t>38529</t>
         </is>
       </c>
       <c r="C56" s="8" t="inlineStr">
         <is>
-          <t>Centenario Azcapotzalco</t>
+          <t>Bosques de Aragon</t>
         </is>
       </c>
       <c r="D56" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E56" s="7" t="n">
@@ -2745,24 +2745,24 @@
       </c>
       <c r="B57" s="14" t="inlineStr">
         <is>
-          <t>43193</t>
+          <t>38837</t>
         </is>
       </c>
       <c r="C57" s="12" t="inlineStr">
         <is>
-          <t>Cosmopol N1</t>
+          <t>Centenario Azcapotzalco</t>
         </is>
       </c>
       <c r="D57" s="12" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E57" s="11" t="n">
         <v>0</v>
       </c>
       <c r="F57" s="11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G57" s="13">
         <f>IFERROR(E57/(E57+F57),0)</f>
@@ -2780,24 +2780,24 @@
       </c>
       <c r="B58" s="16" t="inlineStr">
         <is>
-          <t>38903</t>
+          <t>43193</t>
         </is>
       </c>
       <c r="C58" s="8" t="inlineStr">
         <is>
-          <t>Encuentro Oceania</t>
+          <t>Cosmopol N1</t>
         </is>
       </c>
       <c r="D58" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E58" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F58" s="7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G58" s="9">
         <f>IFERROR(E58/(E58+F58),0)</f>
@@ -2815,12 +2815,12 @@
       </c>
       <c r="B59" s="14" t="inlineStr">
         <is>
-          <t>38995</t>
+          <t>38903</t>
         </is>
       </c>
       <c r="C59" s="12" t="inlineStr">
         <is>
-          <t>Encuentro Oceania II</t>
+          <t>Encuentro Oceania</t>
         </is>
       </c>
       <c r="D59" s="12" t="inlineStr">
@@ -2850,17 +2850,17 @@
       </c>
       <c r="B60" s="16" t="inlineStr">
         <is>
-          <t>38507</t>
+          <t>38995</t>
         </is>
       </c>
       <c r="C60" s="8" t="inlineStr">
         <is>
-          <t>Espacio Vista del Valle</t>
+          <t>Encuentro Oceania II</t>
         </is>
       </c>
       <c r="D60" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E60" s="7" t="n">
@@ -2885,17 +2885,17 @@
       </c>
       <c r="B61" s="14" t="inlineStr">
         <is>
-          <t>38230</t>
+          <t>38507</t>
         </is>
       </c>
       <c r="C61" s="12" t="inlineStr">
         <is>
-          <t>ITEMS Edo de Mexico</t>
+          <t>Espacio Vista del Valle</t>
         </is>
       </c>
       <c r="D61" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E61" s="11" t="n">
@@ -2920,17 +2920,17 @@
       </c>
       <c r="B62" s="16" t="inlineStr">
         <is>
-          <t>38270</t>
+          <t>38230</t>
         </is>
       </c>
       <c r="C62" s="8" t="inlineStr">
         <is>
-          <t>Lomas Verdes II</t>
+          <t>ITEMS Edo de Mexico</t>
         </is>
       </c>
       <c r="D62" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E62" s="7" t="n">
@@ -2955,17 +2955,17 @@
       </c>
       <c r="B63" s="14" t="inlineStr">
         <is>
-          <t>38371</t>
+          <t>38270</t>
         </is>
       </c>
       <c r="C63" s="12" t="inlineStr">
         <is>
-          <t>Montevideo DT</t>
+          <t>Lomas Verdes II</t>
         </is>
       </c>
       <c r="D63" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E63" s="11" t="n">
@@ -2990,17 +2990,17 @@
       </c>
       <c r="B64" s="16" t="inlineStr">
         <is>
-          <t>38674</t>
+          <t>38371</t>
         </is>
       </c>
       <c r="C64" s="8" t="inlineStr">
         <is>
-          <t>Mundo E</t>
+          <t>Montevideo DT</t>
         </is>
       </c>
       <c r="D64" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E64" s="7" t="n">
@@ -3025,12 +3025,12 @@
       </c>
       <c r="B65" s="14" t="inlineStr">
         <is>
-          <t>38845</t>
+          <t>38674</t>
         </is>
       </c>
       <c r="C65" s="12" t="inlineStr">
         <is>
-          <t>Mundo E II</t>
+          <t>Mundo E</t>
         </is>
       </c>
       <c r="D65" s="12" t="inlineStr">
@@ -3060,17 +3060,17 @@
       </c>
       <c r="B66" s="16" t="inlineStr">
         <is>
-          <t>38965</t>
+          <t>38845</t>
         </is>
       </c>
       <c r="C66" s="8" t="inlineStr">
         <is>
-          <t>Parque Tepeyac Piso 2</t>
+          <t>Mundo E II</t>
         </is>
       </c>
       <c r="D66" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E66" s="7" t="n">
@@ -3095,17 +3095,17 @@
       </c>
       <c r="B67" s="14" t="inlineStr">
         <is>
-          <t>38792</t>
+          <t>38965</t>
         </is>
       </c>
       <c r="C67" s="12" t="inlineStr">
         <is>
-          <t>Pasaje Tlanepantla</t>
+          <t>Parque Tepeyac Piso 2</t>
         </is>
       </c>
       <c r="D67" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E67" s="11" t="n">
@@ -3130,17 +3130,17 @@
       </c>
       <c r="B68" s="16" t="inlineStr">
         <is>
-          <t>38515</t>
+          <t>38792</t>
         </is>
       </c>
       <c r="C68" s="8" t="inlineStr">
         <is>
-          <t>Patio Ecatepec</t>
+          <t>Pasaje Tlanepantla</t>
         </is>
       </c>
       <c r="D68" s="8" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E68" s="7" t="n">
@@ -3488,7 +3488,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Centro Norte · Corte 30/08/2026 18:14</t>
+          <t>Centro Norte · Corte 30/08/2026 18:26</t>
         </is>
       </c>
     </row>
@@ -3534,10 +3534,10 @@
         </is>
       </c>
       <c r="C5" s="11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E5" s="13">
         <f>IFERROR(C5/(C5+D5),0)</f>
@@ -3584,10 +3584,10 @@
         </is>
       </c>
       <c r="C7" s="11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E7" s="13">
         <f>IFERROR(C7/(C7+D7),0)</f>

--- a/exports/Resumen_Evidencias_OPS.xlsx
+++ b/exports/Resumen_Evidencias_OPS.xlsx
@@ -577,7 +577,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Centro Norte · Corte 30/08/2026 18:26</t>
+          <t>Centro Norte · Corte 30/08/2026 19:58</t>
         </is>
       </c>
     </row>
@@ -600,10 +600,10 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>644</v>
+        <v>639</v>
       </c>
       <c r="E6" s="5">
         <f>IFERROR(A6/(A6+C6),0)</f>
@@ -661,10 +661,10 @@
         <v>10</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="F10" s="9">
         <f>IFERROR(D10/(D10+E10),0)</f>
@@ -745,10 +745,10 @@
         <v>13</v>
       </c>
       <c r="D13" s="11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E13" s="12" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F13" s="13">
         <f>IFERROR(D13/(D13+E13),0)</f>
@@ -773,10 +773,10 @@
         <v>12</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E14" s="8" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F14" s="9">
         <f>IFERROR(D14/(D14+E14),0)</f>
@@ -873,7 +873,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Centro Norte · Corte 30/08/2026 18:26</t>
+          <t>Centro Norte · Corte 30/08/2026 19:58</t>
         </is>
       </c>
     </row>
@@ -925,24 +925,24 @@
       </c>
       <c r="B5" s="14" t="inlineStr">
         <is>
-          <t>38695</t>
+          <t>38401</t>
         </is>
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>Cetram 4 Caminos</t>
+          <t>Coacalco</t>
         </is>
       </c>
       <c r="D5" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E5" s="11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G5" s="13">
         <f>IFERROR(E5/(E5+F5),0)</f>
@@ -960,12 +960,12 @@
       </c>
       <c r="B6" s="16" t="inlineStr">
         <is>
-          <t>38561</t>
+          <t>38695</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>Parque Toreo</t>
+          <t>Cetram 4 Caminos</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
@@ -995,12 +995,12 @@
       </c>
       <c r="B7" s="14" t="inlineStr">
         <is>
-          <t>38401</t>
+          <t>38333</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>Coacalco</t>
+          <t>Izcalli Mega</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
@@ -1009,10 +1009,10 @@
         </is>
       </c>
       <c r="E7" s="11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G7" s="13">
         <f>IFERROR(E7/(E7+F7),0)</f>
@@ -1030,24 +1030,24 @@
       </c>
       <c r="B8" s="16" t="inlineStr">
         <is>
-          <t>38333</t>
+          <t>38561</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>Izcalli Mega</t>
+          <t>Parque Toreo</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E8" s="7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G8" s="9">
         <f>IFERROR(E8/(E8+F8),0)</f>
@@ -1835,17 +1835,17 @@
       </c>
       <c r="B31" s="14" t="inlineStr">
         <is>
-          <t>43111</t>
+          <t>38270</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>Montevideo Insurgentes</t>
+          <t>Lomas Verdes II</t>
         </is>
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E31" s="11" t="n">
@@ -1870,12 +1870,12 @@
       </c>
       <c r="B32" s="16" t="inlineStr">
         <is>
-          <t>43195</t>
+          <t>43111</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>Parque Jadin kiosko</t>
+          <t>Montevideo Insurgentes</t>
         </is>
       </c>
       <c r="D32" s="8" t="inlineStr">
@@ -1905,17 +1905,17 @@
       </c>
       <c r="B33" s="14" t="inlineStr">
         <is>
-          <t>38937</t>
+          <t>38845</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>Parque Tepeyac Piso 1</t>
+          <t>Mundo E II</t>
         </is>
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E33" s="11" t="n">
@@ -1940,17 +1940,17 @@
       </c>
       <c r="B34" s="16" t="inlineStr">
         <is>
-          <t>38590</t>
+          <t>43195</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>Parque Toreo II</t>
+          <t>Parque Jadin kiosko</t>
         </is>
       </c>
       <c r="D34" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E34" s="7" t="n">
@@ -1975,17 +1975,17 @@
       </c>
       <c r="B35" s="14" t="inlineStr">
         <is>
-          <t>38546</t>
+          <t>38937</t>
         </is>
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>Patio Claveria</t>
+          <t>Parque Tepeyac Piso 1</t>
         </is>
       </c>
       <c r="D35" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E35" s="11" t="n">
@@ -2010,17 +2010,17 @@
       </c>
       <c r="B36" s="16" t="inlineStr">
         <is>
-          <t>38515</t>
+          <t>38590</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>Patio Ecatepec</t>
+          <t>Parque Toreo II</t>
         </is>
       </c>
       <c r="D36" s="8" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E36" s="7" t="n">
@@ -2045,12 +2045,12 @@
       </c>
       <c r="B37" s="14" t="inlineStr">
         <is>
-          <t>38677</t>
+          <t>38546</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>Patio la Raza</t>
+          <t>Patio Claveria</t>
         </is>
       </c>
       <c r="D37" s="12" t="inlineStr">
@@ -2080,17 +2080,17 @@
       </c>
       <c r="B38" s="16" t="inlineStr">
         <is>
-          <t>38427</t>
+          <t>38515</t>
         </is>
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>Plaza Satelite</t>
+          <t>Patio Ecatepec</t>
         </is>
       </c>
       <c r="D38" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E38" s="7" t="n">
@@ -2115,17 +2115,17 @@
       </c>
       <c r="B39" s="14" t="inlineStr">
         <is>
-          <t>38859</t>
+          <t>38677</t>
         </is>
       </c>
       <c r="C39" s="12" t="inlineStr">
         <is>
-          <t>Plaza Satelite II N1</t>
+          <t>Patio la Raza</t>
         </is>
       </c>
       <c r="D39" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E39" s="11" t="n">
@@ -2150,17 +2150,17 @@
       </c>
       <c r="B40" s="16" t="inlineStr">
         <is>
-          <t>43132</t>
+          <t>38427</t>
         </is>
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>Plaza Vista Norte</t>
+          <t>Plaza Satelite</t>
         </is>
       </c>
       <c r="D40" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E40" s="7" t="n">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="B41" s="14" t="inlineStr">
         <is>
-          <t>43152</t>
+          <t>38859</t>
         </is>
       </c>
       <c r="C41" s="12" t="inlineStr">
         <is>
-          <t>Samara Satélite</t>
+          <t>Plaza Satelite II N1</t>
         </is>
       </c>
       <c r="D41" s="12" t="inlineStr">
@@ -2220,17 +2220,17 @@
       </c>
       <c r="B42" s="16" t="inlineStr">
         <is>
-          <t>38266</t>
+          <t>43132</t>
         </is>
       </c>
       <c r="C42" s="8" t="inlineStr">
         <is>
-          <t>San Mateo</t>
+          <t>Plaza Vista Norte</t>
         </is>
       </c>
       <c r="D42" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E42" s="7" t="n">
@@ -2255,12 +2255,12 @@
       </c>
       <c r="B43" s="14" t="inlineStr">
         <is>
-          <t>38117</t>
+          <t>43152</t>
         </is>
       </c>
       <c r="C43" s="12" t="inlineStr">
         <is>
-          <t>Satelite</t>
+          <t>Samara Satélite</t>
         </is>
       </c>
       <c r="D43" s="12" t="inlineStr">
@@ -2290,17 +2290,17 @@
       </c>
       <c r="B44" s="16" t="inlineStr">
         <is>
-          <t>38475</t>
+          <t>38266</t>
         </is>
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t>Satelite Centro Civico</t>
+          <t>San Mateo</t>
         </is>
       </c>
       <c r="D44" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E44" s="7" t="n">
@@ -2325,17 +2325,17 @@
       </c>
       <c r="B45" s="14" t="inlineStr">
         <is>
-          <t>38442</t>
+          <t>38117</t>
         </is>
       </c>
       <c r="C45" s="12" t="inlineStr">
         <is>
-          <t>Sor Juana</t>
+          <t>Satelite</t>
         </is>
       </c>
       <c r="D45" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E45" s="11" t="n">
@@ -2360,17 +2360,17 @@
       </c>
       <c r="B46" s="16" t="inlineStr">
         <is>
-          <t>38925</t>
+          <t>38475</t>
         </is>
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t>Star Medica Lomas Verdes</t>
+          <t>Satelite Centro Civico</t>
         </is>
       </c>
       <c r="D46" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E46" s="7" t="n">
@@ -2395,17 +2395,17 @@
       </c>
       <c r="B47" s="14" t="inlineStr">
         <is>
-          <t>38411</t>
+          <t>38442</t>
         </is>
       </c>
       <c r="C47" s="12" t="inlineStr">
         <is>
-          <t>Torres Lindavista</t>
+          <t>Sor Juana</t>
         </is>
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E47" s="11" t="n">
@@ -2430,12 +2430,12 @@
       </c>
       <c r="B48" s="16" t="inlineStr">
         <is>
-          <t>43130</t>
+          <t>38925</t>
         </is>
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
-          <t>Town Center Nicolás Romero</t>
+          <t>Star Medica Lomas Verdes</t>
         </is>
       </c>
       <c r="D48" s="8" t="inlineStr">
@@ -2465,12 +2465,12 @@
       </c>
       <c r="B49" s="14" t="inlineStr">
         <is>
-          <t>38651</t>
+          <t>38411</t>
         </is>
       </c>
       <c r="C49" s="12" t="inlineStr">
         <is>
-          <t>Via Vallejo</t>
+          <t>Torres Lindavista</t>
         </is>
       </c>
       <c r="D49" s="12" t="inlineStr">
@@ -2500,17 +2500,17 @@
       </c>
       <c r="B50" s="16" t="inlineStr">
         <is>
-          <t>38694</t>
+          <t>43130</t>
         </is>
       </c>
       <c r="C50" s="8" t="inlineStr">
         <is>
-          <t>Villas de la Hacienda</t>
+          <t>Town Center Nicolás Romero</t>
         </is>
       </c>
       <c r="D50" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E50" s="7" t="n">
@@ -2535,17 +2535,17 @@
       </c>
       <c r="B51" s="14" t="inlineStr">
         <is>
-          <t>38656</t>
+          <t>38651</t>
         </is>
       </c>
       <c r="C51" s="12" t="inlineStr">
         <is>
-          <t>Viveros de la Loma</t>
+          <t>Via Vallejo</t>
         </is>
       </c>
       <c r="D51" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E51" s="11" t="n">
@@ -2570,17 +2570,17 @@
       </c>
       <c r="B52" s="16" t="inlineStr">
         <is>
-          <t>38115</t>
+          <t>38694</t>
         </is>
       </c>
       <c r="C52" s="8" t="inlineStr">
         <is>
-          <t>Zona Azul</t>
+          <t>Villas de la Hacienda</t>
         </is>
       </c>
       <c r="D52" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E52" s="7" t="n">
@@ -2605,17 +2605,17 @@
       </c>
       <c r="B53" s="14" t="inlineStr">
         <is>
-          <t>38142</t>
+          <t>38656</t>
         </is>
       </c>
       <c r="C53" s="12" t="inlineStr">
         <is>
-          <t>Zona Esmeralda</t>
+          <t>Viveros de la Loma</t>
         </is>
       </c>
       <c r="D53" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E53" s="11" t="n">
@@ -2640,12 +2640,12 @@
       </c>
       <c r="B54" s="16" t="inlineStr">
         <is>
-          <t>43043</t>
+          <t>38115</t>
         </is>
       </c>
       <c r="C54" s="8" t="inlineStr">
         <is>
-          <t>Atizapan</t>
+          <t>Zona Azul</t>
         </is>
       </c>
       <c r="D54" s="8" t="inlineStr">
@@ -2654,10 +2654,10 @@
         </is>
       </c>
       <c r="E54" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F54" s="7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G54" s="9">
         <f>IFERROR(E54/(E54+F54),0)</f>
@@ -2675,24 +2675,24 @@
       </c>
       <c r="B55" s="14" t="inlineStr">
         <is>
-          <t>38930</t>
+          <t>38142</t>
         </is>
       </c>
       <c r="C55" s="12" t="inlineStr">
         <is>
-          <t>Blvd. Aeropuerto dt</t>
+          <t>Zona Esmeralda</t>
         </is>
       </c>
       <c r="D55" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E55" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F55" s="11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G55" s="13">
         <f>IFERROR(E55/(E55+F55),0)</f>
@@ -2710,17 +2710,17 @@
       </c>
       <c r="B56" s="16" t="inlineStr">
         <is>
-          <t>38529</t>
+          <t>43043</t>
         </is>
       </c>
       <c r="C56" s="8" t="inlineStr">
         <is>
-          <t>Bosques de Aragon</t>
+          <t>Atizapan</t>
         </is>
       </c>
       <c r="D56" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E56" s="7" t="n">
@@ -2745,17 +2745,17 @@
       </c>
       <c r="B57" s="14" t="inlineStr">
         <is>
-          <t>38837</t>
+          <t>38930</t>
         </is>
       </c>
       <c r="C57" s="12" t="inlineStr">
         <is>
-          <t>Centenario Azcapotzalco</t>
+          <t>Blvd. Aeropuerto dt</t>
         </is>
       </c>
       <c r="D57" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E57" s="11" t="n">
@@ -2780,24 +2780,24 @@
       </c>
       <c r="B58" s="16" t="inlineStr">
         <is>
-          <t>43193</t>
+          <t>38529</t>
         </is>
       </c>
       <c r="C58" s="8" t="inlineStr">
         <is>
-          <t>Cosmopol N1</t>
+          <t>Bosques de Aragon</t>
         </is>
       </c>
       <c r="D58" s="8" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E58" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F58" s="7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G58" s="9">
         <f>IFERROR(E58/(E58+F58),0)</f>
@@ -2815,17 +2815,17 @@
       </c>
       <c r="B59" s="14" t="inlineStr">
         <is>
-          <t>38903</t>
+          <t>38837</t>
         </is>
       </c>
       <c r="C59" s="12" t="inlineStr">
         <is>
-          <t>Encuentro Oceania</t>
+          <t>Centenario Azcapotzalco</t>
         </is>
       </c>
       <c r="D59" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E59" s="11" t="n">
@@ -2850,24 +2850,24 @@
       </c>
       <c r="B60" s="16" t="inlineStr">
         <is>
-          <t>38995</t>
+          <t>43193</t>
         </is>
       </c>
       <c r="C60" s="8" t="inlineStr">
         <is>
-          <t>Encuentro Oceania II</t>
+          <t>Cosmopol N1</t>
         </is>
       </c>
       <c r="D60" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E60" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F60" s="7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G60" s="9">
         <f>IFERROR(E60/(E60+F60),0)</f>
@@ -2885,17 +2885,17 @@
       </c>
       <c r="B61" s="14" t="inlineStr">
         <is>
-          <t>38507</t>
+          <t>38903</t>
         </is>
       </c>
       <c r="C61" s="12" t="inlineStr">
         <is>
-          <t>Espacio Vista del Valle</t>
+          <t>Encuentro Oceania</t>
         </is>
       </c>
       <c r="D61" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E61" s="11" t="n">
@@ -2920,17 +2920,17 @@
       </c>
       <c r="B62" s="16" t="inlineStr">
         <is>
-          <t>38230</t>
+          <t>38995</t>
         </is>
       </c>
       <c r="C62" s="8" t="inlineStr">
         <is>
-          <t>ITEMS Edo de Mexico</t>
+          <t>Encuentro Oceania II</t>
         </is>
       </c>
       <c r="D62" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E62" s="7" t="n">
@@ -2955,12 +2955,12 @@
       </c>
       <c r="B63" s="14" t="inlineStr">
         <is>
-          <t>38270</t>
+          <t>38507</t>
         </is>
       </c>
       <c r="C63" s="12" t="inlineStr">
         <is>
-          <t>Lomas Verdes II</t>
+          <t>Espacio Vista del Valle</t>
         </is>
       </c>
       <c r="D63" s="12" t="inlineStr">
@@ -2990,17 +2990,17 @@
       </c>
       <c r="B64" s="16" t="inlineStr">
         <is>
-          <t>38371</t>
+          <t>38230</t>
         </is>
       </c>
       <c r="C64" s="8" t="inlineStr">
         <is>
-          <t>Montevideo DT</t>
+          <t>ITEMS Edo de Mexico</t>
         </is>
       </c>
       <c r="D64" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E64" s="7" t="n">
@@ -3025,17 +3025,17 @@
       </c>
       <c r="B65" s="14" t="inlineStr">
         <is>
-          <t>38674</t>
+          <t>38371</t>
         </is>
       </c>
       <c r="C65" s="12" t="inlineStr">
         <is>
-          <t>Mundo E</t>
+          <t>Montevideo DT</t>
         </is>
       </c>
       <c r="D65" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E65" s="11" t="n">
@@ -3060,12 +3060,12 @@
       </c>
       <c r="B66" s="16" t="inlineStr">
         <is>
-          <t>38845</t>
+          <t>38674</t>
         </is>
       </c>
       <c r="C66" s="8" t="inlineStr">
         <is>
-          <t>Mundo E II</t>
+          <t>Mundo E</t>
         </is>
       </c>
       <c r="D66" s="8" t="inlineStr">
@@ -3488,7 +3488,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Centro Norte · Corte 30/08/2026 18:26</t>
+          <t>Centro Norte · Corte 30/08/2026 19:58</t>
         </is>
       </c>
     </row>
@@ -3609,10 +3609,10 @@
         </is>
       </c>
       <c r="C8" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E8" s="9">
         <f>IFERROR(C8/(C8+D8),0)</f>
@@ -3759,10 +3759,10 @@
         </is>
       </c>
       <c r="C14" s="7" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E14" s="9">
         <f>IFERROR(C14/(C14+D14),0)</f>

--- a/exports/Resumen_Evidencias_OPS.xlsx
+++ b/exports/Resumen_Evidencias_OPS.xlsx
@@ -577,7 +577,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Centro Norte · Corte 30/08/2026 19:58</t>
+          <t>Centro Norte · Corte 30/08/2026 20:48</t>
         </is>
       </c>
     </row>
@@ -600,10 +600,10 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>639</v>
+        <v>634</v>
       </c>
       <c r="E6" s="5">
         <f>IFERROR(A6/(A6+C6),0)</f>
@@ -661,10 +661,10 @@
         <v>10</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="F10" s="9">
         <f>IFERROR(D10/(D10+E10),0)</f>
@@ -773,10 +773,10 @@
         <v>12</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E14" s="8" t="n">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="F14" s="9">
         <f>IFERROR(D14/(D14+E14),0)</f>
@@ -873,7 +873,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Centro Norte · Corte 30/08/2026 19:58</t>
+          <t>Centro Norte · Corte 30/08/2026 20:48</t>
         </is>
       </c>
     </row>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="B12" s="16" t="inlineStr">
         <is>
-          <t>38862</t>
+          <t>38515</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>San Miguel Izcalli</t>
+          <t>Patio Ecatepec</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
@@ -1205,12 +1205,12 @@
       </c>
       <c r="B13" s="14" t="inlineStr">
         <is>
-          <t>38604</t>
+          <t>38862</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>Cosmopol</t>
+          <t>San Miguel Izcalli</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
@@ -1219,10 +1219,10 @@
         </is>
       </c>
       <c r="E13" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G13" s="13">
         <f>IFERROR(E13/(E13+F13),0)</f>
@@ -1240,12 +1240,12 @@
       </c>
       <c r="B14" s="16" t="inlineStr">
         <is>
-          <t>38456</t>
+          <t>38604</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Plaza las Flores</t>
+          <t>Cosmopol</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr">
@@ -1275,17 +1275,17 @@
       </c>
       <c r="B15" s="14" t="inlineStr">
         <is>
-          <t>38606</t>
+          <t>38456</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>TlalnepantlaCarso</t>
+          <t>Plaza las Flores</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E15" s="11" t="n">
@@ -1310,12 +1310,12 @@
       </c>
       <c r="B16" s="16" t="inlineStr">
         <is>
-          <t>38186</t>
+          <t>38606</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>Arboledas</t>
+          <t>TlalnepantlaCarso</t>
         </is>
       </c>
       <c r="D16" s="8" t="inlineStr">
@@ -1324,10 +1324,10 @@
         </is>
       </c>
       <c r="E16" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F16" s="7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G16" s="9">
         <f>IFERROR(E16/(E16+F16),0)</f>
@@ -1345,24 +1345,24 @@
       </c>
       <c r="B17" s="14" t="inlineStr">
         <is>
-          <t>43194</t>
+          <t>43193</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>Atana Lindavista</t>
+          <t>Cosmopol N1</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E17" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G17" s="13">
         <f>IFERROR(E17/(E17+F17),0)</f>
@@ -1380,17 +1380,17 @@
       </c>
       <c r="B18" s="16" t="inlineStr">
         <is>
-          <t>38149</t>
+          <t>38186</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>Bellavista</t>
+          <t>Arboledas</t>
         </is>
       </c>
       <c r="D18" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E18" s="7" t="n">
@@ -1415,12 +1415,12 @@
       </c>
       <c r="B19" s="14" t="inlineStr">
         <is>
-          <t>38527</t>
+          <t>43194</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>Camarones</t>
+          <t>Atana Lindavista</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="B20" s="16" t="inlineStr">
         <is>
-          <t>38394</t>
+          <t>38149</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>Centro Comercial Lomas Verdes</t>
+          <t>Bellavista</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr">
@@ -1485,17 +1485,17 @@
       </c>
       <c r="B21" s="14" t="inlineStr">
         <is>
-          <t>38535</t>
+          <t>38527</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>City Center Esmeralda</t>
+          <t>Camarones</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E21" s="11" t="n">
@@ -1520,17 +1520,17 @@
       </c>
       <c r="B22" s="16" t="inlineStr">
         <is>
-          <t>38197</t>
+          <t>38394</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>Echegaray</t>
+          <t>Centro Comercial Lomas Verdes</t>
         </is>
       </c>
       <c r="D22" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E22" s="7" t="n">
@@ -1555,17 +1555,17 @@
       </c>
       <c r="B23" s="14" t="inlineStr">
         <is>
-          <t>38431</t>
+          <t>38535</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>Eduardo Molina</t>
+          <t>City Center Esmeralda</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E23" s="11" t="n">
@@ -1590,12 +1590,12 @@
       </c>
       <c r="B24" s="16" t="inlineStr">
         <is>
-          <t>38458</t>
+          <t>38197</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>El Rosario</t>
+          <t>Echegaray</t>
         </is>
       </c>
       <c r="D24" s="8" t="inlineStr">
@@ -1625,17 +1625,17 @@
       </c>
       <c r="B25" s="14" t="inlineStr">
         <is>
-          <t>38363</t>
+          <t>38431</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>Galerias Atizapan</t>
+          <t>Eduardo Molina</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E25" s="11" t="n">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="B26" s="16" t="inlineStr">
         <is>
-          <t>38770</t>
+          <t>38458</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>Gustavo Baz 29</t>
+          <t>El Rosario</t>
         </is>
       </c>
       <c r="D26" s="8" t="inlineStr">
@@ -1695,17 +1695,17 @@
       </c>
       <c r="B27" s="14" t="inlineStr">
         <is>
-          <t>38661</t>
+          <t>38363</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>Jinetes</t>
+          <t>Galerias Atizapan</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E27" s="11" t="n">
@@ -1730,17 +1730,17 @@
       </c>
       <c r="B28" s="16" t="inlineStr">
         <is>
-          <t>38205</t>
+          <t>38770</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>Lindavista</t>
+          <t>Gustavo Baz 29</t>
         </is>
       </c>
       <c r="D28" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E28" s="7" t="n">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="B29" s="14" t="inlineStr">
         <is>
-          <t>38207</t>
+          <t>38661</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>Lindavista II</t>
+          <t>Jinetes</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E29" s="11" t="n">
@@ -1800,17 +1800,17 @@
       </c>
       <c r="B30" s="16" t="inlineStr">
         <is>
-          <t>38119</t>
+          <t>38205</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>Lomas Verdes</t>
+          <t>Lindavista</t>
         </is>
       </c>
       <c r="D30" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E30" s="7" t="n">
@@ -1835,17 +1835,17 @@
       </c>
       <c r="B31" s="14" t="inlineStr">
         <is>
-          <t>38270</t>
+          <t>38207</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>Lomas Verdes II</t>
+          <t>Lindavista II</t>
         </is>
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E31" s="11" t="n">
@@ -1870,17 +1870,17 @@
       </c>
       <c r="B32" s="16" t="inlineStr">
         <is>
-          <t>43111</t>
+          <t>38119</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>Montevideo Insurgentes</t>
+          <t>Lomas Verdes</t>
         </is>
       </c>
       <c r="D32" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E32" s="7" t="n">
@@ -1905,17 +1905,17 @@
       </c>
       <c r="B33" s="14" t="inlineStr">
         <is>
-          <t>38845</t>
+          <t>38270</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>Mundo E II</t>
+          <t>Lomas Verdes II</t>
         </is>
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E33" s="11" t="n">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="B34" s="16" t="inlineStr">
         <is>
-          <t>43195</t>
+          <t>43111</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>Parque Jadin kiosko</t>
+          <t>Montevideo Insurgentes</t>
         </is>
       </c>
       <c r="D34" s="8" t="inlineStr">
@@ -1975,17 +1975,17 @@
       </c>
       <c r="B35" s="14" t="inlineStr">
         <is>
-          <t>38937</t>
+          <t>38674</t>
         </is>
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>Parque Tepeyac Piso 1</t>
+          <t>Mundo E</t>
         </is>
       </c>
       <c r="D35" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E35" s="11" t="n">
@@ -2010,17 +2010,17 @@
       </c>
       <c r="B36" s="16" t="inlineStr">
         <is>
-          <t>38590</t>
+          <t>38845</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>Parque Toreo II</t>
+          <t>Mundo E II</t>
         </is>
       </c>
       <c r="D36" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E36" s="7" t="n">
@@ -2045,12 +2045,12 @@
       </c>
       <c r="B37" s="14" t="inlineStr">
         <is>
-          <t>38546</t>
+          <t>43195</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>Patio Claveria</t>
+          <t>Parque Jadin kiosko</t>
         </is>
       </c>
       <c r="D37" s="12" t="inlineStr">
@@ -2080,17 +2080,17 @@
       </c>
       <c r="B38" s="16" t="inlineStr">
         <is>
-          <t>38515</t>
+          <t>38937</t>
         </is>
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>Patio Ecatepec</t>
+          <t>Parque Tepeyac Piso 1</t>
         </is>
       </c>
       <c r="D38" s="8" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E38" s="7" t="n">
@@ -2115,17 +2115,17 @@
       </c>
       <c r="B39" s="14" t="inlineStr">
         <is>
-          <t>38677</t>
+          <t>38590</t>
         </is>
       </c>
       <c r="C39" s="12" t="inlineStr">
         <is>
-          <t>Patio la Raza</t>
+          <t>Parque Toreo II</t>
         </is>
       </c>
       <c r="D39" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E39" s="11" t="n">
@@ -2150,17 +2150,17 @@
       </c>
       <c r="B40" s="16" t="inlineStr">
         <is>
-          <t>38427</t>
+          <t>38546</t>
         </is>
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>Plaza Satelite</t>
+          <t>Patio Claveria</t>
         </is>
       </c>
       <c r="D40" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E40" s="7" t="n">
@@ -2185,17 +2185,17 @@
       </c>
       <c r="B41" s="14" t="inlineStr">
         <is>
-          <t>38859</t>
+          <t>38677</t>
         </is>
       </c>
       <c r="C41" s="12" t="inlineStr">
         <is>
-          <t>Plaza Satelite II N1</t>
+          <t>Patio la Raza</t>
         </is>
       </c>
       <c r="D41" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E41" s="11" t="n">
@@ -2220,17 +2220,17 @@
       </c>
       <c r="B42" s="16" t="inlineStr">
         <is>
-          <t>43132</t>
+          <t>38427</t>
         </is>
       </c>
       <c r="C42" s="8" t="inlineStr">
         <is>
-          <t>Plaza Vista Norte</t>
+          <t>Plaza Satelite</t>
         </is>
       </c>
       <c r="D42" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E42" s="7" t="n">
@@ -2255,12 +2255,12 @@
       </c>
       <c r="B43" s="14" t="inlineStr">
         <is>
-          <t>43152</t>
+          <t>38859</t>
         </is>
       </c>
       <c r="C43" s="12" t="inlineStr">
         <is>
-          <t>Samara Satélite</t>
+          <t>Plaza Satelite II N1</t>
         </is>
       </c>
       <c r="D43" s="12" t="inlineStr">
@@ -2290,17 +2290,17 @@
       </c>
       <c r="B44" s="16" t="inlineStr">
         <is>
-          <t>38266</t>
+          <t>43132</t>
         </is>
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t>San Mateo</t>
+          <t>Plaza Vista Norte</t>
         </is>
       </c>
       <c r="D44" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E44" s="7" t="n">
@@ -2325,17 +2325,17 @@
       </c>
       <c r="B45" s="14" t="inlineStr">
         <is>
-          <t>38117</t>
+          <t>38136</t>
         </is>
       </c>
       <c r="C45" s="12" t="inlineStr">
         <is>
-          <t>Satelite</t>
+          <t>Punta Norte</t>
         </is>
       </c>
       <c r="D45" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E45" s="11" t="n">
@@ -2360,12 +2360,12 @@
       </c>
       <c r="B46" s="16" t="inlineStr">
         <is>
-          <t>38475</t>
+          <t>43152</t>
         </is>
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t>Satelite Centro Civico</t>
+          <t>Samara Satélite</t>
         </is>
       </c>
       <c r="D46" s="8" t="inlineStr">
@@ -2395,17 +2395,17 @@
       </c>
       <c r="B47" s="14" t="inlineStr">
         <is>
-          <t>38442</t>
+          <t>38266</t>
         </is>
       </c>
       <c r="C47" s="12" t="inlineStr">
         <is>
-          <t>Sor Juana</t>
+          <t>San Mateo</t>
         </is>
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E47" s="11" t="n">
@@ -2430,17 +2430,17 @@
       </c>
       <c r="B48" s="16" t="inlineStr">
         <is>
-          <t>38925</t>
+          <t>38117</t>
         </is>
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
-          <t>Star Medica Lomas Verdes</t>
+          <t>Satelite</t>
         </is>
       </c>
       <c r="D48" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E48" s="7" t="n">
@@ -2465,17 +2465,17 @@
       </c>
       <c r="B49" s="14" t="inlineStr">
         <is>
-          <t>38411</t>
+          <t>38475</t>
         </is>
       </c>
       <c r="C49" s="12" t="inlineStr">
         <is>
-          <t>Torres Lindavista</t>
+          <t>Satelite Centro Civico</t>
         </is>
       </c>
       <c r="D49" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E49" s="11" t="n">
@@ -2500,17 +2500,17 @@
       </c>
       <c r="B50" s="16" t="inlineStr">
         <is>
-          <t>43130</t>
+          <t>38442</t>
         </is>
       </c>
       <c r="C50" s="8" t="inlineStr">
         <is>
-          <t>Town Center Nicolás Romero</t>
+          <t>Sor Juana</t>
         </is>
       </c>
       <c r="D50" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E50" s="7" t="n">
@@ -2535,17 +2535,17 @@
       </c>
       <c r="B51" s="14" t="inlineStr">
         <is>
-          <t>38651</t>
+          <t>38925</t>
         </is>
       </c>
       <c r="C51" s="12" t="inlineStr">
         <is>
-          <t>Via Vallejo</t>
+          <t>Star Medica Lomas Verdes</t>
         </is>
       </c>
       <c r="D51" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E51" s="11" t="n">
@@ -2570,17 +2570,17 @@
       </c>
       <c r="B52" s="16" t="inlineStr">
         <is>
-          <t>38694</t>
+          <t>38411</t>
         </is>
       </c>
       <c r="C52" s="8" t="inlineStr">
         <is>
-          <t>Villas de la Hacienda</t>
+          <t>Torres Lindavista</t>
         </is>
       </c>
       <c r="D52" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E52" s="7" t="n">
@@ -2605,17 +2605,17 @@
       </c>
       <c r="B53" s="14" t="inlineStr">
         <is>
-          <t>38656</t>
+          <t>43130</t>
         </is>
       </c>
       <c r="C53" s="12" t="inlineStr">
         <is>
-          <t>Viveros de la Loma</t>
+          <t>Town Center Nicolás Romero</t>
         </is>
       </c>
       <c r="D53" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E53" s="11" t="n">
@@ -2640,17 +2640,17 @@
       </c>
       <c r="B54" s="16" t="inlineStr">
         <is>
-          <t>38115</t>
+          <t>38651</t>
         </is>
       </c>
       <c r="C54" s="8" t="inlineStr">
         <is>
-          <t>Zona Azul</t>
+          <t>Via Vallejo</t>
         </is>
       </c>
       <c r="D54" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E54" s="7" t="n">
@@ -2675,17 +2675,17 @@
       </c>
       <c r="B55" s="14" t="inlineStr">
         <is>
-          <t>38142</t>
+          <t>38694</t>
         </is>
       </c>
       <c r="C55" s="12" t="inlineStr">
         <is>
-          <t>Zona Esmeralda</t>
+          <t>Villas de la Hacienda</t>
         </is>
       </c>
       <c r="D55" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E55" s="11" t="n">
@@ -2710,24 +2710,24 @@
       </c>
       <c r="B56" s="16" t="inlineStr">
         <is>
-          <t>43043</t>
+          <t>38656</t>
         </is>
       </c>
       <c r="C56" s="8" t="inlineStr">
         <is>
-          <t>Atizapan</t>
+          <t>Viveros de la Loma</t>
         </is>
       </c>
       <c r="D56" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E56" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F56" s="7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G56" s="9">
         <f>IFERROR(E56/(E56+F56),0)</f>
@@ -2745,24 +2745,24 @@
       </c>
       <c r="B57" s="14" t="inlineStr">
         <is>
-          <t>38930</t>
+          <t>38115</t>
         </is>
       </c>
       <c r="C57" s="12" t="inlineStr">
         <is>
-          <t>Blvd. Aeropuerto dt</t>
+          <t>Zona Azul</t>
         </is>
       </c>
       <c r="D57" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E57" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F57" s="11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G57" s="13">
         <f>IFERROR(E57/(E57+F57),0)</f>
@@ -2780,24 +2780,24 @@
       </c>
       <c r="B58" s="16" t="inlineStr">
         <is>
-          <t>38529</t>
+          <t>38142</t>
         </is>
       </c>
       <c r="C58" s="8" t="inlineStr">
         <is>
-          <t>Bosques de Aragon</t>
+          <t>Zona Esmeralda</t>
         </is>
       </c>
       <c r="D58" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E58" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F58" s="7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G58" s="9">
         <f>IFERROR(E58/(E58+F58),0)</f>
@@ -2815,17 +2815,17 @@
       </c>
       <c r="B59" s="14" t="inlineStr">
         <is>
-          <t>38837</t>
+          <t>43043</t>
         </is>
       </c>
       <c r="C59" s="12" t="inlineStr">
         <is>
-          <t>Centenario Azcapotzalco</t>
+          <t>Atizapan</t>
         </is>
       </c>
       <c r="D59" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E59" s="11" t="n">
@@ -2850,24 +2850,24 @@
       </c>
       <c r="B60" s="16" t="inlineStr">
         <is>
-          <t>43193</t>
+          <t>38930</t>
         </is>
       </c>
       <c r="C60" s="8" t="inlineStr">
         <is>
-          <t>Cosmopol N1</t>
+          <t>Blvd. Aeropuerto dt</t>
         </is>
       </c>
       <c r="D60" s="8" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E60" s="7" t="n">
         <v>0</v>
       </c>
       <c r="F60" s="7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G60" s="9">
         <f>IFERROR(E60/(E60+F60),0)</f>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="B61" s="14" t="inlineStr">
         <is>
-          <t>38903</t>
+          <t>38529</t>
         </is>
       </c>
       <c r="C61" s="12" t="inlineStr">
         <is>
-          <t>Encuentro Oceania</t>
+          <t>Bosques de Aragon</t>
         </is>
       </c>
       <c r="D61" s="12" t="inlineStr">
@@ -2920,17 +2920,17 @@
       </c>
       <c r="B62" s="16" t="inlineStr">
         <is>
-          <t>38995</t>
+          <t>38837</t>
         </is>
       </c>
       <c r="C62" s="8" t="inlineStr">
         <is>
-          <t>Encuentro Oceania II</t>
+          <t>Centenario Azcapotzalco</t>
         </is>
       </c>
       <c r="D62" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E62" s="7" t="n">
@@ -2955,17 +2955,17 @@
       </c>
       <c r="B63" s="14" t="inlineStr">
         <is>
-          <t>38507</t>
+          <t>38903</t>
         </is>
       </c>
       <c r="C63" s="12" t="inlineStr">
         <is>
-          <t>Espacio Vista del Valle</t>
+          <t>Encuentro Oceania</t>
         </is>
       </c>
       <c r="D63" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E63" s="11" t="n">
@@ -2990,17 +2990,17 @@
       </c>
       <c r="B64" s="16" t="inlineStr">
         <is>
-          <t>38230</t>
+          <t>38995</t>
         </is>
       </c>
       <c r="C64" s="8" t="inlineStr">
         <is>
-          <t>ITEMS Edo de Mexico</t>
+          <t>Encuentro Oceania II</t>
         </is>
       </c>
       <c r="D64" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E64" s="7" t="n">
@@ -3025,17 +3025,17 @@
       </c>
       <c r="B65" s="14" t="inlineStr">
         <is>
-          <t>38371</t>
+          <t>38507</t>
         </is>
       </c>
       <c r="C65" s="12" t="inlineStr">
         <is>
-          <t>Montevideo DT</t>
+          <t>Espacio Vista del Valle</t>
         </is>
       </c>
       <c r="D65" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E65" s="11" t="n">
@@ -3060,12 +3060,12 @@
       </c>
       <c r="B66" s="16" t="inlineStr">
         <is>
-          <t>38674</t>
+          <t>38230</t>
         </is>
       </c>
       <c r="C66" s="8" t="inlineStr">
         <is>
-          <t>Mundo E</t>
+          <t>ITEMS Edo de Mexico</t>
         </is>
       </c>
       <c r="D66" s="8" t="inlineStr">
@@ -3095,17 +3095,17 @@
       </c>
       <c r="B67" s="14" t="inlineStr">
         <is>
-          <t>38965</t>
+          <t>38371</t>
         </is>
       </c>
       <c r="C67" s="12" t="inlineStr">
         <is>
-          <t>Parque Tepeyac Piso 2</t>
+          <t>Montevideo DT</t>
         </is>
       </c>
       <c r="D67" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E67" s="11" t="n">
@@ -3130,17 +3130,17 @@
       </c>
       <c r="B68" s="16" t="inlineStr">
         <is>
-          <t>38792</t>
+          <t>38965</t>
         </is>
       </c>
       <c r="C68" s="8" t="inlineStr">
         <is>
-          <t>Pasaje Tlanepantla</t>
+          <t>Parque Tepeyac Piso 2</t>
         </is>
       </c>
       <c r="D68" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E68" s="7" t="n">
@@ -3165,17 +3165,17 @@
       </c>
       <c r="B69" s="14" t="inlineStr">
         <is>
-          <t>38176</t>
+          <t>38792</t>
         </is>
       </c>
       <c r="C69" s="12" t="inlineStr">
         <is>
-          <t>Periferico Satélite DT</t>
+          <t>Pasaje Tlanepantla</t>
         </is>
       </c>
       <c r="D69" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E69" s="11" t="n">
@@ -3200,17 +3200,17 @@
       </c>
       <c r="B70" s="16" t="inlineStr">
         <is>
-          <t>38924</t>
+          <t>38176</t>
         </is>
       </c>
       <c r="C70" s="8" t="inlineStr">
         <is>
-          <t>Plaza Aeropuerto</t>
+          <t>Periferico Satélite DT</t>
         </is>
       </c>
       <c r="D70" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E70" s="7" t="n">
@@ -3235,12 +3235,12 @@
       </c>
       <c r="B71" s="14" t="inlineStr">
         <is>
-          <t>38719</t>
+          <t>38924</t>
         </is>
       </c>
       <c r="C71" s="12" t="inlineStr">
         <is>
-          <t>Plaza Fortuna</t>
+          <t>Plaza Aeropuerto</t>
         </is>
       </c>
       <c r="D71" s="12" t="inlineStr">
@@ -3270,12 +3270,12 @@
       </c>
       <c r="B72" s="16" t="inlineStr">
         <is>
-          <t>38811</t>
+          <t>38719</t>
         </is>
       </c>
       <c r="C72" s="8" t="inlineStr">
         <is>
-          <t>Plaza Tepeyac</t>
+          <t>Plaza Fortuna</t>
         </is>
       </c>
       <c r="D72" s="8" t="inlineStr">
@@ -3305,17 +3305,17 @@
       </c>
       <c r="B73" s="14" t="inlineStr">
         <is>
-          <t>38136</t>
+          <t>38811</t>
         </is>
       </c>
       <c r="C73" s="12" t="inlineStr">
         <is>
-          <t>Punta Norte</t>
+          <t>Plaza Tepeyac</t>
         </is>
       </c>
       <c r="D73" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E73" s="11" t="n">
@@ -3488,7 +3488,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Centro Norte · Corte 30/08/2026 19:58</t>
+          <t>Centro Norte · Corte 30/08/2026 20:48</t>
         </is>
       </c>
     </row>
@@ -3684,10 +3684,10 @@
         </is>
       </c>
       <c r="C11" s="11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E11" s="13">
         <f>IFERROR(C11/(C11+D11),0)</f>
@@ -3759,10 +3759,10 @@
         </is>
       </c>
       <c r="C14" s="7" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="E14" s="9">
         <f>IFERROR(C14/(C14+D14),0)</f>

--- a/exports/Resumen_Evidencias_OPS.xlsx
+++ b/exports/Resumen_Evidencias_OPS.xlsx
@@ -577,7 +577,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Centro Norte · Corte 30/08/2026 20:48</t>
+          <t>Centro Norte · Corte 30/08/2026 21:18</t>
         </is>
       </c>
     </row>
@@ -600,10 +600,10 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="E6" s="5">
         <f>IFERROR(A6/(A6+C6),0)</f>
@@ -661,10 +661,10 @@
         <v>10</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="F10" s="9">
         <f>IFERROR(D10/(D10+E10),0)</f>
@@ -873,7 +873,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Centro Norte · Corte 30/08/2026 20:48</t>
+          <t>Centro Norte · Corte 30/08/2026 21:18</t>
         </is>
       </c>
     </row>
@@ -1065,12 +1065,12 @@
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>38339</t>
+          <t>38368</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Luna Park</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
@@ -1100,12 +1100,12 @@
       </c>
       <c r="B10" s="16" t="inlineStr">
         <is>
-          <t>38894</t>
+          <t>38339</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>Galerias Perinorte</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
@@ -1114,18 +1114,18 @@
         </is>
       </c>
       <c r="E10" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G10" s="9">
         <f>IFERROR(E10/(E10+F10),0)</f>
         <v/>
       </c>
-      <c r="H10" s="10" t="inlineStr">
-        <is>
-          <t>Atención</t>
+      <c r="H10" s="15" t="inlineStr">
+        <is>
+          <t>Seguimiento</t>
         </is>
       </c>
     </row>
@@ -1135,12 +1135,12 @@
       </c>
       <c r="B11" s="14" t="inlineStr">
         <is>
-          <t>38368</t>
+          <t>38894</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>Luna Park</t>
+          <t>Galerias Perinorte</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
@@ -1240,12 +1240,12 @@
       </c>
       <c r="B14" s="16" t="inlineStr">
         <is>
-          <t>38604</t>
+          <t>38456</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Cosmopol</t>
+          <t>Plaza las Flores</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr">
@@ -1257,7 +1257,7 @@
         <v>2</v>
       </c>
       <c r="F14" s="7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G14" s="9">
         <f>IFERROR(E14/(E14+F14),0)</f>
@@ -1275,12 +1275,12 @@
       </c>
       <c r="B15" s="14" t="inlineStr">
         <is>
-          <t>38456</t>
+          <t>38604</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>Plaza las Flores</t>
+          <t>Cosmopol</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
@@ -3488,7 +3488,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Centro Norte · Corte 30/08/2026 20:48</t>
+          <t>Centro Norte · Corte 30/08/2026 21:18</t>
         </is>
       </c>
     </row>
@@ -3584,10 +3584,10 @@
         </is>
       </c>
       <c r="C7" s="11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E7" s="13">
         <f>IFERROR(C7/(C7+D7),0)</f>
@@ -3737,7 +3737,7 @@
         <v>0</v>
       </c>
       <c r="D13" s="11" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E13" s="13">
         <f>IFERROR(C13/(C13+D13),0)</f>

--- a/exports/Resumen_Evidencias_OPS.xlsx
+++ b/exports/Resumen_Evidencias_OPS.xlsx
@@ -577,7 +577,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Centro Norte · Corte 30/08/2026 21:18</t>
+          <t>Centro Norte · Corte 30/08/2026 21:32</t>
         </is>
       </c>
     </row>
@@ -600,10 +600,10 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="E6" s="5">
         <f>IFERROR(A6/(A6+C6),0)</f>
@@ -661,10 +661,10 @@
         <v>10</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="F10" s="9">
         <f>IFERROR(D10/(D10+E10),0)</f>
@@ -873,7 +873,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Centro Norte · Corte 30/08/2026 21:18</t>
+          <t>Centro Norte · Corte 30/08/2026 21:32</t>
         </is>
       </c>
     </row>
@@ -1030,17 +1030,17 @@
       </c>
       <c r="B8" s="16" t="inlineStr">
         <is>
-          <t>38561</t>
+          <t>38368</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>Parque Toreo</t>
+          <t>Luna Park</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E8" s="7" t="n">
@@ -1065,24 +1065,24 @@
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>38368</t>
+          <t>38561</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>Luna Park</t>
+          <t>Parque Toreo</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E9" s="11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G9" s="13">
         <f>IFERROR(E9/(E9+F9),0)</f>
@@ -1100,12 +1100,12 @@
       </c>
       <c r="B10" s="16" t="inlineStr">
         <is>
-          <t>38339</t>
+          <t>38894</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Galerias Perinorte</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
@@ -1135,12 +1135,12 @@
       </c>
       <c r="B11" s="14" t="inlineStr">
         <is>
-          <t>38894</t>
+          <t>38339</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>Galerias Perinorte</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
@@ -1149,18 +1149,18 @@
         </is>
       </c>
       <c r="E11" s="11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G11" s="13">
         <f>IFERROR(E11/(E11+F11),0)</f>
         <v/>
       </c>
-      <c r="H11" s="10" t="inlineStr">
-        <is>
-          <t>Atención</t>
+      <c r="H11" s="15" t="inlineStr">
+        <is>
+          <t>Seguimiento</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Centro Norte · Corte 30/08/2026 21:18</t>
+          <t>Centro Norte · Corte 30/08/2026 21:32</t>
         </is>
       </c>
     </row>
@@ -3684,10 +3684,10 @@
         </is>
       </c>
       <c r="C11" s="11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E11" s="13">
         <f>IFERROR(C11/(C11+D11),0)</f>
@@ -3759,10 +3759,10 @@
         </is>
       </c>
       <c r="C14" s="7" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E14" s="9">
         <f>IFERROR(C14/(C14+D14),0)</f>

--- a/exports/Resumen_Evidencias_OPS.xlsx
+++ b/exports/Resumen_Evidencias_OPS.xlsx
@@ -12,11 +12,11 @@
     <sheet name="Actividades" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Resumen'!$A$9:$G$15</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Resumen'!$A$1:$G$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Tiendas'!$A$4:$H$76</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Resumen'!$A$9:$H$15</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Resumen'!$A$1:$H$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Tiendas'!$A$4:$I$76</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Tiendas'!$1:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Actividades'!$A$4:$F$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Actividades'!$A$4:$H$14</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -39,7 +39,7 @@
       <name val="Aptos Display"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="20"/>
+      <sz val="21"/>
     </font>
     <font>
       <name val="Aptos"/>
@@ -56,7 +56,7 @@
     <font>
       <name val="Aptos Display"/>
       <b val="1"/>
-      <color rgb="00003B2E"/>
+      <color rgb="00002E24"/>
       <sz val="18"/>
     </font>
     <font>
@@ -92,7 +92,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00003B2E"/>
+        <fgColor rgb="00002E24"/>
       </patternFill>
     </fill>
     <fill>
@@ -550,7 +550,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="00003B2E"/>
+    <tabColor rgb="00006241"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -558,22 +558,23 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1">
+    <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Sistema de Evidencias OPS</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="12" customHeight="1"/>
+    <row r="2" ht="14" customHeight="1"/>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -647,6 +648,11 @@
           <t>Estado</t>
         </is>
       </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>Decisión</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="21" customHeight="1">
       <c r="A10" s="7" t="n">
@@ -673,6 +679,11 @@
       <c r="G10" s="10" t="inlineStr">
         <is>
           <t>Atención</t>
+        </is>
+      </c>
+      <c r="H10" s="10" t="inlineStr">
+        <is>
+          <t>Priorizar hoy</t>
         </is>
       </c>
     </row>
@@ -703,6 +714,11 @@
           <t>Atención</t>
         </is>
       </c>
+      <c r="H11" s="10" t="inlineStr">
+        <is>
+          <t>Priorizar hoy</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="21" customHeight="1">
       <c r="A12" s="7" t="n">
@@ -731,6 +747,11 @@
           <t>Atención</t>
         </is>
       </c>
+      <c r="H12" s="10" t="inlineStr">
+        <is>
+          <t>Priorizar hoy</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="21" customHeight="1">
       <c r="A13" s="11" t="n">
@@ -759,6 +780,11 @@
           <t>Atención</t>
         </is>
       </c>
+      <c r="H13" s="10" t="inlineStr">
+        <is>
+          <t>Priorizar hoy</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="21" customHeight="1">
       <c r="A14" s="7" t="n">
@@ -787,6 +813,11 @@
           <t>Atención</t>
         </is>
       </c>
+      <c r="H14" s="10" t="inlineStr">
+        <is>
+          <t>Priorizar hoy</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="21" customHeight="1">
       <c r="A15" s="11" t="n">
@@ -815,25 +846,30 @@
           <t>Atención</t>
         </is>
       </c>
+      <c r="H15" s="10" t="inlineStr">
+        <is>
+          <t>Priorizar hoy</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A9:G15"/>
+  <autoFilter ref="A9:H15"/>
   <mergeCells count="8">
     <mergeCell ref="E6:G7"/>
-    <mergeCell ref="A1:G2"/>
+    <mergeCell ref="A3:H3"/>
     <mergeCell ref="C6:D7"/>
-    <mergeCell ref="A3:G3"/>
     <mergeCell ref="E5:G5"/>
     <mergeCell ref="C5:D5"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="A6:B7"/>
+    <mergeCell ref="A1:H2"/>
   </mergeCells>
   <conditionalFormatting sqref="F10:F15">
     <cfRule type="dataBar" priority="1">
       <dataBar showValue="1">
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="1"/>
-        <color rgb="00003B2E"/>
+        <color rgb="00002E24"/>
       </dataBar>
     </cfRule>
   </conditionalFormatting>
@@ -845,31 +881,32 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="001E3932"/>
+    <tabColor rgb="00002E24"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H76"/>
+  <dimension ref="A1:I76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1">
+    <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Avance por tienda</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="12" customHeight="1"/>
+    <row r="2" ht="14" customHeight="1"/>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -918,6 +955,11 @@
           <t>Estado</t>
         </is>
       </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>Decisión</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="21" customHeight="1">
       <c r="A5" s="11" t="n">
@@ -951,6 +993,11 @@
       <c r="H5" s="15" t="inlineStr">
         <is>
           <t>Seguimiento</t>
+        </is>
+      </c>
+      <c r="I5" s="15" t="inlineStr">
+        <is>
+          <t>Dar seguimiento</t>
         </is>
       </c>
     </row>
@@ -988,6 +1035,11 @@
           <t>Seguimiento</t>
         </is>
       </c>
+      <c r="I6" s="15" t="inlineStr">
+        <is>
+          <t>Dar seguimiento</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="21" customHeight="1">
       <c r="A7" s="11" t="n">
@@ -1023,6 +1075,11 @@
           <t>Seguimiento</t>
         </is>
       </c>
+      <c r="I7" s="15" t="inlineStr">
+        <is>
+          <t>Dar seguimiento</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="21" customHeight="1">
       <c r="A8" s="7" t="n">
@@ -1058,6 +1115,11 @@
           <t>Seguimiento</t>
         </is>
       </c>
+      <c r="I8" s="15" t="inlineStr">
+        <is>
+          <t>Dar seguimiento</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="21" customHeight="1">
       <c r="A9" s="11" t="n">
@@ -1093,6 +1155,11 @@
           <t>Seguimiento</t>
         </is>
       </c>
+      <c r="I9" s="15" t="inlineStr">
+        <is>
+          <t>Dar seguimiento</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="21" customHeight="1">
       <c r="A10" s="7" t="n">
@@ -1128,6 +1195,11 @@
           <t>Seguimiento</t>
         </is>
       </c>
+      <c r="I10" s="15" t="inlineStr">
+        <is>
+          <t>Dar seguimiento</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="21" customHeight="1">
       <c r="A11" s="11" t="n">
@@ -1163,6 +1235,11 @@
           <t>Seguimiento</t>
         </is>
       </c>
+      <c r="I11" s="15" t="inlineStr">
+        <is>
+          <t>Dar seguimiento</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="21" customHeight="1">
       <c r="A12" s="7" t="n">
@@ -1198,6 +1275,11 @@
           <t>Atención</t>
         </is>
       </c>
+      <c r="I12" s="10" t="inlineStr">
+        <is>
+          <t>Priorizar hoy</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="21" customHeight="1">
       <c r="A13" s="11" t="n">
@@ -1233,6 +1315,11 @@
           <t>Atención</t>
         </is>
       </c>
+      <c r="I13" s="10" t="inlineStr">
+        <is>
+          <t>Priorizar hoy</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="21" customHeight="1">
       <c r="A14" s="7" t="n">
@@ -1268,6 +1355,11 @@
           <t>Atención</t>
         </is>
       </c>
+      <c r="I14" s="10" t="inlineStr">
+        <is>
+          <t>Priorizar hoy</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="21" customHeight="1">
       <c r="A15" s="11" t="n">
@@ -1303,6 +1395,11 @@
           <t>Atención</t>
         </is>
       </c>
+      <c r="I15" s="10" t="inlineStr">
+        <is>
+          <t>Priorizar hoy</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="21" customHeight="1">
       <c r="A16" s="7" t="n">
@@ -1338,6 +1435,11 @@
           <t>Atención</t>
         </is>
       </c>
+      <c r="I16" s="10" t="inlineStr">
+        <is>
+          <t>Priorizar hoy</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="21" customHeight="1">
       <c r="A17" s="11" t="n">
@@ -1373,6 +1475,11 @@
           <t>Atención</t>
         </is>
       </c>
+      <c r="I17" s="10" t="inlineStr">
+        <is>
+          <t>Priorizar hoy</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="21" customHeight="1">
       <c r="A18" s="7" t="n">
@@ -1408,6 +1515,11 @@
           <t>Atención</t>
         </is>
       </c>
+      <c r="I18" s="10" t="inlineStr">
+        <is>
+          <t>Priorizar hoy</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="21" customHeight="1">
       <c r="A19" s="11" t="n">
@@ -1443,6 +1555,11 @@
           <t>Atención</t>
         </is>
       </c>
+      <c r="I19" s="10" t="inlineStr">
+        <is>
+          <t>Priorizar hoy</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="21" customHeight="1">
       <c r="A20" s="7" t="n">
@@ -1478,6 +1595,11 @@
           <t>Atención</t>
         </is>
       </c>
+      <c r="I20" s="10" t="inlineStr">
+        <is>
+          <t>Priorizar hoy</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="21" customHeight="1">
       <c r="A21" s="11" t="n">
@@ -1513,6 +1635,11 @@
           <t>Atención</t>
         </is>
       </c>
+      <c r="I21" s="10" t="inlineStr">
+        <is>
+          <t>Priorizar hoy</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="21" customHeight="1">
       <c r="A22" s="7" t="n">
@@ -1548,6 +1675,11 @@
           <t>Atención</t>
         </is>
       </c>
+      <c r="I22" s="10" t="inlineStr">
+        <is>
+          <t>Priorizar hoy</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="21" customHeight="1">
       <c r="A23" s="11" t="n">
@@ -1583,6 +1715,11 @@
           <t>Atención</t>
         </is>
       </c>
+      <c r="I23" s="10" t="inlineStr">
+        <is>
+          <t>Priorizar hoy</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="21" customHeight="1">
       <c r="A24" s="7" t="n">
@@ -1618,6 +1755,11 @@
           <t>Atención</t>
         </is>
       </c>
+      <c r="I24" s="10" t="inlineStr">
+        <is>
+          <t>Priorizar hoy</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="21" customHeight="1">
       <c r="A25" s="11" t="n">
@@ -1653,6 +1795,11 @@
           <t>Atención</t>
         </is>
       </c>
+      <c r="I25" s="10" t="inlineStr">
+        <is>
+          <t>Priorizar hoy</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="21" customHeight="1">
       <c r="A26" s="7" t="n">
@@ -1688,6 +1835,11 @@
           <t>Atención</t>
         </is>
       </c>
+      <c r="I26" s="10" t="inlineStr">
+        <is>
+          <t>Priorizar hoy</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="21" customHeight="1">
       <c r="A27" s="11" t="n">
@@ -1723,6 +1875,11 @@
           <t>Atención</t>
         </is>
       </c>
+      <c r="I27" s="10" t="inlineStr">
+        <is>
+          <t>Priorizar hoy</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="21" customHeight="1">
       <c r="A28" s="7" t="n">
@@ -1758,6 +1915,11 @@
           <t>Atención</t>
         </is>
       </c>
+      <c r="I28" s="10" t="inlineStr">
+        <is>
+          <t>Priorizar hoy</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="21" customHeight="1">
       <c r="A29" s="11" t="n">
@@ -1793,6 +1955,11 @@
           <t>Atención</t>
         </is>
       </c>
+      <c r="I29" s="10" t="inlineStr">
+        <is>
+          <t>Priorizar hoy</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="21" customHeight="1">
       <c r="A30" s="7" t="n">
@@ -1828,6 +1995,11 @@
           <t>Atención</t>
         </is>
       </c>
+      <c r="I30" s="10" t="inlineStr">
+        <is>
+          <t>Priorizar hoy</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="21" customHeight="1">
       <c r="A31" s="11" t="n">
@@ -1863,6 +2035,11 @@
           <t>Atención</t>
         </is>
       </c>
+      <c r="I31" s="10" t="inlineStr">
+        <is>
+          <t>Priorizar hoy</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="21" customHeight="1">
       <c r="A32" s="7" t="n">
@@ -1898,6 +2075,11 @@
           <t>Atención</t>
         </is>
       </c>
+      <c r="I32" s="10" t="inlineStr">
+        <is>
+          <t>Priorizar hoy</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="21" customHeight="1">
       <c r="A33" s="11" t="n">
@@ -1933,6 +2115,11 @@
           <t>Atención</t>
         </is>
       </c>
+      <c r="I33" s="10" t="inlineStr">
+        <is>
+          <t>Priorizar hoy</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="21" customHeight="1">
       <c r="A34" s="7" t="n">
@@ -1968,6 +2155,11 @@
           <t>Atención</t>
         </is>
       </c>
+      <c r="I34" s="10" t="inlineStr">
+        <is>
+          <t>Priorizar hoy</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="21" customHeight="1">
       <c r="A35" s="11" t="n">
@@ -2003,6 +2195,11 @@
           <t>Atención</t>
         </is>
       </c>
+      <c r="I35" s="10" t="inlineStr">
+        <is>
+          <t>Priorizar hoy</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="21" customHeight="1">
       <c r="A36" s="7" t="n">
@@ -2038,6 +2235,11 @@
           <t>Atención</t>
         </is>
       </c>
+      <c r="I36" s="10" t="inlineStr">
+        <is>
+          <t>Priorizar hoy</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="21" customHeight="1">
       <c r="A37" s="11" t="n">
@@ -2073,6 +2275,11 @@
           <t>Atención</t>
         </is>
       </c>
+      <c r="I37" s="10" t="inlineStr">
+        <is>
+          <t>Priorizar hoy</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="21" customHeight="1">
       <c r="A38" s="7" t="n">
@@ -2108,6 +2315,11 @@
           <t>Atención</t>
         </is>
       </c>
+      <c r="I38" s="10" t="inlineStr">
+        <is>
+          <t>Priorizar hoy</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="21" customHeight="1">
       <c r="A39" s="11" t="n">
@@ -2143,6 +2355,11 @@
           <t>Atención</t>
         </is>
       </c>
+      <c r="I39" s="10" t="inlineStr">
+        <is>
+          <t>Priorizar hoy</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="21" customHeight="1">
       <c r="A40" s="7" t="n">
@@ -2178,6 +2395,11 @@
           <t>Atención</t>
         </is>
       </c>
+      <c r="I40" s="10" t="inlineStr">
+        <is>
+          <t>Priorizar hoy</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="21" customHeight="1">
       <c r="A41" s="11" t="n">
@@ -2213,6 +2435,11 @@
           <t>Atención</t>
         </is>
       </c>
+      <c r="I41" s="10" t="inlineStr">
+        <is>
+          <t>Priorizar hoy</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="21" customHeight="1">
       <c r="A42" s="7" t="n">
@@ -2248,6 +2475,11 @@
           <t>Atención</t>
         </is>
       </c>
+      <c r="I42" s="10" t="inlineStr">
+        <is>
+          <t>Priorizar hoy</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="21" customHeight="1">
       <c r="A43" s="11" t="n">
@@ -2283,6 +2515,11 @@
           <t>Atención</t>
         </is>
       </c>
+      <c r="I43" s="10" t="inlineStr">
+        <is>
+          <t>Priorizar hoy</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="21" customHeight="1">
       <c r="A44" s="7" t="n">
@@ -2318,6 +2555,11 @@
           <t>Atención</t>
         </is>
       </c>
+      <c r="I44" s="10" t="inlineStr">
+        <is>
+          <t>Priorizar hoy</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="21" customHeight="1">
       <c r="A45" s="11" t="n">
@@ -2353,6 +2595,11 @@
           <t>Atención</t>
         </is>
       </c>
+      <c r="I45" s="10" t="inlineStr">
+        <is>
+          <t>Priorizar hoy</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="21" customHeight="1">
       <c r="A46" s="7" t="n">
@@ -2388,6 +2635,11 @@
           <t>Atención</t>
         </is>
       </c>
+      <c r="I46" s="10" t="inlineStr">
+        <is>
+          <t>Priorizar hoy</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="21" customHeight="1">
       <c r="A47" s="11" t="n">
@@ -2423,6 +2675,11 @@
           <t>Atención</t>
         </is>
       </c>
+      <c r="I47" s="10" t="inlineStr">
+        <is>
+          <t>Priorizar hoy</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="21" customHeight="1">
       <c r="A48" s="7" t="n">
@@ -2458,6 +2715,11 @@
           <t>Atención</t>
         </is>
       </c>
+      <c r="I48" s="10" t="inlineStr">
+        <is>
+          <t>Priorizar hoy</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="21" customHeight="1">
       <c r="A49" s="11" t="n">
@@ -2493,6 +2755,11 @@
           <t>Atención</t>
         </is>
       </c>
+      <c r="I49" s="10" t="inlineStr">
+        <is>
+          <t>Priorizar hoy</t>
+        </is>
+      </c>
     </row>
     <row r="50" ht="21" customHeight="1">
       <c r="A50" s="7" t="n">
@@ -2528,6 +2795,11 @@
           <t>Atención</t>
         </is>
       </c>
+      <c r="I50" s="10" t="inlineStr">
+        <is>
+          <t>Priorizar hoy</t>
+        </is>
+      </c>
     </row>
     <row r="51" ht="21" customHeight="1">
       <c r="A51" s="11" t="n">
@@ -2563,6 +2835,11 @@
           <t>Atención</t>
         </is>
       </c>
+      <c r="I51" s="10" t="inlineStr">
+        <is>
+          <t>Priorizar hoy</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="21" customHeight="1">
       <c r="A52" s="7" t="n">
@@ -2598,6 +2875,11 @@
           <t>Atención</t>
         </is>
       </c>
+      <c r="I52" s="10" t="inlineStr">
+        <is>
+          <t>Priorizar hoy</t>
+        </is>
+      </c>
     </row>
     <row r="53" ht="21" customHeight="1">
       <c r="A53" s="11" t="n">
@@ -2633,6 +2915,11 @@
           <t>Atención</t>
         </is>
       </c>
+      <c r="I53" s="10" t="inlineStr">
+        <is>
+          <t>Priorizar hoy</t>
+        </is>
+      </c>
     </row>
     <row r="54" ht="21" customHeight="1">
       <c r="A54" s="7" t="n">
@@ -2668,6 +2955,11 @@
           <t>Atención</t>
         </is>
       </c>
+      <c r="I54" s="10" t="inlineStr">
+        <is>
+          <t>Priorizar hoy</t>
+        </is>
+      </c>
     </row>
     <row r="55" ht="21" customHeight="1">
       <c r="A55" s="11" t="n">
@@ -2703,6 +2995,11 @@
           <t>Atención</t>
         </is>
       </c>
+      <c r="I55" s="10" t="inlineStr">
+        <is>
+          <t>Priorizar hoy</t>
+        </is>
+      </c>
     </row>
     <row r="56" ht="21" customHeight="1">
       <c r="A56" s="7" t="n">
@@ -2738,6 +3035,11 @@
           <t>Atención</t>
         </is>
       </c>
+      <c r="I56" s="10" t="inlineStr">
+        <is>
+          <t>Priorizar hoy</t>
+        </is>
+      </c>
     </row>
     <row r="57" ht="21" customHeight="1">
       <c r="A57" s="11" t="n">
@@ -2773,6 +3075,11 @@
           <t>Atención</t>
         </is>
       </c>
+      <c r="I57" s="10" t="inlineStr">
+        <is>
+          <t>Priorizar hoy</t>
+        </is>
+      </c>
     </row>
     <row r="58" ht="21" customHeight="1">
       <c r="A58" s="7" t="n">
@@ -2808,6 +3115,11 @@
           <t>Atención</t>
         </is>
       </c>
+      <c r="I58" s="10" t="inlineStr">
+        <is>
+          <t>Priorizar hoy</t>
+        </is>
+      </c>
     </row>
     <row r="59" ht="21" customHeight="1">
       <c r="A59" s="11" t="n">
@@ -2843,6 +3155,11 @@
           <t>Atención</t>
         </is>
       </c>
+      <c r="I59" s="10" t="inlineStr">
+        <is>
+          <t>Priorizar hoy</t>
+        </is>
+      </c>
     </row>
     <row r="60" ht="21" customHeight="1">
       <c r="A60" s="7" t="n">
@@ -2878,6 +3195,11 @@
           <t>Atención</t>
         </is>
       </c>
+      <c r="I60" s="10" t="inlineStr">
+        <is>
+          <t>Priorizar hoy</t>
+        </is>
+      </c>
     </row>
     <row r="61" ht="21" customHeight="1">
       <c r="A61" s="11" t="n">
@@ -2913,6 +3235,11 @@
           <t>Atención</t>
         </is>
       </c>
+      <c r="I61" s="10" t="inlineStr">
+        <is>
+          <t>Priorizar hoy</t>
+        </is>
+      </c>
     </row>
     <row r="62" ht="21" customHeight="1">
       <c r="A62" s="7" t="n">
@@ -2948,6 +3275,11 @@
           <t>Atención</t>
         </is>
       </c>
+      <c r="I62" s="10" t="inlineStr">
+        <is>
+          <t>Priorizar hoy</t>
+        </is>
+      </c>
     </row>
     <row r="63" ht="21" customHeight="1">
       <c r="A63" s="11" t="n">
@@ -2983,6 +3315,11 @@
           <t>Atención</t>
         </is>
       </c>
+      <c r="I63" s="10" t="inlineStr">
+        <is>
+          <t>Priorizar hoy</t>
+        </is>
+      </c>
     </row>
     <row r="64" ht="21" customHeight="1">
       <c r="A64" s="7" t="n">
@@ -3018,6 +3355,11 @@
           <t>Atención</t>
         </is>
       </c>
+      <c r="I64" s="10" t="inlineStr">
+        <is>
+          <t>Priorizar hoy</t>
+        </is>
+      </c>
     </row>
     <row r="65" ht="21" customHeight="1">
       <c r="A65" s="11" t="n">
@@ -3053,6 +3395,11 @@
           <t>Atención</t>
         </is>
       </c>
+      <c r="I65" s="10" t="inlineStr">
+        <is>
+          <t>Priorizar hoy</t>
+        </is>
+      </c>
     </row>
     <row r="66" ht="21" customHeight="1">
       <c r="A66" s="7" t="n">
@@ -3088,6 +3435,11 @@
           <t>Atención</t>
         </is>
       </c>
+      <c r="I66" s="10" t="inlineStr">
+        <is>
+          <t>Priorizar hoy</t>
+        </is>
+      </c>
     </row>
     <row r="67" ht="21" customHeight="1">
       <c r="A67" s="11" t="n">
@@ -3123,6 +3475,11 @@
           <t>Atención</t>
         </is>
       </c>
+      <c r="I67" s="10" t="inlineStr">
+        <is>
+          <t>Priorizar hoy</t>
+        </is>
+      </c>
     </row>
     <row r="68" ht="21" customHeight="1">
       <c r="A68" s="7" t="n">
@@ -3158,6 +3515,11 @@
           <t>Atención</t>
         </is>
       </c>
+      <c r="I68" s="10" t="inlineStr">
+        <is>
+          <t>Priorizar hoy</t>
+        </is>
+      </c>
     </row>
     <row r="69" ht="21" customHeight="1">
       <c r="A69" s="11" t="n">
@@ -3193,6 +3555,11 @@
           <t>Atención</t>
         </is>
       </c>
+      <c r="I69" s="10" t="inlineStr">
+        <is>
+          <t>Priorizar hoy</t>
+        </is>
+      </c>
     </row>
     <row r="70" ht="21" customHeight="1">
       <c r="A70" s="7" t="n">
@@ -3228,6 +3595,11 @@
           <t>Atención</t>
         </is>
       </c>
+      <c r="I70" s="10" t="inlineStr">
+        <is>
+          <t>Priorizar hoy</t>
+        </is>
+      </c>
     </row>
     <row r="71" ht="21" customHeight="1">
       <c r="A71" s="11" t="n">
@@ -3263,6 +3635,11 @@
           <t>Atención</t>
         </is>
       </c>
+      <c r="I71" s="10" t="inlineStr">
+        <is>
+          <t>Priorizar hoy</t>
+        </is>
+      </c>
     </row>
     <row r="72" ht="21" customHeight="1">
       <c r="A72" s="7" t="n">
@@ -3298,6 +3675,11 @@
           <t>Atención</t>
         </is>
       </c>
+      <c r="I72" s="10" t="inlineStr">
+        <is>
+          <t>Priorizar hoy</t>
+        </is>
+      </c>
     </row>
     <row r="73" ht="21" customHeight="1">
       <c r="A73" s="11" t="n">
@@ -3333,6 +3715,11 @@
           <t>Atención</t>
         </is>
       </c>
+      <c r="I73" s="10" t="inlineStr">
+        <is>
+          <t>Priorizar hoy</t>
+        </is>
+      </c>
     </row>
     <row r="74" ht="21" customHeight="1">
       <c r="A74" s="7" t="n">
@@ -3368,6 +3755,11 @@
           <t>Atención</t>
         </is>
       </c>
+      <c r="I74" s="10" t="inlineStr">
+        <is>
+          <t>Priorizar hoy</t>
+        </is>
+      </c>
     </row>
     <row r="75" ht="21" customHeight="1">
       <c r="A75" s="11" t="n">
@@ -3403,6 +3795,11 @@
           <t>Atención</t>
         </is>
       </c>
+      <c r="I75" s="10" t="inlineStr">
+        <is>
+          <t>Priorizar hoy</t>
+        </is>
+      </c>
     </row>
     <row r="76" ht="21" customHeight="1">
       <c r="A76" s="7" t="n">
@@ -3438,19 +3835,24 @@
           <t>Atención</t>
         </is>
       </c>
+      <c r="I76" s="10" t="inlineStr">
+        <is>
+          <t>Priorizar hoy</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:H76"/>
+  <autoFilter ref="A4:I76"/>
   <mergeCells count="2">
-    <mergeCell ref="A1:H2"/>
-    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A1:I2"/>
+    <mergeCell ref="A3:I3"/>
   </mergeCells>
   <conditionalFormatting sqref="G5:G76">
     <cfRule type="dataBar" priority="1">
       <dataBar showValue="1">
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="1"/>
-        <color rgb="00003B2E"/>
+        <color rgb="00002E24"/>
       </dataBar>
     </cfRule>
   </conditionalFormatting>
@@ -3466,25 +3868,27 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="44" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1">
+    <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Avance por actividad</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="12" customHeight="1"/>
+    <row r="2" ht="14" customHeight="1"/>
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -3523,6 +3927,16 @@
           <t>Fecha compromiso</t>
         </is>
       </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>Estado</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>Decisión</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="21" customHeight="1">
       <c r="A5" s="11" t="n">
@@ -3546,6 +3960,16 @@
       <c r="F5" s="12" t="inlineStr">
         <is>
           <t>03/09/26</t>
+        </is>
+      </c>
+      <c r="G5" s="10" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="H5" s="10" t="inlineStr">
+        <is>
+          <t>Priorizar hoy</t>
         </is>
       </c>
     </row>
@@ -3573,6 +3997,16 @@
           <t>03/09/26</t>
         </is>
       </c>
+      <c r="G6" s="10" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="H6" s="10" t="inlineStr">
+        <is>
+          <t>Priorizar hoy</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="21" customHeight="1">
       <c r="A7" s="11" t="n">
@@ -3598,6 +4032,16 @@
           <t>06/09/26</t>
         </is>
       </c>
+      <c r="G7" s="10" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="H7" s="10" t="inlineStr">
+        <is>
+          <t>Priorizar hoy</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="21" customHeight="1">
       <c r="A8" s="7" t="n">
@@ -3623,6 +4067,16 @@
           <t>03/09/26</t>
         </is>
       </c>
+      <c r="G8" s="10" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="H8" s="10" t="inlineStr">
+        <is>
+          <t>Priorizar hoy</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="21" customHeight="1">
       <c r="A9" s="11" t="n">
@@ -3648,6 +4102,16 @@
           <t>06/09/26</t>
         </is>
       </c>
+      <c r="G9" s="10" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="H9" s="10" t="inlineStr">
+        <is>
+          <t>Priorizar hoy</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="21" customHeight="1">
       <c r="A10" s="7" t="n">
@@ -3673,6 +4137,16 @@
           <t>06/09/26</t>
         </is>
       </c>
+      <c r="G10" s="10" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="H10" s="10" t="inlineStr">
+        <is>
+          <t>Priorizar hoy</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="21" customHeight="1">
       <c r="A11" s="11" t="n">
@@ -3698,6 +4172,16 @@
           <t>13/09/26</t>
         </is>
       </c>
+      <c r="G11" s="10" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="H11" s="10" t="inlineStr">
+        <is>
+          <t>Priorizar hoy</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="21" customHeight="1">
       <c r="A12" s="7" t="n">
@@ -3723,6 +4207,16 @@
           <t>06/09/26</t>
         </is>
       </c>
+      <c r="G12" s="10" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="H12" s="10" t="inlineStr">
+        <is>
+          <t>Priorizar hoy</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="21" customHeight="1">
       <c r="A13" s="11" t="n">
@@ -3748,6 +4242,16 @@
           <t>03/09/26</t>
         </is>
       </c>
+      <c r="G13" s="10" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="H13" s="10" t="inlineStr">
+        <is>
+          <t>Priorizar hoy</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="21" customHeight="1">
       <c r="A14" s="7" t="n">
@@ -3773,19 +4277,29 @@
           <t>31/08/26</t>
         </is>
       </c>
+      <c r="G14" s="15" t="inlineStr">
+        <is>
+          <t>Seguimiento</t>
+        </is>
+      </c>
+      <c r="H14" s="15" t="inlineStr">
+        <is>
+          <t>Dar seguimiento</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:F14"/>
+  <autoFilter ref="A4:H14"/>
   <mergeCells count="2">
-    <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A1:F2"/>
+    <mergeCell ref="A1:H2"/>
+    <mergeCell ref="A3:H3"/>
   </mergeCells>
   <conditionalFormatting sqref="E5:E14">
     <cfRule type="dataBar" priority="1">
       <dataBar showValue="1">
         <cfvo type="num" val="0"/>
         <cfvo type="num" val="1"/>
-        <color rgb="00003B2E"/>
+        <color rgb="00002E24"/>
       </dataBar>
     </cfRule>
   </conditionalFormatting>

--- a/exports/Resumen_Evidencias_OPS.xlsx
+++ b/exports/Resumen_Evidencias_OPS.xlsx
@@ -578,7 +578,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Centro Norte · Corte 30/08/2026 21:32</t>
+          <t>Centro Norte · Corte 30/08/2026 23:20</t>
         </is>
       </c>
     </row>
@@ -601,10 +601,10 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>630</v>
+        <v>624</v>
       </c>
       <c r="E6" s="5">
         <f>IFERROR(A6/(A6+C6),0)</f>
@@ -700,10 +700,10 @@
         <v>13</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E11" s="12" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F11" s="13">
         <f>IFERROR(D11/(D11+E11),0)</f>
@@ -832,10 +832,10 @@
         <v>11</v>
       </c>
       <c r="D15" s="11" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E15" s="12" t="n">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="F15" s="13">
         <f>IFERROR(D15/(D15+E15),0)</f>
@@ -910,7 +910,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Centro Norte · Corte 30/08/2026 21:32</t>
+          <t>Centro Norte · Corte 30/08/2026 23:20</t>
         </is>
       </c>
     </row>
@@ -967,24 +967,24 @@
       </c>
       <c r="B5" s="14" t="inlineStr">
         <is>
-          <t>38401</t>
+          <t>38695</t>
         </is>
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>Coacalco</t>
+          <t>Cetram 4 Caminos</t>
         </is>
       </c>
       <c r="D5" s="12" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E5" s="11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G5" s="13">
         <f>IFERROR(E5/(E5+F5),0)</f>
@@ -1007,17 +1007,17 @@
       </c>
       <c r="B6" s="16" t="inlineStr">
         <is>
-          <t>38695</t>
+          <t>38401</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>Cetram 4 Caminos</t>
+          <t>Coacalco</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E6" s="7" t="n">
@@ -1167,24 +1167,24 @@
       </c>
       <c r="B10" s="16" t="inlineStr">
         <is>
-          <t>38894</t>
+          <t>38719</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>Galerias Perinorte</t>
+          <t>Plaza Fortuna</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E10" s="7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G10" s="9">
         <f>IFERROR(E10/(E10+F10),0)</f>
@@ -1207,12 +1207,12 @@
       </c>
       <c r="B11" s="14" t="inlineStr">
         <is>
-          <t>38339</t>
+          <t>38894</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Galerias Perinorte</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
@@ -1247,12 +1247,12 @@
       </c>
       <c r="B12" s="16" t="inlineStr">
         <is>
-          <t>38515</t>
+          <t>38339</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Patio Ecatepec</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
@@ -1261,23 +1261,23 @@
         </is>
       </c>
       <c r="E12" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F12" s="7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G12" s="9">
         <f>IFERROR(E12/(E12+F12),0)</f>
         <v/>
       </c>
-      <c r="H12" s="10" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I12" s="10" t="inlineStr">
-        <is>
-          <t>Priorizar hoy</t>
+      <c r="H12" s="15" t="inlineStr">
+        <is>
+          <t>Seguimiento</t>
+        </is>
+      </c>
+      <c r="I12" s="15" t="inlineStr">
+        <is>
+          <t>Dar seguimiento</t>
         </is>
       </c>
     </row>
@@ -1287,12 +1287,12 @@
       </c>
       <c r="B13" s="14" t="inlineStr">
         <is>
-          <t>38862</t>
+          <t>38604</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>San Miguel Izcalli</t>
+          <t>Cosmopol</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
@@ -1327,12 +1327,12 @@
       </c>
       <c r="B14" s="16" t="inlineStr">
         <is>
-          <t>38456</t>
+          <t>38515</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Plaza las Flores</t>
+          <t>Patio Ecatepec</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr">
@@ -1341,7 +1341,7 @@
         </is>
       </c>
       <c r="E14" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F14" s="7" t="n">
         <v>7</v>
@@ -1367,12 +1367,12 @@
       </c>
       <c r="B15" s="14" t="inlineStr">
         <is>
-          <t>38604</t>
+          <t>38862</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>Cosmopol</t>
+          <t>San Miguel Izcalli</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="E15" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G15" s="13">
         <f>IFERROR(E15/(E15+F15),0)</f>
@@ -1407,24 +1407,24 @@
       </c>
       <c r="B16" s="16" t="inlineStr">
         <is>
-          <t>38606</t>
+          <t>38456</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>TlalnepantlaCarso</t>
+          <t>Plaza las Flores</t>
         </is>
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E16" s="7" t="n">
         <v>2</v>
       </c>
       <c r="F16" s="7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G16" s="9">
         <f>IFERROR(E16/(E16+F16),0)</f>
@@ -1447,21 +1447,21 @@
       </c>
       <c r="B17" s="14" t="inlineStr">
         <is>
-          <t>43193</t>
+          <t>38606</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>Cosmopol N1</t>
+          <t>TlalnepantlaCarso</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E17" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F17" s="11" t="n">
         <v>8</v>
@@ -1487,24 +1487,24 @@
       </c>
       <c r="B18" s="16" t="inlineStr">
         <is>
-          <t>38186</t>
+          <t>43193</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>Arboledas</t>
+          <t>Cosmopol N1</t>
         </is>
       </c>
       <c r="D18" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E18" s="7" t="n">
         <v>1</v>
       </c>
       <c r="F18" s="7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G18" s="9">
         <f>IFERROR(E18/(E18+F18),0)</f>
@@ -1527,17 +1527,17 @@
       </c>
       <c r="B19" s="14" t="inlineStr">
         <is>
-          <t>43194</t>
+          <t>38186</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>Atana Lindavista</t>
+          <t>Arboledas</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E19" s="11" t="n">
@@ -1567,17 +1567,17 @@
       </c>
       <c r="B20" s="16" t="inlineStr">
         <is>
-          <t>38149</t>
+          <t>43194</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>Bellavista</t>
+          <t>Atana Lindavista</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E20" s="7" t="n">
@@ -1607,17 +1607,17 @@
       </c>
       <c r="B21" s="14" t="inlineStr">
         <is>
-          <t>38527</t>
+          <t>38149</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>Camarones</t>
+          <t>Bellavista</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E21" s="11" t="n">
@@ -1647,17 +1647,17 @@
       </c>
       <c r="B22" s="16" t="inlineStr">
         <is>
-          <t>38394</t>
+          <t>38527</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>Centro Comercial Lomas Verdes</t>
+          <t>Camarones</t>
         </is>
       </c>
       <c r="D22" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E22" s="7" t="n">
@@ -1687,12 +1687,12 @@
       </c>
       <c r="B23" s="14" t="inlineStr">
         <is>
-          <t>38535</t>
+          <t>38394</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>City Center Esmeralda</t>
+          <t>Centro Comercial Lomas Verdes</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr">
@@ -1727,17 +1727,17 @@
       </c>
       <c r="B24" s="16" t="inlineStr">
         <is>
-          <t>38197</t>
+          <t>38535</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>Echegaray</t>
+          <t>City Center Esmeralda</t>
         </is>
       </c>
       <c r="D24" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E24" s="7" t="n">
@@ -1767,17 +1767,17 @@
       </c>
       <c r="B25" s="14" t="inlineStr">
         <is>
-          <t>38431</t>
+          <t>38197</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>Eduardo Molina</t>
+          <t>Echegaray</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E25" s="11" t="n">
@@ -1807,17 +1807,17 @@
       </c>
       <c r="B26" s="16" t="inlineStr">
         <is>
-          <t>38458</t>
+          <t>38431</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>El Rosario</t>
+          <t>Eduardo Molina</t>
         </is>
       </c>
       <c r="D26" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E26" s="7" t="n">
@@ -1847,17 +1847,17 @@
       </c>
       <c r="B27" s="14" t="inlineStr">
         <is>
-          <t>38363</t>
+          <t>38458</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>Galerias Atizapan</t>
+          <t>El Rosario</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E27" s="11" t="n">
@@ -1887,17 +1887,17 @@
       </c>
       <c r="B28" s="16" t="inlineStr">
         <is>
-          <t>38770</t>
+          <t>38363</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>Gustavo Baz 29</t>
+          <t>Galerias Atizapan</t>
         </is>
       </c>
       <c r="D28" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E28" s="7" t="n">
@@ -1927,17 +1927,17 @@
       </c>
       <c r="B29" s="14" t="inlineStr">
         <is>
-          <t>38661</t>
+          <t>38770</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>Jinetes</t>
+          <t>Gustavo Baz 29</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E29" s="11" t="n">
@@ -1967,17 +1967,17 @@
       </c>
       <c r="B30" s="16" t="inlineStr">
         <is>
-          <t>38205</t>
+          <t>38661</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>Lindavista</t>
+          <t>Jinetes</t>
         </is>
       </c>
       <c r="D30" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E30" s="7" t="n">
@@ -2007,12 +2007,12 @@
       </c>
       <c r="B31" s="14" t="inlineStr">
         <is>
-          <t>38207</t>
+          <t>38205</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>Lindavista II</t>
+          <t>Lindavista</t>
         </is>
       </c>
       <c r="D31" s="12" t="inlineStr">
@@ -2047,17 +2047,17 @@
       </c>
       <c r="B32" s="16" t="inlineStr">
         <is>
-          <t>38119</t>
+          <t>38207</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>Lomas Verdes</t>
+          <t>Lindavista II</t>
         </is>
       </c>
       <c r="D32" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E32" s="7" t="n">
@@ -2087,12 +2087,12 @@
       </c>
       <c r="B33" s="14" t="inlineStr">
         <is>
-          <t>38270</t>
+          <t>38119</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>Lomas Verdes II</t>
+          <t>Lomas Verdes</t>
         </is>
       </c>
       <c r="D33" s="12" t="inlineStr">
@@ -2127,17 +2127,17 @@
       </c>
       <c r="B34" s="16" t="inlineStr">
         <is>
-          <t>43111</t>
+          <t>38270</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>Montevideo Insurgentes</t>
+          <t>Lomas Verdes II</t>
         </is>
       </c>
       <c r="D34" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E34" s="7" t="n">
@@ -2167,17 +2167,17 @@
       </c>
       <c r="B35" s="14" t="inlineStr">
         <is>
-          <t>38674</t>
+          <t>43111</t>
         </is>
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>Mundo E</t>
+          <t>Montevideo Insurgentes</t>
         </is>
       </c>
       <c r="D35" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E35" s="11" t="n">
@@ -2207,12 +2207,12 @@
       </c>
       <c r="B36" s="16" t="inlineStr">
         <is>
-          <t>38845</t>
+          <t>38674</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>Mundo E II</t>
+          <t>Mundo E</t>
         </is>
       </c>
       <c r="D36" s="8" t="inlineStr">
@@ -2247,17 +2247,17 @@
       </c>
       <c r="B37" s="14" t="inlineStr">
         <is>
-          <t>43195</t>
+          <t>38845</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>Parque Jadin kiosko</t>
+          <t>Mundo E II</t>
         </is>
       </c>
       <c r="D37" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E37" s="11" t="n">
@@ -2287,17 +2287,17 @@
       </c>
       <c r="B38" s="16" t="inlineStr">
         <is>
-          <t>38937</t>
+          <t>43195</t>
         </is>
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>Parque Tepeyac Piso 1</t>
+          <t>Parque Jadin kiosko</t>
         </is>
       </c>
       <c r="D38" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E38" s="7" t="n">
@@ -2327,17 +2327,17 @@
       </c>
       <c r="B39" s="14" t="inlineStr">
         <is>
-          <t>38590</t>
+          <t>38937</t>
         </is>
       </c>
       <c r="C39" s="12" t="inlineStr">
         <is>
-          <t>Parque Toreo II</t>
+          <t>Parque Tepeyac Piso 1</t>
         </is>
       </c>
       <c r="D39" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E39" s="11" t="n">
@@ -2367,17 +2367,17 @@
       </c>
       <c r="B40" s="16" t="inlineStr">
         <is>
-          <t>38546</t>
+          <t>38590</t>
         </is>
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>Patio Claveria</t>
+          <t>Parque Toreo II</t>
         </is>
       </c>
       <c r="D40" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E40" s="7" t="n">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="B41" s="14" t="inlineStr">
         <is>
-          <t>38677</t>
+          <t>38546</t>
         </is>
       </c>
       <c r="C41" s="12" t="inlineStr">
         <is>
-          <t>Patio la Raza</t>
+          <t>Patio Claveria</t>
         </is>
       </c>
       <c r="D41" s="12" t="inlineStr">
@@ -2447,17 +2447,17 @@
       </c>
       <c r="B42" s="16" t="inlineStr">
         <is>
-          <t>38427</t>
+          <t>38677</t>
         </is>
       </c>
       <c r="C42" s="8" t="inlineStr">
         <is>
-          <t>Plaza Satelite</t>
+          <t>Patio la Raza</t>
         </is>
       </c>
       <c r="D42" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E42" s="7" t="n">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="B43" s="14" t="inlineStr">
         <is>
-          <t>38859</t>
+          <t>38176</t>
         </is>
       </c>
       <c r="C43" s="12" t="inlineStr">
         <is>
-          <t>Plaza Satelite II N1</t>
+          <t>Periferico Satélite DT</t>
         </is>
       </c>
       <c r="D43" s="12" t="inlineStr">
@@ -2527,17 +2527,17 @@
       </c>
       <c r="B44" s="16" t="inlineStr">
         <is>
-          <t>43132</t>
+          <t>38427</t>
         </is>
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t>Plaza Vista Norte</t>
+          <t>Plaza Satelite</t>
         </is>
       </c>
       <c r="D44" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E44" s="7" t="n">
@@ -2567,17 +2567,17 @@
       </c>
       <c r="B45" s="14" t="inlineStr">
         <is>
-          <t>38136</t>
+          <t>38859</t>
         </is>
       </c>
       <c r="C45" s="12" t="inlineStr">
         <is>
-          <t>Punta Norte</t>
+          <t>Plaza Satelite II N1</t>
         </is>
       </c>
       <c r="D45" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E45" s="11" t="n">
@@ -2607,17 +2607,17 @@
       </c>
       <c r="B46" s="16" t="inlineStr">
         <is>
-          <t>43152</t>
+          <t>43132</t>
         </is>
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t>Samara Satélite</t>
+          <t>Plaza Vista Norte</t>
         </is>
       </c>
       <c r="D46" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E46" s="7" t="n">
@@ -2647,17 +2647,17 @@
       </c>
       <c r="B47" s="14" t="inlineStr">
         <is>
-          <t>38266</t>
+          <t>38136</t>
         </is>
       </c>
       <c r="C47" s="12" t="inlineStr">
         <is>
-          <t>San Mateo</t>
+          <t>Punta Norte</t>
         </is>
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E47" s="11" t="n">
@@ -2687,12 +2687,12 @@
       </c>
       <c r="B48" s="16" t="inlineStr">
         <is>
-          <t>38117</t>
+          <t>43152</t>
         </is>
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
-          <t>Satelite</t>
+          <t>Samara Satélite</t>
         </is>
       </c>
       <c r="D48" s="8" t="inlineStr">
@@ -2727,17 +2727,17 @@
       </c>
       <c r="B49" s="14" t="inlineStr">
         <is>
-          <t>38475</t>
+          <t>38266</t>
         </is>
       </c>
       <c r="C49" s="12" t="inlineStr">
         <is>
-          <t>Satelite Centro Civico</t>
+          <t>San Mateo</t>
         </is>
       </c>
       <c r="D49" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E49" s="11" t="n">
@@ -2767,17 +2767,17 @@
       </c>
       <c r="B50" s="16" t="inlineStr">
         <is>
-          <t>38442</t>
+          <t>38117</t>
         </is>
       </c>
       <c r="C50" s="8" t="inlineStr">
         <is>
-          <t>Sor Juana</t>
+          <t>Satelite</t>
         </is>
       </c>
       <c r="D50" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E50" s="7" t="n">
@@ -2807,17 +2807,17 @@
       </c>
       <c r="B51" s="14" t="inlineStr">
         <is>
-          <t>38925</t>
+          <t>38475</t>
         </is>
       </c>
       <c r="C51" s="12" t="inlineStr">
         <is>
-          <t>Star Medica Lomas Verdes</t>
+          <t>Satelite Centro Civico</t>
         </is>
       </c>
       <c r="D51" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E51" s="11" t="n">
@@ -2847,17 +2847,17 @@
       </c>
       <c r="B52" s="16" t="inlineStr">
         <is>
-          <t>38411</t>
+          <t>38442</t>
         </is>
       </c>
       <c r="C52" s="8" t="inlineStr">
         <is>
-          <t>Torres Lindavista</t>
+          <t>Sor Juana</t>
         </is>
       </c>
       <c r="D52" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E52" s="7" t="n">
@@ -2887,12 +2887,12 @@
       </c>
       <c r="B53" s="14" t="inlineStr">
         <is>
-          <t>43130</t>
+          <t>38925</t>
         </is>
       </c>
       <c r="C53" s="12" t="inlineStr">
         <is>
-          <t>Town Center Nicolás Romero</t>
+          <t>Star Medica Lomas Verdes</t>
         </is>
       </c>
       <c r="D53" s="12" t="inlineStr">
@@ -2927,12 +2927,12 @@
       </c>
       <c r="B54" s="16" t="inlineStr">
         <is>
-          <t>38651</t>
+          <t>38411</t>
         </is>
       </c>
       <c r="C54" s="8" t="inlineStr">
         <is>
-          <t>Via Vallejo</t>
+          <t>Torres Lindavista</t>
         </is>
       </c>
       <c r="D54" s="8" t="inlineStr">
@@ -2967,17 +2967,17 @@
       </c>
       <c r="B55" s="14" t="inlineStr">
         <is>
-          <t>38694</t>
+          <t>43130</t>
         </is>
       </c>
       <c r="C55" s="12" t="inlineStr">
         <is>
-          <t>Villas de la Hacienda</t>
+          <t>Town Center Nicolás Romero</t>
         </is>
       </c>
       <c r="D55" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E55" s="11" t="n">
@@ -3007,17 +3007,17 @@
       </c>
       <c r="B56" s="16" t="inlineStr">
         <is>
-          <t>38656</t>
+          <t>38651</t>
         </is>
       </c>
       <c r="C56" s="8" t="inlineStr">
         <is>
-          <t>Viveros de la Loma</t>
+          <t>Via Vallejo</t>
         </is>
       </c>
       <c r="D56" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E56" s="7" t="n">
@@ -3047,17 +3047,17 @@
       </c>
       <c r="B57" s="14" t="inlineStr">
         <is>
-          <t>38115</t>
+          <t>38694</t>
         </is>
       </c>
       <c r="C57" s="12" t="inlineStr">
         <is>
-          <t>Zona Azul</t>
+          <t>Villas de la Hacienda</t>
         </is>
       </c>
       <c r="D57" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E57" s="11" t="n">
@@ -3087,17 +3087,17 @@
       </c>
       <c r="B58" s="16" t="inlineStr">
         <is>
-          <t>38142</t>
+          <t>38656</t>
         </is>
       </c>
       <c r="C58" s="8" t="inlineStr">
         <is>
-          <t>Zona Esmeralda</t>
+          <t>Viveros de la Loma</t>
         </is>
       </c>
       <c r="D58" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E58" s="7" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="B59" s="14" t="inlineStr">
         <is>
-          <t>43043</t>
+          <t>38115</t>
         </is>
       </c>
       <c r="C59" s="12" t="inlineStr">
         <is>
-          <t>Atizapan</t>
+          <t>Zona Azul</t>
         </is>
       </c>
       <c r="D59" s="12" t="inlineStr">
@@ -3141,10 +3141,10 @@
         </is>
       </c>
       <c r="E59" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F59" s="11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G59" s="13">
         <f>IFERROR(E59/(E59+F59),0)</f>
@@ -3167,24 +3167,24 @@
       </c>
       <c r="B60" s="16" t="inlineStr">
         <is>
-          <t>38930</t>
+          <t>38142</t>
         </is>
       </c>
       <c r="C60" s="8" t="inlineStr">
         <is>
-          <t>Blvd. Aeropuerto dt</t>
+          <t>Zona Esmeralda</t>
         </is>
       </c>
       <c r="D60" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E60" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F60" s="7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G60" s="9">
         <f>IFERROR(E60/(E60+F60),0)</f>
@@ -3207,17 +3207,17 @@
       </c>
       <c r="B61" s="14" t="inlineStr">
         <is>
-          <t>38529</t>
+          <t>43043</t>
         </is>
       </c>
       <c r="C61" s="12" t="inlineStr">
         <is>
-          <t>Bosques de Aragon</t>
+          <t>Atizapan</t>
         </is>
       </c>
       <c r="D61" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E61" s="11" t="n">
@@ -3247,17 +3247,17 @@
       </c>
       <c r="B62" s="16" t="inlineStr">
         <is>
-          <t>38837</t>
+          <t>38930</t>
         </is>
       </c>
       <c r="C62" s="8" t="inlineStr">
         <is>
-          <t>Centenario Azcapotzalco</t>
+          <t>Blvd. Aeropuerto dt</t>
         </is>
       </c>
       <c r="D62" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E62" s="7" t="n">
@@ -3287,12 +3287,12 @@
       </c>
       <c r="B63" s="14" t="inlineStr">
         <is>
-          <t>38903</t>
+          <t>38529</t>
         </is>
       </c>
       <c r="C63" s="12" t="inlineStr">
         <is>
-          <t>Encuentro Oceania</t>
+          <t>Bosques de Aragon</t>
         </is>
       </c>
       <c r="D63" s="12" t="inlineStr">
@@ -3327,17 +3327,17 @@
       </c>
       <c r="B64" s="16" t="inlineStr">
         <is>
-          <t>38995</t>
+          <t>38837</t>
         </is>
       </c>
       <c r="C64" s="8" t="inlineStr">
         <is>
-          <t>Encuentro Oceania II</t>
+          <t>Centenario Azcapotzalco</t>
         </is>
       </c>
       <c r="D64" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E64" s="7" t="n">
@@ -3367,17 +3367,17 @@
       </c>
       <c r="B65" s="14" t="inlineStr">
         <is>
-          <t>38507</t>
+          <t>38903</t>
         </is>
       </c>
       <c r="C65" s="12" t="inlineStr">
         <is>
-          <t>Espacio Vista del Valle</t>
+          <t>Encuentro Oceania</t>
         </is>
       </c>
       <c r="D65" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E65" s="11" t="n">
@@ -3407,17 +3407,17 @@
       </c>
       <c r="B66" s="16" t="inlineStr">
         <is>
-          <t>38230</t>
+          <t>38995</t>
         </is>
       </c>
       <c r="C66" s="8" t="inlineStr">
         <is>
-          <t>ITEMS Edo de Mexico</t>
+          <t>Encuentro Oceania II</t>
         </is>
       </c>
       <c r="D66" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E66" s="7" t="n">
@@ -3447,17 +3447,17 @@
       </c>
       <c r="B67" s="14" t="inlineStr">
         <is>
-          <t>38371</t>
+          <t>38507</t>
         </is>
       </c>
       <c r="C67" s="12" t="inlineStr">
         <is>
-          <t>Montevideo DT</t>
+          <t>Espacio Vista del Valle</t>
         </is>
       </c>
       <c r="D67" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E67" s="11" t="n">
@@ -3487,17 +3487,17 @@
       </c>
       <c r="B68" s="16" t="inlineStr">
         <is>
-          <t>38965</t>
+          <t>38230</t>
         </is>
       </c>
       <c r="C68" s="8" t="inlineStr">
         <is>
-          <t>Parque Tepeyac Piso 2</t>
+          <t>ITEMS Edo de Mexico</t>
         </is>
       </c>
       <c r="D68" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E68" s="7" t="n">
@@ -3527,17 +3527,17 @@
       </c>
       <c r="B69" s="14" t="inlineStr">
         <is>
-          <t>38792</t>
+          <t>38371</t>
         </is>
       </c>
       <c r="C69" s="12" t="inlineStr">
         <is>
-          <t>Pasaje Tlanepantla</t>
+          <t>Montevideo DT</t>
         </is>
       </c>
       <c r="D69" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E69" s="11" t="n">
@@ -3567,17 +3567,17 @@
       </c>
       <c r="B70" s="16" t="inlineStr">
         <is>
-          <t>38176</t>
+          <t>38965</t>
         </is>
       </c>
       <c r="C70" s="8" t="inlineStr">
         <is>
-          <t>Periferico Satélite DT</t>
+          <t>Parque Tepeyac Piso 2</t>
         </is>
       </c>
       <c r="D70" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E70" s="7" t="n">
@@ -3607,17 +3607,17 @@
       </c>
       <c r="B71" s="14" t="inlineStr">
         <is>
-          <t>38924</t>
+          <t>38792</t>
         </is>
       </c>
       <c r="C71" s="12" t="inlineStr">
         <is>
-          <t>Plaza Aeropuerto</t>
+          <t>Pasaje Tlanepantla</t>
         </is>
       </c>
       <c r="D71" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E71" s="11" t="n">
@@ -3647,12 +3647,12 @@
       </c>
       <c r="B72" s="16" t="inlineStr">
         <is>
-          <t>38719</t>
+          <t>38924</t>
         </is>
       </c>
       <c r="C72" s="8" t="inlineStr">
         <is>
-          <t>Plaza Fortuna</t>
+          <t>Plaza Aeropuerto</t>
         </is>
       </c>
       <c r="D72" s="8" t="inlineStr">
@@ -3892,7 +3892,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Centro Norte · Corte 30/08/2026 21:32</t>
+          <t>Centro Norte · Corte 30/08/2026 23:20</t>
         </is>
       </c>
     </row>
@@ -3948,10 +3948,10 @@
         </is>
       </c>
       <c r="C5" s="11" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E5" s="13">
         <f>IFERROR(C5/(C5+D5),0)</f>
@@ -4018,10 +4018,10 @@
         </is>
       </c>
       <c r="C7" s="11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E7" s="13">
         <f>IFERROR(C7/(C7+D7),0)</f>
@@ -4053,10 +4053,10 @@
         </is>
       </c>
       <c r="C8" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E8" s="9">
         <f>IFERROR(C8/(C8+D8),0)</f>
@@ -4088,10 +4088,10 @@
         </is>
       </c>
       <c r="C9" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D9" s="11" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E9" s="13">
         <f>IFERROR(C9/(C9+D9),0)</f>
@@ -4123,10 +4123,10 @@
         </is>
       </c>
       <c r="C10" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E10" s="9">
         <f>IFERROR(C10/(C10+D10),0)</f>
@@ -4158,10 +4158,10 @@
         </is>
       </c>
       <c r="C11" s="11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E11" s="13">
         <f>IFERROR(C11/(C11+D11),0)</f>
@@ -4263,10 +4263,10 @@
         </is>
       </c>
       <c r="C14" s="7" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E14" s="9">
         <f>IFERROR(C14/(C14+D14),0)</f>

--- a/exports/Resumen_Evidencias_OPS.xlsx
+++ b/exports/Resumen_Evidencias_OPS.xlsx
@@ -578,7 +578,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Centro Norte · Corte 30/08/2026 23:20</t>
+          <t>Centro Norte · Corte 31/08/2026 07:51</t>
         </is>
       </c>
     </row>
@@ -601,10 +601,10 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="E6" s="5">
         <f>IFERROR(A6/(A6+C6),0)</f>
@@ -667,10 +667,10 @@
         <v>10</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F10" s="9">
         <f>IFERROR(D10/(D10+E10),0)</f>
@@ -832,10 +832,10 @@
         <v>11</v>
       </c>
       <c r="D15" s="11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E15" s="12" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F15" s="13">
         <f>IFERROR(D15/(D15+E15),0)</f>
@@ -910,7 +910,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Centro Norte · Corte 30/08/2026 23:20</t>
+          <t>Centro Norte · Corte 31/08/2026 07:51</t>
         </is>
       </c>
     </row>
@@ -1287,12 +1287,12 @@
       </c>
       <c r="B13" s="14" t="inlineStr">
         <is>
-          <t>38604</t>
+          <t>38862</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>Cosmopol</t>
+          <t>San Miguel Izcalli</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
@@ -1301,23 +1301,23 @@
         </is>
       </c>
       <c r="E13" s="11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G13" s="13">
         <f>IFERROR(E13/(E13+F13),0)</f>
         <v/>
       </c>
-      <c r="H13" s="10" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I13" s="10" t="inlineStr">
-        <is>
-          <t>Priorizar hoy</t>
+      <c r="H13" s="15" t="inlineStr">
+        <is>
+          <t>Seguimiento</t>
+        </is>
+      </c>
+      <c r="I13" s="15" t="inlineStr">
+        <is>
+          <t>Dar seguimiento</t>
         </is>
       </c>
     </row>
@@ -1327,12 +1327,12 @@
       </c>
       <c r="B14" s="16" t="inlineStr">
         <is>
-          <t>38515</t>
+          <t>38604</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Patio Ecatepec</t>
+          <t>Cosmopol</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr">
@@ -1367,12 +1367,12 @@
       </c>
       <c r="B15" s="14" t="inlineStr">
         <is>
-          <t>38862</t>
+          <t>38515</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>San Miguel Izcalli</t>
+          <t>Patio Ecatepec</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
@@ -2527,17 +2527,17 @@
       </c>
       <c r="B44" s="16" t="inlineStr">
         <is>
-          <t>38427</t>
+          <t>38924</t>
         </is>
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t>Plaza Satelite</t>
+          <t>Plaza Aeropuerto</t>
         </is>
       </c>
       <c r="D44" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E44" s="7" t="n">
@@ -2567,12 +2567,12 @@
       </c>
       <c r="B45" s="14" t="inlineStr">
         <is>
-          <t>38859</t>
+          <t>38427</t>
         </is>
       </c>
       <c r="C45" s="12" t="inlineStr">
         <is>
-          <t>Plaza Satelite II N1</t>
+          <t>Plaza Satelite</t>
         </is>
       </c>
       <c r="D45" s="12" t="inlineStr">
@@ -2607,17 +2607,17 @@
       </c>
       <c r="B46" s="16" t="inlineStr">
         <is>
-          <t>43132</t>
+          <t>38859</t>
         </is>
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t>Plaza Vista Norte</t>
+          <t>Plaza Satelite II N1</t>
         </is>
       </c>
       <c r="D46" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E46" s="7" t="n">
@@ -2647,17 +2647,17 @@
       </c>
       <c r="B47" s="14" t="inlineStr">
         <is>
-          <t>38136</t>
+          <t>43132</t>
         </is>
       </c>
       <c r="C47" s="12" t="inlineStr">
         <is>
-          <t>Punta Norte</t>
+          <t>Plaza Vista Norte</t>
         </is>
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E47" s="11" t="n">
@@ -2687,17 +2687,17 @@
       </c>
       <c r="B48" s="16" t="inlineStr">
         <is>
-          <t>43152</t>
+          <t>38136</t>
         </is>
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
-          <t>Samara Satélite</t>
+          <t>Punta Norte</t>
         </is>
       </c>
       <c r="D48" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E48" s="7" t="n">
@@ -2727,17 +2727,17 @@
       </c>
       <c r="B49" s="14" t="inlineStr">
         <is>
-          <t>38266</t>
+          <t>43152</t>
         </is>
       </c>
       <c r="C49" s="12" t="inlineStr">
         <is>
-          <t>San Mateo</t>
+          <t>Samara Satélite</t>
         </is>
       </c>
       <c r="D49" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E49" s="11" t="n">
@@ -2767,17 +2767,17 @@
       </c>
       <c r="B50" s="16" t="inlineStr">
         <is>
-          <t>38117</t>
+          <t>38266</t>
         </is>
       </c>
       <c r="C50" s="8" t="inlineStr">
         <is>
-          <t>Satelite</t>
+          <t>San Mateo</t>
         </is>
       </c>
       <c r="D50" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E50" s="7" t="n">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="B51" s="14" t="inlineStr">
         <is>
-          <t>38475</t>
+          <t>38117</t>
         </is>
       </c>
       <c r="C51" s="12" t="inlineStr">
         <is>
-          <t>Satelite Centro Civico</t>
+          <t>Satelite</t>
         </is>
       </c>
       <c r="D51" s="12" t="inlineStr">
@@ -2847,17 +2847,17 @@
       </c>
       <c r="B52" s="16" t="inlineStr">
         <is>
-          <t>38442</t>
+          <t>38475</t>
         </is>
       </c>
       <c r="C52" s="8" t="inlineStr">
         <is>
-          <t>Sor Juana</t>
+          <t>Satelite Centro Civico</t>
         </is>
       </c>
       <c r="D52" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E52" s="7" t="n">
@@ -2887,17 +2887,17 @@
       </c>
       <c r="B53" s="14" t="inlineStr">
         <is>
-          <t>38925</t>
+          <t>38442</t>
         </is>
       </c>
       <c r="C53" s="12" t="inlineStr">
         <is>
-          <t>Star Medica Lomas Verdes</t>
+          <t>Sor Juana</t>
         </is>
       </c>
       <c r="D53" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E53" s="11" t="n">
@@ -2927,17 +2927,17 @@
       </c>
       <c r="B54" s="16" t="inlineStr">
         <is>
-          <t>38411</t>
+          <t>38925</t>
         </is>
       </c>
       <c r="C54" s="8" t="inlineStr">
         <is>
-          <t>Torres Lindavista</t>
+          <t>Star Medica Lomas Verdes</t>
         </is>
       </c>
       <c r="D54" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E54" s="7" t="n">
@@ -2967,17 +2967,17 @@
       </c>
       <c r="B55" s="14" t="inlineStr">
         <is>
-          <t>43130</t>
+          <t>38411</t>
         </is>
       </c>
       <c r="C55" s="12" t="inlineStr">
         <is>
-          <t>Town Center Nicolás Romero</t>
+          <t>Torres Lindavista</t>
         </is>
       </c>
       <c r="D55" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E55" s="11" t="n">
@@ -3007,17 +3007,17 @@
       </c>
       <c r="B56" s="16" t="inlineStr">
         <is>
-          <t>38651</t>
+          <t>43130</t>
         </is>
       </c>
       <c r="C56" s="8" t="inlineStr">
         <is>
-          <t>Via Vallejo</t>
+          <t>Town Center Nicolás Romero</t>
         </is>
       </c>
       <c r="D56" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E56" s="7" t="n">
@@ -3047,17 +3047,17 @@
       </c>
       <c r="B57" s="14" t="inlineStr">
         <is>
-          <t>38694</t>
+          <t>38651</t>
         </is>
       </c>
       <c r="C57" s="12" t="inlineStr">
         <is>
-          <t>Villas de la Hacienda</t>
+          <t>Via Vallejo</t>
         </is>
       </c>
       <c r="D57" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E57" s="11" t="n">
@@ -3087,17 +3087,17 @@
       </c>
       <c r="B58" s="16" t="inlineStr">
         <is>
-          <t>38656</t>
+          <t>38694</t>
         </is>
       </c>
       <c r="C58" s="8" t="inlineStr">
         <is>
-          <t>Viveros de la Loma</t>
+          <t>Villas de la Hacienda</t>
         </is>
       </c>
       <c r="D58" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E58" s="7" t="n">
@@ -3127,17 +3127,17 @@
       </c>
       <c r="B59" s="14" t="inlineStr">
         <is>
-          <t>38115</t>
+          <t>38656</t>
         </is>
       </c>
       <c r="C59" s="12" t="inlineStr">
         <is>
-          <t>Zona Azul</t>
+          <t>Viveros de la Loma</t>
         </is>
       </c>
       <c r="D59" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E59" s="11" t="n">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="B60" s="16" t="inlineStr">
         <is>
-          <t>38142</t>
+          <t>38115</t>
         </is>
       </c>
       <c r="C60" s="8" t="inlineStr">
         <is>
-          <t>Zona Esmeralda</t>
+          <t>Zona Azul</t>
         </is>
       </c>
       <c r="D60" s="8" t="inlineStr">
@@ -3207,12 +3207,12 @@
       </c>
       <c r="B61" s="14" t="inlineStr">
         <is>
-          <t>43043</t>
+          <t>38142</t>
         </is>
       </c>
       <c r="C61" s="12" t="inlineStr">
         <is>
-          <t>Atizapan</t>
+          <t>Zona Esmeralda</t>
         </is>
       </c>
       <c r="D61" s="12" t="inlineStr">
@@ -3221,10 +3221,10 @@
         </is>
       </c>
       <c r="E61" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F61" s="11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G61" s="13">
         <f>IFERROR(E61/(E61+F61),0)</f>
@@ -3247,17 +3247,17 @@
       </c>
       <c r="B62" s="16" t="inlineStr">
         <is>
-          <t>38930</t>
+          <t>43043</t>
         </is>
       </c>
       <c r="C62" s="8" t="inlineStr">
         <is>
-          <t>Blvd. Aeropuerto dt</t>
+          <t>Atizapan</t>
         </is>
       </c>
       <c r="D62" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E62" s="7" t="n">
@@ -3287,12 +3287,12 @@
       </c>
       <c r="B63" s="14" t="inlineStr">
         <is>
-          <t>38529</t>
+          <t>38930</t>
         </is>
       </c>
       <c r="C63" s="12" t="inlineStr">
         <is>
-          <t>Bosques de Aragon</t>
+          <t>Blvd. Aeropuerto dt</t>
         </is>
       </c>
       <c r="D63" s="12" t="inlineStr">
@@ -3327,17 +3327,17 @@
       </c>
       <c r="B64" s="16" t="inlineStr">
         <is>
-          <t>38837</t>
+          <t>38529</t>
         </is>
       </c>
       <c r="C64" s="8" t="inlineStr">
         <is>
-          <t>Centenario Azcapotzalco</t>
+          <t>Bosques de Aragon</t>
         </is>
       </c>
       <c r="D64" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E64" s="7" t="n">
@@ -3367,17 +3367,17 @@
       </c>
       <c r="B65" s="14" t="inlineStr">
         <is>
-          <t>38903</t>
+          <t>38837</t>
         </is>
       </c>
       <c r="C65" s="12" t="inlineStr">
         <is>
-          <t>Encuentro Oceania</t>
+          <t>Centenario Azcapotzalco</t>
         </is>
       </c>
       <c r="D65" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E65" s="11" t="n">
@@ -3407,12 +3407,12 @@
       </c>
       <c r="B66" s="16" t="inlineStr">
         <is>
-          <t>38995</t>
+          <t>38903</t>
         </is>
       </c>
       <c r="C66" s="8" t="inlineStr">
         <is>
-          <t>Encuentro Oceania II</t>
+          <t>Encuentro Oceania</t>
         </is>
       </c>
       <c r="D66" s="8" t="inlineStr">
@@ -3447,17 +3447,17 @@
       </c>
       <c r="B67" s="14" t="inlineStr">
         <is>
-          <t>38507</t>
+          <t>38995</t>
         </is>
       </c>
       <c r="C67" s="12" t="inlineStr">
         <is>
-          <t>Espacio Vista del Valle</t>
+          <t>Encuentro Oceania II</t>
         </is>
       </c>
       <c r="D67" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E67" s="11" t="n">
@@ -3487,17 +3487,17 @@
       </c>
       <c r="B68" s="16" t="inlineStr">
         <is>
-          <t>38230</t>
+          <t>38507</t>
         </is>
       </c>
       <c r="C68" s="8" t="inlineStr">
         <is>
-          <t>ITEMS Edo de Mexico</t>
+          <t>Espacio Vista del Valle</t>
         </is>
       </c>
       <c r="D68" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E68" s="7" t="n">
@@ -3527,17 +3527,17 @@
       </c>
       <c r="B69" s="14" t="inlineStr">
         <is>
-          <t>38371</t>
+          <t>38230</t>
         </is>
       </c>
       <c r="C69" s="12" t="inlineStr">
         <is>
-          <t>Montevideo DT</t>
+          <t>ITEMS Edo de Mexico</t>
         </is>
       </c>
       <c r="D69" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E69" s="11" t="n">
@@ -3567,17 +3567,17 @@
       </c>
       <c r="B70" s="16" t="inlineStr">
         <is>
-          <t>38965</t>
+          <t>38371</t>
         </is>
       </c>
       <c r="C70" s="8" t="inlineStr">
         <is>
-          <t>Parque Tepeyac Piso 2</t>
+          <t>Montevideo DT</t>
         </is>
       </c>
       <c r="D70" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E70" s="7" t="n">
@@ -3607,17 +3607,17 @@
       </c>
       <c r="B71" s="14" t="inlineStr">
         <is>
-          <t>38792</t>
+          <t>38965</t>
         </is>
       </c>
       <c r="C71" s="12" t="inlineStr">
         <is>
-          <t>Pasaje Tlanepantla</t>
+          <t>Parque Tepeyac Piso 2</t>
         </is>
       </c>
       <c r="D71" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E71" s="11" t="n">
@@ -3647,17 +3647,17 @@
       </c>
       <c r="B72" s="16" t="inlineStr">
         <is>
-          <t>38924</t>
+          <t>38792</t>
         </is>
       </c>
       <c r="C72" s="8" t="inlineStr">
         <is>
-          <t>Plaza Aeropuerto</t>
+          <t>Pasaje Tlanepantla</t>
         </is>
       </c>
       <c r="D72" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E72" s="7" t="n">
@@ -3892,7 +3892,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Centro Norte · Corte 30/08/2026 23:20</t>
+          <t>Centro Norte · Corte 31/08/2026 07:51</t>
         </is>
       </c>
     </row>
@@ -4088,10 +4088,10 @@
         </is>
       </c>
       <c r="C9" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D9" s="11" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E9" s="13">
         <f>IFERROR(C9/(C9+D9),0)</f>
@@ -4263,10 +4263,10 @@
         </is>
       </c>
       <c r="C14" s="7" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E14" s="9">
         <f>IFERROR(C14/(C14+D14),0)</f>

--- a/exports/Resumen_Evidencias_OPS.xlsx
+++ b/exports/Resumen_Evidencias_OPS.xlsx
@@ -578,7 +578,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Centro Norte · Corte 31/08/2026 07:51</t>
+          <t>Centro Norte · Corte 31/08/2026 12:28</t>
         </is>
       </c>
     </row>
@@ -601,10 +601,10 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>622</v>
+        <v>616</v>
       </c>
       <c r="E6" s="5">
         <f>IFERROR(A6/(A6+C6),0)</f>
@@ -667,10 +667,10 @@
         <v>10</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="F10" s="9">
         <f>IFERROR(D10/(D10+E10),0)</f>
@@ -726,17 +726,17 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño</t>
+          <t>Veronica Garcia</t>
         </is>
       </c>
       <c r="C12" s="7" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D12" s="7" t="n">
         <v>11</v>
       </c>
       <c r="E12" s="8" t="n">
-        <v>119</v>
+        <v>99</v>
       </c>
       <c r="F12" s="9">
         <f>IFERROR(D12/(D12+E12),0)</f>
@@ -759,7 +759,7 @@
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Garcia</t>
+          <t>Vanessa Carreño</t>
         </is>
       </c>
       <c r="C13" s="11" t="n">
@@ -792,17 +792,17 @@
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina</t>
+          <t>Yazmin Garcia</t>
         </is>
       </c>
       <c r="C14" s="7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E14" s="8" t="n">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="F14" s="9">
         <f>IFERROR(D14/(D14+E14),0)</f>
@@ -825,17 +825,17 @@
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia</t>
+          <t>Nancy Carolina</t>
         </is>
       </c>
       <c r="C15" s="11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D15" s="11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E15" s="12" t="n">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="F15" s="13">
         <f>IFERROR(D15/(D15+E15),0)</f>
@@ -910,7 +910,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Centro Norte · Corte 31/08/2026 07:51</t>
+          <t>Centro Norte · Corte 31/08/2026 12:28</t>
         </is>
       </c>
     </row>
@@ -967,24 +967,24 @@
       </c>
       <c r="B5" s="14" t="inlineStr">
         <is>
-          <t>38695</t>
+          <t>38719</t>
         </is>
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>Cetram 4 Caminos</t>
+          <t>Plaza Fortuna</t>
         </is>
       </c>
       <c r="D5" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E5" s="11" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G5" s="13">
         <f>IFERROR(E5/(E5+F5),0)</f>
@@ -1007,17 +1007,17 @@
       </c>
       <c r="B6" s="16" t="inlineStr">
         <is>
-          <t>38401</t>
+          <t>38695</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>Coacalco</t>
+          <t>Cetram 4 Caminos</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E6" s="7" t="n">
@@ -1047,12 +1047,12 @@
       </c>
       <c r="B7" s="14" t="inlineStr">
         <is>
-          <t>38333</t>
+          <t>38401</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>Izcalli Mega</t>
+          <t>Coacalco</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="B8" s="16" t="inlineStr">
         <is>
-          <t>38368</t>
+          <t>38333</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>Luna Park</t>
+          <t>Izcalli Mega</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
@@ -1127,17 +1127,17 @@
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>38561</t>
+          <t>38368</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>Parque Toreo</t>
+          <t>Luna Park</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E9" s="11" t="n">
@@ -1167,17 +1167,17 @@
       </c>
       <c r="B10" s="16" t="inlineStr">
         <is>
-          <t>38719</t>
+          <t>38561</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>Plaza Fortuna</t>
+          <t>Parque Toreo</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E10" s="7" t="n">
@@ -1207,12 +1207,12 @@
       </c>
       <c r="B11" s="14" t="inlineStr">
         <is>
-          <t>38894</t>
+          <t>38862</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>Galerias Perinorte</t>
+          <t>San Miguel Izcalli</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
@@ -1221,10 +1221,10 @@
         </is>
       </c>
       <c r="E11" s="11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G11" s="13">
         <f>IFERROR(E11/(E11+F11),0)</f>
@@ -1247,12 +1247,12 @@
       </c>
       <c r="B12" s="16" t="inlineStr">
         <is>
-          <t>38339</t>
+          <t>38894</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Galerias Perinorte</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
@@ -1287,12 +1287,12 @@
       </c>
       <c r="B13" s="14" t="inlineStr">
         <is>
-          <t>38862</t>
+          <t>38515</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>San Miguel Izcalli</t>
+          <t>Patio Ecatepec</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
@@ -1327,12 +1327,12 @@
       </c>
       <c r="B14" s="16" t="inlineStr">
         <is>
-          <t>38604</t>
+          <t>38339</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Cosmopol</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr">
@@ -1341,23 +1341,23 @@
         </is>
       </c>
       <c r="E14" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F14" s="7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G14" s="9">
         <f>IFERROR(E14/(E14+F14),0)</f>
         <v/>
       </c>
-      <c r="H14" s="10" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I14" s="10" t="inlineStr">
-        <is>
-          <t>Priorizar hoy</t>
+      <c r="H14" s="15" t="inlineStr">
+        <is>
+          <t>Seguimiento</t>
+        </is>
+      </c>
+      <c r="I14" s="15" t="inlineStr">
+        <is>
+          <t>Dar seguimiento</t>
         </is>
       </c>
     </row>
@@ -1367,12 +1367,12 @@
       </c>
       <c r="B15" s="14" t="inlineStr">
         <is>
-          <t>38515</t>
+          <t>38604</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>Patio Ecatepec</t>
+          <t>Cosmopol</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
@@ -1407,12 +1407,12 @@
       </c>
       <c r="B16" s="16" t="inlineStr">
         <is>
-          <t>38456</t>
+          <t>43193</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>Plaza las Flores</t>
+          <t>Cosmopol N1</t>
         </is>
       </c>
       <c r="D16" s="8" t="inlineStr">
@@ -1447,24 +1447,24 @@
       </c>
       <c r="B17" s="14" t="inlineStr">
         <is>
-          <t>38606</t>
+          <t>38456</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>TlalnepantlaCarso</t>
+          <t>Plaza las Flores</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E17" s="11" t="n">
         <v>2</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G17" s="13">
         <f>IFERROR(E17/(E17+F17),0)</f>
@@ -1487,21 +1487,21 @@
       </c>
       <c r="B18" s="16" t="inlineStr">
         <is>
-          <t>43193</t>
+          <t>38606</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>Cosmopol N1</t>
+          <t>TlalnepantlaCarso</t>
         </is>
       </c>
       <c r="D18" s="8" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E18" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F18" s="7" t="n">
         <v>8</v>
@@ -1647,17 +1647,17 @@
       </c>
       <c r="B22" s="16" t="inlineStr">
         <is>
-          <t>38527</t>
+          <t>38930</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>Camarones</t>
+          <t>Blvd. Aeropuerto dt</t>
         </is>
       </c>
       <c r="D22" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E22" s="7" t="n">
@@ -1687,17 +1687,17 @@
       </c>
       <c r="B23" s="14" t="inlineStr">
         <is>
-          <t>38394</t>
+          <t>38527</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>Centro Comercial Lomas Verdes</t>
+          <t>Camarones</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E23" s="11" t="n">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="B24" s="16" t="inlineStr">
         <is>
-          <t>38535</t>
+          <t>38394</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>City Center Esmeralda</t>
+          <t>Centro Comercial Lomas Verdes</t>
         </is>
       </c>
       <c r="D24" s="8" t="inlineStr">
@@ -1767,17 +1767,17 @@
       </c>
       <c r="B25" s="14" t="inlineStr">
         <is>
-          <t>38197</t>
+          <t>38535</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>Echegaray</t>
+          <t>City Center Esmeralda</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E25" s="11" t="n">
@@ -1807,17 +1807,17 @@
       </c>
       <c r="B26" s="16" t="inlineStr">
         <is>
-          <t>38431</t>
+          <t>38197</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>Eduardo Molina</t>
+          <t>Echegaray</t>
         </is>
       </c>
       <c r="D26" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E26" s="7" t="n">
@@ -1847,17 +1847,17 @@
       </c>
       <c r="B27" s="14" t="inlineStr">
         <is>
-          <t>38458</t>
+          <t>38431</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>El Rosario</t>
+          <t>Eduardo Molina</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E27" s="11" t="n">
@@ -1887,17 +1887,17 @@
       </c>
       <c r="B28" s="16" t="inlineStr">
         <is>
-          <t>38363</t>
+          <t>38458</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>Galerias Atizapan</t>
+          <t>El Rosario</t>
         </is>
       </c>
       <c r="D28" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E28" s="7" t="n">
@@ -1927,17 +1927,17 @@
       </c>
       <c r="B29" s="14" t="inlineStr">
         <is>
-          <t>38770</t>
+          <t>38363</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>Gustavo Baz 29</t>
+          <t>Galerias Atizapan</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E29" s="11" t="n">
@@ -1967,17 +1967,17 @@
       </c>
       <c r="B30" s="16" t="inlineStr">
         <is>
-          <t>38661</t>
+          <t>38770</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>Jinetes</t>
+          <t>Gustavo Baz 29</t>
         </is>
       </c>
       <c r="D30" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E30" s="7" t="n">
@@ -2007,17 +2007,17 @@
       </c>
       <c r="B31" s="14" t="inlineStr">
         <is>
-          <t>38205</t>
+          <t>38661</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>Lindavista</t>
+          <t>Jinetes</t>
         </is>
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E31" s="11" t="n">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="B32" s="16" t="inlineStr">
         <is>
-          <t>38207</t>
+          <t>38205</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>Lindavista II</t>
+          <t>Lindavista</t>
         </is>
       </c>
       <c r="D32" s="8" t="inlineStr">
@@ -2087,17 +2087,17 @@
       </c>
       <c r="B33" s="14" t="inlineStr">
         <is>
-          <t>38119</t>
+          <t>38207</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>Lomas Verdes</t>
+          <t>Lindavista II</t>
         </is>
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E33" s="11" t="n">
@@ -2127,12 +2127,12 @@
       </c>
       <c r="B34" s="16" t="inlineStr">
         <is>
-          <t>38270</t>
+          <t>38119</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>Lomas Verdes II</t>
+          <t>Lomas Verdes</t>
         </is>
       </c>
       <c r="D34" s="8" t="inlineStr">
@@ -2167,17 +2167,17 @@
       </c>
       <c r="B35" s="14" t="inlineStr">
         <is>
-          <t>43111</t>
+          <t>38270</t>
         </is>
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>Montevideo Insurgentes</t>
+          <t>Lomas Verdes II</t>
         </is>
       </c>
       <c r="D35" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E35" s="11" t="n">
@@ -2207,17 +2207,17 @@
       </c>
       <c r="B36" s="16" t="inlineStr">
         <is>
-          <t>38674</t>
+          <t>43111</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>Mundo E</t>
+          <t>Montevideo Insurgentes</t>
         </is>
       </c>
       <c r="D36" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E36" s="7" t="n">
@@ -2247,12 +2247,12 @@
       </c>
       <c r="B37" s="14" t="inlineStr">
         <is>
-          <t>38845</t>
+          <t>38674</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>Mundo E II</t>
+          <t>Mundo E</t>
         </is>
       </c>
       <c r="D37" s="12" t="inlineStr">
@@ -2287,17 +2287,17 @@
       </c>
       <c r="B38" s="16" t="inlineStr">
         <is>
-          <t>43195</t>
+          <t>38845</t>
         </is>
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>Parque Jadin kiosko</t>
+          <t>Mundo E II</t>
         </is>
       </c>
       <c r="D38" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E38" s="7" t="n">
@@ -2327,17 +2327,17 @@
       </c>
       <c r="B39" s="14" t="inlineStr">
         <is>
-          <t>38937</t>
+          <t>43195</t>
         </is>
       </c>
       <c r="C39" s="12" t="inlineStr">
         <is>
-          <t>Parque Tepeyac Piso 1</t>
+          <t>Parque Jadin kiosko</t>
         </is>
       </c>
       <c r="D39" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E39" s="11" t="n">
@@ -2367,17 +2367,17 @@
       </c>
       <c r="B40" s="16" t="inlineStr">
         <is>
-          <t>38590</t>
+          <t>38937</t>
         </is>
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>Parque Toreo II</t>
+          <t>Parque Tepeyac Piso 1</t>
         </is>
       </c>
       <c r="D40" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E40" s="7" t="n">
@@ -2407,17 +2407,17 @@
       </c>
       <c r="B41" s="14" t="inlineStr">
         <is>
-          <t>38546</t>
+          <t>38590</t>
         </is>
       </c>
       <c r="C41" s="12" t="inlineStr">
         <is>
-          <t>Patio Claveria</t>
+          <t>Parque Toreo II</t>
         </is>
       </c>
       <c r="D41" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E41" s="11" t="n">
@@ -2447,12 +2447,12 @@
       </c>
       <c r="B42" s="16" t="inlineStr">
         <is>
-          <t>38677</t>
+          <t>38546</t>
         </is>
       </c>
       <c r="C42" s="8" t="inlineStr">
         <is>
-          <t>Patio la Raza</t>
+          <t>Patio Claveria</t>
         </is>
       </c>
       <c r="D42" s="8" t="inlineStr">
@@ -2487,17 +2487,17 @@
       </c>
       <c r="B43" s="14" t="inlineStr">
         <is>
-          <t>38176</t>
+          <t>38677</t>
         </is>
       </c>
       <c r="C43" s="12" t="inlineStr">
         <is>
-          <t>Periferico Satélite DT</t>
+          <t>Patio la Raza</t>
         </is>
       </c>
       <c r="D43" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E43" s="11" t="n">
@@ -2527,17 +2527,17 @@
       </c>
       <c r="B44" s="16" t="inlineStr">
         <is>
-          <t>38924</t>
+          <t>38176</t>
         </is>
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t>Plaza Aeropuerto</t>
+          <t>Periferico Satélite DT</t>
         </is>
       </c>
       <c r="D44" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E44" s="7" t="n">
@@ -2567,17 +2567,17 @@
       </c>
       <c r="B45" s="14" t="inlineStr">
         <is>
-          <t>38427</t>
+          <t>38924</t>
         </is>
       </c>
       <c r="C45" s="12" t="inlineStr">
         <is>
-          <t>Plaza Satelite</t>
+          <t>Plaza Aeropuerto</t>
         </is>
       </c>
       <c r="D45" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E45" s="11" t="n">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="B46" s="16" t="inlineStr">
         <is>
-          <t>38859</t>
+          <t>38427</t>
         </is>
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t>Plaza Satelite II N1</t>
+          <t>Plaza Satelite</t>
         </is>
       </c>
       <c r="D46" s="8" t="inlineStr">
@@ -2647,17 +2647,17 @@
       </c>
       <c r="B47" s="14" t="inlineStr">
         <is>
-          <t>43132</t>
+          <t>38859</t>
         </is>
       </c>
       <c r="C47" s="12" t="inlineStr">
         <is>
-          <t>Plaza Vista Norte</t>
+          <t>Plaza Satelite II N1</t>
         </is>
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E47" s="11" t="n">
@@ -2687,17 +2687,17 @@
       </c>
       <c r="B48" s="16" t="inlineStr">
         <is>
-          <t>38136</t>
+          <t>43132</t>
         </is>
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
-          <t>Punta Norte</t>
+          <t>Plaza Vista Norte</t>
         </is>
       </c>
       <c r="D48" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E48" s="7" t="n">
@@ -2727,17 +2727,17 @@
       </c>
       <c r="B49" s="14" t="inlineStr">
         <is>
-          <t>43152</t>
+          <t>38136</t>
         </is>
       </c>
       <c r="C49" s="12" t="inlineStr">
         <is>
-          <t>Samara Satélite</t>
+          <t>Punta Norte</t>
         </is>
       </c>
       <c r="D49" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E49" s="11" t="n">
@@ -2767,17 +2767,17 @@
       </c>
       <c r="B50" s="16" t="inlineStr">
         <is>
-          <t>38266</t>
+          <t>43152</t>
         </is>
       </c>
       <c r="C50" s="8" t="inlineStr">
         <is>
-          <t>San Mateo</t>
+          <t>Samara Satélite</t>
         </is>
       </c>
       <c r="D50" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E50" s="7" t="n">
@@ -2807,17 +2807,17 @@
       </c>
       <c r="B51" s="14" t="inlineStr">
         <is>
-          <t>38117</t>
+          <t>38266</t>
         </is>
       </c>
       <c r="C51" s="12" t="inlineStr">
         <is>
-          <t>Satelite</t>
+          <t>San Mateo</t>
         </is>
       </c>
       <c r="D51" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E51" s="11" t="n">
@@ -2847,12 +2847,12 @@
       </c>
       <c r="B52" s="16" t="inlineStr">
         <is>
-          <t>38475</t>
+          <t>38117</t>
         </is>
       </c>
       <c r="C52" s="8" t="inlineStr">
         <is>
-          <t>Satelite Centro Civico</t>
+          <t>Satelite</t>
         </is>
       </c>
       <c r="D52" s="8" t="inlineStr">
@@ -2887,17 +2887,17 @@
       </c>
       <c r="B53" s="14" t="inlineStr">
         <is>
-          <t>38442</t>
+          <t>38475</t>
         </is>
       </c>
       <c r="C53" s="12" t="inlineStr">
         <is>
-          <t>Sor Juana</t>
+          <t>Satelite Centro Civico</t>
         </is>
       </c>
       <c r="D53" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E53" s="11" t="n">
@@ -2927,17 +2927,17 @@
       </c>
       <c r="B54" s="16" t="inlineStr">
         <is>
-          <t>38925</t>
+          <t>38442</t>
         </is>
       </c>
       <c r="C54" s="8" t="inlineStr">
         <is>
-          <t>Star Medica Lomas Verdes</t>
+          <t>Sor Juana</t>
         </is>
       </c>
       <c r="D54" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E54" s="7" t="n">
@@ -2967,17 +2967,17 @@
       </c>
       <c r="B55" s="14" t="inlineStr">
         <is>
-          <t>38411</t>
+          <t>38925</t>
         </is>
       </c>
       <c r="C55" s="12" t="inlineStr">
         <is>
-          <t>Torres Lindavista</t>
+          <t>Star Medica Lomas Verdes</t>
         </is>
       </c>
       <c r="D55" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E55" s="11" t="n">
@@ -3007,17 +3007,17 @@
       </c>
       <c r="B56" s="16" t="inlineStr">
         <is>
-          <t>43130</t>
+          <t>38411</t>
         </is>
       </c>
       <c r="C56" s="8" t="inlineStr">
         <is>
-          <t>Town Center Nicolás Romero</t>
+          <t>Torres Lindavista</t>
         </is>
       </c>
       <c r="D56" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E56" s="7" t="n">
@@ -3047,17 +3047,17 @@
       </c>
       <c r="B57" s="14" t="inlineStr">
         <is>
-          <t>38651</t>
+          <t>43130</t>
         </is>
       </c>
       <c r="C57" s="12" t="inlineStr">
         <is>
-          <t>Via Vallejo</t>
+          <t>Town Center Nicolás Romero</t>
         </is>
       </c>
       <c r="D57" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E57" s="11" t="n">
@@ -3087,17 +3087,17 @@
       </c>
       <c r="B58" s="16" t="inlineStr">
         <is>
-          <t>38694</t>
+          <t>38651</t>
         </is>
       </c>
       <c r="C58" s="8" t="inlineStr">
         <is>
-          <t>Villas de la Hacienda</t>
+          <t>Via Vallejo</t>
         </is>
       </c>
       <c r="D58" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E58" s="7" t="n">
@@ -3127,17 +3127,17 @@
       </c>
       <c r="B59" s="14" t="inlineStr">
         <is>
-          <t>38656</t>
+          <t>38694</t>
         </is>
       </c>
       <c r="C59" s="12" t="inlineStr">
         <is>
-          <t>Viveros de la Loma</t>
+          <t>Villas de la Hacienda</t>
         </is>
       </c>
       <c r="D59" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E59" s="11" t="n">
@@ -3167,17 +3167,17 @@
       </c>
       <c r="B60" s="16" t="inlineStr">
         <is>
-          <t>38115</t>
+          <t>38656</t>
         </is>
       </c>
       <c r="C60" s="8" t="inlineStr">
         <is>
-          <t>Zona Azul</t>
+          <t>Viveros de la Loma</t>
         </is>
       </c>
       <c r="D60" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E60" s="7" t="n">
@@ -3207,12 +3207,12 @@
       </c>
       <c r="B61" s="14" t="inlineStr">
         <is>
-          <t>38142</t>
+          <t>38115</t>
         </is>
       </c>
       <c r="C61" s="12" t="inlineStr">
         <is>
-          <t>Zona Esmeralda</t>
+          <t>Zona Azul</t>
         </is>
       </c>
       <c r="D61" s="12" t="inlineStr">
@@ -3247,12 +3247,12 @@
       </c>
       <c r="B62" s="16" t="inlineStr">
         <is>
-          <t>43043</t>
+          <t>38142</t>
         </is>
       </c>
       <c r="C62" s="8" t="inlineStr">
         <is>
-          <t>Atizapan</t>
+          <t>Zona Esmeralda</t>
         </is>
       </c>
       <c r="D62" s="8" t="inlineStr">
@@ -3261,10 +3261,10 @@
         </is>
       </c>
       <c r="E62" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F62" s="7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G62" s="9">
         <f>IFERROR(E62/(E62+F62),0)</f>
@@ -3287,17 +3287,17 @@
       </c>
       <c r="B63" s="14" t="inlineStr">
         <is>
-          <t>38930</t>
+          <t>43043</t>
         </is>
       </c>
       <c r="C63" s="12" t="inlineStr">
         <is>
-          <t>Blvd. Aeropuerto dt</t>
+          <t>Atizapan</t>
         </is>
       </c>
       <c r="D63" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E63" s="11" t="n">
@@ -3892,7 +3892,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Centro Norte · Corte 31/08/2026 07:51</t>
+          <t>Centro Norte · Corte 31/08/2026 12:28</t>
         </is>
       </c>
     </row>
@@ -3983,10 +3983,10 @@
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D6" s="7" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E6" s="9">
         <f>IFERROR(C6/(C6+D6),0)</f>
@@ -4018,10 +4018,10 @@
         </is>
       </c>
       <c r="C7" s="11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E7" s="13">
         <f>IFERROR(C7/(C7+D7),0)</f>
@@ -4088,10 +4088,10 @@
         </is>
       </c>
       <c r="C9" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D9" s="11" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E9" s="13">
         <f>IFERROR(C9/(C9+D9),0)</f>
@@ -4263,10 +4263,10 @@
         </is>
       </c>
       <c r="C14" s="7" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E14" s="9">
         <f>IFERROR(C14/(C14+D14),0)</f>

--- a/exports/Resumen_Evidencias_OPS.xlsx
+++ b/exports/Resumen_Evidencias_OPS.xlsx
@@ -27,7 +27,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -79,11 +79,17 @@
     <font>
       <name val="Aptos"/>
       <b val="1"/>
+      <color rgb="00116444"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Aptos"/>
+      <b val="1"/>
       <color rgb="0080520C"/>
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -117,6 +123,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00DAF1E6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00FFF0D5"/>
       </patternFill>
     </fill>
@@ -138,7 +149,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -187,6 +198,9 @@
     </xf>
     <xf numFmtId="49" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -578,7 +592,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Centro Norte · Corte 31/08/2026 12:28</t>
+          <t>Centro Norte · Corte 31/08/2026 12:45</t>
         </is>
       </c>
     </row>
@@ -601,10 +615,10 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="E6" s="5">
         <f>IFERROR(A6/(A6+C6),0)</f>
@@ -733,10 +747,10 @@
         <v>11</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E12" s="8" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F12" s="9">
         <f>IFERROR(D12/(D12+E12),0)</f>
@@ -766,10 +780,10 @@
         <v>13</v>
       </c>
       <c r="D13" s="11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E13" s="12" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F13" s="13">
         <f>IFERROR(D13/(D13+E13),0)</f>
@@ -910,7 +924,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Centro Norte · Corte 31/08/2026 12:28</t>
+          <t>Centro Norte · Corte 31/08/2026 12:45</t>
         </is>
       </c>
     </row>
@@ -981,10 +995,10 @@
         </is>
       </c>
       <c r="E5" s="11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G5" s="13">
         <f>IFERROR(E5/(E5+F5),0)</f>
@@ -992,12 +1006,12 @@
       </c>
       <c r="H5" s="15" t="inlineStr">
         <is>
-          <t>Seguimiento</t>
+          <t>En meta</t>
         </is>
       </c>
       <c r="I5" s="15" t="inlineStr">
         <is>
-          <t>Dar seguimiento</t>
+          <t>Mantener estándar</t>
         </is>
       </c>
     </row>
@@ -1030,12 +1044,12 @@
         <f>IFERROR(E6/(E6+F6),0)</f>
         <v/>
       </c>
-      <c r="H6" s="15" t="inlineStr">
+      <c r="H6" s="17" t="inlineStr">
         <is>
           <t>Seguimiento</t>
         </is>
       </c>
-      <c r="I6" s="15" t="inlineStr">
+      <c r="I6" s="17" t="inlineStr">
         <is>
           <t>Dar seguimiento</t>
         </is>
@@ -1070,12 +1084,12 @@
         <f>IFERROR(E7/(E7+F7),0)</f>
         <v/>
       </c>
-      <c r="H7" s="15" t="inlineStr">
+      <c r="H7" s="17" t="inlineStr">
         <is>
           <t>Seguimiento</t>
         </is>
       </c>
-      <c r="I7" s="15" t="inlineStr">
+      <c r="I7" s="17" t="inlineStr">
         <is>
           <t>Dar seguimiento</t>
         </is>
@@ -1110,12 +1124,12 @@
         <f>IFERROR(E8/(E8+F8),0)</f>
         <v/>
       </c>
-      <c r="H8" s="15" t="inlineStr">
+      <c r="H8" s="17" t="inlineStr">
         <is>
           <t>Seguimiento</t>
         </is>
       </c>
-      <c r="I8" s="15" t="inlineStr">
+      <c r="I8" s="17" t="inlineStr">
         <is>
           <t>Dar seguimiento</t>
         </is>
@@ -1150,12 +1164,12 @@
         <f>IFERROR(E9/(E9+F9),0)</f>
         <v/>
       </c>
-      <c r="H9" s="15" t="inlineStr">
+      <c r="H9" s="17" t="inlineStr">
         <is>
           <t>Seguimiento</t>
         </is>
       </c>
-      <c r="I9" s="15" t="inlineStr">
+      <c r="I9" s="17" t="inlineStr">
         <is>
           <t>Dar seguimiento</t>
         </is>
@@ -1190,12 +1204,12 @@
         <f>IFERROR(E10/(E10+F10),0)</f>
         <v/>
       </c>
-      <c r="H10" s="15" t="inlineStr">
+      <c r="H10" s="17" t="inlineStr">
         <is>
           <t>Seguimiento</t>
         </is>
       </c>
-      <c r="I10" s="15" t="inlineStr">
+      <c r="I10" s="17" t="inlineStr">
         <is>
           <t>Dar seguimiento</t>
         </is>
@@ -1230,12 +1244,12 @@
         <f>IFERROR(E11/(E11+F11),0)</f>
         <v/>
       </c>
-      <c r="H11" s="15" t="inlineStr">
+      <c r="H11" s="17" t="inlineStr">
         <is>
           <t>Seguimiento</t>
         </is>
       </c>
-      <c r="I11" s="15" t="inlineStr">
+      <c r="I11" s="17" t="inlineStr">
         <is>
           <t>Dar seguimiento</t>
         </is>
@@ -1270,12 +1284,12 @@
         <f>IFERROR(E12/(E12+F12),0)</f>
         <v/>
       </c>
-      <c r="H12" s="15" t="inlineStr">
+      <c r="H12" s="17" t="inlineStr">
         <is>
           <t>Seguimiento</t>
         </is>
       </c>
-      <c r="I12" s="15" t="inlineStr">
+      <c r="I12" s="17" t="inlineStr">
         <is>
           <t>Dar seguimiento</t>
         </is>
@@ -1310,12 +1324,12 @@
         <f>IFERROR(E13/(E13+F13),0)</f>
         <v/>
       </c>
-      <c r="H13" s="15" t="inlineStr">
+      <c r="H13" s="17" t="inlineStr">
         <is>
           <t>Seguimiento</t>
         </is>
       </c>
-      <c r="I13" s="15" t="inlineStr">
+      <c r="I13" s="17" t="inlineStr">
         <is>
           <t>Dar seguimiento</t>
         </is>
@@ -1350,12 +1364,12 @@
         <f>IFERROR(E14/(E14+F14),0)</f>
         <v/>
       </c>
-      <c r="H14" s="15" t="inlineStr">
+      <c r="H14" s="17" t="inlineStr">
         <is>
           <t>Seguimiento</t>
         </is>
       </c>
-      <c r="I14" s="15" t="inlineStr">
+      <c r="I14" s="17" t="inlineStr">
         <is>
           <t>Dar seguimiento</t>
         </is>
@@ -2207,12 +2221,12 @@
       </c>
       <c r="B36" s="16" t="inlineStr">
         <is>
-          <t>43111</t>
+          <t>38371</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>Montevideo Insurgentes</t>
+          <t>Montevideo DT</t>
         </is>
       </c>
       <c r="D36" s="8" t="inlineStr">
@@ -2247,17 +2261,17 @@
       </c>
       <c r="B37" s="14" t="inlineStr">
         <is>
-          <t>38674</t>
+          <t>43111</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>Mundo E</t>
+          <t>Montevideo Insurgentes</t>
         </is>
       </c>
       <c r="D37" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E37" s="11" t="n">
@@ -2287,12 +2301,12 @@
       </c>
       <c r="B38" s="16" t="inlineStr">
         <is>
-          <t>38845</t>
+          <t>38674</t>
         </is>
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>Mundo E II</t>
+          <t>Mundo E</t>
         </is>
       </c>
       <c r="D38" s="8" t="inlineStr">
@@ -2327,17 +2341,17 @@
       </c>
       <c r="B39" s="14" t="inlineStr">
         <is>
-          <t>43195</t>
+          <t>38845</t>
         </is>
       </c>
       <c r="C39" s="12" t="inlineStr">
         <is>
-          <t>Parque Jadin kiosko</t>
+          <t>Mundo E II</t>
         </is>
       </c>
       <c r="D39" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E39" s="11" t="n">
@@ -2367,17 +2381,17 @@
       </c>
       <c r="B40" s="16" t="inlineStr">
         <is>
-          <t>38937</t>
+          <t>43195</t>
         </is>
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>Parque Tepeyac Piso 1</t>
+          <t>Parque Jadin kiosko</t>
         </is>
       </c>
       <c r="D40" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E40" s="7" t="n">
@@ -2407,17 +2421,17 @@
       </c>
       <c r="B41" s="14" t="inlineStr">
         <is>
-          <t>38590</t>
+          <t>38937</t>
         </is>
       </c>
       <c r="C41" s="12" t="inlineStr">
         <is>
-          <t>Parque Toreo II</t>
+          <t>Parque Tepeyac Piso 1</t>
         </is>
       </c>
       <c r="D41" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E41" s="11" t="n">
@@ -2447,17 +2461,17 @@
       </c>
       <c r="B42" s="16" t="inlineStr">
         <is>
-          <t>38546</t>
+          <t>38590</t>
         </is>
       </c>
       <c r="C42" s="8" t="inlineStr">
         <is>
-          <t>Patio Claveria</t>
+          <t>Parque Toreo II</t>
         </is>
       </c>
       <c r="D42" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E42" s="7" t="n">
@@ -2487,12 +2501,12 @@
       </c>
       <c r="B43" s="14" t="inlineStr">
         <is>
-          <t>38677</t>
+          <t>38546</t>
         </is>
       </c>
       <c r="C43" s="12" t="inlineStr">
         <is>
-          <t>Patio la Raza</t>
+          <t>Patio Claveria</t>
         </is>
       </c>
       <c r="D43" s="12" t="inlineStr">
@@ -2527,17 +2541,17 @@
       </c>
       <c r="B44" s="16" t="inlineStr">
         <is>
-          <t>38176</t>
+          <t>38677</t>
         </is>
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t>Periferico Satélite DT</t>
+          <t>Patio la Raza</t>
         </is>
       </c>
       <c r="D44" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E44" s="7" t="n">
@@ -2567,17 +2581,17 @@
       </c>
       <c r="B45" s="14" t="inlineStr">
         <is>
-          <t>38924</t>
+          <t>38176</t>
         </is>
       </c>
       <c r="C45" s="12" t="inlineStr">
         <is>
-          <t>Plaza Aeropuerto</t>
+          <t>Periferico Satélite DT</t>
         </is>
       </c>
       <c r="D45" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E45" s="11" t="n">
@@ -2607,17 +2621,17 @@
       </c>
       <c r="B46" s="16" t="inlineStr">
         <is>
-          <t>38427</t>
+          <t>38924</t>
         </is>
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t>Plaza Satelite</t>
+          <t>Plaza Aeropuerto</t>
         </is>
       </c>
       <c r="D46" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E46" s="7" t="n">
@@ -2647,12 +2661,12 @@
       </c>
       <c r="B47" s="14" t="inlineStr">
         <is>
-          <t>38859</t>
+          <t>38427</t>
         </is>
       </c>
       <c r="C47" s="12" t="inlineStr">
         <is>
-          <t>Plaza Satelite II N1</t>
+          <t>Plaza Satelite</t>
         </is>
       </c>
       <c r="D47" s="12" t="inlineStr">
@@ -2687,17 +2701,17 @@
       </c>
       <c r="B48" s="16" t="inlineStr">
         <is>
-          <t>43132</t>
+          <t>38859</t>
         </is>
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
-          <t>Plaza Vista Norte</t>
+          <t>Plaza Satelite II N1</t>
         </is>
       </c>
       <c r="D48" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E48" s="7" t="n">
@@ -2727,17 +2741,17 @@
       </c>
       <c r="B49" s="14" t="inlineStr">
         <is>
-          <t>38136</t>
+          <t>43132</t>
         </is>
       </c>
       <c r="C49" s="12" t="inlineStr">
         <is>
-          <t>Punta Norte</t>
+          <t>Plaza Vista Norte</t>
         </is>
       </c>
       <c r="D49" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E49" s="11" t="n">
@@ -2767,17 +2781,17 @@
       </c>
       <c r="B50" s="16" t="inlineStr">
         <is>
-          <t>43152</t>
+          <t>38136</t>
         </is>
       </c>
       <c r="C50" s="8" t="inlineStr">
         <is>
-          <t>Samara Satélite</t>
+          <t>Punta Norte</t>
         </is>
       </c>
       <c r="D50" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E50" s="7" t="n">
@@ -2807,17 +2821,17 @@
       </c>
       <c r="B51" s="14" t="inlineStr">
         <is>
-          <t>38266</t>
+          <t>43152</t>
         </is>
       </c>
       <c r="C51" s="12" t="inlineStr">
         <is>
-          <t>San Mateo</t>
+          <t>Samara Satélite</t>
         </is>
       </c>
       <c r="D51" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E51" s="11" t="n">
@@ -2847,17 +2861,17 @@
       </c>
       <c r="B52" s="16" t="inlineStr">
         <is>
-          <t>38117</t>
+          <t>38266</t>
         </is>
       </c>
       <c r="C52" s="8" t="inlineStr">
         <is>
-          <t>Satelite</t>
+          <t>San Mateo</t>
         </is>
       </c>
       <c r="D52" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E52" s="7" t="n">
@@ -2887,12 +2901,12 @@
       </c>
       <c r="B53" s="14" t="inlineStr">
         <is>
-          <t>38475</t>
+          <t>38117</t>
         </is>
       </c>
       <c r="C53" s="12" t="inlineStr">
         <is>
-          <t>Satelite Centro Civico</t>
+          <t>Satelite</t>
         </is>
       </c>
       <c r="D53" s="12" t="inlineStr">
@@ -2927,17 +2941,17 @@
       </c>
       <c r="B54" s="16" t="inlineStr">
         <is>
-          <t>38442</t>
+          <t>38475</t>
         </is>
       </c>
       <c r="C54" s="8" t="inlineStr">
         <is>
-          <t>Sor Juana</t>
+          <t>Satelite Centro Civico</t>
         </is>
       </c>
       <c r="D54" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E54" s="7" t="n">
@@ -2967,17 +2981,17 @@
       </c>
       <c r="B55" s="14" t="inlineStr">
         <is>
-          <t>38925</t>
+          <t>38442</t>
         </is>
       </c>
       <c r="C55" s="12" t="inlineStr">
         <is>
-          <t>Star Medica Lomas Verdes</t>
+          <t>Sor Juana</t>
         </is>
       </c>
       <c r="D55" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E55" s="11" t="n">
@@ -3007,17 +3021,17 @@
       </c>
       <c r="B56" s="16" t="inlineStr">
         <is>
-          <t>38411</t>
+          <t>38925</t>
         </is>
       </c>
       <c r="C56" s="8" t="inlineStr">
         <is>
-          <t>Torres Lindavista</t>
+          <t>Star Medica Lomas Verdes</t>
         </is>
       </c>
       <c r="D56" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E56" s="7" t="n">
@@ -3047,17 +3061,17 @@
       </c>
       <c r="B57" s="14" t="inlineStr">
         <is>
-          <t>43130</t>
+          <t>38992</t>
         </is>
       </c>
       <c r="C57" s="12" t="inlineStr">
         <is>
-          <t>Town Center Nicolás Romero</t>
+          <t>Tapo Puerta Oriente</t>
         </is>
       </c>
       <c r="D57" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E57" s="11" t="n">
@@ -3087,12 +3101,12 @@
       </c>
       <c r="B58" s="16" t="inlineStr">
         <is>
-          <t>38651</t>
+          <t>38411</t>
         </is>
       </c>
       <c r="C58" s="8" t="inlineStr">
         <is>
-          <t>Via Vallejo</t>
+          <t>Torres Lindavista</t>
         </is>
       </c>
       <c r="D58" s="8" t="inlineStr">
@@ -3127,17 +3141,17 @@
       </c>
       <c r="B59" s="14" t="inlineStr">
         <is>
-          <t>38694</t>
+          <t>43130</t>
         </is>
       </c>
       <c r="C59" s="12" t="inlineStr">
         <is>
-          <t>Villas de la Hacienda</t>
+          <t>Town Center Nicolás Romero</t>
         </is>
       </c>
       <c r="D59" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E59" s="11" t="n">
@@ -3167,17 +3181,17 @@
       </c>
       <c r="B60" s="16" t="inlineStr">
         <is>
-          <t>38656</t>
+          <t>38651</t>
         </is>
       </c>
       <c r="C60" s="8" t="inlineStr">
         <is>
-          <t>Viveros de la Loma</t>
+          <t>Via Vallejo</t>
         </is>
       </c>
       <c r="D60" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E60" s="7" t="n">
@@ -3207,17 +3221,17 @@
       </c>
       <c r="B61" s="14" t="inlineStr">
         <is>
-          <t>38115</t>
+          <t>38694</t>
         </is>
       </c>
       <c r="C61" s="12" t="inlineStr">
         <is>
-          <t>Zona Azul</t>
+          <t>Villas de la Hacienda</t>
         </is>
       </c>
       <c r="D61" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E61" s="11" t="n">
@@ -3247,17 +3261,17 @@
       </c>
       <c r="B62" s="16" t="inlineStr">
         <is>
-          <t>38142</t>
+          <t>38656</t>
         </is>
       </c>
       <c r="C62" s="8" t="inlineStr">
         <is>
-          <t>Zona Esmeralda</t>
+          <t>Viveros de la Loma</t>
         </is>
       </c>
       <c r="D62" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E62" s="7" t="n">
@@ -3287,12 +3301,12 @@
       </c>
       <c r="B63" s="14" t="inlineStr">
         <is>
-          <t>43043</t>
+          <t>38115</t>
         </is>
       </c>
       <c r="C63" s="12" t="inlineStr">
         <is>
-          <t>Atizapan</t>
+          <t>Zona Azul</t>
         </is>
       </c>
       <c r="D63" s="12" t="inlineStr">
@@ -3301,10 +3315,10 @@
         </is>
       </c>
       <c r="E63" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F63" s="11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G63" s="13">
         <f>IFERROR(E63/(E63+F63),0)</f>
@@ -3327,24 +3341,24 @@
       </c>
       <c r="B64" s="16" t="inlineStr">
         <is>
-          <t>38529</t>
+          <t>38142</t>
         </is>
       </c>
       <c r="C64" s="8" t="inlineStr">
         <is>
-          <t>Bosques de Aragon</t>
+          <t>Zona Esmeralda</t>
         </is>
       </c>
       <c r="D64" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E64" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F64" s="7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G64" s="9">
         <f>IFERROR(E64/(E64+F64),0)</f>
@@ -3367,17 +3381,17 @@
       </c>
       <c r="B65" s="14" t="inlineStr">
         <is>
-          <t>38837</t>
+          <t>43043</t>
         </is>
       </c>
       <c r="C65" s="12" t="inlineStr">
         <is>
-          <t>Centenario Azcapotzalco</t>
+          <t>Atizapan</t>
         </is>
       </c>
       <c r="D65" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E65" s="11" t="n">
@@ -3407,12 +3421,12 @@
       </c>
       <c r="B66" s="16" t="inlineStr">
         <is>
-          <t>38903</t>
+          <t>38529</t>
         </is>
       </c>
       <c r="C66" s="8" t="inlineStr">
         <is>
-          <t>Encuentro Oceania</t>
+          <t>Bosques de Aragon</t>
         </is>
       </c>
       <c r="D66" s="8" t="inlineStr">
@@ -3447,17 +3461,17 @@
       </c>
       <c r="B67" s="14" t="inlineStr">
         <is>
-          <t>38995</t>
+          <t>38837</t>
         </is>
       </c>
       <c r="C67" s="12" t="inlineStr">
         <is>
-          <t>Encuentro Oceania II</t>
+          <t>Centenario Azcapotzalco</t>
         </is>
       </c>
       <c r="D67" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E67" s="11" t="n">
@@ -3487,17 +3501,17 @@
       </c>
       <c r="B68" s="16" t="inlineStr">
         <is>
-          <t>38507</t>
+          <t>38903</t>
         </is>
       </c>
       <c r="C68" s="8" t="inlineStr">
         <is>
-          <t>Espacio Vista del Valle</t>
+          <t>Encuentro Oceania</t>
         </is>
       </c>
       <c r="D68" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E68" s="7" t="n">
@@ -3527,17 +3541,17 @@
       </c>
       <c r="B69" s="14" t="inlineStr">
         <is>
-          <t>38230</t>
+          <t>38995</t>
         </is>
       </c>
       <c r="C69" s="12" t="inlineStr">
         <is>
-          <t>ITEMS Edo de Mexico</t>
+          <t>Encuentro Oceania II</t>
         </is>
       </c>
       <c r="D69" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E69" s="11" t="n">
@@ -3567,17 +3581,17 @@
       </c>
       <c r="B70" s="16" t="inlineStr">
         <is>
-          <t>38371</t>
+          <t>38507</t>
         </is>
       </c>
       <c r="C70" s="8" t="inlineStr">
         <is>
-          <t>Montevideo DT</t>
+          <t>Espacio Vista del Valle</t>
         </is>
       </c>
       <c r="D70" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E70" s="7" t="n">
@@ -3607,17 +3621,17 @@
       </c>
       <c r="B71" s="14" t="inlineStr">
         <is>
-          <t>38965</t>
+          <t>38230</t>
         </is>
       </c>
       <c r="C71" s="12" t="inlineStr">
         <is>
-          <t>Parque Tepeyac Piso 2</t>
+          <t>ITEMS Edo de Mexico</t>
         </is>
       </c>
       <c r="D71" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E71" s="11" t="n">
@@ -3647,17 +3661,17 @@
       </c>
       <c r="B72" s="16" t="inlineStr">
         <is>
-          <t>38792</t>
+          <t>38965</t>
         </is>
       </c>
       <c r="C72" s="8" t="inlineStr">
         <is>
-          <t>Pasaje Tlanepantla</t>
+          <t>Parque Tepeyac Piso 2</t>
         </is>
       </c>
       <c r="D72" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E72" s="7" t="n">
@@ -3687,17 +3701,17 @@
       </c>
       <c r="B73" s="14" t="inlineStr">
         <is>
-          <t>38811</t>
+          <t>38792</t>
         </is>
       </c>
       <c r="C73" s="12" t="inlineStr">
         <is>
-          <t>Plaza Tepeyac</t>
+          <t>Pasaje Tlanepantla</t>
         </is>
       </c>
       <c r="D73" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E73" s="11" t="n">
@@ -3727,17 +3741,17 @@
       </c>
       <c r="B74" s="16" t="inlineStr">
         <is>
-          <t>38460</t>
+          <t>38811</t>
         </is>
       </c>
       <c r="C74" s="8" t="inlineStr">
         <is>
-          <t>Santa Monica</t>
+          <t>Plaza Tepeyac</t>
         </is>
       </c>
       <c r="D74" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E74" s="7" t="n">
@@ -3767,17 +3781,17 @@
       </c>
       <c r="B75" s="14" t="inlineStr">
         <is>
-          <t>38992</t>
+          <t>38460</t>
         </is>
       </c>
       <c r="C75" s="12" t="inlineStr">
         <is>
-          <t>Tapo Puerta Oriente</t>
+          <t>Santa Monica</t>
         </is>
       </c>
       <c r="D75" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E75" s="11" t="n">
@@ -3892,7 +3906,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Centro Norte · Corte 31/08/2026 12:28</t>
+          <t>Centro Norte · Corte 31/08/2026 12:45</t>
         </is>
       </c>
     </row>
@@ -4263,10 +4277,10 @@
         </is>
       </c>
       <c r="C14" s="7" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E14" s="9">
         <f>IFERROR(C14/(C14+D14),0)</f>
@@ -4277,12 +4291,12 @@
           <t>31/08/26</t>
         </is>
       </c>
-      <c r="G14" s="15" t="inlineStr">
+      <c r="G14" s="17" t="inlineStr">
         <is>
           <t>Seguimiento</t>
         </is>
       </c>
-      <c r="H14" s="15" t="inlineStr">
+      <c r="H14" s="17" t="inlineStr">
         <is>
           <t>Dar seguimiento</t>
         </is>

--- a/exports/Resumen_Evidencias_OPS.xlsx
+++ b/exports/Resumen_Evidencias_OPS.xlsx
@@ -73,6 +73,12 @@
     <font>
       <name val="Aptos"/>
       <b val="1"/>
+      <color rgb="0080520C"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Aptos"/>
+      <b val="1"/>
       <color rgb="00922F24"/>
       <sz val="9"/>
     </font>
@@ -80,12 +86,6 @@
       <name val="Aptos"/>
       <b val="1"/>
       <color rgb="00116444"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Aptos"/>
-      <b val="1"/>
-      <color rgb="0080520C"/>
       <sz val="9"/>
     </font>
   </fonts>
@@ -118,17 +118,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00FFF0D5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00F9E6E3"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00DAF1E6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF0D5"/>
       </patternFill>
     </fill>
   </fills>
@@ -190,17 +190,17 @@
     <xf numFmtId="164" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -592,7 +592,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Centro Norte · Corte 31/08/2026 12:45</t>
+          <t>Centro Norte · Corte 31/08/2026 15:53</t>
         </is>
       </c>
     </row>
@@ -615,10 +615,10 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>105</v>
+        <v>118</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>613</v>
+        <v>600</v>
       </c>
       <c r="E6" s="5">
         <f>IFERROR(A6/(A6+C6),0)</f>
@@ -681,10 +681,10 @@
         <v>10</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="F10" s="9">
         <f>IFERROR(D10/(D10+E10),0)</f>
@@ -692,12 +692,12 @@
       </c>
       <c r="G10" s="10" t="inlineStr">
         <is>
-          <t>Atención</t>
+          <t>Seguimiento</t>
         </is>
       </c>
       <c r="H10" s="10" t="inlineStr">
         <is>
-          <t>Priorizar hoy</t>
+          <t>Dar seguimiento</t>
         </is>
       </c>
     </row>
@@ -714,21 +714,21 @@
         <v>13</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E11" s="12" t="n">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="F11" s="13">
         <f>IFERROR(D11/(D11+E11),0)</f>
         <v/>
       </c>
-      <c r="G11" s="10" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="H11" s="10" t="inlineStr">
+      <c r="G11" s="14" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="H11" s="14" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -747,21 +747,21 @@
         <v>11</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E12" s="8" t="n">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F12" s="9">
         <f>IFERROR(D12/(D12+E12),0)</f>
         <v/>
       </c>
-      <c r="G12" s="10" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="H12" s="10" t="inlineStr">
+      <c r="G12" s="14" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="H12" s="14" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -780,21 +780,21 @@
         <v>13</v>
       </c>
       <c r="D13" s="11" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E13" s="12" t="n">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="F13" s="13">
         <f>IFERROR(D13/(D13+E13),0)</f>
         <v/>
       </c>
-      <c r="G13" s="10" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="H13" s="10" t="inlineStr">
+      <c r="G13" s="14" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="H13" s="14" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -806,28 +806,28 @@
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Garcia</t>
+          <t>Nancy Carolina</t>
         </is>
       </c>
       <c r="C14" s="7" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E14" s="8" t="n">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="F14" s="9">
         <f>IFERROR(D14/(D14+E14),0)</f>
         <v/>
       </c>
-      <c r="G14" s="10" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="H14" s="10" t="inlineStr">
+      <c r="G14" s="14" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="H14" s="14" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -839,28 +839,28 @@
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina</t>
+          <t>Yazmin Garcia</t>
         </is>
       </c>
       <c r="C15" s="11" t="n">
+        <v>13</v>
+      </c>
+      <c r="D15" s="11" t="n">
         <v>12</v>
       </c>
-      <c r="D15" s="11" t="n">
-        <v>9</v>
-      </c>
       <c r="E15" s="12" t="n">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="F15" s="13">
         <f>IFERROR(D15/(D15+E15),0)</f>
         <v/>
       </c>
-      <c r="G15" s="10" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="H15" s="10" t="inlineStr">
+      <c r="G15" s="14" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="H15" s="14" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -924,7 +924,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Centro Norte · Corte 31/08/2026 12:45</t>
+          <t>Centro Norte · Corte 31/08/2026 15:53</t>
         </is>
       </c>
     </row>
@@ -979,7 +979,7 @@
       <c r="A5" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="14" t="inlineStr">
+      <c r="B5" s="15" t="inlineStr">
         <is>
           <t>38719</t>
         </is>
@@ -1004,12 +1004,12 @@
         <f>IFERROR(E5/(E5+F5),0)</f>
         <v/>
       </c>
-      <c r="H5" s="15" t="inlineStr">
+      <c r="H5" s="16" t="inlineStr">
         <is>
           <t>En meta</t>
         </is>
       </c>
-      <c r="I5" s="15" t="inlineStr">
+      <c r="I5" s="16" t="inlineStr">
         <is>
           <t>Mantener estándar</t>
         </is>
@@ -1019,37 +1019,37 @@
       <c r="A6" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>38695</t>
+      <c r="B6" s="17" t="inlineStr">
+        <is>
+          <t>38515</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>Cetram 4 Caminos</t>
+          <t>Patio Ecatepec</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E6" s="7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G6" s="9">
         <f>IFERROR(E6/(E6+F6),0)</f>
         <v/>
       </c>
-      <c r="H6" s="17" t="inlineStr">
+      <c r="H6" s="10" t="inlineStr">
         <is>
           <t>Seguimiento</t>
         </is>
       </c>
-      <c r="I6" s="17" t="inlineStr">
+      <c r="I6" s="10" t="inlineStr">
         <is>
           <t>Dar seguimiento</t>
         </is>
@@ -1059,14 +1059,14 @@
       <c r="A7" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="14" t="inlineStr">
-        <is>
-          <t>38401</t>
+      <c r="B7" s="15" t="inlineStr">
+        <is>
+          <t>38862</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>Coacalco</t>
+          <t>San Miguel Izcalli</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
@@ -1075,21 +1075,21 @@
         </is>
       </c>
       <c r="E7" s="11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G7" s="13">
         <f>IFERROR(E7/(E7+F7),0)</f>
         <v/>
       </c>
-      <c r="H7" s="17" t="inlineStr">
+      <c r="H7" s="10" t="inlineStr">
         <is>
           <t>Seguimiento</t>
         </is>
       </c>
-      <c r="I7" s="17" t="inlineStr">
+      <c r="I7" s="10" t="inlineStr">
         <is>
           <t>Dar seguimiento</t>
         </is>
@@ -1099,19 +1099,19 @@
       <c r="A8" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="16" t="inlineStr">
-        <is>
-          <t>38333</t>
+      <c r="B8" s="17" t="inlineStr">
+        <is>
+          <t>38695</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>Izcalli Mega</t>
+          <t>Cetram 4 Caminos</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E8" s="7" t="n">
@@ -1124,12 +1124,12 @@
         <f>IFERROR(E8/(E8+F8),0)</f>
         <v/>
       </c>
-      <c r="H8" s="17" t="inlineStr">
+      <c r="H8" s="10" t="inlineStr">
         <is>
           <t>Seguimiento</t>
         </is>
       </c>
-      <c r="I8" s="17" t="inlineStr">
+      <c r="I8" s="10" t="inlineStr">
         <is>
           <t>Dar seguimiento</t>
         </is>
@@ -1139,14 +1139,14 @@
       <c r="A9" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="14" t="inlineStr">
-        <is>
-          <t>38368</t>
+      <c r="B9" s="15" t="inlineStr">
+        <is>
+          <t>38401</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>Luna Park</t>
+          <t>Coacalco</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
@@ -1164,12 +1164,12 @@
         <f>IFERROR(E9/(E9+F9),0)</f>
         <v/>
       </c>
-      <c r="H9" s="17" t="inlineStr">
+      <c r="H9" s="10" t="inlineStr">
         <is>
           <t>Seguimiento</t>
         </is>
       </c>
-      <c r="I9" s="17" t="inlineStr">
+      <c r="I9" s="10" t="inlineStr">
         <is>
           <t>Dar seguimiento</t>
         </is>
@@ -1179,19 +1179,19 @@
       <c r="A10" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="16" t="inlineStr">
-        <is>
-          <t>38561</t>
+      <c r="B10" s="17" t="inlineStr">
+        <is>
+          <t>38333</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>Parque Toreo</t>
+          <t>Izcalli Mega</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E10" s="7" t="n">
@@ -1204,12 +1204,12 @@
         <f>IFERROR(E10/(E10+F10),0)</f>
         <v/>
       </c>
-      <c r="H10" s="17" t="inlineStr">
+      <c r="H10" s="10" t="inlineStr">
         <is>
           <t>Seguimiento</t>
         </is>
       </c>
-      <c r="I10" s="17" t="inlineStr">
+      <c r="I10" s="10" t="inlineStr">
         <is>
           <t>Dar seguimiento</t>
         </is>
@@ -1219,14 +1219,14 @@
       <c r="A11" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="14" t="inlineStr">
-        <is>
-          <t>38862</t>
+      <c r="B11" s="15" t="inlineStr">
+        <is>
+          <t>38368</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>San Miguel Izcalli</t>
+          <t>Luna Park</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
@@ -1244,12 +1244,12 @@
         <f>IFERROR(E11/(E11+F11),0)</f>
         <v/>
       </c>
-      <c r="H11" s="17" t="inlineStr">
+      <c r="H11" s="10" t="inlineStr">
         <is>
           <t>Seguimiento</t>
         </is>
       </c>
-      <c r="I11" s="17" t="inlineStr">
+      <c r="I11" s="10" t="inlineStr">
         <is>
           <t>Dar seguimiento</t>
         </is>
@@ -1259,37 +1259,37 @@
       <c r="A12" s="7" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="16" t="inlineStr">
-        <is>
-          <t>38894</t>
+      <c r="B12" s="17" t="inlineStr">
+        <is>
+          <t>38561</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Galerias Perinorte</t>
+          <t>Parque Toreo</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E12" s="7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F12" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G12" s="9">
         <f>IFERROR(E12/(E12+F12),0)</f>
         <v/>
       </c>
-      <c r="H12" s="17" t="inlineStr">
+      <c r="H12" s="10" t="inlineStr">
         <is>
           <t>Seguimiento</t>
         </is>
       </c>
-      <c r="I12" s="17" t="inlineStr">
+      <c r="I12" s="10" t="inlineStr">
         <is>
           <t>Dar seguimiento</t>
         </is>
@@ -1299,14 +1299,14 @@
       <c r="A13" s="11" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="14" t="inlineStr">
-        <is>
-          <t>38515</t>
+      <c r="B13" s="15" t="inlineStr">
+        <is>
+          <t>38894</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>Patio Ecatepec</t>
+          <t>Galerias Perinorte</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
@@ -1324,12 +1324,12 @@
         <f>IFERROR(E13/(E13+F13),0)</f>
         <v/>
       </c>
-      <c r="H13" s="17" t="inlineStr">
+      <c r="H13" s="10" t="inlineStr">
         <is>
           <t>Seguimiento</t>
         </is>
       </c>
-      <c r="I13" s="17" t="inlineStr">
+      <c r="I13" s="10" t="inlineStr">
         <is>
           <t>Dar seguimiento</t>
         </is>
@@ -1339,7 +1339,7 @@
       <c r="A14" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="16" t="inlineStr">
+      <c r="B14" s="17" t="inlineStr">
         <is>
           <t>38339</t>
         </is>
@@ -1364,12 +1364,12 @@
         <f>IFERROR(E14/(E14+F14),0)</f>
         <v/>
       </c>
-      <c r="H14" s="17" t="inlineStr">
+      <c r="H14" s="10" t="inlineStr">
         <is>
           <t>Seguimiento</t>
         </is>
       </c>
-      <c r="I14" s="17" t="inlineStr">
+      <c r="I14" s="10" t="inlineStr">
         <is>
           <t>Dar seguimiento</t>
         </is>
@@ -1379,7 +1379,7 @@
       <c r="A15" s="11" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="14" t="inlineStr">
+      <c r="B15" s="15" t="inlineStr">
         <is>
           <t>38604</t>
         </is>
@@ -1404,12 +1404,12 @@
         <f>IFERROR(E15/(E15+F15),0)</f>
         <v/>
       </c>
-      <c r="H15" s="10" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I15" s="10" t="inlineStr">
+      <c r="H15" s="14" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="I15" s="14" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -1419,7 +1419,7 @@
       <c r="A16" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="16" t="inlineStr">
+      <c r="B16" s="17" t="inlineStr">
         <is>
           <t>43193</t>
         </is>
@@ -1444,12 +1444,12 @@
         <f>IFERROR(E16/(E16+F16),0)</f>
         <v/>
       </c>
-      <c r="H16" s="10" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I16" s="10" t="inlineStr">
+      <c r="H16" s="14" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="I16" s="14" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -1459,7 +1459,7 @@
       <c r="A17" s="11" t="n">
         <v>13</v>
       </c>
-      <c r="B17" s="14" t="inlineStr">
+      <c r="B17" s="15" t="inlineStr">
         <is>
           <t>38456</t>
         </is>
@@ -1484,12 +1484,12 @@
         <f>IFERROR(E17/(E17+F17),0)</f>
         <v/>
       </c>
-      <c r="H17" s="10" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I17" s="10" t="inlineStr">
+      <c r="H17" s="14" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="I17" s="14" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -1499,19 +1499,19 @@
       <c r="A18" s="7" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="16" t="inlineStr">
-        <is>
-          <t>38606</t>
+      <c r="B18" s="17" t="inlineStr">
+        <is>
+          <t>43194</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>TlalnepantlaCarso</t>
+          <t>Atana Lindavista</t>
         </is>
       </c>
       <c r="D18" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E18" s="7" t="n">
@@ -1524,12 +1524,12 @@
         <f>IFERROR(E18/(E18+F18),0)</f>
         <v/>
       </c>
-      <c r="H18" s="10" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I18" s="10" t="inlineStr">
+      <c r="H18" s="14" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="I18" s="14" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -1539,37 +1539,37 @@
       <c r="A19" s="11" t="n">
         <v>15</v>
       </c>
-      <c r="B19" s="14" t="inlineStr">
-        <is>
-          <t>38186</t>
+      <c r="B19" s="15" t="inlineStr">
+        <is>
+          <t>38859</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>Arboledas</t>
+          <t>Plaza Satelite II N1</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E19" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G19" s="13">
         <f>IFERROR(E19/(E19+F19),0)</f>
         <v/>
       </c>
-      <c r="H19" s="10" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I19" s="10" t="inlineStr">
+      <c r="H19" s="14" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="I19" s="14" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -1579,37 +1579,37 @@
       <c r="A20" s="7" t="n">
         <v>16</v>
       </c>
-      <c r="B20" s="16" t="inlineStr">
-        <is>
-          <t>43194</t>
+      <c r="B20" s="17" t="inlineStr">
+        <is>
+          <t>38475</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>Atana Lindavista</t>
+          <t>Satelite Centro Civico</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E20" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F20" s="7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G20" s="9">
         <f>IFERROR(E20/(E20+F20),0)</f>
         <v/>
       </c>
-      <c r="H20" s="10" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I20" s="10" t="inlineStr">
+      <c r="H20" s="14" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="I20" s="14" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -1619,37 +1619,37 @@
       <c r="A21" s="11" t="n">
         <v>17</v>
       </c>
-      <c r="B21" s="14" t="inlineStr">
-        <is>
-          <t>38149</t>
+      <c r="B21" s="15" t="inlineStr">
+        <is>
+          <t>38606</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>Bellavista</t>
+          <t>TlalnepantlaCarso</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E21" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G21" s="13">
         <f>IFERROR(E21/(E21+F21),0)</f>
         <v/>
       </c>
-      <c r="H21" s="10" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I21" s="10" t="inlineStr">
+      <c r="H21" s="14" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="I21" s="14" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -1659,37 +1659,37 @@
       <c r="A22" s="7" t="n">
         <v>18</v>
       </c>
-      <c r="B22" s="16" t="inlineStr">
-        <is>
-          <t>38930</t>
+      <c r="B22" s="17" t="inlineStr">
+        <is>
+          <t>38374</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>Blvd. Aeropuerto dt</t>
+          <t>Valle Dorado</t>
         </is>
       </c>
       <c r="D22" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E22" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G22" s="9">
         <f>IFERROR(E22/(E22+F22),0)</f>
         <v/>
       </c>
-      <c r="H22" s="10" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I22" s="10" t="inlineStr">
+      <c r="H22" s="14" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="I22" s="14" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -1699,19 +1699,19 @@
       <c r="A23" s="11" t="n">
         <v>19</v>
       </c>
-      <c r="B23" s="14" t="inlineStr">
-        <is>
-          <t>38527</t>
+      <c r="B23" s="15" t="inlineStr">
+        <is>
+          <t>38186</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>Camarones</t>
+          <t>Arboledas</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E23" s="11" t="n">
@@ -1724,12 +1724,12 @@
         <f>IFERROR(E23/(E23+F23),0)</f>
         <v/>
       </c>
-      <c r="H23" s="10" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I23" s="10" t="inlineStr">
+      <c r="H23" s="14" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="I23" s="14" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -1739,14 +1739,14 @@
       <c r="A24" s="7" t="n">
         <v>20</v>
       </c>
-      <c r="B24" s="16" t="inlineStr">
-        <is>
-          <t>38394</t>
+      <c r="B24" s="17" t="inlineStr">
+        <is>
+          <t>43043</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>Centro Comercial Lomas Verdes</t>
+          <t>Atizapan</t>
         </is>
       </c>
       <c r="D24" s="8" t="inlineStr">
@@ -1764,12 +1764,12 @@
         <f>IFERROR(E24/(E24+F24),0)</f>
         <v/>
       </c>
-      <c r="H24" s="10" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I24" s="10" t="inlineStr">
+      <c r="H24" s="14" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="I24" s="14" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -1779,14 +1779,14 @@
       <c r="A25" s="11" t="n">
         <v>21</v>
       </c>
-      <c r="B25" s="14" t="inlineStr">
-        <is>
-          <t>38535</t>
+      <c r="B25" s="15" t="inlineStr">
+        <is>
+          <t>38149</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>City Center Esmeralda</t>
+          <t>Bellavista</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
@@ -1804,12 +1804,12 @@
         <f>IFERROR(E25/(E25+F25),0)</f>
         <v/>
       </c>
-      <c r="H25" s="10" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I25" s="10" t="inlineStr">
+      <c r="H25" s="14" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="I25" s="14" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -1819,19 +1819,19 @@
       <c r="A26" s="7" t="n">
         <v>22</v>
       </c>
-      <c r="B26" s="16" t="inlineStr">
-        <is>
-          <t>38197</t>
+      <c r="B26" s="17" t="inlineStr">
+        <is>
+          <t>38930</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>Echegaray</t>
+          <t>Blvd. Aeropuerto dt</t>
         </is>
       </c>
       <c r="D26" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E26" s="7" t="n">
@@ -1844,12 +1844,12 @@
         <f>IFERROR(E26/(E26+F26),0)</f>
         <v/>
       </c>
-      <c r="H26" s="10" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I26" s="10" t="inlineStr">
+      <c r="H26" s="14" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="I26" s="14" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -1859,19 +1859,19 @@
       <c r="A27" s="11" t="n">
         <v>23</v>
       </c>
-      <c r="B27" s="14" t="inlineStr">
-        <is>
-          <t>38431</t>
+      <c r="B27" s="15" t="inlineStr">
+        <is>
+          <t>38527</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>Eduardo Molina</t>
+          <t>Camarones</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E27" s="11" t="n">
@@ -1884,12 +1884,12 @@
         <f>IFERROR(E27/(E27+F27),0)</f>
         <v/>
       </c>
-      <c r="H27" s="10" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I27" s="10" t="inlineStr">
+      <c r="H27" s="14" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="I27" s="14" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -1899,19 +1899,19 @@
       <c r="A28" s="7" t="n">
         <v>24</v>
       </c>
-      <c r="B28" s="16" t="inlineStr">
-        <is>
-          <t>38458</t>
+      <c r="B28" s="17" t="inlineStr">
+        <is>
+          <t>38837</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>El Rosario</t>
+          <t>Centenario Azcapotzalco</t>
         </is>
       </c>
       <c r="D28" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E28" s="7" t="n">
@@ -1924,12 +1924,12 @@
         <f>IFERROR(E28/(E28+F28),0)</f>
         <v/>
       </c>
-      <c r="H28" s="10" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I28" s="10" t="inlineStr">
+      <c r="H28" s="14" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="I28" s="14" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -1939,14 +1939,14 @@
       <c r="A29" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="B29" s="14" t="inlineStr">
-        <is>
-          <t>38363</t>
+      <c r="B29" s="15" t="inlineStr">
+        <is>
+          <t>38394</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>Galerias Atizapan</t>
+          <t>Centro Comercial Lomas Verdes</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr">
@@ -1964,12 +1964,12 @@
         <f>IFERROR(E29/(E29+F29),0)</f>
         <v/>
       </c>
-      <c r="H29" s="10" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I29" s="10" t="inlineStr">
+      <c r="H29" s="14" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="I29" s="14" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -1979,19 +1979,19 @@
       <c r="A30" s="7" t="n">
         <v>26</v>
       </c>
-      <c r="B30" s="16" t="inlineStr">
-        <is>
-          <t>38770</t>
+      <c r="B30" s="17" t="inlineStr">
+        <is>
+          <t>38535</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>Gustavo Baz 29</t>
+          <t>City Center Esmeralda</t>
         </is>
       </c>
       <c r="D30" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E30" s="7" t="n">
@@ -2004,12 +2004,12 @@
         <f>IFERROR(E30/(E30+F30),0)</f>
         <v/>
       </c>
-      <c r="H30" s="10" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I30" s="10" t="inlineStr">
+      <c r="H30" s="14" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="I30" s="14" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -2019,19 +2019,19 @@
       <c r="A31" s="11" t="n">
         <v>27</v>
       </c>
-      <c r="B31" s="14" t="inlineStr">
-        <is>
-          <t>38661</t>
+      <c r="B31" s="15" t="inlineStr">
+        <is>
+          <t>38197</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>Jinetes</t>
+          <t>Echegaray</t>
         </is>
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E31" s="11" t="n">
@@ -2044,12 +2044,12 @@
         <f>IFERROR(E31/(E31+F31),0)</f>
         <v/>
       </c>
-      <c r="H31" s="10" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I31" s="10" t="inlineStr">
+      <c r="H31" s="14" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="I31" s="14" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -2059,19 +2059,19 @@
       <c r="A32" s="7" t="n">
         <v>28</v>
       </c>
-      <c r="B32" s="16" t="inlineStr">
-        <is>
-          <t>38205</t>
+      <c r="B32" s="17" t="inlineStr">
+        <is>
+          <t>38431</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>Lindavista</t>
+          <t>Eduardo Molina</t>
         </is>
       </c>
       <c r="D32" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E32" s="7" t="n">
@@ -2084,12 +2084,12 @@
         <f>IFERROR(E32/(E32+F32),0)</f>
         <v/>
       </c>
-      <c r="H32" s="10" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I32" s="10" t="inlineStr">
+      <c r="H32" s="14" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="I32" s="14" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -2099,19 +2099,19 @@
       <c r="A33" s="11" t="n">
         <v>29</v>
       </c>
-      <c r="B33" s="14" t="inlineStr">
-        <is>
-          <t>38207</t>
+      <c r="B33" s="15" t="inlineStr">
+        <is>
+          <t>38458</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>Lindavista II</t>
+          <t>El Rosario</t>
         </is>
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E33" s="11" t="n">
@@ -2124,12 +2124,12 @@
         <f>IFERROR(E33/(E33+F33),0)</f>
         <v/>
       </c>
-      <c r="H33" s="10" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I33" s="10" t="inlineStr">
+      <c r="H33" s="14" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="I33" s="14" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -2139,14 +2139,14 @@
       <c r="A34" s="7" t="n">
         <v>30</v>
       </c>
-      <c r="B34" s="16" t="inlineStr">
-        <is>
-          <t>38119</t>
+      <c r="B34" s="17" t="inlineStr">
+        <is>
+          <t>38363</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>Lomas Verdes</t>
+          <t>Galerias Atizapan</t>
         </is>
       </c>
       <c r="D34" s="8" t="inlineStr">
@@ -2164,12 +2164,12 @@
         <f>IFERROR(E34/(E34+F34),0)</f>
         <v/>
       </c>
-      <c r="H34" s="10" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I34" s="10" t="inlineStr">
+      <c r="H34" s="14" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="I34" s="14" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -2179,19 +2179,19 @@
       <c r="A35" s="11" t="n">
         <v>31</v>
       </c>
-      <c r="B35" s="14" t="inlineStr">
-        <is>
-          <t>38270</t>
+      <c r="B35" s="15" t="inlineStr">
+        <is>
+          <t>38770</t>
         </is>
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>Lomas Verdes II</t>
+          <t>Gustavo Baz 29</t>
         </is>
       </c>
       <c r="D35" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E35" s="11" t="n">
@@ -2204,12 +2204,12 @@
         <f>IFERROR(E35/(E35+F35),0)</f>
         <v/>
       </c>
-      <c r="H35" s="10" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I35" s="10" t="inlineStr">
+      <c r="H35" s="14" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="I35" s="14" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -2219,19 +2219,19 @@
       <c r="A36" s="7" t="n">
         <v>32</v>
       </c>
-      <c r="B36" s="16" t="inlineStr">
-        <is>
-          <t>38371</t>
+      <c r="B36" s="17" t="inlineStr">
+        <is>
+          <t>38661</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>Montevideo DT</t>
+          <t>Jinetes</t>
         </is>
       </c>
       <c r="D36" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E36" s="7" t="n">
@@ -2244,12 +2244,12 @@
         <f>IFERROR(E36/(E36+F36),0)</f>
         <v/>
       </c>
-      <c r="H36" s="10" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I36" s="10" t="inlineStr">
+      <c r="H36" s="14" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="I36" s="14" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -2259,14 +2259,14 @@
       <c r="A37" s="11" t="n">
         <v>33</v>
       </c>
-      <c r="B37" s="14" t="inlineStr">
-        <is>
-          <t>43111</t>
+      <c r="B37" s="15" t="inlineStr">
+        <is>
+          <t>38205</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>Montevideo Insurgentes</t>
+          <t>Lindavista</t>
         </is>
       </c>
       <c r="D37" s="12" t="inlineStr">
@@ -2284,12 +2284,12 @@
         <f>IFERROR(E37/(E37+F37),0)</f>
         <v/>
       </c>
-      <c r="H37" s="10" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I37" s="10" t="inlineStr">
+      <c r="H37" s="14" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="I37" s="14" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -2299,19 +2299,19 @@
       <c r="A38" s="7" t="n">
         <v>34</v>
       </c>
-      <c r="B38" s="16" t="inlineStr">
-        <is>
-          <t>38674</t>
+      <c r="B38" s="17" t="inlineStr">
+        <is>
+          <t>38207</t>
         </is>
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>Mundo E</t>
+          <t>Lindavista II</t>
         </is>
       </c>
       <c r="D38" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E38" s="7" t="n">
@@ -2324,12 +2324,12 @@
         <f>IFERROR(E38/(E38+F38),0)</f>
         <v/>
       </c>
-      <c r="H38" s="10" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I38" s="10" t="inlineStr">
+      <c r="H38" s="14" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="I38" s="14" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -2339,19 +2339,19 @@
       <c r="A39" s="11" t="n">
         <v>35</v>
       </c>
-      <c r="B39" s="14" t="inlineStr">
-        <is>
-          <t>38845</t>
+      <c r="B39" s="15" t="inlineStr">
+        <is>
+          <t>38119</t>
         </is>
       </c>
       <c r="C39" s="12" t="inlineStr">
         <is>
-          <t>Mundo E II</t>
+          <t>Lomas Verdes</t>
         </is>
       </c>
       <c r="D39" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E39" s="11" t="n">
@@ -2364,12 +2364,12 @@
         <f>IFERROR(E39/(E39+F39),0)</f>
         <v/>
       </c>
-      <c r="H39" s="10" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I39" s="10" t="inlineStr">
+      <c r="H39" s="14" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="I39" s="14" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -2379,19 +2379,19 @@
       <c r="A40" s="7" t="n">
         <v>36</v>
       </c>
-      <c r="B40" s="16" t="inlineStr">
-        <is>
-          <t>43195</t>
+      <c r="B40" s="17" t="inlineStr">
+        <is>
+          <t>38270</t>
         </is>
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>Parque Jadin kiosko</t>
+          <t>Lomas Verdes II</t>
         </is>
       </c>
       <c r="D40" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E40" s="7" t="n">
@@ -2404,12 +2404,12 @@
         <f>IFERROR(E40/(E40+F40),0)</f>
         <v/>
       </c>
-      <c r="H40" s="10" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I40" s="10" t="inlineStr">
+      <c r="H40" s="14" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="I40" s="14" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -2419,19 +2419,19 @@
       <c r="A41" s="11" t="n">
         <v>37</v>
       </c>
-      <c r="B41" s="14" t="inlineStr">
-        <is>
-          <t>38937</t>
+      <c r="B41" s="15" t="inlineStr">
+        <is>
+          <t>38371</t>
         </is>
       </c>
       <c r="C41" s="12" t="inlineStr">
         <is>
-          <t>Parque Tepeyac Piso 1</t>
+          <t>Montevideo DT</t>
         </is>
       </c>
       <c r="D41" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E41" s="11" t="n">
@@ -2444,12 +2444,12 @@
         <f>IFERROR(E41/(E41+F41),0)</f>
         <v/>
       </c>
-      <c r="H41" s="10" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I41" s="10" t="inlineStr">
+      <c r="H41" s="14" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="I41" s="14" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -2459,19 +2459,19 @@
       <c r="A42" s="7" t="n">
         <v>38</v>
       </c>
-      <c r="B42" s="16" t="inlineStr">
-        <is>
-          <t>38590</t>
+      <c r="B42" s="17" t="inlineStr">
+        <is>
+          <t>43111</t>
         </is>
       </c>
       <c r="C42" s="8" t="inlineStr">
         <is>
-          <t>Parque Toreo II</t>
+          <t>Montevideo Insurgentes</t>
         </is>
       </c>
       <c r="D42" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E42" s="7" t="n">
@@ -2484,12 +2484,12 @@
         <f>IFERROR(E42/(E42+F42),0)</f>
         <v/>
       </c>
-      <c r="H42" s="10" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I42" s="10" t="inlineStr">
+      <c r="H42" s="14" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="I42" s="14" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -2499,19 +2499,19 @@
       <c r="A43" s="11" t="n">
         <v>39</v>
       </c>
-      <c r="B43" s="14" t="inlineStr">
-        <is>
-          <t>38546</t>
+      <c r="B43" s="15" t="inlineStr">
+        <is>
+          <t>38674</t>
         </is>
       </c>
       <c r="C43" s="12" t="inlineStr">
         <is>
-          <t>Patio Claveria</t>
+          <t>Mundo E</t>
         </is>
       </c>
       <c r="D43" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E43" s="11" t="n">
@@ -2524,12 +2524,12 @@
         <f>IFERROR(E43/(E43+F43),0)</f>
         <v/>
       </c>
-      <c r="H43" s="10" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I43" s="10" t="inlineStr">
+      <c r="H43" s="14" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="I43" s="14" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -2539,19 +2539,19 @@
       <c r="A44" s="7" t="n">
         <v>40</v>
       </c>
-      <c r="B44" s="16" t="inlineStr">
-        <is>
-          <t>38677</t>
+      <c r="B44" s="17" t="inlineStr">
+        <is>
+          <t>38845</t>
         </is>
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t>Patio la Raza</t>
+          <t>Mundo E II</t>
         </is>
       </c>
       <c r="D44" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E44" s="7" t="n">
@@ -2564,12 +2564,12 @@
         <f>IFERROR(E44/(E44+F44),0)</f>
         <v/>
       </c>
-      <c r="H44" s="10" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I44" s="10" t="inlineStr">
+      <c r="H44" s="14" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="I44" s="14" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -2579,19 +2579,19 @@
       <c r="A45" s="11" t="n">
         <v>41</v>
       </c>
-      <c r="B45" s="14" t="inlineStr">
-        <is>
-          <t>38176</t>
+      <c r="B45" s="15" t="inlineStr">
+        <is>
+          <t>43195</t>
         </is>
       </c>
       <c r="C45" s="12" t="inlineStr">
         <is>
-          <t>Periferico Satélite DT</t>
+          <t>Parque Jadin kiosko</t>
         </is>
       </c>
       <c r="D45" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E45" s="11" t="n">
@@ -2604,12 +2604,12 @@
         <f>IFERROR(E45/(E45+F45),0)</f>
         <v/>
       </c>
-      <c r="H45" s="10" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I45" s="10" t="inlineStr">
+      <c r="H45" s="14" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="I45" s="14" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -2619,14 +2619,14 @@
       <c r="A46" s="7" t="n">
         <v>42</v>
       </c>
-      <c r="B46" s="16" t="inlineStr">
-        <is>
-          <t>38924</t>
+      <c r="B46" s="17" t="inlineStr">
+        <is>
+          <t>38937</t>
         </is>
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t>Plaza Aeropuerto</t>
+          <t>Parque Tepeyac Piso 1</t>
         </is>
       </c>
       <c r="D46" s="8" t="inlineStr">
@@ -2644,12 +2644,12 @@
         <f>IFERROR(E46/(E46+F46),0)</f>
         <v/>
       </c>
-      <c r="H46" s="10" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I46" s="10" t="inlineStr">
+      <c r="H46" s="14" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="I46" s="14" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -2659,19 +2659,19 @@
       <c r="A47" s="11" t="n">
         <v>43</v>
       </c>
-      <c r="B47" s="14" t="inlineStr">
-        <is>
-          <t>38427</t>
+      <c r="B47" s="15" t="inlineStr">
+        <is>
+          <t>38965</t>
         </is>
       </c>
       <c r="C47" s="12" t="inlineStr">
         <is>
-          <t>Plaza Satelite</t>
+          <t>Parque Tepeyac Piso 2</t>
         </is>
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E47" s="11" t="n">
@@ -2684,12 +2684,12 @@
         <f>IFERROR(E47/(E47+F47),0)</f>
         <v/>
       </c>
-      <c r="H47" s="10" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I47" s="10" t="inlineStr">
+      <c r="H47" s="14" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="I47" s="14" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -2699,14 +2699,14 @@
       <c r="A48" s="7" t="n">
         <v>44</v>
       </c>
-      <c r="B48" s="16" t="inlineStr">
-        <is>
-          <t>38859</t>
+      <c r="B48" s="17" t="inlineStr">
+        <is>
+          <t>38590</t>
         </is>
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
-          <t>Plaza Satelite II N1</t>
+          <t>Parque Toreo II</t>
         </is>
       </c>
       <c r="D48" s="8" t="inlineStr">
@@ -2724,12 +2724,12 @@
         <f>IFERROR(E48/(E48+F48),0)</f>
         <v/>
       </c>
-      <c r="H48" s="10" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I48" s="10" t="inlineStr">
+      <c r="H48" s="14" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="I48" s="14" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -2739,14 +2739,14 @@
       <c r="A49" s="11" t="n">
         <v>45</v>
       </c>
-      <c r="B49" s="14" t="inlineStr">
-        <is>
-          <t>43132</t>
+      <c r="B49" s="15" t="inlineStr">
+        <is>
+          <t>38546</t>
         </is>
       </c>
       <c r="C49" s="12" t="inlineStr">
         <is>
-          <t>Plaza Vista Norte</t>
+          <t>Patio Claveria</t>
         </is>
       </c>
       <c r="D49" s="12" t="inlineStr">
@@ -2764,12 +2764,12 @@
         <f>IFERROR(E49/(E49+F49),0)</f>
         <v/>
       </c>
-      <c r="H49" s="10" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I49" s="10" t="inlineStr">
+      <c r="H49" s="14" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="I49" s="14" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -2779,19 +2779,19 @@
       <c r="A50" s="7" t="n">
         <v>46</v>
       </c>
-      <c r="B50" s="16" t="inlineStr">
-        <is>
-          <t>38136</t>
+      <c r="B50" s="17" t="inlineStr">
+        <is>
+          <t>38677</t>
         </is>
       </c>
       <c r="C50" s="8" t="inlineStr">
         <is>
-          <t>Punta Norte</t>
+          <t>Patio la Raza</t>
         </is>
       </c>
       <c r="D50" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E50" s="7" t="n">
@@ -2804,12 +2804,12 @@
         <f>IFERROR(E50/(E50+F50),0)</f>
         <v/>
       </c>
-      <c r="H50" s="10" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I50" s="10" t="inlineStr">
+      <c r="H50" s="14" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="I50" s="14" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -2819,14 +2819,14 @@
       <c r="A51" s="11" t="n">
         <v>47</v>
       </c>
-      <c r="B51" s="14" t="inlineStr">
-        <is>
-          <t>43152</t>
+      <c r="B51" s="15" t="inlineStr">
+        <is>
+          <t>38176</t>
         </is>
       </c>
       <c r="C51" s="12" t="inlineStr">
         <is>
-          <t>Samara Satélite</t>
+          <t>Periferico Satélite DT</t>
         </is>
       </c>
       <c r="D51" s="12" t="inlineStr">
@@ -2844,12 +2844,12 @@
         <f>IFERROR(E51/(E51+F51),0)</f>
         <v/>
       </c>
-      <c r="H51" s="10" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I51" s="10" t="inlineStr">
+      <c r="H51" s="14" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="I51" s="14" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -2859,19 +2859,19 @@
       <c r="A52" s="7" t="n">
         <v>48</v>
       </c>
-      <c r="B52" s="16" t="inlineStr">
-        <is>
-          <t>38266</t>
+      <c r="B52" s="17" t="inlineStr">
+        <is>
+          <t>38924</t>
         </is>
       </c>
       <c r="C52" s="8" t="inlineStr">
         <is>
-          <t>San Mateo</t>
+          <t>Plaza Aeropuerto</t>
         </is>
       </c>
       <c r="D52" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E52" s="7" t="n">
@@ -2884,12 +2884,12 @@
         <f>IFERROR(E52/(E52+F52),0)</f>
         <v/>
       </c>
-      <c r="H52" s="10" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I52" s="10" t="inlineStr">
+      <c r="H52" s="14" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="I52" s="14" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -2899,14 +2899,14 @@
       <c r="A53" s="11" t="n">
         <v>49</v>
       </c>
-      <c r="B53" s="14" t="inlineStr">
-        <is>
-          <t>38117</t>
+      <c r="B53" s="15" t="inlineStr">
+        <is>
+          <t>38427</t>
         </is>
       </c>
       <c r="C53" s="12" t="inlineStr">
         <is>
-          <t>Satelite</t>
+          <t>Plaza Satelite</t>
         </is>
       </c>
       <c r="D53" s="12" t="inlineStr">
@@ -2924,12 +2924,12 @@
         <f>IFERROR(E53/(E53+F53),0)</f>
         <v/>
       </c>
-      <c r="H53" s="10" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I53" s="10" t="inlineStr">
+      <c r="H53" s="14" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="I53" s="14" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -2939,19 +2939,19 @@
       <c r="A54" s="7" t="n">
         <v>50</v>
       </c>
-      <c r="B54" s="16" t="inlineStr">
-        <is>
-          <t>38475</t>
+      <c r="B54" s="17" t="inlineStr">
+        <is>
+          <t>38811</t>
         </is>
       </c>
       <c r="C54" s="8" t="inlineStr">
         <is>
-          <t>Satelite Centro Civico</t>
+          <t>Plaza Tepeyac</t>
         </is>
       </c>
       <c r="D54" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E54" s="7" t="n">
@@ -2964,12 +2964,12 @@
         <f>IFERROR(E54/(E54+F54),0)</f>
         <v/>
       </c>
-      <c r="H54" s="10" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I54" s="10" t="inlineStr">
+      <c r="H54" s="14" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="I54" s="14" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -2979,19 +2979,19 @@
       <c r="A55" s="11" t="n">
         <v>51</v>
       </c>
-      <c r="B55" s="14" t="inlineStr">
-        <is>
-          <t>38442</t>
+      <c r="B55" s="15" t="inlineStr">
+        <is>
+          <t>43132</t>
         </is>
       </c>
       <c r="C55" s="12" t="inlineStr">
         <is>
-          <t>Sor Juana</t>
+          <t>Plaza Vista Norte</t>
         </is>
       </c>
       <c r="D55" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E55" s="11" t="n">
@@ -3004,12 +3004,12 @@
         <f>IFERROR(E55/(E55+F55),0)</f>
         <v/>
       </c>
-      <c r="H55" s="10" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I55" s="10" t="inlineStr">
+      <c r="H55" s="14" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="I55" s="14" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -3019,19 +3019,19 @@
       <c r="A56" s="7" t="n">
         <v>52</v>
       </c>
-      <c r="B56" s="16" t="inlineStr">
-        <is>
-          <t>38925</t>
+      <c r="B56" s="17" t="inlineStr">
+        <is>
+          <t>38136</t>
         </is>
       </c>
       <c r="C56" s="8" t="inlineStr">
         <is>
-          <t>Star Medica Lomas Verdes</t>
+          <t>Punta Norte</t>
         </is>
       </c>
       <c r="D56" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E56" s="7" t="n">
@@ -3044,12 +3044,12 @@
         <f>IFERROR(E56/(E56+F56),0)</f>
         <v/>
       </c>
-      <c r="H56" s="10" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I56" s="10" t="inlineStr">
+      <c r="H56" s="14" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="I56" s="14" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -3059,19 +3059,19 @@
       <c r="A57" s="11" t="n">
         <v>53</v>
       </c>
-      <c r="B57" s="14" t="inlineStr">
-        <is>
-          <t>38992</t>
+      <c r="B57" s="15" t="inlineStr">
+        <is>
+          <t>43152</t>
         </is>
       </c>
       <c r="C57" s="12" t="inlineStr">
         <is>
-          <t>Tapo Puerta Oriente</t>
+          <t>Samara Satélite</t>
         </is>
       </c>
       <c r="D57" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E57" s="11" t="n">
@@ -3084,12 +3084,12 @@
         <f>IFERROR(E57/(E57+F57),0)</f>
         <v/>
       </c>
-      <c r="H57" s="10" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I57" s="10" t="inlineStr">
+      <c r="H57" s="14" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="I57" s="14" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -3099,19 +3099,19 @@
       <c r="A58" s="7" t="n">
         <v>54</v>
       </c>
-      <c r="B58" s="16" t="inlineStr">
-        <is>
-          <t>38411</t>
+      <c r="B58" s="17" t="inlineStr">
+        <is>
+          <t>38266</t>
         </is>
       </c>
       <c r="C58" s="8" t="inlineStr">
         <is>
-          <t>Torres Lindavista</t>
+          <t>San Mateo</t>
         </is>
       </c>
       <c r="D58" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E58" s="7" t="n">
@@ -3124,12 +3124,12 @@
         <f>IFERROR(E58/(E58+F58),0)</f>
         <v/>
       </c>
-      <c r="H58" s="10" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I58" s="10" t="inlineStr">
+      <c r="H58" s="14" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="I58" s="14" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -3139,19 +3139,19 @@
       <c r="A59" s="11" t="n">
         <v>55</v>
       </c>
-      <c r="B59" s="14" t="inlineStr">
-        <is>
-          <t>43130</t>
+      <c r="B59" s="15" t="inlineStr">
+        <is>
+          <t>38460</t>
         </is>
       </c>
       <c r="C59" s="12" t="inlineStr">
         <is>
-          <t>Town Center Nicolás Romero</t>
+          <t>Santa Monica</t>
         </is>
       </c>
       <c r="D59" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E59" s="11" t="n">
@@ -3164,12 +3164,12 @@
         <f>IFERROR(E59/(E59+F59),0)</f>
         <v/>
       </c>
-      <c r="H59" s="10" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I59" s="10" t="inlineStr">
+      <c r="H59" s="14" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="I59" s="14" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -3179,19 +3179,19 @@
       <c r="A60" s="7" t="n">
         <v>56</v>
       </c>
-      <c r="B60" s="16" t="inlineStr">
-        <is>
-          <t>38651</t>
+      <c r="B60" s="17" t="inlineStr">
+        <is>
+          <t>38117</t>
         </is>
       </c>
       <c r="C60" s="8" t="inlineStr">
         <is>
-          <t>Via Vallejo</t>
+          <t>Satelite</t>
         </is>
       </c>
       <c r="D60" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E60" s="7" t="n">
@@ -3204,12 +3204,12 @@
         <f>IFERROR(E60/(E60+F60),0)</f>
         <v/>
       </c>
-      <c r="H60" s="10" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I60" s="10" t="inlineStr">
+      <c r="H60" s="14" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="I60" s="14" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -3219,14 +3219,14 @@
       <c r="A61" s="11" t="n">
         <v>57</v>
       </c>
-      <c r="B61" s="14" t="inlineStr">
-        <is>
-          <t>38694</t>
+      <c r="B61" s="15" t="inlineStr">
+        <is>
+          <t>38442</t>
         </is>
       </c>
       <c r="C61" s="12" t="inlineStr">
         <is>
-          <t>Villas de la Hacienda</t>
+          <t>Sor Juana</t>
         </is>
       </c>
       <c r="D61" s="12" t="inlineStr">
@@ -3244,12 +3244,12 @@
         <f>IFERROR(E61/(E61+F61),0)</f>
         <v/>
       </c>
-      <c r="H61" s="10" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I61" s="10" t="inlineStr">
+      <c r="H61" s="14" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="I61" s="14" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -3259,19 +3259,19 @@
       <c r="A62" s="7" t="n">
         <v>58</v>
       </c>
-      <c r="B62" s="16" t="inlineStr">
-        <is>
-          <t>38656</t>
+      <c r="B62" s="17" t="inlineStr">
+        <is>
+          <t>38925</t>
         </is>
       </c>
       <c r="C62" s="8" t="inlineStr">
         <is>
-          <t>Viveros de la Loma</t>
+          <t>Star Medica Lomas Verdes</t>
         </is>
       </c>
       <c r="D62" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E62" s="7" t="n">
@@ -3284,12 +3284,12 @@
         <f>IFERROR(E62/(E62+F62),0)</f>
         <v/>
       </c>
-      <c r="H62" s="10" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I62" s="10" t="inlineStr">
+      <c r="H62" s="14" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="I62" s="14" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -3299,19 +3299,19 @@
       <c r="A63" s="11" t="n">
         <v>59</v>
       </c>
-      <c r="B63" s="14" t="inlineStr">
-        <is>
-          <t>38115</t>
+      <c r="B63" s="15" t="inlineStr">
+        <is>
+          <t>38992</t>
         </is>
       </c>
       <c r="C63" s="12" t="inlineStr">
         <is>
-          <t>Zona Azul</t>
+          <t>Tapo Puerta Oriente</t>
         </is>
       </c>
       <c r="D63" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E63" s="11" t="n">
@@ -3324,12 +3324,12 @@
         <f>IFERROR(E63/(E63+F63),0)</f>
         <v/>
       </c>
-      <c r="H63" s="10" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I63" s="10" t="inlineStr">
+      <c r="H63" s="14" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="I63" s="14" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -3339,19 +3339,19 @@
       <c r="A64" s="7" t="n">
         <v>60</v>
       </c>
-      <c r="B64" s="16" t="inlineStr">
-        <is>
-          <t>38142</t>
+      <c r="B64" s="17" t="inlineStr">
+        <is>
+          <t>38411</t>
         </is>
       </c>
       <c r="C64" s="8" t="inlineStr">
         <is>
-          <t>Zona Esmeralda</t>
+          <t>Torres Lindavista</t>
         </is>
       </c>
       <c r="D64" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E64" s="7" t="n">
@@ -3364,12 +3364,12 @@
         <f>IFERROR(E64/(E64+F64),0)</f>
         <v/>
       </c>
-      <c r="H64" s="10" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I64" s="10" t="inlineStr">
+      <c r="H64" s="14" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="I64" s="14" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -3379,14 +3379,14 @@
       <c r="A65" s="11" t="n">
         <v>61</v>
       </c>
-      <c r="B65" s="14" t="inlineStr">
-        <is>
-          <t>43043</t>
+      <c r="B65" s="15" t="inlineStr">
+        <is>
+          <t>43130</t>
         </is>
       </c>
       <c r="C65" s="12" t="inlineStr">
         <is>
-          <t>Atizapan</t>
+          <t>Town Center Nicolás Romero</t>
         </is>
       </c>
       <c r="D65" s="12" t="inlineStr">
@@ -3395,21 +3395,21 @@
         </is>
       </c>
       <c r="E65" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F65" s="11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G65" s="13">
         <f>IFERROR(E65/(E65+F65),0)</f>
         <v/>
       </c>
-      <c r="H65" s="10" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I65" s="10" t="inlineStr">
+      <c r="H65" s="14" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="I65" s="14" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -3419,37 +3419,37 @@
       <c r="A66" s="7" t="n">
         <v>62</v>
       </c>
-      <c r="B66" s="16" t="inlineStr">
-        <is>
-          <t>38529</t>
+      <c r="B66" s="17" t="inlineStr">
+        <is>
+          <t>38651</t>
         </is>
       </c>
       <c r="C66" s="8" t="inlineStr">
         <is>
-          <t>Bosques de Aragon</t>
+          <t>Via Vallejo</t>
         </is>
       </c>
       <c r="D66" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E66" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F66" s="7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G66" s="9">
         <f>IFERROR(E66/(E66+F66),0)</f>
         <v/>
       </c>
-      <c r="H66" s="10" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I66" s="10" t="inlineStr">
+      <c r="H66" s="14" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="I66" s="14" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -3459,37 +3459,37 @@
       <c r="A67" s="11" t="n">
         <v>63</v>
       </c>
-      <c r="B67" s="14" t="inlineStr">
-        <is>
-          <t>38837</t>
+      <c r="B67" s="15" t="inlineStr">
+        <is>
+          <t>38694</t>
         </is>
       </c>
       <c r="C67" s="12" t="inlineStr">
         <is>
-          <t>Centenario Azcapotzalco</t>
+          <t>Villas de la Hacienda</t>
         </is>
       </c>
       <c r="D67" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E67" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F67" s="11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G67" s="13">
         <f>IFERROR(E67/(E67+F67),0)</f>
         <v/>
       </c>
-      <c r="H67" s="10" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I67" s="10" t="inlineStr">
+      <c r="H67" s="14" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="I67" s="14" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -3499,37 +3499,37 @@
       <c r="A68" s="7" t="n">
         <v>64</v>
       </c>
-      <c r="B68" s="16" t="inlineStr">
-        <is>
-          <t>38903</t>
+      <c r="B68" s="17" t="inlineStr">
+        <is>
+          <t>38656</t>
         </is>
       </c>
       <c r="C68" s="8" t="inlineStr">
         <is>
-          <t>Encuentro Oceania</t>
+          <t>Viveros de la Loma</t>
         </is>
       </c>
       <c r="D68" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E68" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F68" s="7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G68" s="9">
         <f>IFERROR(E68/(E68+F68),0)</f>
         <v/>
       </c>
-      <c r="H68" s="10" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I68" s="10" t="inlineStr">
+      <c r="H68" s="14" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="I68" s="14" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -3539,37 +3539,37 @@
       <c r="A69" s="11" t="n">
         <v>65</v>
       </c>
-      <c r="B69" s="14" t="inlineStr">
-        <is>
-          <t>38995</t>
+      <c r="B69" s="15" t="inlineStr">
+        <is>
+          <t>38115</t>
         </is>
       </c>
       <c r="C69" s="12" t="inlineStr">
         <is>
-          <t>Encuentro Oceania II</t>
+          <t>Zona Azul</t>
         </is>
       </c>
       <c r="D69" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E69" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F69" s="11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G69" s="13">
         <f>IFERROR(E69/(E69+F69),0)</f>
         <v/>
       </c>
-      <c r="H69" s="10" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I69" s="10" t="inlineStr">
+      <c r="H69" s="14" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="I69" s="14" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -3579,14 +3579,14 @@
       <c r="A70" s="7" t="n">
         <v>66</v>
       </c>
-      <c r="B70" s="16" t="inlineStr">
-        <is>
-          <t>38507</t>
+      <c r="B70" s="17" t="inlineStr">
+        <is>
+          <t>38142</t>
         </is>
       </c>
       <c r="C70" s="8" t="inlineStr">
         <is>
-          <t>Espacio Vista del Valle</t>
+          <t>Zona Esmeralda</t>
         </is>
       </c>
       <c r="D70" s="8" t="inlineStr">
@@ -3595,21 +3595,21 @@
         </is>
       </c>
       <c r="E70" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F70" s="7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G70" s="9">
         <f>IFERROR(E70/(E70+F70),0)</f>
         <v/>
       </c>
-      <c r="H70" s="10" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I70" s="10" t="inlineStr">
+      <c r="H70" s="14" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="I70" s="14" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -3619,19 +3619,19 @@
       <c r="A71" s="11" t="n">
         <v>67</v>
       </c>
-      <c r="B71" s="14" t="inlineStr">
-        <is>
-          <t>38230</t>
+      <c r="B71" s="15" t="inlineStr">
+        <is>
+          <t>38529</t>
         </is>
       </c>
       <c r="C71" s="12" t="inlineStr">
         <is>
-          <t>ITEMS Edo de Mexico</t>
+          <t>Bosques de Aragon</t>
         </is>
       </c>
       <c r="D71" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E71" s="11" t="n">
@@ -3644,12 +3644,12 @@
         <f>IFERROR(E71/(E71+F71),0)</f>
         <v/>
       </c>
-      <c r="H71" s="10" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I71" s="10" t="inlineStr">
+      <c r="H71" s="14" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="I71" s="14" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -3659,14 +3659,14 @@
       <c r="A72" s="7" t="n">
         <v>68</v>
       </c>
-      <c r="B72" s="16" t="inlineStr">
-        <is>
-          <t>38965</t>
+      <c r="B72" s="17" t="inlineStr">
+        <is>
+          <t>38903</t>
         </is>
       </c>
       <c r="C72" s="8" t="inlineStr">
         <is>
-          <t>Parque Tepeyac Piso 2</t>
+          <t>Encuentro Oceania</t>
         </is>
       </c>
       <c r="D72" s="8" t="inlineStr">
@@ -3684,12 +3684,12 @@
         <f>IFERROR(E72/(E72+F72),0)</f>
         <v/>
       </c>
-      <c r="H72" s="10" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I72" s="10" t="inlineStr">
+      <c r="H72" s="14" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="I72" s="14" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -3699,19 +3699,19 @@
       <c r="A73" s="11" t="n">
         <v>69</v>
       </c>
-      <c r="B73" s="14" t="inlineStr">
-        <is>
-          <t>38792</t>
+      <c r="B73" s="15" t="inlineStr">
+        <is>
+          <t>38995</t>
         </is>
       </c>
       <c r="C73" s="12" t="inlineStr">
         <is>
-          <t>Pasaje Tlanepantla</t>
+          <t>Encuentro Oceania II</t>
         </is>
       </c>
       <c r="D73" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E73" s="11" t="n">
@@ -3724,12 +3724,12 @@
         <f>IFERROR(E73/(E73+F73),0)</f>
         <v/>
       </c>
-      <c r="H73" s="10" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I73" s="10" t="inlineStr">
+      <c r="H73" s="14" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="I73" s="14" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -3739,19 +3739,19 @@
       <c r="A74" s="7" t="n">
         <v>70</v>
       </c>
-      <c r="B74" s="16" t="inlineStr">
-        <is>
-          <t>38811</t>
+      <c r="B74" s="17" t="inlineStr">
+        <is>
+          <t>38507</t>
         </is>
       </c>
       <c r="C74" s="8" t="inlineStr">
         <is>
-          <t>Plaza Tepeyac</t>
+          <t>Espacio Vista del Valle</t>
         </is>
       </c>
       <c r="D74" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E74" s="7" t="n">
@@ -3764,12 +3764,12 @@
         <f>IFERROR(E74/(E74+F74),0)</f>
         <v/>
       </c>
-      <c r="H74" s="10" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I74" s="10" t="inlineStr">
+      <c r="H74" s="14" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="I74" s="14" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -3779,14 +3779,14 @@
       <c r="A75" s="11" t="n">
         <v>71</v>
       </c>
-      <c r="B75" s="14" t="inlineStr">
-        <is>
-          <t>38460</t>
+      <c r="B75" s="15" t="inlineStr">
+        <is>
+          <t>38230</t>
         </is>
       </c>
       <c r="C75" s="12" t="inlineStr">
         <is>
-          <t>Santa Monica</t>
+          <t>ITEMS Edo de Mexico</t>
         </is>
       </c>
       <c r="D75" s="12" t="inlineStr">
@@ -3804,12 +3804,12 @@
         <f>IFERROR(E75/(E75+F75),0)</f>
         <v/>
       </c>
-      <c r="H75" s="10" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I75" s="10" t="inlineStr">
+      <c r="H75" s="14" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="I75" s="14" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -3819,14 +3819,14 @@
       <c r="A76" s="7" t="n">
         <v>72</v>
       </c>
-      <c r="B76" s="16" t="inlineStr">
-        <is>
-          <t>38374</t>
+      <c r="B76" s="17" t="inlineStr">
+        <is>
+          <t>38792</t>
         </is>
       </c>
       <c r="C76" s="8" t="inlineStr">
         <is>
-          <t>Valle Dorado</t>
+          <t>Pasaje Tlanepantla</t>
         </is>
       </c>
       <c r="D76" s="8" t="inlineStr">
@@ -3844,12 +3844,12 @@
         <f>IFERROR(E76/(E76+F76),0)</f>
         <v/>
       </c>
-      <c r="H76" s="10" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I76" s="10" t="inlineStr">
+      <c r="H76" s="14" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="I76" s="14" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -3906,7 +3906,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Centro Norte · Corte 31/08/2026 12:45</t>
+          <t>Centro Norte · Corte 31/08/2026 15:53</t>
         </is>
       </c>
     </row>
@@ -3976,12 +3976,12 @@
           <t>03/09/26</t>
         </is>
       </c>
-      <c r="G5" s="10" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="H5" s="10" t="inlineStr">
+      <c r="G5" s="14" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="H5" s="14" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -4011,12 +4011,12 @@
           <t>03/09/26</t>
         </is>
       </c>
-      <c r="G6" s="10" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="H6" s="10" t="inlineStr">
+      <c r="G6" s="14" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="H6" s="14" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -4032,10 +4032,10 @@
         </is>
       </c>
       <c r="C7" s="11" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E7" s="13">
         <f>IFERROR(C7/(C7+D7),0)</f>
@@ -4046,12 +4046,12 @@
           <t>06/09/26</t>
         </is>
       </c>
-      <c r="G7" s="10" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="H7" s="10" t="inlineStr">
+      <c r="G7" s="14" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="H7" s="14" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -4081,12 +4081,12 @@
           <t>03/09/26</t>
         </is>
       </c>
-      <c r="G8" s="10" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="H8" s="10" t="inlineStr">
+      <c r="G8" s="14" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="H8" s="14" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -4116,12 +4116,12 @@
           <t>06/09/26</t>
         </is>
       </c>
-      <c r="G9" s="10" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="H9" s="10" t="inlineStr">
+      <c r="G9" s="14" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="H9" s="14" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -4137,10 +4137,10 @@
         </is>
       </c>
       <c r="C10" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E10" s="9">
         <f>IFERROR(C10/(C10+D10),0)</f>
@@ -4151,12 +4151,12 @@
           <t>06/09/26</t>
         </is>
       </c>
-      <c r="G10" s="10" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="H10" s="10" t="inlineStr">
+      <c r="G10" s="14" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="H10" s="14" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -4186,12 +4186,12 @@
           <t>13/09/26</t>
         </is>
       </c>
-      <c r="G11" s="10" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="H11" s="10" t="inlineStr">
+      <c r="G11" s="14" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="H11" s="14" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -4207,10 +4207,10 @@
         </is>
       </c>
       <c r="C12" s="7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E12" s="9">
         <f>IFERROR(C12/(C12+D12),0)</f>
@@ -4221,12 +4221,12 @@
           <t>06/09/26</t>
         </is>
       </c>
-      <c r="G12" s="10" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="H12" s="10" t="inlineStr">
+      <c r="G12" s="14" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="H12" s="14" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -4256,12 +4256,12 @@
           <t>03/09/26</t>
         </is>
       </c>
-      <c r="G13" s="10" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="H13" s="10" t="inlineStr">
+      <c r="G13" s="14" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="H13" s="14" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -4277,10 +4277,10 @@
         </is>
       </c>
       <c r="C14" s="7" t="n">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E14" s="9">
         <f>IFERROR(C14/(C14+D14),0)</f>
@@ -4291,14 +4291,14 @@
           <t>31/08/26</t>
         </is>
       </c>
-      <c r="G14" s="17" t="inlineStr">
-        <is>
-          <t>Seguimiento</t>
-        </is>
-      </c>
-      <c r="H14" s="17" t="inlineStr">
-        <is>
-          <t>Dar seguimiento</t>
+      <c r="G14" s="16" t="inlineStr">
+        <is>
+          <t>En meta</t>
+        </is>
+      </c>
+      <c r="H14" s="16" t="inlineStr">
+        <is>
+          <t>Mantener estándar</t>
         </is>
       </c>
     </row>

--- a/exports/Resumen_Evidencias_OPS.xlsx
+++ b/exports/Resumen_Evidencias_OPS.xlsx
@@ -592,7 +592,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Centro Norte · Corte 31/08/2026 15:53</t>
+          <t>Centro Norte · Corte 31/08/2026 16:00</t>
         </is>
       </c>
     </row>
@@ -615,10 +615,10 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="E6" s="5">
         <f>IFERROR(A6/(A6+C6),0)</f>
@@ -681,10 +681,10 @@
         <v>10</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F10" s="9">
         <f>IFERROR(D10/(D10+E10),0)</f>
@@ -924,7 +924,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Centro Norte · Corte 31/08/2026 15:53</t>
+          <t>Centro Norte · Corte 31/08/2026 16:00</t>
         </is>
       </c>
     </row>
@@ -1181,12 +1181,12 @@
       </c>
       <c r="B10" s="17" t="inlineStr">
         <is>
-          <t>38333</t>
+          <t>38894</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>Izcalli Mega</t>
+          <t>Galerias Perinorte</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>38368</t>
+          <t>38333</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>Luna Park</t>
+          <t>Izcalli Mega</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
@@ -1261,17 +1261,17 @@
       </c>
       <c r="B12" s="17" t="inlineStr">
         <is>
-          <t>38561</t>
+          <t>38368</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Parque Toreo</t>
+          <t>Luna Park</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E12" s="7" t="n">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>38894</t>
+          <t>38561</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>Galerias Perinorte</t>
+          <t>Parque Toreo</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E13" s="11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G13" s="13">
         <f>IFERROR(E13/(E13+F13),0)</f>
@@ -3906,7 +3906,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Centro Norte · Corte 31/08/2026 15:53</t>
+          <t>Centro Norte · Corte 31/08/2026 16:00</t>
         </is>
       </c>
     </row>
@@ -4242,10 +4242,10 @@
         </is>
       </c>
       <c r="C13" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D13" s="11" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E13" s="13">
         <f>IFERROR(C13/(C13+D13),0)</f>

--- a/exports/Resumen_Evidencias_OPS.xlsx
+++ b/exports/Resumen_Evidencias_OPS.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Resumen" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Tiendas" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Actividades" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tiendas" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Actividades" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Resumen'!$A$9:$H$15</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Resumen'!$A$1:$H$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Tiendas'!$A$4:$I$76</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Tiendas'!$1:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Actividades'!$A$4:$H$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Actividades'!$A$4:$H$13</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -592,7 +592,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Centro Norte · Corte 31/08/2026 16:00</t>
+          <t>Centro Norte · Corte 31/08/2026 20:06</t>
         </is>
       </c>
     </row>
@@ -615,10 +615,10 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>599</v>
+        <v>521</v>
       </c>
       <c r="E6" s="5">
         <f>IFERROR(A6/(A6+C6),0)</f>
@@ -681,10 +681,10 @@
         <v>10</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="F10" s="9">
         <f>IFERROR(D10/(D10+E10),0)</f>
@@ -707,17 +707,17 @@
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela</t>
+          <t>Veronica Garcia</t>
         </is>
       </c>
       <c r="C11" s="11" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E11" s="12" t="n">
-        <v>107</v>
+        <v>79</v>
       </c>
       <c r="F11" s="13">
         <f>IFERROR(D11/(D11+E11),0)</f>
@@ -740,14 +740,14 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia</t>
+          <t>Yazmin Chabela</t>
         </is>
       </c>
       <c r="C12" s="7" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E12" s="8" t="n">
         <v>95</v>
@@ -773,17 +773,17 @@
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño</t>
+          <t>Nancy Carolina</t>
         </is>
       </c>
       <c r="C13" s="11" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D13" s="11" t="n">
         <v>14</v>
       </c>
       <c r="E13" s="12" t="n">
-        <v>116</v>
+        <v>94</v>
       </c>
       <c r="F13" s="13">
         <f>IFERROR(D13/(D13+E13),0)</f>
@@ -806,17 +806,17 @@
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina</t>
+          <t>Vanessa Carreño</t>
         </is>
       </c>
       <c r="C14" s="7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E14" s="8" t="n">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="F14" s="9">
         <f>IFERROR(D14/(D14+E14),0)</f>
@@ -846,10 +846,10 @@
         <v>13</v>
       </c>
       <c r="D15" s="11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E15" s="12" t="n">
-        <v>118</v>
+        <v>104</v>
       </c>
       <c r="F15" s="13">
         <f>IFERROR(D15/(D15+E15),0)</f>
@@ -924,7 +924,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Centro Norte · Corte 31/08/2026 16:00</t>
+          <t>Centro Norte · Corte 31/08/2026 20:06</t>
         </is>
       </c>
     </row>
@@ -995,10 +995,10 @@
         </is>
       </c>
       <c r="E5" s="11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G5" s="13">
         <f>IFERROR(E5/(E5+F5),0)</f>
@@ -1035,10 +1035,10 @@
         </is>
       </c>
       <c r="E6" s="7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G6" s="9">
         <f>IFERROR(E6/(E6+F6),0)</f>
@@ -1078,7 +1078,7 @@
         <v>6</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G7" s="13">
         <f>IFERROR(E7/(E7+F7),0)</f>
@@ -1101,24 +1101,24 @@
       </c>
       <c r="B8" s="17" t="inlineStr">
         <is>
-          <t>38695</t>
+          <t>38894</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>Cetram 4 Caminos</t>
+          <t>Galerias Perinorte</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E8" s="7" t="n">
         <v>5</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G8" s="9">
         <f>IFERROR(E8/(E8+F8),0)</f>
@@ -1141,12 +1141,12 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>38401</t>
+          <t>38368</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>Coacalco</t>
+          <t>Luna Park</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
@@ -1158,7 +1158,7 @@
         <v>5</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G9" s="13">
         <f>IFERROR(E9/(E9+F9),0)</f>
@@ -1181,24 +1181,24 @@
       </c>
       <c r="B10" s="17" t="inlineStr">
         <is>
-          <t>38894</t>
+          <t>38561</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>Galerias Perinorte</t>
+          <t>Parque Toreo</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E10" s="7" t="n">
         <v>5</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G10" s="9">
         <f>IFERROR(E10/(E10+F10),0)</f>
@@ -1221,21 +1221,21 @@
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>38333</t>
+          <t>38695</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>Izcalli Mega</t>
+          <t>Cetram 4 Caminos</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E11" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F11" s="11" t="n">
         <v>5</v>
@@ -1261,12 +1261,12 @@
       </c>
       <c r="B12" s="17" t="inlineStr">
         <is>
-          <t>38368</t>
+          <t>38401</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Luna Park</t>
+          <t>Coacalco</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
@@ -1275,7 +1275,7 @@
         </is>
       </c>
       <c r="E12" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F12" s="7" t="n">
         <v>5</v>
@@ -1301,21 +1301,21 @@
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>38561</t>
+          <t>38333</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>Parque Toreo</t>
+          <t>Izcalli Mega</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E13" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F13" s="11" t="n">
         <v>5</v>
@@ -1358,7 +1358,7 @@
         <v>4</v>
       </c>
       <c r="F14" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G14" s="9">
         <f>IFERROR(E14/(E14+F14),0)</f>
@@ -1398,7 +1398,7 @@
         <v>3</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G15" s="13">
         <f>IFERROR(E15/(E15+F15),0)</f>
@@ -1438,7 +1438,7 @@
         <v>2</v>
       </c>
       <c r="F16" s="7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G16" s="9">
         <f>IFERROR(E16/(E16+F16),0)</f>
@@ -1478,7 +1478,7 @@
         <v>2</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G17" s="13">
         <f>IFERROR(E17/(E17+F17),0)</f>
@@ -1518,7 +1518,7 @@
         <v>2</v>
       </c>
       <c r="F18" s="7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G18" s="9">
         <f>IFERROR(E18/(E18+F18),0)</f>
@@ -1541,24 +1541,24 @@
       </c>
       <c r="B19" s="15" t="inlineStr">
         <is>
-          <t>38859</t>
+          <t>38924</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>Plaza Satelite II N1</t>
+          <t>Plaza Aeropuerto</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E19" s="11" t="n">
         <v>2</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G19" s="13">
         <f>IFERROR(E19/(E19+F19),0)</f>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="B20" s="17" t="inlineStr">
         <is>
-          <t>38475</t>
+          <t>38859</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>Satelite Centro Civico</t>
+          <t>Plaza Satelite II N1</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr">
@@ -1598,7 +1598,7 @@
         <v>2</v>
       </c>
       <c r="F20" s="7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G20" s="9">
         <f>IFERROR(E20/(E20+F20),0)</f>
@@ -1621,24 +1621,24 @@
       </c>
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t>38606</t>
+          <t>38475</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>TlalnepantlaCarso</t>
+          <t>Satelite Centro Civico</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E21" s="11" t="n">
         <v>2</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G21" s="13">
         <f>IFERROR(E21/(E21+F21),0)</f>
@@ -1661,12 +1661,12 @@
       </c>
       <c r="B22" s="17" t="inlineStr">
         <is>
-          <t>38374</t>
+          <t>38606</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>Valle Dorado</t>
+          <t>TlalnepantlaCarso</t>
         </is>
       </c>
       <c r="D22" s="8" t="inlineStr">
@@ -1678,7 +1678,7 @@
         <v>2</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G22" s="9">
         <f>IFERROR(E22/(E22+F22),0)</f>
@@ -1701,12 +1701,12 @@
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>38186</t>
+          <t>38374</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>Arboledas</t>
+          <t>Valle Dorado</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr">
@@ -1715,10 +1715,10 @@
         </is>
       </c>
       <c r="E23" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G23" s="13">
         <f>IFERROR(E23/(E23+F23),0)</f>
@@ -1741,24 +1741,24 @@
       </c>
       <c r="B24" s="17" t="inlineStr">
         <is>
-          <t>43043</t>
+          <t>38186</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>Atizapan</t>
+          <t>Arboledas</t>
         </is>
       </c>
       <c r="D24" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E24" s="7" t="n">
         <v>1</v>
       </c>
       <c r="F24" s="7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G24" s="9">
         <f>IFERROR(E24/(E24+F24),0)</f>
@@ -1781,12 +1781,12 @@
       </c>
       <c r="B25" s="15" t="inlineStr">
         <is>
-          <t>38149</t>
+          <t>43043</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>Bellavista</t>
+          <t>Atizapan</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
@@ -1798,7 +1798,7 @@
         <v>1</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G25" s="13">
         <f>IFERROR(E25/(E25+F25),0)</f>
@@ -1821,24 +1821,24 @@
       </c>
       <c r="B26" s="17" t="inlineStr">
         <is>
-          <t>38930</t>
+          <t>38149</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>Blvd. Aeropuerto dt</t>
+          <t>Bellavista</t>
         </is>
       </c>
       <c r="D26" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E26" s="7" t="n">
         <v>1</v>
       </c>
       <c r="F26" s="7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G26" s="9">
         <f>IFERROR(E26/(E26+F26),0)</f>
@@ -1861,24 +1861,24 @@
       </c>
       <c r="B27" s="15" t="inlineStr">
         <is>
-          <t>38527</t>
+          <t>38930</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>Camarones</t>
+          <t>Blvd. Aeropuerto dt</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E27" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G27" s="13">
         <f>IFERROR(E27/(E27+F27),0)</f>
@@ -1901,24 +1901,24 @@
       </c>
       <c r="B28" s="17" t="inlineStr">
         <is>
-          <t>38837</t>
+          <t>38529</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>Centenario Azcapotzalco</t>
+          <t>Bosques de Aragon</t>
         </is>
       </c>
       <c r="D28" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E28" s="7" t="n">
         <v>1</v>
       </c>
       <c r="F28" s="7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G28" s="9">
         <f>IFERROR(E28/(E28+F28),0)</f>
@@ -1941,24 +1941,24 @@
       </c>
       <c r="B29" s="15" t="inlineStr">
         <is>
-          <t>38394</t>
+          <t>38527</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>Centro Comercial Lomas Verdes</t>
+          <t>Camarones</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E29" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G29" s="13">
         <f>IFERROR(E29/(E29+F29),0)</f>
@@ -1981,24 +1981,24 @@
       </c>
       <c r="B30" s="17" t="inlineStr">
         <is>
-          <t>38535</t>
+          <t>38837</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>City Center Esmeralda</t>
+          <t>Centenario Azcapotzalco</t>
         </is>
       </c>
       <c r="D30" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E30" s="7" t="n">
         <v>1</v>
       </c>
       <c r="F30" s="7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G30" s="9">
         <f>IFERROR(E30/(E30+F30),0)</f>
@@ -2021,24 +2021,24 @@
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>38197</t>
+          <t>38394</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>Echegaray</t>
+          <t>Centro Comercial Lomas Verdes</t>
         </is>
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E31" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G31" s="13">
         <f>IFERROR(E31/(E31+F31),0)</f>
@@ -2061,24 +2061,24 @@
       </c>
       <c r="B32" s="17" t="inlineStr">
         <is>
-          <t>38431</t>
+          <t>38535</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>Eduardo Molina</t>
+          <t>City Center Esmeralda</t>
         </is>
       </c>
       <c r="D32" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E32" s="7" t="n">
         <v>1</v>
       </c>
       <c r="F32" s="7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G32" s="9">
         <f>IFERROR(E32/(E32+F32),0)</f>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="B33" s="15" t="inlineStr">
         <is>
-          <t>38458</t>
+          <t>38197</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>El Rosario</t>
+          <t>Echegaray</t>
         </is>
       </c>
       <c r="D33" s="12" t="inlineStr">
@@ -2118,7 +2118,7 @@
         <v>1</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G33" s="13">
         <f>IFERROR(E33/(E33+F33),0)</f>
@@ -2141,24 +2141,24 @@
       </c>
       <c r="B34" s="17" t="inlineStr">
         <is>
-          <t>38363</t>
+          <t>38431</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>Galerias Atizapan</t>
+          <t>Eduardo Molina</t>
         </is>
       </c>
       <c r="D34" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E34" s="7" t="n">
         <v>1</v>
       </c>
       <c r="F34" s="7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G34" s="9">
         <f>IFERROR(E34/(E34+F34),0)</f>
@@ -2181,12 +2181,12 @@
       </c>
       <c r="B35" s="15" t="inlineStr">
         <is>
-          <t>38770</t>
+          <t>38458</t>
         </is>
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>Gustavo Baz 29</t>
+          <t>El Rosario</t>
         </is>
       </c>
       <c r="D35" s="12" t="inlineStr">
@@ -2198,7 +2198,7 @@
         <v>1</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G35" s="13">
         <f>IFERROR(E35/(E35+F35),0)</f>
@@ -2221,24 +2221,24 @@
       </c>
       <c r="B36" s="17" t="inlineStr">
         <is>
-          <t>38661</t>
+          <t>38903</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>Jinetes</t>
+          <t>Encuentro Oceania</t>
         </is>
       </c>
       <c r="D36" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E36" s="7" t="n">
         <v>1</v>
       </c>
       <c r="F36" s="7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G36" s="9">
         <f>IFERROR(E36/(E36+F36),0)</f>
@@ -2261,24 +2261,24 @@
       </c>
       <c r="B37" s="15" t="inlineStr">
         <is>
-          <t>38205</t>
+          <t>38995</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>Lindavista</t>
+          <t>Encuentro Oceania II</t>
         </is>
       </c>
       <c r="D37" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E37" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G37" s="13">
         <f>IFERROR(E37/(E37+F37),0)</f>
@@ -2301,24 +2301,24 @@
       </c>
       <c r="B38" s="17" t="inlineStr">
         <is>
-          <t>38207</t>
+          <t>38507</t>
         </is>
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>Lindavista II</t>
+          <t>Espacio Vista del Valle</t>
         </is>
       </c>
       <c r="D38" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E38" s="7" t="n">
         <v>1</v>
       </c>
       <c r="F38" s="7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G38" s="9">
         <f>IFERROR(E38/(E38+F38),0)</f>
@@ -2341,12 +2341,12 @@
       </c>
       <c r="B39" s="15" t="inlineStr">
         <is>
-          <t>38119</t>
+          <t>38363</t>
         </is>
       </c>
       <c r="C39" s="12" t="inlineStr">
         <is>
-          <t>Lomas Verdes</t>
+          <t>Galerias Atizapan</t>
         </is>
       </c>
       <c r="D39" s="12" t="inlineStr">
@@ -2358,7 +2358,7 @@
         <v>1</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G39" s="13">
         <f>IFERROR(E39/(E39+F39),0)</f>
@@ -2381,24 +2381,24 @@
       </c>
       <c r="B40" s="17" t="inlineStr">
         <is>
-          <t>38270</t>
+          <t>38770</t>
         </is>
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>Lomas Verdes II</t>
+          <t>Gustavo Baz 29</t>
         </is>
       </c>
       <c r="D40" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E40" s="7" t="n">
         <v>1</v>
       </c>
       <c r="F40" s="7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G40" s="9">
         <f>IFERROR(E40/(E40+F40),0)</f>
@@ -2421,24 +2421,24 @@
       </c>
       <c r="B41" s="15" t="inlineStr">
         <is>
-          <t>38371</t>
+          <t>38230</t>
         </is>
       </c>
       <c r="C41" s="12" t="inlineStr">
         <is>
-          <t>Montevideo DT</t>
+          <t>ITEMS Edo de Mexico</t>
         </is>
       </c>
       <c r="D41" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E41" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G41" s="13">
         <f>IFERROR(E41/(E41+F41),0)</f>
@@ -2461,24 +2461,24 @@
       </c>
       <c r="B42" s="17" t="inlineStr">
         <is>
-          <t>43111</t>
+          <t>38661</t>
         </is>
       </c>
       <c r="C42" s="8" t="inlineStr">
         <is>
-          <t>Montevideo Insurgentes</t>
+          <t>Jinetes</t>
         </is>
       </c>
       <c r="D42" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E42" s="7" t="n">
         <v>1</v>
       </c>
       <c r="F42" s="7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G42" s="9">
         <f>IFERROR(E42/(E42+F42),0)</f>
@@ -2501,24 +2501,24 @@
       </c>
       <c r="B43" s="15" t="inlineStr">
         <is>
-          <t>38674</t>
+          <t>38205</t>
         </is>
       </c>
       <c r="C43" s="12" t="inlineStr">
         <is>
-          <t>Mundo E</t>
+          <t>Lindavista</t>
         </is>
       </c>
       <c r="D43" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E43" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G43" s="13">
         <f>IFERROR(E43/(E43+F43),0)</f>
@@ -2541,24 +2541,24 @@
       </c>
       <c r="B44" s="17" t="inlineStr">
         <is>
-          <t>38845</t>
+          <t>38207</t>
         </is>
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t>Mundo E II</t>
+          <t>Lindavista II</t>
         </is>
       </c>
       <c r="D44" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E44" s="7" t="n">
         <v>1</v>
       </c>
       <c r="F44" s="7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G44" s="9">
         <f>IFERROR(E44/(E44+F44),0)</f>
@@ -2581,24 +2581,24 @@
       </c>
       <c r="B45" s="15" t="inlineStr">
         <is>
-          <t>43195</t>
+          <t>38119</t>
         </is>
       </c>
       <c r="C45" s="12" t="inlineStr">
         <is>
-          <t>Parque Jadin kiosko</t>
+          <t>Lomas Verdes</t>
         </is>
       </c>
       <c r="D45" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E45" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G45" s="13">
         <f>IFERROR(E45/(E45+F45),0)</f>
@@ -2621,24 +2621,24 @@
       </c>
       <c r="B46" s="17" t="inlineStr">
         <is>
-          <t>38937</t>
+          <t>38270</t>
         </is>
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t>Parque Tepeyac Piso 1</t>
+          <t>Lomas Verdes II</t>
         </is>
       </c>
       <c r="D46" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E46" s="7" t="n">
         <v>1</v>
       </c>
       <c r="F46" s="7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G46" s="9">
         <f>IFERROR(E46/(E46+F46),0)</f>
@@ -2661,24 +2661,24 @@
       </c>
       <c r="B47" s="15" t="inlineStr">
         <is>
-          <t>38965</t>
+          <t>38371</t>
         </is>
       </c>
       <c r="C47" s="12" t="inlineStr">
         <is>
-          <t>Parque Tepeyac Piso 2</t>
+          <t>Montevideo DT</t>
         </is>
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E47" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G47" s="13">
         <f>IFERROR(E47/(E47+F47),0)</f>
@@ -2701,24 +2701,24 @@
       </c>
       <c r="B48" s="17" t="inlineStr">
         <is>
-          <t>38590</t>
+          <t>43111</t>
         </is>
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
-          <t>Parque Toreo II</t>
+          <t>Montevideo Insurgentes</t>
         </is>
       </c>
       <c r="D48" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E48" s="7" t="n">
         <v>1</v>
       </c>
       <c r="F48" s="7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G48" s="9">
         <f>IFERROR(E48/(E48+F48),0)</f>
@@ -2741,24 +2741,24 @@
       </c>
       <c r="B49" s="15" t="inlineStr">
         <is>
-          <t>38546</t>
+          <t>38674</t>
         </is>
       </c>
       <c r="C49" s="12" t="inlineStr">
         <is>
-          <t>Patio Claveria</t>
+          <t>Mundo E</t>
         </is>
       </c>
       <c r="D49" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E49" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G49" s="13">
         <f>IFERROR(E49/(E49+F49),0)</f>
@@ -2781,24 +2781,24 @@
       </c>
       <c r="B50" s="17" t="inlineStr">
         <is>
-          <t>38677</t>
+          <t>38845</t>
         </is>
       </c>
       <c r="C50" s="8" t="inlineStr">
         <is>
-          <t>Patio la Raza</t>
+          <t>Mundo E II</t>
         </is>
       </c>
       <c r="D50" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E50" s="7" t="n">
         <v>1</v>
       </c>
       <c r="F50" s="7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G50" s="9">
         <f>IFERROR(E50/(E50+F50),0)</f>
@@ -2821,24 +2821,24 @@
       </c>
       <c r="B51" s="15" t="inlineStr">
         <is>
-          <t>38176</t>
+          <t>43195</t>
         </is>
       </c>
       <c r="C51" s="12" t="inlineStr">
         <is>
-          <t>Periferico Satélite DT</t>
+          <t>Parque Jadin kiosko</t>
         </is>
       </c>
       <c r="D51" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E51" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G51" s="13">
         <f>IFERROR(E51/(E51+F51),0)</f>
@@ -2861,12 +2861,12 @@
       </c>
       <c r="B52" s="17" t="inlineStr">
         <is>
-          <t>38924</t>
+          <t>38937</t>
         </is>
       </c>
       <c r="C52" s="8" t="inlineStr">
         <is>
-          <t>Plaza Aeropuerto</t>
+          <t>Parque Tepeyac Piso 1</t>
         </is>
       </c>
       <c r="D52" s="8" t="inlineStr">
@@ -2878,7 +2878,7 @@
         <v>1</v>
       </c>
       <c r="F52" s="7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G52" s="9">
         <f>IFERROR(E52/(E52+F52),0)</f>
@@ -2901,24 +2901,24 @@
       </c>
       <c r="B53" s="15" t="inlineStr">
         <is>
-          <t>38427</t>
+          <t>38965</t>
         </is>
       </c>
       <c r="C53" s="12" t="inlineStr">
         <is>
-          <t>Plaza Satelite</t>
+          <t>Parque Tepeyac Piso 2</t>
         </is>
       </c>
       <c r="D53" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E53" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F53" s="11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G53" s="13">
         <f>IFERROR(E53/(E53+F53),0)</f>
@@ -2941,24 +2941,24 @@
       </c>
       <c r="B54" s="17" t="inlineStr">
         <is>
-          <t>38811</t>
+          <t>38590</t>
         </is>
       </c>
       <c r="C54" s="8" t="inlineStr">
         <is>
-          <t>Plaza Tepeyac</t>
+          <t>Parque Toreo II</t>
         </is>
       </c>
       <c r="D54" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E54" s="7" t="n">
         <v>1</v>
       </c>
       <c r="F54" s="7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G54" s="9">
         <f>IFERROR(E54/(E54+F54),0)</f>
@@ -2981,24 +2981,24 @@
       </c>
       <c r="B55" s="15" t="inlineStr">
         <is>
-          <t>43132</t>
+          <t>38792</t>
         </is>
       </c>
       <c r="C55" s="12" t="inlineStr">
         <is>
-          <t>Plaza Vista Norte</t>
+          <t>Pasaje Tlanepantla</t>
         </is>
       </c>
       <c r="D55" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E55" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F55" s="11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G55" s="13">
         <f>IFERROR(E55/(E55+F55),0)</f>
@@ -3021,24 +3021,24 @@
       </c>
       <c r="B56" s="17" t="inlineStr">
         <is>
-          <t>38136</t>
+          <t>38546</t>
         </is>
       </c>
       <c r="C56" s="8" t="inlineStr">
         <is>
-          <t>Punta Norte</t>
+          <t>Patio Claveria</t>
         </is>
       </c>
       <c r="D56" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E56" s="7" t="n">
         <v>1</v>
       </c>
       <c r="F56" s="7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G56" s="9">
         <f>IFERROR(E56/(E56+F56),0)</f>
@@ -3061,24 +3061,24 @@
       </c>
       <c r="B57" s="15" t="inlineStr">
         <is>
-          <t>43152</t>
+          <t>38677</t>
         </is>
       </c>
       <c r="C57" s="12" t="inlineStr">
         <is>
-          <t>Samara Satélite</t>
+          <t>Patio la Raza</t>
         </is>
       </c>
       <c r="D57" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E57" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F57" s="11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G57" s="13">
         <f>IFERROR(E57/(E57+F57),0)</f>
@@ -3101,24 +3101,24 @@
       </c>
       <c r="B58" s="17" t="inlineStr">
         <is>
-          <t>38266</t>
+          <t>38176</t>
         </is>
       </c>
       <c r="C58" s="8" t="inlineStr">
         <is>
-          <t>San Mateo</t>
+          <t>Periferico Satélite DT</t>
         </is>
       </c>
       <c r="D58" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E58" s="7" t="n">
         <v>1</v>
       </c>
       <c r="F58" s="7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G58" s="9">
         <f>IFERROR(E58/(E58+F58),0)</f>
@@ -3141,24 +3141,24 @@
       </c>
       <c r="B59" s="15" t="inlineStr">
         <is>
-          <t>38460</t>
+          <t>38427</t>
         </is>
       </c>
       <c r="C59" s="12" t="inlineStr">
         <is>
-          <t>Santa Monica</t>
+          <t>Plaza Satelite</t>
         </is>
       </c>
       <c r="D59" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E59" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F59" s="11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G59" s="13">
         <f>IFERROR(E59/(E59+F59),0)</f>
@@ -3181,24 +3181,24 @@
       </c>
       <c r="B60" s="17" t="inlineStr">
         <is>
-          <t>38117</t>
+          <t>38811</t>
         </is>
       </c>
       <c r="C60" s="8" t="inlineStr">
         <is>
-          <t>Satelite</t>
+          <t>Plaza Tepeyac</t>
         </is>
       </c>
       <c r="D60" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E60" s="7" t="n">
         <v>1</v>
       </c>
       <c r="F60" s="7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G60" s="9">
         <f>IFERROR(E60/(E60+F60),0)</f>
@@ -3221,24 +3221,24 @@
       </c>
       <c r="B61" s="15" t="inlineStr">
         <is>
-          <t>38442</t>
+          <t>43132</t>
         </is>
       </c>
       <c r="C61" s="12" t="inlineStr">
         <is>
-          <t>Sor Juana</t>
+          <t>Plaza Vista Norte</t>
         </is>
       </c>
       <c r="D61" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E61" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F61" s="11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G61" s="13">
         <f>IFERROR(E61/(E61+F61),0)</f>
@@ -3261,24 +3261,24 @@
       </c>
       <c r="B62" s="17" t="inlineStr">
         <is>
-          <t>38925</t>
+          <t>38136</t>
         </is>
       </c>
       <c r="C62" s="8" t="inlineStr">
         <is>
-          <t>Star Medica Lomas Verdes</t>
+          <t>Punta Norte</t>
         </is>
       </c>
       <c r="D62" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E62" s="7" t="n">
         <v>1</v>
       </c>
       <c r="F62" s="7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G62" s="9">
         <f>IFERROR(E62/(E62+F62),0)</f>
@@ -3301,24 +3301,24 @@
       </c>
       <c r="B63" s="15" t="inlineStr">
         <is>
-          <t>38992</t>
+          <t>43152</t>
         </is>
       </c>
       <c r="C63" s="12" t="inlineStr">
         <is>
-          <t>Tapo Puerta Oriente</t>
+          <t>Samara Satélite</t>
         </is>
       </c>
       <c r="D63" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E63" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F63" s="11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G63" s="13">
         <f>IFERROR(E63/(E63+F63),0)</f>
@@ -3341,24 +3341,24 @@
       </c>
       <c r="B64" s="17" t="inlineStr">
         <is>
-          <t>38411</t>
+          <t>38266</t>
         </is>
       </c>
       <c r="C64" s="8" t="inlineStr">
         <is>
-          <t>Torres Lindavista</t>
+          <t>San Mateo</t>
         </is>
       </c>
       <c r="D64" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E64" s="7" t="n">
         <v>1</v>
       </c>
       <c r="F64" s="7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G64" s="9">
         <f>IFERROR(E64/(E64+F64),0)</f>
@@ -3381,24 +3381,24 @@
       </c>
       <c r="B65" s="15" t="inlineStr">
         <is>
-          <t>43130</t>
+          <t>38460</t>
         </is>
       </c>
       <c r="C65" s="12" t="inlineStr">
         <is>
-          <t>Town Center Nicolás Romero</t>
+          <t>Santa Monica</t>
         </is>
       </c>
       <c r="D65" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E65" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F65" s="11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G65" s="13">
         <f>IFERROR(E65/(E65+F65),0)</f>
@@ -3421,24 +3421,24 @@
       </c>
       <c r="B66" s="17" t="inlineStr">
         <is>
-          <t>38651</t>
+          <t>38117</t>
         </is>
       </c>
       <c r="C66" s="8" t="inlineStr">
         <is>
-          <t>Via Vallejo</t>
+          <t>Satelite</t>
         </is>
       </c>
       <c r="D66" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E66" s="7" t="n">
         <v>1</v>
       </c>
       <c r="F66" s="7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G66" s="9">
         <f>IFERROR(E66/(E66+F66),0)</f>
@@ -3461,12 +3461,12 @@
       </c>
       <c r="B67" s="15" t="inlineStr">
         <is>
-          <t>38694</t>
+          <t>38442</t>
         </is>
       </c>
       <c r="C67" s="12" t="inlineStr">
         <is>
-          <t>Villas de la Hacienda</t>
+          <t>Sor Juana</t>
         </is>
       </c>
       <c r="D67" s="12" t="inlineStr">
@@ -3478,7 +3478,7 @@
         <v>1</v>
       </c>
       <c r="F67" s="11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G67" s="13">
         <f>IFERROR(E67/(E67+F67),0)</f>
@@ -3501,24 +3501,24 @@
       </c>
       <c r="B68" s="17" t="inlineStr">
         <is>
-          <t>38656</t>
+          <t>38925</t>
         </is>
       </c>
       <c r="C68" s="8" t="inlineStr">
         <is>
-          <t>Viveros de la Loma</t>
+          <t>Star Medica Lomas Verdes</t>
         </is>
       </c>
       <c r="D68" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E68" s="7" t="n">
         <v>1</v>
       </c>
       <c r="F68" s="7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G68" s="9">
         <f>IFERROR(E68/(E68+F68),0)</f>
@@ -3541,24 +3541,24 @@
       </c>
       <c r="B69" s="15" t="inlineStr">
         <is>
-          <t>38115</t>
+          <t>38992</t>
         </is>
       </c>
       <c r="C69" s="12" t="inlineStr">
         <is>
-          <t>Zona Azul</t>
+          <t>Tapo Puerta Oriente</t>
         </is>
       </c>
       <c r="D69" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E69" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F69" s="11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G69" s="13">
         <f>IFERROR(E69/(E69+F69),0)</f>
@@ -3581,24 +3581,24 @@
       </c>
       <c r="B70" s="17" t="inlineStr">
         <is>
-          <t>38142</t>
+          <t>38411</t>
         </is>
       </c>
       <c r="C70" s="8" t="inlineStr">
         <is>
-          <t>Zona Esmeralda</t>
+          <t>Torres Lindavista</t>
         </is>
       </c>
       <c r="D70" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E70" s="7" t="n">
         <v>1</v>
       </c>
       <c r="F70" s="7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G70" s="9">
         <f>IFERROR(E70/(E70+F70),0)</f>
@@ -3621,24 +3621,24 @@
       </c>
       <c r="B71" s="15" t="inlineStr">
         <is>
-          <t>38529</t>
+          <t>43130</t>
         </is>
       </c>
       <c r="C71" s="12" t="inlineStr">
         <is>
-          <t>Bosques de Aragon</t>
+          <t>Town Center Nicolás Romero</t>
         </is>
       </c>
       <c r="D71" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E71" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F71" s="11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G71" s="13">
         <f>IFERROR(E71/(E71+F71),0)</f>
@@ -3661,24 +3661,24 @@
       </c>
       <c r="B72" s="17" t="inlineStr">
         <is>
-          <t>38903</t>
+          <t>38651</t>
         </is>
       </c>
       <c r="C72" s="8" t="inlineStr">
         <is>
-          <t>Encuentro Oceania</t>
+          <t>Via Vallejo</t>
         </is>
       </c>
       <c r="D72" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E72" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F72" s="7" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G72" s="9">
         <f>IFERROR(E72/(E72+F72),0)</f>
@@ -3701,24 +3701,24 @@
       </c>
       <c r="B73" s="15" t="inlineStr">
         <is>
-          <t>38995</t>
+          <t>38694</t>
         </is>
       </c>
       <c r="C73" s="12" t="inlineStr">
         <is>
-          <t>Encuentro Oceania II</t>
+          <t>Villas de la Hacienda</t>
         </is>
       </c>
       <c r="D73" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E73" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F73" s="11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G73" s="13">
         <f>IFERROR(E73/(E73+F73),0)</f>
@@ -3741,24 +3741,24 @@
       </c>
       <c r="B74" s="17" t="inlineStr">
         <is>
-          <t>38507</t>
+          <t>38656</t>
         </is>
       </c>
       <c r="C74" s="8" t="inlineStr">
         <is>
-          <t>Espacio Vista del Valle</t>
+          <t>Viveros de la Loma</t>
         </is>
       </c>
       <c r="D74" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E74" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F74" s="7" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G74" s="9">
         <f>IFERROR(E74/(E74+F74),0)</f>
@@ -3781,24 +3781,24 @@
       </c>
       <c r="B75" s="15" t="inlineStr">
         <is>
-          <t>38230</t>
+          <t>38115</t>
         </is>
       </c>
       <c r="C75" s="12" t="inlineStr">
         <is>
-          <t>ITEMS Edo de Mexico</t>
+          <t>Zona Azul</t>
         </is>
       </c>
       <c r="D75" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E75" s="11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F75" s="11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G75" s="13">
         <f>IFERROR(E75/(E75+F75),0)</f>
@@ -3821,24 +3821,24 @@
       </c>
       <c r="B76" s="17" t="inlineStr">
         <is>
-          <t>38792</t>
+          <t>38142</t>
         </is>
       </c>
       <c r="C76" s="8" t="inlineStr">
         <is>
-          <t>Pasaje Tlanepantla</t>
+          <t>Zona Esmeralda</t>
         </is>
       </c>
       <c r="D76" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E76" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F76" s="7" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G76" s="9">
         <f>IFERROR(E76/(E76+F76),0)</f>
@@ -3882,7 +3882,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -3906,7 +3906,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Centro Norte · Corte 31/08/2026 16:00</t>
+          <t>Centro Norte · Corte 31/08/2026 20:06</t>
         </is>
       </c>
     </row>
@@ -4063,14 +4063,14 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>QR - Qualtrics</t>
+          <t>Max &amp; Min</t>
         </is>
       </c>
       <c r="C8" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E8" s="9">
         <f>IFERROR(C8/(C8+D8),0)</f>
@@ -4078,7 +4078,7 @@
       </c>
       <c r="F8" s="8" t="inlineStr">
         <is>
-          <t>03/09/26</t>
+          <t>06/09/26</t>
         </is>
       </c>
       <c r="G8" s="14" t="inlineStr">
@@ -4098,14 +4098,14 @@
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
-          <t>Max &amp; Min</t>
+          <t>Fotografia - SM</t>
         </is>
       </c>
       <c r="C9" s="11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D9" s="11" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E9" s="13">
         <f>IFERROR(C9/(C9+D9),0)</f>
@@ -4133,14 +4133,14 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>Fotografia - SM</t>
+          <t>Mandil Verde</t>
         </is>
       </c>
       <c r="C10" s="7" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E10" s="9">
         <f>IFERROR(C10/(C10+D10),0)</f>
@@ -4148,7 +4148,7 @@
       </c>
       <c r="F10" s="8" t="inlineStr">
         <is>
-          <t>06/09/26</t>
+          <t>13/09/26</t>
         </is>
       </c>
       <c r="G10" s="14" t="inlineStr">
@@ -4168,7 +4168,7 @@
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>Mandil Verde</t>
+          <t>Lay Out</t>
         </is>
       </c>
       <c r="C11" s="11" t="n">
@@ -4183,7 +4183,7 @@
       </c>
       <c r="F11" s="12" t="inlineStr">
         <is>
-          <t>13/09/26</t>
+          <t>06/09/26</t>
         </is>
       </c>
       <c r="G11" s="14" t="inlineStr">
@@ -4203,11 +4203,11 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Lay Out</t>
+          <t>Community Board</t>
         </is>
       </c>
       <c r="C12" s="7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D12" s="7" t="n">
         <v>67</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="F12" s="8" t="inlineStr">
         <is>
-          <t>06/09/26</t>
+          <t>03/09/26</t>
         </is>
       </c>
       <c r="G12" s="14" t="inlineStr">
@@ -4238,14 +4238,14 @@
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>Community Board</t>
+          <t>Activacion PSL Sharpie</t>
         </is>
       </c>
       <c r="C13" s="11" t="n">
-        <v>1</v>
+        <v>72</v>
       </c>
       <c r="D13" s="11" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="E13" s="13">
         <f>IFERROR(C13/(C13+D13),0)</f>
@@ -4253,62 +4253,27 @@
       </c>
       <c r="F13" s="12" t="inlineStr">
         <is>
-          <t>03/09/26</t>
-        </is>
-      </c>
-      <c r="G13" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="H13" s="14" t="inlineStr">
-        <is>
-          <t>Priorizar hoy</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="21" customHeight="1">
-      <c r="A14" s="7" t="n">
-        <v>10</v>
-      </c>
-      <c r="B14" s="8" t="inlineStr">
-        <is>
-          <t>Activacion PSL Sharpie</t>
-        </is>
-      </c>
-      <c r="C14" s="7" t="n">
-        <v>66</v>
-      </c>
-      <c r="D14" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="E14" s="9">
-        <f>IFERROR(C14/(C14+D14),0)</f>
-        <v/>
-      </c>
-      <c r="F14" s="8" t="inlineStr">
-        <is>
           <t>31/08/26</t>
         </is>
       </c>
-      <c r="G14" s="16" t="inlineStr">
+      <c r="G13" s="16" t="inlineStr">
         <is>
           <t>En meta</t>
         </is>
       </c>
-      <c r="H14" s="16" t="inlineStr">
+      <c r="H13" s="16" t="inlineStr">
         <is>
           <t>Mantener estándar</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:H14"/>
+  <autoFilter ref="A4:H13"/>
   <mergeCells count="2">
     <mergeCell ref="A1:H2"/>
     <mergeCell ref="A3:H3"/>
   </mergeCells>
-  <conditionalFormatting sqref="E5:E14">
+  <conditionalFormatting sqref="E5:E13">
     <cfRule type="dataBar" priority="1">
       <dataBar showValue="1">
         <cfvo type="num" val="0"/>

--- a/exports/Resumen_Evidencias_OPS.xlsx
+++ b/exports/Resumen_Evidencias_OPS.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tiendas" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Actividades" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Resumen" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Tiendas" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Actividades" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Resumen'!$A$9:$H$15</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Resumen'!$A$1:$H$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Tiendas'!$A$4:$I$76</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Tiendas'!$1:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Actividades'!$A$4:$H$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Actividades'!$A$4:$H$15</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -615,10 +615,10 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>521</v>
+        <v>663</v>
       </c>
       <c r="E6" s="5">
         <f>IFERROR(A6/(A6+C6),0)</f>
@@ -681,10 +681,10 @@
         <v>10</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>46</v>
+        <v>64</v>
       </c>
       <c r="F10" s="9">
         <f>IFERROR(D10/(D10+E10),0)</f>
@@ -717,7 +717,7 @@
         <v>20</v>
       </c>
       <c r="E11" s="12" t="n">
-        <v>79</v>
+        <v>101</v>
       </c>
       <c r="F11" s="13">
         <f>IFERROR(D11/(D11+E11),0)</f>
@@ -750,7 +750,7 @@
         <v>22</v>
       </c>
       <c r="E12" s="8" t="n">
-        <v>95</v>
+        <v>121</v>
       </c>
       <c r="F12" s="9">
         <f>IFERROR(D12/(D12+E12),0)</f>
@@ -783,7 +783,7 @@
         <v>14</v>
       </c>
       <c r="E13" s="12" t="n">
-        <v>94</v>
+        <v>118</v>
       </c>
       <c r="F13" s="13">
         <f>IFERROR(D13/(D13+E13),0)</f>
@@ -816,7 +816,7 @@
         <v>14</v>
       </c>
       <c r="E14" s="8" t="n">
-        <v>103</v>
+        <v>129</v>
       </c>
       <c r="F14" s="9">
         <f>IFERROR(D14/(D14+E14),0)</f>
@@ -849,7 +849,7 @@
         <v>13</v>
       </c>
       <c r="E15" s="12" t="n">
-        <v>104</v>
+        <v>130</v>
       </c>
       <c r="F15" s="13">
         <f>IFERROR(D15/(D15+E15),0)</f>
@@ -998,7 +998,7 @@
         <v>9</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G5" s="13">
         <f>IFERROR(E5/(E5+F5),0)</f>
@@ -1021,12 +1021,12 @@
       </c>
       <c r="B6" s="17" t="inlineStr">
         <is>
-          <t>38515</t>
+          <t>38862</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>Patio Ecatepec</t>
+          <t>San Miguel Izcalli</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
@@ -1035,10 +1035,10 @@
         </is>
       </c>
       <c r="E6" s="7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G6" s="9">
         <f>IFERROR(E6/(E6+F6),0)</f>
@@ -1061,12 +1061,12 @@
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>38862</t>
+          <t>38515</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>San Miguel Izcalli</t>
+          <t>Patio Ecatepec</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
@@ -1075,10 +1075,10 @@
         </is>
       </c>
       <c r="E7" s="11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G7" s="13">
         <f>IFERROR(E7/(E7+F7),0)</f>
@@ -1118,7 +1118,7 @@
         <v>5</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G8" s="9">
         <f>IFERROR(E8/(E8+F8),0)</f>
@@ -1158,7 +1158,7 @@
         <v>5</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G9" s="13">
         <f>IFERROR(E9/(E9+F9),0)</f>
@@ -1198,7 +1198,7 @@
         <v>5</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G10" s="9">
         <f>IFERROR(E10/(E10+F10),0)</f>
@@ -1238,20 +1238,20 @@
         <v>4</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G11" s="13">
         <f>IFERROR(E11/(E11+F11),0)</f>
         <v/>
       </c>
-      <c r="H11" s="10" t="inlineStr">
-        <is>
-          <t>Seguimiento</t>
-        </is>
-      </c>
-      <c r="I11" s="10" t="inlineStr">
-        <is>
-          <t>Dar seguimiento</t>
+      <c r="H11" s="14" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="I11" s="14" t="inlineStr">
+        <is>
+          <t>Priorizar hoy</t>
         </is>
       </c>
     </row>
@@ -1278,20 +1278,20 @@
         <v>4</v>
       </c>
       <c r="F12" s="7" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G12" s="9">
         <f>IFERROR(E12/(E12+F12),0)</f>
         <v/>
       </c>
-      <c r="H12" s="10" t="inlineStr">
-        <is>
-          <t>Seguimiento</t>
-        </is>
-      </c>
-      <c r="I12" s="10" t="inlineStr">
-        <is>
-          <t>Dar seguimiento</t>
+      <c r="H12" s="14" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="I12" s="14" t="inlineStr">
+        <is>
+          <t>Priorizar hoy</t>
         </is>
       </c>
     </row>
@@ -1318,20 +1318,20 @@
         <v>4</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G13" s="13">
         <f>IFERROR(E13/(E13+F13),0)</f>
         <v/>
       </c>
-      <c r="H13" s="10" t="inlineStr">
-        <is>
-          <t>Seguimiento</t>
-        </is>
-      </c>
-      <c r="I13" s="10" t="inlineStr">
-        <is>
-          <t>Dar seguimiento</t>
+      <c r="H13" s="14" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="I13" s="14" t="inlineStr">
+        <is>
+          <t>Priorizar hoy</t>
         </is>
       </c>
     </row>
@@ -1358,20 +1358,20 @@
         <v>4</v>
       </c>
       <c r="F14" s="7" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G14" s="9">
         <f>IFERROR(E14/(E14+F14),0)</f>
         <v/>
       </c>
-      <c r="H14" s="10" t="inlineStr">
-        <is>
-          <t>Seguimiento</t>
-        </is>
-      </c>
-      <c r="I14" s="10" t="inlineStr">
-        <is>
-          <t>Dar seguimiento</t>
+      <c r="H14" s="14" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="I14" s="14" t="inlineStr">
+        <is>
+          <t>Priorizar hoy</t>
         </is>
       </c>
     </row>
@@ -1398,7 +1398,7 @@
         <v>3</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G15" s="13">
         <f>IFERROR(E15/(E15+F15),0)</f>
@@ -1438,7 +1438,7 @@
         <v>2</v>
       </c>
       <c r="F16" s="7" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G16" s="9">
         <f>IFERROR(E16/(E16+F16),0)</f>
@@ -1478,7 +1478,7 @@
         <v>2</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G17" s="13">
         <f>IFERROR(E17/(E17+F17),0)</f>
@@ -1518,7 +1518,7 @@
         <v>2</v>
       </c>
       <c r="F18" s="7" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G18" s="9">
         <f>IFERROR(E18/(E18+F18),0)</f>
@@ -1558,7 +1558,7 @@
         <v>2</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G19" s="13">
         <f>IFERROR(E19/(E19+F19),0)</f>
@@ -1598,7 +1598,7 @@
         <v>2</v>
       </c>
       <c r="F20" s="7" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G20" s="9">
         <f>IFERROR(E20/(E20+F20),0)</f>
@@ -1638,7 +1638,7 @@
         <v>2</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G21" s="13">
         <f>IFERROR(E21/(E21+F21),0)</f>
@@ -1678,7 +1678,7 @@
         <v>2</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G22" s="9">
         <f>IFERROR(E22/(E22+F22),0)</f>
@@ -1718,7 +1718,7 @@
         <v>2</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G23" s="13">
         <f>IFERROR(E23/(E23+F23),0)</f>
@@ -1758,7 +1758,7 @@
         <v>1</v>
       </c>
       <c r="F24" s="7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G24" s="9">
         <f>IFERROR(E24/(E24+F24),0)</f>
@@ -1798,7 +1798,7 @@
         <v>1</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G25" s="13">
         <f>IFERROR(E25/(E25+F25),0)</f>
@@ -1838,7 +1838,7 @@
         <v>1</v>
       </c>
       <c r="F26" s="7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G26" s="9">
         <f>IFERROR(E26/(E26+F26),0)</f>
@@ -1878,7 +1878,7 @@
         <v>1</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G27" s="13">
         <f>IFERROR(E27/(E27+F27),0)</f>
@@ -1918,7 +1918,7 @@
         <v>1</v>
       </c>
       <c r="F28" s="7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G28" s="9">
         <f>IFERROR(E28/(E28+F28),0)</f>
@@ -1958,7 +1958,7 @@
         <v>1</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G29" s="13">
         <f>IFERROR(E29/(E29+F29),0)</f>
@@ -1998,7 +1998,7 @@
         <v>1</v>
       </c>
       <c r="F30" s="7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G30" s="9">
         <f>IFERROR(E30/(E30+F30),0)</f>
@@ -2038,7 +2038,7 @@
         <v>1</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G31" s="13">
         <f>IFERROR(E31/(E31+F31),0)</f>
@@ -2078,7 +2078,7 @@
         <v>1</v>
       </c>
       <c r="F32" s="7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G32" s="9">
         <f>IFERROR(E32/(E32+F32),0)</f>
@@ -2118,7 +2118,7 @@
         <v>1</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G33" s="13">
         <f>IFERROR(E33/(E33+F33),0)</f>
@@ -2158,7 +2158,7 @@
         <v>1</v>
       </c>
       <c r="F34" s="7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G34" s="9">
         <f>IFERROR(E34/(E34+F34),0)</f>
@@ -2198,7 +2198,7 @@
         <v>1</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G35" s="13">
         <f>IFERROR(E35/(E35+F35),0)</f>
@@ -2238,7 +2238,7 @@
         <v>1</v>
       </c>
       <c r="F36" s="7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G36" s="9">
         <f>IFERROR(E36/(E36+F36),0)</f>
@@ -2278,7 +2278,7 @@
         <v>1</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G37" s="13">
         <f>IFERROR(E37/(E37+F37),0)</f>
@@ -2318,7 +2318,7 @@
         <v>1</v>
       </c>
       <c r="F38" s="7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G38" s="9">
         <f>IFERROR(E38/(E38+F38),0)</f>
@@ -2358,7 +2358,7 @@
         <v>1</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G39" s="13">
         <f>IFERROR(E39/(E39+F39),0)</f>
@@ -2398,7 +2398,7 @@
         <v>1</v>
       </c>
       <c r="F40" s="7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G40" s="9">
         <f>IFERROR(E40/(E40+F40),0)</f>
@@ -2438,7 +2438,7 @@
         <v>1</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G41" s="13">
         <f>IFERROR(E41/(E41+F41),0)</f>
@@ -2478,7 +2478,7 @@
         <v>1</v>
       </c>
       <c r="F42" s="7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G42" s="9">
         <f>IFERROR(E42/(E42+F42),0)</f>
@@ -2518,7 +2518,7 @@
         <v>1</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G43" s="13">
         <f>IFERROR(E43/(E43+F43),0)</f>
@@ -2558,7 +2558,7 @@
         <v>1</v>
       </c>
       <c r="F44" s="7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G44" s="9">
         <f>IFERROR(E44/(E44+F44),0)</f>
@@ -2598,7 +2598,7 @@
         <v>1</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G45" s="13">
         <f>IFERROR(E45/(E45+F45),0)</f>
@@ -2638,7 +2638,7 @@
         <v>1</v>
       </c>
       <c r="F46" s="7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G46" s="9">
         <f>IFERROR(E46/(E46+F46),0)</f>
@@ -2678,7 +2678,7 @@
         <v>1</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G47" s="13">
         <f>IFERROR(E47/(E47+F47),0)</f>
@@ -2718,7 +2718,7 @@
         <v>1</v>
       </c>
       <c r="F48" s="7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G48" s="9">
         <f>IFERROR(E48/(E48+F48),0)</f>
@@ -2758,7 +2758,7 @@
         <v>1</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G49" s="13">
         <f>IFERROR(E49/(E49+F49),0)</f>
@@ -2798,7 +2798,7 @@
         <v>1</v>
       </c>
       <c r="F50" s="7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G50" s="9">
         <f>IFERROR(E50/(E50+F50),0)</f>
@@ -2838,7 +2838,7 @@
         <v>1</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G51" s="13">
         <f>IFERROR(E51/(E51+F51),0)</f>
@@ -2878,7 +2878,7 @@
         <v>1</v>
       </c>
       <c r="F52" s="7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G52" s="9">
         <f>IFERROR(E52/(E52+F52),0)</f>
@@ -2918,7 +2918,7 @@
         <v>1</v>
       </c>
       <c r="F53" s="11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G53" s="13">
         <f>IFERROR(E53/(E53+F53),0)</f>
@@ -2958,7 +2958,7 @@
         <v>1</v>
       </c>
       <c r="F54" s="7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G54" s="9">
         <f>IFERROR(E54/(E54+F54),0)</f>
@@ -2998,7 +2998,7 @@
         <v>1</v>
       </c>
       <c r="F55" s="11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G55" s="13">
         <f>IFERROR(E55/(E55+F55),0)</f>
@@ -3038,7 +3038,7 @@
         <v>1</v>
       </c>
       <c r="F56" s="7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G56" s="9">
         <f>IFERROR(E56/(E56+F56),0)</f>
@@ -3078,7 +3078,7 @@
         <v>1</v>
       </c>
       <c r="F57" s="11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G57" s="13">
         <f>IFERROR(E57/(E57+F57),0)</f>
@@ -3118,7 +3118,7 @@
         <v>1</v>
       </c>
       <c r="F58" s="7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G58" s="9">
         <f>IFERROR(E58/(E58+F58),0)</f>
@@ -3158,7 +3158,7 @@
         <v>1</v>
       </c>
       <c r="F59" s="11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G59" s="13">
         <f>IFERROR(E59/(E59+F59),0)</f>
@@ -3198,7 +3198,7 @@
         <v>1</v>
       </c>
       <c r="F60" s="7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G60" s="9">
         <f>IFERROR(E60/(E60+F60),0)</f>
@@ -3238,7 +3238,7 @@
         <v>1</v>
       </c>
       <c r="F61" s="11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G61" s="13">
         <f>IFERROR(E61/(E61+F61),0)</f>
@@ -3278,7 +3278,7 @@
         <v>1</v>
       </c>
       <c r="F62" s="7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G62" s="9">
         <f>IFERROR(E62/(E62+F62),0)</f>
@@ -3318,7 +3318,7 @@
         <v>1</v>
       </c>
       <c r="F63" s="11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G63" s="13">
         <f>IFERROR(E63/(E63+F63),0)</f>
@@ -3358,7 +3358,7 @@
         <v>1</v>
       </c>
       <c r="F64" s="7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G64" s="9">
         <f>IFERROR(E64/(E64+F64),0)</f>
@@ -3398,7 +3398,7 @@
         <v>1</v>
       </c>
       <c r="F65" s="11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G65" s="13">
         <f>IFERROR(E65/(E65+F65),0)</f>
@@ -3438,7 +3438,7 @@
         <v>1</v>
       </c>
       <c r="F66" s="7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G66" s="9">
         <f>IFERROR(E66/(E66+F66),0)</f>
@@ -3478,7 +3478,7 @@
         <v>1</v>
       </c>
       <c r="F67" s="11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G67" s="13">
         <f>IFERROR(E67/(E67+F67),0)</f>
@@ -3518,7 +3518,7 @@
         <v>1</v>
       </c>
       <c r="F68" s="7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G68" s="9">
         <f>IFERROR(E68/(E68+F68),0)</f>
@@ -3558,7 +3558,7 @@
         <v>1</v>
       </c>
       <c r="F69" s="11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G69" s="13">
         <f>IFERROR(E69/(E69+F69),0)</f>
@@ -3598,7 +3598,7 @@
         <v>1</v>
       </c>
       <c r="F70" s="7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G70" s="9">
         <f>IFERROR(E70/(E70+F70),0)</f>
@@ -3638,7 +3638,7 @@
         <v>1</v>
       </c>
       <c r="F71" s="11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G71" s="13">
         <f>IFERROR(E71/(E71+F71),0)</f>
@@ -3678,7 +3678,7 @@
         <v>1</v>
       </c>
       <c r="F72" s="7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G72" s="9">
         <f>IFERROR(E72/(E72+F72),0)</f>
@@ -3718,7 +3718,7 @@
         <v>1</v>
       </c>
       <c r="F73" s="11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G73" s="13">
         <f>IFERROR(E73/(E73+F73),0)</f>
@@ -3758,7 +3758,7 @@
         <v>1</v>
       </c>
       <c r="F74" s="7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G74" s="9">
         <f>IFERROR(E74/(E74+F74),0)</f>
@@ -3798,7 +3798,7 @@
         <v>1</v>
       </c>
       <c r="F75" s="11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G75" s="13">
         <f>IFERROR(E75/(E75+F75),0)</f>
@@ -3838,7 +3838,7 @@
         <v>1</v>
       </c>
       <c r="F76" s="7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G76" s="9">
         <f>IFERROR(E76/(E76+F76),0)</f>
@@ -3882,7 +3882,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -4267,13 +4267,83 @@
         </is>
       </c>
     </row>
+    <row r="14" ht="21" customHeight="1">
+      <c r="A14" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>Señaletica Back</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" s="7" t="n">
+        <v>71</v>
+      </c>
+      <c r="E14" s="9">
+        <f>IFERROR(C14/(C14+D14),0)</f>
+        <v/>
+      </c>
+      <c r="F14" s="8" t="inlineStr">
+        <is>
+          <t>30/09/26</t>
+        </is>
+      </c>
+      <c r="G14" s="14" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="H14" s="14" t="inlineStr">
+        <is>
+          <t>Priorizar hoy</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="21" customHeight="1">
+      <c r="A15" s="11" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="12" t="inlineStr">
+        <is>
+          <t>Señaletica Lobby</t>
+        </is>
+      </c>
+      <c r="C15" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" s="11" t="n">
+        <v>71</v>
+      </c>
+      <c r="E15" s="13">
+        <f>IFERROR(C15/(C15+D15),0)</f>
+        <v/>
+      </c>
+      <c r="F15" s="12" t="inlineStr">
+        <is>
+          <t>30/09/26</t>
+        </is>
+      </c>
+      <c r="G15" s="14" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="H15" s="14" t="inlineStr">
+        <is>
+          <t>Priorizar hoy</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:H13"/>
+  <autoFilter ref="A4:H15"/>
   <mergeCells count="2">
     <mergeCell ref="A1:H2"/>
     <mergeCell ref="A3:H3"/>
   </mergeCells>
-  <conditionalFormatting sqref="E5:E13">
+  <conditionalFormatting sqref="E5:E15">
     <cfRule type="dataBar" priority="1">
       <dataBar showValue="1">
         <cfvo type="num" val="0"/>

--- a/exports/Resumen_Evidencias_OPS.xlsx
+++ b/exports/Resumen_Evidencias_OPS.xlsx
@@ -592,7 +592,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Centro Norte · Corte 31/08/2026 20:06</t>
+          <t>Centro Norte · Corte 01/09/2026 10:05</t>
         </is>
       </c>
     </row>
@@ -615,10 +615,10 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>127</v>
+        <v>150</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>663</v>
+        <v>639</v>
       </c>
       <c r="E6" s="5">
         <f>IFERROR(A6/(A6+C6),0)</f>
@@ -681,10 +681,10 @@
         <v>10</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="F10" s="9">
         <f>IFERROR(D10/(D10+E10),0)</f>
@@ -714,10 +714,10 @@
         <v>11</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="E11" s="12" t="n">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="F11" s="13">
         <f>IFERROR(D11/(D11+E11),0)</f>
@@ -740,17 +740,17 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela</t>
+          <t>Vanessa Carreño</t>
         </is>
       </c>
       <c r="C12" s="7" t="n">
         <v>13</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="E12" s="8" t="n">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="F12" s="9">
         <f>IFERROR(D12/(D12+E12),0)</f>
@@ -773,17 +773,17 @@
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina</t>
+          <t>Yazmin Chabela</t>
         </is>
       </c>
       <c r="C13" s="11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D13" s="11" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="E13" s="12" t="n">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="F13" s="13">
         <f>IFERROR(D13/(D13+E13),0)</f>
@@ -806,17 +806,17 @@
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño</t>
+          <t>Nancy Carolina</t>
         </is>
       </c>
       <c r="C14" s="7" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E14" s="8" t="n">
-        <v>129</v>
+        <v>117</v>
       </c>
       <c r="F14" s="9">
         <f>IFERROR(D14/(D14+E14),0)</f>
@@ -846,10 +846,10 @@
         <v>13</v>
       </c>
       <c r="D15" s="11" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E15" s="12" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F15" s="13">
         <f>IFERROR(D15/(D15+E15),0)</f>
@@ -924,7 +924,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Centro Norte · Corte 31/08/2026 20:06</t>
+          <t>Centro Norte · Corte 01/09/2026 10:05</t>
         </is>
       </c>
     </row>
@@ -1035,23 +1035,23 @@
         </is>
       </c>
       <c r="E6" s="7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G6" s="9">
         <f>IFERROR(E6/(E6+F6),0)</f>
         <v/>
       </c>
-      <c r="H6" s="10" t="inlineStr">
-        <is>
-          <t>Seguimiento</t>
-        </is>
-      </c>
-      <c r="I6" s="10" t="inlineStr">
-        <is>
-          <t>Dar seguimiento</t>
+      <c r="H6" s="16" t="inlineStr">
+        <is>
+          <t>En meta</t>
+        </is>
+      </c>
+      <c r="I6" s="16" t="inlineStr">
+        <is>
+          <t>Mantener estándar</t>
         </is>
       </c>
     </row>
@@ -1101,12 +1101,12 @@
       </c>
       <c r="B8" s="17" t="inlineStr">
         <is>
-          <t>38894</t>
+          <t>38368</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>Galerias Perinorte</t>
+          <t>Luna Park</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
@@ -1115,10 +1115,10 @@
         </is>
       </c>
       <c r="E8" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="F8" s="7" t="n">
         <v>5</v>
-      </c>
-      <c r="F8" s="7" t="n">
-        <v>6</v>
       </c>
       <c r="G8" s="9">
         <f>IFERROR(E8/(E8+F8),0)</f>
@@ -1141,24 +1141,24 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>38368</t>
+          <t>38561</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>Luna Park</t>
+          <t>Parque Toreo</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E9" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="F9" s="11" t="n">
         <v>5</v>
-      </c>
-      <c r="F9" s="11" t="n">
-        <v>6</v>
       </c>
       <c r="G9" s="13">
         <f>IFERROR(E9/(E9+F9),0)</f>
@@ -1181,17 +1181,17 @@
       </c>
       <c r="B10" s="17" t="inlineStr">
         <is>
-          <t>38561</t>
+          <t>38894</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>Parque Toreo</t>
+          <t>Galerias Perinorte</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E10" s="7" t="n">
@@ -1221,37 +1221,37 @@
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>38695</t>
+          <t>38333</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>Cetram 4 Caminos</t>
+          <t>Izcalli Mega</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E11" s="11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G11" s="13">
         <f>IFERROR(E11/(E11+F11),0)</f>
         <v/>
       </c>
-      <c r="H11" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I11" s="14" t="inlineStr">
-        <is>
-          <t>Priorizar hoy</t>
+      <c r="H11" s="10" t="inlineStr">
+        <is>
+          <t>Seguimiento</t>
+        </is>
+      </c>
+      <c r="I11" s="10" t="inlineStr">
+        <is>
+          <t>Dar seguimiento</t>
         </is>
       </c>
     </row>
@@ -1261,12 +1261,12 @@
       </c>
       <c r="B12" s="17" t="inlineStr">
         <is>
-          <t>38401</t>
+          <t>38339</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Coacalco</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
@@ -1275,23 +1275,23 @@
         </is>
       </c>
       <c r="E12" s="7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F12" s="7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G12" s="9">
         <f>IFERROR(E12/(E12+F12),0)</f>
         <v/>
       </c>
-      <c r="H12" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I12" s="14" t="inlineStr">
-        <is>
-          <t>Priorizar hoy</t>
+      <c r="H12" s="10" t="inlineStr">
+        <is>
+          <t>Seguimiento</t>
+        </is>
+      </c>
+      <c r="I12" s="10" t="inlineStr">
+        <is>
+          <t>Dar seguimiento</t>
         </is>
       </c>
     </row>
@@ -1301,17 +1301,17 @@
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>38333</t>
+          <t>38695</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>Izcalli Mega</t>
+          <t>Cetram 4 Caminos</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E13" s="11" t="n">
@@ -1341,12 +1341,12 @@
       </c>
       <c r="B14" s="17" t="inlineStr">
         <is>
-          <t>38339</t>
+          <t>38401</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Coacalco</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr">
@@ -1381,17 +1381,17 @@
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>38604</t>
+          <t>43194</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>Cosmopol</t>
+          <t>Atana Lindavista</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E15" s="11" t="n">
@@ -1421,12 +1421,12 @@
       </c>
       <c r="B16" s="17" t="inlineStr">
         <is>
-          <t>43193</t>
+          <t>38604</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>Cosmopol N1</t>
+          <t>Cosmopol</t>
         </is>
       </c>
       <c r="D16" s="8" t="inlineStr">
@@ -1435,7 +1435,7 @@
         </is>
       </c>
       <c r="E16" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F16" s="7" t="n">
         <v>8</v>
@@ -1461,21 +1461,21 @@
       </c>
       <c r="B17" s="15" t="inlineStr">
         <is>
-          <t>38456</t>
+          <t>38965</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>Plaza las Flores</t>
+          <t>Parque Tepeyac Piso 2</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E17" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F17" s="11" t="n">
         <v>8</v>
@@ -1501,24 +1501,24 @@
       </c>
       <c r="B18" s="17" t="inlineStr">
         <is>
-          <t>43194</t>
+          <t>43193</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>Atana Lindavista</t>
+          <t>Cosmopol N1</t>
         </is>
       </c>
       <c r="D18" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E18" s="7" t="n">
         <v>2</v>
       </c>
       <c r="F18" s="7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G18" s="9">
         <f>IFERROR(E18/(E18+F18),0)</f>
@@ -1541,24 +1541,24 @@
       </c>
       <c r="B19" s="15" t="inlineStr">
         <is>
-          <t>38924</t>
+          <t>38456</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>Plaza Aeropuerto</t>
+          <t>Plaza las Flores</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E19" s="11" t="n">
         <v>2</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G19" s="13">
         <f>IFERROR(E19/(E19+F19),0)</f>
@@ -1581,17 +1581,17 @@
       </c>
       <c r="B20" s="17" t="inlineStr">
         <is>
-          <t>38859</t>
+          <t>43043</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>Plaza Satelite II N1</t>
+          <t>Atizapan</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E20" s="7" t="n">
@@ -1621,17 +1621,17 @@
       </c>
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t>38475</t>
+          <t>38930</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>Satelite Centro Civico</t>
+          <t>Blvd. Aeropuerto dt</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E21" s="11" t="n">
@@ -1661,17 +1661,17 @@
       </c>
       <c r="B22" s="17" t="inlineStr">
         <is>
-          <t>38606</t>
+          <t>38527</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>TlalnepantlaCarso</t>
+          <t>Camarones</t>
         </is>
       </c>
       <c r="D22" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E22" s="7" t="n">
@@ -1701,17 +1701,17 @@
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>38374</t>
+          <t>38837</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>Valle Dorado</t>
+          <t>Centenario Azcapotzalco</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E23" s="11" t="n">
@@ -1741,24 +1741,24 @@
       </c>
       <c r="B24" s="17" t="inlineStr">
         <is>
-          <t>38186</t>
+          <t>38995</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>Arboledas</t>
+          <t>Encuentro Oceania II</t>
         </is>
       </c>
       <c r="D24" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E24" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F24" s="7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G24" s="9">
         <f>IFERROR(E24/(E24+F24),0)</f>
@@ -1781,24 +1781,24 @@
       </c>
       <c r="B25" s="15" t="inlineStr">
         <is>
-          <t>43043</t>
+          <t>38205</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>Atizapan</t>
+          <t>Lindavista</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E25" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G25" s="13">
         <f>IFERROR(E25/(E25+F25),0)</f>
@@ -1821,24 +1821,24 @@
       </c>
       <c r="B26" s="17" t="inlineStr">
         <is>
-          <t>38149</t>
+          <t>38371</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>Bellavista</t>
+          <t>Montevideo DT</t>
         </is>
       </c>
       <c r="D26" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E26" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F26" s="7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G26" s="9">
         <f>IFERROR(E26/(E26+F26),0)</f>
@@ -1861,24 +1861,24 @@
       </c>
       <c r="B27" s="15" t="inlineStr">
         <is>
-          <t>38930</t>
+          <t>43111</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>Blvd. Aeropuerto dt</t>
+          <t>Montevideo Insurgentes</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E27" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G27" s="13">
         <f>IFERROR(E27/(E27+F27),0)</f>
@@ -1901,24 +1901,24 @@
       </c>
       <c r="B28" s="17" t="inlineStr">
         <is>
-          <t>38529</t>
+          <t>38674</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>Bosques de Aragon</t>
+          <t>Mundo E</t>
         </is>
       </c>
       <c r="D28" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E28" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F28" s="7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G28" s="9">
         <f>IFERROR(E28/(E28+F28),0)</f>
@@ -1941,12 +1941,12 @@
       </c>
       <c r="B29" s="15" t="inlineStr">
         <is>
-          <t>38527</t>
+          <t>43195</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>Camarones</t>
+          <t>Parque Jadin kiosko</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr">
@@ -1955,10 +1955,10 @@
         </is>
       </c>
       <c r="E29" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G29" s="13">
         <f>IFERROR(E29/(E29+F29),0)</f>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="B30" s="17" t="inlineStr">
         <is>
-          <t>38837</t>
+          <t>38546</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>Centenario Azcapotzalco</t>
+          <t>Patio Claveria</t>
         </is>
       </c>
       <c r="D30" s="8" t="inlineStr">
@@ -1995,10 +1995,10 @@
         </is>
       </c>
       <c r="E30" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F30" s="7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G30" s="9">
         <f>IFERROR(E30/(E30+F30),0)</f>
@@ -2021,24 +2021,24 @@
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>38394</t>
+          <t>38677</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>Centro Comercial Lomas Verdes</t>
+          <t>Patio la Raza</t>
         </is>
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E31" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G31" s="13">
         <f>IFERROR(E31/(E31+F31),0)</f>
@@ -2061,24 +2061,24 @@
       </c>
       <c r="B32" s="17" t="inlineStr">
         <is>
-          <t>38535</t>
+          <t>38924</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>City Center Esmeralda</t>
+          <t>Plaza Aeropuerto</t>
         </is>
       </c>
       <c r="D32" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E32" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F32" s="7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G32" s="9">
         <f>IFERROR(E32/(E32+F32),0)</f>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="B33" s="15" t="inlineStr">
         <is>
-          <t>38197</t>
+          <t>38859</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>Echegaray</t>
+          <t>Plaza Satelite II N1</t>
         </is>
       </c>
       <c r="D33" s="12" t="inlineStr">
@@ -2115,10 +2115,10 @@
         </is>
       </c>
       <c r="E33" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G33" s="13">
         <f>IFERROR(E33/(E33+F33),0)</f>
@@ -2141,24 +2141,24 @@
       </c>
       <c r="B34" s="17" t="inlineStr">
         <is>
-          <t>38431</t>
+          <t>43132</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>Eduardo Molina</t>
+          <t>Plaza Vista Norte</t>
         </is>
       </c>
       <c r="D34" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E34" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F34" s="7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G34" s="9">
         <f>IFERROR(E34/(E34+F34),0)</f>
@@ -2181,12 +2181,12 @@
       </c>
       <c r="B35" s="15" t="inlineStr">
         <is>
-          <t>38458</t>
+          <t>38475</t>
         </is>
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>El Rosario</t>
+          <t>Satelite Centro Civico</t>
         </is>
       </c>
       <c r="D35" s="12" t="inlineStr">
@@ -2195,10 +2195,10 @@
         </is>
       </c>
       <c r="E35" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G35" s="13">
         <f>IFERROR(E35/(E35+F35),0)</f>
@@ -2221,24 +2221,24 @@
       </c>
       <c r="B36" s="17" t="inlineStr">
         <is>
-          <t>38903</t>
+          <t>38606</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>Encuentro Oceania</t>
+          <t>TlalnepantlaCarso</t>
         </is>
       </c>
       <c r="D36" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E36" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F36" s="7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G36" s="9">
         <f>IFERROR(E36/(E36+F36),0)</f>
@@ -2261,24 +2261,24 @@
       </c>
       <c r="B37" s="15" t="inlineStr">
         <is>
-          <t>38995</t>
+          <t>38411</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>Encuentro Oceania II</t>
+          <t>Torres Lindavista</t>
         </is>
       </c>
       <c r="D37" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E37" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G37" s="13">
         <f>IFERROR(E37/(E37+F37),0)</f>
@@ -2301,24 +2301,24 @@
       </c>
       <c r="B38" s="17" t="inlineStr">
         <is>
-          <t>38507</t>
+          <t>38374</t>
         </is>
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>Espacio Vista del Valle</t>
+          <t>Valle Dorado</t>
         </is>
       </c>
       <c r="D38" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E38" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F38" s="7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G38" s="9">
         <f>IFERROR(E38/(E38+F38),0)</f>
@@ -2341,24 +2341,24 @@
       </c>
       <c r="B39" s="15" t="inlineStr">
         <is>
-          <t>38363</t>
+          <t>38651</t>
         </is>
       </c>
       <c r="C39" s="12" t="inlineStr">
         <is>
-          <t>Galerias Atizapan</t>
+          <t>Via Vallejo</t>
         </is>
       </c>
       <c r="D39" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E39" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G39" s="13">
         <f>IFERROR(E39/(E39+F39),0)</f>
@@ -2381,24 +2381,24 @@
       </c>
       <c r="B40" s="17" t="inlineStr">
         <is>
-          <t>38770</t>
+          <t>38207</t>
         </is>
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>Gustavo Baz 29</t>
+          <t>Lindavista II</t>
         </is>
       </c>
       <c r="D40" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E40" s="7" t="n">
         <v>1</v>
       </c>
       <c r="F40" s="7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G40" s="9">
         <f>IFERROR(E40/(E40+F40),0)</f>
@@ -2421,12 +2421,12 @@
       </c>
       <c r="B41" s="15" t="inlineStr">
         <is>
-          <t>38230</t>
+          <t>38186</t>
         </is>
       </c>
       <c r="C41" s="12" t="inlineStr">
         <is>
-          <t>ITEMS Edo de Mexico</t>
+          <t>Arboledas</t>
         </is>
       </c>
       <c r="D41" s="12" t="inlineStr">
@@ -2461,17 +2461,17 @@
       </c>
       <c r="B42" s="17" t="inlineStr">
         <is>
-          <t>38661</t>
+          <t>38149</t>
         </is>
       </c>
       <c r="C42" s="8" t="inlineStr">
         <is>
-          <t>Jinetes</t>
+          <t>Bellavista</t>
         </is>
       </c>
       <c r="D42" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E42" s="7" t="n">
@@ -2501,17 +2501,17 @@
       </c>
       <c r="B43" s="15" t="inlineStr">
         <is>
-          <t>38205</t>
+          <t>38529</t>
         </is>
       </c>
       <c r="C43" s="12" t="inlineStr">
         <is>
-          <t>Lindavista</t>
+          <t>Bosques de Aragon</t>
         </is>
       </c>
       <c r="D43" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E43" s="11" t="n">
@@ -2541,17 +2541,17 @@
       </c>
       <c r="B44" s="17" t="inlineStr">
         <is>
-          <t>38207</t>
+          <t>38394</t>
         </is>
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t>Lindavista II</t>
+          <t>Centro Comercial Lomas Verdes</t>
         </is>
       </c>
       <c r="D44" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E44" s="7" t="n">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="B45" s="15" t="inlineStr">
         <is>
-          <t>38119</t>
+          <t>38535</t>
         </is>
       </c>
       <c r="C45" s="12" t="inlineStr">
         <is>
-          <t>Lomas Verdes</t>
+          <t>City Center Esmeralda</t>
         </is>
       </c>
       <c r="D45" s="12" t="inlineStr">
@@ -2621,17 +2621,17 @@
       </c>
       <c r="B46" s="17" t="inlineStr">
         <is>
-          <t>38270</t>
+          <t>38197</t>
         </is>
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t>Lomas Verdes II</t>
+          <t>Echegaray</t>
         </is>
       </c>
       <c r="D46" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E46" s="7" t="n">
@@ -2661,17 +2661,17 @@
       </c>
       <c r="B47" s="15" t="inlineStr">
         <is>
-          <t>38371</t>
+          <t>38431</t>
         </is>
       </c>
       <c r="C47" s="12" t="inlineStr">
         <is>
-          <t>Montevideo DT</t>
+          <t>Eduardo Molina</t>
         </is>
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E47" s="11" t="n">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="B48" s="17" t="inlineStr">
         <is>
-          <t>43111</t>
+          <t>38458</t>
         </is>
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
-          <t>Montevideo Insurgentes</t>
+          <t>El Rosario</t>
         </is>
       </c>
       <c r="D48" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E48" s="7" t="n">
@@ -2741,17 +2741,17 @@
       </c>
       <c r="B49" s="15" t="inlineStr">
         <is>
-          <t>38674</t>
+          <t>38903</t>
         </is>
       </c>
       <c r="C49" s="12" t="inlineStr">
         <is>
-          <t>Mundo E</t>
+          <t>Encuentro Oceania</t>
         </is>
       </c>
       <c r="D49" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E49" s="11" t="n">
@@ -2781,17 +2781,17 @@
       </c>
       <c r="B50" s="17" t="inlineStr">
         <is>
-          <t>38845</t>
+          <t>38507</t>
         </is>
       </c>
       <c r="C50" s="8" t="inlineStr">
         <is>
-          <t>Mundo E II</t>
+          <t>Espacio Vista del Valle</t>
         </is>
       </c>
       <c r="D50" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E50" s="7" t="n">
@@ -2821,17 +2821,17 @@
       </c>
       <c r="B51" s="15" t="inlineStr">
         <is>
-          <t>43195</t>
+          <t>38363</t>
         </is>
       </c>
       <c r="C51" s="12" t="inlineStr">
         <is>
-          <t>Parque Jadin kiosko</t>
+          <t>Galerias Atizapan</t>
         </is>
       </c>
       <c r="D51" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E51" s="11" t="n">
@@ -2861,17 +2861,17 @@
       </c>
       <c r="B52" s="17" t="inlineStr">
         <is>
-          <t>38937</t>
+          <t>38770</t>
         </is>
       </c>
       <c r="C52" s="8" t="inlineStr">
         <is>
-          <t>Parque Tepeyac Piso 1</t>
+          <t>Gustavo Baz 29</t>
         </is>
       </c>
       <c r="D52" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E52" s="7" t="n">
@@ -2901,17 +2901,17 @@
       </c>
       <c r="B53" s="15" t="inlineStr">
         <is>
-          <t>38965</t>
+          <t>38230</t>
         </is>
       </c>
       <c r="C53" s="12" t="inlineStr">
         <is>
-          <t>Parque Tepeyac Piso 2</t>
+          <t>ITEMS Edo de Mexico</t>
         </is>
       </c>
       <c r="D53" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E53" s="11" t="n">
@@ -2941,17 +2941,17 @@
       </c>
       <c r="B54" s="17" t="inlineStr">
         <is>
-          <t>38590</t>
+          <t>38661</t>
         </is>
       </c>
       <c r="C54" s="8" t="inlineStr">
         <is>
-          <t>Parque Toreo II</t>
+          <t>Jinetes</t>
         </is>
       </c>
       <c r="D54" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E54" s="7" t="n">
@@ -2981,17 +2981,17 @@
       </c>
       <c r="B55" s="15" t="inlineStr">
         <is>
-          <t>38792</t>
+          <t>38119</t>
         </is>
       </c>
       <c r="C55" s="12" t="inlineStr">
         <is>
-          <t>Pasaje Tlanepantla</t>
+          <t>Lomas Verdes</t>
         </is>
       </c>
       <c r="D55" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E55" s="11" t="n">
@@ -3021,17 +3021,17 @@
       </c>
       <c r="B56" s="17" t="inlineStr">
         <is>
-          <t>38546</t>
+          <t>38270</t>
         </is>
       </c>
       <c r="C56" s="8" t="inlineStr">
         <is>
-          <t>Patio Claveria</t>
+          <t>Lomas Verdes II</t>
         </is>
       </c>
       <c r="D56" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E56" s="7" t="n">
@@ -3061,17 +3061,17 @@
       </c>
       <c r="B57" s="15" t="inlineStr">
         <is>
-          <t>38677</t>
+          <t>38845</t>
         </is>
       </c>
       <c r="C57" s="12" t="inlineStr">
         <is>
-          <t>Patio la Raza</t>
+          <t>Mundo E II</t>
         </is>
       </c>
       <c r="D57" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E57" s="11" t="n">
@@ -3101,17 +3101,17 @@
       </c>
       <c r="B58" s="17" t="inlineStr">
         <is>
-          <t>38176</t>
+          <t>38937</t>
         </is>
       </c>
       <c r="C58" s="8" t="inlineStr">
         <is>
-          <t>Periferico Satélite DT</t>
+          <t>Parque Tepeyac Piso 1</t>
         </is>
       </c>
       <c r="D58" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E58" s="7" t="n">
@@ -3141,12 +3141,12 @@
       </c>
       <c r="B59" s="15" t="inlineStr">
         <is>
-          <t>38427</t>
+          <t>38590</t>
         </is>
       </c>
       <c r="C59" s="12" t="inlineStr">
         <is>
-          <t>Plaza Satelite</t>
+          <t>Parque Toreo II</t>
         </is>
       </c>
       <c r="D59" s="12" t="inlineStr">
@@ -3181,17 +3181,17 @@
       </c>
       <c r="B60" s="17" t="inlineStr">
         <is>
-          <t>38811</t>
+          <t>38792</t>
         </is>
       </c>
       <c r="C60" s="8" t="inlineStr">
         <is>
-          <t>Plaza Tepeyac</t>
+          <t>Pasaje Tlanepantla</t>
         </is>
       </c>
       <c r="D60" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E60" s="7" t="n">
@@ -3221,17 +3221,17 @@
       </c>
       <c r="B61" s="15" t="inlineStr">
         <is>
-          <t>43132</t>
+          <t>38176</t>
         </is>
       </c>
       <c r="C61" s="12" t="inlineStr">
         <is>
-          <t>Plaza Vista Norte</t>
+          <t>Periferico Satélite DT</t>
         </is>
       </c>
       <c r="D61" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E61" s="11" t="n">
@@ -3261,17 +3261,17 @@
       </c>
       <c r="B62" s="17" t="inlineStr">
         <is>
-          <t>38136</t>
+          <t>38427</t>
         </is>
       </c>
       <c r="C62" s="8" t="inlineStr">
         <is>
-          <t>Punta Norte</t>
+          <t>Plaza Satelite</t>
         </is>
       </c>
       <c r="D62" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E62" s="7" t="n">
@@ -3301,17 +3301,17 @@
       </c>
       <c r="B63" s="15" t="inlineStr">
         <is>
-          <t>43152</t>
+          <t>38811</t>
         </is>
       </c>
       <c r="C63" s="12" t="inlineStr">
         <is>
-          <t>Samara Satélite</t>
+          <t>Plaza Tepeyac</t>
         </is>
       </c>
       <c r="D63" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E63" s="11" t="n">
@@ -3341,17 +3341,17 @@
       </c>
       <c r="B64" s="17" t="inlineStr">
         <is>
-          <t>38266</t>
+          <t>38136</t>
         </is>
       </c>
       <c r="C64" s="8" t="inlineStr">
         <is>
-          <t>San Mateo</t>
+          <t>Punta Norte</t>
         </is>
       </c>
       <c r="D64" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E64" s="7" t="n">
@@ -3381,17 +3381,17 @@
       </c>
       <c r="B65" s="15" t="inlineStr">
         <is>
-          <t>38460</t>
+          <t>43152</t>
         </is>
       </c>
       <c r="C65" s="12" t="inlineStr">
         <is>
-          <t>Santa Monica</t>
+          <t>Samara Satélite</t>
         </is>
       </c>
       <c r="D65" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E65" s="11" t="n">
@@ -3421,17 +3421,17 @@
       </c>
       <c r="B66" s="17" t="inlineStr">
         <is>
-          <t>38117</t>
+          <t>38266</t>
         </is>
       </c>
       <c r="C66" s="8" t="inlineStr">
         <is>
-          <t>Satelite</t>
+          <t>San Mateo</t>
         </is>
       </c>
       <c r="D66" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E66" s="7" t="n">
@@ -3461,12 +3461,12 @@
       </c>
       <c r="B67" s="15" t="inlineStr">
         <is>
-          <t>38442</t>
+          <t>38460</t>
         </is>
       </c>
       <c r="C67" s="12" t="inlineStr">
         <is>
-          <t>Sor Juana</t>
+          <t>Santa Monica</t>
         </is>
       </c>
       <c r="D67" s="12" t="inlineStr">
@@ -3501,17 +3501,17 @@
       </c>
       <c r="B68" s="17" t="inlineStr">
         <is>
-          <t>38925</t>
+          <t>38117</t>
         </is>
       </c>
       <c r="C68" s="8" t="inlineStr">
         <is>
-          <t>Star Medica Lomas Verdes</t>
+          <t>Satelite</t>
         </is>
       </c>
       <c r="D68" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E68" s="7" t="n">
@@ -3541,17 +3541,17 @@
       </c>
       <c r="B69" s="15" t="inlineStr">
         <is>
-          <t>38992</t>
+          <t>38442</t>
         </is>
       </c>
       <c r="C69" s="12" t="inlineStr">
         <is>
-          <t>Tapo Puerta Oriente</t>
+          <t>Sor Juana</t>
         </is>
       </c>
       <c r="D69" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E69" s="11" t="n">
@@ -3581,17 +3581,17 @@
       </c>
       <c r="B70" s="17" t="inlineStr">
         <is>
-          <t>38411</t>
+          <t>38925</t>
         </is>
       </c>
       <c r="C70" s="8" t="inlineStr">
         <is>
-          <t>Torres Lindavista</t>
+          <t>Star Medica Lomas Verdes</t>
         </is>
       </c>
       <c r="D70" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E70" s="7" t="n">
@@ -3621,17 +3621,17 @@
       </c>
       <c r="B71" s="15" t="inlineStr">
         <is>
-          <t>43130</t>
+          <t>38992</t>
         </is>
       </c>
       <c r="C71" s="12" t="inlineStr">
         <is>
-          <t>Town Center Nicolás Romero</t>
+          <t>Tapo Puerta Oriente</t>
         </is>
       </c>
       <c r="D71" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E71" s="11" t="n">
@@ -3661,17 +3661,17 @@
       </c>
       <c r="B72" s="17" t="inlineStr">
         <is>
-          <t>38651</t>
+          <t>43130</t>
         </is>
       </c>
       <c r="C72" s="8" t="inlineStr">
         <is>
-          <t>Via Vallejo</t>
+          <t>Town Center Nicolás Romero</t>
         </is>
       </c>
       <c r="D72" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E72" s="7" t="n">
@@ -3906,7 +3906,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Centro Norte · Corte 31/08/2026 20:06</t>
+          <t>Centro Norte · Corte 01/09/2026 10:05</t>
         </is>
       </c>
     </row>
@@ -3997,10 +3997,10 @@
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="D6" s="7" t="n">
-        <v>68</v>
+        <v>47</v>
       </c>
       <c r="E6" s="9">
         <f>IFERROR(C6/(C6+D6),0)</f>
@@ -4172,10 +4172,10 @@
         </is>
       </c>
       <c r="C11" s="11" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E11" s="13">
         <f>IFERROR(C11/(C11+D11),0)</f>
@@ -4207,10 +4207,10 @@
         </is>
       </c>
       <c r="C12" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E12" s="9">
         <f>IFERROR(C12/(C12+D12),0)</f>

--- a/exports/Resumen_Evidencias_OPS.xlsx
+++ b/exports/Resumen_Evidencias_OPS.xlsx
@@ -592,7 +592,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Centro Norte · Corte 01/09/2026 10:05</t>
+          <t>Centro Norte · Corte 01/09/2026 13:22</t>
         </is>
       </c>
     </row>
@@ -615,10 +615,10 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>150</v>
+        <v>169</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>639</v>
+        <v>620</v>
       </c>
       <c r="E6" s="5">
         <f>IFERROR(A6/(A6+C6),0)</f>
@@ -681,10 +681,10 @@
         <v>10</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F10" s="9">
         <f>IFERROR(D10/(D10+E10),0)</f>
@@ -714,10 +714,10 @@
         <v>11</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E11" s="12" t="n">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="F11" s="13">
         <f>IFERROR(D11/(D11+E11),0)</f>
@@ -773,17 +773,17 @@
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela</t>
+          <t>Nancy Carolina</t>
         </is>
       </c>
       <c r="C13" s="11" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D13" s="11" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E13" s="12" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="F13" s="13">
         <f>IFERROR(D13/(D13+E13),0)</f>
@@ -806,17 +806,17 @@
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina</t>
+          <t>Yazmin Chabela</t>
         </is>
       </c>
       <c r="C14" s="7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="E14" s="8" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="F14" s="9">
         <f>IFERROR(D14/(D14+E14),0)</f>
@@ -846,10 +846,10 @@
         <v>13</v>
       </c>
       <c r="D15" s="11" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="E15" s="12" t="n">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="F15" s="13">
         <f>IFERROR(D15/(D15+E15),0)</f>
@@ -924,7 +924,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Centro Norte · Corte 01/09/2026 10:05</t>
+          <t>Centro Norte · Corte 01/09/2026 13:22</t>
         </is>
       </c>
     </row>
@@ -981,24 +981,24 @@
       </c>
       <c r="B5" s="15" t="inlineStr">
         <is>
-          <t>38719</t>
+          <t>38862</t>
         </is>
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>Plaza Fortuna</t>
+          <t>San Miguel Izcalli</t>
         </is>
       </c>
       <c r="D5" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E5" s="11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G5" s="13">
         <f>IFERROR(E5/(E5+F5),0)</f>
@@ -1021,17 +1021,17 @@
       </c>
       <c r="B6" s="17" t="inlineStr">
         <is>
-          <t>38862</t>
+          <t>38719</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>San Miguel Izcalli</t>
+          <t>Plaza Fortuna</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E6" s="7" t="n">
@@ -1501,21 +1501,21 @@
       </c>
       <c r="B18" s="17" t="inlineStr">
         <is>
-          <t>43193</t>
+          <t>38924</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>Cosmopol N1</t>
+          <t>Plaza Aeropuerto</t>
         </is>
       </c>
       <c r="D18" s="8" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E18" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F18" s="7" t="n">
         <v>8</v>
@@ -1541,21 +1541,21 @@
       </c>
       <c r="B19" s="15" t="inlineStr">
         <is>
-          <t>38456</t>
+          <t>38606</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>Plaza las Flores</t>
+          <t>TlalnepantlaCarso</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E19" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F19" s="11" t="n">
         <v>8</v>
@@ -1581,24 +1581,24 @@
       </c>
       <c r="B20" s="17" t="inlineStr">
         <is>
-          <t>43043</t>
+          <t>43193</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>Atizapan</t>
+          <t>Cosmopol N1</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E20" s="7" t="n">
         <v>2</v>
       </c>
       <c r="F20" s="7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G20" s="9">
         <f>IFERROR(E20/(E20+F20),0)</f>
@@ -1621,24 +1621,24 @@
       </c>
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t>38930</t>
+          <t>38456</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>Blvd. Aeropuerto dt</t>
+          <t>Plaza las Flores</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E21" s="11" t="n">
         <v>2</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G21" s="13">
         <f>IFERROR(E21/(E21+F21),0)</f>
@@ -1661,17 +1661,17 @@
       </c>
       <c r="B22" s="17" t="inlineStr">
         <is>
-          <t>38527</t>
+          <t>38186</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>Camarones</t>
+          <t>Arboledas</t>
         </is>
       </c>
       <c r="D22" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E22" s="7" t="n">
@@ -1701,17 +1701,17 @@
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>38837</t>
+          <t>43043</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>Centenario Azcapotzalco</t>
+          <t>Atizapan</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E23" s="11" t="n">
@@ -1741,17 +1741,17 @@
       </c>
       <c r="B24" s="17" t="inlineStr">
         <is>
-          <t>38995</t>
+          <t>38149</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>Encuentro Oceania II</t>
+          <t>Bellavista</t>
         </is>
       </c>
       <c r="D24" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E24" s="7" t="n">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="B25" s="15" t="inlineStr">
         <is>
-          <t>38205</t>
+          <t>38930</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>Lindavista</t>
+          <t>Blvd. Aeropuerto dt</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E25" s="11" t="n">
@@ -1821,17 +1821,17 @@
       </c>
       <c r="B26" s="17" t="inlineStr">
         <is>
-          <t>38371</t>
+          <t>38529</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>Montevideo DT</t>
+          <t>Bosques de Aragon</t>
         </is>
       </c>
       <c r="D26" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E26" s="7" t="n">
@@ -1861,12 +1861,12 @@
       </c>
       <c r="B27" s="15" t="inlineStr">
         <is>
-          <t>43111</t>
+          <t>38527</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>Montevideo Insurgentes</t>
+          <t>Camarones</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
@@ -1901,17 +1901,17 @@
       </c>
       <c r="B28" s="17" t="inlineStr">
         <is>
-          <t>38674</t>
+          <t>38837</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>Mundo E</t>
+          <t>Centenario Azcapotzalco</t>
         </is>
       </c>
       <c r="D28" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E28" s="7" t="n">
@@ -1941,17 +1941,17 @@
       </c>
       <c r="B29" s="15" t="inlineStr">
         <is>
-          <t>43195</t>
+          <t>38394</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>Parque Jadin kiosko</t>
+          <t>Centro Comercial Lomas Verdes</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E29" s="11" t="n">
@@ -1981,17 +1981,17 @@
       </c>
       <c r="B30" s="17" t="inlineStr">
         <is>
-          <t>38546</t>
+          <t>38535</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>Patio Claveria</t>
+          <t>City Center Esmeralda</t>
         </is>
       </c>
       <c r="D30" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E30" s="7" t="n">
@@ -2021,17 +2021,17 @@
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>38677</t>
+          <t>38431</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>Patio la Raza</t>
+          <t>Eduardo Molina</t>
         </is>
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E31" s="11" t="n">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="B32" s="17" t="inlineStr">
         <is>
-          <t>38924</t>
+          <t>38995</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>Plaza Aeropuerto</t>
+          <t>Encuentro Oceania II</t>
         </is>
       </c>
       <c r="D32" s="8" t="inlineStr">
@@ -2101,17 +2101,17 @@
       </c>
       <c r="B33" s="15" t="inlineStr">
         <is>
-          <t>38859</t>
+          <t>38507</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>Plaza Satelite II N1</t>
+          <t>Espacio Vista del Valle</t>
         </is>
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E33" s="11" t="n">
@@ -2141,17 +2141,17 @@
       </c>
       <c r="B34" s="17" t="inlineStr">
         <is>
-          <t>43132</t>
+          <t>38363</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>Plaza Vista Norte</t>
+          <t>Galerias Atizapan</t>
         </is>
       </c>
       <c r="D34" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E34" s="7" t="n">
@@ -2181,17 +2181,17 @@
       </c>
       <c r="B35" s="15" t="inlineStr">
         <is>
-          <t>38475</t>
+          <t>38661</t>
         </is>
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>Satelite Centro Civico</t>
+          <t>Jinetes</t>
         </is>
       </c>
       <c r="D35" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E35" s="11" t="n">
@@ -2221,17 +2221,17 @@
       </c>
       <c r="B36" s="17" t="inlineStr">
         <is>
-          <t>38606</t>
+          <t>38205</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>TlalnepantlaCarso</t>
+          <t>Lindavista</t>
         </is>
       </c>
       <c r="D36" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E36" s="7" t="n">
@@ -2261,12 +2261,12 @@
       </c>
       <c r="B37" s="15" t="inlineStr">
         <is>
-          <t>38411</t>
+          <t>38371</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>Torres Lindavista</t>
+          <t>Montevideo DT</t>
         </is>
       </c>
       <c r="D37" s="12" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="B38" s="17" t="inlineStr">
         <is>
-          <t>38374</t>
+          <t>43111</t>
         </is>
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>Valle Dorado</t>
+          <t>Montevideo Insurgentes</t>
         </is>
       </c>
       <c r="D38" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E38" s="7" t="n">
@@ -2341,17 +2341,17 @@
       </c>
       <c r="B39" s="15" t="inlineStr">
         <is>
-          <t>38651</t>
+          <t>38674</t>
         </is>
       </c>
       <c r="C39" s="12" t="inlineStr">
         <is>
-          <t>Via Vallejo</t>
+          <t>Mundo E</t>
         </is>
       </c>
       <c r="D39" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E39" s="11" t="n">
@@ -2381,12 +2381,12 @@
       </c>
       <c r="B40" s="17" t="inlineStr">
         <is>
-          <t>38207</t>
+          <t>43195</t>
         </is>
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>Lindavista II</t>
+          <t>Parque Jadin kiosko</t>
         </is>
       </c>
       <c r="D40" s="8" t="inlineStr">
@@ -2395,7 +2395,7 @@
         </is>
       </c>
       <c r="E40" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F40" s="7" t="n">
         <v>9</v>
@@ -2421,12 +2421,12 @@
       </c>
       <c r="B41" s="15" t="inlineStr">
         <is>
-          <t>38186</t>
+          <t>38792</t>
         </is>
       </c>
       <c r="C41" s="12" t="inlineStr">
         <is>
-          <t>Arboledas</t>
+          <t>Pasaje Tlanepantla</t>
         </is>
       </c>
       <c r="D41" s="12" t="inlineStr">
@@ -2435,10 +2435,10 @@
         </is>
       </c>
       <c r="E41" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G41" s="13">
         <f>IFERROR(E41/(E41+F41),0)</f>
@@ -2461,24 +2461,24 @@
       </c>
       <c r="B42" s="17" t="inlineStr">
         <is>
-          <t>38149</t>
+          <t>38546</t>
         </is>
       </c>
       <c r="C42" s="8" t="inlineStr">
         <is>
-          <t>Bellavista</t>
+          <t>Patio Claveria</t>
         </is>
       </c>
       <c r="D42" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E42" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F42" s="7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G42" s="9">
         <f>IFERROR(E42/(E42+F42),0)</f>
@@ -2501,24 +2501,24 @@
       </c>
       <c r="B43" s="15" t="inlineStr">
         <is>
-          <t>38529</t>
+          <t>38677</t>
         </is>
       </c>
       <c r="C43" s="12" t="inlineStr">
         <is>
-          <t>Bosques de Aragon</t>
+          <t>Patio la Raza</t>
         </is>
       </c>
       <c r="D43" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E43" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G43" s="13">
         <f>IFERROR(E43/(E43+F43),0)</f>
@@ -2541,24 +2541,24 @@
       </c>
       <c r="B44" s="17" t="inlineStr">
         <is>
-          <t>38394</t>
+          <t>38859</t>
         </is>
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t>Centro Comercial Lomas Verdes</t>
+          <t>Plaza Satelite II N1</t>
         </is>
       </c>
       <c r="D44" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E44" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F44" s="7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G44" s="9">
         <f>IFERROR(E44/(E44+F44),0)</f>
@@ -2581,24 +2581,24 @@
       </c>
       <c r="B45" s="15" t="inlineStr">
         <is>
-          <t>38535</t>
+          <t>38811</t>
         </is>
       </c>
       <c r="C45" s="12" t="inlineStr">
         <is>
-          <t>City Center Esmeralda</t>
+          <t>Plaza Tepeyac</t>
         </is>
       </c>
       <c r="D45" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E45" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G45" s="13">
         <f>IFERROR(E45/(E45+F45),0)</f>
@@ -2621,24 +2621,24 @@
       </c>
       <c r="B46" s="17" t="inlineStr">
         <is>
-          <t>38197</t>
+          <t>43132</t>
         </is>
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t>Echegaray</t>
+          <t>Plaza Vista Norte</t>
         </is>
       </c>
       <c r="D46" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E46" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F46" s="7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G46" s="9">
         <f>IFERROR(E46/(E46+F46),0)</f>
@@ -2661,24 +2661,24 @@
       </c>
       <c r="B47" s="15" t="inlineStr">
         <is>
-          <t>38431</t>
+          <t>38136</t>
         </is>
       </c>
       <c r="C47" s="12" t="inlineStr">
         <is>
-          <t>Eduardo Molina</t>
+          <t>Punta Norte</t>
         </is>
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E47" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G47" s="13">
         <f>IFERROR(E47/(E47+F47),0)</f>
@@ -2701,24 +2701,24 @@
       </c>
       <c r="B48" s="17" t="inlineStr">
         <is>
-          <t>38458</t>
+          <t>38460</t>
         </is>
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
-          <t>El Rosario</t>
+          <t>Santa Monica</t>
         </is>
       </c>
       <c r="D48" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E48" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F48" s="7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G48" s="9">
         <f>IFERROR(E48/(E48+F48),0)</f>
@@ -2741,24 +2741,24 @@
       </c>
       <c r="B49" s="15" t="inlineStr">
         <is>
-          <t>38903</t>
+          <t>38475</t>
         </is>
       </c>
       <c r="C49" s="12" t="inlineStr">
         <is>
-          <t>Encuentro Oceania</t>
+          <t>Satelite Centro Civico</t>
         </is>
       </c>
       <c r="D49" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E49" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G49" s="13">
         <f>IFERROR(E49/(E49+F49),0)</f>
@@ -2781,24 +2781,24 @@
       </c>
       <c r="B50" s="17" t="inlineStr">
         <is>
-          <t>38507</t>
+          <t>38442</t>
         </is>
       </c>
       <c r="C50" s="8" t="inlineStr">
         <is>
-          <t>Espacio Vista del Valle</t>
+          <t>Sor Juana</t>
         </is>
       </c>
       <c r="D50" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E50" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F50" s="7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G50" s="9">
         <f>IFERROR(E50/(E50+F50),0)</f>
@@ -2821,12 +2821,12 @@
       </c>
       <c r="B51" s="15" t="inlineStr">
         <is>
-          <t>38363</t>
+          <t>38925</t>
         </is>
       </c>
       <c r="C51" s="12" t="inlineStr">
         <is>
-          <t>Galerias Atizapan</t>
+          <t>Star Medica Lomas Verdes</t>
         </is>
       </c>
       <c r="D51" s="12" t="inlineStr">
@@ -2835,10 +2835,10 @@
         </is>
       </c>
       <c r="E51" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G51" s="13">
         <f>IFERROR(E51/(E51+F51),0)</f>
@@ -2861,24 +2861,24 @@
       </c>
       <c r="B52" s="17" t="inlineStr">
         <is>
-          <t>38770</t>
+          <t>38411</t>
         </is>
       </c>
       <c r="C52" s="8" t="inlineStr">
         <is>
-          <t>Gustavo Baz 29</t>
+          <t>Torres Lindavista</t>
         </is>
       </c>
       <c r="D52" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E52" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F52" s="7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G52" s="9">
         <f>IFERROR(E52/(E52+F52),0)</f>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="B53" s="15" t="inlineStr">
         <is>
-          <t>38230</t>
+          <t>38374</t>
         </is>
       </c>
       <c r="C53" s="12" t="inlineStr">
         <is>
-          <t>ITEMS Edo de Mexico</t>
+          <t>Valle Dorado</t>
         </is>
       </c>
       <c r="D53" s="12" t="inlineStr">
@@ -2915,10 +2915,10 @@
         </is>
       </c>
       <c r="E53" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F53" s="11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G53" s="13">
         <f>IFERROR(E53/(E53+F53),0)</f>
@@ -2941,24 +2941,24 @@
       </c>
       <c r="B54" s="17" t="inlineStr">
         <is>
-          <t>38661</t>
+          <t>38651</t>
         </is>
       </c>
       <c r="C54" s="8" t="inlineStr">
         <is>
-          <t>Jinetes</t>
+          <t>Via Vallejo</t>
         </is>
       </c>
       <c r="D54" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E54" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F54" s="7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G54" s="9">
         <f>IFERROR(E54/(E54+F54),0)</f>
@@ -2981,12 +2981,12 @@
       </c>
       <c r="B55" s="15" t="inlineStr">
         <is>
-          <t>38119</t>
+          <t>38142</t>
         </is>
       </c>
       <c r="C55" s="12" t="inlineStr">
         <is>
-          <t>Lomas Verdes</t>
+          <t>Zona Esmeralda</t>
         </is>
       </c>
       <c r="D55" s="12" t="inlineStr">
@@ -2995,10 +2995,10 @@
         </is>
       </c>
       <c r="E55" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F55" s="11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G55" s="13">
         <f>IFERROR(E55/(E55+F55),0)</f>
@@ -3021,24 +3021,24 @@
       </c>
       <c r="B56" s="17" t="inlineStr">
         <is>
-          <t>38270</t>
+          <t>38207</t>
         </is>
       </c>
       <c r="C56" s="8" t="inlineStr">
         <is>
-          <t>Lomas Verdes II</t>
+          <t>Lindavista II</t>
         </is>
       </c>
       <c r="D56" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E56" s="7" t="n">
         <v>1</v>
       </c>
       <c r="F56" s="7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G56" s="9">
         <f>IFERROR(E56/(E56+F56),0)</f>
@@ -3061,17 +3061,17 @@
       </c>
       <c r="B57" s="15" t="inlineStr">
         <is>
-          <t>38845</t>
+          <t>38197</t>
         </is>
       </c>
       <c r="C57" s="12" t="inlineStr">
         <is>
-          <t>Mundo E II</t>
+          <t>Echegaray</t>
         </is>
       </c>
       <c r="D57" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E57" s="11" t="n">
@@ -3101,17 +3101,17 @@
       </c>
       <c r="B58" s="17" t="inlineStr">
         <is>
-          <t>38937</t>
+          <t>38458</t>
         </is>
       </c>
       <c r="C58" s="8" t="inlineStr">
         <is>
-          <t>Parque Tepeyac Piso 1</t>
+          <t>El Rosario</t>
         </is>
       </c>
       <c r="D58" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E58" s="7" t="n">
@@ -3141,17 +3141,17 @@
       </c>
       <c r="B59" s="15" t="inlineStr">
         <is>
-          <t>38590</t>
+          <t>38903</t>
         </is>
       </c>
       <c r="C59" s="12" t="inlineStr">
         <is>
-          <t>Parque Toreo II</t>
+          <t>Encuentro Oceania</t>
         </is>
       </c>
       <c r="D59" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E59" s="11" t="n">
@@ -3181,17 +3181,17 @@
       </c>
       <c r="B60" s="17" t="inlineStr">
         <is>
-          <t>38792</t>
+          <t>38770</t>
         </is>
       </c>
       <c r="C60" s="8" t="inlineStr">
         <is>
-          <t>Pasaje Tlanepantla</t>
+          <t>Gustavo Baz 29</t>
         </is>
       </c>
       <c r="D60" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E60" s="7" t="n">
@@ -3221,17 +3221,17 @@
       </c>
       <c r="B61" s="15" t="inlineStr">
         <is>
-          <t>38176</t>
+          <t>38230</t>
         </is>
       </c>
       <c r="C61" s="12" t="inlineStr">
         <is>
-          <t>Periferico Satélite DT</t>
+          <t>ITEMS Edo de Mexico</t>
         </is>
       </c>
       <c r="D61" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E61" s="11" t="n">
@@ -3261,17 +3261,17 @@
       </c>
       <c r="B62" s="17" t="inlineStr">
         <is>
-          <t>38427</t>
+          <t>38119</t>
         </is>
       </c>
       <c r="C62" s="8" t="inlineStr">
         <is>
-          <t>Plaza Satelite</t>
+          <t>Lomas Verdes</t>
         </is>
       </c>
       <c r="D62" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E62" s="7" t="n">
@@ -3301,17 +3301,17 @@
       </c>
       <c r="B63" s="15" t="inlineStr">
         <is>
-          <t>38811</t>
+          <t>38270</t>
         </is>
       </c>
       <c r="C63" s="12" t="inlineStr">
         <is>
-          <t>Plaza Tepeyac</t>
+          <t>Lomas Verdes II</t>
         </is>
       </c>
       <c r="D63" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E63" s="11" t="n">
@@ -3341,12 +3341,12 @@
       </c>
       <c r="B64" s="17" t="inlineStr">
         <is>
-          <t>38136</t>
+          <t>38845</t>
         </is>
       </c>
       <c r="C64" s="8" t="inlineStr">
         <is>
-          <t>Punta Norte</t>
+          <t>Mundo E II</t>
         </is>
       </c>
       <c r="D64" s="8" t="inlineStr">
@@ -3381,17 +3381,17 @@
       </c>
       <c r="B65" s="15" t="inlineStr">
         <is>
-          <t>43152</t>
+          <t>38937</t>
         </is>
       </c>
       <c r="C65" s="12" t="inlineStr">
         <is>
-          <t>Samara Satélite</t>
+          <t>Parque Tepeyac Piso 1</t>
         </is>
       </c>
       <c r="D65" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E65" s="11" t="n">
@@ -3421,17 +3421,17 @@
       </c>
       <c r="B66" s="17" t="inlineStr">
         <is>
-          <t>38266</t>
+          <t>38590</t>
         </is>
       </c>
       <c r="C66" s="8" t="inlineStr">
         <is>
-          <t>San Mateo</t>
+          <t>Parque Toreo II</t>
         </is>
       </c>
       <c r="D66" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E66" s="7" t="n">
@@ -3461,17 +3461,17 @@
       </c>
       <c r="B67" s="15" t="inlineStr">
         <is>
-          <t>38460</t>
+          <t>38176</t>
         </is>
       </c>
       <c r="C67" s="12" t="inlineStr">
         <is>
-          <t>Santa Monica</t>
+          <t>Periferico Satélite DT</t>
         </is>
       </c>
       <c r="D67" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E67" s="11" t="n">
@@ -3501,12 +3501,12 @@
       </c>
       <c r="B68" s="17" t="inlineStr">
         <is>
-          <t>38117</t>
+          <t>38427</t>
         </is>
       </c>
       <c r="C68" s="8" t="inlineStr">
         <is>
-          <t>Satelite</t>
+          <t>Plaza Satelite</t>
         </is>
       </c>
       <c r="D68" s="8" t="inlineStr">
@@ -3541,17 +3541,17 @@
       </c>
       <c r="B69" s="15" t="inlineStr">
         <is>
-          <t>38442</t>
+          <t>43152</t>
         </is>
       </c>
       <c r="C69" s="12" t="inlineStr">
         <is>
-          <t>Sor Juana</t>
+          <t>Samara Satélite</t>
         </is>
       </c>
       <c r="D69" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E69" s="11" t="n">
@@ -3581,12 +3581,12 @@
       </c>
       <c r="B70" s="17" t="inlineStr">
         <is>
-          <t>38925</t>
+          <t>38266</t>
         </is>
       </c>
       <c r="C70" s="8" t="inlineStr">
         <is>
-          <t>Star Medica Lomas Verdes</t>
+          <t>San Mateo</t>
         </is>
       </c>
       <c r="D70" s="8" t="inlineStr">
@@ -3621,17 +3621,17 @@
       </c>
       <c r="B71" s="15" t="inlineStr">
         <is>
-          <t>38992</t>
+          <t>38117</t>
         </is>
       </c>
       <c r="C71" s="12" t="inlineStr">
         <is>
-          <t>Tapo Puerta Oriente</t>
+          <t>Satelite</t>
         </is>
       </c>
       <c r="D71" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E71" s="11" t="n">
@@ -3661,17 +3661,17 @@
       </c>
       <c r="B72" s="17" t="inlineStr">
         <is>
-          <t>43130</t>
+          <t>38992</t>
         </is>
       </c>
       <c r="C72" s="8" t="inlineStr">
         <is>
-          <t>Town Center Nicolás Romero</t>
+          <t>Tapo Puerta Oriente</t>
         </is>
       </c>
       <c r="D72" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E72" s="7" t="n">
@@ -3701,17 +3701,17 @@
       </c>
       <c r="B73" s="15" t="inlineStr">
         <is>
-          <t>38694</t>
+          <t>43130</t>
         </is>
       </c>
       <c r="C73" s="12" t="inlineStr">
         <is>
-          <t>Villas de la Hacienda</t>
+          <t>Town Center Nicolás Romero</t>
         </is>
       </c>
       <c r="D73" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E73" s="11" t="n">
@@ -3741,17 +3741,17 @@
       </c>
       <c r="B74" s="17" t="inlineStr">
         <is>
-          <t>38656</t>
+          <t>38694</t>
         </is>
       </c>
       <c r="C74" s="8" t="inlineStr">
         <is>
-          <t>Viveros de la Loma</t>
+          <t>Villas de la Hacienda</t>
         </is>
       </c>
       <c r="D74" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E74" s="7" t="n">
@@ -3781,17 +3781,17 @@
       </c>
       <c r="B75" s="15" t="inlineStr">
         <is>
-          <t>38115</t>
+          <t>38656</t>
         </is>
       </c>
       <c r="C75" s="12" t="inlineStr">
         <is>
-          <t>Zona Azul</t>
+          <t>Viveros de la Loma</t>
         </is>
       </c>
       <c r="D75" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E75" s="11" t="n">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="B76" s="17" t="inlineStr">
         <is>
-          <t>38142</t>
+          <t>38115</t>
         </is>
       </c>
       <c r="C76" s="8" t="inlineStr">
         <is>
-          <t>Zona Esmeralda</t>
+          <t>Zona Azul</t>
         </is>
       </c>
       <c r="D76" s="8" t="inlineStr">
@@ -3906,7 +3906,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Centro Norte · Corte 01/09/2026 10:05</t>
+          <t>Centro Norte · Corte 01/09/2026 13:22</t>
         </is>
       </c>
     </row>
@@ -3997,10 +3997,10 @@
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="D6" s="7" t="n">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="E6" s="9">
         <f>IFERROR(C6/(C6+D6),0)</f>
@@ -4011,14 +4011,14 @@
           <t>03/09/26</t>
         </is>
       </c>
-      <c r="G6" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="H6" s="14" t="inlineStr">
-        <is>
-          <t>Priorizar hoy</t>
+      <c r="G6" s="10" t="inlineStr">
+        <is>
+          <t>Seguimiento</t>
+        </is>
+      </c>
+      <c r="H6" s="10" t="inlineStr">
+        <is>
+          <t>Dar seguimiento</t>
         </is>
       </c>
     </row>
@@ -4102,10 +4102,10 @@
         </is>
       </c>
       <c r="C9" s="11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D9" s="11" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E9" s="13">
         <f>IFERROR(C9/(C9+D9),0)</f>

--- a/exports/Resumen_Evidencias_OPS.xlsx
+++ b/exports/Resumen_Evidencias_OPS.xlsx
@@ -592,7 +592,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Centro Norte · Corte 01/09/2026 13:22</t>
+          <t>Centro Norte · Corte 01/09/2026 18:42</t>
         </is>
       </c>
     </row>
@@ -615,10 +615,10 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>620</v>
+        <v>598</v>
       </c>
       <c r="E6" s="5">
         <f>IFERROR(A6/(A6+C6),0)</f>
@@ -681,10 +681,10 @@
         <v>10</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="F10" s="9">
         <f>IFERROR(D10/(D10+E10),0)</f>
@@ -714,10 +714,10 @@
         <v>11</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E11" s="12" t="n">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="F11" s="13">
         <f>IFERROR(D11/(D11+E11),0)</f>
@@ -740,17 +740,17 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño</t>
+          <t>Nancy Carolina</t>
         </is>
       </c>
       <c r="C12" s="7" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E12" s="8" t="n">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="F12" s="9">
         <f>IFERROR(D12/(D12+E12),0)</f>
@@ -773,17 +773,17 @@
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina</t>
+          <t>Yazmin Chabela</t>
         </is>
       </c>
       <c r="C13" s="11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D13" s="11" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="E13" s="12" t="n">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="F13" s="13">
         <f>IFERROR(D13/(D13+E13),0)</f>
@@ -806,17 +806,17 @@
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela</t>
+          <t>Vanessa Carreño</t>
         </is>
       </c>
       <c r="C14" s="7" t="n">
         <v>13</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E14" s="8" t="n">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F14" s="9">
         <f>IFERROR(D14/(D14+E14),0)</f>
@@ -846,10 +846,10 @@
         <v>13</v>
       </c>
       <c r="D15" s="11" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E15" s="12" t="n">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="F15" s="13">
         <f>IFERROR(D15/(D15+E15),0)</f>
@@ -924,7 +924,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Centro Norte · Corte 01/09/2026 13:22</t>
+          <t>Centro Norte · Corte 01/09/2026 18:42</t>
         </is>
       </c>
     </row>
@@ -1181,12 +1181,12 @@
       </c>
       <c r="B10" s="17" t="inlineStr">
         <is>
-          <t>38894</t>
+          <t>43193</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>Galerias Perinorte</t>
+          <t>Cosmopol N1</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
@@ -1198,7 +1198,7 @@
         <v>5</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G10" s="9">
         <f>IFERROR(E10/(E10+F10),0)</f>
@@ -1221,12 +1221,12 @@
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>38333</t>
+          <t>38401</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>Izcalli Mega</t>
+          <t>Coacalco</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
@@ -1261,17 +1261,17 @@
       </c>
       <c r="B12" s="17" t="inlineStr">
         <is>
-          <t>38339</t>
+          <t>38458</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>El Rosario</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E12" s="7" t="n">
@@ -1301,37 +1301,37 @@
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>38695</t>
+          <t>38894</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>Cetram 4 Caminos</t>
+          <t>Galerias Perinorte</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E13" s="11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G13" s="13">
         <f>IFERROR(E13/(E13+F13),0)</f>
         <v/>
       </c>
-      <c r="H13" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I13" s="14" t="inlineStr">
-        <is>
-          <t>Priorizar hoy</t>
+      <c r="H13" s="10" t="inlineStr">
+        <is>
+          <t>Seguimiento</t>
+        </is>
+      </c>
+      <c r="I13" s="10" t="inlineStr">
+        <is>
+          <t>Dar seguimiento</t>
         </is>
       </c>
     </row>
@@ -1341,12 +1341,12 @@
       </c>
       <c r="B14" s="17" t="inlineStr">
         <is>
-          <t>38401</t>
+          <t>38333</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Coacalco</t>
+          <t>Izcalli Mega</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr">
@@ -1355,23 +1355,23 @@
         </is>
       </c>
       <c r="E14" s="7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F14" s="7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G14" s="9">
         <f>IFERROR(E14/(E14+F14),0)</f>
         <v/>
       </c>
-      <c r="H14" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I14" s="14" t="inlineStr">
-        <is>
-          <t>Priorizar hoy</t>
+      <c r="H14" s="10" t="inlineStr">
+        <is>
+          <t>Seguimiento</t>
+        </is>
+      </c>
+      <c r="I14" s="10" t="inlineStr">
+        <is>
+          <t>Dar seguimiento</t>
         </is>
       </c>
     </row>
@@ -1381,37 +1381,37 @@
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>43194</t>
+          <t>38339</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>Atana Lindavista</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E15" s="11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G15" s="13">
         <f>IFERROR(E15/(E15+F15),0)</f>
         <v/>
       </c>
-      <c r="H15" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I15" s="14" t="inlineStr">
-        <is>
-          <t>Priorizar hoy</t>
+      <c r="H15" s="10" t="inlineStr">
+        <is>
+          <t>Seguimiento</t>
+        </is>
+      </c>
+      <c r="I15" s="10" t="inlineStr">
+        <is>
+          <t>Dar seguimiento</t>
         </is>
       </c>
     </row>
@@ -1421,24 +1421,24 @@
       </c>
       <c r="B16" s="17" t="inlineStr">
         <is>
-          <t>38604</t>
+          <t>38695</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>Cosmopol</t>
+          <t>Cetram 4 Caminos</t>
         </is>
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E16" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F16" s="7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G16" s="9">
         <f>IFERROR(E16/(E16+F16),0)</f>
@@ -1461,24 +1461,24 @@
       </c>
       <c r="B17" s="15" t="inlineStr">
         <is>
-          <t>38965</t>
+          <t>38661</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>Parque Tepeyac Piso 2</t>
+          <t>Jinetes</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E17" s="11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G17" s="13">
         <f>IFERROR(E17/(E17+F17),0)</f>
@@ -1501,24 +1501,24 @@
       </c>
       <c r="B18" s="17" t="inlineStr">
         <is>
-          <t>38924</t>
+          <t>38456</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>Plaza Aeropuerto</t>
+          <t>Plaza las Flores</t>
         </is>
       </c>
       <c r="D18" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E18" s="7" t="n">
         <v>3</v>
       </c>
       <c r="F18" s="7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G18" s="9">
         <f>IFERROR(E18/(E18+F18),0)</f>
@@ -1541,17 +1541,17 @@
       </c>
       <c r="B19" s="15" t="inlineStr">
         <is>
-          <t>38606</t>
+          <t>43194</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>TlalnepantlaCarso</t>
+          <t>Atana Lindavista</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E19" s="11" t="n">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="B20" s="17" t="inlineStr">
         <is>
-          <t>43193</t>
+          <t>38604</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>Cosmopol N1</t>
+          <t>Cosmopol</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr">
@@ -1595,7 +1595,7 @@
         </is>
       </c>
       <c r="E20" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F20" s="7" t="n">
         <v>8</v>
@@ -1621,21 +1621,21 @@
       </c>
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t>38456</t>
+          <t>38903</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>Plaza las Flores</t>
+          <t>Encuentro Oceania</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E21" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F21" s="11" t="n">
         <v>8</v>
@@ -1661,24 +1661,24 @@
       </c>
       <c r="B22" s="17" t="inlineStr">
         <is>
-          <t>38186</t>
+          <t>38965</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>Arboledas</t>
+          <t>Parque Tepeyac Piso 2</t>
         </is>
       </c>
       <c r="D22" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E22" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G22" s="9">
         <f>IFERROR(E22/(E22+F22),0)</f>
@@ -1701,24 +1701,24 @@
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>43043</t>
+          <t>38924</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>Atizapan</t>
+          <t>Plaza Aeropuerto</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E23" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G23" s="13">
         <f>IFERROR(E23/(E23+F23),0)</f>
@@ -1741,24 +1741,24 @@
       </c>
       <c r="B24" s="17" t="inlineStr">
         <is>
-          <t>38149</t>
+          <t>38606</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>Bellavista</t>
+          <t>TlalnepantlaCarso</t>
         </is>
       </c>
       <c r="D24" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E24" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F24" s="7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G24" s="9">
         <f>IFERROR(E24/(E24+F24),0)</f>
@@ -1781,24 +1781,24 @@
       </c>
       <c r="B25" s="15" t="inlineStr">
         <is>
-          <t>38930</t>
+          <t>38374</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>Blvd. Aeropuerto dt</t>
+          <t>Valle Dorado</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E25" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G25" s="13">
         <f>IFERROR(E25/(E25+F25),0)</f>
@@ -1821,17 +1821,17 @@
       </c>
       <c r="B26" s="17" t="inlineStr">
         <is>
-          <t>38529</t>
+          <t>38186</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>Bosques de Aragon</t>
+          <t>Arboledas</t>
         </is>
       </c>
       <c r="D26" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E26" s="7" t="n">
@@ -1861,17 +1861,17 @@
       </c>
       <c r="B27" s="15" t="inlineStr">
         <is>
-          <t>38527</t>
+          <t>43043</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>Camarones</t>
+          <t>Atizapan</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E27" s="11" t="n">
@@ -1901,17 +1901,17 @@
       </c>
       <c r="B28" s="17" t="inlineStr">
         <is>
-          <t>38837</t>
+          <t>38149</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>Centenario Azcapotzalco</t>
+          <t>Bellavista</t>
         </is>
       </c>
       <c r="D28" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E28" s="7" t="n">
@@ -1941,17 +1941,17 @@
       </c>
       <c r="B29" s="15" t="inlineStr">
         <is>
-          <t>38394</t>
+          <t>38930</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>Centro Comercial Lomas Verdes</t>
+          <t>Blvd. Aeropuerto dt</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E29" s="11" t="n">
@@ -1981,17 +1981,17 @@
       </c>
       <c r="B30" s="17" t="inlineStr">
         <is>
-          <t>38535</t>
+          <t>38529</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>City Center Esmeralda</t>
+          <t>Bosques de Aragon</t>
         </is>
       </c>
       <c r="D30" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E30" s="7" t="n">
@@ -2021,17 +2021,17 @@
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>38431</t>
+          <t>38527</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>Eduardo Molina</t>
+          <t>Camarones</t>
         </is>
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E31" s="11" t="n">
@@ -2061,17 +2061,17 @@
       </c>
       <c r="B32" s="17" t="inlineStr">
         <is>
-          <t>38995</t>
+          <t>38837</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>Encuentro Oceania II</t>
+          <t>Centenario Azcapotzalco</t>
         </is>
       </c>
       <c r="D32" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E32" s="7" t="n">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="B33" s="15" t="inlineStr">
         <is>
-          <t>38507</t>
+          <t>38394</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>Espacio Vista del Valle</t>
+          <t>Centro Comercial Lomas Verdes</t>
         </is>
       </c>
       <c r="D33" s="12" t="inlineStr">
@@ -2141,12 +2141,12 @@
       </c>
       <c r="B34" s="17" t="inlineStr">
         <is>
-          <t>38363</t>
+          <t>38535</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>Galerias Atizapan</t>
+          <t>City Center Esmeralda</t>
         </is>
       </c>
       <c r="D34" s="8" t="inlineStr">
@@ -2181,17 +2181,17 @@
       </c>
       <c r="B35" s="15" t="inlineStr">
         <is>
-          <t>38661</t>
+          <t>38431</t>
         </is>
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>Jinetes</t>
+          <t>Eduardo Molina</t>
         </is>
       </c>
       <c r="D35" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E35" s="11" t="n">
@@ -2221,17 +2221,17 @@
       </c>
       <c r="B36" s="17" t="inlineStr">
         <is>
-          <t>38205</t>
+          <t>38995</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>Lindavista</t>
+          <t>Encuentro Oceania II</t>
         </is>
       </c>
       <c r="D36" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E36" s="7" t="n">
@@ -2261,17 +2261,17 @@
       </c>
       <c r="B37" s="15" t="inlineStr">
         <is>
-          <t>38371</t>
+          <t>38507</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>Montevideo DT</t>
+          <t>Espacio Vista del Valle</t>
         </is>
       </c>
       <c r="D37" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E37" s="11" t="n">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="B38" s="17" t="inlineStr">
         <is>
-          <t>43111</t>
+          <t>38363</t>
         </is>
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>Montevideo Insurgentes</t>
+          <t>Galerias Atizapan</t>
         </is>
       </c>
       <c r="D38" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E38" s="7" t="n">
@@ -2341,12 +2341,12 @@
       </c>
       <c r="B39" s="15" t="inlineStr">
         <is>
-          <t>38674</t>
+          <t>38230</t>
         </is>
       </c>
       <c r="C39" s="12" t="inlineStr">
         <is>
-          <t>Mundo E</t>
+          <t>ITEMS Edo de Mexico</t>
         </is>
       </c>
       <c r="D39" s="12" t="inlineStr">
@@ -2381,12 +2381,12 @@
       </c>
       <c r="B40" s="17" t="inlineStr">
         <is>
-          <t>43195</t>
+          <t>38205</t>
         </is>
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>Parque Jadin kiosko</t>
+          <t>Lindavista</t>
         </is>
       </c>
       <c r="D40" s="8" t="inlineStr">
@@ -2421,17 +2421,17 @@
       </c>
       <c r="B41" s="15" t="inlineStr">
         <is>
-          <t>38792</t>
+          <t>38371</t>
         </is>
       </c>
       <c r="C41" s="12" t="inlineStr">
         <is>
-          <t>Pasaje Tlanepantla</t>
+          <t>Montevideo DT</t>
         </is>
       </c>
       <c r="D41" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E41" s="11" t="n">
@@ -2461,12 +2461,12 @@
       </c>
       <c r="B42" s="17" t="inlineStr">
         <is>
-          <t>38546</t>
+          <t>43111</t>
         </is>
       </c>
       <c r="C42" s="8" t="inlineStr">
         <is>
-          <t>Patio Claveria</t>
+          <t>Montevideo Insurgentes</t>
         </is>
       </c>
       <c r="D42" s="8" t="inlineStr">
@@ -2501,17 +2501,17 @@
       </c>
       <c r="B43" s="15" t="inlineStr">
         <is>
-          <t>38677</t>
+          <t>38674</t>
         </is>
       </c>
       <c r="C43" s="12" t="inlineStr">
         <is>
-          <t>Patio la Raza</t>
+          <t>Mundo E</t>
         </is>
       </c>
       <c r="D43" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E43" s="11" t="n">
@@ -2541,17 +2541,17 @@
       </c>
       <c r="B44" s="17" t="inlineStr">
         <is>
-          <t>38859</t>
+          <t>43195</t>
         </is>
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t>Plaza Satelite II N1</t>
+          <t>Parque Jadin kiosko</t>
         </is>
       </c>
       <c r="D44" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E44" s="7" t="n">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="B45" s="15" t="inlineStr">
         <is>
-          <t>38811</t>
+          <t>38937</t>
         </is>
       </c>
       <c r="C45" s="12" t="inlineStr">
         <is>
-          <t>Plaza Tepeyac</t>
+          <t>Parque Tepeyac Piso 1</t>
         </is>
       </c>
       <c r="D45" s="12" t="inlineStr">
@@ -2621,17 +2621,17 @@
       </c>
       <c r="B46" s="17" t="inlineStr">
         <is>
-          <t>43132</t>
+          <t>38792</t>
         </is>
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t>Plaza Vista Norte</t>
+          <t>Pasaje Tlanepantla</t>
         </is>
       </c>
       <c r="D46" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E46" s="7" t="n">
@@ -2661,17 +2661,17 @@
       </c>
       <c r="B47" s="15" t="inlineStr">
         <is>
-          <t>38136</t>
+          <t>38546</t>
         </is>
       </c>
       <c r="C47" s="12" t="inlineStr">
         <is>
-          <t>Punta Norte</t>
+          <t>Patio Claveria</t>
         </is>
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E47" s="11" t="n">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="B48" s="17" t="inlineStr">
         <is>
-          <t>38460</t>
+          <t>38677</t>
         </is>
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
-          <t>Santa Monica</t>
+          <t>Patio la Raza</t>
         </is>
       </c>
       <c r="D48" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E48" s="7" t="n">
@@ -2741,12 +2741,12 @@
       </c>
       <c r="B49" s="15" t="inlineStr">
         <is>
-          <t>38475</t>
+          <t>38859</t>
         </is>
       </c>
       <c r="C49" s="12" t="inlineStr">
         <is>
-          <t>Satelite Centro Civico</t>
+          <t>Plaza Satelite II N1</t>
         </is>
       </c>
       <c r="D49" s="12" t="inlineStr">
@@ -2781,17 +2781,17 @@
       </c>
       <c r="B50" s="17" t="inlineStr">
         <is>
-          <t>38442</t>
+          <t>38811</t>
         </is>
       </c>
       <c r="C50" s="8" t="inlineStr">
         <is>
-          <t>Sor Juana</t>
+          <t>Plaza Tepeyac</t>
         </is>
       </c>
       <c r="D50" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E50" s="7" t="n">
@@ -2821,17 +2821,17 @@
       </c>
       <c r="B51" s="15" t="inlineStr">
         <is>
-          <t>38925</t>
+          <t>43132</t>
         </is>
       </c>
       <c r="C51" s="12" t="inlineStr">
         <is>
-          <t>Star Medica Lomas Verdes</t>
+          <t>Plaza Vista Norte</t>
         </is>
       </c>
       <c r="D51" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E51" s="11" t="n">
@@ -2861,17 +2861,17 @@
       </c>
       <c r="B52" s="17" t="inlineStr">
         <is>
-          <t>38411</t>
+          <t>38136</t>
         </is>
       </c>
       <c r="C52" s="8" t="inlineStr">
         <is>
-          <t>Torres Lindavista</t>
+          <t>Punta Norte</t>
         </is>
       </c>
       <c r="D52" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E52" s="7" t="n">
@@ -2901,12 +2901,12 @@
       </c>
       <c r="B53" s="15" t="inlineStr">
         <is>
-          <t>38374</t>
+          <t>38460</t>
         </is>
       </c>
       <c r="C53" s="12" t="inlineStr">
         <is>
-          <t>Valle Dorado</t>
+          <t>Santa Monica</t>
         </is>
       </c>
       <c r="D53" s="12" t="inlineStr">
@@ -2941,17 +2941,17 @@
       </c>
       <c r="B54" s="17" t="inlineStr">
         <is>
-          <t>38651</t>
+          <t>38475</t>
         </is>
       </c>
       <c r="C54" s="8" t="inlineStr">
         <is>
-          <t>Via Vallejo</t>
+          <t>Satelite Centro Civico</t>
         </is>
       </c>
       <c r="D54" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E54" s="7" t="n">
@@ -2981,17 +2981,17 @@
       </c>
       <c r="B55" s="15" t="inlineStr">
         <is>
-          <t>38142</t>
+          <t>38442</t>
         </is>
       </c>
       <c r="C55" s="12" t="inlineStr">
         <is>
-          <t>Zona Esmeralda</t>
+          <t>Sor Juana</t>
         </is>
       </c>
       <c r="D55" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E55" s="11" t="n">
@@ -3021,21 +3021,21 @@
       </c>
       <c r="B56" s="17" t="inlineStr">
         <is>
-          <t>38207</t>
+          <t>38925</t>
         </is>
       </c>
       <c r="C56" s="8" t="inlineStr">
         <is>
-          <t>Lindavista II</t>
+          <t>Star Medica Lomas Verdes</t>
         </is>
       </c>
       <c r="D56" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E56" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F56" s="7" t="n">
         <v>9</v>
@@ -3061,24 +3061,24 @@
       </c>
       <c r="B57" s="15" t="inlineStr">
         <is>
-          <t>38197</t>
+          <t>38992</t>
         </is>
       </c>
       <c r="C57" s="12" t="inlineStr">
         <is>
-          <t>Echegaray</t>
+          <t>Tapo Puerta Oriente</t>
         </is>
       </c>
       <c r="D57" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E57" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F57" s="11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G57" s="13">
         <f>IFERROR(E57/(E57+F57),0)</f>
@@ -3101,24 +3101,24 @@
       </c>
       <c r="B58" s="17" t="inlineStr">
         <is>
-          <t>38458</t>
+          <t>38411</t>
         </is>
       </c>
       <c r="C58" s="8" t="inlineStr">
         <is>
-          <t>El Rosario</t>
+          <t>Torres Lindavista</t>
         </is>
       </c>
       <c r="D58" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E58" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F58" s="7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G58" s="9">
         <f>IFERROR(E58/(E58+F58),0)</f>
@@ -3141,24 +3141,24 @@
       </c>
       <c r="B59" s="15" t="inlineStr">
         <is>
-          <t>38903</t>
+          <t>43130</t>
         </is>
       </c>
       <c r="C59" s="12" t="inlineStr">
         <is>
-          <t>Encuentro Oceania</t>
+          <t>Town Center Nicolás Romero</t>
         </is>
       </c>
       <c r="D59" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E59" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F59" s="11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G59" s="13">
         <f>IFERROR(E59/(E59+F59),0)</f>
@@ -3181,24 +3181,24 @@
       </c>
       <c r="B60" s="17" t="inlineStr">
         <is>
-          <t>38770</t>
+          <t>38651</t>
         </is>
       </c>
       <c r="C60" s="8" t="inlineStr">
         <is>
-          <t>Gustavo Baz 29</t>
+          <t>Via Vallejo</t>
         </is>
       </c>
       <c r="D60" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E60" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F60" s="7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G60" s="9">
         <f>IFERROR(E60/(E60+F60),0)</f>
@@ -3221,12 +3221,12 @@
       </c>
       <c r="B61" s="15" t="inlineStr">
         <is>
-          <t>38230</t>
+          <t>38694</t>
         </is>
       </c>
       <c r="C61" s="12" t="inlineStr">
         <is>
-          <t>ITEMS Edo de Mexico</t>
+          <t>Villas de la Hacienda</t>
         </is>
       </c>
       <c r="D61" s="12" t="inlineStr">
@@ -3235,10 +3235,10 @@
         </is>
       </c>
       <c r="E61" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F61" s="11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G61" s="13">
         <f>IFERROR(E61/(E61+F61),0)</f>
@@ -3261,12 +3261,12 @@
       </c>
       <c r="B62" s="17" t="inlineStr">
         <is>
-          <t>38119</t>
+          <t>38115</t>
         </is>
       </c>
       <c r="C62" s="8" t="inlineStr">
         <is>
-          <t>Lomas Verdes</t>
+          <t>Zona Azul</t>
         </is>
       </c>
       <c r="D62" s="8" t="inlineStr">
@@ -3275,10 +3275,10 @@
         </is>
       </c>
       <c r="E62" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F62" s="7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G62" s="9">
         <f>IFERROR(E62/(E62+F62),0)</f>
@@ -3301,12 +3301,12 @@
       </c>
       <c r="B63" s="15" t="inlineStr">
         <is>
-          <t>38270</t>
+          <t>38142</t>
         </is>
       </c>
       <c r="C63" s="12" t="inlineStr">
         <is>
-          <t>Lomas Verdes II</t>
+          <t>Zona Esmeralda</t>
         </is>
       </c>
       <c r="D63" s="12" t="inlineStr">
@@ -3315,10 +3315,10 @@
         </is>
       </c>
       <c r="E63" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F63" s="11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G63" s="13">
         <f>IFERROR(E63/(E63+F63),0)</f>
@@ -3341,24 +3341,24 @@
       </c>
       <c r="B64" s="17" t="inlineStr">
         <is>
-          <t>38845</t>
+          <t>38207</t>
         </is>
       </c>
       <c r="C64" s="8" t="inlineStr">
         <is>
-          <t>Mundo E II</t>
+          <t>Lindavista II</t>
         </is>
       </c>
       <c r="D64" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E64" s="7" t="n">
         <v>1</v>
       </c>
       <c r="F64" s="7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G64" s="9">
         <f>IFERROR(E64/(E64+F64),0)</f>
@@ -3381,24 +3381,24 @@
       </c>
       <c r="B65" s="15" t="inlineStr">
         <is>
-          <t>38937</t>
+          <t>38845</t>
         </is>
       </c>
       <c r="C65" s="12" t="inlineStr">
         <is>
-          <t>Parque Tepeyac Piso 1</t>
+          <t>Mundo E II</t>
         </is>
       </c>
       <c r="D65" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E65" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F65" s="11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G65" s="13">
         <f>IFERROR(E65/(E65+F65),0)</f>
@@ -3421,24 +3421,24 @@
       </c>
       <c r="B66" s="17" t="inlineStr">
         <is>
-          <t>38590</t>
+          <t>38266</t>
         </is>
       </c>
       <c r="C66" s="8" t="inlineStr">
         <is>
-          <t>Parque Toreo II</t>
+          <t>San Mateo</t>
         </is>
       </c>
       <c r="D66" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E66" s="7" t="n">
         <v>1</v>
       </c>
       <c r="F66" s="7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G66" s="9">
         <f>IFERROR(E66/(E66+F66),0)</f>
@@ -3461,12 +3461,12 @@
       </c>
       <c r="B67" s="15" t="inlineStr">
         <is>
-          <t>38176</t>
+          <t>38197</t>
         </is>
       </c>
       <c r="C67" s="12" t="inlineStr">
         <is>
-          <t>Periferico Satélite DT</t>
+          <t>Echegaray</t>
         </is>
       </c>
       <c r="D67" s="12" t="inlineStr">
@@ -3501,12 +3501,12 @@
       </c>
       <c r="B68" s="17" t="inlineStr">
         <is>
-          <t>38427</t>
+          <t>38770</t>
         </is>
       </c>
       <c r="C68" s="8" t="inlineStr">
         <is>
-          <t>Plaza Satelite</t>
+          <t>Gustavo Baz 29</t>
         </is>
       </c>
       <c r="D68" s="8" t="inlineStr">
@@ -3541,17 +3541,17 @@
       </c>
       <c r="B69" s="15" t="inlineStr">
         <is>
-          <t>43152</t>
+          <t>38119</t>
         </is>
       </c>
       <c r="C69" s="12" t="inlineStr">
         <is>
-          <t>Samara Satélite</t>
+          <t>Lomas Verdes</t>
         </is>
       </c>
       <c r="D69" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E69" s="11" t="n">
@@ -3581,12 +3581,12 @@
       </c>
       <c r="B70" s="17" t="inlineStr">
         <is>
-          <t>38266</t>
+          <t>38270</t>
         </is>
       </c>
       <c r="C70" s="8" t="inlineStr">
         <is>
-          <t>San Mateo</t>
+          <t>Lomas Verdes II</t>
         </is>
       </c>
       <c r="D70" s="8" t="inlineStr">
@@ -3621,12 +3621,12 @@
       </c>
       <c r="B71" s="15" t="inlineStr">
         <is>
-          <t>38117</t>
+          <t>38590</t>
         </is>
       </c>
       <c r="C71" s="12" t="inlineStr">
         <is>
-          <t>Satelite</t>
+          <t>Parque Toreo II</t>
         </is>
       </c>
       <c r="D71" s="12" t="inlineStr">
@@ -3661,17 +3661,17 @@
       </c>
       <c r="B72" s="17" t="inlineStr">
         <is>
-          <t>38992</t>
+          <t>38176</t>
         </is>
       </c>
       <c r="C72" s="8" t="inlineStr">
         <is>
-          <t>Tapo Puerta Oriente</t>
+          <t>Periferico Satélite DT</t>
         </is>
       </c>
       <c r="D72" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E72" s="7" t="n">
@@ -3701,17 +3701,17 @@
       </c>
       <c r="B73" s="15" t="inlineStr">
         <is>
-          <t>43130</t>
+          <t>38427</t>
         </is>
       </c>
       <c r="C73" s="12" t="inlineStr">
         <is>
-          <t>Town Center Nicolás Romero</t>
+          <t>Plaza Satelite</t>
         </is>
       </c>
       <c r="D73" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E73" s="11" t="n">
@@ -3741,17 +3741,17 @@
       </c>
       <c r="B74" s="17" t="inlineStr">
         <is>
-          <t>38694</t>
+          <t>43152</t>
         </is>
       </c>
       <c r="C74" s="8" t="inlineStr">
         <is>
-          <t>Villas de la Hacienda</t>
+          <t>Samara Satélite</t>
         </is>
       </c>
       <c r="D74" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E74" s="7" t="n">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="B75" s="15" t="inlineStr">
         <is>
-          <t>38656</t>
+          <t>38117</t>
         </is>
       </c>
       <c r="C75" s="12" t="inlineStr">
         <is>
-          <t>Viveros de la Loma</t>
+          <t>Satelite</t>
         </is>
       </c>
       <c r="D75" s="12" t="inlineStr">
@@ -3821,17 +3821,17 @@
       </c>
       <c r="B76" s="17" t="inlineStr">
         <is>
-          <t>38115</t>
+          <t>38656</t>
         </is>
       </c>
       <c r="C76" s="8" t="inlineStr">
         <is>
-          <t>Zona Azul</t>
+          <t>Viveros de la Loma</t>
         </is>
       </c>
       <c r="D76" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E76" s="7" t="n">
@@ -3906,7 +3906,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Centro Norte · Corte 01/09/2026 13:22</t>
+          <t>Centro Norte · Corte 01/09/2026 18:42</t>
         </is>
       </c>
     </row>
@@ -3962,10 +3962,10 @@
         </is>
       </c>
       <c r="C5" s="11" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="E5" s="13">
         <f>IFERROR(C5/(C5+D5),0)</f>
@@ -3997,10 +3997,10 @@
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="D6" s="7" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="E6" s="9">
         <f>IFERROR(C6/(C6+D6),0)</f>
@@ -4032,10 +4032,10 @@
         </is>
       </c>
       <c r="C7" s="11" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E7" s="13">
         <f>IFERROR(C7/(C7+D7),0)</f>
@@ -4102,10 +4102,10 @@
         </is>
       </c>
       <c r="C9" s="11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D9" s="11" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E9" s="13">
         <f>IFERROR(C9/(C9+D9),0)</f>
@@ -4207,10 +4207,10 @@
         </is>
       </c>
       <c r="C12" s="7" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E12" s="9">
         <f>IFERROR(C12/(C12+D12),0)</f>
@@ -4277,10 +4277,10 @@
         </is>
       </c>
       <c r="C14" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E14" s="9">
         <f>IFERROR(C14/(C14+D14),0)</f>

--- a/exports/Resumen_Evidencias_OPS.xlsx
+++ b/exports/Resumen_Evidencias_OPS.xlsx
@@ -592,7 +592,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Centro Norte · Corte 01/09/2026 18:42</t>
+          <t>Centro Norte · Corte 01/09/2026 20:26</t>
         </is>
       </c>
     </row>
@@ -615,10 +615,10 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="E6" s="5">
         <f>IFERROR(A6/(A6+C6),0)</f>
@@ -681,10 +681,10 @@
         <v>10</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="F10" s="9">
         <f>IFERROR(D10/(D10+E10),0)</f>
@@ -924,7 +924,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Centro Norte · Corte 01/09/2026 18:42</t>
+          <t>Centro Norte · Corte 01/09/2026 20:26</t>
         </is>
       </c>
     </row>
@@ -1101,12 +1101,12 @@
       </c>
       <c r="B8" s="17" t="inlineStr">
         <is>
-          <t>38368</t>
+          <t>38401</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>Luna Park</t>
+          <t>Coacalco</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
@@ -1141,17 +1141,17 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>38561</t>
+          <t>38333</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>Parque Toreo</t>
+          <t>Izcalli Mega</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E9" s="11" t="n">
@@ -1181,12 +1181,12 @@
       </c>
       <c r="B10" s="17" t="inlineStr">
         <is>
-          <t>43193</t>
+          <t>38368</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>Cosmopol N1</t>
+          <t>Luna Park</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
@@ -1195,7 +1195,7 @@
         </is>
       </c>
       <c r="E10" s="7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F10" s="7" t="n">
         <v>5</v>
@@ -1221,24 +1221,24 @@
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>38401</t>
+          <t>38561</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>Coacalco</t>
+          <t>Parque Toreo</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E11" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="F11" s="11" t="n">
         <v>5</v>
-      </c>
-      <c r="F11" s="11" t="n">
-        <v>6</v>
       </c>
       <c r="G11" s="13">
         <f>IFERROR(E11/(E11+F11),0)</f>
@@ -1261,24 +1261,24 @@
       </c>
       <c r="B12" s="17" t="inlineStr">
         <is>
-          <t>38458</t>
+          <t>38339</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>El Rosario</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E12" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="F12" s="7" t="n">
         <v>5</v>
-      </c>
-      <c r="F12" s="7" t="n">
-        <v>6</v>
       </c>
       <c r="G12" s="9">
         <f>IFERROR(E12/(E12+F12),0)</f>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>38894</t>
+          <t>43193</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>Galerias Perinorte</t>
+          <t>Cosmopol N1</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
@@ -1318,7 +1318,7 @@
         <v>5</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G13" s="13">
         <f>IFERROR(E13/(E13+F13),0)</f>
@@ -1341,17 +1341,17 @@
       </c>
       <c r="B14" s="17" t="inlineStr">
         <is>
-          <t>38333</t>
+          <t>38458</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Izcalli Mega</t>
+          <t>El Rosario</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E14" s="7" t="n">
@@ -1381,12 +1381,12 @@
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>38339</t>
+          <t>38894</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Galerias Perinorte</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="B18" s="17" t="inlineStr">
         <is>
-          <t>38456</t>
+          <t>38604</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>Plaza las Flores</t>
+          <t>Cosmopol</t>
         </is>
       </c>
       <c r="D18" s="8" t="inlineStr">
@@ -1541,24 +1541,24 @@
       </c>
       <c r="B19" s="15" t="inlineStr">
         <is>
-          <t>43194</t>
+          <t>38456</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>Atana Lindavista</t>
+          <t>Plaza las Flores</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E19" s="11" t="n">
         <v>3</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G19" s="13">
         <f>IFERROR(E19/(E19+F19),0)</f>
@@ -1581,17 +1581,17 @@
       </c>
       <c r="B20" s="17" t="inlineStr">
         <is>
-          <t>38604</t>
+          <t>43194</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>Cosmopol</t>
+          <t>Atana Lindavista</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E20" s="7" t="n">
@@ -3906,7 +3906,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Centro Norte · Corte 01/09/2026 18:42</t>
+          <t>Centro Norte · Corte 01/09/2026 20:26</t>
         </is>
       </c>
     </row>
@@ -4207,10 +4207,10 @@
         </is>
       </c>
       <c r="C12" s="7" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E12" s="9">
         <f>IFERROR(C12/(C12+D12),0)</f>

--- a/exports/Resumen_Evidencias_OPS.xlsx
+++ b/exports/Resumen_Evidencias_OPS.xlsx
@@ -592,7 +592,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Centro Norte · Corte 01/09/2026 20:26</t>
+          <t>Centro Norte · Corte 02/09/2026 10:46</t>
         </is>
       </c>
     </row>
@@ -615,10 +615,10 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>594</v>
+        <v>588</v>
       </c>
       <c r="E6" s="5">
         <f>IFERROR(A6/(A6+C6),0)</f>
@@ -681,10 +681,10 @@
         <v>10</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F10" s="9">
         <f>IFERROR(D10/(D10+E10),0)</f>
@@ -714,10 +714,10 @@
         <v>11</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E11" s="12" t="n">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F11" s="13">
         <f>IFERROR(D11/(D11+E11),0)</f>
@@ -747,10 +747,10 @@
         <v>12</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E12" s="8" t="n">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F12" s="9">
         <f>IFERROR(D12/(D12+E12),0)</f>
@@ -924,7 +924,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Centro Norte · Corte 01/09/2026 20:26</t>
+          <t>Centro Norte · Corte 02/09/2026 10:46</t>
         </is>
       </c>
     </row>
@@ -995,10 +995,10 @@
         </is>
       </c>
       <c r="E5" s="11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G5" s="13">
         <f>IFERROR(E5/(E5+F5),0)</f>
@@ -1061,12 +1061,12 @@
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>38515</t>
+          <t>38368</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>Patio Ecatepec</t>
+          <t>Luna Park</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
@@ -1101,12 +1101,12 @@
       </c>
       <c r="B8" s="17" t="inlineStr">
         <is>
-          <t>38401</t>
+          <t>38515</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>Coacalco</t>
+          <t>Patio Ecatepec</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
@@ -1115,10 +1115,10 @@
         </is>
       </c>
       <c r="E8" s="7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G8" s="9">
         <f>IFERROR(E8/(E8+F8),0)</f>
@@ -1141,12 +1141,12 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>38333</t>
+          <t>38401</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>Izcalli Mega</t>
+          <t>Coacalco</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
@@ -1181,12 +1181,12 @@
       </c>
       <c r="B10" s="17" t="inlineStr">
         <is>
-          <t>38368</t>
+          <t>38333</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>Luna Park</t>
+          <t>Izcalli Mega</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
@@ -1621,12 +1621,12 @@
       </c>
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t>38903</t>
+          <t>38431</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>Encuentro Oceania</t>
+          <t>Eduardo Molina</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
@@ -1661,12 +1661,12 @@
       </c>
       <c r="B22" s="17" t="inlineStr">
         <is>
-          <t>38965</t>
+          <t>38903</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>Parque Tepeyac Piso 2</t>
+          <t>Encuentro Oceania</t>
         </is>
       </c>
       <c r="D22" s="8" t="inlineStr">
@@ -1701,17 +1701,17 @@
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>38924</t>
+          <t>38230</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>Plaza Aeropuerto</t>
+          <t>ITEMS Edo de Mexico</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E23" s="11" t="n">
@@ -1741,17 +1741,17 @@
       </c>
       <c r="B24" s="17" t="inlineStr">
         <is>
-          <t>38606</t>
+          <t>38965</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>TlalnepantlaCarso</t>
+          <t>Parque Tepeyac Piso 2</t>
         </is>
       </c>
       <c r="D24" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E24" s="7" t="n">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="B25" s="15" t="inlineStr">
         <is>
-          <t>38374</t>
+          <t>38924</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>Valle Dorado</t>
+          <t>Plaza Aeropuerto</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E25" s="11" t="n">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="B26" s="17" t="inlineStr">
         <is>
-          <t>38186</t>
+          <t>38136</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>Arboledas</t>
+          <t>Punta Norte</t>
         </is>
       </c>
       <c r="D26" s="8" t="inlineStr">
@@ -1835,10 +1835,10 @@
         </is>
       </c>
       <c r="E26" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F26" s="7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G26" s="9">
         <f>IFERROR(E26/(E26+F26),0)</f>
@@ -1861,24 +1861,24 @@
       </c>
       <c r="B27" s="15" t="inlineStr">
         <is>
-          <t>43043</t>
+          <t>38992</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>Atizapan</t>
+          <t>Tapo Puerta Oriente</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E27" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G27" s="13">
         <f>IFERROR(E27/(E27+F27),0)</f>
@@ -1901,24 +1901,24 @@
       </c>
       <c r="B28" s="17" t="inlineStr">
         <is>
-          <t>38149</t>
+          <t>38606</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>Bellavista</t>
+          <t>TlalnepantlaCarso</t>
         </is>
       </c>
       <c r="D28" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E28" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F28" s="7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G28" s="9">
         <f>IFERROR(E28/(E28+F28),0)</f>
@@ -1941,24 +1941,24 @@
       </c>
       <c r="B29" s="15" t="inlineStr">
         <is>
-          <t>38930</t>
+          <t>38374</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>Blvd. Aeropuerto dt</t>
+          <t>Valle Dorado</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E29" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G29" s="13">
         <f>IFERROR(E29/(E29+F29),0)</f>
@@ -1981,17 +1981,17 @@
       </c>
       <c r="B30" s="17" t="inlineStr">
         <is>
-          <t>38529</t>
+          <t>38186</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>Bosques de Aragon</t>
+          <t>Arboledas</t>
         </is>
       </c>
       <c r="D30" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E30" s="7" t="n">
@@ -2021,17 +2021,17 @@
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>38527</t>
+          <t>43043</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>Camarones</t>
+          <t>Atizapan</t>
         </is>
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E31" s="11" t="n">
@@ -2061,17 +2061,17 @@
       </c>
       <c r="B32" s="17" t="inlineStr">
         <is>
-          <t>38837</t>
+          <t>38149</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>Centenario Azcapotzalco</t>
+          <t>Bellavista</t>
         </is>
       </c>
       <c r="D32" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E32" s="7" t="n">
@@ -2101,17 +2101,17 @@
       </c>
       <c r="B33" s="15" t="inlineStr">
         <is>
-          <t>38394</t>
+          <t>38930</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>Centro Comercial Lomas Verdes</t>
+          <t>Blvd. Aeropuerto dt</t>
         </is>
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E33" s="11" t="n">
@@ -2141,17 +2141,17 @@
       </c>
       <c r="B34" s="17" t="inlineStr">
         <is>
-          <t>38535</t>
+          <t>38529</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>City Center Esmeralda</t>
+          <t>Bosques de Aragon</t>
         </is>
       </c>
       <c r="D34" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E34" s="7" t="n">
@@ -2181,17 +2181,17 @@
       </c>
       <c r="B35" s="15" t="inlineStr">
         <is>
-          <t>38431</t>
+          <t>38527</t>
         </is>
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>Eduardo Molina</t>
+          <t>Camarones</t>
         </is>
       </c>
       <c r="D35" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E35" s="11" t="n">
@@ -2221,17 +2221,17 @@
       </c>
       <c r="B36" s="17" t="inlineStr">
         <is>
-          <t>38995</t>
+          <t>38837</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>Encuentro Oceania II</t>
+          <t>Centenario Azcapotzalco</t>
         </is>
       </c>
       <c r="D36" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E36" s="7" t="n">
@@ -2261,12 +2261,12 @@
       </c>
       <c r="B37" s="15" t="inlineStr">
         <is>
-          <t>38507</t>
+          <t>38394</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>Espacio Vista del Valle</t>
+          <t>Centro Comercial Lomas Verdes</t>
         </is>
       </c>
       <c r="D37" s="12" t="inlineStr">
@@ -2301,12 +2301,12 @@
       </c>
       <c r="B38" s="17" t="inlineStr">
         <is>
-          <t>38363</t>
+          <t>38535</t>
         </is>
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>Galerias Atizapan</t>
+          <t>City Center Esmeralda</t>
         </is>
       </c>
       <c r="D38" s="8" t="inlineStr">
@@ -2341,17 +2341,17 @@
       </c>
       <c r="B39" s="15" t="inlineStr">
         <is>
-          <t>38230</t>
+          <t>38995</t>
         </is>
       </c>
       <c r="C39" s="12" t="inlineStr">
         <is>
-          <t>ITEMS Edo de Mexico</t>
+          <t>Encuentro Oceania II</t>
         </is>
       </c>
       <c r="D39" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E39" s="11" t="n">
@@ -2381,17 +2381,17 @@
       </c>
       <c r="B40" s="17" t="inlineStr">
         <is>
-          <t>38205</t>
+          <t>38507</t>
         </is>
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>Lindavista</t>
+          <t>Espacio Vista del Valle</t>
         </is>
       </c>
       <c r="D40" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E40" s="7" t="n">
@@ -2421,17 +2421,17 @@
       </c>
       <c r="B41" s="15" t="inlineStr">
         <is>
-          <t>38371</t>
+          <t>38363</t>
         </is>
       </c>
       <c r="C41" s="12" t="inlineStr">
         <is>
-          <t>Montevideo DT</t>
+          <t>Galerias Atizapan</t>
         </is>
       </c>
       <c r="D41" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E41" s="11" t="n">
@@ -2461,12 +2461,12 @@
       </c>
       <c r="B42" s="17" t="inlineStr">
         <is>
-          <t>43111</t>
+          <t>38205</t>
         </is>
       </c>
       <c r="C42" s="8" t="inlineStr">
         <is>
-          <t>Montevideo Insurgentes</t>
+          <t>Lindavista</t>
         </is>
       </c>
       <c r="D42" s="8" t="inlineStr">
@@ -2501,17 +2501,17 @@
       </c>
       <c r="B43" s="15" t="inlineStr">
         <is>
-          <t>38674</t>
+          <t>38371</t>
         </is>
       </c>
       <c r="C43" s="12" t="inlineStr">
         <is>
-          <t>Mundo E</t>
+          <t>Montevideo DT</t>
         </is>
       </c>
       <c r="D43" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E43" s="11" t="n">
@@ -2541,12 +2541,12 @@
       </c>
       <c r="B44" s="17" t="inlineStr">
         <is>
-          <t>43195</t>
+          <t>43111</t>
         </is>
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t>Parque Jadin kiosko</t>
+          <t>Montevideo Insurgentes</t>
         </is>
       </c>
       <c r="D44" s="8" t="inlineStr">
@@ -2581,17 +2581,17 @@
       </c>
       <c r="B45" s="15" t="inlineStr">
         <is>
-          <t>38937</t>
+          <t>38674</t>
         </is>
       </c>
       <c r="C45" s="12" t="inlineStr">
         <is>
-          <t>Parque Tepeyac Piso 1</t>
+          <t>Mundo E</t>
         </is>
       </c>
       <c r="D45" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E45" s="11" t="n">
@@ -2621,17 +2621,17 @@
       </c>
       <c r="B46" s="17" t="inlineStr">
         <is>
-          <t>38792</t>
+          <t>43195</t>
         </is>
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t>Pasaje Tlanepantla</t>
+          <t>Parque Jadin kiosko</t>
         </is>
       </c>
       <c r="D46" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E46" s="7" t="n">
@@ -2661,17 +2661,17 @@
       </c>
       <c r="B47" s="15" t="inlineStr">
         <is>
-          <t>38546</t>
+          <t>38937</t>
         </is>
       </c>
       <c r="C47" s="12" t="inlineStr">
         <is>
-          <t>Patio Claveria</t>
+          <t>Parque Tepeyac Piso 1</t>
         </is>
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E47" s="11" t="n">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="B48" s="17" t="inlineStr">
         <is>
-          <t>38677</t>
+          <t>38792</t>
         </is>
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
-          <t>Patio la Raza</t>
+          <t>Pasaje Tlanepantla</t>
         </is>
       </c>
       <c r="D48" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E48" s="7" t="n">
@@ -2741,17 +2741,17 @@
       </c>
       <c r="B49" s="15" t="inlineStr">
         <is>
-          <t>38859</t>
+          <t>38546</t>
         </is>
       </c>
       <c r="C49" s="12" t="inlineStr">
         <is>
-          <t>Plaza Satelite II N1</t>
+          <t>Patio Claveria</t>
         </is>
       </c>
       <c r="D49" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E49" s="11" t="n">
@@ -2781,17 +2781,17 @@
       </c>
       <c r="B50" s="17" t="inlineStr">
         <is>
-          <t>38811</t>
+          <t>38677</t>
         </is>
       </c>
       <c r="C50" s="8" t="inlineStr">
         <is>
-          <t>Plaza Tepeyac</t>
+          <t>Patio la Raza</t>
         </is>
       </c>
       <c r="D50" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E50" s="7" t="n">
@@ -2821,17 +2821,17 @@
       </c>
       <c r="B51" s="15" t="inlineStr">
         <is>
-          <t>43132</t>
+          <t>38859</t>
         </is>
       </c>
       <c r="C51" s="12" t="inlineStr">
         <is>
-          <t>Plaza Vista Norte</t>
+          <t>Plaza Satelite II N1</t>
         </is>
       </c>
       <c r="D51" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E51" s="11" t="n">
@@ -2861,17 +2861,17 @@
       </c>
       <c r="B52" s="17" t="inlineStr">
         <is>
-          <t>38136</t>
+          <t>38811</t>
         </is>
       </c>
       <c r="C52" s="8" t="inlineStr">
         <is>
-          <t>Punta Norte</t>
+          <t>Plaza Tepeyac</t>
         </is>
       </c>
       <c r="D52" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E52" s="7" t="n">
@@ -2901,17 +2901,17 @@
       </c>
       <c r="B53" s="15" t="inlineStr">
         <is>
-          <t>38460</t>
+          <t>43132</t>
         </is>
       </c>
       <c r="C53" s="12" t="inlineStr">
         <is>
-          <t>Santa Monica</t>
+          <t>Plaza Vista Norte</t>
         </is>
       </c>
       <c r="D53" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E53" s="11" t="n">
@@ -2941,17 +2941,17 @@
       </c>
       <c r="B54" s="17" t="inlineStr">
         <is>
-          <t>38475</t>
+          <t>38460</t>
         </is>
       </c>
       <c r="C54" s="8" t="inlineStr">
         <is>
-          <t>Satelite Centro Civico</t>
+          <t>Santa Monica</t>
         </is>
       </c>
       <c r="D54" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E54" s="7" t="n">
@@ -2981,17 +2981,17 @@
       </c>
       <c r="B55" s="15" t="inlineStr">
         <is>
-          <t>38442</t>
+          <t>38475</t>
         </is>
       </c>
       <c r="C55" s="12" t="inlineStr">
         <is>
-          <t>Sor Juana</t>
+          <t>Satelite Centro Civico</t>
         </is>
       </c>
       <c r="D55" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E55" s="11" t="n">
@@ -3021,17 +3021,17 @@
       </c>
       <c r="B56" s="17" t="inlineStr">
         <is>
-          <t>38925</t>
+          <t>38442</t>
         </is>
       </c>
       <c r="C56" s="8" t="inlineStr">
         <is>
-          <t>Star Medica Lomas Verdes</t>
+          <t>Sor Juana</t>
         </is>
       </c>
       <c r="D56" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E56" s="7" t="n">
@@ -3061,17 +3061,17 @@
       </c>
       <c r="B57" s="15" t="inlineStr">
         <is>
-          <t>38992</t>
+          <t>38925</t>
         </is>
       </c>
       <c r="C57" s="12" t="inlineStr">
         <is>
-          <t>Tapo Puerta Oriente</t>
+          <t>Star Medica Lomas Verdes</t>
         </is>
       </c>
       <c r="D57" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E57" s="11" t="n">
@@ -3906,7 +3906,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Centro Norte · Corte 01/09/2026 20:26</t>
+          <t>Centro Norte · Corte 02/09/2026 10:46</t>
         </is>
       </c>
     </row>
@@ -3962,10 +3962,10 @@
         </is>
       </c>
       <c r="C5" s="11" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E5" s="13">
         <f>IFERROR(C5/(C5+D5),0)</f>
@@ -3997,10 +3997,10 @@
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D6" s="7" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E6" s="9">
         <f>IFERROR(C6/(C6+D6),0)</f>
@@ -4172,10 +4172,10 @@
         </is>
       </c>
       <c r="C11" s="11" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E11" s="13">
         <f>IFERROR(C11/(C11+D11),0)</f>
@@ -4207,10 +4207,10 @@
         </is>
       </c>
       <c r="C12" s="7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E12" s="9">
         <f>IFERROR(C12/(C12+D12),0)</f>

--- a/exports/Resumen_Evidencias_OPS.xlsx
+++ b/exports/Resumen_Evidencias_OPS.xlsx
@@ -592,7 +592,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Centro Norte · Corte 02/09/2026 10:46</t>
+          <t>Centro Norte · Corte 02/09/2026 20:23</t>
         </is>
       </c>
     </row>
@@ -615,10 +615,10 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>198</v>
+        <v>256</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>588</v>
+        <v>527</v>
       </c>
       <c r="E6" s="5">
         <f>IFERROR(A6/(A6+C6),0)</f>
@@ -707,30 +707,30 @@
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia</t>
+          <t>Yazmin Chabela</t>
         </is>
       </c>
       <c r="C11" s="11" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="E11" s="12" t="n">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="F11" s="13">
         <f>IFERROR(D11/(D11+E11),0)</f>
         <v/>
       </c>
-      <c r="G11" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="H11" s="14" t="inlineStr">
-        <is>
-          <t>Priorizar hoy</t>
+      <c r="G11" s="10" t="inlineStr">
+        <is>
+          <t>Seguimiento</t>
+        </is>
+      </c>
+      <c r="H11" s="10" t="inlineStr">
+        <is>
+          <t>Dar seguimiento</t>
         </is>
       </c>
     </row>
@@ -740,17 +740,17 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina</t>
+          <t>Veronica Garcia</t>
         </is>
       </c>
       <c r="C12" s="7" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="E12" s="8" t="n">
-        <v>102</v>
+        <v>77</v>
       </c>
       <c r="F12" s="9">
         <f>IFERROR(D12/(D12+E12),0)</f>
@@ -773,17 +773,17 @@
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela</t>
+          <t>Nancy Carolina</t>
         </is>
       </c>
       <c r="C13" s="11" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D13" s="11" t="n">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="E13" s="12" t="n">
-        <v>116</v>
+        <v>91</v>
       </c>
       <c r="F13" s="13">
         <f>IFERROR(D13/(D13+E13),0)</f>
@@ -813,10 +813,10 @@
         <v>13</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E14" s="8" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F14" s="9">
         <f>IFERROR(D14/(D14+E14),0)</f>
@@ -846,10 +846,10 @@
         <v>13</v>
       </c>
       <c r="D15" s="11" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E15" s="12" t="n">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="F15" s="13">
         <f>IFERROR(D15/(D15+E15),0)</f>
@@ -924,7 +924,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Centro Norte · Corte 02/09/2026 10:46</t>
+          <t>Centro Norte · Corte 02/09/2026 20:23</t>
         </is>
       </c>
     </row>
@@ -1061,24 +1061,24 @@
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>38368</t>
+          <t>38903</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>Luna Park</t>
+          <t>Encuentro Oceania</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E7" s="11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G7" s="13">
         <f>IFERROR(E7/(E7+F7),0)</f>
@@ -1101,24 +1101,24 @@
       </c>
       <c r="B8" s="17" t="inlineStr">
         <is>
-          <t>38515</t>
+          <t>38561</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>Patio Ecatepec</t>
+          <t>Parque Toreo</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E8" s="7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G8" s="9">
         <f>IFERROR(E8/(E8+F8),0)</f>
@@ -1141,24 +1141,24 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>38401</t>
+          <t>38590</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>Coacalco</t>
+          <t>Parque Toreo II</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E9" s="11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G9" s="13">
         <f>IFERROR(E9/(E9+F9),0)</f>
@@ -1181,24 +1181,24 @@
       </c>
       <c r="B10" s="17" t="inlineStr">
         <is>
-          <t>38333</t>
+          <t>38695</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>Izcalli Mega</t>
+          <t>Cetram 4 Caminos</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E10" s="7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G10" s="9">
         <f>IFERROR(E10/(E10+F10),0)</f>
@@ -1221,12 +1221,12 @@
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>38561</t>
+          <t>38458</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>Parque Toreo</t>
+          <t>El Rosario</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
@@ -1235,10 +1235,10 @@
         </is>
       </c>
       <c r="E11" s="11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G11" s="13">
         <f>IFERROR(E11/(E11+F11),0)</f>
@@ -1261,12 +1261,12 @@
       </c>
       <c r="B12" s="17" t="inlineStr">
         <is>
-          <t>38339</t>
+          <t>38368</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Luna Park</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="E12" s="7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F12" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G12" s="9">
         <f>IFERROR(E12/(E12+F12),0)</f>
@@ -1301,24 +1301,24 @@
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>43193</t>
+          <t>38674</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>Cosmopol N1</t>
+          <t>Mundo E</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E13" s="11" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G13" s="13">
         <f>IFERROR(E13/(E13+F13),0)</f>
@@ -1341,24 +1341,24 @@
       </c>
       <c r="B14" s="17" t="inlineStr">
         <is>
-          <t>38458</t>
+          <t>38515</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>El Rosario</t>
+          <t>Patio Ecatepec</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E14" s="7" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F14" s="7" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G14" s="9">
         <f>IFERROR(E14/(E14+F14),0)</f>
@@ -1381,24 +1381,24 @@
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>38894</t>
+          <t>38859</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>Galerias Perinorte</t>
+          <t>Plaza Satelite II N1</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E15" s="11" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G15" s="13">
         <f>IFERROR(E15/(E15+F15),0)</f>
@@ -1421,37 +1421,37 @@
       </c>
       <c r="B16" s="17" t="inlineStr">
         <is>
-          <t>38695</t>
+          <t>38401</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>Cetram 4 Caminos</t>
+          <t>Coacalco</t>
         </is>
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E16" s="7" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F16" s="7" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G16" s="9">
         <f>IFERROR(E16/(E16+F16),0)</f>
         <v/>
       </c>
-      <c r="H16" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I16" s="14" t="inlineStr">
-        <is>
-          <t>Priorizar hoy</t>
+      <c r="H16" s="10" t="inlineStr">
+        <is>
+          <t>Seguimiento</t>
+        </is>
+      </c>
+      <c r="I16" s="10" t="inlineStr">
+        <is>
+          <t>Dar seguimiento</t>
         </is>
       </c>
     </row>
@@ -1461,37 +1461,37 @@
       </c>
       <c r="B17" s="15" t="inlineStr">
         <is>
-          <t>38661</t>
+          <t>38333</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>Jinetes</t>
+          <t>Izcalli Mega</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E17" s="11" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G17" s="13">
         <f>IFERROR(E17/(E17+F17),0)</f>
         <v/>
       </c>
-      <c r="H17" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I17" s="14" t="inlineStr">
-        <is>
-          <t>Priorizar hoy</t>
+      <c r="H17" s="10" t="inlineStr">
+        <is>
+          <t>Seguimiento</t>
+        </is>
+      </c>
+      <c r="I17" s="10" t="inlineStr">
+        <is>
+          <t>Dar seguimiento</t>
         </is>
       </c>
     </row>
@@ -1501,12 +1501,12 @@
       </c>
       <c r="B18" s="17" t="inlineStr">
         <is>
-          <t>38604</t>
+          <t>38339</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>Cosmopol</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="D18" s="8" t="inlineStr">
@@ -1515,23 +1515,23 @@
         </is>
       </c>
       <c r="E18" s="7" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F18" s="7" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G18" s="9">
         <f>IFERROR(E18/(E18+F18),0)</f>
         <v/>
       </c>
-      <c r="H18" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I18" s="14" t="inlineStr">
-        <is>
-          <t>Priorizar hoy</t>
+      <c r="H18" s="10" t="inlineStr">
+        <is>
+          <t>Seguimiento</t>
+        </is>
+      </c>
+      <c r="I18" s="10" t="inlineStr">
+        <is>
+          <t>Dar seguimiento</t>
         </is>
       </c>
     </row>
@@ -1541,37 +1541,37 @@
       </c>
       <c r="B19" s="15" t="inlineStr">
         <is>
-          <t>38456</t>
+          <t>38117</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>Plaza las Flores</t>
+          <t>Satelite</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E19" s="11" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G19" s="13">
         <f>IFERROR(E19/(E19+F19),0)</f>
         <v/>
       </c>
-      <c r="H19" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I19" s="14" t="inlineStr">
-        <is>
-          <t>Priorizar hoy</t>
+      <c r="H19" s="10" t="inlineStr">
+        <is>
+          <t>Seguimiento</t>
+        </is>
+      </c>
+      <c r="I19" s="10" t="inlineStr">
+        <is>
+          <t>Dar seguimiento</t>
         </is>
       </c>
     </row>
@@ -1581,37 +1581,37 @@
       </c>
       <c r="B20" s="17" t="inlineStr">
         <is>
-          <t>43194</t>
+          <t>38475</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>Atana Lindavista</t>
+          <t>Satelite Centro Civico</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E20" s="7" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F20" s="7" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G20" s="9">
         <f>IFERROR(E20/(E20+F20),0)</f>
         <v/>
       </c>
-      <c r="H20" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I20" s="14" t="inlineStr">
-        <is>
-          <t>Priorizar hoy</t>
+      <c r="H20" s="10" t="inlineStr">
+        <is>
+          <t>Seguimiento</t>
+        </is>
+      </c>
+      <c r="I20" s="10" t="inlineStr">
+        <is>
+          <t>Dar seguimiento</t>
         </is>
       </c>
     </row>
@@ -1621,37 +1621,37 @@
       </c>
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t>38431</t>
+          <t>43193</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>Eduardo Molina</t>
+          <t>Cosmopol N1</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E21" s="11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G21" s="13">
         <f>IFERROR(E21/(E21+F21),0)</f>
         <v/>
       </c>
-      <c r="H21" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I21" s="14" t="inlineStr">
-        <is>
-          <t>Priorizar hoy</t>
+      <c r="H21" s="10" t="inlineStr">
+        <is>
+          <t>Seguimiento</t>
+        </is>
+      </c>
+      <c r="I21" s="10" t="inlineStr">
+        <is>
+          <t>Dar seguimiento</t>
         </is>
       </c>
     </row>
@@ -1661,37 +1661,37 @@
       </c>
       <c r="B22" s="17" t="inlineStr">
         <is>
-          <t>38903</t>
+          <t>38894</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>Encuentro Oceania</t>
+          <t>Galerias Perinorte</t>
         </is>
       </c>
       <c r="D22" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E22" s="7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G22" s="9">
         <f>IFERROR(E22/(E22+F22),0)</f>
         <v/>
       </c>
-      <c r="H22" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I22" s="14" t="inlineStr">
-        <is>
-          <t>Priorizar hoy</t>
+      <c r="H22" s="10" t="inlineStr">
+        <is>
+          <t>Seguimiento</t>
+        </is>
+      </c>
+      <c r="I22" s="10" t="inlineStr">
+        <is>
+          <t>Dar seguimiento</t>
         </is>
       </c>
     </row>
@@ -1701,12 +1701,12 @@
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>38230</t>
+          <t>38661</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>ITEMS Edo de Mexico</t>
+          <t>Jinetes</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr">
@@ -1715,23 +1715,23 @@
         </is>
       </c>
       <c r="E23" s="11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G23" s="13">
         <f>IFERROR(E23/(E23+F23),0)</f>
         <v/>
       </c>
-      <c r="H23" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I23" s="14" t="inlineStr">
-        <is>
-          <t>Priorizar hoy</t>
+      <c r="H23" s="10" t="inlineStr">
+        <is>
+          <t>Seguimiento</t>
+        </is>
+      </c>
+      <c r="I23" s="10" t="inlineStr">
+        <is>
+          <t>Dar seguimiento</t>
         </is>
       </c>
     </row>
@@ -1741,37 +1741,37 @@
       </c>
       <c r="B24" s="17" t="inlineStr">
         <is>
-          <t>38965</t>
+          <t>38606</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>Parque Tepeyac Piso 2</t>
+          <t>TlalnepantlaCarso</t>
         </is>
       </c>
       <c r="D24" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E24" s="7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F24" s="7" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G24" s="9">
         <f>IFERROR(E24/(E24+F24),0)</f>
         <v/>
       </c>
-      <c r="H24" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I24" s="14" t="inlineStr">
-        <is>
-          <t>Priorizar hoy</t>
+      <c r="H24" s="10" t="inlineStr">
+        <is>
+          <t>Seguimiento</t>
+        </is>
+      </c>
+      <c r="I24" s="10" t="inlineStr">
+        <is>
+          <t>Dar seguimiento</t>
         </is>
       </c>
     </row>
@@ -1781,37 +1781,37 @@
       </c>
       <c r="B25" s="15" t="inlineStr">
         <is>
-          <t>38924</t>
+          <t>38374</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>Plaza Aeropuerto</t>
+          <t>Valle Dorado</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E25" s="11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G25" s="13">
         <f>IFERROR(E25/(E25+F25),0)</f>
         <v/>
       </c>
-      <c r="H25" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I25" s="14" t="inlineStr">
-        <is>
-          <t>Priorizar hoy</t>
+      <c r="H25" s="10" t="inlineStr">
+        <is>
+          <t>Seguimiento</t>
+        </is>
+      </c>
+      <c r="I25" s="10" t="inlineStr">
+        <is>
+          <t>Dar seguimiento</t>
         </is>
       </c>
     </row>
@@ -1821,24 +1821,24 @@
       </c>
       <c r="B26" s="17" t="inlineStr">
         <is>
-          <t>38136</t>
+          <t>38937</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>Punta Norte</t>
+          <t>Parque Tepeyac Piso 1</t>
         </is>
       </c>
       <c r="D26" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E26" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F26" s="7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G26" s="9">
         <f>IFERROR(E26/(E26+F26),0)</f>
@@ -1861,24 +1861,24 @@
       </c>
       <c r="B27" s="15" t="inlineStr">
         <is>
-          <t>38992</t>
+          <t>38427</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>Tapo Puerta Oriente</t>
+          <t>Plaza Satelite</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E27" s="11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G27" s="13">
         <f>IFERROR(E27/(E27+F27),0)</f>
@@ -1901,24 +1901,24 @@
       </c>
       <c r="B28" s="17" t="inlineStr">
         <is>
-          <t>38606</t>
+          <t>38604</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>TlalnepantlaCarso</t>
+          <t>Cosmopol</t>
         </is>
       </c>
       <c r="D28" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E28" s="7" t="n">
         <v>3</v>
       </c>
       <c r="F28" s="7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G28" s="9">
         <f>IFERROR(E28/(E28+F28),0)</f>
@@ -1941,24 +1941,24 @@
       </c>
       <c r="B29" s="15" t="inlineStr">
         <is>
-          <t>38374</t>
+          <t>38770</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>Valle Dorado</t>
+          <t>Gustavo Baz 29</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E29" s="11" t="n">
         <v>3</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G29" s="13">
         <f>IFERROR(E29/(E29+F29),0)</f>
@@ -1981,24 +1981,24 @@
       </c>
       <c r="B30" s="17" t="inlineStr">
         <is>
-          <t>38186</t>
+          <t>38456</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>Arboledas</t>
+          <t>Plaza las Flores</t>
         </is>
       </c>
       <c r="D30" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E30" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F30" s="7" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G30" s="9">
         <f>IFERROR(E30/(E30+F30),0)</f>
@@ -2021,24 +2021,24 @@
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>43043</t>
+          <t>43152</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>Atizapan</t>
+          <t>Samara Satélite</t>
         </is>
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E31" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G31" s="13">
         <f>IFERROR(E31/(E31+F31),0)</f>
@@ -2061,24 +2061,24 @@
       </c>
       <c r="B32" s="17" t="inlineStr">
         <is>
-          <t>38149</t>
+          <t>43194</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>Bellavista</t>
+          <t>Atana Lindavista</t>
         </is>
       </c>
       <c r="D32" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E32" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F32" s="7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G32" s="9">
         <f>IFERROR(E32/(E32+F32),0)</f>
@@ -2115,10 +2115,10 @@
         </is>
       </c>
       <c r="E33" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G33" s="13">
         <f>IFERROR(E33/(E33+F33),0)</f>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="E34" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F34" s="7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G34" s="9">
         <f>IFERROR(E34/(E34+F34),0)</f>
@@ -2181,24 +2181,24 @@
       </c>
       <c r="B35" s="15" t="inlineStr">
         <is>
-          <t>38527</t>
+          <t>38431</t>
         </is>
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>Camarones</t>
+          <t>Eduardo Molina</t>
         </is>
       </c>
       <c r="D35" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E35" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G35" s="13">
         <f>IFERROR(E35/(E35+F35),0)</f>
@@ -2221,24 +2221,24 @@
       </c>
       <c r="B36" s="17" t="inlineStr">
         <is>
-          <t>38837</t>
+          <t>38230</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>Centenario Azcapotzalco</t>
+          <t>ITEMS Edo de Mexico</t>
         </is>
       </c>
       <c r="D36" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E36" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F36" s="7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G36" s="9">
         <f>IFERROR(E36/(E36+F36),0)</f>
@@ -2261,24 +2261,24 @@
       </c>
       <c r="B37" s="15" t="inlineStr">
         <is>
-          <t>38394</t>
+          <t>38965</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>Centro Comercial Lomas Verdes</t>
+          <t>Parque Tepeyac Piso 2</t>
         </is>
       </c>
       <c r="D37" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E37" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G37" s="13">
         <f>IFERROR(E37/(E37+F37),0)</f>
@@ -2301,24 +2301,24 @@
       </c>
       <c r="B38" s="17" t="inlineStr">
         <is>
-          <t>38535</t>
+          <t>38792</t>
         </is>
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>City Center Esmeralda</t>
+          <t>Pasaje Tlanepantla</t>
         </is>
       </c>
       <c r="D38" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E38" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F38" s="7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G38" s="9">
         <f>IFERROR(E38/(E38+F38),0)</f>
@@ -2341,12 +2341,12 @@
       </c>
       <c r="B39" s="15" t="inlineStr">
         <is>
-          <t>38995</t>
+          <t>38924</t>
         </is>
       </c>
       <c r="C39" s="12" t="inlineStr">
         <is>
-          <t>Encuentro Oceania II</t>
+          <t>Plaza Aeropuerto</t>
         </is>
       </c>
       <c r="D39" s="12" t="inlineStr">
@@ -2355,10 +2355,10 @@
         </is>
       </c>
       <c r="E39" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G39" s="13">
         <f>IFERROR(E39/(E39+F39),0)</f>
@@ -2381,24 +2381,24 @@
       </c>
       <c r="B40" s="17" t="inlineStr">
         <is>
-          <t>38507</t>
+          <t>38811</t>
         </is>
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>Espacio Vista del Valle</t>
+          <t>Plaza Tepeyac</t>
         </is>
       </c>
       <c r="D40" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E40" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F40" s="7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G40" s="9">
         <f>IFERROR(E40/(E40+F40),0)</f>
@@ -2421,24 +2421,24 @@
       </c>
       <c r="B41" s="15" t="inlineStr">
         <is>
-          <t>38363</t>
+          <t>38136</t>
         </is>
       </c>
       <c r="C41" s="12" t="inlineStr">
         <is>
-          <t>Galerias Atizapan</t>
+          <t>Punta Norte</t>
         </is>
       </c>
       <c r="D41" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E41" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G41" s="13">
         <f>IFERROR(E41/(E41+F41),0)</f>
@@ -2461,24 +2461,24 @@
       </c>
       <c r="B42" s="17" t="inlineStr">
         <is>
-          <t>38205</t>
+          <t>38992</t>
         </is>
       </c>
       <c r="C42" s="8" t="inlineStr">
         <is>
-          <t>Lindavista</t>
+          <t>Tapo Puerta Oriente</t>
         </is>
       </c>
       <c r="D42" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E42" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F42" s="7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G42" s="9">
         <f>IFERROR(E42/(E42+F42),0)</f>
@@ -2501,12 +2501,12 @@
       </c>
       <c r="B43" s="15" t="inlineStr">
         <is>
-          <t>38371</t>
+          <t>38651</t>
         </is>
       </c>
       <c r="C43" s="12" t="inlineStr">
         <is>
-          <t>Montevideo DT</t>
+          <t>Via Vallejo</t>
         </is>
       </c>
       <c r="D43" s="12" t="inlineStr">
@@ -2515,10 +2515,10 @@
         </is>
       </c>
       <c r="E43" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G43" s="13">
         <f>IFERROR(E43/(E43+F43),0)</f>
@@ -2541,17 +2541,17 @@
       </c>
       <c r="B44" s="17" t="inlineStr">
         <is>
-          <t>43111</t>
+          <t>38186</t>
         </is>
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t>Montevideo Insurgentes</t>
+          <t>Arboledas</t>
         </is>
       </c>
       <c r="D44" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E44" s="7" t="n">
@@ -2581,17 +2581,17 @@
       </c>
       <c r="B45" s="15" t="inlineStr">
         <is>
-          <t>38674</t>
+          <t>43043</t>
         </is>
       </c>
       <c r="C45" s="12" t="inlineStr">
         <is>
-          <t>Mundo E</t>
+          <t>Atizapan</t>
         </is>
       </c>
       <c r="D45" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E45" s="11" t="n">
@@ -2621,17 +2621,17 @@
       </c>
       <c r="B46" s="17" t="inlineStr">
         <is>
-          <t>43195</t>
+          <t>38149</t>
         </is>
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t>Parque Jadin kiosko</t>
+          <t>Bellavista</t>
         </is>
       </c>
       <c r="D46" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E46" s="7" t="n">
@@ -2661,17 +2661,17 @@
       </c>
       <c r="B47" s="15" t="inlineStr">
         <is>
-          <t>38937</t>
+          <t>38527</t>
         </is>
       </c>
       <c r="C47" s="12" t="inlineStr">
         <is>
-          <t>Parque Tepeyac Piso 1</t>
+          <t>Camarones</t>
         </is>
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E47" s="11" t="n">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="B48" s="17" t="inlineStr">
         <is>
-          <t>38792</t>
+          <t>38837</t>
         </is>
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
-          <t>Pasaje Tlanepantla</t>
+          <t>Centenario Azcapotzalco</t>
         </is>
       </c>
       <c r="D48" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E48" s="7" t="n">
@@ -2741,17 +2741,17 @@
       </c>
       <c r="B49" s="15" t="inlineStr">
         <is>
-          <t>38546</t>
+          <t>38394</t>
         </is>
       </c>
       <c r="C49" s="12" t="inlineStr">
         <is>
-          <t>Patio Claveria</t>
+          <t>Centro Comercial Lomas Verdes</t>
         </is>
       </c>
       <c r="D49" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E49" s="11" t="n">
@@ -2781,17 +2781,17 @@
       </c>
       <c r="B50" s="17" t="inlineStr">
         <is>
-          <t>38677</t>
+          <t>38535</t>
         </is>
       </c>
       <c r="C50" s="8" t="inlineStr">
         <is>
-          <t>Patio la Raza</t>
+          <t>City Center Esmeralda</t>
         </is>
       </c>
       <c r="D50" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E50" s="7" t="n">
@@ -2821,17 +2821,17 @@
       </c>
       <c r="B51" s="15" t="inlineStr">
         <is>
-          <t>38859</t>
+          <t>38995</t>
         </is>
       </c>
       <c r="C51" s="12" t="inlineStr">
         <is>
-          <t>Plaza Satelite II N1</t>
+          <t>Encuentro Oceania II</t>
         </is>
       </c>
       <c r="D51" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E51" s="11" t="n">
@@ -2861,17 +2861,17 @@
       </c>
       <c r="B52" s="17" t="inlineStr">
         <is>
-          <t>38811</t>
+          <t>38507</t>
         </is>
       </c>
       <c r="C52" s="8" t="inlineStr">
         <is>
-          <t>Plaza Tepeyac</t>
+          <t>Espacio Vista del Valle</t>
         </is>
       </c>
       <c r="D52" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E52" s="7" t="n">
@@ -2901,17 +2901,17 @@
       </c>
       <c r="B53" s="15" t="inlineStr">
         <is>
-          <t>43132</t>
+          <t>38363</t>
         </is>
       </c>
       <c r="C53" s="12" t="inlineStr">
         <is>
-          <t>Plaza Vista Norte</t>
+          <t>Galerias Atizapan</t>
         </is>
       </c>
       <c r="D53" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E53" s="11" t="n">
@@ -2941,17 +2941,17 @@
       </c>
       <c r="B54" s="17" t="inlineStr">
         <is>
-          <t>38460</t>
+          <t>38205</t>
         </is>
       </c>
       <c r="C54" s="8" t="inlineStr">
         <is>
-          <t>Santa Monica</t>
+          <t>Lindavista</t>
         </is>
       </c>
       <c r="D54" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E54" s="7" t="n">
@@ -2981,17 +2981,17 @@
       </c>
       <c r="B55" s="15" t="inlineStr">
         <is>
-          <t>38475</t>
+          <t>38119</t>
         </is>
       </c>
       <c r="C55" s="12" t="inlineStr">
         <is>
-          <t>Satelite Centro Civico</t>
+          <t>Lomas Verdes</t>
         </is>
       </c>
       <c r="D55" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E55" s="11" t="n">
@@ -3021,17 +3021,17 @@
       </c>
       <c r="B56" s="17" t="inlineStr">
         <is>
-          <t>38442</t>
+          <t>38270</t>
         </is>
       </c>
       <c r="C56" s="8" t="inlineStr">
         <is>
-          <t>Sor Juana</t>
+          <t>Lomas Verdes II</t>
         </is>
       </c>
       <c r="D56" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E56" s="7" t="n">
@@ -3061,17 +3061,17 @@
       </c>
       <c r="B57" s="15" t="inlineStr">
         <is>
-          <t>38925</t>
+          <t>38371</t>
         </is>
       </c>
       <c r="C57" s="12" t="inlineStr">
         <is>
-          <t>Star Medica Lomas Verdes</t>
+          <t>Montevideo DT</t>
         </is>
       </c>
       <c r="D57" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E57" s="11" t="n">
@@ -3101,12 +3101,12 @@
       </c>
       <c r="B58" s="17" t="inlineStr">
         <is>
-          <t>38411</t>
+          <t>43111</t>
         </is>
       </c>
       <c r="C58" s="8" t="inlineStr">
         <is>
-          <t>Torres Lindavista</t>
+          <t>Montevideo Insurgentes</t>
         </is>
       </c>
       <c r="D58" s="8" t="inlineStr">
@@ -3141,17 +3141,17 @@
       </c>
       <c r="B59" s="15" t="inlineStr">
         <is>
-          <t>43130</t>
+          <t>43195</t>
         </is>
       </c>
       <c r="C59" s="12" t="inlineStr">
         <is>
-          <t>Town Center Nicolás Romero</t>
+          <t>Parque Jadin kiosko</t>
         </is>
       </c>
       <c r="D59" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E59" s="11" t="n">
@@ -3181,12 +3181,12 @@
       </c>
       <c r="B60" s="17" t="inlineStr">
         <is>
-          <t>38651</t>
+          <t>38546</t>
         </is>
       </c>
       <c r="C60" s="8" t="inlineStr">
         <is>
-          <t>Via Vallejo</t>
+          <t>Patio Claveria</t>
         </is>
       </c>
       <c r="D60" s="8" t="inlineStr">
@@ -3221,17 +3221,17 @@
       </c>
       <c r="B61" s="15" t="inlineStr">
         <is>
-          <t>38694</t>
+          <t>38677</t>
         </is>
       </c>
       <c r="C61" s="12" t="inlineStr">
         <is>
-          <t>Villas de la Hacienda</t>
+          <t>Patio la Raza</t>
         </is>
       </c>
       <c r="D61" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E61" s="11" t="n">
@@ -3261,17 +3261,17 @@
       </c>
       <c r="B62" s="17" t="inlineStr">
         <is>
-          <t>38115</t>
+          <t>43132</t>
         </is>
       </c>
       <c r="C62" s="8" t="inlineStr">
         <is>
-          <t>Zona Azul</t>
+          <t>Plaza Vista Norte</t>
         </is>
       </c>
       <c r="D62" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E62" s="7" t="n">
@@ -3301,17 +3301,17 @@
       </c>
       <c r="B63" s="15" t="inlineStr">
         <is>
-          <t>38142</t>
+          <t>38460</t>
         </is>
       </c>
       <c r="C63" s="12" t="inlineStr">
         <is>
-          <t>Zona Esmeralda</t>
+          <t>Santa Monica</t>
         </is>
       </c>
       <c r="D63" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E63" s="11" t="n">
@@ -3341,21 +3341,21 @@
       </c>
       <c r="B64" s="17" t="inlineStr">
         <is>
-          <t>38207</t>
+          <t>38442</t>
         </is>
       </c>
       <c r="C64" s="8" t="inlineStr">
         <is>
-          <t>Lindavista II</t>
+          <t>Sor Juana</t>
         </is>
       </c>
       <c r="D64" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E64" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F64" s="7" t="n">
         <v>9</v>
@@ -3381,21 +3381,21 @@
       </c>
       <c r="B65" s="15" t="inlineStr">
         <is>
-          <t>38845</t>
+          <t>38925</t>
         </is>
       </c>
       <c r="C65" s="12" t="inlineStr">
         <is>
-          <t>Mundo E II</t>
+          <t>Star Medica Lomas Verdes</t>
         </is>
       </c>
       <c r="D65" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E65" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F65" s="11" t="n">
         <v>9</v>
@@ -3421,21 +3421,21 @@
       </c>
       <c r="B66" s="17" t="inlineStr">
         <is>
-          <t>38266</t>
+          <t>38411</t>
         </is>
       </c>
       <c r="C66" s="8" t="inlineStr">
         <is>
-          <t>San Mateo</t>
+          <t>Torres Lindavista</t>
         </is>
       </c>
       <c r="D66" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E66" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F66" s="7" t="n">
         <v>9</v>
@@ -3461,24 +3461,24 @@
       </c>
       <c r="B67" s="15" t="inlineStr">
         <is>
-          <t>38197</t>
+          <t>43130</t>
         </is>
       </c>
       <c r="C67" s="12" t="inlineStr">
         <is>
-          <t>Echegaray</t>
+          <t>Town Center Nicolás Romero</t>
         </is>
       </c>
       <c r="D67" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E67" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F67" s="11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G67" s="13">
         <f>IFERROR(E67/(E67+F67),0)</f>
@@ -3501,24 +3501,24 @@
       </c>
       <c r="B68" s="17" t="inlineStr">
         <is>
-          <t>38770</t>
+          <t>38694</t>
         </is>
       </c>
       <c r="C68" s="8" t="inlineStr">
         <is>
-          <t>Gustavo Baz 29</t>
+          <t>Villas de la Hacienda</t>
         </is>
       </c>
       <c r="D68" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E68" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F68" s="7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G68" s="9">
         <f>IFERROR(E68/(E68+F68),0)</f>
@@ -3541,12 +3541,12 @@
       </c>
       <c r="B69" s="15" t="inlineStr">
         <is>
-          <t>38119</t>
+          <t>38115</t>
         </is>
       </c>
       <c r="C69" s="12" t="inlineStr">
         <is>
-          <t>Lomas Verdes</t>
+          <t>Zona Azul</t>
         </is>
       </c>
       <c r="D69" s="12" t="inlineStr">
@@ -3555,10 +3555,10 @@
         </is>
       </c>
       <c r="E69" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F69" s="11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G69" s="13">
         <f>IFERROR(E69/(E69+F69),0)</f>
@@ -3581,12 +3581,12 @@
       </c>
       <c r="B70" s="17" t="inlineStr">
         <is>
-          <t>38270</t>
+          <t>38142</t>
         </is>
       </c>
       <c r="C70" s="8" t="inlineStr">
         <is>
-          <t>Lomas Verdes II</t>
+          <t>Zona Esmeralda</t>
         </is>
       </c>
       <c r="D70" s="8" t="inlineStr">
@@ -3595,10 +3595,10 @@
         </is>
       </c>
       <c r="E70" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F70" s="7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G70" s="9">
         <f>IFERROR(E70/(E70+F70),0)</f>
@@ -3621,24 +3621,24 @@
       </c>
       <c r="B71" s="15" t="inlineStr">
         <is>
-          <t>38590</t>
+          <t>38207</t>
         </is>
       </c>
       <c r="C71" s="12" t="inlineStr">
         <is>
-          <t>Parque Toreo II</t>
+          <t>Lindavista II</t>
         </is>
       </c>
       <c r="D71" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E71" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F71" s="11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G71" s="13">
         <f>IFERROR(E71/(E71+F71),0)</f>
@@ -3661,24 +3661,24 @@
       </c>
       <c r="B72" s="17" t="inlineStr">
         <is>
-          <t>38176</t>
+          <t>38845</t>
         </is>
       </c>
       <c r="C72" s="8" t="inlineStr">
         <is>
-          <t>Periferico Satélite DT</t>
+          <t>Mundo E II</t>
         </is>
       </c>
       <c r="D72" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E72" s="7" t="n">
         <v>1</v>
       </c>
       <c r="F72" s="7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G72" s="9">
         <f>IFERROR(E72/(E72+F72),0)</f>
@@ -3701,24 +3701,24 @@
       </c>
       <c r="B73" s="15" t="inlineStr">
         <is>
-          <t>38427</t>
+          <t>38266</t>
         </is>
       </c>
       <c r="C73" s="12" t="inlineStr">
         <is>
-          <t>Plaza Satelite</t>
+          <t>San Mateo</t>
         </is>
       </c>
       <c r="D73" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E73" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F73" s="11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G73" s="13">
         <f>IFERROR(E73/(E73+F73),0)</f>
@@ -3741,12 +3741,12 @@
       </c>
       <c r="B74" s="17" t="inlineStr">
         <is>
-          <t>43152</t>
+          <t>38197</t>
         </is>
       </c>
       <c r="C74" s="8" t="inlineStr">
         <is>
-          <t>Samara Satélite</t>
+          <t>Echegaray</t>
         </is>
       </c>
       <c r="D74" s="8" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="B75" s="15" t="inlineStr">
         <is>
-          <t>38117</t>
+          <t>38176</t>
         </is>
       </c>
       <c r="C75" s="12" t="inlineStr">
         <is>
-          <t>Satelite</t>
+          <t>Periferico Satélite DT</t>
         </is>
       </c>
       <c r="D75" s="12" t="inlineStr">
@@ -3906,7 +3906,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Centro Norte · Corte 02/09/2026 10:46</t>
+          <t>Centro Norte · Corte 02/09/2026 20:23</t>
         </is>
       </c>
     </row>
@@ -3962,10 +3962,10 @@
         </is>
       </c>
       <c r="C5" s="11" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="E5" s="13">
         <f>IFERROR(C5/(C5+D5),0)</f>
@@ -3976,14 +3976,14 @@
           <t>03/09/26</t>
         </is>
       </c>
-      <c r="G5" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="H5" s="14" t="inlineStr">
-        <is>
-          <t>Priorizar hoy</t>
+      <c r="G5" s="10" t="inlineStr">
+        <is>
+          <t>Seguimiento</t>
+        </is>
+      </c>
+      <c r="H5" s="10" t="inlineStr">
+        <is>
+          <t>Dar seguimiento</t>
         </is>
       </c>
     </row>
@@ -3997,10 +3997,10 @@
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="D6" s="7" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="E6" s="9">
         <f>IFERROR(C6/(C6+D6),0)</f>
@@ -4011,14 +4011,14 @@
           <t>03/09/26</t>
         </is>
       </c>
-      <c r="G6" s="10" t="inlineStr">
-        <is>
-          <t>Seguimiento</t>
-        </is>
-      </c>
-      <c r="H6" s="10" t="inlineStr">
-        <is>
-          <t>Dar seguimiento</t>
+      <c r="G6" s="16" t="inlineStr">
+        <is>
+          <t>En meta</t>
+        </is>
+      </c>
+      <c r="H6" s="16" t="inlineStr">
+        <is>
+          <t>Mantener estándar</t>
         </is>
       </c>
     </row>
@@ -4032,10 +4032,10 @@
         </is>
       </c>
       <c r="C7" s="11" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="E7" s="13">
         <f>IFERROR(C7/(C7+D7),0)</f>
@@ -4067,10 +4067,10 @@
         </is>
       </c>
       <c r="C8" s="7" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="E8" s="9">
         <f>IFERROR(C8/(C8+D8),0)</f>
@@ -4102,10 +4102,10 @@
         </is>
       </c>
       <c r="C9" s="11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D9" s="11" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E9" s="13">
         <f>IFERROR(C9/(C9+D9),0)</f>
@@ -4137,10 +4137,10 @@
         </is>
       </c>
       <c r="C10" s="7" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="E10" s="9">
         <f>IFERROR(C10/(C10+D10),0)</f>
@@ -4172,10 +4172,10 @@
         </is>
       </c>
       <c r="C11" s="11" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="E11" s="13">
         <f>IFERROR(C11/(C11+D11),0)</f>
@@ -4207,10 +4207,10 @@
         </is>
       </c>
       <c r="C12" s="7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="E12" s="9">
         <f>IFERROR(C12/(C12+D12),0)</f>
@@ -4277,10 +4277,10 @@
         </is>
       </c>
       <c r="C14" s="7" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="E14" s="9">
         <f>IFERROR(C14/(C14+D14),0)</f>
@@ -4312,10 +4312,10 @@
         </is>
       </c>
       <c r="C15" s="11" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D15" s="11" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E15" s="13">
         <f>IFERROR(C15/(C15+D15),0)</f>

--- a/exports/Resumen_Evidencias_OPS.xlsx
+++ b/exports/Resumen_Evidencias_OPS.xlsx
@@ -592,7 +592,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Centro Norte · Corte 02/09/2026 20:23</t>
+          <t>Centro Norte · Corte 03/09/2026 13:30</t>
         </is>
       </c>
     </row>
@@ -615,10 +615,10 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>527</v>
+        <v>518</v>
       </c>
       <c r="E6" s="5">
         <f>IFERROR(A6/(A6+C6),0)</f>
@@ -714,10 +714,10 @@
         <v>13</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E11" s="12" t="n">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F11" s="13">
         <f>IFERROR(D11/(D11+E11),0)</f>
@@ -747,10 +747,10 @@
         <v>11</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="E12" s="8" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="F12" s="9">
         <f>IFERROR(D12/(D12+E12),0)</f>
@@ -780,10 +780,10 @@
         <v>12</v>
       </c>
       <c r="D13" s="11" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E13" s="12" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F13" s="13">
         <f>IFERROR(D13/(D13+E13),0)</f>
@@ -924,7 +924,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Centro Norte · Corte 02/09/2026 20:23</t>
+          <t>Centro Norte · Corte 03/09/2026 13:30</t>
         </is>
       </c>
     </row>
@@ -1061,17 +1061,17 @@
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>38903</t>
+          <t>38458</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>Encuentro Oceania</t>
+          <t>El Rosario</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E7" s="11" t="n">
@@ -1101,17 +1101,17 @@
       </c>
       <c r="B8" s="17" t="inlineStr">
         <is>
-          <t>38561</t>
+          <t>38903</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>Parque Toreo</t>
+          <t>Encuentro Oceania</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E8" s="7" t="n">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>38590</t>
+          <t>38561</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>Parque Toreo II</t>
+          <t>Parque Toreo</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
@@ -1155,7 +1155,7 @@
         </is>
       </c>
       <c r="E9" s="11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F9" s="11" t="n">
         <v>3</v>
@@ -1181,12 +1181,12 @@
       </c>
       <c r="B10" s="17" t="inlineStr">
         <is>
-          <t>38695</t>
+          <t>38590</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>Cetram 4 Caminos</t>
+          <t>Parque Toreo II</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
@@ -1198,7 +1198,7 @@
         <v>7</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G10" s="9">
         <f>IFERROR(E10/(E10+F10),0)</f>
@@ -1221,12 +1221,12 @@
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>38458</t>
+          <t>38859</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>El Rosario</t>
+          <t>Plaza Satelite II N1</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
@@ -1238,7 +1238,7 @@
         <v>7</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G11" s="13">
         <f>IFERROR(E11/(E11+F11),0)</f>
@@ -1261,17 +1261,17 @@
       </c>
       <c r="B12" s="17" t="inlineStr">
         <is>
-          <t>38368</t>
+          <t>38695</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Luna Park</t>
+          <t>Cetram 4 Caminos</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E12" s="7" t="n">
@@ -1301,17 +1301,17 @@
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>38674</t>
+          <t>38368</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>Mundo E</t>
+          <t>Luna Park</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E13" s="11" t="n">
@@ -1341,17 +1341,17 @@
       </c>
       <c r="B14" s="17" t="inlineStr">
         <is>
-          <t>38515</t>
+          <t>38674</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Patio Ecatepec</t>
+          <t>Mundo E</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E14" s="7" t="n">
@@ -1381,17 +1381,17 @@
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>38859</t>
+          <t>38515</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>Plaza Satelite II N1</t>
+          <t>Patio Ecatepec</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E15" s="11" t="n">
@@ -1421,24 +1421,24 @@
       </c>
       <c r="B16" s="17" t="inlineStr">
         <is>
-          <t>38401</t>
+          <t>38117</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>Coacalco</t>
+          <t>Satelite</t>
         </is>
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E16" s="7" t="n">
         <v>6</v>
       </c>
       <c r="F16" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G16" s="9">
         <f>IFERROR(E16/(E16+F16),0)</f>
@@ -1461,12 +1461,12 @@
       </c>
       <c r="B17" s="15" t="inlineStr">
         <is>
-          <t>38333</t>
+          <t>38401</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>Izcalli Mega</t>
+          <t>Coacalco</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="B18" s="17" t="inlineStr">
         <is>
-          <t>38339</t>
+          <t>38333</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Izcalli Mega</t>
         </is>
       </c>
       <c r="D18" s="8" t="inlineStr">
@@ -1541,17 +1541,17 @@
       </c>
       <c r="B19" s="15" t="inlineStr">
         <is>
-          <t>38117</t>
+          <t>38339</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>Satelite</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E19" s="11" t="n">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="B26" s="17" t="inlineStr">
         <is>
-          <t>38937</t>
+          <t>38930</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>Parque Tepeyac Piso 1</t>
+          <t>Blvd. Aeropuerto dt</t>
         </is>
       </c>
       <c r="D26" s="8" t="inlineStr">
@@ -1861,17 +1861,17 @@
       </c>
       <c r="B27" s="15" t="inlineStr">
         <is>
-          <t>38427</t>
+          <t>38995</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>Plaza Satelite</t>
+          <t>Encuentro Oceania II</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E27" s="11" t="n">
@@ -1901,21 +1901,21 @@
       </c>
       <c r="B28" s="17" t="inlineStr">
         <is>
-          <t>38604</t>
+          <t>38230</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>Cosmopol</t>
+          <t>ITEMS Edo de Mexico</t>
         </is>
       </c>
       <c r="D28" s="8" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E28" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F28" s="7" t="n">
         <v>7</v>
@@ -1941,21 +1941,21 @@
       </c>
       <c r="B29" s="15" t="inlineStr">
         <is>
-          <t>38770</t>
+          <t>38937</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>Gustavo Baz 29</t>
+          <t>Parque Tepeyac Piso 1</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E29" s="11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F29" s="11" t="n">
         <v>7</v>
@@ -1981,21 +1981,21 @@
       </c>
       <c r="B30" s="17" t="inlineStr">
         <is>
-          <t>38456</t>
+          <t>38427</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>Plaza las Flores</t>
+          <t>Plaza Satelite</t>
         </is>
       </c>
       <c r="D30" s="8" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E30" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F30" s="7" t="n">
         <v>7</v>
@@ -2021,21 +2021,21 @@
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>43152</t>
+          <t>38992</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>Samara Satélite</t>
+          <t>Tapo Puerta Oriente</t>
         </is>
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E31" s="11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F31" s="11" t="n">
         <v>7</v>
@@ -2061,24 +2061,24 @@
       </c>
       <c r="B32" s="17" t="inlineStr">
         <is>
-          <t>43194</t>
+          <t>38604</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>Atana Lindavista</t>
+          <t>Cosmopol</t>
         </is>
       </c>
       <c r="D32" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E32" s="7" t="n">
         <v>3</v>
       </c>
       <c r="F32" s="7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G32" s="9">
         <f>IFERROR(E32/(E32+F32),0)</f>
@@ -2101,24 +2101,24 @@
       </c>
       <c r="B33" s="15" t="inlineStr">
         <is>
-          <t>38930</t>
+          <t>38770</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>Blvd. Aeropuerto dt</t>
+          <t>Gustavo Baz 29</t>
         </is>
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E33" s="11" t="n">
         <v>3</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G33" s="13">
         <f>IFERROR(E33/(E33+F33),0)</f>
@@ -2141,24 +2141,24 @@
       </c>
       <c r="B34" s="17" t="inlineStr">
         <is>
-          <t>38529</t>
+          <t>38456</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>Bosques de Aragon</t>
+          <t>Plaza las Flores</t>
         </is>
       </c>
       <c r="D34" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E34" s="7" t="n">
         <v>3</v>
       </c>
       <c r="F34" s="7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G34" s="9">
         <f>IFERROR(E34/(E34+F34),0)</f>
@@ -2181,24 +2181,24 @@
       </c>
       <c r="B35" s="15" t="inlineStr">
         <is>
-          <t>38431</t>
+          <t>43152</t>
         </is>
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>Eduardo Molina</t>
+          <t>Samara Satélite</t>
         </is>
       </c>
       <c r="D35" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E35" s="11" t="n">
         <v>3</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G35" s="13">
         <f>IFERROR(E35/(E35+F35),0)</f>
@@ -2221,17 +2221,17 @@
       </c>
       <c r="B36" s="17" t="inlineStr">
         <is>
-          <t>38230</t>
+          <t>43194</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>ITEMS Edo de Mexico</t>
+          <t>Atana Lindavista</t>
         </is>
       </c>
       <c r="D36" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E36" s="7" t="n">
@@ -2261,12 +2261,12 @@
       </c>
       <c r="B37" s="15" t="inlineStr">
         <is>
-          <t>38965</t>
+          <t>38529</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>Parque Tepeyac Piso 2</t>
+          <t>Bosques de Aragon</t>
         </is>
       </c>
       <c r="D37" s="12" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="B38" s="17" t="inlineStr">
         <is>
-          <t>38792</t>
+          <t>38431</t>
         </is>
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>Pasaje Tlanepantla</t>
+          <t>Eduardo Molina</t>
         </is>
       </c>
       <c r="D38" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E38" s="7" t="n">
@@ -2341,12 +2341,12 @@
       </c>
       <c r="B39" s="15" t="inlineStr">
         <is>
-          <t>38924</t>
+          <t>38965</t>
         </is>
       </c>
       <c r="C39" s="12" t="inlineStr">
         <is>
-          <t>Plaza Aeropuerto</t>
+          <t>Parque Tepeyac Piso 2</t>
         </is>
       </c>
       <c r="D39" s="12" t="inlineStr">
@@ -2381,17 +2381,17 @@
       </c>
       <c r="B40" s="17" t="inlineStr">
         <is>
-          <t>38811</t>
+          <t>38792</t>
         </is>
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>Plaza Tepeyac</t>
+          <t>Pasaje Tlanepantla</t>
         </is>
       </c>
       <c r="D40" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E40" s="7" t="n">
@@ -2421,17 +2421,17 @@
       </c>
       <c r="B41" s="15" t="inlineStr">
         <is>
-          <t>38136</t>
+          <t>38924</t>
         </is>
       </c>
       <c r="C41" s="12" t="inlineStr">
         <is>
-          <t>Punta Norte</t>
+          <t>Plaza Aeropuerto</t>
         </is>
       </c>
       <c r="D41" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E41" s="11" t="n">
@@ -2461,12 +2461,12 @@
       </c>
       <c r="B42" s="17" t="inlineStr">
         <is>
-          <t>38992</t>
+          <t>38811</t>
         </is>
       </c>
       <c r="C42" s="8" t="inlineStr">
         <is>
-          <t>Tapo Puerta Oriente</t>
+          <t>Plaza Tepeyac</t>
         </is>
       </c>
       <c r="D42" s="8" t="inlineStr">
@@ -2501,17 +2501,17 @@
       </c>
       <c r="B43" s="15" t="inlineStr">
         <is>
-          <t>38651</t>
+          <t>38136</t>
         </is>
       </c>
       <c r="C43" s="12" t="inlineStr">
         <is>
-          <t>Via Vallejo</t>
+          <t>Punta Norte</t>
         </is>
       </c>
       <c r="D43" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E43" s="11" t="n">
@@ -2541,24 +2541,24 @@
       </c>
       <c r="B44" s="17" t="inlineStr">
         <is>
-          <t>38186</t>
+          <t>38651</t>
         </is>
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t>Arboledas</t>
+          <t>Via Vallejo</t>
         </is>
       </c>
       <c r="D44" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E44" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F44" s="7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G44" s="9">
         <f>IFERROR(E44/(E44+F44),0)</f>
@@ -2581,17 +2581,17 @@
       </c>
       <c r="B45" s="15" t="inlineStr">
         <is>
-          <t>43043</t>
+          <t>38186</t>
         </is>
       </c>
       <c r="C45" s="12" t="inlineStr">
         <is>
-          <t>Atizapan</t>
+          <t>Arboledas</t>
         </is>
       </c>
       <c r="D45" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E45" s="11" t="n">
@@ -2621,12 +2621,12 @@
       </c>
       <c r="B46" s="17" t="inlineStr">
         <is>
-          <t>38149</t>
+          <t>43043</t>
         </is>
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t>Bellavista</t>
+          <t>Atizapan</t>
         </is>
       </c>
       <c r="D46" s="8" t="inlineStr">
@@ -2661,17 +2661,17 @@
       </c>
       <c r="B47" s="15" t="inlineStr">
         <is>
-          <t>38527</t>
+          <t>38149</t>
         </is>
       </c>
       <c r="C47" s="12" t="inlineStr">
         <is>
-          <t>Camarones</t>
+          <t>Bellavista</t>
         </is>
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E47" s="11" t="n">
@@ -2701,12 +2701,12 @@
       </c>
       <c r="B48" s="17" t="inlineStr">
         <is>
-          <t>38837</t>
+          <t>38527</t>
         </is>
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
-          <t>Centenario Azcapotzalco</t>
+          <t>Camarones</t>
         </is>
       </c>
       <c r="D48" s="8" t="inlineStr">
@@ -2741,17 +2741,17 @@
       </c>
       <c r="B49" s="15" t="inlineStr">
         <is>
-          <t>38394</t>
+          <t>38837</t>
         </is>
       </c>
       <c r="C49" s="12" t="inlineStr">
         <is>
-          <t>Centro Comercial Lomas Verdes</t>
+          <t>Centenario Azcapotzalco</t>
         </is>
       </c>
       <c r="D49" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E49" s="11" t="n">
@@ -2781,12 +2781,12 @@
       </c>
       <c r="B50" s="17" t="inlineStr">
         <is>
-          <t>38535</t>
+          <t>38394</t>
         </is>
       </c>
       <c r="C50" s="8" t="inlineStr">
         <is>
-          <t>City Center Esmeralda</t>
+          <t>Centro Comercial Lomas Verdes</t>
         </is>
       </c>
       <c r="D50" s="8" t="inlineStr">
@@ -2821,17 +2821,17 @@
       </c>
       <c r="B51" s="15" t="inlineStr">
         <is>
-          <t>38995</t>
+          <t>38535</t>
         </is>
       </c>
       <c r="C51" s="12" t="inlineStr">
         <is>
-          <t>Encuentro Oceania II</t>
+          <t>City Center Esmeralda</t>
         </is>
       </c>
       <c r="D51" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E51" s="11" t="n">
@@ -2861,17 +2861,17 @@
       </c>
       <c r="B52" s="17" t="inlineStr">
         <is>
-          <t>38507</t>
+          <t>38197</t>
         </is>
       </c>
       <c r="C52" s="8" t="inlineStr">
         <is>
-          <t>Espacio Vista del Valle</t>
+          <t>Echegaray</t>
         </is>
       </c>
       <c r="D52" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E52" s="7" t="n">
@@ -2901,12 +2901,12 @@
       </c>
       <c r="B53" s="15" t="inlineStr">
         <is>
-          <t>38363</t>
+          <t>38507</t>
         </is>
       </c>
       <c r="C53" s="12" t="inlineStr">
         <is>
-          <t>Galerias Atizapan</t>
+          <t>Espacio Vista del Valle</t>
         </is>
       </c>
       <c r="D53" s="12" t="inlineStr">
@@ -2941,17 +2941,17 @@
       </c>
       <c r="B54" s="17" t="inlineStr">
         <is>
-          <t>38205</t>
+          <t>38363</t>
         </is>
       </c>
       <c r="C54" s="8" t="inlineStr">
         <is>
-          <t>Lindavista</t>
+          <t>Galerias Atizapan</t>
         </is>
       </c>
       <c r="D54" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E54" s="7" t="n">
@@ -2981,17 +2981,17 @@
       </c>
       <c r="B55" s="15" t="inlineStr">
         <is>
-          <t>38119</t>
+          <t>38205</t>
         </is>
       </c>
       <c r="C55" s="12" t="inlineStr">
         <is>
-          <t>Lomas Verdes</t>
+          <t>Lindavista</t>
         </is>
       </c>
       <c r="D55" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E55" s="11" t="n">
@@ -3021,12 +3021,12 @@
       </c>
       <c r="B56" s="17" t="inlineStr">
         <is>
-          <t>38270</t>
+          <t>38119</t>
         </is>
       </c>
       <c r="C56" s="8" t="inlineStr">
         <is>
-          <t>Lomas Verdes II</t>
+          <t>Lomas Verdes</t>
         </is>
       </c>
       <c r="D56" s="8" t="inlineStr">
@@ -3061,17 +3061,17 @@
       </c>
       <c r="B57" s="15" t="inlineStr">
         <is>
-          <t>38371</t>
+          <t>38270</t>
         </is>
       </c>
       <c r="C57" s="12" t="inlineStr">
         <is>
-          <t>Montevideo DT</t>
+          <t>Lomas Verdes II</t>
         </is>
       </c>
       <c r="D57" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E57" s="11" t="n">
@@ -3101,12 +3101,12 @@
       </c>
       <c r="B58" s="17" t="inlineStr">
         <is>
-          <t>43111</t>
+          <t>38371</t>
         </is>
       </c>
       <c r="C58" s="8" t="inlineStr">
         <is>
-          <t>Montevideo Insurgentes</t>
+          <t>Montevideo DT</t>
         </is>
       </c>
       <c r="D58" s="8" t="inlineStr">
@@ -3141,12 +3141,12 @@
       </c>
       <c r="B59" s="15" t="inlineStr">
         <is>
-          <t>43195</t>
+          <t>43111</t>
         </is>
       </c>
       <c r="C59" s="12" t="inlineStr">
         <is>
-          <t>Parque Jadin kiosko</t>
+          <t>Montevideo Insurgentes</t>
         </is>
       </c>
       <c r="D59" s="12" t="inlineStr">
@@ -3181,12 +3181,12 @@
       </c>
       <c r="B60" s="17" t="inlineStr">
         <is>
-          <t>38546</t>
+          <t>43195</t>
         </is>
       </c>
       <c r="C60" s="8" t="inlineStr">
         <is>
-          <t>Patio Claveria</t>
+          <t>Parque Jadin kiosko</t>
         </is>
       </c>
       <c r="D60" s="8" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="B61" s="15" t="inlineStr">
         <is>
-          <t>38677</t>
+          <t>38546</t>
         </is>
       </c>
       <c r="C61" s="12" t="inlineStr">
         <is>
-          <t>Patio la Raza</t>
+          <t>Patio Claveria</t>
         </is>
       </c>
       <c r="D61" s="12" t="inlineStr">
@@ -3261,12 +3261,12 @@
       </c>
       <c r="B62" s="17" t="inlineStr">
         <is>
-          <t>43132</t>
+          <t>38677</t>
         </is>
       </c>
       <c r="C62" s="8" t="inlineStr">
         <is>
-          <t>Plaza Vista Norte</t>
+          <t>Patio la Raza</t>
         </is>
       </c>
       <c r="D62" s="8" t="inlineStr">
@@ -3301,17 +3301,17 @@
       </c>
       <c r="B63" s="15" t="inlineStr">
         <is>
-          <t>38460</t>
+          <t>43132</t>
         </is>
       </c>
       <c r="C63" s="12" t="inlineStr">
         <is>
-          <t>Santa Monica</t>
+          <t>Plaza Vista Norte</t>
         </is>
       </c>
       <c r="D63" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E63" s="11" t="n">
@@ -3341,12 +3341,12 @@
       </c>
       <c r="B64" s="17" t="inlineStr">
         <is>
-          <t>38442</t>
+          <t>38460</t>
         </is>
       </c>
       <c r="C64" s="8" t="inlineStr">
         <is>
-          <t>Sor Juana</t>
+          <t>Santa Monica</t>
         </is>
       </c>
       <c r="D64" s="8" t="inlineStr">
@@ -3381,17 +3381,17 @@
       </c>
       <c r="B65" s="15" t="inlineStr">
         <is>
-          <t>38925</t>
+          <t>38442</t>
         </is>
       </c>
       <c r="C65" s="12" t="inlineStr">
         <is>
-          <t>Star Medica Lomas Verdes</t>
+          <t>Sor Juana</t>
         </is>
       </c>
       <c r="D65" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E65" s="11" t="n">
@@ -3421,17 +3421,17 @@
       </c>
       <c r="B66" s="17" t="inlineStr">
         <is>
-          <t>38411</t>
+          <t>38925</t>
         </is>
       </c>
       <c r="C66" s="8" t="inlineStr">
         <is>
-          <t>Torres Lindavista</t>
+          <t>Star Medica Lomas Verdes</t>
         </is>
       </c>
       <c r="D66" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E66" s="7" t="n">
@@ -3461,17 +3461,17 @@
       </c>
       <c r="B67" s="15" t="inlineStr">
         <is>
-          <t>43130</t>
+          <t>38411</t>
         </is>
       </c>
       <c r="C67" s="12" t="inlineStr">
         <is>
-          <t>Town Center Nicolás Romero</t>
+          <t>Torres Lindavista</t>
         </is>
       </c>
       <c r="D67" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E67" s="11" t="n">
@@ -3501,17 +3501,17 @@
       </c>
       <c r="B68" s="17" t="inlineStr">
         <is>
-          <t>38694</t>
+          <t>43130</t>
         </is>
       </c>
       <c r="C68" s="8" t="inlineStr">
         <is>
-          <t>Villas de la Hacienda</t>
+          <t>Town Center Nicolás Romero</t>
         </is>
       </c>
       <c r="D68" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E68" s="7" t="n">
@@ -3541,17 +3541,17 @@
       </c>
       <c r="B69" s="15" t="inlineStr">
         <is>
-          <t>38115</t>
+          <t>38694</t>
         </is>
       </c>
       <c r="C69" s="12" t="inlineStr">
         <is>
-          <t>Zona Azul</t>
+          <t>Villas de la Hacienda</t>
         </is>
       </c>
       <c r="D69" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E69" s="11" t="n">
@@ -3581,12 +3581,12 @@
       </c>
       <c r="B70" s="17" t="inlineStr">
         <is>
-          <t>38142</t>
+          <t>38115</t>
         </is>
       </c>
       <c r="C70" s="8" t="inlineStr">
         <is>
-          <t>Zona Esmeralda</t>
+          <t>Zona Azul</t>
         </is>
       </c>
       <c r="D70" s="8" t="inlineStr">
@@ -3621,21 +3621,21 @@
       </c>
       <c r="B71" s="15" t="inlineStr">
         <is>
-          <t>38207</t>
+          <t>38142</t>
         </is>
       </c>
       <c r="C71" s="12" t="inlineStr">
         <is>
-          <t>Lindavista II</t>
+          <t>Zona Esmeralda</t>
         </is>
       </c>
       <c r="D71" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E71" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F71" s="11" t="n">
         <v>9</v>
@@ -3661,17 +3661,17 @@
       </c>
       <c r="B72" s="17" t="inlineStr">
         <is>
-          <t>38845</t>
+          <t>38207</t>
         </is>
       </c>
       <c r="C72" s="8" t="inlineStr">
         <is>
-          <t>Mundo E II</t>
+          <t>Lindavista II</t>
         </is>
       </c>
       <c r="D72" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E72" s="7" t="n">
@@ -3701,17 +3701,17 @@
       </c>
       <c r="B73" s="15" t="inlineStr">
         <is>
-          <t>38266</t>
+          <t>38845</t>
         </is>
       </c>
       <c r="C73" s="12" t="inlineStr">
         <is>
-          <t>San Mateo</t>
+          <t>Mundo E II</t>
         </is>
       </c>
       <c r="D73" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E73" s="11" t="n">
@@ -3741,24 +3741,24 @@
       </c>
       <c r="B74" s="17" t="inlineStr">
         <is>
-          <t>38197</t>
+          <t>38266</t>
         </is>
       </c>
       <c r="C74" s="8" t="inlineStr">
         <is>
-          <t>Echegaray</t>
+          <t>San Mateo</t>
         </is>
       </c>
       <c r="D74" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E74" s="7" t="n">
         <v>1</v>
       </c>
       <c r="F74" s="7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G74" s="9">
         <f>IFERROR(E74/(E74+F74),0)</f>
@@ -3906,7 +3906,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Centro Norte · Corte 02/09/2026 20:23</t>
+          <t>Centro Norte · Corte 03/09/2026 13:30</t>
         </is>
       </c>
     </row>
@@ -3962,10 +3962,10 @@
         </is>
       </c>
       <c r="C5" s="11" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E5" s="13">
         <f>IFERROR(C5/(C5+D5),0)</f>
@@ -3997,10 +3997,10 @@
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D6" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E6" s="9">
         <f>IFERROR(C6/(C6+D6),0)</f>
@@ -4032,10 +4032,10 @@
         </is>
       </c>
       <c r="C7" s="11" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E7" s="13">
         <f>IFERROR(C7/(C7+D7),0)</f>
@@ -4172,10 +4172,10 @@
         </is>
       </c>
       <c r="C11" s="11" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E11" s="13">
         <f>IFERROR(C11/(C11+D11),0)</f>
@@ -4210,7 +4210,7 @@
         <v>15</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E12" s="9">
         <f>IFERROR(C12/(C12+D12),0)</f>

--- a/exports/Resumen_Evidencias_OPS.xlsx
+++ b/exports/Resumen_Evidencias_OPS.xlsx
@@ -592,7 +592,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Centro Norte · Corte 03/09/2026 13:30</t>
+          <t>Centro Norte · Corte 03/09/2026 13:37</t>
         </is>
       </c>
     </row>
@@ -615,10 +615,10 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="E6" s="5">
         <f>IFERROR(A6/(A6+C6),0)</f>
@@ -714,10 +714,10 @@
         <v>13</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E11" s="12" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F11" s="13">
         <f>IFERROR(D11/(D11+E11),0)</f>
@@ -924,7 +924,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Centro Norte · Corte 03/09/2026 13:30</t>
+          <t>Centro Norte · Corte 03/09/2026 13:37</t>
         </is>
       </c>
     </row>
@@ -1061,12 +1061,12 @@
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>38458</t>
+          <t>38695</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>El Rosario</t>
+          <t>Cetram 4 Caminos</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
@@ -1101,17 +1101,17 @@
       </c>
       <c r="B8" s="17" t="inlineStr">
         <is>
-          <t>38903</t>
+          <t>38458</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>Encuentro Oceania</t>
+          <t>El Rosario</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E8" s="7" t="n">
@@ -1141,17 +1141,17 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>38561</t>
+          <t>38903</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>Parque Toreo</t>
+          <t>Encuentro Oceania</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E9" s="11" t="n">
@@ -1181,12 +1181,12 @@
       </c>
       <c r="B10" s="17" t="inlineStr">
         <is>
-          <t>38590</t>
+          <t>38561</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>Parque Toreo II</t>
+          <t>Parque Toreo</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
@@ -1195,7 +1195,7 @@
         </is>
       </c>
       <c r="E10" s="7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F10" s="7" t="n">
         <v>3</v>
@@ -1221,12 +1221,12 @@
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>38859</t>
+          <t>38590</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>Plaza Satelite II N1</t>
+          <t>Parque Toreo II</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
@@ -1261,12 +1261,12 @@
       </c>
       <c r="B12" s="17" t="inlineStr">
         <is>
-          <t>38695</t>
+          <t>38859</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Cetram 4 Caminos</t>
+          <t>Plaza Satelite II N1</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
@@ -1278,7 +1278,7 @@
         <v>7</v>
       </c>
       <c r="F12" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G12" s="9">
         <f>IFERROR(E12/(E12+F12),0)</f>
@@ -3906,7 +3906,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Centro Norte · Corte 03/09/2026 13:30</t>
+          <t>Centro Norte · Corte 03/09/2026 13:37</t>
         </is>
       </c>
     </row>
@@ -4137,10 +4137,10 @@
         </is>
       </c>
       <c r="C10" s="7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E10" s="9">
         <f>IFERROR(C10/(C10+D10),0)</f>

--- a/exports/Resumen_Evidencias_OPS.xlsx
+++ b/exports/Resumen_Evidencias_OPS.xlsx
@@ -592,7 +592,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Centro Norte · Corte 03/09/2026 13:37</t>
+          <t>Centro Norte · Corte 03/09/2026 13:44</t>
         </is>
       </c>
     </row>
@@ -615,10 +615,10 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="E6" s="5">
         <f>IFERROR(A6/(A6+C6),0)</f>
@@ -714,10 +714,10 @@
         <v>13</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E11" s="12" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F11" s="13">
         <f>IFERROR(D11/(D11+E11),0)</f>
@@ -924,7 +924,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Centro Norte · Corte 03/09/2026 13:37</t>
+          <t>Centro Norte · Corte 03/09/2026 13:44</t>
         </is>
       </c>
     </row>
@@ -1861,17 +1861,17 @@
       </c>
       <c r="B27" s="15" t="inlineStr">
         <is>
-          <t>38995</t>
+          <t>38197</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>Encuentro Oceania II</t>
+          <t>Echegaray</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E27" s="11" t="n">
@@ -1901,17 +1901,17 @@
       </c>
       <c r="B28" s="17" t="inlineStr">
         <is>
-          <t>38230</t>
+          <t>38995</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>ITEMS Edo de Mexico</t>
+          <t>Encuentro Oceania II</t>
         </is>
       </c>
       <c r="D28" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E28" s="7" t="n">
@@ -1941,17 +1941,17 @@
       </c>
       <c r="B29" s="15" t="inlineStr">
         <is>
-          <t>38937</t>
+          <t>38230</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>Parque Tepeyac Piso 1</t>
+          <t>ITEMS Edo de Mexico</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E29" s="11" t="n">
@@ -1981,17 +1981,17 @@
       </c>
       <c r="B30" s="17" t="inlineStr">
         <is>
-          <t>38427</t>
+          <t>38937</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>Plaza Satelite</t>
+          <t>Parque Tepeyac Piso 1</t>
         </is>
       </c>
       <c r="D30" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E30" s="7" t="n">
@@ -2021,17 +2021,17 @@
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>38992</t>
+          <t>38427</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>Tapo Puerta Oriente</t>
+          <t>Plaza Satelite</t>
         </is>
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E31" s="11" t="n">
@@ -2061,21 +2061,21 @@
       </c>
       <c r="B32" s="17" t="inlineStr">
         <is>
-          <t>38604</t>
+          <t>38992</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>Cosmopol</t>
+          <t>Tapo Puerta Oriente</t>
         </is>
       </c>
       <c r="D32" s="8" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E32" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F32" s="7" t="n">
         <v>7</v>
@@ -2101,17 +2101,17 @@
       </c>
       <c r="B33" s="15" t="inlineStr">
         <is>
-          <t>38770</t>
+          <t>38604</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>Gustavo Baz 29</t>
+          <t>Cosmopol</t>
         </is>
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E33" s="11" t="n">
@@ -2141,17 +2141,17 @@
       </c>
       <c r="B34" s="17" t="inlineStr">
         <is>
-          <t>38456</t>
+          <t>38770</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>Plaza las Flores</t>
+          <t>Gustavo Baz 29</t>
         </is>
       </c>
       <c r="D34" s="8" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E34" s="7" t="n">
@@ -2181,17 +2181,17 @@
       </c>
       <c r="B35" s="15" t="inlineStr">
         <is>
-          <t>43152</t>
+          <t>38456</t>
         </is>
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>Samara Satélite</t>
+          <t>Plaza las Flores</t>
         </is>
       </c>
       <c r="D35" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E35" s="11" t="n">
@@ -2221,24 +2221,24 @@
       </c>
       <c r="B36" s="17" t="inlineStr">
         <is>
-          <t>43194</t>
+          <t>43152</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>Atana Lindavista</t>
+          <t>Samara Satélite</t>
         </is>
       </c>
       <c r="D36" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E36" s="7" t="n">
         <v>3</v>
       </c>
       <c r="F36" s="7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G36" s="9">
         <f>IFERROR(E36/(E36+F36),0)</f>
@@ -2261,17 +2261,17 @@
       </c>
       <c r="B37" s="15" t="inlineStr">
         <is>
-          <t>38529</t>
+          <t>43194</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>Bosques de Aragon</t>
+          <t>Atana Lindavista</t>
         </is>
       </c>
       <c r="D37" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E37" s="11" t="n">
@@ -2301,12 +2301,12 @@
       </c>
       <c r="B38" s="17" t="inlineStr">
         <is>
-          <t>38431</t>
+          <t>38529</t>
         </is>
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>Eduardo Molina</t>
+          <t>Bosques de Aragon</t>
         </is>
       </c>
       <c r="D38" s="8" t="inlineStr">
@@ -2341,12 +2341,12 @@
       </c>
       <c r="B39" s="15" t="inlineStr">
         <is>
-          <t>38965</t>
+          <t>38431</t>
         </is>
       </c>
       <c r="C39" s="12" t="inlineStr">
         <is>
-          <t>Parque Tepeyac Piso 2</t>
+          <t>Eduardo Molina</t>
         </is>
       </c>
       <c r="D39" s="12" t="inlineStr">
@@ -2381,17 +2381,17 @@
       </c>
       <c r="B40" s="17" t="inlineStr">
         <is>
-          <t>38792</t>
+          <t>38965</t>
         </is>
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>Pasaje Tlanepantla</t>
+          <t>Parque Tepeyac Piso 2</t>
         </is>
       </c>
       <c r="D40" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E40" s="7" t="n">
@@ -2421,17 +2421,17 @@
       </c>
       <c r="B41" s="15" t="inlineStr">
         <is>
-          <t>38924</t>
+          <t>38792</t>
         </is>
       </c>
       <c r="C41" s="12" t="inlineStr">
         <is>
-          <t>Plaza Aeropuerto</t>
+          <t>Pasaje Tlanepantla</t>
         </is>
       </c>
       <c r="D41" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E41" s="11" t="n">
@@ -2461,12 +2461,12 @@
       </c>
       <c r="B42" s="17" t="inlineStr">
         <is>
-          <t>38811</t>
+          <t>38924</t>
         </is>
       </c>
       <c r="C42" s="8" t="inlineStr">
         <is>
-          <t>Plaza Tepeyac</t>
+          <t>Plaza Aeropuerto</t>
         </is>
       </c>
       <c r="D42" s="8" t="inlineStr">
@@ -2501,17 +2501,17 @@
       </c>
       <c r="B43" s="15" t="inlineStr">
         <is>
-          <t>38136</t>
+          <t>38811</t>
         </is>
       </c>
       <c r="C43" s="12" t="inlineStr">
         <is>
-          <t>Punta Norte</t>
+          <t>Plaza Tepeyac</t>
         </is>
       </c>
       <c r="D43" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E43" s="11" t="n">
@@ -2541,17 +2541,17 @@
       </c>
       <c r="B44" s="17" t="inlineStr">
         <is>
-          <t>38651</t>
+          <t>38136</t>
         </is>
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t>Via Vallejo</t>
+          <t>Punta Norte</t>
         </is>
       </c>
       <c r="D44" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E44" s="7" t="n">
@@ -2581,24 +2581,24 @@
       </c>
       <c r="B45" s="15" t="inlineStr">
         <is>
-          <t>38186</t>
+          <t>38651</t>
         </is>
       </c>
       <c r="C45" s="12" t="inlineStr">
         <is>
-          <t>Arboledas</t>
+          <t>Via Vallejo</t>
         </is>
       </c>
       <c r="D45" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E45" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G45" s="13">
         <f>IFERROR(E45/(E45+F45),0)</f>
@@ -2621,17 +2621,17 @@
       </c>
       <c r="B46" s="17" t="inlineStr">
         <is>
-          <t>43043</t>
+          <t>38186</t>
         </is>
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t>Atizapan</t>
+          <t>Arboledas</t>
         </is>
       </c>
       <c r="D46" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E46" s="7" t="n">
@@ -2661,12 +2661,12 @@
       </c>
       <c r="B47" s="15" t="inlineStr">
         <is>
-          <t>38149</t>
+          <t>43043</t>
         </is>
       </c>
       <c r="C47" s="12" t="inlineStr">
         <is>
-          <t>Bellavista</t>
+          <t>Atizapan</t>
         </is>
       </c>
       <c r="D47" s="12" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="B48" s="17" t="inlineStr">
         <is>
-          <t>38527</t>
+          <t>38149</t>
         </is>
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
-          <t>Camarones</t>
+          <t>Bellavista</t>
         </is>
       </c>
       <c r="D48" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E48" s="7" t="n">
@@ -2741,12 +2741,12 @@
       </c>
       <c r="B49" s="15" t="inlineStr">
         <is>
-          <t>38837</t>
+          <t>38527</t>
         </is>
       </c>
       <c r="C49" s="12" t="inlineStr">
         <is>
-          <t>Centenario Azcapotzalco</t>
+          <t>Camarones</t>
         </is>
       </c>
       <c r="D49" s="12" t="inlineStr">
@@ -2781,17 +2781,17 @@
       </c>
       <c r="B50" s="17" t="inlineStr">
         <is>
-          <t>38394</t>
+          <t>38837</t>
         </is>
       </c>
       <c r="C50" s="8" t="inlineStr">
         <is>
-          <t>Centro Comercial Lomas Verdes</t>
+          <t>Centenario Azcapotzalco</t>
         </is>
       </c>
       <c r="D50" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E50" s="7" t="n">
@@ -2821,12 +2821,12 @@
       </c>
       <c r="B51" s="15" t="inlineStr">
         <is>
-          <t>38535</t>
+          <t>38394</t>
         </is>
       </c>
       <c r="C51" s="12" t="inlineStr">
         <is>
-          <t>City Center Esmeralda</t>
+          <t>Centro Comercial Lomas Verdes</t>
         </is>
       </c>
       <c r="D51" s="12" t="inlineStr">
@@ -2861,17 +2861,17 @@
       </c>
       <c r="B52" s="17" t="inlineStr">
         <is>
-          <t>38197</t>
+          <t>38535</t>
         </is>
       </c>
       <c r="C52" s="8" t="inlineStr">
         <is>
-          <t>Echegaray</t>
+          <t>City Center Esmeralda</t>
         </is>
       </c>
       <c r="D52" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E52" s="7" t="n">
@@ -3906,7 +3906,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Centro Norte · Corte 03/09/2026 13:37</t>
+          <t>Centro Norte · Corte 03/09/2026 13:44</t>
         </is>
       </c>
     </row>
@@ -4032,10 +4032,10 @@
         </is>
       </c>
       <c r="C7" s="11" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E7" s="13">
         <f>IFERROR(C7/(C7+D7),0)</f>
@@ -4207,10 +4207,10 @@
         </is>
       </c>
       <c r="C12" s="7" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E12" s="9">
         <f>IFERROR(C12/(C12+D12),0)</f>

--- a/exports/Resumen_Evidencias_OPS.xlsx
+++ b/exports/Resumen_Evidencias_OPS.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tiendas" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Actividades" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Resumen" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Tiendas" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Actividades" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Resumen'!$A$9:$H$38</definedName>

--- a/exports/Resumen_Evidencias_OPS.xlsx
+++ b/exports/Resumen_Evidencias_OPS.xlsx
@@ -592,7 +592,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Todas las regiones · Corte 03/09/2026 13:44</t>
+          <t>Todas las regiones · Corte 03/09/2026 13:49</t>
         </is>
       </c>
     </row>
@@ -615,10 +615,10 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>3815</v>
+        <v>3810</v>
       </c>
       <c r="E6" s="5">
         <f>IFERROR(A6/(A6+C6),0)</f>
@@ -714,10 +714,10 @@
         <v>13</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="E11" s="12" t="n">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="F11" s="13">
         <f>IFERROR(D11/(D11+E11),0)</f>
@@ -1683,7 +1683,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Todas las regiones · Corte 03/09/2026 13:44</t>
+          <t>Todas las regiones · Corte 03/09/2026 13:49</t>
         </is>
       </c>
     </row>
@@ -1780,17 +1780,17 @@
       </c>
       <c r="B6" s="17" t="inlineStr">
         <is>
-          <t>38719</t>
+          <t>38695</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>Plaza Fortuna</t>
+          <t>Cetram 4 Caminos</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E6" s="7" t="n">
@@ -1820,37 +1820,37 @@
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>38695</t>
+          <t>38719</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>Cetram 4 Caminos</t>
+          <t>Plaza Fortuna</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E7" s="11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G7" s="13">
         <f>IFERROR(E7/(E7+F7),0)</f>
         <v/>
       </c>
-      <c r="H7" s="10" t="inlineStr">
-        <is>
-          <t>Seguimiento</t>
-        </is>
-      </c>
-      <c r="I7" s="10" t="inlineStr">
-        <is>
-          <t>Dar seguimiento</t>
+      <c r="H7" s="16" t="inlineStr">
+        <is>
+          <t>En meta</t>
+        </is>
+      </c>
+      <c r="I7" s="16" t="inlineStr">
+        <is>
+          <t>Mantener estándar</t>
         </is>
       </c>
     </row>
@@ -2500,17 +2500,17 @@
       </c>
       <c r="B24" s="17" t="inlineStr">
         <is>
-          <t>38606</t>
+          <t>38176</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>TlalnepantlaCarso</t>
+          <t>Periferico Satélite DT</t>
         </is>
       </c>
       <c r="D24" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E24" s="7" t="n">
@@ -2540,12 +2540,12 @@
       </c>
       <c r="B25" s="15" t="inlineStr">
         <is>
-          <t>38374</t>
+          <t>38606</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>Valle Dorado</t>
+          <t>TlalnepantlaCarso</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
@@ -2580,37 +2580,37 @@
       </c>
       <c r="B26" s="17" t="inlineStr">
         <is>
-          <t>38930</t>
+          <t>38374</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>Blvd. Aeropuerto dt</t>
+          <t>Valle Dorado</t>
         </is>
       </c>
       <c r="D26" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E26" s="7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F26" s="7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G26" s="9">
         <f>IFERROR(E26/(E26+F26),0)</f>
         <v/>
       </c>
-      <c r="H26" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I26" s="14" t="inlineStr">
-        <is>
-          <t>Priorizar hoy</t>
+      <c r="H26" s="10" t="inlineStr">
+        <is>
+          <t>Seguimiento</t>
+        </is>
+      </c>
+      <c r="I26" s="10" t="inlineStr">
+        <is>
+          <t>Dar seguimiento</t>
         </is>
       </c>
     </row>
@@ -2620,17 +2620,17 @@
       </c>
       <c r="B27" s="15" t="inlineStr">
         <is>
-          <t>38197</t>
+          <t>38930</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>Echegaray</t>
+          <t>Blvd. Aeropuerto dt</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E27" s="11" t="n">
@@ -2660,17 +2660,17 @@
       </c>
       <c r="B28" s="17" t="inlineStr">
         <is>
-          <t>38995</t>
+          <t>38197</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>Encuentro Oceania II</t>
+          <t>Echegaray</t>
         </is>
       </c>
       <c r="D28" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E28" s="7" t="n">
@@ -2700,17 +2700,17 @@
       </c>
       <c r="B29" s="15" t="inlineStr">
         <is>
-          <t>38230</t>
+          <t>38995</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>ITEMS Edo de Mexico</t>
+          <t>Encuentro Oceania II</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E29" s="11" t="n">
@@ -2740,17 +2740,17 @@
       </c>
       <c r="B30" s="17" t="inlineStr">
         <is>
-          <t>38937</t>
+          <t>38230</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>Parque Tepeyac Piso 1</t>
+          <t>ITEMS Edo de Mexico</t>
         </is>
       </c>
       <c r="D30" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E30" s="7" t="n">
@@ -2780,17 +2780,17 @@
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>38427</t>
+          <t>38937</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>Plaza Satelite</t>
+          <t>Parque Tepeyac Piso 1</t>
         </is>
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E31" s="11" t="n">
@@ -2820,17 +2820,17 @@
       </c>
       <c r="B32" s="17" t="inlineStr">
         <is>
-          <t>38992</t>
+          <t>38427</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>Tapo Puerta Oriente</t>
+          <t>Plaza Satelite</t>
         </is>
       </c>
       <c r="D32" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E32" s="7" t="n">
@@ -2860,21 +2860,21 @@
       </c>
       <c r="B33" s="15" t="inlineStr">
         <is>
-          <t>38604</t>
+          <t>38992</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>Cosmopol</t>
+          <t>Tapo Puerta Oriente</t>
         </is>
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E33" s="11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F33" s="11" t="n">
         <v>7</v>
@@ -2900,17 +2900,17 @@
       </c>
       <c r="B34" s="17" t="inlineStr">
         <is>
-          <t>38770</t>
+          <t>38604</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>Gustavo Baz 29</t>
+          <t>Cosmopol</t>
         </is>
       </c>
       <c r="D34" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E34" s="7" t="n">
@@ -2940,17 +2940,17 @@
       </c>
       <c r="B35" s="15" t="inlineStr">
         <is>
-          <t>38456</t>
+          <t>38770</t>
         </is>
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>Plaza las Flores</t>
+          <t>Gustavo Baz 29</t>
         </is>
       </c>
       <c r="D35" s="12" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E35" s="11" t="n">
@@ -2980,17 +2980,17 @@
       </c>
       <c r="B36" s="17" t="inlineStr">
         <is>
-          <t>43152</t>
+          <t>38456</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>Samara Satélite</t>
+          <t>Plaza las Flores</t>
         </is>
       </c>
       <c r="D36" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E36" s="7" t="n">
@@ -3020,24 +3020,24 @@
       </c>
       <c r="B37" s="15" t="inlineStr">
         <is>
-          <t>43194</t>
+          <t>43152</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>Atana Lindavista</t>
+          <t>Samara Satélite</t>
         </is>
       </c>
       <c r="D37" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E37" s="11" t="n">
         <v>3</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G37" s="13">
         <f>IFERROR(E37/(E37+F37),0)</f>
@@ -3060,17 +3060,17 @@
       </c>
       <c r="B38" s="17" t="inlineStr">
         <is>
-          <t>38529</t>
+          <t>43194</t>
         </is>
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>Bosques de Aragon</t>
+          <t>Atana Lindavista</t>
         </is>
       </c>
       <c r="D38" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E38" s="7" t="n">
@@ -3100,12 +3100,12 @@
       </c>
       <c r="B39" s="15" t="inlineStr">
         <is>
-          <t>38431</t>
+          <t>38529</t>
         </is>
       </c>
       <c r="C39" s="12" t="inlineStr">
         <is>
-          <t>Eduardo Molina</t>
+          <t>Bosques de Aragon</t>
         </is>
       </c>
       <c r="D39" s="12" t="inlineStr">
@@ -3140,12 +3140,12 @@
       </c>
       <c r="B40" s="17" t="inlineStr">
         <is>
-          <t>38965</t>
+          <t>38431</t>
         </is>
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>Parque Tepeyac Piso 2</t>
+          <t>Eduardo Molina</t>
         </is>
       </c>
       <c r="D40" s="8" t="inlineStr">
@@ -3180,17 +3180,17 @@
       </c>
       <c r="B41" s="15" t="inlineStr">
         <is>
-          <t>38792</t>
+          <t>38965</t>
         </is>
       </c>
       <c r="C41" s="12" t="inlineStr">
         <is>
-          <t>Pasaje Tlanepantla</t>
+          <t>Parque Tepeyac Piso 2</t>
         </is>
       </c>
       <c r="D41" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E41" s="11" t="n">
@@ -3220,17 +3220,17 @@
       </c>
       <c r="B42" s="17" t="inlineStr">
         <is>
-          <t>38924</t>
+          <t>38792</t>
         </is>
       </c>
       <c r="C42" s="8" t="inlineStr">
         <is>
-          <t>Plaza Aeropuerto</t>
+          <t>Pasaje Tlanepantla</t>
         </is>
       </c>
       <c r="D42" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E42" s="7" t="n">
@@ -3260,12 +3260,12 @@
       </c>
       <c r="B43" s="15" t="inlineStr">
         <is>
-          <t>38811</t>
+          <t>38924</t>
         </is>
       </c>
       <c r="C43" s="12" t="inlineStr">
         <is>
-          <t>Plaza Tepeyac</t>
+          <t>Plaza Aeropuerto</t>
         </is>
       </c>
       <c r="D43" s="12" t="inlineStr">
@@ -3300,17 +3300,17 @@
       </c>
       <c r="B44" s="17" t="inlineStr">
         <is>
-          <t>38136</t>
+          <t>38811</t>
         </is>
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t>Punta Norte</t>
+          <t>Plaza Tepeyac</t>
         </is>
       </c>
       <c r="D44" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E44" s="7" t="n">
@@ -3340,17 +3340,17 @@
       </c>
       <c r="B45" s="15" t="inlineStr">
         <is>
-          <t>38651</t>
+          <t>38136</t>
         </is>
       </c>
       <c r="C45" s="12" t="inlineStr">
         <is>
-          <t>Via Vallejo</t>
+          <t>Punta Norte</t>
         </is>
       </c>
       <c r="D45" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E45" s="11" t="n">
@@ -3380,24 +3380,24 @@
       </c>
       <c r="B46" s="17" t="inlineStr">
         <is>
-          <t>38186</t>
+          <t>38651</t>
         </is>
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t>Arboledas</t>
+          <t>Via Vallejo</t>
         </is>
       </c>
       <c r="D46" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E46" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F46" s="7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G46" s="9">
         <f>IFERROR(E46/(E46+F46),0)</f>
@@ -3420,17 +3420,17 @@
       </c>
       <c r="B47" s="15" t="inlineStr">
         <is>
-          <t>43043</t>
+          <t>38186</t>
         </is>
       </c>
       <c r="C47" s="12" t="inlineStr">
         <is>
-          <t>Atizapan</t>
+          <t>Arboledas</t>
         </is>
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E47" s="11" t="n">
@@ -3460,12 +3460,12 @@
       </c>
       <c r="B48" s="17" t="inlineStr">
         <is>
-          <t>38149</t>
+          <t>43043</t>
         </is>
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
-          <t>Bellavista</t>
+          <t>Atizapan</t>
         </is>
       </c>
       <c r="D48" s="8" t="inlineStr">
@@ -3500,17 +3500,17 @@
       </c>
       <c r="B49" s="15" t="inlineStr">
         <is>
-          <t>38527</t>
+          <t>38149</t>
         </is>
       </c>
       <c r="C49" s="12" t="inlineStr">
         <is>
-          <t>Camarones</t>
+          <t>Bellavista</t>
         </is>
       </c>
       <c r="D49" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E49" s="11" t="n">
@@ -3540,12 +3540,12 @@
       </c>
       <c r="B50" s="17" t="inlineStr">
         <is>
-          <t>38837</t>
+          <t>38527</t>
         </is>
       </c>
       <c r="C50" s="8" t="inlineStr">
         <is>
-          <t>Centenario Azcapotzalco</t>
+          <t>Camarones</t>
         </is>
       </c>
       <c r="D50" s="8" t="inlineStr">
@@ -3580,17 +3580,17 @@
       </c>
       <c r="B51" s="15" t="inlineStr">
         <is>
-          <t>38394</t>
+          <t>38837</t>
         </is>
       </c>
       <c r="C51" s="12" t="inlineStr">
         <is>
-          <t>Centro Comercial Lomas Verdes</t>
+          <t>Centenario Azcapotzalco</t>
         </is>
       </c>
       <c r="D51" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E51" s="11" t="n">
@@ -3620,12 +3620,12 @@
       </c>
       <c r="B52" s="17" t="inlineStr">
         <is>
-          <t>38535</t>
+          <t>38394</t>
         </is>
       </c>
       <c r="C52" s="8" t="inlineStr">
         <is>
-          <t>City Center Esmeralda</t>
+          <t>Centro Comercial Lomas Verdes</t>
         </is>
       </c>
       <c r="D52" s="8" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="B53" s="15" t="inlineStr">
         <is>
-          <t>38507</t>
+          <t>38535</t>
         </is>
       </c>
       <c r="C53" s="12" t="inlineStr">
         <is>
-          <t>Espacio Vista del Valle</t>
+          <t>City Center Esmeralda</t>
         </is>
       </c>
       <c r="D53" s="12" t="inlineStr">
@@ -3700,12 +3700,12 @@
       </c>
       <c r="B54" s="17" t="inlineStr">
         <is>
-          <t>38363</t>
+          <t>38507</t>
         </is>
       </c>
       <c r="C54" s="8" t="inlineStr">
         <is>
-          <t>Galerias Atizapan</t>
+          <t>Espacio Vista del Valle</t>
         </is>
       </c>
       <c r="D54" s="8" t="inlineStr">
@@ -3740,17 +3740,17 @@
       </c>
       <c r="B55" s="15" t="inlineStr">
         <is>
-          <t>38205</t>
+          <t>38363</t>
         </is>
       </c>
       <c r="C55" s="12" t="inlineStr">
         <is>
-          <t>Lindavista</t>
+          <t>Galerias Atizapan</t>
         </is>
       </c>
       <c r="D55" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E55" s="11" t="n">
@@ -3780,17 +3780,17 @@
       </c>
       <c r="B56" s="17" t="inlineStr">
         <is>
-          <t>38119</t>
+          <t>38205</t>
         </is>
       </c>
       <c r="C56" s="8" t="inlineStr">
         <is>
-          <t>Lomas Verdes</t>
+          <t>Lindavista</t>
         </is>
       </c>
       <c r="D56" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E56" s="7" t="n">
@@ -3820,12 +3820,12 @@
       </c>
       <c r="B57" s="15" t="inlineStr">
         <is>
-          <t>38270</t>
+          <t>38119</t>
         </is>
       </c>
       <c r="C57" s="12" t="inlineStr">
         <is>
-          <t>Lomas Verdes II</t>
+          <t>Lomas Verdes</t>
         </is>
       </c>
       <c r="D57" s="12" t="inlineStr">
@@ -3860,17 +3860,17 @@
       </c>
       <c r="B58" s="17" t="inlineStr">
         <is>
-          <t>38371</t>
+          <t>38270</t>
         </is>
       </c>
       <c r="C58" s="8" t="inlineStr">
         <is>
-          <t>Montevideo DT</t>
+          <t>Lomas Verdes II</t>
         </is>
       </c>
       <c r="D58" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E58" s="7" t="n">
@@ -3900,12 +3900,12 @@
       </c>
       <c r="B59" s="15" t="inlineStr">
         <is>
-          <t>43111</t>
+          <t>38371</t>
         </is>
       </c>
       <c r="C59" s="12" t="inlineStr">
         <is>
-          <t>Montevideo Insurgentes</t>
+          <t>Montevideo DT</t>
         </is>
       </c>
       <c r="D59" s="12" t="inlineStr">
@@ -3940,12 +3940,12 @@
       </c>
       <c r="B60" s="17" t="inlineStr">
         <is>
-          <t>43195</t>
+          <t>43111</t>
         </is>
       </c>
       <c r="C60" s="8" t="inlineStr">
         <is>
-          <t>Parque Jadin kiosko</t>
+          <t>Montevideo Insurgentes</t>
         </is>
       </c>
       <c r="D60" s="8" t="inlineStr">
@@ -3980,12 +3980,12 @@
       </c>
       <c r="B61" s="15" t="inlineStr">
         <is>
-          <t>38546</t>
+          <t>43195</t>
         </is>
       </c>
       <c r="C61" s="12" t="inlineStr">
         <is>
-          <t>Patio Claveria</t>
+          <t>Parque Jadin kiosko</t>
         </is>
       </c>
       <c r="D61" s="12" t="inlineStr">
@@ -4020,12 +4020,12 @@
       </c>
       <c r="B62" s="17" t="inlineStr">
         <is>
-          <t>38677</t>
+          <t>38546</t>
         </is>
       </c>
       <c r="C62" s="8" t="inlineStr">
         <is>
-          <t>Patio la Raza</t>
+          <t>Patio Claveria</t>
         </is>
       </c>
       <c r="D62" s="8" t="inlineStr">
@@ -4060,12 +4060,12 @@
       </c>
       <c r="B63" s="15" t="inlineStr">
         <is>
-          <t>43132</t>
+          <t>38677</t>
         </is>
       </c>
       <c r="C63" s="12" t="inlineStr">
         <is>
-          <t>Plaza Vista Norte</t>
+          <t>Patio la Raza</t>
         </is>
       </c>
       <c r="D63" s="12" t="inlineStr">
@@ -4100,17 +4100,17 @@
       </c>
       <c r="B64" s="17" t="inlineStr">
         <is>
-          <t>38460</t>
+          <t>43132</t>
         </is>
       </c>
       <c r="C64" s="8" t="inlineStr">
         <is>
-          <t>Santa Monica</t>
+          <t>Plaza Vista Norte</t>
         </is>
       </c>
       <c r="D64" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E64" s="7" t="n">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="B65" s="15" t="inlineStr">
         <is>
-          <t>38442</t>
+          <t>38460</t>
         </is>
       </c>
       <c r="C65" s="12" t="inlineStr">
         <is>
-          <t>Sor Juana</t>
+          <t>Santa Monica</t>
         </is>
       </c>
       <c r="D65" s="12" t="inlineStr">
@@ -4180,17 +4180,17 @@
       </c>
       <c r="B66" s="17" t="inlineStr">
         <is>
-          <t>38925</t>
+          <t>38442</t>
         </is>
       </c>
       <c r="C66" s="8" t="inlineStr">
         <is>
-          <t>Star Medica Lomas Verdes</t>
+          <t>Sor Juana</t>
         </is>
       </c>
       <c r="D66" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E66" s="7" t="n">
@@ -4220,17 +4220,17 @@
       </c>
       <c r="B67" s="15" t="inlineStr">
         <is>
-          <t>38411</t>
+          <t>38925</t>
         </is>
       </c>
       <c r="C67" s="12" t="inlineStr">
         <is>
-          <t>Torres Lindavista</t>
+          <t>Star Medica Lomas Verdes</t>
         </is>
       </c>
       <c r="D67" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E67" s="11" t="n">
@@ -4260,17 +4260,17 @@
       </c>
       <c r="B68" s="17" t="inlineStr">
         <is>
-          <t>43130</t>
+          <t>38411</t>
         </is>
       </c>
       <c r="C68" s="8" t="inlineStr">
         <is>
-          <t>Town Center Nicolás Romero</t>
+          <t>Torres Lindavista</t>
         </is>
       </c>
       <c r="D68" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E68" s="7" t="n">
@@ -4300,17 +4300,17 @@
       </c>
       <c r="B69" s="15" t="inlineStr">
         <is>
-          <t>38694</t>
+          <t>43130</t>
         </is>
       </c>
       <c r="C69" s="12" t="inlineStr">
         <is>
-          <t>Villas de la Hacienda</t>
+          <t>Town Center Nicolás Romero</t>
         </is>
       </c>
       <c r="D69" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E69" s="11" t="n">
@@ -4340,17 +4340,17 @@
       </c>
       <c r="B70" s="17" t="inlineStr">
         <is>
-          <t>38115</t>
+          <t>38694</t>
         </is>
       </c>
       <c r="C70" s="8" t="inlineStr">
         <is>
-          <t>Zona Azul</t>
+          <t>Villas de la Hacienda</t>
         </is>
       </c>
       <c r="D70" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E70" s="7" t="n">
@@ -4380,12 +4380,12 @@
       </c>
       <c r="B71" s="15" t="inlineStr">
         <is>
-          <t>38142</t>
+          <t>38115</t>
         </is>
       </c>
       <c r="C71" s="12" t="inlineStr">
         <is>
-          <t>Zona Esmeralda</t>
+          <t>Zona Azul</t>
         </is>
       </c>
       <c r="D71" s="12" t="inlineStr">
@@ -4420,21 +4420,21 @@
       </c>
       <c r="B72" s="17" t="inlineStr">
         <is>
-          <t>38207</t>
+          <t>38142</t>
         </is>
       </c>
       <c r="C72" s="8" t="inlineStr">
         <is>
-          <t>Lindavista II</t>
+          <t>Zona Esmeralda</t>
         </is>
       </c>
       <c r="D72" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E72" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F72" s="7" t="n">
         <v>9</v>
@@ -4460,17 +4460,17 @@
       </c>
       <c r="B73" s="15" t="inlineStr">
         <is>
-          <t>38845</t>
+          <t>38207</t>
         </is>
       </c>
       <c r="C73" s="12" t="inlineStr">
         <is>
-          <t>Mundo E II</t>
+          <t>Lindavista II</t>
         </is>
       </c>
       <c r="D73" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E73" s="11" t="n">
@@ -4500,17 +4500,17 @@
       </c>
       <c r="B74" s="17" t="inlineStr">
         <is>
-          <t>38266</t>
+          <t>38845</t>
         </is>
       </c>
       <c r="C74" s="8" t="inlineStr">
         <is>
-          <t>San Mateo</t>
+          <t>Mundo E II</t>
         </is>
       </c>
       <c r="D74" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E74" s="7" t="n">
@@ -4540,24 +4540,24 @@
       </c>
       <c r="B75" s="15" t="inlineStr">
         <is>
-          <t>38176</t>
+          <t>38266</t>
         </is>
       </c>
       <c r="C75" s="12" t="inlineStr">
         <is>
-          <t>Periferico Satélite DT</t>
+          <t>San Mateo</t>
         </is>
       </c>
       <c r="D75" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E75" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F75" s="11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G75" s="13">
         <f>IFERROR(E75/(E75+F75),0)</f>
@@ -16665,7 +16665,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Todas las regiones · Corte 03/09/2026 13:44</t>
+          <t>Todas las regiones · Corte 03/09/2026 13:49</t>
         </is>
       </c>
     </row>
@@ -16721,10 +16721,10 @@
         </is>
       </c>
       <c r="C5" s="11" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E5" s="13">
         <f>IFERROR(C5/(C5+D5),0)</f>
@@ -16756,10 +16756,10 @@
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D6" s="7" t="n">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="E6" s="9">
         <f>IFERROR(C6/(C6+D6),0)</f>
@@ -16791,10 +16791,10 @@
         </is>
       </c>
       <c r="C7" s="11" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E7" s="13">
         <f>IFERROR(C7/(C7+D7),0)</f>
@@ -16966,10 +16966,10 @@
         </is>
       </c>
       <c r="C12" s="7" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="E12" s="9">
         <f>IFERROR(C12/(C12+D12),0)</f>
@@ -17071,10 +17071,10 @@
         </is>
       </c>
       <c r="C15" s="11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D15" s="11" t="n">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="E15" s="13">
         <f>IFERROR(C15/(C15+D15),0)</f>

--- a/exports/Resumen_Evidencias_OPS.xlsx
+++ b/exports/Resumen_Evidencias_OPS.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Resumen" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Tiendas" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Actividades" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tiendas" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Actividades" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Resumen'!$A$9:$H$38</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Resumen'!$A$1:$H$38</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Tiendas'!$A$4:$I$376</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Resumen'!$A$9:$H$37</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Resumen'!$A$1:$H$37</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Tiendas'!$A$4:$I$361</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Tiendas'!$1:$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Actividades'!$A$4:$H$15</definedName>
   </definedNames>
@@ -568,7 +568,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H38"/>
+  <dimension ref="A1:H37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -592,7 +592,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Todas las regiones · Corte 03/09/2026 13:49</t>
+          <t>Todas las regiones · Corte 03/09/2026 13:44</t>
         </is>
       </c>
     </row>
@@ -615,10 +615,10 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>3810</v>
+        <v>3650</v>
       </c>
       <c r="E6" s="5">
         <f>IFERROR(A6/(A6+C6),0)</f>
@@ -714,10 +714,10 @@
         <v>13</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="E11" s="12" t="n">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="F11" s="13">
         <f>IFERROR(D11/(D11+E11),0)</f>
@@ -876,13 +876,13 @@
         </is>
       </c>
       <c r="C16" s="7" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D16" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E16" s="8" t="n">
-        <v>154</v>
+        <v>132</v>
       </c>
       <c r="F16" s="9">
         <f>IFERROR(D16/(D16+E16),0)</f>
@@ -909,13 +909,13 @@
         </is>
       </c>
       <c r="C17" s="11" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D17" s="11" t="n">
         <v>0</v>
       </c>
       <c r="E17" s="12" t="n">
-        <v>154</v>
+        <v>143</v>
       </c>
       <c r="F17" s="13">
         <f>IFERROR(D17/(D17+E17),0)</f>
@@ -975,13 +975,13 @@
         </is>
       </c>
       <c r="C19" s="11" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D19" s="11" t="n">
         <v>0</v>
       </c>
       <c r="E19" s="12" t="n">
-        <v>165</v>
+        <v>143</v>
       </c>
       <c r="F19" s="13">
         <f>IFERROR(D19/(D19+E19),0)</f>
@@ -1070,17 +1070,17 @@
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>DM pendiente</t>
+          <t>Daniel Flores Maldonado</t>
         </is>
       </c>
       <c r="C22" s="7" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="D22" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E22" s="8" t="n">
-        <v>33</v>
+        <v>143</v>
       </c>
       <c r="F22" s="9">
         <f>IFERROR(D22/(D22+E22),0)</f>
@@ -1103,17 +1103,17 @@
       </c>
       <c r="B23" s="12" t="inlineStr">
         <is>
-          <t>Daniel Flores Maldonado</t>
+          <t>Erika Julieta Contreras Aguilera</t>
         </is>
       </c>
       <c r="C23" s="11" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D23" s="11" t="n">
         <v>0</v>
       </c>
       <c r="E23" s="12" t="n">
-        <v>143</v>
+        <v>165</v>
       </c>
       <c r="F23" s="13">
         <f>IFERROR(D23/(D23+E23),0)</f>
@@ -1136,17 +1136,17 @@
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>Erika Julieta Contreras Aguilera</t>
+          <t>Fernando Eduardo Verdugo Saldaña</t>
         </is>
       </c>
       <c r="C24" s="7" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D24" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E24" s="8" t="n">
-        <v>165</v>
+        <v>132</v>
       </c>
       <c r="F24" s="9">
         <f>IFERROR(D24/(D24+E24),0)</f>
@@ -1169,7 +1169,7 @@
       </c>
       <c r="B25" s="12" t="inlineStr">
         <is>
-          <t>Fernando Eduardo Verdugo Saldaña</t>
+          <t>Guadalupe Ibarra Martínez</t>
         </is>
       </c>
       <c r="C25" s="11" t="n">
@@ -1202,17 +1202,17 @@
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>Guadalupe Ibarra Martínez</t>
+          <t>Hazar Susim Trejo Hernandez</t>
         </is>
       </c>
       <c r="C26" s="7" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D26" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E26" s="8" t="n">
-        <v>154</v>
+        <v>132</v>
       </c>
       <c r="F26" s="9">
         <f>IFERROR(D26/(D26+E26),0)</f>
@@ -1235,17 +1235,17 @@
       </c>
       <c r="B27" s="12" t="inlineStr">
         <is>
-          <t>Hazar Susim Trejo Hernandez</t>
+          <t>Jaqueline Cortes Ayala</t>
         </is>
       </c>
       <c r="C27" s="11" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D27" s="11" t="n">
         <v>0</v>
       </c>
       <c r="E27" s="12" t="n">
-        <v>154</v>
+        <v>143</v>
       </c>
       <c r="F27" s="13">
         <f>IFERROR(D27/(D27+E27),0)</f>
@@ -1268,17 +1268,17 @@
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>Jaqueline Cortes Ayala</t>
+          <t>Jesus Antonio Elguera Flores</t>
         </is>
       </c>
       <c r="C28" s="7" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D28" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E28" s="8" t="n">
-        <v>143</v>
+        <v>110</v>
       </c>
       <c r="F28" s="9">
         <f>IFERROR(D28/(D28+E28),0)</f>
@@ -1301,17 +1301,17 @@
       </c>
       <c r="B29" s="12" t="inlineStr">
         <is>
-          <t>Jesus Antonio Elguera Flores</t>
+          <t>Jose De Jesus Magos Arzaluz</t>
         </is>
       </c>
       <c r="C29" s="11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D29" s="11" t="n">
         <v>0</v>
       </c>
       <c r="E29" s="12" t="n">
-        <v>110</v>
+        <v>165</v>
       </c>
       <c r="F29" s="13">
         <f>IFERROR(D29/(D29+E29),0)</f>
@@ -1334,17 +1334,17 @@
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>Jose De Jesus Magos Arzaluz</t>
+          <t>Juan Jesus Zuñiga Flores</t>
         </is>
       </c>
       <c r="C30" s="7" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D30" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E30" s="8" t="n">
-        <v>165</v>
+        <v>121</v>
       </c>
       <c r="F30" s="9">
         <f>IFERROR(D30/(D30+E30),0)</f>
@@ -1367,17 +1367,17 @@
       </c>
       <c r="B31" s="12" t="inlineStr">
         <is>
-          <t>Juan Jesus Zuñiga Flores</t>
+          <t>Luis Alberto Quevedo Rodriguez</t>
         </is>
       </c>
       <c r="C31" s="11" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D31" s="11" t="n">
         <v>0</v>
       </c>
       <c r="E31" s="12" t="n">
-        <v>121</v>
+        <v>154</v>
       </c>
       <c r="F31" s="13">
         <f>IFERROR(D31/(D31+E31),0)</f>
@@ -1400,17 +1400,17 @@
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>Luis Alberto Quevedo Rodriguez</t>
+          <t>Luis Manuel Neri Saldaña</t>
         </is>
       </c>
       <c r="C32" s="7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D32" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E32" s="8" t="n">
-        <v>154</v>
+        <v>165</v>
       </c>
       <c r="F32" s="9">
         <f>IFERROR(D32/(D32+E32),0)</f>
@@ -1433,17 +1433,17 @@
       </c>
       <c r="B33" s="12" t="inlineStr">
         <is>
-          <t>Luis Manuel Neri Saldaña</t>
+          <t>Manuel Alejandro Avila Molina</t>
         </is>
       </c>
       <c r="C33" s="11" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D33" s="11" t="n">
         <v>0</v>
       </c>
       <c r="E33" s="12" t="n">
-        <v>165</v>
+        <v>143</v>
       </c>
       <c r="F33" s="13">
         <f>IFERROR(D33/(D33+E33),0)</f>
@@ -1466,17 +1466,17 @@
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>Manuel Alejandro Avila Molina</t>
+          <t>Maria Anallely Sanchez Garcia</t>
         </is>
       </c>
       <c r="C34" s="7" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D34" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E34" s="8" t="n">
-        <v>143</v>
+        <v>176</v>
       </c>
       <c r="F34" s="9">
         <f>IFERROR(D34/(D34+E34),0)</f>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="B35" s="12" t="inlineStr">
         <is>
-          <t>Maria Anallely Sanchez Garcia</t>
+          <t>Monica Selene Morales Ibarra</t>
         </is>
       </c>
       <c r="C35" s="11" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="D35" s="11" t="n">
         <v>0</v>
       </c>
       <c r="E35" s="12" t="n">
-        <v>198</v>
+        <v>143</v>
       </c>
       <c r="F35" s="13">
         <f>IFERROR(D35/(D35+E35),0)</f>
@@ -1532,17 +1532,17 @@
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>Monica Selene Morales Ibarra</t>
+          <t>Nora Caracas Saldaña</t>
         </is>
       </c>
       <c r="C36" s="7" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D36" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E36" s="8" t="n">
-        <v>143</v>
+        <v>187</v>
       </c>
       <c r="F36" s="9">
         <f>IFERROR(D36/(D36+E36),0)</f>
@@ -1565,17 +1565,17 @@
       </c>
       <c r="B37" s="12" t="inlineStr">
         <is>
-          <t>Nora Caracas Saldaña</t>
+          <t>Vacante</t>
         </is>
       </c>
       <c r="C37" s="11" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="D37" s="11" t="n">
         <v>0</v>
       </c>
       <c r="E37" s="12" t="n">
-        <v>187</v>
+        <v>132</v>
       </c>
       <c r="F37" s="13">
         <f>IFERROR(D37/(D37+E37),0)</f>
@@ -1592,41 +1592,8 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="21" customHeight="1">
-      <c r="A38" s="7" t="n">
-        <v>29</v>
-      </c>
-      <c r="B38" s="8" t="inlineStr">
-        <is>
-          <t>Vacante</t>
-        </is>
-      </c>
-      <c r="C38" s="7" t="n">
-        <v>13</v>
-      </c>
-      <c r="D38" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E38" s="8" t="n">
-        <v>143</v>
-      </c>
-      <c r="F38" s="9">
-        <f>IFERROR(D38/(D38+E38),0)</f>
-        <v/>
-      </c>
-      <c r="G38" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="H38" s="14" t="inlineStr">
-        <is>
-          <t>Priorizar hoy</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A9:H38"/>
+  <autoFilter ref="A9:H37"/>
   <mergeCells count="8">
     <mergeCell ref="E6:G7"/>
     <mergeCell ref="A3:H3"/>
@@ -1637,7 +1604,7 @@
     <mergeCell ref="A6:B7"/>
     <mergeCell ref="A1:H2"/>
   </mergeCells>
-  <conditionalFormatting sqref="F10:F38">
+  <conditionalFormatting sqref="F10:F37">
     <cfRule type="dataBar" priority="1">
       <dataBar showValue="1">
         <cfvo type="num" val="0"/>
@@ -1658,7 +1625,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:I376"/>
+  <dimension ref="A1:I361"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1683,7 +1650,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Todas las regiones · Corte 03/09/2026 13:49</t>
+          <t>Todas las regiones · Corte 03/09/2026 13:44</t>
         </is>
       </c>
     </row>
@@ -1780,17 +1747,17 @@
       </c>
       <c r="B6" s="17" t="inlineStr">
         <is>
-          <t>38695</t>
+          <t>38719</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>Cetram 4 Caminos</t>
+          <t>Plaza Fortuna</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E6" s="7" t="n">
@@ -1820,37 +1787,37 @@
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>38719</t>
+          <t>38695</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>Plaza Fortuna</t>
+          <t>Cetram 4 Caminos</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E7" s="11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G7" s="13">
         <f>IFERROR(E7/(E7+F7),0)</f>
         <v/>
       </c>
-      <c r="H7" s="16" t="inlineStr">
-        <is>
-          <t>En meta</t>
-        </is>
-      </c>
-      <c r="I7" s="16" t="inlineStr">
-        <is>
-          <t>Mantener estándar</t>
+      <c r="H7" s="10" t="inlineStr">
+        <is>
+          <t>Seguimiento</t>
+        </is>
+      </c>
+      <c r="I7" s="10" t="inlineStr">
+        <is>
+          <t>Dar seguimiento</t>
         </is>
       </c>
     </row>
@@ -2500,17 +2467,17 @@
       </c>
       <c r="B24" s="17" t="inlineStr">
         <is>
-          <t>38176</t>
+          <t>38606</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>Periferico Satélite DT</t>
+          <t>TlalnepantlaCarso</t>
         </is>
       </c>
       <c r="D24" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E24" s="7" t="n">
@@ -2540,12 +2507,12 @@
       </c>
       <c r="B25" s="15" t="inlineStr">
         <is>
-          <t>38606</t>
+          <t>38374</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>TlalnepantlaCarso</t>
+          <t>Valle Dorado</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
@@ -2580,37 +2547,37 @@
       </c>
       <c r="B26" s="17" t="inlineStr">
         <is>
-          <t>38374</t>
+          <t>38930</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>Valle Dorado</t>
+          <t>Blvd. Aeropuerto dt</t>
         </is>
       </c>
       <c r="D26" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E26" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F26" s="7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G26" s="9">
         <f>IFERROR(E26/(E26+F26),0)</f>
         <v/>
       </c>
-      <c r="H26" s="10" t="inlineStr">
-        <is>
-          <t>Seguimiento</t>
-        </is>
-      </c>
-      <c r="I26" s="10" t="inlineStr">
-        <is>
-          <t>Dar seguimiento</t>
+      <c r="H26" s="14" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="I26" s="14" t="inlineStr">
+        <is>
+          <t>Priorizar hoy</t>
         </is>
       </c>
     </row>
@@ -2620,17 +2587,17 @@
       </c>
       <c r="B27" s="15" t="inlineStr">
         <is>
-          <t>38930</t>
+          <t>38197</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>Blvd. Aeropuerto dt</t>
+          <t>Echegaray</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E27" s="11" t="n">
@@ -2660,17 +2627,17 @@
       </c>
       <c r="B28" s="17" t="inlineStr">
         <is>
-          <t>38197</t>
+          <t>38995</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>Echegaray</t>
+          <t>Encuentro Oceania II</t>
         </is>
       </c>
       <c r="D28" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E28" s="7" t="n">
@@ -2700,17 +2667,17 @@
       </c>
       <c r="B29" s="15" t="inlineStr">
         <is>
-          <t>38995</t>
+          <t>38230</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>Encuentro Oceania II</t>
+          <t>ITEMS Edo de Mexico</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E29" s="11" t="n">
@@ -2740,17 +2707,17 @@
       </c>
       <c r="B30" s="17" t="inlineStr">
         <is>
-          <t>38230</t>
+          <t>38937</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>ITEMS Edo de Mexico</t>
+          <t>Parque Tepeyac Piso 1</t>
         </is>
       </c>
       <c r="D30" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E30" s="7" t="n">
@@ -2780,17 +2747,17 @@
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>38937</t>
+          <t>38427</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>Parque Tepeyac Piso 1</t>
+          <t>Plaza Satelite</t>
         </is>
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E31" s="11" t="n">
@@ -2820,17 +2787,17 @@
       </c>
       <c r="B32" s="17" t="inlineStr">
         <is>
-          <t>38427</t>
+          <t>38992</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>Plaza Satelite</t>
+          <t>Tapo Puerta Oriente</t>
         </is>
       </c>
       <c r="D32" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E32" s="7" t="n">
@@ -2860,21 +2827,21 @@
       </c>
       <c r="B33" s="15" t="inlineStr">
         <is>
-          <t>38992</t>
+          <t>38604</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>Tapo Puerta Oriente</t>
+          <t>Cosmopol</t>
         </is>
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E33" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F33" s="11" t="n">
         <v>7</v>
@@ -2900,17 +2867,17 @@
       </c>
       <c r="B34" s="17" t="inlineStr">
         <is>
-          <t>38604</t>
+          <t>38770</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>Cosmopol</t>
+          <t>Gustavo Baz 29</t>
         </is>
       </c>
       <c r="D34" s="8" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E34" s="7" t="n">
@@ -2940,17 +2907,17 @@
       </c>
       <c r="B35" s="15" t="inlineStr">
         <is>
-          <t>38770</t>
+          <t>38456</t>
         </is>
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>Gustavo Baz 29</t>
+          <t>Plaza las Flores</t>
         </is>
       </c>
       <c r="D35" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E35" s="11" t="n">
@@ -2980,17 +2947,17 @@
       </c>
       <c r="B36" s="17" t="inlineStr">
         <is>
-          <t>38456</t>
+          <t>43152</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>Plaza las Flores</t>
+          <t>Samara Satélite</t>
         </is>
       </c>
       <c r="D36" s="8" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E36" s="7" t="n">
@@ -3020,24 +2987,24 @@
       </c>
       <c r="B37" s="15" t="inlineStr">
         <is>
-          <t>43152</t>
+          <t>43194</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>Samara Satélite</t>
+          <t>Atana Lindavista</t>
         </is>
       </c>
       <c r="D37" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E37" s="11" t="n">
         <v>3</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G37" s="13">
         <f>IFERROR(E37/(E37+F37),0)</f>
@@ -3060,17 +3027,17 @@
       </c>
       <c r="B38" s="17" t="inlineStr">
         <is>
-          <t>43194</t>
+          <t>38529</t>
         </is>
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>Atana Lindavista</t>
+          <t>Bosques de Aragon</t>
         </is>
       </c>
       <c r="D38" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E38" s="7" t="n">
@@ -3100,12 +3067,12 @@
       </c>
       <c r="B39" s="15" t="inlineStr">
         <is>
-          <t>38529</t>
+          <t>38431</t>
         </is>
       </c>
       <c r="C39" s="12" t="inlineStr">
         <is>
-          <t>Bosques de Aragon</t>
+          <t>Eduardo Molina</t>
         </is>
       </c>
       <c r="D39" s="12" t="inlineStr">
@@ -3140,12 +3107,12 @@
       </c>
       <c r="B40" s="17" t="inlineStr">
         <is>
-          <t>38431</t>
+          <t>38965</t>
         </is>
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>Eduardo Molina</t>
+          <t>Parque Tepeyac Piso 2</t>
         </is>
       </c>
       <c r="D40" s="8" t="inlineStr">
@@ -3180,17 +3147,17 @@
       </c>
       <c r="B41" s="15" t="inlineStr">
         <is>
-          <t>38965</t>
+          <t>38792</t>
         </is>
       </c>
       <c r="C41" s="12" t="inlineStr">
         <is>
-          <t>Parque Tepeyac Piso 2</t>
+          <t>Pasaje Tlanepantla</t>
         </is>
       </c>
       <c r="D41" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E41" s="11" t="n">
@@ -3220,17 +3187,17 @@
       </c>
       <c r="B42" s="17" t="inlineStr">
         <is>
-          <t>38792</t>
+          <t>38924</t>
         </is>
       </c>
       <c r="C42" s="8" t="inlineStr">
         <is>
-          <t>Pasaje Tlanepantla</t>
+          <t>Plaza Aeropuerto</t>
         </is>
       </c>
       <c r="D42" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E42" s="7" t="n">
@@ -3260,12 +3227,12 @@
       </c>
       <c r="B43" s="15" t="inlineStr">
         <is>
-          <t>38924</t>
+          <t>38811</t>
         </is>
       </c>
       <c r="C43" s="12" t="inlineStr">
         <is>
-          <t>Plaza Aeropuerto</t>
+          <t>Plaza Tepeyac</t>
         </is>
       </c>
       <c r="D43" s="12" t="inlineStr">
@@ -3300,17 +3267,17 @@
       </c>
       <c r="B44" s="17" t="inlineStr">
         <is>
-          <t>38811</t>
+          <t>38136</t>
         </is>
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t>Plaza Tepeyac</t>
+          <t>Punta Norte</t>
         </is>
       </c>
       <c r="D44" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E44" s="7" t="n">
@@ -3340,17 +3307,17 @@
       </c>
       <c r="B45" s="15" t="inlineStr">
         <is>
-          <t>38136</t>
+          <t>38651</t>
         </is>
       </c>
       <c r="C45" s="12" t="inlineStr">
         <is>
-          <t>Punta Norte</t>
+          <t>Via Vallejo</t>
         </is>
       </c>
       <c r="D45" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E45" s="11" t="n">
@@ -3380,24 +3347,24 @@
       </c>
       <c r="B46" s="17" t="inlineStr">
         <is>
-          <t>38651</t>
+          <t>38186</t>
         </is>
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t>Via Vallejo</t>
+          <t>Arboledas</t>
         </is>
       </c>
       <c r="D46" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E46" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F46" s="7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G46" s="9">
         <f>IFERROR(E46/(E46+F46),0)</f>
@@ -3420,17 +3387,17 @@
       </c>
       <c r="B47" s="15" t="inlineStr">
         <is>
-          <t>38186</t>
+          <t>43043</t>
         </is>
       </c>
       <c r="C47" s="12" t="inlineStr">
         <is>
-          <t>Arboledas</t>
+          <t>Atizapan</t>
         </is>
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E47" s="11" t="n">
@@ -3460,12 +3427,12 @@
       </c>
       <c r="B48" s="17" t="inlineStr">
         <is>
-          <t>43043</t>
+          <t>38149</t>
         </is>
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
-          <t>Atizapan</t>
+          <t>Bellavista</t>
         </is>
       </c>
       <c r="D48" s="8" t="inlineStr">
@@ -3500,17 +3467,17 @@
       </c>
       <c r="B49" s="15" t="inlineStr">
         <is>
-          <t>38149</t>
+          <t>38527</t>
         </is>
       </c>
       <c r="C49" s="12" t="inlineStr">
         <is>
-          <t>Bellavista</t>
+          <t>Camarones</t>
         </is>
       </c>
       <c r="D49" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E49" s="11" t="n">
@@ -3540,12 +3507,12 @@
       </c>
       <c r="B50" s="17" t="inlineStr">
         <is>
-          <t>38527</t>
+          <t>38837</t>
         </is>
       </c>
       <c r="C50" s="8" t="inlineStr">
         <is>
-          <t>Camarones</t>
+          <t>Centenario Azcapotzalco</t>
         </is>
       </c>
       <c r="D50" s="8" t="inlineStr">
@@ -3580,17 +3547,17 @@
       </c>
       <c r="B51" s="15" t="inlineStr">
         <is>
-          <t>38837</t>
+          <t>38394</t>
         </is>
       </c>
       <c r="C51" s="12" t="inlineStr">
         <is>
-          <t>Centenario Azcapotzalco</t>
+          <t>Centro Comercial Lomas Verdes</t>
         </is>
       </c>
       <c r="D51" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E51" s="11" t="n">
@@ -3620,12 +3587,12 @@
       </c>
       <c r="B52" s="17" t="inlineStr">
         <is>
-          <t>38394</t>
+          <t>38535</t>
         </is>
       </c>
       <c r="C52" s="8" t="inlineStr">
         <is>
-          <t>Centro Comercial Lomas Verdes</t>
+          <t>City Center Esmeralda</t>
         </is>
       </c>
       <c r="D52" s="8" t="inlineStr">
@@ -3660,12 +3627,12 @@
       </c>
       <c r="B53" s="15" t="inlineStr">
         <is>
-          <t>38535</t>
+          <t>38507</t>
         </is>
       </c>
       <c r="C53" s="12" t="inlineStr">
         <is>
-          <t>City Center Esmeralda</t>
+          <t>Espacio Vista del Valle</t>
         </is>
       </c>
       <c r="D53" s="12" t="inlineStr">
@@ -3700,12 +3667,12 @@
       </c>
       <c r="B54" s="17" t="inlineStr">
         <is>
-          <t>38507</t>
+          <t>38363</t>
         </is>
       </c>
       <c r="C54" s="8" t="inlineStr">
         <is>
-          <t>Espacio Vista del Valle</t>
+          <t>Galerias Atizapan</t>
         </is>
       </c>
       <c r="D54" s="8" t="inlineStr">
@@ -3740,17 +3707,17 @@
       </c>
       <c r="B55" s="15" t="inlineStr">
         <is>
-          <t>38363</t>
+          <t>38205</t>
         </is>
       </c>
       <c r="C55" s="12" t="inlineStr">
         <is>
-          <t>Galerias Atizapan</t>
+          <t>Lindavista</t>
         </is>
       </c>
       <c r="D55" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E55" s="11" t="n">
@@ -3780,17 +3747,17 @@
       </c>
       <c r="B56" s="17" t="inlineStr">
         <is>
-          <t>38205</t>
+          <t>38119</t>
         </is>
       </c>
       <c r="C56" s="8" t="inlineStr">
         <is>
-          <t>Lindavista</t>
+          <t>Lomas Verdes</t>
         </is>
       </c>
       <c r="D56" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E56" s="7" t="n">
@@ -3820,12 +3787,12 @@
       </c>
       <c r="B57" s="15" t="inlineStr">
         <is>
-          <t>38119</t>
+          <t>38270</t>
         </is>
       </c>
       <c r="C57" s="12" t="inlineStr">
         <is>
-          <t>Lomas Verdes</t>
+          <t>Lomas Verdes II</t>
         </is>
       </c>
       <c r="D57" s="12" t="inlineStr">
@@ -3860,17 +3827,17 @@
       </c>
       <c r="B58" s="17" t="inlineStr">
         <is>
-          <t>38270</t>
+          <t>38371</t>
         </is>
       </c>
       <c r="C58" s="8" t="inlineStr">
         <is>
-          <t>Lomas Verdes II</t>
+          <t>Montevideo DT</t>
         </is>
       </c>
       <c r="D58" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E58" s="7" t="n">
@@ -3900,12 +3867,12 @@
       </c>
       <c r="B59" s="15" t="inlineStr">
         <is>
-          <t>38371</t>
+          <t>43111</t>
         </is>
       </c>
       <c r="C59" s="12" t="inlineStr">
         <is>
-          <t>Montevideo DT</t>
+          <t>Montevideo Insurgentes</t>
         </is>
       </c>
       <c r="D59" s="12" t="inlineStr">
@@ -3940,12 +3907,12 @@
       </c>
       <c r="B60" s="17" t="inlineStr">
         <is>
-          <t>43111</t>
+          <t>43195</t>
         </is>
       </c>
       <c r="C60" s="8" t="inlineStr">
         <is>
-          <t>Montevideo Insurgentes</t>
+          <t>Parque Jadin kiosko</t>
         </is>
       </c>
       <c r="D60" s="8" t="inlineStr">
@@ -3980,12 +3947,12 @@
       </c>
       <c r="B61" s="15" t="inlineStr">
         <is>
-          <t>43195</t>
+          <t>38546</t>
         </is>
       </c>
       <c r="C61" s="12" t="inlineStr">
         <is>
-          <t>Parque Jadin kiosko</t>
+          <t>Patio Claveria</t>
         </is>
       </c>
       <c r="D61" s="12" t="inlineStr">
@@ -4020,12 +3987,12 @@
       </c>
       <c r="B62" s="17" t="inlineStr">
         <is>
-          <t>38546</t>
+          <t>38677</t>
         </is>
       </c>
       <c r="C62" s="8" t="inlineStr">
         <is>
-          <t>Patio Claveria</t>
+          <t>Patio la Raza</t>
         </is>
       </c>
       <c r="D62" s="8" t="inlineStr">
@@ -4060,12 +4027,12 @@
       </c>
       <c r="B63" s="15" t="inlineStr">
         <is>
-          <t>38677</t>
+          <t>43132</t>
         </is>
       </c>
       <c r="C63" s="12" t="inlineStr">
         <is>
-          <t>Patio la Raza</t>
+          <t>Plaza Vista Norte</t>
         </is>
       </c>
       <c r="D63" s="12" t="inlineStr">
@@ -4100,17 +4067,17 @@
       </c>
       <c r="B64" s="17" t="inlineStr">
         <is>
-          <t>43132</t>
+          <t>38460</t>
         </is>
       </c>
       <c r="C64" s="8" t="inlineStr">
         <is>
-          <t>Plaza Vista Norte</t>
+          <t>Santa Monica</t>
         </is>
       </c>
       <c r="D64" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E64" s="7" t="n">
@@ -4140,12 +4107,12 @@
       </c>
       <c r="B65" s="15" t="inlineStr">
         <is>
-          <t>38460</t>
+          <t>38442</t>
         </is>
       </c>
       <c r="C65" s="12" t="inlineStr">
         <is>
-          <t>Santa Monica</t>
+          <t>Sor Juana</t>
         </is>
       </c>
       <c r="D65" s="12" t="inlineStr">
@@ -4180,17 +4147,17 @@
       </c>
       <c r="B66" s="17" t="inlineStr">
         <is>
-          <t>38442</t>
+          <t>38925</t>
         </is>
       </c>
       <c r="C66" s="8" t="inlineStr">
         <is>
-          <t>Sor Juana</t>
+          <t>Star Medica Lomas Verdes</t>
         </is>
       </c>
       <c r="D66" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E66" s="7" t="n">
@@ -4220,17 +4187,17 @@
       </c>
       <c r="B67" s="15" t="inlineStr">
         <is>
-          <t>38925</t>
+          <t>38411</t>
         </is>
       </c>
       <c r="C67" s="12" t="inlineStr">
         <is>
-          <t>Star Medica Lomas Verdes</t>
+          <t>Torres Lindavista</t>
         </is>
       </c>
       <c r="D67" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E67" s="11" t="n">
@@ -4260,17 +4227,17 @@
       </c>
       <c r="B68" s="17" t="inlineStr">
         <is>
-          <t>38411</t>
+          <t>43130</t>
         </is>
       </c>
       <c r="C68" s="8" t="inlineStr">
         <is>
-          <t>Torres Lindavista</t>
+          <t>Town Center Nicolás Romero</t>
         </is>
       </c>
       <c r="D68" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E68" s="7" t="n">
@@ -4300,17 +4267,17 @@
       </c>
       <c r="B69" s="15" t="inlineStr">
         <is>
-          <t>43130</t>
+          <t>38694</t>
         </is>
       </c>
       <c r="C69" s="12" t="inlineStr">
         <is>
-          <t>Town Center Nicolás Romero</t>
+          <t>Villas de la Hacienda</t>
         </is>
       </c>
       <c r="D69" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E69" s="11" t="n">
@@ -4340,17 +4307,17 @@
       </c>
       <c r="B70" s="17" t="inlineStr">
         <is>
-          <t>38694</t>
+          <t>38115</t>
         </is>
       </c>
       <c r="C70" s="8" t="inlineStr">
         <is>
-          <t>Villas de la Hacienda</t>
+          <t>Zona Azul</t>
         </is>
       </c>
       <c r="D70" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E70" s="7" t="n">
@@ -4380,12 +4347,12 @@
       </c>
       <c r="B71" s="15" t="inlineStr">
         <is>
-          <t>38115</t>
+          <t>38142</t>
         </is>
       </c>
       <c r="C71" s="12" t="inlineStr">
         <is>
-          <t>Zona Azul</t>
+          <t>Zona Esmeralda</t>
         </is>
       </c>
       <c r="D71" s="12" t="inlineStr">
@@ -4420,21 +4387,21 @@
       </c>
       <c r="B72" s="17" t="inlineStr">
         <is>
-          <t>38142</t>
+          <t>38207</t>
         </is>
       </c>
       <c r="C72" s="8" t="inlineStr">
         <is>
-          <t>Zona Esmeralda</t>
+          <t>Lindavista II</t>
         </is>
       </c>
       <c r="D72" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E72" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F72" s="7" t="n">
         <v>9</v>
@@ -4460,17 +4427,17 @@
       </c>
       <c r="B73" s="15" t="inlineStr">
         <is>
-          <t>38207</t>
+          <t>38845</t>
         </is>
       </c>
       <c r="C73" s="12" t="inlineStr">
         <is>
-          <t>Lindavista II</t>
+          <t>Mundo E II</t>
         </is>
       </c>
       <c r="D73" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E73" s="11" t="n">
@@ -4500,17 +4467,17 @@
       </c>
       <c r="B74" s="17" t="inlineStr">
         <is>
-          <t>38845</t>
+          <t>38266</t>
         </is>
       </c>
       <c r="C74" s="8" t="inlineStr">
         <is>
-          <t>Mundo E II</t>
+          <t>San Mateo</t>
         </is>
       </c>
       <c r="D74" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E74" s="7" t="n">
@@ -4540,24 +4507,24 @@
       </c>
       <c r="B75" s="15" t="inlineStr">
         <is>
-          <t>38266</t>
+          <t>38176</t>
         </is>
       </c>
       <c r="C75" s="12" t="inlineStr">
         <is>
-          <t>San Mateo</t>
+          <t>Periferico Satélite DT</t>
         </is>
       </c>
       <c r="D75" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E75" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F75" s="11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G75" s="13">
         <f>IFERROR(E75/(E75+F75),0)</f>
@@ -5060,17 +5027,17 @@
       </c>
       <c r="B88" s="17" t="inlineStr">
         <is>
-          <t>38240</t>
+          <t>38375</t>
         </is>
       </c>
       <c r="C88" s="8" t="inlineStr">
         <is>
-          <t>Amberes</t>
+          <t>Americas Ecatepec</t>
         </is>
       </c>
       <c r="D88" s="8" t="inlineStr">
         <is>
-          <t>Guadalupe Ibarra Martínez</t>
+          <t>Monica Selene Morales Ibarra</t>
         </is>
       </c>
       <c r="E88" s="7" t="n">
@@ -5100,17 +5067,17 @@
       </c>
       <c r="B89" s="15" t="inlineStr">
         <is>
-          <t>38375</t>
+          <t>38508</t>
         </is>
       </c>
       <c r="C89" s="12" t="inlineStr">
         <is>
-          <t>Americas Ecatepec</t>
+          <t>Ampliacion Santa Fe</t>
         </is>
       </c>
       <c r="D89" s="12" t="inlineStr">
         <is>
-          <t>Monica Selene Morales Ibarra</t>
+          <t>Erika Julieta Contreras Aguilera</t>
         </is>
       </c>
       <c r="E89" s="11" t="n">
@@ -5140,17 +5107,17 @@
       </c>
       <c r="B90" s="17" t="inlineStr">
         <is>
-          <t>38508</t>
+          <t>38415</t>
         </is>
       </c>
       <c r="C90" s="8" t="inlineStr">
         <is>
-          <t>Ampliacion Santa Fe</t>
+          <t>Amsterdam</t>
         </is>
       </c>
       <c r="D90" s="8" t="inlineStr">
         <is>
-          <t>Erika Julieta Contreras Aguilera</t>
+          <t>Alberto Torrado Aguilar Cauz</t>
         </is>
       </c>
       <c r="E90" s="7" t="n">
@@ -5180,17 +5147,17 @@
       </c>
       <c r="B91" s="15" t="inlineStr">
         <is>
-          <t>38415</t>
+          <t>38101</t>
         </is>
       </c>
       <c r="C91" s="12" t="inlineStr">
         <is>
-          <t>Amsterdam</t>
+          <t>Angel</t>
         </is>
       </c>
       <c r="D91" s="12" t="inlineStr">
         <is>
-          <t>Alberto Torrado Aguilar Cauz</t>
+          <t>Guadalupe Ibarra Martínez</t>
         </is>
       </c>
       <c r="E91" s="11" t="n">
@@ -5220,17 +5187,17 @@
       </c>
       <c r="B92" s="17" t="inlineStr">
         <is>
-          <t>38101</t>
+          <t>38471</t>
         </is>
       </c>
       <c r="C92" s="8" t="inlineStr">
         <is>
-          <t>Angel</t>
+          <t>Angeles Acoxpa</t>
         </is>
       </c>
       <c r="D92" s="8" t="inlineStr">
         <is>
-          <t>Guadalupe Ibarra Martínez</t>
+          <t>Fernando Eduardo Verdugo Saldaña</t>
         </is>
       </c>
       <c r="E92" s="7" t="n">
@@ -5260,17 +5227,17 @@
       </c>
       <c r="B93" s="15" t="inlineStr">
         <is>
-          <t>38471</t>
+          <t>38194</t>
         </is>
       </c>
       <c r="C93" s="12" t="inlineStr">
         <is>
-          <t>Angeles Acoxpa</t>
+          <t>Antara</t>
         </is>
       </c>
       <c r="D93" s="12" t="inlineStr">
         <is>
-          <t>Fernando Eduardo Verdugo Saldaña</t>
+          <t>Luis Manuel Neri Saldaña</t>
         </is>
       </c>
       <c r="E93" s="11" t="n">
@@ -5300,12 +5267,12 @@
       </c>
       <c r="B94" s="17" t="inlineStr">
         <is>
-          <t>38194</t>
+          <t>38612</t>
         </is>
       </c>
       <c r="C94" s="8" t="inlineStr">
         <is>
-          <t>Antara</t>
+          <t>Antara II</t>
         </is>
       </c>
       <c r="D94" s="8" t="inlineStr">
@@ -5340,17 +5307,17 @@
       </c>
       <c r="B95" s="15" t="inlineStr">
         <is>
-          <t>38612</t>
+          <t>38800</t>
         </is>
       </c>
       <c r="C95" s="12" t="inlineStr">
         <is>
-          <t>Antara II</t>
+          <t>Antenas PA</t>
         </is>
       </c>
       <c r="D95" s="12" t="inlineStr">
         <is>
-          <t>Luis Manuel Neri Saldaña</t>
+          <t>Jesus Antonio Elguera Flores</t>
         </is>
       </c>
       <c r="E95" s="11" t="n">
@@ -5380,12 +5347,12 @@
       </c>
       <c r="B96" s="17" t="inlineStr">
         <is>
-          <t>38800</t>
+          <t>38801</t>
         </is>
       </c>
       <c r="C96" s="8" t="inlineStr">
         <is>
-          <t>Antenas PA</t>
+          <t>Antenas PB</t>
         </is>
       </c>
       <c r="D96" s="8" t="inlineStr">
@@ -5420,17 +5387,17 @@
       </c>
       <c r="B97" s="15" t="inlineStr">
         <is>
-          <t>38801</t>
+          <t>38803</t>
         </is>
       </c>
       <c r="C97" s="12" t="inlineStr">
         <is>
-          <t>Antenas PB</t>
+          <t>Apto T1 AMB Puerta 8</t>
         </is>
       </c>
       <c r="D97" s="12" t="inlineStr">
         <is>
-          <t>Jesus Antonio Elguera Flores</t>
+          <t>Maria Anallely Sanchez Garcia</t>
         </is>
       </c>
       <c r="E97" s="11" t="n">
@@ -5460,12 +5427,12 @@
       </c>
       <c r="B98" s="17" t="inlineStr">
         <is>
-          <t>38803</t>
+          <t>38796</t>
         </is>
       </c>
       <c r="C98" s="8" t="inlineStr">
         <is>
-          <t>Apto T1 AMB Puerta 8</t>
+          <t>Apto T1 AMB Sala J</t>
         </is>
       </c>
       <c r="D98" s="8" t="inlineStr">
@@ -5500,12 +5467,12 @@
       </c>
       <c r="B99" s="15" t="inlineStr">
         <is>
-          <t>38796</t>
+          <t>38795</t>
         </is>
       </c>
       <c r="C99" s="12" t="inlineStr">
         <is>
-          <t>Apto T1 AMB Sala J</t>
+          <t>Apto T1 Pb N Pta 7</t>
         </is>
       </c>
       <c r="D99" s="12" t="inlineStr">
@@ -5540,17 +5507,17 @@
       </c>
       <c r="B100" s="17" t="inlineStr">
         <is>
-          <t>38795</t>
+          <t>43162</t>
         </is>
       </c>
       <c r="C100" s="8" t="inlineStr">
         <is>
-          <t>Apto T1 Pb N Pta 7</t>
+          <t>Apto Toluca SUE</t>
         </is>
       </c>
       <c r="D100" s="8" t="inlineStr">
         <is>
-          <t>Maria Anallely Sanchez Garcia</t>
+          <t>Jose De Jesus Magos Arzaluz</t>
         </is>
       </c>
       <c r="E100" s="7" t="n">
@@ -5580,17 +5547,17 @@
       </c>
       <c r="B101" s="15" t="inlineStr">
         <is>
-          <t>43162</t>
+          <t>38567</t>
         </is>
       </c>
       <c r="C101" s="12" t="inlineStr">
         <is>
-          <t>Apto Toluca SUE</t>
+          <t>Aragon II</t>
         </is>
       </c>
       <c r="D101" s="12" t="inlineStr">
         <is>
-          <t>Jose De Jesus Magos Arzaluz</t>
+          <t>Monica Selene Morales Ibarra</t>
         </is>
       </c>
       <c r="E101" s="11" t="n">
@@ -5620,17 +5587,17 @@
       </c>
       <c r="B102" s="17" t="inlineStr">
         <is>
-          <t>38567</t>
+          <t>38746</t>
         </is>
       </c>
       <c r="C102" s="8" t="inlineStr">
         <is>
-          <t>Aragon II</t>
+          <t>Arcos Bosques II</t>
         </is>
       </c>
       <c r="D102" s="8" t="inlineStr">
         <is>
-          <t>Monica Selene Morales Ibarra</t>
+          <t>Adriana Alejandra Tanus Buhler</t>
         </is>
       </c>
       <c r="E102" s="7" t="n">
@@ -5660,17 +5627,17 @@
       </c>
       <c r="B103" s="15" t="inlineStr">
         <is>
-          <t>38746</t>
+          <t>38784</t>
         </is>
       </c>
       <c r="C103" s="12" t="inlineStr">
         <is>
-          <t>Arcos Bosques II</t>
+          <t>Artz Pedregal PB CC</t>
         </is>
       </c>
       <c r="D103" s="12" t="inlineStr">
         <is>
-          <t>Adriana Alejandra Tanus Buhler</t>
+          <t>Hazar Susim Trejo Hernandez</t>
         </is>
       </c>
       <c r="E103" s="11" t="n">
@@ -5700,12 +5667,12 @@
       </c>
       <c r="B104" s="17" t="inlineStr">
         <is>
-          <t>38784</t>
+          <t>38791</t>
         </is>
       </c>
       <c r="C104" s="8" t="inlineStr">
         <is>
-          <t>Artz Pedregal PB CC</t>
+          <t>Artz Pedregal Reserve</t>
         </is>
       </c>
       <c r="D104" s="8" t="inlineStr">
@@ -5740,17 +5707,17 @@
       </c>
       <c r="B105" s="15" t="inlineStr">
         <is>
-          <t>38791</t>
+          <t>38717</t>
         </is>
       </c>
       <c r="C105" s="12" t="inlineStr">
         <is>
-          <t>Artz Pedregal Reserve</t>
+          <t>Av Revolucion</t>
         </is>
       </c>
       <c r="D105" s="12" t="inlineStr">
         <is>
-          <t>Hazar Susim Trejo Hernandez</t>
+          <t>Manuel Alejandro Avila Molina</t>
         </is>
       </c>
       <c r="E105" s="11" t="n">
@@ -5780,17 +5747,17 @@
       </c>
       <c r="B106" s="17" t="inlineStr">
         <is>
-          <t>38717</t>
+          <t>38568</t>
         </is>
       </c>
       <c r="C106" s="8" t="inlineStr">
         <is>
-          <t>Av Revolucion</t>
+          <t>Av Stim</t>
         </is>
       </c>
       <c r="D106" s="8" t="inlineStr">
         <is>
-          <t>Manuel Alejandro Avila Molina</t>
+          <t>Areli Anahi Lazcano Lezama</t>
         </is>
       </c>
       <c r="E106" s="7" t="n">
@@ -5820,17 +5787,17 @@
       </c>
       <c r="B107" s="15" t="inlineStr">
         <is>
-          <t>38568</t>
+          <t>38715</t>
         </is>
       </c>
       <c r="C107" s="12" t="inlineStr">
         <is>
-          <t>Av Stim</t>
+          <t>Av. Coyoacan DT only</t>
         </is>
       </c>
       <c r="D107" s="12" t="inlineStr">
         <is>
-          <t>Areli Anahi Lazcano Lezama</t>
+          <t>Juan Jesus Zuñiga Flores</t>
         </is>
       </c>
       <c r="E107" s="11" t="n">
@@ -5860,17 +5827,17 @@
       </c>
       <c r="B108" s="17" t="inlineStr">
         <is>
-          <t>38715</t>
+          <t>43163</t>
         </is>
       </c>
       <c r="C108" s="8" t="inlineStr">
         <is>
-          <t>Av. Coyoacan DT only</t>
+          <t>Av. México Ixtapaluca</t>
         </is>
       </c>
       <c r="D108" s="8" t="inlineStr">
         <is>
-          <t>Juan Jesus Zuñiga Flores</t>
+          <t>Jesus Antonio Elguera Flores</t>
         </is>
       </c>
       <c r="E108" s="7" t="n">
@@ -5900,17 +5867,17 @@
       </c>
       <c r="B109" s="15" t="inlineStr">
         <is>
-          <t>43163</t>
+          <t>38957</t>
         </is>
       </c>
       <c r="C109" s="12" t="inlineStr">
         <is>
-          <t>Av. México Ixtapaluca</t>
+          <t>Avándaro</t>
         </is>
       </c>
       <c r="D109" s="12" t="inlineStr">
         <is>
-          <t>Jesus Antonio Elguera Flores</t>
+          <t>Daniel Flores Maldonado</t>
         </is>
       </c>
       <c r="E109" s="11" t="n">
@@ -5940,17 +5907,17 @@
       </c>
       <c r="B110" s="17" t="inlineStr">
         <is>
-          <t>38957</t>
+          <t>38617</t>
         </is>
       </c>
       <c r="C110" s="8" t="inlineStr">
         <is>
-          <t>Avándaro</t>
+          <t>Axomiatla</t>
         </is>
       </c>
       <c r="D110" s="8" t="inlineStr">
         <is>
-          <t>Daniel Flores Maldonado</t>
+          <t>Adriana Alejandra Tanus Buhler</t>
         </is>
       </c>
       <c r="E110" s="7" t="n">
@@ -5980,17 +5947,17 @@
       </c>
       <c r="B111" s="15" t="inlineStr">
         <is>
-          <t>38617</t>
+          <t>38419</t>
         </is>
       </c>
       <c r="C111" s="12" t="inlineStr">
         <is>
-          <t>Axomiatla</t>
+          <t>Balbuena</t>
         </is>
       </c>
       <c r="D111" s="12" t="inlineStr">
         <is>
-          <t>Adriana Alejandra Tanus Buhler</t>
+          <t>Ariana Janet Gutierrez Martinez</t>
         </is>
       </c>
       <c r="E111" s="11" t="n">
@@ -6020,17 +5987,17 @@
       </c>
       <c r="B112" s="17" t="inlineStr">
         <is>
-          <t>38419</t>
+          <t>38964</t>
         </is>
       </c>
       <c r="C112" s="8" t="inlineStr">
         <is>
-          <t>Balbuena</t>
+          <t>Biblioteca Tec</t>
         </is>
       </c>
       <c r="D112" s="8" t="inlineStr">
         <is>
-          <t>Ariana Janet Gutierrez Martinez</t>
+          <t>Fernando Eduardo Verdugo Saldaña</t>
         </is>
       </c>
       <c r="E112" s="7" t="n">
@@ -6060,17 +6027,17 @@
       </c>
       <c r="B113" s="15" t="inlineStr">
         <is>
-          <t>38964</t>
+          <t>43164</t>
         </is>
       </c>
       <c r="C113" s="12" t="inlineStr">
         <is>
-          <t>Biblioteca Tec</t>
+          <t>Blvd Ojo de Agua DT</t>
         </is>
       </c>
       <c r="D113" s="12" t="inlineStr">
         <is>
-          <t>Fernando Eduardo Verdugo Saldaña</t>
+          <t>Monica Selene Morales Ibarra</t>
         </is>
       </c>
       <c r="E113" s="11" t="n">
@@ -6100,17 +6067,17 @@
       </c>
       <c r="B114" s="17" t="inlineStr">
         <is>
-          <t>43164</t>
+          <t>38433</t>
         </is>
       </c>
       <c r="C114" s="8" t="inlineStr">
         <is>
-          <t>Blvd Ojo de Agua DT</t>
+          <t>Bolsa Mexicana de Valores</t>
         </is>
       </c>
       <c r="D114" s="8" t="inlineStr">
         <is>
-          <t>Monica Selene Morales Ibarra</t>
+          <t>Guadalupe Ibarra Martínez</t>
         </is>
       </c>
       <c r="E114" s="7" t="n">
@@ -6140,17 +6107,17 @@
       </c>
       <c r="B115" s="15" t="inlineStr">
         <is>
-          <t>38433</t>
+          <t>38918</t>
         </is>
       </c>
       <c r="C115" s="12" t="inlineStr">
         <is>
-          <t>Bolsa Mexicana de Valores</t>
+          <t>Bosque Real</t>
         </is>
       </c>
       <c r="D115" s="12" t="inlineStr">
         <is>
-          <t>Guadalupe Ibarra Martínez</t>
+          <t>Areli Anahi Lazcano Lezama</t>
         </is>
       </c>
       <c r="E115" s="11" t="n">
@@ -6180,17 +6147,17 @@
       </c>
       <c r="B116" s="17" t="inlineStr">
         <is>
-          <t>38918</t>
+          <t>38367</t>
         </is>
       </c>
       <c r="C116" s="8" t="inlineStr">
         <is>
-          <t>Bosque Real</t>
+          <t>CM Coapa</t>
         </is>
       </c>
       <c r="D116" s="8" t="inlineStr">
         <is>
-          <t>Areli Anahi Lazcano Lezama</t>
+          <t>Fernando Eduardo Verdugo Saldaña</t>
         </is>
       </c>
       <c r="E116" s="7" t="n">
@@ -6220,17 +6187,17 @@
       </c>
       <c r="B117" s="15" t="inlineStr">
         <is>
-          <t>38367</t>
+          <t>38619</t>
         </is>
       </c>
       <c r="C117" s="12" t="inlineStr">
         <is>
-          <t>CM Coapa</t>
+          <t>Calzada de Tlalpan</t>
         </is>
       </c>
       <c r="D117" s="12" t="inlineStr">
         <is>
-          <t>Fernando Eduardo Verdugo Saldaña</t>
+          <t>Luis Alberto Quevedo Rodriguez</t>
         </is>
       </c>
       <c r="E117" s="11" t="n">
@@ -6260,17 +6227,17 @@
       </c>
       <c r="B118" s="17" t="inlineStr">
         <is>
-          <t>38619</t>
+          <t>38108</t>
         </is>
       </c>
       <c r="C118" s="8" t="inlineStr">
         <is>
-          <t>Calzada de Tlalpan</t>
+          <t>Campos Eliseos</t>
         </is>
       </c>
       <c r="D118" s="8" t="inlineStr">
         <is>
-          <t>Luis Alberto Quevedo Rodriguez</t>
+          <t>Alberto Torrado Aguilar Cauz</t>
         </is>
       </c>
       <c r="E118" s="7" t="n">
@@ -6300,17 +6267,17 @@
       </c>
       <c r="B119" s="15" t="inlineStr">
         <is>
-          <t>38108</t>
+          <t>38555</t>
         </is>
       </c>
       <c r="C119" s="12" t="inlineStr">
         <is>
-          <t>Campos Eliseos</t>
+          <t>Capital Reforma</t>
         </is>
       </c>
       <c r="D119" s="12" t="inlineStr">
         <is>
-          <t>Alberto Torrado Aguilar Cauz</t>
+          <t>Guadalupe Ibarra Martínez</t>
         </is>
       </c>
       <c r="E119" s="11" t="n">
@@ -6340,17 +6307,17 @@
       </c>
       <c r="B120" s="17" t="inlineStr">
         <is>
-          <t>38555</t>
+          <t>38547</t>
         </is>
       </c>
       <c r="C120" s="8" t="inlineStr">
         <is>
-          <t>Capital Reforma</t>
+          <t>Carr Toluca Mexico KM48</t>
         </is>
       </c>
       <c r="D120" s="8" t="inlineStr">
         <is>
-          <t>Guadalupe Ibarra Martínez</t>
+          <t>Daniel Flores Maldonado</t>
         </is>
       </c>
       <c r="E120" s="7" t="n">
@@ -6380,17 +6347,17 @@
       </c>
       <c r="B121" s="15" t="inlineStr">
         <is>
-          <t>38547</t>
+          <t>43011</t>
         </is>
       </c>
       <c r="C121" s="12" t="inlineStr">
         <is>
-          <t>Carr Toluca Mexico KM48</t>
+          <t>Carr Toluca-Atlacomulco DT</t>
         </is>
       </c>
       <c r="D121" s="12" t="inlineStr">
         <is>
-          <t>Daniel Flores Maldonado</t>
+          <t>Andrea Nava Guzman</t>
         </is>
       </c>
       <c r="E121" s="11" t="n">
@@ -6420,17 +6387,17 @@
       </c>
       <c r="B122" s="17" t="inlineStr">
         <is>
-          <t>43011</t>
+          <t>38646</t>
         </is>
       </c>
       <c r="C122" s="8" t="inlineStr">
         <is>
-          <t>Carr Toluca-Atlacomulco DT</t>
+          <t>Carracci</t>
         </is>
       </c>
       <c r="D122" s="8" t="inlineStr">
         <is>
-          <t>Andrea Nava Guzman</t>
+          <t>Adriana Alejandra Tanus Buhler</t>
         </is>
       </c>
       <c r="E122" s="7" t="n">
@@ -6460,17 +6427,17 @@
       </c>
       <c r="B123" s="15" t="inlineStr">
         <is>
-          <t>38646</t>
+          <t>38594</t>
         </is>
       </c>
       <c r="C123" s="12" t="inlineStr">
         <is>
-          <t>Carracci</t>
+          <t>Carretera Mexico Puebla</t>
         </is>
       </c>
       <c r="D123" s="12" t="inlineStr">
         <is>
-          <t>Adriana Alejandra Tanus Buhler</t>
+          <t>Jesus Antonio Elguera Flores</t>
         </is>
       </c>
       <c r="E123" s="11" t="n">
@@ -6500,17 +6467,17 @@
       </c>
       <c r="B124" s="17" t="inlineStr">
         <is>
-          <t>38594</t>
+          <t>38607</t>
         </is>
       </c>
       <c r="C124" s="8" t="inlineStr">
         <is>
-          <t>Carretera Mexico Puebla</t>
+          <t>Carretera Mexico Toluca KM42</t>
         </is>
       </c>
       <c r="D124" s="8" t="inlineStr">
         <is>
-          <t>Jesus Antonio Elguera Flores</t>
+          <t>Erika Julieta Contreras Aguilera</t>
         </is>
       </c>
       <c r="E124" s="7" t="n">
@@ -6540,12 +6507,12 @@
       </c>
       <c r="B125" s="15" t="inlineStr">
         <is>
-          <t>38607</t>
+          <t>38633</t>
         </is>
       </c>
       <c r="C125" s="12" t="inlineStr">
         <is>
-          <t>Carretera Mexico Toluca KM42</t>
+          <t>Carretera Toluca Mexico (plaza cedros DT)</t>
         </is>
       </c>
       <c r="D125" s="12" t="inlineStr">
@@ -6580,17 +6547,17 @@
       </c>
       <c r="B126" s="17" t="inlineStr">
         <is>
-          <t>38633</t>
+          <t>38399</t>
         </is>
       </c>
       <c r="C126" s="8" t="inlineStr">
         <is>
-          <t>Carretera Toluca Mexico (plaza cedros DT)</t>
+          <t>Carso Polanco I</t>
         </is>
       </c>
       <c r="D126" s="8" t="inlineStr">
         <is>
-          <t>Erika Julieta Contreras Aguilera</t>
+          <t>Luis Manuel Neri Saldaña</t>
         </is>
       </c>
       <c r="E126" s="7" t="n">
@@ -6620,17 +6587,17 @@
       </c>
       <c r="B127" s="15" t="inlineStr">
         <is>
-          <t>38399</t>
+          <t>38496</t>
         </is>
       </c>
       <c r="C127" s="12" t="inlineStr">
         <is>
-          <t>Carso Polanco I</t>
+          <t>Casa Taxqueña</t>
         </is>
       </c>
       <c r="D127" s="12" t="inlineStr">
         <is>
-          <t>Luis Manuel Neri Saldaña</t>
+          <t>Ariana Janet Gutierrez Martinez</t>
         </is>
       </c>
       <c r="E127" s="11" t="n">
@@ -6660,17 +6627,17 @@
       </c>
       <c r="B128" s="17" t="inlineStr">
         <is>
-          <t>38496</t>
+          <t>43058</t>
         </is>
       </c>
       <c r="C128" s="8" t="inlineStr">
         <is>
-          <t>Casa Taxqueña</t>
+          <t>Casa de Gobierno DT</t>
         </is>
       </c>
       <c r="D128" s="8" t="inlineStr">
         <is>
-          <t>Ariana Janet Gutierrez Martinez</t>
+          <t>Andrea Nava Guzman</t>
         </is>
       </c>
       <c r="E128" s="7" t="n">
@@ -6700,17 +6667,17 @@
       </c>
       <c r="B129" s="15" t="inlineStr">
         <is>
-          <t>43058</t>
+          <t>38361</t>
         </is>
       </c>
       <c r="C129" s="12" t="inlineStr">
         <is>
-          <t>Casa de Gobierno DT</t>
+          <t>Castorena</t>
         </is>
       </c>
       <c r="D129" s="12" t="inlineStr">
         <is>
-          <t>Andrea Nava Guzman</t>
+          <t>Erika Julieta Contreras Aguilera</t>
         </is>
       </c>
       <c r="E129" s="11" t="n">
@@ -6740,17 +6707,17 @@
       </c>
       <c r="B130" s="17" t="inlineStr">
         <is>
-          <t>38361</t>
+          <t>38815</t>
         </is>
       </c>
       <c r="C130" s="8" t="inlineStr">
         <is>
-          <t>Castorena</t>
+          <t>Central Interlomas</t>
         </is>
       </c>
       <c r="D130" s="8" t="inlineStr">
         <is>
-          <t>Erika Julieta Contreras Aguilera</t>
+          <t>Areli Anahi Lazcano Lezama</t>
         </is>
       </c>
       <c r="E130" s="7" t="n">
@@ -6780,17 +6747,17 @@
       </c>
       <c r="B131" s="15" t="inlineStr">
         <is>
-          <t>38815</t>
+          <t>38148</t>
         </is>
       </c>
       <c r="C131" s="12" t="inlineStr">
         <is>
-          <t>Central Interlomas</t>
+          <t>Centro Comercial Santa Fe 1</t>
         </is>
       </c>
       <c r="D131" s="12" t="inlineStr">
         <is>
-          <t>Areli Anahi Lazcano Lezama</t>
+          <t>Erika Julieta Contreras Aguilera</t>
         </is>
       </c>
       <c r="E131" s="11" t="n">
@@ -6820,12 +6787,12 @@
       </c>
       <c r="B132" s="17" t="inlineStr">
         <is>
-          <t>38148</t>
+          <t>38225</t>
         </is>
       </c>
       <c r="C132" s="8" t="inlineStr">
         <is>
-          <t>Centro Comercial Santa Fe 1</t>
+          <t>Centro Comercial Santa Fe 2</t>
         </is>
       </c>
       <c r="D132" s="8" t="inlineStr">
@@ -6860,12 +6827,12 @@
       </c>
       <c r="B133" s="15" t="inlineStr">
         <is>
-          <t>38225</t>
+          <t>38747</t>
         </is>
       </c>
       <c r="C133" s="12" t="inlineStr">
         <is>
-          <t>Centro Comercial Santa Fe 2</t>
+          <t>Centro Comercial Santa Fe 3</t>
         </is>
       </c>
       <c r="D133" s="12" t="inlineStr">
@@ -6900,17 +6867,17 @@
       </c>
       <c r="B134" s="17" t="inlineStr">
         <is>
-          <t>38747</t>
+          <t>38400</t>
         </is>
       </c>
       <c r="C134" s="8" t="inlineStr">
         <is>
-          <t>Centro Comercial Santa Fe 3</t>
+          <t>Centro Medico ABC Santa Fe</t>
         </is>
       </c>
       <c r="D134" s="8" t="inlineStr">
         <is>
-          <t>Erika Julieta Contreras Aguilera</t>
+          <t>Jose De Jesus Magos Arzaluz</t>
         </is>
       </c>
       <c r="E134" s="7" t="n">
@@ -6940,17 +6907,17 @@
       </c>
       <c r="B135" s="15" t="inlineStr">
         <is>
-          <t>38400</t>
+          <t>38727</t>
         </is>
       </c>
       <c r="C135" s="12" t="inlineStr">
         <is>
-          <t>Centro Medico ABC Santa Fe</t>
+          <t>Centro Tk</t>
         </is>
       </c>
       <c r="D135" s="12" t="inlineStr">
         <is>
-          <t>Jose De Jesus Magos Arzaluz</t>
+          <t>Manuel Alejandro Avila Molina</t>
         </is>
       </c>
       <c r="E135" s="11" t="n">
@@ -6980,17 +6947,17 @@
       </c>
       <c r="B136" s="17" t="inlineStr">
         <is>
-          <t>38727</t>
+          <t>38470</t>
         </is>
       </c>
       <c r="C136" s="8" t="inlineStr">
         <is>
-          <t>Centro Tk</t>
+          <t>Chapultepec Reforma</t>
         </is>
       </c>
       <c r="D136" s="8" t="inlineStr">
         <is>
-          <t>Manuel Alejandro Avila Molina</t>
+          <t>Luis Manuel Neri Saldaña</t>
         </is>
       </c>
       <c r="E136" s="7" t="n">
@@ -7020,17 +6987,17 @@
       </c>
       <c r="B137" s="15" t="inlineStr">
         <is>
-          <t>38470</t>
+          <t>38526</t>
         </is>
       </c>
       <c r="C137" s="12" t="inlineStr">
         <is>
-          <t>Chapultepec Reforma</t>
+          <t>City Shops Del Valle</t>
         </is>
       </c>
       <c r="D137" s="12" t="inlineStr">
         <is>
-          <t>Luis Manuel Neri Saldaña</t>
+          <t>Luis Alberto Quevedo Rodriguez</t>
         </is>
       </c>
       <c r="E137" s="11" t="n">
@@ -7060,17 +7027,17 @@
       </c>
       <c r="B138" s="17" t="inlineStr">
         <is>
-          <t>38856</t>
+          <t>38438</t>
         </is>
       </c>
       <c r="C138" s="8" t="inlineStr">
         <is>
-          <t>Cinemex Artz</t>
+          <t>City Walk</t>
         </is>
       </c>
       <c r="D138" s="8" t="inlineStr">
         <is>
-          <t>Hazar Susim Trejo Hernandez</t>
+          <t>Erika Julieta Contreras Aguilera</t>
         </is>
       </c>
       <c r="E138" s="7" t="n">
@@ -7100,17 +7067,17 @@
       </c>
       <c r="B139" s="15" t="inlineStr">
         <is>
-          <t>38915</t>
+          <t>38351</t>
         </is>
       </c>
       <c r="C139" s="12" t="inlineStr">
         <is>
-          <t>Cinemex Galerias Insurgentes</t>
+          <t>Ciudad Jardin l</t>
         </is>
       </c>
       <c r="D139" s="12" t="inlineStr">
         <is>
-          <t>DM pendiente</t>
+          <t>Monica Selene Morales Ibarra</t>
         </is>
       </c>
       <c r="E139" s="11" t="n">
@@ -7140,17 +7107,17 @@
       </c>
       <c r="B140" s="17" t="inlineStr">
         <is>
-          <t>38914</t>
+          <t>38511</t>
         </is>
       </c>
       <c r="C140" s="8" t="inlineStr">
         <is>
-          <t>Cinemex Terraza Interlomas</t>
+          <t>Ciudad Jardin ll</t>
         </is>
       </c>
       <c r="D140" s="8" t="inlineStr">
         <is>
-          <t>Areli Anahi Lazcano Lezama</t>
+          <t>Monica Selene Morales Ibarra</t>
         </is>
       </c>
       <c r="E140" s="7" t="n">
@@ -7180,17 +7147,17 @@
       </c>
       <c r="B141" s="15" t="inlineStr">
         <is>
-          <t>38526</t>
+          <t>38393</t>
         </is>
       </c>
       <c r="C141" s="12" t="inlineStr">
         <is>
-          <t>City Shops Del Valle</t>
+          <t>Coapa Chedraui</t>
         </is>
       </c>
       <c r="D141" s="12" t="inlineStr">
         <is>
-          <t>Luis Alberto Quevedo Rodriguez</t>
+          <t>Fernando Eduardo Verdugo Saldaña</t>
         </is>
       </c>
       <c r="E141" s="11" t="n">
@@ -7220,17 +7187,17 @@
       </c>
       <c r="B142" s="17" t="inlineStr">
         <is>
-          <t>38438</t>
+          <t>38773</t>
         </is>
       </c>
       <c r="C142" s="8" t="inlineStr">
         <is>
-          <t>City Walk</t>
+          <t>Colegio Americano</t>
         </is>
       </c>
       <c r="D142" s="8" t="inlineStr">
         <is>
-          <t>Erika Julieta Contreras Aguilera</t>
+          <t>Manuel Alejandro Avila Molina</t>
         </is>
       </c>
       <c r="E142" s="7" t="n">
@@ -7260,17 +7227,17 @@
       </c>
       <c r="B143" s="15" t="inlineStr">
         <is>
-          <t>38351</t>
+          <t>38128</t>
         </is>
       </c>
       <c r="C143" s="12" t="inlineStr">
         <is>
-          <t>Ciudad Jardin l</t>
+          <t>Condesa</t>
         </is>
       </c>
       <c r="D143" s="12" t="inlineStr">
         <is>
-          <t>Monica Selene Morales Ibarra</t>
+          <t>Alberto Torrado Aguilar Cauz</t>
         </is>
       </c>
       <c r="E143" s="11" t="n">
@@ -7300,17 +7267,17 @@
       </c>
       <c r="B144" s="17" t="inlineStr">
         <is>
-          <t>38511</t>
+          <t>38663</t>
         </is>
       </c>
       <c r="C144" s="8" t="inlineStr">
         <is>
-          <t>Ciudad Jardin ll</t>
+          <t>Copilco 20</t>
         </is>
       </c>
       <c r="D144" s="8" t="inlineStr">
         <is>
-          <t>Monica Selene Morales Ibarra</t>
+          <t>Jaqueline Cortes Ayala</t>
         </is>
       </c>
       <c r="E144" s="7" t="n">
@@ -7340,17 +7307,17 @@
       </c>
       <c r="B145" s="15" t="inlineStr">
         <is>
-          <t>38393</t>
+          <t>38798</t>
         </is>
       </c>
       <c r="C145" s="12" t="inlineStr">
         <is>
-          <t>Coapa Chedraui</t>
+          <t>Corp. Televisa Sta Fe</t>
         </is>
       </c>
       <c r="D145" s="12" t="inlineStr">
         <is>
-          <t>Fernando Eduardo Verdugo Saldaña</t>
+          <t>Jose De Jesus Magos Arzaluz</t>
         </is>
       </c>
       <c r="E145" s="11" t="n">
@@ -7380,12 +7347,12 @@
       </c>
       <c r="B146" s="17" t="inlineStr">
         <is>
-          <t>38773</t>
+          <t>38709</t>
         </is>
       </c>
       <c r="C146" s="8" t="inlineStr">
         <is>
-          <t>Colegio Americano</t>
+          <t>Corporativo Barranca</t>
         </is>
       </c>
       <c r="D146" s="8" t="inlineStr">
@@ -7420,17 +7387,17 @@
       </c>
       <c r="B147" s="15" t="inlineStr">
         <is>
-          <t>38128</t>
+          <t>38464</t>
         </is>
       </c>
       <c r="C147" s="12" t="inlineStr">
         <is>
-          <t>Condesa</t>
+          <t>Corporativo Coyoacan</t>
         </is>
       </c>
       <c r="D147" s="12" t="inlineStr">
         <is>
-          <t>Alberto Torrado Aguilar Cauz</t>
+          <t>Luis Alberto Quevedo Rodriguez</t>
         </is>
       </c>
       <c r="E147" s="11" t="n">
@@ -7460,17 +7427,17 @@
       </c>
       <c r="B148" s="17" t="inlineStr">
         <is>
-          <t>38156</t>
+          <t>38422</t>
         </is>
       </c>
       <c r="C148" s="8" t="inlineStr">
         <is>
-          <t>Condesa II Tamaulipas</t>
+          <t>Corporativo HSBC</t>
         </is>
       </c>
       <c r="D148" s="8" t="inlineStr">
         <is>
-          <t>DM pendiente</t>
+          <t>Guadalupe Ibarra Martínez</t>
         </is>
       </c>
       <c r="E148" s="7" t="n">
@@ -7500,17 +7467,17 @@
       </c>
       <c r="B149" s="15" t="inlineStr">
         <is>
-          <t>38663</t>
+          <t>38118</t>
         </is>
       </c>
       <c r="C149" s="12" t="inlineStr">
         <is>
-          <t>Copilco 20</t>
+          <t>Corporativo Polanco</t>
         </is>
       </c>
       <c r="D149" s="12" t="inlineStr">
         <is>
-          <t>Jaqueline Cortes Ayala</t>
+          <t>Luis Manuel Neri Saldaña</t>
         </is>
       </c>
       <c r="E149" s="11" t="n">
@@ -7540,12 +7507,12 @@
       </c>
       <c r="B150" s="17" t="inlineStr">
         <is>
-          <t>38798</t>
+          <t>38755</t>
         </is>
       </c>
       <c r="C150" s="8" t="inlineStr">
         <is>
-          <t>Corp. Televisa Sta Fe</t>
+          <t>Corporativo Santander</t>
         </is>
       </c>
       <c r="D150" s="8" t="inlineStr">
@@ -7580,17 +7547,17 @@
       </c>
       <c r="B151" s="15" t="inlineStr">
         <is>
-          <t>38709</t>
+          <t>38704</t>
         </is>
       </c>
       <c r="C151" s="12" t="inlineStr">
         <is>
-          <t>Corporativo Barranca</t>
+          <t>Corportivo Banamex</t>
         </is>
       </c>
       <c r="D151" s="12" t="inlineStr">
         <is>
-          <t>Manuel Alejandro Avila Molina</t>
+          <t>Erika Julieta Contreras Aguilera</t>
         </is>
       </c>
       <c r="E151" s="11" t="n">
@@ -7620,17 +7587,17 @@
       </c>
       <c r="B152" s="17" t="inlineStr">
         <is>
-          <t>38464</t>
+          <t>38365</t>
         </is>
       </c>
       <c r="C152" s="8" t="inlineStr">
         <is>
-          <t>Corporativo Coyoacan</t>
+          <t>Coyoacan Centro</t>
         </is>
       </c>
       <c r="D152" s="8" t="inlineStr">
         <is>
-          <t>Luis Alberto Quevedo Rodriguez</t>
+          <t>Jaqueline Cortes Ayala</t>
         </is>
       </c>
       <c r="E152" s="7" t="n">
@@ -7660,17 +7627,17 @@
       </c>
       <c r="B153" s="15" t="inlineStr">
         <is>
-          <t>38422</t>
+          <t>38340</t>
         </is>
       </c>
       <c r="C153" s="12" t="inlineStr">
         <is>
-          <t>Corporativo HSBC</t>
+          <t>Division del Norte</t>
         </is>
       </c>
       <c r="D153" s="12" t="inlineStr">
         <is>
-          <t>Guadalupe Ibarra Martínez</t>
+          <t>Luis Alberto Quevedo Rodriguez</t>
         </is>
       </c>
       <c r="E153" s="11" t="n">
@@ -7700,17 +7667,17 @@
       </c>
       <c r="B154" s="17" t="inlineStr">
         <is>
-          <t>38118</t>
+          <t>38579</t>
         </is>
       </c>
       <c r="C154" s="8" t="inlineStr">
         <is>
-          <t>Corporativo Polanco</t>
+          <t>Division del Norte II</t>
         </is>
       </c>
       <c r="D154" s="8" t="inlineStr">
         <is>
-          <t>Luis Manuel Neri Saldaña</t>
+          <t>Luis Alberto Quevedo Rodriguez</t>
         </is>
       </c>
       <c r="E154" s="7" t="n">
@@ -7740,17 +7707,17 @@
       </c>
       <c r="B155" s="15" t="inlineStr">
         <is>
-          <t>38755</t>
+          <t>38386</t>
         </is>
       </c>
       <c r="C155" s="12" t="inlineStr">
         <is>
-          <t>Corporativo Santander</t>
+          <t>Duraznos</t>
         </is>
       </c>
       <c r="D155" s="12" t="inlineStr">
         <is>
-          <t>Jose De Jesus Magos Arzaluz</t>
+          <t>Manuel Alejandro Avila Molina</t>
         </is>
       </c>
       <c r="E155" s="11" t="n">
@@ -7780,17 +7747,17 @@
       </c>
       <c r="B156" s="17" t="inlineStr">
         <is>
-          <t>38704</t>
+          <t>38405</t>
         </is>
       </c>
       <c r="C156" s="8" t="inlineStr">
         <is>
-          <t>Corportivo Banamex</t>
+          <t>Ejercito Nacional</t>
         </is>
       </c>
       <c r="D156" s="8" t="inlineStr">
         <is>
-          <t>Erika Julieta Contreras Aguilera</t>
+          <t>Luis Manuel Neri Saldaña</t>
         </is>
       </c>
       <c r="E156" s="7" t="n">
@@ -7820,17 +7787,17 @@
       </c>
       <c r="B157" s="15" t="inlineStr">
         <is>
-          <t>38365</t>
+          <t>38847</t>
         </is>
       </c>
       <c r="C157" s="12" t="inlineStr">
         <is>
-          <t>Coyoacan Centro</t>
+          <t>El Molino</t>
         </is>
       </c>
       <c r="D157" s="12" t="inlineStr">
         <is>
-          <t>Jaqueline Cortes Ayala</t>
+          <t>Andrea Nava Guzman</t>
         </is>
       </c>
       <c r="E157" s="11" t="n">
@@ -7860,17 +7827,17 @@
       </c>
       <c r="B158" s="17" t="inlineStr">
         <is>
-          <t>38340</t>
+          <t>38203</t>
         </is>
       </c>
       <c r="C158" s="8" t="inlineStr">
         <is>
-          <t>Division del Norte</t>
+          <t>Embassy Suites</t>
         </is>
       </c>
       <c r="D158" s="8" t="inlineStr">
         <is>
-          <t>Luis Alberto Quevedo Rodriguez</t>
+          <t>Vacante</t>
         </is>
       </c>
       <c r="E158" s="7" t="n">
@@ -7900,17 +7867,17 @@
       </c>
       <c r="B159" s="15" t="inlineStr">
         <is>
-          <t>38579</t>
+          <t>38597</t>
         </is>
       </c>
       <c r="C159" s="12" t="inlineStr">
         <is>
-          <t>Division del Norte II</t>
+          <t>Emerson</t>
         </is>
       </c>
       <c r="D159" s="12" t="inlineStr">
         <is>
-          <t>Luis Alberto Quevedo Rodriguez</t>
+          <t>Alberto Torrado Aguilar Cauz</t>
         </is>
       </c>
       <c r="E159" s="11" t="n">
@@ -7940,17 +7907,17 @@
       </c>
       <c r="B160" s="17" t="inlineStr">
         <is>
-          <t>38386</t>
+          <t>38372</t>
         </is>
       </c>
       <c r="C160" s="8" t="inlineStr">
         <is>
-          <t>Duraznos</t>
+          <t>Felix Cuevas</t>
         </is>
       </c>
       <c r="D160" s="8" t="inlineStr">
         <is>
-          <t>Manuel Alejandro Avila Molina</t>
+          <t>Juan Jesus Zuñiga Flores</t>
         </is>
       </c>
       <c r="E160" s="7" t="n">
@@ -7980,17 +7947,17 @@
       </c>
       <c r="B161" s="15" t="inlineStr">
         <is>
-          <t>38405</t>
+          <t>38234</t>
         </is>
       </c>
       <c r="C161" s="12" t="inlineStr">
         <is>
-          <t>Ejercito Nacional</t>
+          <t>Fiesta Americana Reforma</t>
         </is>
       </c>
       <c r="D161" s="12" t="inlineStr">
         <is>
-          <t>Luis Manuel Neri Saldaña</t>
+          <t>Vacante</t>
         </is>
       </c>
       <c r="E161" s="11" t="n">
@@ -8020,17 +7987,17 @@
       </c>
       <c r="B162" s="17" t="inlineStr">
         <is>
-          <t>38847</t>
+          <t>38483</t>
         </is>
       </c>
       <c r="C162" s="8" t="inlineStr">
         <is>
-          <t>El Molino</t>
+          <t>Forum Buenavista</t>
         </is>
       </c>
       <c r="D162" s="8" t="inlineStr">
         <is>
-          <t>Andrea Nava Guzman</t>
+          <t>Nora Caracas Saldaña</t>
         </is>
       </c>
       <c r="E162" s="7" t="n">
@@ -8060,17 +8027,17 @@
       </c>
       <c r="B163" s="15" t="inlineStr">
         <is>
-          <t>38203</t>
+          <t>38554</t>
         </is>
       </c>
       <c r="C163" s="12" t="inlineStr">
         <is>
-          <t>Embassy Suites</t>
+          <t>Forum Buenavista II</t>
         </is>
       </c>
       <c r="D163" s="12" t="inlineStr">
         <is>
-          <t>Vacante</t>
+          <t>Nora Caracas Saldaña</t>
         </is>
       </c>
       <c r="E163" s="11" t="n">
@@ -8100,17 +8067,17 @@
       </c>
       <c r="B164" s="17" t="inlineStr">
         <is>
-          <t>38597</t>
+          <t>38461</t>
         </is>
       </c>
       <c r="C164" s="8" t="inlineStr">
         <is>
-          <t>Emerson</t>
+          <t>Fuente de Tritones</t>
         </is>
       </c>
       <c r="D164" s="8" t="inlineStr">
         <is>
-          <t>Alberto Torrado Aguilar Cauz</t>
+          <t>Manuel Alejandro Avila Molina</t>
         </is>
       </c>
       <c r="E164" s="7" t="n">
@@ -8140,17 +8107,17 @@
       </c>
       <c r="B165" s="15" t="inlineStr">
         <is>
-          <t>38372</t>
+          <t>38469</t>
         </is>
       </c>
       <c r="C165" s="12" t="inlineStr">
         <is>
-          <t>Felix Cuevas</t>
+          <t>Galerias Coapa</t>
         </is>
       </c>
       <c r="D165" s="12" t="inlineStr">
         <is>
-          <t>Juan Jesus Zuñiga Flores</t>
+          <t>Fernando Eduardo Verdugo Saldaña</t>
         </is>
       </c>
       <c r="E165" s="11" t="n">
@@ -8180,17 +8147,17 @@
       </c>
       <c r="B166" s="17" t="inlineStr">
         <is>
-          <t>38234</t>
+          <t>38549</t>
         </is>
       </c>
       <c r="C166" s="8" t="inlineStr">
         <is>
-          <t>Fiesta Americana Reforma</t>
+          <t>Galerias Insurgentes</t>
         </is>
       </c>
       <c r="D166" s="8" t="inlineStr">
         <is>
-          <t>Vacante</t>
+          <t>Juan Jesus Zuñiga Flores</t>
         </is>
       </c>
       <c r="E166" s="7" t="n">
@@ -8220,17 +8187,17 @@
       </c>
       <c r="B167" s="15" t="inlineStr">
         <is>
-          <t>38483</t>
+          <t>43068</t>
         </is>
       </c>
       <c r="C167" s="12" t="inlineStr">
         <is>
-          <t>Forum Buenavista</t>
+          <t>Galerias Metepec II</t>
         </is>
       </c>
       <c r="D167" s="12" t="inlineStr">
         <is>
-          <t>Nora Caracas Saldaña</t>
+          <t>Daniel Flores Maldonado</t>
         </is>
       </c>
       <c r="E167" s="11" t="n">
@@ -8260,17 +8227,17 @@
       </c>
       <c r="B168" s="17" t="inlineStr">
         <is>
-          <t>38554</t>
+          <t>38578</t>
         </is>
       </c>
       <c r="C168" s="8" t="inlineStr">
         <is>
-          <t>Forum Buenavista II</t>
+          <t>Galerias Toluca</t>
         </is>
       </c>
       <c r="D168" s="8" t="inlineStr">
         <is>
-          <t>Nora Caracas Saldaña</t>
+          <t>Andrea Nava Guzman</t>
         </is>
       </c>
       <c r="E168" s="7" t="n">
@@ -8300,17 +8267,17 @@
       </c>
       <c r="B169" s="15" t="inlineStr">
         <is>
-          <t>38461</t>
+          <t>38138</t>
         </is>
       </c>
       <c r="C169" s="12" t="inlineStr">
         <is>
-          <t>Fuente de Tritones</t>
+          <t>Galerias metepec 1</t>
         </is>
       </c>
       <c r="D169" s="12" t="inlineStr">
         <is>
-          <t>Manuel Alejandro Avila Molina</t>
+          <t>Daniel Flores Maldonado</t>
         </is>
       </c>
       <c r="E169" s="11" t="n">
@@ -8340,17 +8307,17 @@
       </c>
       <c r="B170" s="17" t="inlineStr">
         <is>
-          <t>38469</t>
+          <t>38484</t>
         </is>
       </c>
       <c r="C170" s="8" t="inlineStr">
         <is>
-          <t>Galerias Coapa</t>
+          <t>Gandhi</t>
         </is>
       </c>
       <c r="D170" s="8" t="inlineStr">
         <is>
-          <t>Fernando Eduardo Verdugo Saldaña</t>
+          <t>Jaqueline Cortes Ayala</t>
         </is>
       </c>
       <c r="E170" s="7" t="n">
@@ -8380,17 +8347,17 @@
       </c>
       <c r="B171" s="15" t="inlineStr">
         <is>
-          <t>38549</t>
+          <t>38512</t>
         </is>
       </c>
       <c r="C171" s="12" t="inlineStr">
         <is>
-          <t>Galerias Insurgentes</t>
+          <t>Garden Santa Fe</t>
         </is>
       </c>
       <c r="D171" s="12" t="inlineStr">
         <is>
-          <t>Juan Jesus Zuñiga Flores</t>
+          <t>Jose De Jesus Magos Arzaluz</t>
         </is>
       </c>
       <c r="E171" s="11" t="n">
@@ -8420,17 +8387,17 @@
       </c>
       <c r="B172" s="17" t="inlineStr">
         <is>
-          <t>43068</t>
+          <t>38172</t>
         </is>
       </c>
       <c r="C172" s="8" t="inlineStr">
         <is>
-          <t>Galerias Metepec II</t>
+          <t>Gran Sur</t>
         </is>
       </c>
       <c r="D172" s="8" t="inlineStr">
         <is>
-          <t>Daniel Flores Maldonado</t>
+          <t>Hazar Susim Trejo Hernandez</t>
         </is>
       </c>
       <c r="E172" s="7" t="n">
@@ -8460,17 +8427,17 @@
       </c>
       <c r="B173" s="15" t="inlineStr">
         <is>
-          <t>38578</t>
+          <t>38615</t>
         </is>
       </c>
       <c r="C173" s="12" t="inlineStr">
         <is>
-          <t>Galerias Toluca</t>
+          <t>Grand San Jeronimo</t>
         </is>
       </c>
       <c r="D173" s="12" t="inlineStr">
         <is>
-          <t>Andrea Nava Guzman</t>
+          <t>Cesar Alfonso Castillo Romero</t>
         </is>
       </c>
       <c r="E173" s="11" t="n">
@@ -8500,17 +8467,17 @@
       </c>
       <c r="B174" s="17" t="inlineStr">
         <is>
-          <t>38138</t>
+          <t>38121</t>
         </is>
       </c>
       <c r="C174" s="8" t="inlineStr">
         <is>
-          <t>Galerias metepec 1</t>
+          <t>Herradura</t>
         </is>
       </c>
       <c r="D174" s="8" t="inlineStr">
         <is>
-          <t>Daniel Flores Maldonado</t>
+          <t>Manuel Alejandro Avila Molina</t>
         </is>
       </c>
       <c r="E174" s="7" t="n">
@@ -8540,17 +8507,17 @@
       </c>
       <c r="B175" s="15" t="inlineStr">
         <is>
-          <t>38484</t>
+          <t>38382</t>
         </is>
       </c>
       <c r="C175" s="12" t="inlineStr">
         <is>
-          <t>Gandhi</t>
+          <t>Homero</t>
         </is>
       </c>
       <c r="D175" s="12" t="inlineStr">
         <is>
-          <t>Jaqueline Cortes Ayala</t>
+          <t>Alberto Torrado Aguilar Cauz</t>
         </is>
       </c>
       <c r="E175" s="11" t="n">
@@ -8580,17 +8547,17 @@
       </c>
       <c r="B176" s="17" t="inlineStr">
         <is>
-          <t>38512</t>
+          <t>38366</t>
         </is>
       </c>
       <c r="C176" s="8" t="inlineStr">
         <is>
-          <t>Garden Santa Fe</t>
+          <t>Hospital ABC</t>
         </is>
       </c>
       <c r="D176" s="8" t="inlineStr">
         <is>
-          <t>Jose De Jesus Magos Arzaluz</t>
+          <t>Manuel Alejandro Avila Molina</t>
         </is>
       </c>
       <c r="E176" s="7" t="n">
@@ -8620,17 +8587,17 @@
       </c>
       <c r="B177" s="15" t="inlineStr">
         <is>
-          <t>38172</t>
+          <t>38850</t>
         </is>
       </c>
       <c r="C177" s="12" t="inlineStr">
         <is>
-          <t>Gran Sur</t>
+          <t>Hospital Angeles Clinica Londres</t>
         </is>
       </c>
       <c r="D177" s="12" t="inlineStr">
         <is>
-          <t>Hazar Susim Trejo Hernandez</t>
+          <t>Nora Caracas Saldaña</t>
         </is>
       </c>
       <c r="E177" s="11" t="n">
@@ -8660,17 +8627,17 @@
       </c>
       <c r="B178" s="17" t="inlineStr">
         <is>
-          <t>38615</t>
+          <t>38440</t>
         </is>
       </c>
       <c r="C178" s="8" t="inlineStr">
         <is>
-          <t>Grand San Jeronimo</t>
+          <t>Hospital Angeles Metropolitano</t>
         </is>
       </c>
       <c r="D178" s="8" t="inlineStr">
         <is>
-          <t>Cesar Alfonso Castillo Romero</t>
+          <t>Nora Caracas Saldaña</t>
         </is>
       </c>
       <c r="E178" s="7" t="n">
@@ -8700,17 +8667,17 @@
       </c>
       <c r="B179" s="15" t="inlineStr">
         <is>
-          <t>38121</t>
+          <t>38447</t>
         </is>
       </c>
       <c r="C179" s="12" t="inlineStr">
         <is>
-          <t>Herradura</t>
+          <t>Hospital Angeles del Pedregal</t>
         </is>
       </c>
       <c r="D179" s="12" t="inlineStr">
         <is>
-          <t>Manuel Alejandro Avila Molina</t>
+          <t>Cesar Alfonso Castillo Romero</t>
         </is>
       </c>
       <c r="E179" s="11" t="n">
@@ -8740,17 +8707,17 @@
       </c>
       <c r="B180" s="17" t="inlineStr">
         <is>
-          <t>38382</t>
+          <t>43159</t>
         </is>
       </c>
       <c r="C180" s="8" t="inlineStr">
         <is>
-          <t>Homero</t>
+          <t>Hospital Angeles del Pedregal II</t>
         </is>
       </c>
       <c r="D180" s="8" t="inlineStr">
         <is>
-          <t>Alberto Torrado Aguilar Cauz</t>
+          <t>Cesar Alfonso Castillo Romero</t>
         </is>
       </c>
       <c r="E180" s="7" t="n">
@@ -8780,17 +8747,17 @@
       </c>
       <c r="B181" s="15" t="inlineStr">
         <is>
-          <t>38202</t>
+          <t>43105</t>
         </is>
       </c>
       <c r="C181" s="12" t="inlineStr">
         <is>
-          <t>Horacio</t>
+          <t>Insurgentes Capital</t>
         </is>
       </c>
       <c r="D181" s="12" t="inlineStr">
         <is>
-          <t>Alberto Torrado Aguilar Cauz</t>
+          <t>Juan Jesus Zuñiga Flores</t>
         </is>
       </c>
       <c r="E181" s="11" t="n">
@@ -8820,17 +8787,17 @@
       </c>
       <c r="B182" s="17" t="inlineStr">
         <is>
-          <t>38366</t>
+          <t>38112</t>
         </is>
       </c>
       <c r="C182" s="8" t="inlineStr">
         <is>
-          <t>Hospital ABC</t>
+          <t>Insurgentes Parroquia</t>
         </is>
       </c>
       <c r="D182" s="8" t="inlineStr">
         <is>
-          <t>Manuel Alejandro Avila Molina</t>
+          <t>Adriana Alejandra Tanus Buhler</t>
         </is>
       </c>
       <c r="E182" s="7" t="n">
@@ -8860,17 +8827,17 @@
       </c>
       <c r="B183" s="15" t="inlineStr">
         <is>
-          <t>38850</t>
+          <t>38152</t>
         </is>
       </c>
       <c r="C183" s="12" t="inlineStr">
         <is>
-          <t>Hospital Angeles Clinica Londres</t>
+          <t>Insurgentes Relox</t>
         </is>
       </c>
       <c r="D183" s="12" t="inlineStr">
         <is>
-          <t>Nora Caracas Saldaña</t>
+          <t>Jaqueline Cortes Ayala</t>
         </is>
       </c>
       <c r="E183" s="11" t="n">
@@ -8900,17 +8867,17 @@
       </c>
       <c r="B184" s="17" t="inlineStr">
         <is>
-          <t>38440</t>
+          <t>43188</t>
         </is>
       </c>
       <c r="C184" s="8" t="inlineStr">
         <is>
-          <t>Hospital Angeles Metropolitano</t>
+          <t>Insurgentes Tehuantepec</t>
         </is>
       </c>
       <c r="D184" s="8" t="inlineStr">
         <is>
-          <t>Nora Caracas Saldaña</t>
+          <t>Guadalupe Ibarra Martínez</t>
         </is>
       </c>
       <c r="E184" s="7" t="n">
@@ -8940,17 +8907,17 @@
       </c>
       <c r="B185" s="15" t="inlineStr">
         <is>
-          <t>38447</t>
+          <t>38504</t>
         </is>
       </c>
       <c r="C185" s="12" t="inlineStr">
         <is>
-          <t>Hospital Angeles del Pedregal</t>
+          <t>Insurgentes Wtc</t>
         </is>
       </c>
       <c r="D185" s="12" t="inlineStr">
         <is>
-          <t>Cesar Alfonso Castillo Romero</t>
+          <t>Nora Caracas Saldaña</t>
         </is>
       </c>
       <c r="E185" s="11" t="n">
@@ -8980,17 +8947,17 @@
       </c>
       <c r="B186" s="17" t="inlineStr">
         <is>
-          <t>43159</t>
+          <t>38126</t>
         </is>
       </c>
       <c r="C186" s="8" t="inlineStr">
         <is>
-          <t>Hospital Angeles del Pedregal II</t>
+          <t>Interlomas</t>
         </is>
       </c>
       <c r="D186" s="8" t="inlineStr">
         <is>
-          <t>Cesar Alfonso Castillo Romero</t>
+          <t>Areli Anahi Lazcano Lezama</t>
         </is>
       </c>
       <c r="E186" s="7" t="n">
@@ -9020,17 +8987,17 @@
       </c>
       <c r="B187" s="15" t="inlineStr">
         <is>
-          <t>38772</t>
+          <t>38219</t>
         </is>
       </c>
       <c r="C187" s="12" t="inlineStr">
         <is>
-          <t>Hospital Ángeles Interlomas</t>
+          <t>Irrigacion</t>
         </is>
       </c>
       <c r="D187" s="12" t="inlineStr">
         <is>
-          <t>Areli Anahi Lazcano Lezama</t>
+          <t>Luis Manuel Neri Saldaña</t>
         </is>
       </c>
       <c r="E187" s="11" t="n">
@@ -9060,17 +9027,17 @@
       </c>
       <c r="B188" s="17" t="inlineStr">
         <is>
-          <t>43105</t>
+          <t>38428</t>
         </is>
       </c>
       <c r="C188" s="8" t="inlineStr">
         <is>
-          <t>Insurgentes Capital</t>
+          <t>Jardines del Pedregal</t>
         </is>
       </c>
       <c r="D188" s="8" t="inlineStr">
         <is>
-          <t>Juan Jesus Zuñiga Flores</t>
+          <t>Cesar Alfonso Castillo Romero</t>
         </is>
       </c>
       <c r="E188" s="7" t="n">
@@ -9100,17 +9067,17 @@
       </c>
       <c r="B189" s="15" t="inlineStr">
         <is>
-          <t>38112</t>
+          <t>38292</t>
         </is>
       </c>
       <c r="C189" s="12" t="inlineStr">
         <is>
-          <t>Insurgentes Parroquia</t>
+          <t>Jesús del Monte</t>
         </is>
       </c>
       <c r="D189" s="12" t="inlineStr">
         <is>
-          <t>Adriana Alejandra Tanus Buhler</t>
+          <t>Areli Anahi Lazcano Lezama</t>
         </is>
       </c>
       <c r="E189" s="11" t="n">
@@ -9140,17 +9107,17 @@
       </c>
       <c r="B190" s="17" t="inlineStr">
         <is>
-          <t>38152</t>
+          <t>38571</t>
         </is>
       </c>
       <c r="C190" s="8" t="inlineStr">
         <is>
-          <t>Insurgentes Relox</t>
+          <t>Jolie Place</t>
         </is>
       </c>
       <c r="D190" s="8" t="inlineStr">
         <is>
-          <t>Jaqueline Cortes Ayala</t>
+          <t>Cesar Alfonso Castillo Romero</t>
         </is>
       </c>
       <c r="E190" s="7" t="n">
@@ -9180,17 +9147,17 @@
       </c>
       <c r="B191" s="15" t="inlineStr">
         <is>
-          <t>43188</t>
+          <t>38113</t>
         </is>
       </c>
       <c r="C191" s="12" t="inlineStr">
         <is>
-          <t>Insurgentes Tehuantepec</t>
+          <t>Juan Pablo II</t>
         </is>
       </c>
       <c r="D191" s="12" t="inlineStr">
         <is>
-          <t>Guadalupe Ibarra Martínez</t>
+          <t>Jaqueline Cortes Ayala</t>
         </is>
       </c>
       <c r="E191" s="11" t="n">
@@ -9220,17 +9187,17 @@
       </c>
       <c r="B192" s="17" t="inlineStr">
         <is>
-          <t>38504</t>
+          <t>38465</t>
         </is>
       </c>
       <c r="C192" s="8" t="inlineStr">
         <is>
-          <t>Insurgentes Wtc</t>
+          <t>Juarez 32</t>
         </is>
       </c>
       <c r="D192" s="8" t="inlineStr">
         <is>
-          <t>Nora Caracas Saldaña</t>
+          <t>Vacante</t>
         </is>
       </c>
       <c r="E192" s="7" t="n">
@@ -9260,17 +9227,17 @@
       </c>
       <c r="B193" s="15" t="inlineStr">
         <is>
-          <t>38126</t>
+          <t>43147</t>
         </is>
       </c>
       <c r="C193" s="12" t="inlineStr">
         <is>
-          <t>Interlomas</t>
+          <t>Juarez 70</t>
         </is>
       </c>
       <c r="D193" s="12" t="inlineStr">
         <is>
-          <t>Areli Anahi Lazcano Lezama</t>
+          <t>Andrea Nava Guzman</t>
         </is>
       </c>
       <c r="E193" s="11" t="n">
@@ -9300,17 +9267,17 @@
       </c>
       <c r="B194" s="17" t="inlineStr">
         <is>
-          <t>38219</t>
+          <t>43059</t>
         </is>
       </c>
       <c r="C194" s="8" t="inlineStr">
         <is>
-          <t>Irrigacion</t>
+          <t>La Providencia DT</t>
         </is>
       </c>
       <c r="D194" s="8" t="inlineStr">
         <is>
-          <t>Luis Manuel Neri Saldaña</t>
+          <t>Daniel Flores Maldonado</t>
         </is>
       </c>
       <c r="E194" s="7" t="n">
@@ -9340,17 +9307,17 @@
       </c>
       <c r="B195" s="15" t="inlineStr">
         <is>
-          <t>38428</t>
+          <t>38312</t>
         </is>
       </c>
       <c r="C195" s="12" t="inlineStr">
         <is>
-          <t>Jardines del Pedregal</t>
+          <t>La Salle</t>
         </is>
       </c>
       <c r="D195" s="12" t="inlineStr">
         <is>
-          <t>Cesar Alfonso Castillo Romero</t>
+          <t>Nora Caracas Saldaña</t>
         </is>
       </c>
       <c r="E195" s="11" t="n">
@@ -9380,17 +9347,17 @@
       </c>
       <c r="B196" s="17" t="inlineStr">
         <is>
-          <t>38292</t>
+          <t>38227</t>
         </is>
       </c>
       <c r="C196" s="8" t="inlineStr">
         <is>
-          <t>Jesús del Monte</t>
+          <t>Lomas Plaza</t>
         </is>
       </c>
       <c r="D196" s="8" t="inlineStr">
         <is>
-          <t>Areli Anahi Lazcano Lezama</t>
+          <t>Adriana Alejandra Tanus Buhler</t>
         </is>
       </c>
       <c r="E196" s="7" t="n">
@@ -9420,17 +9387,17 @@
       </c>
       <c r="B197" s="15" t="inlineStr">
         <is>
-          <t>38571</t>
+          <t>38272</t>
         </is>
       </c>
       <c r="C197" s="12" t="inlineStr">
         <is>
-          <t>Jolie Place</t>
+          <t>Londres</t>
         </is>
       </c>
       <c r="D197" s="12" t="inlineStr">
         <is>
-          <t>Cesar Alfonso Castillo Romero</t>
+          <t>Guadalupe Ibarra Martínez</t>
         </is>
       </c>
       <c r="E197" s="11" t="n">
@@ -9460,17 +9427,17 @@
       </c>
       <c r="B198" s="17" t="inlineStr">
         <is>
-          <t>38113</t>
+          <t>43034</t>
         </is>
       </c>
       <c r="C198" s="8" t="inlineStr">
         <is>
-          <t>Juan Pablo II</t>
+          <t>Macroplaza Tecamac</t>
         </is>
       </c>
       <c r="D198" s="8" t="inlineStr">
         <is>
-          <t>Jaqueline Cortes Ayala</t>
+          <t>Monica Selene Morales Ibarra</t>
         </is>
       </c>
       <c r="E198" s="7" t="n">
@@ -9500,12 +9467,12 @@
       </c>
       <c r="B199" s="15" t="inlineStr">
         <is>
-          <t>38465</t>
+          <t>38487</t>
         </is>
       </c>
       <c r="C199" s="12" t="inlineStr">
         <is>
-          <t>Juarez 32</t>
+          <t>Madero</t>
         </is>
       </c>
       <c r="D199" s="12" t="inlineStr">
@@ -9540,17 +9507,17 @@
       </c>
       <c r="B200" s="17" t="inlineStr">
         <is>
-          <t>43147</t>
+          <t>38185</t>
         </is>
       </c>
       <c r="C200" s="8" t="inlineStr">
         <is>
-          <t>Juarez 70</t>
+          <t>Magnocentro</t>
         </is>
       </c>
       <c r="D200" s="8" t="inlineStr">
         <is>
-          <t>Andrea Nava Guzman</t>
+          <t>Areli Anahi Lazcano Lezama</t>
         </is>
       </c>
       <c r="E200" s="7" t="n">
@@ -9580,17 +9547,17 @@
       </c>
       <c r="B201" s="15" t="inlineStr">
         <is>
-          <t>43059</t>
+          <t>38730</t>
         </is>
       </c>
       <c r="C201" s="12" t="inlineStr">
         <is>
-          <t>La Providencia DT</t>
+          <t>Manacar PB</t>
         </is>
       </c>
       <c r="D201" s="12" t="inlineStr">
         <is>
-          <t>Daniel Flores Maldonado</t>
+          <t>Adriana Alejandra Tanus Buhler</t>
         </is>
       </c>
       <c r="E201" s="11" t="n">
@@ -9620,17 +9587,17 @@
       </c>
       <c r="B202" s="17" t="inlineStr">
         <is>
-          <t>38312</t>
+          <t>38111</t>
         </is>
       </c>
       <c r="C202" s="8" t="inlineStr">
         <is>
-          <t>La Salle</t>
+          <t>Masarik</t>
         </is>
       </c>
       <c r="D202" s="8" t="inlineStr">
         <is>
-          <t>Nora Caracas Saldaña</t>
+          <t>Luis Manuel Neri Saldaña</t>
         </is>
       </c>
       <c r="E202" s="7" t="n">
@@ -9660,17 +9627,17 @@
       </c>
       <c r="B203" s="15" t="inlineStr">
         <is>
-          <t>38227</t>
+          <t>38191</t>
         </is>
       </c>
       <c r="C203" s="12" t="inlineStr">
         <is>
-          <t>Lomas Plaza</t>
+          <t>Masarik Spencer</t>
         </is>
       </c>
       <c r="D203" s="12" t="inlineStr">
         <is>
-          <t>Adriana Alejandra Tanus Buhler</t>
+          <t>Alberto Torrado Aguilar Cauz</t>
         </is>
       </c>
       <c r="E203" s="11" t="n">
@@ -9700,17 +9667,17 @@
       </c>
       <c r="B204" s="17" t="inlineStr">
         <is>
-          <t>38272</t>
+          <t>38406</t>
         </is>
       </c>
       <c r="C204" s="8" t="inlineStr">
         <is>
-          <t>Londres</t>
+          <t>Medica Sur</t>
         </is>
       </c>
       <c r="D204" s="8" t="inlineStr">
         <is>
-          <t>Guadalupe Ibarra Martínez</t>
+          <t>Hazar Susim Trejo Hernandez</t>
         </is>
       </c>
       <c r="E204" s="7" t="n">
@@ -9740,17 +9707,17 @@
       </c>
       <c r="B205" s="15" t="inlineStr">
         <is>
-          <t>43034</t>
+          <t>38441</t>
         </is>
       </c>
       <c r="C205" s="12" t="inlineStr">
         <is>
-          <t>Macroplaza Tecamac</t>
+          <t>Metepec Plaza del Parque</t>
         </is>
       </c>
       <c r="D205" s="12" t="inlineStr">
         <is>
-          <t>Monica Selene Morales Ibarra</t>
+          <t>Daniel Flores Maldonado</t>
         </is>
       </c>
       <c r="E205" s="11" t="n">
@@ -9780,17 +9747,17 @@
       </c>
       <c r="B206" s="17" t="inlineStr">
         <is>
-          <t>38487</t>
+          <t>38193</t>
         </is>
       </c>
       <c r="C206" s="8" t="inlineStr">
         <is>
-          <t>Madero</t>
+          <t>Metropoli Patriotismo</t>
         </is>
       </c>
       <c r="D206" s="8" t="inlineStr">
         <is>
-          <t>Vacante</t>
+          <t>Juan Jesus Zuñiga Flores</t>
         </is>
       </c>
       <c r="E206" s="7" t="n">
@@ -9820,17 +9787,17 @@
       </c>
       <c r="B207" s="15" t="inlineStr">
         <is>
-          <t>38632</t>
+          <t>38398</t>
         </is>
       </c>
       <c r="C207" s="12" t="inlineStr">
         <is>
-          <t>Madero II</t>
+          <t>Mexfund Pedregal</t>
         </is>
       </c>
       <c r="D207" s="12" t="inlineStr">
         <is>
-          <t>Vacante</t>
+          <t>Cesar Alfonso Castillo Romero</t>
         </is>
       </c>
       <c r="E207" s="11" t="n">
@@ -9860,17 +9827,17 @@
       </c>
       <c r="B208" s="17" t="inlineStr">
         <is>
-          <t>38185</t>
+          <t>38208</t>
         </is>
       </c>
       <c r="C208" s="8" t="inlineStr">
         <is>
-          <t>Magnocentro</t>
+          <t>Miguel Angel de Quevedo II</t>
         </is>
       </c>
       <c r="D208" s="8" t="inlineStr">
         <is>
-          <t>Areli Anahi Lazcano Lezama</t>
+          <t>Jaqueline Cortes Ayala</t>
         </is>
       </c>
       <c r="E208" s="7" t="n">
@@ -9900,17 +9867,17 @@
       </c>
       <c r="B209" s="15" t="inlineStr">
         <is>
-          <t>38730</t>
+          <t>38239</t>
         </is>
       </c>
       <c r="C209" s="12" t="inlineStr">
         <is>
-          <t>Manacar PB</t>
+          <t>Miguel Angel de Quevedo III</t>
         </is>
       </c>
       <c r="D209" s="12" t="inlineStr">
         <is>
-          <t>Adriana Alejandra Tanus Buhler</t>
+          <t>Jaqueline Cortes Ayala</t>
         </is>
       </c>
       <c r="E209" s="11" t="n">
@@ -9940,17 +9907,17 @@
       </c>
       <c r="B210" s="17" t="inlineStr">
         <is>
-          <t>38111</t>
+          <t>38114</t>
         </is>
       </c>
       <c r="C210" s="8" t="inlineStr">
         <is>
-          <t>Masarik</t>
+          <t>Miramontes</t>
         </is>
       </c>
       <c r="D210" s="8" t="inlineStr">
         <is>
-          <t>Luis Manuel Neri Saldaña</t>
+          <t>Fernando Eduardo Verdugo Saldaña</t>
         </is>
       </c>
       <c r="E210" s="7" t="n">
@@ -9980,17 +9947,17 @@
       </c>
       <c r="B211" s="15" t="inlineStr">
         <is>
-          <t>38191</t>
+          <t>38888</t>
         </is>
       </c>
       <c r="C211" s="12" t="inlineStr">
         <is>
-          <t>Masarik Spencer</t>
+          <t>Mitikah</t>
         </is>
       </c>
       <c r="D211" s="12" t="inlineStr">
         <is>
-          <t>Alberto Torrado Aguilar Cauz</t>
+          <t>Luis Alberto Quevedo Rodriguez</t>
         </is>
       </c>
       <c r="E211" s="11" t="n">
@@ -10020,17 +9987,17 @@
       </c>
       <c r="B212" s="17" t="inlineStr">
         <is>
-          <t>38406</t>
+          <t>38941</t>
         </is>
       </c>
       <c r="C212" s="8" t="inlineStr">
         <is>
-          <t>Medica Sur</t>
+          <t>Mitikah Restaurantes</t>
         </is>
       </c>
       <c r="D212" s="8" t="inlineStr">
         <is>
-          <t>Hazar Susim Trejo Hernandez</t>
+          <t>Luis Alberto Quevedo Rodriguez</t>
         </is>
       </c>
       <c r="E212" s="7" t="n">
@@ -10060,17 +10027,17 @@
       </c>
       <c r="B213" s="15" t="inlineStr">
         <is>
-          <t>38771</t>
+          <t>38416</t>
         </is>
       </c>
       <c r="C213" s="12" t="inlineStr">
         <is>
-          <t>Medica SurTlalpan</t>
+          <t>Mixcoac</t>
         </is>
       </c>
       <c r="D213" s="12" t="inlineStr">
         <is>
-          <t>Hazar Susim Trejo Hernandez</t>
+          <t>Juan Jesus Zuñiga Flores</t>
         </is>
       </c>
       <c r="E213" s="11" t="n">
@@ -10100,17 +10067,17 @@
       </c>
       <c r="B214" s="17" t="inlineStr">
         <is>
-          <t>38441</t>
+          <t>38676</t>
         </is>
       </c>
       <c r="C214" s="8" t="inlineStr">
         <is>
-          <t>Metepec Plaza del Parque</t>
+          <t>Miyana</t>
         </is>
       </c>
       <c r="D214" s="8" t="inlineStr">
         <is>
-          <t>Daniel Flores Maldonado</t>
+          <t>Luis Manuel Neri Saldaña</t>
         </is>
       </c>
       <c r="E214" s="7" t="n">
@@ -10140,17 +10107,17 @@
       </c>
       <c r="B215" s="15" t="inlineStr">
         <is>
-          <t>38193</t>
+          <t>38982</t>
         </is>
       </c>
       <c r="C215" s="12" t="inlineStr">
         <is>
-          <t>Metropoli Patriotismo</t>
+          <t>Miyana II</t>
         </is>
       </c>
       <c r="D215" s="12" t="inlineStr">
         <is>
-          <t>Juan Jesus Zuñiga Flores</t>
+          <t>Luis Manuel Neri Saldaña</t>
         </is>
       </c>
       <c r="E215" s="11" t="n">
@@ -10180,17 +10147,17 @@
       </c>
       <c r="B216" s="17" t="inlineStr">
         <is>
-          <t>38398</t>
+          <t>38627</t>
         </is>
       </c>
       <c r="C216" s="8" t="inlineStr">
         <is>
-          <t>Mexfund Pedregal</t>
+          <t>Moliere 222</t>
         </is>
       </c>
       <c r="D216" s="8" t="inlineStr">
         <is>
-          <t>Cesar Alfonso Castillo Romero</t>
+          <t>Alberto Torrado Aguilar Cauz</t>
         </is>
       </c>
       <c r="E216" s="7" t="n">
@@ -10220,17 +10187,17 @@
       </c>
       <c r="B217" s="15" t="inlineStr">
         <is>
-          <t>38208</t>
+          <t>38538</t>
         </is>
       </c>
       <c r="C217" s="12" t="inlineStr">
         <is>
-          <t>Miguel Angel de Quevedo II</t>
+          <t>Monte Pelvoux</t>
         </is>
       </c>
       <c r="D217" s="12" t="inlineStr">
         <is>
-          <t>Jaqueline Cortes Ayala</t>
+          <t>Manuel Alejandro Avila Molina</t>
         </is>
       </c>
       <c r="E217" s="11" t="n">
@@ -10260,17 +10227,17 @@
       </c>
       <c r="B218" s="17" t="inlineStr">
         <is>
-          <t>38239</t>
+          <t>38498</t>
         </is>
       </c>
       <c r="C218" s="8" t="inlineStr">
         <is>
-          <t>Miguel Angel de Quevedo III</t>
+          <t>Montecitos Wtc</t>
         </is>
       </c>
       <c r="D218" s="8" t="inlineStr">
         <is>
-          <t>Jaqueline Cortes Ayala</t>
+          <t>Nora Caracas Saldaña</t>
         </is>
       </c>
       <c r="E218" s="7" t="n">
@@ -10300,17 +10267,17 @@
       </c>
       <c r="B219" s="15" t="inlineStr">
         <is>
-          <t>38114</t>
+          <t>43142</t>
         </is>
       </c>
       <c r="C219" s="12" t="inlineStr">
         <is>
-          <t>Miramontes</t>
+          <t>Montes Urales</t>
         </is>
       </c>
       <c r="D219" s="12" t="inlineStr">
         <is>
-          <t>Fernando Eduardo Verdugo Saldaña</t>
+          <t>Adriana Alejandra Tanus Buhler</t>
         </is>
       </c>
       <c r="E219" s="11" t="n">
@@ -10340,17 +10307,17 @@
       </c>
       <c r="B220" s="17" t="inlineStr">
         <is>
-          <t>38888</t>
+          <t>38716</t>
         </is>
       </c>
       <c r="C220" s="8" t="inlineStr">
         <is>
-          <t>Mitikah</t>
+          <t>Multiplaza Bosques</t>
         </is>
       </c>
       <c r="D220" s="8" t="inlineStr">
         <is>
-          <t>Luis Alberto Quevedo Rodriguez</t>
+          <t>Monica Selene Morales Ibarra</t>
         </is>
       </c>
       <c r="E220" s="7" t="n">
@@ -10380,17 +10347,17 @@
       </c>
       <c r="B221" s="15" t="inlineStr">
         <is>
-          <t>38941</t>
+          <t>38530</t>
         </is>
       </c>
       <c r="C221" s="12" t="inlineStr">
         <is>
-          <t>Mitikah Restaurantes</t>
+          <t>Narvarte</t>
         </is>
       </c>
       <c r="D221" s="12" t="inlineStr">
         <is>
-          <t>Luis Alberto Quevedo Rodriguez</t>
+          <t>Juan Jesus Zuñiga Flores</t>
         </is>
       </c>
       <c r="E221" s="11" t="n">
@@ -10420,17 +10387,17 @@
       </c>
       <c r="B222" s="17" t="inlineStr">
         <is>
-          <t>38416</t>
+          <t>38187</t>
         </is>
       </c>
       <c r="C222" s="8" t="inlineStr">
         <is>
-          <t>Mixcoac</t>
+          <t>Nuevo Leon DT</t>
         </is>
       </c>
       <c r="D222" s="8" t="inlineStr">
         <is>
-          <t>Juan Jesus Zuñiga Flores</t>
+          <t>Alberto Torrado Aguilar Cauz</t>
         </is>
       </c>
       <c r="E222" s="7" t="n">
@@ -10460,17 +10427,17 @@
       </c>
       <c r="B223" s="15" t="inlineStr">
         <is>
-          <t>38676</t>
+          <t>38620</t>
         </is>
       </c>
       <c r="C223" s="12" t="inlineStr">
         <is>
-          <t>Miyana</t>
+          <t>Oasis I</t>
         </is>
       </c>
       <c r="D223" s="12" t="inlineStr">
         <is>
-          <t>Luis Manuel Neri Saldaña</t>
+          <t>Jaqueline Cortes Ayala</t>
         </is>
       </c>
       <c r="E223" s="11" t="n">
@@ -10500,17 +10467,17 @@
       </c>
       <c r="B224" s="17" t="inlineStr">
         <is>
-          <t>38982</t>
+          <t>38585</t>
         </is>
       </c>
       <c r="C224" s="8" t="inlineStr">
         <is>
-          <t>Miyana II</t>
+          <t>Oasis II</t>
         </is>
       </c>
       <c r="D224" s="8" t="inlineStr">
         <is>
-          <t>Luis Manuel Neri Saldaña</t>
+          <t>Jaqueline Cortes Ayala</t>
         </is>
       </c>
       <c r="E224" s="7" t="n">
@@ -10540,12 +10507,12 @@
       </c>
       <c r="B225" s="15" t="inlineStr">
         <is>
-          <t>38627</t>
+          <t>38220</t>
         </is>
       </c>
       <c r="C225" s="12" t="inlineStr">
         <is>
-          <t>Moliere 222</t>
+          <t>Obelisco</t>
         </is>
       </c>
       <c r="D225" s="12" t="inlineStr">
@@ -10580,17 +10547,17 @@
       </c>
       <c r="B226" s="17" t="inlineStr">
         <is>
-          <t>38135</t>
+          <t>38602</t>
         </is>
       </c>
       <c r="C226" s="8" t="inlineStr">
         <is>
-          <t>Monte Everest</t>
+          <t>Obrero Mundial</t>
         </is>
       </c>
       <c r="D226" s="8" t="inlineStr">
         <is>
-          <t>Adriana Alejandra Tanus Buhler</t>
+          <t>Nora Caracas Saldaña</t>
         </is>
       </c>
       <c r="E226" s="7" t="n">
@@ -10620,17 +10587,17 @@
       </c>
       <c r="B227" s="15" t="inlineStr">
         <is>
-          <t>38538</t>
+          <t>38532</t>
         </is>
       </c>
       <c r="C227" s="12" t="inlineStr">
         <is>
-          <t>Monte Pelvoux</t>
+          <t>One o One</t>
         </is>
       </c>
       <c r="D227" s="12" t="inlineStr">
         <is>
-          <t>Manuel Alejandro Avila Molina</t>
+          <t>Jose De Jesus Magos Arzaluz</t>
         </is>
       </c>
       <c r="E227" s="11" t="n">
@@ -10660,17 +10627,17 @@
       </c>
       <c r="B228" s="17" t="inlineStr">
         <is>
-          <t>38498</t>
+          <t>38829</t>
         </is>
       </c>
       <c r="C228" s="8" t="inlineStr">
         <is>
-          <t>Montecitos Wtc</t>
+          <t>Outlet Lerma</t>
         </is>
       </c>
       <c r="D228" s="8" t="inlineStr">
         <is>
-          <t>Nora Caracas Saldaña</t>
+          <t>Andrea Nava Guzman</t>
         </is>
       </c>
       <c r="E228" s="7" t="n">
@@ -10700,17 +10667,17 @@
       </c>
       <c r="B229" s="15" t="inlineStr">
         <is>
-          <t>43142</t>
+          <t>38494</t>
         </is>
       </c>
       <c r="C229" s="12" t="inlineStr">
         <is>
-          <t>Montes Urales</t>
+          <t>Pabellon Cuemanco</t>
         </is>
       </c>
       <c r="D229" s="12" t="inlineStr">
         <is>
-          <t>Adriana Alejandra Tanus Buhler</t>
+          <t>Fernando Eduardo Verdugo Saldaña</t>
         </is>
       </c>
       <c r="E229" s="11" t="n">
@@ -10740,17 +10707,17 @@
       </c>
       <c r="B230" s="17" t="inlineStr">
         <is>
-          <t>38716</t>
+          <t>38668</t>
         </is>
       </c>
       <c r="C230" s="8" t="inlineStr">
         <is>
-          <t>Multiplaza Bosques</t>
+          <t>Pabellon Metepec</t>
         </is>
       </c>
       <c r="D230" s="8" t="inlineStr">
         <is>
-          <t>Monica Selene Morales Ibarra</t>
+          <t>Daniel Flores Maldonado</t>
         </is>
       </c>
       <c r="E230" s="7" t="n">
@@ -10780,17 +10747,17 @@
       </c>
       <c r="B231" s="15" t="inlineStr">
         <is>
-          <t>38530</t>
+          <t>43107</t>
         </is>
       </c>
       <c r="C231" s="12" t="inlineStr">
         <is>
-          <t>Narvarte</t>
+          <t>Pabellón Bosques</t>
         </is>
       </c>
       <c r="D231" s="12" t="inlineStr">
         <is>
-          <t>Juan Jesus Zuñiga Flores</t>
+          <t>Areli Anahi Lazcano Lezama</t>
         </is>
       </c>
       <c r="E231" s="11" t="n">
@@ -10820,17 +10787,17 @@
       </c>
       <c r="B232" s="17" t="inlineStr">
         <is>
-          <t>38187</t>
+          <t>38188</t>
         </is>
       </c>
       <c r="C232" s="8" t="inlineStr">
         <is>
-          <t>Nuevo Leon DT</t>
+          <t>Palmas</t>
         </is>
       </c>
       <c r="D232" s="8" t="inlineStr">
         <is>
-          <t>Alberto Torrado Aguilar Cauz</t>
+          <t>Adriana Alejandra Tanus Buhler</t>
         </is>
       </c>
       <c r="E232" s="7" t="n">
@@ -10860,17 +10827,17 @@
       </c>
       <c r="B233" s="15" t="inlineStr">
         <is>
-          <t>38620</t>
+          <t>38414</t>
         </is>
       </c>
       <c r="C233" s="12" t="inlineStr">
         <is>
-          <t>Oasis I</t>
+          <t>Park Plaza</t>
         </is>
       </c>
       <c r="D233" s="12" t="inlineStr">
         <is>
-          <t>Jaqueline Cortes Ayala</t>
+          <t>Erika Julieta Contreras Aguilera</t>
         </is>
       </c>
       <c r="E233" s="11" t="n">
@@ -10900,17 +10867,17 @@
       </c>
       <c r="B234" s="17" t="inlineStr">
         <is>
-          <t>38585</t>
+          <t>43041</t>
         </is>
       </c>
       <c r="C234" s="8" t="inlineStr">
         <is>
-          <t>Oasis II</t>
+          <t>Parque Aztlan</t>
         </is>
       </c>
       <c r="D234" s="8" t="inlineStr">
         <is>
-          <t>Jaqueline Cortes Ayala</t>
+          <t>Manuel Alejandro Avila Molina</t>
         </is>
       </c>
       <c r="E234" s="7" t="n">
@@ -10940,17 +10907,17 @@
       </c>
       <c r="B235" s="15" t="inlineStr">
         <is>
-          <t>38220</t>
+          <t>38452</t>
         </is>
       </c>
       <c r="C235" s="12" t="inlineStr">
         <is>
-          <t>Obelisco</t>
+          <t>Parque Interlomas</t>
         </is>
       </c>
       <c r="D235" s="12" t="inlineStr">
         <is>
-          <t>Alberto Torrado Aguilar Cauz</t>
+          <t>Areli Anahi Lazcano Lezama</t>
         </is>
       </c>
       <c r="E235" s="11" t="n">
@@ -10980,17 +10947,17 @@
       </c>
       <c r="B236" s="17" t="inlineStr">
         <is>
-          <t>38602</t>
+          <t>38777</t>
         </is>
       </c>
       <c r="C236" s="8" t="inlineStr">
         <is>
-          <t>Obrero Mundial</t>
+          <t>Parque la Mexicana</t>
         </is>
       </c>
       <c r="D236" s="8" t="inlineStr">
         <is>
-          <t>Nora Caracas Saldaña</t>
+          <t>Jose De Jesus Magos Arzaluz</t>
         </is>
       </c>
       <c r="E236" s="7" t="n">
@@ -11020,17 +10987,17 @@
       </c>
       <c r="B237" s="15" t="inlineStr">
         <is>
-          <t>38104</t>
+          <t>38581</t>
         </is>
       </c>
       <c r="C237" s="12" t="inlineStr">
         <is>
-          <t>Olivar</t>
+          <t>Parques BBVA</t>
         </is>
       </c>
       <c r="D237" s="12" t="inlineStr">
         <is>
-          <t>Adriana Alejandra Tanus Buhler</t>
+          <t>Luis Manuel Neri Saldaña</t>
         </is>
       </c>
       <c r="E237" s="11" t="n">
@@ -11060,17 +11027,17 @@
       </c>
       <c r="B238" s="17" t="inlineStr">
         <is>
-          <t>38532</t>
+          <t>38344</t>
         </is>
       </c>
       <c r="C238" s="8" t="inlineStr">
         <is>
-          <t>One o One</t>
+          <t>Parques Polanco</t>
         </is>
       </c>
       <c r="D238" s="8" t="inlineStr">
         <is>
-          <t>Jose De Jesus Magos Arzaluz</t>
+          <t>Maria Anallely Sanchez Garcia</t>
         </is>
       </c>
       <c r="E238" s="7" t="n">
@@ -11100,17 +11067,17 @@
       </c>
       <c r="B239" s="15" t="inlineStr">
         <is>
-          <t>38829</t>
+          <t>38580</t>
         </is>
       </c>
       <c r="C239" s="12" t="inlineStr">
         <is>
-          <t>Outlet Lerma</t>
+          <t>Pasaje San Jeronimo</t>
         </is>
       </c>
       <c r="D239" s="12" t="inlineStr">
         <is>
-          <t>Andrea Nava Guzman</t>
+          <t>Cesar Alfonso Castillo Romero</t>
         </is>
       </c>
       <c r="E239" s="11" t="n">
@@ -11140,17 +11107,17 @@
       </c>
       <c r="B240" s="17" t="inlineStr">
         <is>
-          <t>38494</t>
+          <t>38466</t>
         </is>
       </c>
       <c r="C240" s="8" t="inlineStr">
         <is>
-          <t>Pabellon Cuemanco</t>
+          <t>Paseo Interlomas I</t>
         </is>
       </c>
       <c r="D240" s="8" t="inlineStr">
         <is>
-          <t>Fernando Eduardo Verdugo Saldaña</t>
+          <t>Areli Anahi Lazcano Lezama</t>
         </is>
       </c>
       <c r="E240" s="7" t="n">
@@ -11180,17 +11147,17 @@
       </c>
       <c r="B241" s="15" t="inlineStr">
         <is>
-          <t>38668</t>
+          <t>38553</t>
         </is>
       </c>
       <c r="C241" s="12" t="inlineStr">
         <is>
-          <t>Pabellon Metepec</t>
+          <t>Paseo Interlomas II</t>
         </is>
       </c>
       <c r="D241" s="12" t="inlineStr">
         <is>
-          <t>Daniel Flores Maldonado</t>
+          <t>Areli Anahi Lazcano Lezama</t>
         </is>
       </c>
       <c r="E241" s="11" t="n">
@@ -11220,12 +11187,12 @@
       </c>
       <c r="B242" s="17" t="inlineStr">
         <is>
-          <t>43107</t>
+          <t>38799</t>
         </is>
       </c>
       <c r="C242" s="8" t="inlineStr">
         <is>
-          <t>Pabellón Bosques</t>
+          <t>Paseo Interlomas III</t>
         </is>
       </c>
       <c r="D242" s="8" t="inlineStr">
@@ -11260,17 +11227,17 @@
       </c>
       <c r="B243" s="15" t="inlineStr">
         <is>
-          <t>38188</t>
+          <t>38896</t>
         </is>
       </c>
       <c r="C243" s="12" t="inlineStr">
         <is>
-          <t>Palmas</t>
+          <t>Paseo Tollocan DT</t>
         </is>
       </c>
       <c r="D243" s="12" t="inlineStr">
         <is>
-          <t>Adriana Alejandra Tanus Buhler</t>
+          <t>Daniel Flores Maldonado</t>
         </is>
       </c>
       <c r="E243" s="11" t="n">
@@ -11300,17 +11267,17 @@
       </c>
       <c r="B244" s="17" t="inlineStr">
         <is>
-          <t>38414</t>
+          <t>38718</t>
         </is>
       </c>
       <c r="C244" s="8" t="inlineStr">
         <is>
-          <t>Park Plaza</t>
+          <t>Paseo Ventura</t>
         </is>
       </c>
       <c r="D244" s="8" t="inlineStr">
         <is>
-          <t>Erika Julieta Contreras Aguilera</t>
+          <t>Monica Selene Morales Ibarra</t>
         </is>
       </c>
       <c r="E244" s="7" t="n">
@@ -11340,12 +11307,12 @@
       </c>
       <c r="B245" s="15" t="inlineStr">
         <is>
-          <t>43041</t>
+          <t>38722</t>
         </is>
       </c>
       <c r="C245" s="12" t="inlineStr">
         <is>
-          <t>Parque Aztlan</t>
+          <t>Patio Barranca N2</t>
         </is>
       </c>
       <c r="D245" s="12" t="inlineStr">
@@ -11380,17 +11347,17 @@
       </c>
       <c r="B246" s="17" t="inlineStr">
         <is>
-          <t>38452</t>
+          <t>38720</t>
         </is>
       </c>
       <c r="C246" s="8" t="inlineStr">
         <is>
-          <t>Parque Interlomas</t>
+          <t>Patio Barranca PB</t>
         </is>
       </c>
       <c r="D246" s="8" t="inlineStr">
         <is>
-          <t>Areli Anahi Lazcano Lezama</t>
+          <t>Manuel Alejandro Avila Molina</t>
         </is>
       </c>
       <c r="E246" s="7" t="n">
@@ -11420,17 +11387,17 @@
       </c>
       <c r="B247" s="15" t="inlineStr">
         <is>
-          <t>38777</t>
+          <t>38762</t>
         </is>
       </c>
       <c r="C247" s="12" t="inlineStr">
         <is>
-          <t>Parque la Mexicana</t>
+          <t>Patio Boturini</t>
         </is>
       </c>
       <c r="D247" s="12" t="inlineStr">
         <is>
-          <t>Jose De Jesus Magos Arzaluz</t>
+          <t>Vacante</t>
         </is>
       </c>
       <c r="E247" s="11" t="n">
@@ -11460,17 +11427,17 @@
       </c>
       <c r="B248" s="17" t="inlineStr">
         <is>
-          <t>38581</t>
+          <t>38657</t>
         </is>
       </c>
       <c r="C248" s="8" t="inlineStr">
         <is>
-          <t>Parques BBVA</t>
+          <t>Patio Lomas Estrella</t>
         </is>
       </c>
       <c r="D248" s="8" t="inlineStr">
         <is>
-          <t>Luis Manuel Neri Saldaña</t>
+          <t>Jesus Antonio Elguera Flores</t>
         </is>
       </c>
       <c r="E248" s="7" t="n">
@@ -11500,17 +11467,17 @@
       </c>
       <c r="B249" s="15" t="inlineStr">
         <is>
-          <t>38344</t>
+          <t>38691</t>
         </is>
       </c>
       <c r="C249" s="12" t="inlineStr">
         <is>
-          <t>Parques Polanco</t>
+          <t>Patio Revolución</t>
         </is>
       </c>
       <c r="D249" s="12" t="inlineStr">
         <is>
-          <t>Maria Anallely Sanchez Garcia</t>
+          <t>Cesar Alfonso Castillo Romero</t>
         </is>
       </c>
       <c r="E249" s="11" t="n">
@@ -11540,17 +11507,17 @@
       </c>
       <c r="B250" s="17" t="inlineStr">
         <is>
-          <t>38580</t>
+          <t>38534</t>
         </is>
       </c>
       <c r="C250" s="8" t="inlineStr">
         <is>
-          <t>Pasaje San Jeronimo</t>
+          <t>Patio Santa Fe 1</t>
         </is>
       </c>
       <c r="D250" s="8" t="inlineStr">
         <is>
-          <t>Cesar Alfonso Castillo Romero</t>
+          <t>Erika Julieta Contreras Aguilera</t>
         </is>
       </c>
       <c r="E250" s="7" t="n">
@@ -11580,17 +11547,17 @@
       </c>
       <c r="B251" s="15" t="inlineStr">
         <is>
-          <t>38466</t>
+          <t>38749</t>
         </is>
       </c>
       <c r="C251" s="12" t="inlineStr">
         <is>
-          <t>Paseo Interlomas I</t>
+          <t>Patio Santa Fe 2</t>
         </is>
       </c>
       <c r="D251" s="12" t="inlineStr">
         <is>
-          <t>Areli Anahi Lazcano Lezama</t>
+          <t>Erika Julieta Contreras Aguilera</t>
         </is>
       </c>
       <c r="E251" s="11" t="n">
@@ -11620,17 +11587,17 @@
       </c>
       <c r="B252" s="17" t="inlineStr">
         <is>
-          <t>38553</t>
+          <t>38806</t>
         </is>
       </c>
       <c r="C252" s="8" t="inlineStr">
         <is>
-          <t>Paseo Interlomas II</t>
+          <t>Patio Tlalpan</t>
         </is>
       </c>
       <c r="D252" s="8" t="inlineStr">
         <is>
-          <t>Areli Anahi Lazcano Lezama</t>
+          <t>Hazar Susim Trejo Hernandez</t>
         </is>
       </c>
       <c r="E252" s="7" t="n">
@@ -11660,17 +11627,17 @@
       </c>
       <c r="B253" s="15" t="inlineStr">
         <is>
-          <t>38799</t>
+          <t>38769</t>
         </is>
       </c>
       <c r="C253" s="12" t="inlineStr">
         <is>
-          <t>Paseo Interlomas III</t>
+          <t>Patio Toluca</t>
         </is>
       </c>
       <c r="D253" s="12" t="inlineStr">
         <is>
-          <t>Areli Anahi Lazcano Lezama</t>
+          <t>Andrea Nava Guzman</t>
         </is>
       </c>
       <c r="E253" s="11" t="n">
@@ -11700,17 +11667,17 @@
       </c>
       <c r="B254" s="17" t="inlineStr">
         <is>
-          <t>38896</t>
+          <t>38501</t>
         </is>
       </c>
       <c r="C254" s="8" t="inlineStr">
         <is>
-          <t>Paseo Tollocan DT</t>
+          <t>Patio Universidad</t>
         </is>
       </c>
       <c r="D254" s="8" t="inlineStr">
         <is>
-          <t>Daniel Flores Maldonado</t>
+          <t>Luis Alberto Quevedo Rodriguez</t>
         </is>
       </c>
       <c r="E254" s="7" t="n">
@@ -11740,17 +11707,17 @@
       </c>
       <c r="B255" s="15" t="inlineStr">
         <is>
-          <t>38718</t>
+          <t>38107</t>
         </is>
       </c>
       <c r="C255" s="12" t="inlineStr">
         <is>
-          <t>Paseo Ventura</t>
+          <t>Pedregal</t>
         </is>
       </c>
       <c r="D255" s="12" t="inlineStr">
         <is>
-          <t>Monica Selene Morales Ibarra</t>
+          <t>Cesar Alfonso Castillo Romero</t>
         </is>
       </c>
       <c r="E255" s="11" t="n">
@@ -11780,17 +11747,17 @@
       </c>
       <c r="B256" s="17" t="inlineStr">
         <is>
-          <t>38722</t>
+          <t>38499</t>
         </is>
       </c>
       <c r="C256" s="8" t="inlineStr">
         <is>
-          <t>Patio Barranca N2</t>
+          <t>Pennsylvania</t>
         </is>
       </c>
       <c r="D256" s="8" t="inlineStr">
         <is>
-          <t>Manuel Alejandro Avila Molina</t>
+          <t>Juan Jesus Zuñiga Flores</t>
         </is>
       </c>
       <c r="E256" s="7" t="n">
@@ -11820,17 +11787,17 @@
       </c>
       <c r="B257" s="15" t="inlineStr">
         <is>
-          <t>38720</t>
+          <t>38402</t>
         </is>
       </c>
       <c r="C257" s="12" t="inlineStr">
         <is>
-          <t>Patio Barranca PB</t>
+          <t>PeriSur</t>
         </is>
       </c>
       <c r="D257" s="12" t="inlineStr">
         <is>
-          <t>Manuel Alejandro Avila Molina</t>
+          <t>Hazar Susim Trejo Hernandez</t>
         </is>
       </c>
       <c r="E257" s="11" t="n">
@@ -11860,17 +11827,17 @@
       </c>
       <c r="B258" s="17" t="inlineStr">
         <is>
-          <t>38762</t>
+          <t>43045</t>
         </is>
       </c>
       <c r="C258" s="8" t="inlineStr">
         <is>
-          <t>Patio Boturini</t>
+          <t>Periferico Polanco DT</t>
         </is>
       </c>
       <c r="D258" s="8" t="inlineStr">
         <is>
-          <t>Vacante</t>
+          <t>Luis Manuel Neri Saldaña</t>
         </is>
       </c>
       <c r="E258" s="7" t="n">
@@ -11900,17 +11867,17 @@
       </c>
       <c r="B259" s="15" t="inlineStr">
         <is>
-          <t>38657</t>
+          <t>38866</t>
         </is>
       </c>
       <c r="C259" s="12" t="inlineStr">
         <is>
-          <t>Patio Lomas Estrella</t>
+          <t>Perisur Reserve</t>
         </is>
       </c>
       <c r="D259" s="12" t="inlineStr">
         <is>
-          <t>Jesus Antonio Elguera Flores</t>
+          <t>Hazar Susim Trejo Hernandez</t>
         </is>
       </c>
       <c r="E259" s="11" t="n">
@@ -11940,17 +11907,17 @@
       </c>
       <c r="B260" s="17" t="inlineStr">
         <is>
-          <t>38691</t>
+          <t>38482</t>
         </is>
       </c>
       <c r="C260" s="8" t="inlineStr">
         <is>
-          <t>Patio Revolución</t>
+          <t>Pestalozzi</t>
         </is>
       </c>
       <c r="D260" s="8" t="inlineStr">
         <is>
-          <t>Cesar Alfonso Castillo Romero</t>
+          <t>Luis Alberto Quevedo Rodriguez</t>
         </is>
       </c>
       <c r="E260" s="7" t="n">
@@ -11980,17 +11947,17 @@
       </c>
       <c r="B261" s="15" t="inlineStr">
         <is>
-          <t>38534</t>
+          <t>38544</t>
         </is>
       </c>
       <c r="C261" s="12" t="inlineStr">
         <is>
-          <t>Patio Santa Fe 1</t>
+          <t>Picacho Ajusco</t>
         </is>
       </c>
       <c r="D261" s="12" t="inlineStr">
         <is>
-          <t>Erika Julieta Contreras Aguilera</t>
+          <t>Cesar Alfonso Castillo Romero</t>
         </is>
       </c>
       <c r="E261" s="11" t="n">
@@ -12020,17 +11987,17 @@
       </c>
       <c r="B262" s="17" t="inlineStr">
         <is>
-          <t>38749</t>
+          <t>38134</t>
         </is>
       </c>
       <c r="C262" s="8" t="inlineStr">
         <is>
-          <t>Patio Santa Fe 2</t>
+          <t>Pilares</t>
         </is>
       </c>
       <c r="D262" s="8" t="inlineStr">
         <is>
-          <t>Erika Julieta Contreras Aguilera</t>
+          <t>Luis Alberto Quevedo Rodriguez</t>
         </is>
       </c>
       <c r="E262" s="7" t="n">
@@ -12060,17 +12027,17 @@
       </c>
       <c r="B263" s="15" t="inlineStr">
         <is>
-          <t>38806</t>
+          <t>38587</t>
         </is>
       </c>
       <c r="C263" s="12" t="inlineStr">
         <is>
-          <t>Patio Tlalpan</t>
+          <t>Plateros</t>
         </is>
       </c>
       <c r="D263" s="12" t="inlineStr">
         <is>
-          <t>Hazar Susim Trejo Hernandez</t>
+          <t>Juan Jesus Zuñiga Flores</t>
         </is>
       </c>
       <c r="E263" s="11" t="n">
@@ -12100,17 +12067,17 @@
       </c>
       <c r="B264" s="17" t="inlineStr">
         <is>
-          <t>38769</t>
+          <t>38123</t>
         </is>
       </c>
       <c r="C264" s="8" t="inlineStr">
         <is>
-          <t>Patio Toluca</t>
+          <t>Plaza Alameda</t>
         </is>
       </c>
       <c r="D264" s="8" t="inlineStr">
         <is>
-          <t>Andrea Nava Guzman</t>
+          <t>Vacante</t>
         </is>
       </c>
       <c r="E264" s="7" t="n">
@@ -12140,17 +12107,17 @@
       </c>
       <c r="B265" s="15" t="inlineStr">
         <is>
-          <t>38501</t>
+          <t>38472</t>
         </is>
       </c>
       <c r="C265" s="12" t="inlineStr">
         <is>
-          <t>Patio Universidad</t>
+          <t>Plaza America DT</t>
         </is>
       </c>
       <c r="D265" s="12" t="inlineStr">
         <is>
-          <t>Luis Alberto Quevedo Rodriguez</t>
+          <t>Fernando Eduardo Verdugo Saldaña</t>
         </is>
       </c>
       <c r="E265" s="11" t="n">
@@ -12180,17 +12147,17 @@
       </c>
       <c r="B266" s="17" t="inlineStr">
         <is>
-          <t>38107</t>
+          <t>38429</t>
         </is>
       </c>
       <c r="C266" s="8" t="inlineStr">
         <is>
-          <t>Pedregal</t>
+          <t>Plaza Aragon</t>
         </is>
       </c>
       <c r="D266" s="8" t="inlineStr">
         <is>
-          <t>Cesar Alfonso Castillo Romero</t>
+          <t>Monica Selene Morales Ibarra</t>
         </is>
       </c>
       <c r="E266" s="7" t="n">
@@ -12220,17 +12187,17 @@
       </c>
       <c r="B267" s="15" t="inlineStr">
         <is>
-          <t>38499</t>
+          <t>38611</t>
         </is>
       </c>
       <c r="C267" s="12" t="inlineStr">
         <is>
-          <t>Pennsylvania</t>
+          <t>Plaza Basica</t>
         </is>
       </c>
       <c r="D267" s="12" t="inlineStr">
         <is>
-          <t>Juan Jesus Zuñiga Flores</t>
+          <t>Ariana Janet Gutierrez Martinez</t>
         </is>
       </c>
       <c r="E267" s="11" t="n">
@@ -12260,17 +12227,17 @@
       </c>
       <c r="B268" s="17" t="inlineStr">
         <is>
-          <t>38402</t>
+          <t>38810</t>
         </is>
       </c>
       <c r="C268" s="8" t="inlineStr">
         <is>
-          <t>PeriSur</t>
+          <t>Plaza Centenario ( Tenaria)</t>
         </is>
       </c>
       <c r="D268" s="8" t="inlineStr">
         <is>
-          <t>Hazar Susim Trejo Hernandez</t>
+          <t>Jose De Jesus Magos Arzaluz</t>
         </is>
       </c>
       <c r="E268" s="7" t="n">
@@ -12300,17 +12267,17 @@
       </c>
       <c r="B269" s="15" t="inlineStr">
         <is>
-          <t>43045</t>
+          <t>38645</t>
         </is>
       </c>
       <c r="C269" s="12" t="inlineStr">
         <is>
-          <t>Periferico Polanco DT</t>
+          <t>Plaza Central</t>
         </is>
       </c>
       <c r="D269" s="12" t="inlineStr">
         <is>
-          <t>Luis Manuel Neri Saldaña</t>
+          <t>Ariana Janet Gutierrez Martinez</t>
         </is>
       </c>
       <c r="E269" s="11" t="n">
@@ -12340,17 +12307,17 @@
       </c>
       <c r="B270" s="17" t="inlineStr">
         <is>
-          <t>38866</t>
+          <t>38684</t>
         </is>
       </c>
       <c r="C270" s="8" t="inlineStr">
         <is>
-          <t>Perisur Reserve</t>
+          <t>Plaza Chimalhuacan</t>
         </is>
       </c>
       <c r="D270" s="8" t="inlineStr">
         <is>
-          <t>Hazar Susim Trejo Hernandez</t>
+          <t>Monica Selene Morales Ibarra</t>
         </is>
       </c>
       <c r="E270" s="7" t="n">
@@ -12380,17 +12347,17 @@
       </c>
       <c r="B271" s="15" t="inlineStr">
         <is>
-          <t>38482</t>
+          <t>38605</t>
         </is>
       </c>
       <c r="C271" s="12" t="inlineStr">
         <is>
-          <t>Pestalozzi</t>
+          <t>Plaza Cuicuilco</t>
         </is>
       </c>
       <c r="D271" s="12" t="inlineStr">
         <is>
-          <t>Luis Alberto Quevedo Rodriguez</t>
+          <t>Hazar Susim Trejo Hernandez</t>
         </is>
       </c>
       <c r="E271" s="11" t="n">
@@ -12420,17 +12387,17 @@
       </c>
       <c r="B272" s="17" t="inlineStr">
         <is>
-          <t>38544</t>
+          <t>38173</t>
         </is>
       </c>
       <c r="C272" s="8" t="inlineStr">
         <is>
-          <t>Picacho Ajusco</t>
+          <t>Plaza Delta Planta Alta</t>
         </is>
       </c>
       <c r="D272" s="8" t="inlineStr">
         <is>
-          <t>Cesar Alfonso Castillo Romero</t>
+          <t>Nora Caracas Saldaña</t>
         </is>
       </c>
       <c r="E272" s="7" t="n">
@@ -12460,17 +12427,17 @@
       </c>
       <c r="B273" s="15" t="inlineStr">
         <is>
-          <t>38134</t>
+          <t>38658</t>
         </is>
       </c>
       <c r="C273" s="12" t="inlineStr">
         <is>
-          <t>Pilares</t>
+          <t>Plaza Delta Planta Baja</t>
         </is>
       </c>
       <c r="D273" s="12" t="inlineStr">
         <is>
-          <t>Luis Alberto Quevedo Rodriguez</t>
+          <t>Nora Caracas Saldaña</t>
         </is>
       </c>
       <c r="E273" s="11" t="n">
@@ -12500,17 +12467,17 @@
       </c>
       <c r="B274" s="17" t="inlineStr">
         <is>
-          <t>38587</t>
+          <t>43026</t>
         </is>
       </c>
       <c r="C274" s="8" t="inlineStr">
         <is>
-          <t>Plateros</t>
+          <t>Plaza Ermita</t>
         </is>
       </c>
       <c r="D274" s="8" t="inlineStr">
         <is>
-          <t>Juan Jesus Zuñiga Flores</t>
+          <t>Jesus Antonio Elguera Flores</t>
         </is>
       </c>
       <c r="E274" s="7" t="n">
@@ -12540,17 +12507,17 @@
       </c>
       <c r="B275" s="15" t="inlineStr">
         <is>
-          <t>38123</t>
+          <t>38692</t>
         </is>
       </c>
       <c r="C275" s="12" t="inlineStr">
         <is>
-          <t>Plaza Alameda</t>
+          <t>Plaza Exhibimex</t>
         </is>
       </c>
       <c r="D275" s="12" t="inlineStr">
         <is>
-          <t>Vacante</t>
+          <t>Adriana Alejandra Tanus Buhler</t>
         </is>
       </c>
       <c r="E275" s="11" t="n">
@@ -12580,17 +12547,17 @@
       </c>
       <c r="B276" s="17" t="inlineStr">
         <is>
-          <t>38472</t>
+          <t>38139</t>
         </is>
       </c>
       <c r="C276" s="8" t="inlineStr">
         <is>
-          <t>Plaza America DT</t>
+          <t>Plaza Inn</t>
         </is>
       </c>
       <c r="D276" s="8" t="inlineStr">
         <is>
-          <t>Fernando Eduardo Verdugo Saldaña</t>
+          <t>Jaqueline Cortes Ayala</t>
         </is>
       </c>
       <c r="E276" s="7" t="n">
@@ -12620,17 +12587,17 @@
       </c>
       <c r="B277" s="15" t="inlineStr">
         <is>
-          <t>38429</t>
+          <t>38158</t>
         </is>
       </c>
       <c r="C277" s="12" t="inlineStr">
         <is>
-          <t>Plaza Aragon</t>
+          <t>Plaza Lilas</t>
         </is>
       </c>
       <c r="D277" s="12" t="inlineStr">
         <is>
-          <t>Monica Selene Morales Ibarra</t>
+          <t>Jose De Jesus Magos Arzaluz</t>
         </is>
       </c>
       <c r="E277" s="11" t="n">
@@ -12660,17 +12627,17 @@
       </c>
       <c r="B278" s="17" t="inlineStr">
         <is>
-          <t>38611</t>
+          <t>38432</t>
         </is>
       </c>
       <c r="C278" s="8" t="inlineStr">
         <is>
-          <t>Plaza Basica</t>
+          <t>Plaza Luis Cabrera</t>
         </is>
       </c>
       <c r="D278" s="8" t="inlineStr">
         <is>
-          <t>Ariana Janet Gutierrez Martinez</t>
+          <t>Nora Caracas Saldaña</t>
         </is>
       </c>
       <c r="E278" s="7" t="n">
@@ -12700,17 +12667,17 @@
       </c>
       <c r="B279" s="15" t="inlineStr">
         <is>
-          <t>38810</t>
+          <t>38141</t>
         </is>
       </c>
       <c r="C279" s="12" t="inlineStr">
         <is>
-          <t>Plaza Centenario ( Tenaria)</t>
+          <t>Plaza Mayor Metepec</t>
         </is>
       </c>
       <c r="D279" s="12" t="inlineStr">
         <is>
-          <t>Jose De Jesus Magos Arzaluz</t>
+          <t>Daniel Flores Maldonado</t>
         </is>
       </c>
       <c r="E279" s="11" t="n">
@@ -12740,12 +12707,12 @@
       </c>
       <c r="B280" s="17" t="inlineStr">
         <is>
-          <t>38645</t>
+          <t>38418</t>
         </is>
       </c>
       <c r="C280" s="8" t="inlineStr">
         <is>
-          <t>Plaza Central</t>
+          <t>Plaza Oriente l</t>
         </is>
       </c>
       <c r="D280" s="8" t="inlineStr">
@@ -12780,17 +12747,17 @@
       </c>
       <c r="B281" s="15" t="inlineStr">
         <is>
-          <t>38684</t>
+          <t>38725</t>
         </is>
       </c>
       <c r="C281" s="12" t="inlineStr">
         <is>
-          <t>Plaza Chimalhuacan</t>
+          <t>Plaza Oriente ll</t>
         </is>
       </c>
       <c r="D281" s="12" t="inlineStr">
         <is>
-          <t>Monica Selene Morales Ibarra</t>
+          <t>Ariana Janet Gutierrez Martinez</t>
         </is>
       </c>
       <c r="E281" s="11" t="n">
@@ -12820,17 +12787,17 @@
       </c>
       <c r="B282" s="17" t="inlineStr">
         <is>
-          <t>38605</t>
+          <t>38129</t>
         </is>
       </c>
       <c r="C282" s="8" t="inlineStr">
         <is>
-          <t>Plaza Cuicuilco</t>
+          <t>Plaza Santa Teresa</t>
         </is>
       </c>
       <c r="D282" s="8" t="inlineStr">
         <is>
-          <t>Hazar Susim Trejo Hernandez</t>
+          <t>Cesar Alfonso Castillo Romero</t>
         </is>
       </c>
       <c r="E282" s="7" t="n">
@@ -12860,17 +12827,17 @@
       </c>
       <c r="B283" s="15" t="inlineStr">
         <is>
-          <t>38173</t>
+          <t>43169</t>
         </is>
       </c>
       <c r="C283" s="12" t="inlineStr">
         <is>
-          <t>Plaza Delta Planta Alta</t>
+          <t>Plaza Tepozán</t>
         </is>
       </c>
       <c r="D283" s="12" t="inlineStr">
         <is>
-          <t>Nora Caracas Saldaña</t>
+          <t>Jesus Antonio Elguera Flores</t>
         </is>
       </c>
       <c r="E283" s="11" t="n">
@@ -12900,17 +12867,17 @@
       </c>
       <c r="B284" s="17" t="inlineStr">
         <is>
-          <t>38658</t>
+          <t>43123</t>
         </is>
       </c>
       <c r="C284" s="8" t="inlineStr">
         <is>
-          <t>Plaza Delta Planta Baja</t>
+          <t>Plaza Tlatelolco</t>
         </is>
       </c>
       <c r="D284" s="8" t="inlineStr">
         <is>
-          <t>Nora Caracas Saldaña</t>
+          <t>Vacante</t>
         </is>
       </c>
       <c r="E284" s="7" t="n">
@@ -12940,17 +12907,17 @@
       </c>
       <c r="B285" s="15" t="inlineStr">
         <is>
-          <t>43026</t>
+          <t>38569</t>
         </is>
       </c>
       <c r="C285" s="12" t="inlineStr">
         <is>
-          <t>Plaza Ermita</t>
+          <t>Plaza Universidad</t>
         </is>
       </c>
       <c r="D285" s="12" t="inlineStr">
         <is>
-          <t>Jesus Antonio Elguera Flores</t>
+          <t>Luis Alberto Quevedo Rodriguez</t>
         </is>
       </c>
       <c r="E285" s="11" t="n">
@@ -12980,17 +12947,17 @@
       </c>
       <c r="B286" s="17" t="inlineStr">
         <is>
-          <t>38692</t>
+          <t>38855</t>
         </is>
       </c>
       <c r="C286" s="8" t="inlineStr">
         <is>
-          <t>Plaza Exhibimex</t>
+          <t>Plaza Zapotitlán DT</t>
         </is>
       </c>
       <c r="D286" s="8" t="inlineStr">
         <is>
-          <t>Adriana Alejandra Tanus Buhler</t>
+          <t>Jesus Antonio Elguera Flores</t>
         </is>
       </c>
       <c r="E286" s="7" t="n">
@@ -13020,17 +12987,17 @@
       </c>
       <c r="B287" s="15" t="inlineStr">
         <is>
-          <t>38139</t>
+          <t>38360</t>
         </is>
       </c>
       <c r="C287" s="12" t="inlineStr">
         <is>
-          <t>Plaza Inn</t>
+          <t>Plaza la Hacienda</t>
         </is>
       </c>
       <c r="D287" s="12" t="inlineStr">
         <is>
-          <t>Jaqueline Cortes Ayala</t>
+          <t>Fernando Eduardo Verdugo Saldaña</t>
         </is>
       </c>
       <c r="E287" s="11" t="n">
@@ -13060,17 +13027,17 @@
       </c>
       <c r="B288" s="17" t="inlineStr">
         <is>
-          <t>38158</t>
+          <t>38468</t>
         </is>
       </c>
       <c r="C288" s="8" t="inlineStr">
         <is>
-          <t>Plaza Lilas</t>
+          <t>Portal Churubusco</t>
         </is>
       </c>
       <c r="D288" s="8" t="inlineStr">
         <is>
-          <t>Jose De Jesus Magos Arzaluz</t>
+          <t>Ariana Janet Gutierrez Martinez</t>
         </is>
       </c>
       <c r="E288" s="7" t="n">
@@ -13100,17 +13067,17 @@
       </c>
       <c r="B289" s="15" t="inlineStr">
         <is>
-          <t>38432</t>
+          <t>38678</t>
         </is>
       </c>
       <c r="C289" s="12" t="inlineStr">
         <is>
-          <t>Plaza Luis Cabrera</t>
+          <t>Power Center las Americas</t>
         </is>
       </c>
       <c r="D289" s="12" t="inlineStr">
         <is>
-          <t>Nora Caracas Saldaña</t>
+          <t>Monica Selene Morales Ibarra</t>
         </is>
       </c>
       <c r="E289" s="11" t="n">
@@ -13140,17 +13107,17 @@
       </c>
       <c r="B290" s="17" t="inlineStr">
         <is>
-          <t>38141</t>
+          <t>38106</t>
         </is>
       </c>
       <c r="C290" s="8" t="inlineStr">
         <is>
-          <t>Plaza Mayor Metepec</t>
+          <t>Prado Norte</t>
         </is>
       </c>
       <c r="D290" s="8" t="inlineStr">
         <is>
-          <t>Daniel Flores Maldonado</t>
+          <t>Adriana Alejandra Tanus Buhler</t>
         </is>
       </c>
       <c r="E290" s="7" t="n">
@@ -13180,17 +13147,17 @@
       </c>
       <c r="B291" s="15" t="inlineStr">
         <is>
-          <t>38418</t>
+          <t>38430</t>
         </is>
       </c>
       <c r="C291" s="12" t="inlineStr">
         <is>
-          <t>Plaza Oriente l</t>
+          <t>Prisma Insurgentes</t>
         </is>
       </c>
       <c r="D291" s="12" t="inlineStr">
         <is>
-          <t>Ariana Janet Gutierrez Martinez</t>
+          <t>Jaqueline Cortes Ayala</t>
         </is>
       </c>
       <c r="E291" s="11" t="n">
@@ -13220,17 +13187,17 @@
       </c>
       <c r="B292" s="17" t="inlineStr">
         <is>
-          <t>38725</t>
+          <t>43183</t>
         </is>
       </c>
       <c r="C292" s="8" t="inlineStr">
         <is>
-          <t>Plaza Oriente ll</t>
+          <t>Puerta Texcoco</t>
         </is>
       </c>
       <c r="D292" s="8" t="inlineStr">
         <is>
-          <t>Ariana Janet Gutierrez Martinez</t>
+          <t>Monica Selene Morales Ibarra</t>
         </is>
       </c>
       <c r="E292" s="7" t="n">
@@ -13260,17 +13227,17 @@
       </c>
       <c r="B293" s="15" t="inlineStr">
         <is>
-          <t>38129</t>
+          <t>38987</t>
         </is>
       </c>
       <c r="C293" s="12" t="inlineStr">
         <is>
-          <t>Plaza Santa Teresa</t>
+          <t>Punta Zero Calimaya DT</t>
         </is>
       </c>
       <c r="D293" s="12" t="inlineStr">
         <is>
-          <t>Cesar Alfonso Castillo Romero</t>
+          <t>Daniel Flores Maldonado</t>
         </is>
       </c>
       <c r="E293" s="11" t="n">
@@ -13300,17 +13267,17 @@
       </c>
       <c r="B294" s="17" t="inlineStr">
         <is>
-          <t>43169</t>
+          <t>43025</t>
         </is>
       </c>
       <c r="C294" s="8" t="inlineStr">
         <is>
-          <t>Plaza Tepozán</t>
+          <t>Punto MAQ</t>
         </is>
       </c>
       <c r="D294" s="8" t="inlineStr">
         <is>
-          <t>Jesus Antonio Elguera Flores</t>
+          <t>Jaqueline Cortes Ayala</t>
         </is>
       </c>
       <c r="E294" s="7" t="n">
@@ -13340,17 +13307,17 @@
       </c>
       <c r="B295" s="15" t="inlineStr">
         <is>
-          <t>43123</t>
+          <t>38635</t>
         </is>
       </c>
       <c r="C295" s="12" t="inlineStr">
         <is>
-          <t>Plaza Tlatelolco</t>
+          <t>Punto Polanco</t>
         </is>
       </c>
       <c r="D295" s="12" t="inlineStr">
         <is>
-          <t>Vacante</t>
+          <t>Maria Anallely Sanchez Garcia</t>
         </is>
       </c>
       <c r="E295" s="11" t="n">
@@ -13380,17 +13347,17 @@
       </c>
       <c r="B296" s="17" t="inlineStr">
         <is>
-          <t>38569</t>
+          <t>38654</t>
         </is>
       </c>
       <c r="C296" s="8" t="inlineStr">
         <is>
-          <t>Plaza Universidad</t>
+          <t>Reforma 180</t>
         </is>
       </c>
       <c r="D296" s="8" t="inlineStr">
         <is>
-          <t>Luis Alberto Quevedo Rodriguez</t>
+          <t>Guadalupe Ibarra Martínez</t>
         </is>
       </c>
       <c r="E296" s="7" t="n">
@@ -13420,17 +13387,17 @@
       </c>
       <c r="B297" s="15" t="inlineStr">
         <is>
-          <t>38855</t>
+          <t>38285</t>
         </is>
       </c>
       <c r="C297" s="12" t="inlineStr">
         <is>
-          <t>Plaza Zapotitlán DT</t>
+          <t>Reforma 222</t>
         </is>
       </c>
       <c r="D297" s="12" t="inlineStr">
         <is>
-          <t>Jesus Antonio Elguera Flores</t>
+          <t>Guadalupe Ibarra Martínez</t>
         </is>
       </c>
       <c r="E297" s="11" t="n">
@@ -13460,17 +13427,17 @@
       </c>
       <c r="B298" s="17" t="inlineStr">
         <is>
-          <t>38360</t>
+          <t>38291</t>
         </is>
       </c>
       <c r="C298" s="8" t="inlineStr">
         <is>
-          <t>Plaza la Hacienda</t>
+          <t>Reforma 222 II</t>
         </is>
       </c>
       <c r="D298" s="8" t="inlineStr">
         <is>
-          <t>Fernando Eduardo Verdugo Saldaña</t>
+          <t>Guadalupe Ibarra Martínez</t>
         </is>
       </c>
       <c r="E298" s="7" t="n">
@@ -13500,17 +13467,17 @@
       </c>
       <c r="B299" s="15" t="inlineStr">
         <is>
-          <t>38468</t>
+          <t>38560</t>
         </is>
       </c>
       <c r="C299" s="12" t="inlineStr">
         <is>
-          <t>Portal Churubusco</t>
+          <t>Renato Leduc</t>
         </is>
       </c>
       <c r="D299" s="12" t="inlineStr">
         <is>
-          <t>Ariana Janet Gutierrez Martinez</t>
+          <t>Hazar Susim Trejo Hernandez</t>
         </is>
       </c>
       <c r="E299" s="11" t="n">
@@ -13540,17 +13507,17 @@
       </c>
       <c r="B300" s="17" t="inlineStr">
         <is>
-          <t>38678</t>
+          <t>38522</t>
         </is>
       </c>
       <c r="C300" s="8" t="inlineStr">
         <is>
-          <t>Power Center las Americas</t>
+          <t>Rio Hudson</t>
         </is>
       </c>
       <c r="D300" s="8" t="inlineStr">
         <is>
-          <t>Monica Selene Morales Ibarra</t>
+          <t>Alberto Torrado Aguilar Cauz</t>
         </is>
       </c>
       <c r="E300" s="7" t="n">
@@ -13580,17 +13547,17 @@
       </c>
       <c r="B301" s="15" t="inlineStr">
         <is>
-          <t>38106</t>
+          <t>38389</t>
         </is>
       </c>
       <c r="C301" s="12" t="inlineStr">
         <is>
-          <t>Prado Norte</t>
+          <t>Rio Marne</t>
         </is>
       </c>
       <c r="D301" s="12" t="inlineStr">
         <is>
-          <t>Adriana Alejandra Tanus Buhler</t>
+          <t>Guadalupe Ibarra Martínez</t>
         </is>
       </c>
       <c r="E301" s="11" t="n">
@@ -13620,17 +13587,17 @@
       </c>
       <c r="B302" s="17" t="inlineStr">
         <is>
-          <t>38430</t>
+          <t>38557</t>
         </is>
       </c>
       <c r="C302" s="8" t="inlineStr">
         <is>
-          <t>Prisma Insurgentes</t>
+          <t>Rio San Joaquin</t>
         </is>
       </c>
       <c r="D302" s="8" t="inlineStr">
         <is>
-          <t>Jaqueline Cortes Ayala</t>
+          <t>Luis Manuel Neri Saldaña</t>
         </is>
       </c>
       <c r="E302" s="7" t="n">
@@ -13660,17 +13627,17 @@
       </c>
       <c r="B303" s="15" t="inlineStr">
         <is>
-          <t>43183</t>
+          <t>43070</t>
         </is>
       </c>
       <c r="C303" s="12" t="inlineStr">
         <is>
-          <t>Puerta Texcoco</t>
+          <t>Rojo Gomez DT</t>
         </is>
       </c>
       <c r="D303" s="12" t="inlineStr">
         <is>
-          <t>Monica Selene Morales Ibarra</t>
+          <t>Ariana Janet Gutierrez Martinez</t>
         </is>
       </c>
       <c r="E303" s="11" t="n">
@@ -13700,17 +13667,17 @@
       </c>
       <c r="B304" s="17" t="inlineStr">
         <is>
-          <t>38987</t>
+          <t>38558</t>
         </is>
       </c>
       <c r="C304" s="8" t="inlineStr">
         <is>
-          <t>Punta Zero Calimaya DT</t>
+          <t>Roma Sur</t>
         </is>
       </c>
       <c r="D304" s="8" t="inlineStr">
         <is>
-          <t>Daniel Flores Maldonado</t>
+          <t>Nora Caracas Saldaña</t>
         </is>
       </c>
       <c r="E304" s="7" t="n">
@@ -13740,17 +13707,17 @@
       </c>
       <c r="B305" s="15" t="inlineStr">
         <is>
-          <t>43025</t>
+          <t>38653</t>
         </is>
       </c>
       <c r="C305" s="12" t="inlineStr">
         <is>
-          <t>Punto MAQ</t>
+          <t>Salon Ejecutivo T1 AICM</t>
         </is>
       </c>
       <c r="D305" s="12" t="inlineStr">
         <is>
-          <t>Jaqueline Cortes Ayala</t>
+          <t>Maria Anallely Sanchez Garcia</t>
         </is>
       </c>
       <c r="E305" s="11" t="n">
@@ -13780,17 +13747,17 @@
       </c>
       <c r="B306" s="17" t="inlineStr">
         <is>
-          <t>38635</t>
+          <t>38390</t>
         </is>
       </c>
       <c r="C306" s="8" t="inlineStr">
         <is>
-          <t>Punto Polanco</t>
+          <t>Samara I</t>
         </is>
       </c>
       <c r="D306" s="8" t="inlineStr">
         <is>
-          <t>Maria Anallely Sanchez Garcia</t>
+          <t>Jose De Jesus Magos Arzaluz</t>
         </is>
       </c>
       <c r="E306" s="7" t="n">
@@ -13820,17 +13787,17 @@
       </c>
       <c r="B307" s="15" t="inlineStr">
         <is>
-          <t>38654</t>
+          <t>38445</t>
         </is>
       </c>
       <c r="C307" s="12" t="inlineStr">
         <is>
-          <t>Reforma 180</t>
+          <t>Samara II</t>
         </is>
       </c>
       <c r="D307" s="12" t="inlineStr">
         <is>
-          <t>Guadalupe Ibarra Martínez</t>
+          <t>Jose De Jesus Magos Arzaluz</t>
         </is>
       </c>
       <c r="E307" s="11" t="n">
@@ -13860,17 +13827,17 @@
       </c>
       <c r="B308" s="17" t="inlineStr">
         <is>
-          <t>38285</t>
+          <t>38124</t>
         </is>
       </c>
       <c r="C308" s="8" t="inlineStr">
         <is>
-          <t>Reforma 222</t>
+          <t>San Jeronimo</t>
         </is>
       </c>
       <c r="D308" s="8" t="inlineStr">
         <is>
-          <t>Guadalupe Ibarra Martínez</t>
+          <t>Cesar Alfonso Castillo Romero</t>
         </is>
       </c>
       <c r="E308" s="7" t="n">
@@ -13900,17 +13867,17 @@
       </c>
       <c r="B309" s="15" t="inlineStr">
         <is>
-          <t>38291</t>
+          <t>38417</t>
         </is>
       </c>
       <c r="C309" s="12" t="inlineStr">
         <is>
-          <t>Reforma 222 II</t>
+          <t>San Jose Insurgentes</t>
         </is>
       </c>
       <c r="D309" s="12" t="inlineStr">
         <is>
-          <t>Guadalupe Ibarra Martínez</t>
+          <t>Jaqueline Cortes Ayala</t>
         </is>
       </c>
       <c r="E309" s="11" t="n">
@@ -13940,17 +13907,17 @@
       </c>
       <c r="B310" s="17" t="inlineStr">
         <is>
-          <t>38560</t>
+          <t>38513</t>
         </is>
       </c>
       <c r="C310" s="8" t="inlineStr">
         <is>
-          <t>Renato Leduc</t>
+          <t>San Lorenzo</t>
         </is>
       </c>
       <c r="D310" s="8" t="inlineStr">
         <is>
-          <t>Hazar Susim Trejo Hernandez</t>
+          <t>Luis Alberto Quevedo Rodriguez</t>
         </is>
       </c>
       <c r="E310" s="7" t="n">
@@ -13980,17 +13947,17 @@
       </c>
       <c r="B311" s="15" t="inlineStr">
         <is>
-          <t>38522</t>
+          <t>38502</t>
         </is>
       </c>
       <c r="C311" s="12" t="inlineStr">
         <is>
-          <t>Rio Hudson</t>
+          <t>San Marcos DT</t>
         </is>
       </c>
       <c r="D311" s="12" t="inlineStr">
         <is>
-          <t>Alberto Torrado Aguilar Cauz</t>
+          <t>Jesus Antonio Elguera Flores</t>
         </is>
       </c>
       <c r="E311" s="11" t="n">
@@ -14020,17 +13987,17 @@
       </c>
       <c r="B312" s="17" t="inlineStr">
         <is>
-          <t>38389</t>
+          <t>38122</t>
         </is>
       </c>
       <c r="C312" s="8" t="inlineStr">
         <is>
-          <t>Rio Marne</t>
+          <t>Santa Fe</t>
         </is>
       </c>
       <c r="D312" s="8" t="inlineStr">
         <is>
-          <t>Guadalupe Ibarra Martínez</t>
+          <t>Erika Julieta Contreras Aguilera</t>
         </is>
       </c>
       <c r="E312" s="7" t="n">
@@ -14060,17 +14027,17 @@
       </c>
       <c r="B313" s="15" t="inlineStr">
         <is>
-          <t>38557</t>
+          <t>38150</t>
         </is>
       </c>
       <c r="C313" s="12" t="inlineStr">
         <is>
-          <t>Rio San Joaquin</t>
+          <t>Santa Fe 2</t>
         </is>
       </c>
       <c r="D313" s="12" t="inlineStr">
         <is>
-          <t>Luis Manuel Neri Saldaña</t>
+          <t>Erika Julieta Contreras Aguilera</t>
         </is>
       </c>
       <c r="E313" s="11" t="n">
@@ -14100,17 +14067,17 @@
       </c>
       <c r="B314" s="17" t="inlineStr">
         <is>
-          <t>43070</t>
+          <t>38189</t>
         </is>
       </c>
       <c r="C314" s="8" t="inlineStr">
         <is>
-          <t>Rojo Gomez DT</t>
+          <t>Santa Fe Imax</t>
         </is>
       </c>
       <c r="D314" s="8" t="inlineStr">
         <is>
-          <t>Ariana Janet Gutierrez Martinez</t>
+          <t>Erika Julieta Contreras Aguilera</t>
         </is>
       </c>
       <c r="E314" s="7" t="n">
@@ -14140,17 +14107,17 @@
       </c>
       <c r="B315" s="15" t="inlineStr">
         <is>
-          <t>38558</t>
+          <t>38116</t>
         </is>
       </c>
       <c r="C315" s="12" t="inlineStr">
         <is>
-          <t>Roma Sur</t>
+          <t>Santa Teresa</t>
         </is>
       </c>
       <c r="D315" s="12" t="inlineStr">
         <is>
-          <t>Nora Caracas Saldaña</t>
+          <t>Cesar Alfonso Castillo Romero</t>
         </is>
       </c>
       <c r="E315" s="11" t="n">
@@ -14180,17 +14147,17 @@
       </c>
       <c r="B316" s="17" t="inlineStr">
         <is>
-          <t>38653</t>
+          <t>38659</t>
         </is>
       </c>
       <c r="C316" s="8" t="inlineStr">
         <is>
-          <t>Salon Ejecutivo T1 AICM</t>
+          <t>Sendero Ixtapaluca</t>
         </is>
       </c>
       <c r="D316" s="8" t="inlineStr">
         <is>
-          <t>Maria Anallely Sanchez Garcia</t>
+          <t>Jesus Antonio Elguera Flores</t>
         </is>
       </c>
       <c r="E316" s="7" t="n">
@@ -14220,17 +14187,17 @@
       </c>
       <c r="B317" s="15" t="inlineStr">
         <is>
-          <t>38390</t>
+          <t>38485</t>
         </is>
       </c>
       <c r="C317" s="12" t="inlineStr">
         <is>
-          <t>Samara I</t>
+          <t>Sendero Toluca</t>
         </is>
       </c>
       <c r="D317" s="12" t="inlineStr">
         <is>
-          <t>Jose De Jesus Magos Arzaluz</t>
+          <t>Daniel Flores Maldonado</t>
         </is>
       </c>
       <c r="E317" s="11" t="n">
@@ -14260,17 +14227,17 @@
       </c>
       <c r="B318" s="17" t="inlineStr">
         <is>
-          <t>38445</t>
+          <t>38764</t>
         </is>
       </c>
       <c r="C318" s="8" t="inlineStr">
         <is>
-          <t>Samara II</t>
+          <t>Star Medica Napoles</t>
         </is>
       </c>
       <c r="D318" s="8" t="inlineStr">
         <is>
-          <t>Jose De Jesus Magos Arzaluz</t>
+          <t>Juan Jesus Zuñiga Flores</t>
         </is>
       </c>
       <c r="E318" s="7" t="n">
@@ -14300,17 +14267,17 @@
       </c>
       <c r="B319" s="15" t="inlineStr">
         <is>
-          <t>38124</t>
+          <t>38752</t>
         </is>
       </c>
       <c r="C319" s="12" t="inlineStr">
         <is>
-          <t>San Jeronimo</t>
+          <t>Star Medica Roma</t>
         </is>
       </c>
       <c r="D319" s="12" t="inlineStr">
         <is>
-          <t>Cesar Alfonso Castillo Romero</t>
+          <t>Nora Caracas Saldaña</t>
         </is>
       </c>
       <c r="E319" s="11" t="n">
@@ -14340,17 +14307,17 @@
       </c>
       <c r="B320" s="17" t="inlineStr">
         <is>
-          <t>38417</t>
+          <t>38166</t>
         </is>
       </c>
       <c r="C320" s="8" t="inlineStr">
         <is>
-          <t>San Jose Insurgentes</t>
+          <t>Superama SantaFe</t>
         </is>
       </c>
       <c r="D320" s="8" t="inlineStr">
         <is>
-          <t>Jaqueline Cortes Ayala</t>
+          <t>Jose De Jesus Magos Arzaluz</t>
         </is>
       </c>
       <c r="E320" s="7" t="n">
@@ -14380,17 +14347,17 @@
       </c>
       <c r="B321" s="15" t="inlineStr">
         <is>
-          <t>38513</t>
+          <t>38299</t>
         </is>
       </c>
       <c r="C321" s="12" t="inlineStr">
         <is>
-          <t>San Lorenzo</t>
+          <t>T2 Llegadas</t>
         </is>
       </c>
       <c r="D321" s="12" t="inlineStr">
         <is>
-          <t>Luis Alberto Quevedo Rodriguez</t>
+          <t>Maria Anallely Sanchez Garcia</t>
         </is>
       </c>
       <c r="E321" s="11" t="n">
@@ -14420,17 +14387,17 @@
       </c>
       <c r="B322" s="17" t="inlineStr">
         <is>
-          <t>38502</t>
+          <t>38297</t>
         </is>
       </c>
       <c r="C322" s="8" t="inlineStr">
         <is>
-          <t>San Marcos DT</t>
+          <t>T2 Salida Internacional</t>
         </is>
       </c>
       <c r="D322" s="8" t="inlineStr">
         <is>
-          <t>Jesus Antonio Elguera Flores</t>
+          <t>Maria Anallely Sanchez Garcia</t>
         </is>
       </c>
       <c r="E322" s="7" t="n">
@@ -14460,17 +14427,17 @@
       </c>
       <c r="B323" s="15" t="inlineStr">
         <is>
-          <t>38122</t>
+          <t>38298</t>
         </is>
       </c>
       <c r="C323" s="12" t="inlineStr">
         <is>
-          <t>Santa Fe</t>
+          <t>T2 Salida Nacional</t>
         </is>
       </c>
       <c r="D323" s="12" t="inlineStr">
         <is>
-          <t>Erika Julieta Contreras Aguilera</t>
+          <t>Maria Anallely Sanchez Garcia</t>
         </is>
       </c>
       <c r="E323" s="11" t="n">
@@ -14500,17 +14467,17 @@
       </c>
       <c r="B324" s="17" t="inlineStr">
         <is>
-          <t>38150</t>
+          <t>38780</t>
         </is>
       </c>
       <c r="C324" s="8" t="inlineStr">
         <is>
-          <t>Santa Fe 2</t>
+          <t>Tec Santa Fe</t>
         </is>
       </c>
       <c r="D324" s="8" t="inlineStr">
         <is>
-          <t>Erika Julieta Contreras Aguilera</t>
+          <t>Jose De Jesus Magos Arzaluz</t>
         </is>
       </c>
       <c r="E324" s="7" t="n">
@@ -14540,17 +14507,17 @@
       </c>
       <c r="B325" s="15" t="inlineStr">
         <is>
-          <t>38189</t>
+          <t>38817</t>
         </is>
       </c>
       <c r="C325" s="12" t="inlineStr">
         <is>
-          <t>Santa Fe Imax</t>
+          <t>Tec de Monterrey CCM</t>
         </is>
       </c>
       <c r="D325" s="12" t="inlineStr">
         <is>
-          <t>Erika Julieta Contreras Aguilera</t>
+          <t>Fernando Eduardo Verdugo Saldaña</t>
         </is>
       </c>
       <c r="E325" s="11" t="n">
@@ -14580,17 +14547,17 @@
       </c>
       <c r="B326" s="17" t="inlineStr">
         <is>
-          <t>38116</t>
+          <t>38319</t>
         </is>
       </c>
       <c r="C326" s="8" t="inlineStr">
         <is>
-          <t>Santa Teresa</t>
+          <t>Tecnologico Metepec</t>
         </is>
       </c>
       <c r="D326" s="8" t="inlineStr">
         <is>
-          <t>Cesar Alfonso Castillo Romero</t>
+          <t>Daniel Flores Maldonado</t>
         </is>
       </c>
       <c r="E326" s="7" t="n">
@@ -14620,17 +14587,17 @@
       </c>
       <c r="B327" s="15" t="inlineStr">
         <is>
-          <t>38659</t>
+          <t>38131</t>
         </is>
       </c>
       <c r="C327" s="12" t="inlineStr">
         <is>
-          <t>Sendero Ixtapaluca</t>
+          <t>Tepepan</t>
         </is>
       </c>
       <c r="D327" s="12" t="inlineStr">
         <is>
-          <t>Jesus Antonio Elguera Flores</t>
+          <t>Hazar Susim Trejo Hernandez</t>
         </is>
       </c>
       <c r="E327" s="11" t="n">
@@ -14660,17 +14627,17 @@
       </c>
       <c r="B328" s="17" t="inlineStr">
         <is>
-          <t>38485</t>
+          <t>38943</t>
         </is>
       </c>
       <c r="C328" s="8" t="inlineStr">
         <is>
-          <t>Sendero Toluca</t>
+          <t>Terraza T2 Amb</t>
         </is>
       </c>
       <c r="D328" s="8" t="inlineStr">
         <is>
-          <t>Daniel Flores Maldonado</t>
+          <t>Maria Anallely Sanchez Garcia</t>
         </is>
       </c>
       <c r="E328" s="7" t="n">
@@ -14700,17 +14667,17 @@
       </c>
       <c r="B329" s="15" t="inlineStr">
         <is>
-          <t>38764</t>
+          <t>38289</t>
         </is>
       </c>
       <c r="C329" s="12" t="inlineStr">
         <is>
-          <t>Star Medica Napoles</t>
+          <t>Tezontle l</t>
         </is>
       </c>
       <c r="D329" s="12" t="inlineStr">
         <is>
-          <t>Juan Jesus Zuñiga Flores</t>
+          <t>Ariana Janet Gutierrez Martinez</t>
         </is>
       </c>
       <c r="E329" s="11" t="n">
@@ -14740,17 +14707,17 @@
       </c>
       <c r="B330" s="17" t="inlineStr">
         <is>
-          <t>38752</t>
+          <t>38279</t>
         </is>
       </c>
       <c r="C330" s="8" t="inlineStr">
         <is>
-          <t>Star Medica Roma</t>
+          <t>Tezontle ll</t>
         </is>
       </c>
       <c r="D330" s="8" t="inlineStr">
         <is>
-          <t>Nora Caracas Saldaña</t>
+          <t>Ariana Janet Gutierrez Martinez</t>
         </is>
       </c>
       <c r="E330" s="7" t="n">
@@ -14780,17 +14747,17 @@
       </c>
       <c r="B331" s="15" t="inlineStr">
         <is>
-          <t>38166</t>
+          <t>38625</t>
         </is>
       </c>
       <c r="C331" s="12" t="inlineStr">
         <is>
-          <t>Superama SantaFe</t>
+          <t>Tezoquipa</t>
         </is>
       </c>
       <c r="D331" s="12" t="inlineStr">
         <is>
-          <t>Jose De Jesus Magos Arzaluz</t>
+          <t>Hazar Susim Trejo Hernandez</t>
         </is>
       </c>
       <c r="E331" s="11" t="n">
@@ -14820,17 +14787,17 @@
       </c>
       <c r="B332" s="17" t="inlineStr">
         <is>
-          <t>38652</t>
+          <t>38260</t>
         </is>
       </c>
       <c r="C332" s="8" t="inlineStr">
         <is>
-          <t>T1 S21</t>
+          <t>Tlacoquemecatl</t>
         </is>
       </c>
       <c r="D332" s="8" t="inlineStr">
         <is>
-          <t>Maria Anallely Sanchez Garcia</t>
+          <t>Luis Alberto Quevedo Rodriguez</t>
         </is>
       </c>
       <c r="E332" s="7" t="n">
@@ -14860,17 +14827,17 @@
       </c>
       <c r="B333" s="15" t="inlineStr">
         <is>
-          <t>38299</t>
+          <t>38543</t>
         </is>
       </c>
       <c r="C333" s="12" t="inlineStr">
         <is>
-          <t>T2 Llegadas</t>
+          <t>Tlalpan Hospitales</t>
         </is>
       </c>
       <c r="D333" s="12" t="inlineStr">
         <is>
-          <t>Maria Anallely Sanchez Garcia</t>
+          <t>Hazar Susim Trejo Hernandez</t>
         </is>
       </c>
       <c r="E333" s="11" t="n">
@@ -14900,17 +14867,17 @@
       </c>
       <c r="B334" s="17" t="inlineStr">
         <is>
-          <t>38168</t>
+          <t>38637</t>
         </is>
       </c>
       <c r="C334" s="8" t="inlineStr">
         <is>
-          <t>T2 Planta Alta</t>
+          <t>Tlalpan Nativitas</t>
         </is>
       </c>
       <c r="D334" s="8" t="inlineStr">
         <is>
-          <t>Maria Anallely Sanchez Garcia</t>
+          <t>Fernando Eduardo Verdugo Saldaña</t>
         </is>
       </c>
       <c r="E334" s="7" t="n">
@@ -14940,17 +14907,17 @@
       </c>
       <c r="B335" s="15" t="inlineStr">
         <is>
-          <t>38297</t>
+          <t>38233</t>
         </is>
       </c>
       <c r="C335" s="12" t="inlineStr">
         <is>
-          <t>T2 Salida Internacional</t>
+          <t>Toluca Colon</t>
         </is>
       </c>
       <c r="D335" s="12" t="inlineStr">
         <is>
-          <t>Maria Anallely Sanchez Garcia</t>
+          <t>Andrea Nava Guzman</t>
         </is>
       </c>
       <c r="E335" s="11" t="n">
@@ -14980,17 +14947,17 @@
       </c>
       <c r="B336" s="17" t="inlineStr">
         <is>
-          <t>38298</t>
+          <t>38600</t>
         </is>
       </c>
       <c r="C336" s="8" t="inlineStr">
         <is>
-          <t>T2 Salida Nacional</t>
+          <t>Torre BBVA</t>
         </is>
       </c>
       <c r="D336" s="8" t="inlineStr">
         <is>
-          <t>Maria Anallely Sanchez Garcia</t>
+          <t>Luis Manuel Neri Saldaña</t>
         </is>
       </c>
       <c r="E336" s="7" t="n">
@@ -15020,17 +14987,17 @@
       </c>
       <c r="B337" s="15" t="inlineStr">
         <is>
-          <t>38780</t>
+          <t>38376</t>
         </is>
       </c>
       <c r="C337" s="12" t="inlineStr">
         <is>
-          <t>Tec Santa Fe</t>
+          <t>Torre Caballito</t>
         </is>
       </c>
       <c r="D337" s="12" t="inlineStr">
         <is>
-          <t>Jose De Jesus Magos Arzaluz</t>
+          <t>Vacante</t>
         </is>
       </c>
       <c r="E337" s="11" t="n">
@@ -15060,17 +15027,17 @@
       </c>
       <c r="B338" s="17" t="inlineStr">
         <is>
-          <t>38817</t>
+          <t>38681</t>
         </is>
       </c>
       <c r="C338" s="8" t="inlineStr">
         <is>
-          <t>Tec de Monterrey CCM</t>
+          <t>Torre Diana</t>
         </is>
       </c>
       <c r="D338" s="8" t="inlineStr">
         <is>
-          <t>Fernando Eduardo Verdugo Saldaña</t>
+          <t>Guadalupe Ibarra Martínez</t>
         </is>
       </c>
       <c r="E338" s="7" t="n">
@@ -15100,17 +15067,17 @@
       </c>
       <c r="B339" s="15" t="inlineStr">
         <is>
-          <t>38319</t>
+          <t>38349</t>
         </is>
       </c>
       <c r="C339" s="12" t="inlineStr">
         <is>
-          <t>Tecnologico Metepec</t>
+          <t>Torre Inverlat</t>
         </is>
       </c>
       <c r="D339" s="12" t="inlineStr">
         <is>
-          <t>Daniel Flores Maldonado</t>
+          <t>Luis Manuel Neri Saldaña</t>
         </is>
       </c>
       <c r="E339" s="11" t="n">
@@ -15140,17 +15107,17 @@
       </c>
       <c r="B340" s="17" t="inlineStr">
         <is>
-          <t>38131</t>
+          <t>38110</t>
         </is>
       </c>
       <c r="C340" s="8" t="inlineStr">
         <is>
-          <t>Tepepan</t>
+          <t>Torre Mayor</t>
         </is>
       </c>
       <c r="D340" s="8" t="inlineStr">
         <is>
-          <t>Hazar Susim Trejo Hernandez</t>
+          <t>Alberto Torrado Aguilar Cauz</t>
         </is>
       </c>
       <c r="E340" s="7" t="n">
@@ -15180,17 +15147,17 @@
       </c>
       <c r="B341" s="15" t="inlineStr">
         <is>
-          <t>38943</t>
+          <t>38378</t>
         </is>
       </c>
       <c r="C341" s="12" t="inlineStr">
         <is>
-          <t>Terraza T2 Amb</t>
+          <t>Torre Mexicana</t>
         </is>
       </c>
       <c r="D341" s="12" t="inlineStr">
         <is>
-          <t>Maria Anallely Sanchez Garcia</t>
+          <t>Nora Caracas Saldaña</t>
         </is>
       </c>
       <c r="E341" s="11" t="n">
@@ -15220,17 +15187,17 @@
       </c>
       <c r="B342" s="17" t="inlineStr">
         <is>
-          <t>38289</t>
+          <t>38541</t>
         </is>
       </c>
       <c r="C342" s="8" t="inlineStr">
         <is>
-          <t>Tezontle l</t>
+          <t>Torre Polanco</t>
         </is>
       </c>
       <c r="D342" s="8" t="inlineStr">
         <is>
-          <t>Ariana Janet Gutierrez Martinez</t>
+          <t>Alberto Torrado Aguilar Cauz</t>
         </is>
       </c>
       <c r="E342" s="7" t="n">
@@ -15260,17 +15227,17 @@
       </c>
       <c r="B343" s="15" t="inlineStr">
         <is>
-          <t>38279</t>
+          <t>38644</t>
         </is>
       </c>
       <c r="C343" s="12" t="inlineStr">
         <is>
-          <t>Tezontle ll</t>
+          <t>Torre Virreyes</t>
         </is>
       </c>
       <c r="D343" s="12" t="inlineStr">
         <is>
-          <t>Ariana Janet Gutierrez Martinez</t>
+          <t>Manuel Alejandro Avila Molina</t>
         </is>
       </c>
       <c r="E343" s="11" t="n">
@@ -15300,17 +15267,17 @@
       </c>
       <c r="B344" s="17" t="inlineStr">
         <is>
-          <t>38625</t>
+          <t>38423</t>
         </is>
       </c>
       <c r="C344" s="8" t="inlineStr">
         <is>
-          <t>Tezoquipa</t>
+          <t>Torre Wtc</t>
         </is>
       </c>
       <c r="D344" s="8" t="inlineStr">
         <is>
-          <t>Hazar Susim Trejo Hernandez</t>
+          <t>Nora Caracas Saldaña</t>
         </is>
       </c>
       <c r="E344" s="7" t="n">
@@ -15340,17 +15307,17 @@
       </c>
       <c r="B345" s="15" t="inlineStr">
         <is>
-          <t>38260</t>
+          <t>38751</t>
         </is>
       </c>
       <c r="C345" s="12" t="inlineStr">
         <is>
-          <t>Tlacoquemecatl</t>
+          <t>Torre Zentrrum II</t>
         </is>
       </c>
       <c r="D345" s="12" t="inlineStr">
         <is>
-          <t>Luis Alberto Quevedo Rodriguez</t>
+          <t>Jose De Jesus Magos Arzaluz</t>
         </is>
       </c>
       <c r="E345" s="11" t="n">
@@ -15380,17 +15347,17 @@
       </c>
       <c r="B346" s="17" t="inlineStr">
         <is>
-          <t>38543</t>
+          <t>38858</t>
         </is>
       </c>
       <c r="C346" s="8" t="inlineStr">
         <is>
-          <t>Tlalpan Hospitales</t>
+          <t>Torre de Pemex</t>
         </is>
       </c>
       <c r="D346" s="8" t="inlineStr">
         <is>
-          <t>Hazar Susim Trejo Hernandez</t>
+          <t>Maria Anallely Sanchez Garcia</t>
         </is>
       </c>
       <c r="E346" s="7" t="n">
@@ -15420,17 +15387,17 @@
       </c>
       <c r="B347" s="15" t="inlineStr">
         <is>
-          <t>38637</t>
+          <t>38841</t>
         </is>
       </c>
       <c r="C347" s="12" t="inlineStr">
         <is>
-          <t>Tlalpan Nativitas</t>
+          <t>Townsquare Metepec</t>
         </is>
       </c>
       <c r="D347" s="12" t="inlineStr">
         <is>
-          <t>Fernando Eduardo Verdugo Saldaña</t>
+          <t>Daniel Flores Maldonado</t>
         </is>
       </c>
       <c r="E347" s="11" t="n">
@@ -15460,17 +15427,17 @@
       </c>
       <c r="B348" s="17" t="inlineStr">
         <is>
-          <t>38233</t>
+          <t>38556</t>
         </is>
       </c>
       <c r="C348" s="8" t="inlineStr">
         <is>
-          <t>Toluca Colon</t>
+          <t>Tuxpan 53</t>
         </is>
       </c>
       <c r="D348" s="8" t="inlineStr">
         <is>
-          <t>Andrea Nava Guzman</t>
+          <t>Nora Caracas Saldaña</t>
         </is>
       </c>
       <c r="E348" s="7" t="n">
@@ -15500,17 +15467,17 @@
       </c>
       <c r="B349" s="15" t="inlineStr">
         <is>
-          <t>38600</t>
+          <t>38570</t>
         </is>
       </c>
       <c r="C349" s="12" t="inlineStr">
         <is>
-          <t>Torre BBVA</t>
+          <t>Universidad 767</t>
         </is>
       </c>
       <c r="D349" s="12" t="inlineStr">
         <is>
-          <t>Luis Manuel Neri Saldaña</t>
+          <t>Luis Alberto Quevedo Rodriguez</t>
         </is>
       </c>
       <c r="E349" s="11" t="n">
@@ -15540,17 +15507,17 @@
       </c>
       <c r="B350" s="17" t="inlineStr">
         <is>
-          <t>38376</t>
+          <t>38954</t>
         </is>
       </c>
       <c r="C350" s="8" t="inlineStr">
         <is>
-          <t>Torre Caballito</t>
+          <t>Universidad Anahuac Campus Sur</t>
         </is>
       </c>
       <c r="D350" s="8" t="inlineStr">
         <is>
-          <t>Vacante</t>
+          <t>Adriana Alejandra Tanus Buhler</t>
         </is>
       </c>
       <c r="E350" s="7" t="n">
@@ -15580,17 +15547,17 @@
       </c>
       <c r="B351" s="15" t="inlineStr">
         <is>
-          <t>38455</t>
+          <t>38179</t>
         </is>
       </c>
       <c r="C351" s="12" t="inlineStr">
         <is>
-          <t>Torre Diamante</t>
+          <t>Universidad Anáhuac</t>
         </is>
       </c>
       <c r="D351" s="12" t="inlineStr">
         <is>
-          <t>DM pendiente</t>
+          <t>Areli Anahi Lazcano Lezama</t>
         </is>
       </c>
       <c r="E351" s="11" t="n">
@@ -15620,17 +15587,17 @@
       </c>
       <c r="B352" s="17" t="inlineStr">
         <is>
-          <t>38681</t>
+          <t>38951</t>
         </is>
       </c>
       <c r="C352" s="8" t="inlineStr">
         <is>
-          <t>Torre Diana</t>
+          <t>Universidad Panamericana</t>
         </is>
       </c>
       <c r="D352" s="8" t="inlineStr">
         <is>
-          <t>Guadalupe Ibarra Martínez</t>
+          <t>Juan Jesus Zuñiga Flores</t>
         </is>
       </c>
       <c r="E352" s="7" t="n">
@@ -15660,17 +15627,17 @@
       </c>
       <c r="B353" s="15" t="inlineStr">
         <is>
-          <t>38349</t>
+          <t>38463</t>
         </is>
       </c>
       <c r="C353" s="12" t="inlineStr">
         <is>
-          <t>Torre Inverlat</t>
+          <t>Uruguay</t>
         </is>
       </c>
       <c r="D353" s="12" t="inlineStr">
         <is>
-          <t>Luis Manuel Neri Saldaña</t>
+          <t>Vacante</t>
         </is>
       </c>
       <c r="E353" s="11" t="n">
@@ -15700,17 +15667,17 @@
       </c>
       <c r="B354" s="17" t="inlineStr">
         <is>
-          <t>38110</t>
+          <t>38996</t>
         </is>
       </c>
       <c r="C354" s="8" t="inlineStr">
         <is>
-          <t>Torre Mayor</t>
+          <t>Valle de Aragon</t>
         </is>
       </c>
       <c r="D354" s="8" t="inlineStr">
         <is>
-          <t>Alberto Torrado Aguilar Cauz</t>
+          <t>Monica Selene Morales Ibarra</t>
         </is>
       </c>
       <c r="E354" s="7" t="n">
@@ -15740,17 +15707,17 @@
       </c>
       <c r="B355" s="15" t="inlineStr">
         <is>
-          <t>38378</t>
+          <t>38404</t>
         </is>
       </c>
       <c r="C355" s="12" t="inlineStr">
         <is>
-          <t>Torre Mexicana</t>
+          <t>Varsovia</t>
         </is>
       </c>
       <c r="D355" s="12" t="inlineStr">
         <is>
-          <t>Nora Caracas Saldaña</t>
+          <t>Guadalupe Ibarra Martínez</t>
         </is>
       </c>
       <c r="E355" s="11" t="n">
@@ -15780,17 +15747,17 @@
       </c>
       <c r="B356" s="17" t="inlineStr">
         <is>
-          <t>38541</t>
+          <t>38785</t>
         </is>
       </c>
       <c r="C356" s="8" t="inlineStr">
         <is>
-          <t>Torre Polanco</t>
+          <t>Versalles</t>
         </is>
       </c>
       <c r="D356" s="8" t="inlineStr">
         <is>
-          <t>Alberto Torrado Aguilar Cauz</t>
+          <t>Vacante</t>
         </is>
       </c>
       <c r="E356" s="7" t="n">
@@ -15820,17 +15787,17 @@
       </c>
       <c r="B357" s="15" t="inlineStr">
         <is>
-          <t>38644</t>
+          <t>38379</t>
         </is>
       </c>
       <c r="C357" s="12" t="inlineStr">
         <is>
-          <t>Torre Virreyes</t>
+          <t>Via Acoxpa</t>
         </is>
       </c>
       <c r="D357" s="12" t="inlineStr">
         <is>
-          <t>Manuel Alejandro Avila Molina</t>
+          <t>Fernando Eduardo Verdugo Saldaña</t>
         </is>
       </c>
       <c r="E357" s="11" t="n">
@@ -15860,17 +15827,17 @@
       </c>
       <c r="B358" s="17" t="inlineStr">
         <is>
-          <t>38423</t>
+          <t>38226</t>
         </is>
       </c>
       <c r="C358" s="8" t="inlineStr">
         <is>
-          <t>Torre Wtc</t>
+          <t>Via kiosko 515</t>
         </is>
       </c>
       <c r="D358" s="8" t="inlineStr">
         <is>
-          <t>Nora Caracas Saldaña</t>
+          <t>Ariana Janet Gutierrez Martinez</t>
         </is>
       </c>
       <c r="E358" s="7" t="n">
@@ -15900,17 +15867,17 @@
       </c>
       <c r="B359" s="15" t="inlineStr">
         <is>
-          <t>38751</t>
+          <t>38109</t>
         </is>
       </c>
       <c r="C359" s="12" t="inlineStr">
         <is>
-          <t>Torre Zentrrum II</t>
+          <t>Wtc</t>
         </is>
       </c>
       <c r="D359" s="12" t="inlineStr">
         <is>
-          <t>Jose De Jesus Magos Arzaluz</t>
+          <t>Nora Caracas Saldaña</t>
         </is>
       </c>
       <c r="E359" s="11" t="n">
@@ -15940,17 +15907,17 @@
       </c>
       <c r="B360" s="17" t="inlineStr">
         <is>
-          <t>38858</t>
+          <t>38477</t>
         </is>
       </c>
       <c r="C360" s="8" t="inlineStr">
         <is>
-          <t>Torre de Pemex</t>
+          <t>Zentralia churubusco</t>
         </is>
       </c>
       <c r="D360" s="8" t="inlineStr">
         <is>
-          <t>Maria Anallely Sanchez Garcia</t>
+          <t>Ariana Janet Gutierrez Martinez</t>
         </is>
       </c>
       <c r="E360" s="7" t="n">
@@ -15980,17 +15947,17 @@
       </c>
       <c r="B361" s="15" t="inlineStr">
         <is>
-          <t>38841</t>
+          <t>38439</t>
         </is>
       </c>
       <c r="C361" s="12" t="inlineStr">
         <is>
-          <t>Townsquare Metepec</t>
+          <t>Ángeles Interlomas</t>
         </is>
       </c>
       <c r="D361" s="12" t="inlineStr">
         <is>
-          <t>Daniel Flores Maldonado</t>
+          <t>Areli Anahi Lazcano Lezama</t>
         </is>
       </c>
       <c r="E361" s="11" t="n">
@@ -16014,613 +15981,13 @@
         </is>
       </c>
     </row>
-    <row r="362" ht="21" customHeight="1">
-      <c r="A362" s="7" t="n">
-        <v>358</v>
-      </c>
-      <c r="B362" s="17" t="inlineStr">
-        <is>
-          <t>38556</t>
-        </is>
-      </c>
-      <c r="C362" s="8" t="inlineStr">
-        <is>
-          <t>Tuxpan 53</t>
-        </is>
-      </c>
-      <c r="D362" s="8" t="inlineStr">
-        <is>
-          <t>Nora Caracas Saldaña</t>
-        </is>
-      </c>
-      <c r="E362" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F362" s="7" t="n">
-        <v>11</v>
-      </c>
-      <c r="G362" s="9">
-        <f>IFERROR(E362/(E362+F362),0)</f>
-        <v/>
-      </c>
-      <c r="H362" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I362" s="14" t="inlineStr">
-        <is>
-          <t>Priorizar hoy</t>
-        </is>
-      </c>
-    </row>
-    <row r="363" ht="21" customHeight="1">
-      <c r="A363" s="11" t="n">
-        <v>359</v>
-      </c>
-      <c r="B363" s="15" t="inlineStr">
-        <is>
-          <t>38570</t>
-        </is>
-      </c>
-      <c r="C363" s="12" t="inlineStr">
-        <is>
-          <t>Universidad 767</t>
-        </is>
-      </c>
-      <c r="D363" s="12" t="inlineStr">
-        <is>
-          <t>Luis Alberto Quevedo Rodriguez</t>
-        </is>
-      </c>
-      <c r="E363" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F363" s="11" t="n">
-        <v>11</v>
-      </c>
-      <c r="G363" s="13">
-        <f>IFERROR(E363/(E363+F363),0)</f>
-        <v/>
-      </c>
-      <c r="H363" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I363" s="14" t="inlineStr">
-        <is>
-          <t>Priorizar hoy</t>
-        </is>
-      </c>
-    </row>
-    <row r="364" ht="21" customHeight="1">
-      <c r="A364" s="7" t="n">
-        <v>360</v>
-      </c>
-      <c r="B364" s="17" t="inlineStr">
-        <is>
-          <t>38954</t>
-        </is>
-      </c>
-      <c r="C364" s="8" t="inlineStr">
-        <is>
-          <t>Universidad Anahuac Campus Sur</t>
-        </is>
-      </c>
-      <c r="D364" s="8" t="inlineStr">
-        <is>
-          <t>Adriana Alejandra Tanus Buhler</t>
-        </is>
-      </c>
-      <c r="E364" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F364" s="7" t="n">
-        <v>11</v>
-      </c>
-      <c r="G364" s="9">
-        <f>IFERROR(E364/(E364+F364),0)</f>
-        <v/>
-      </c>
-      <c r="H364" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I364" s="14" t="inlineStr">
-        <is>
-          <t>Priorizar hoy</t>
-        </is>
-      </c>
-    </row>
-    <row r="365" ht="21" customHeight="1">
-      <c r="A365" s="11" t="n">
-        <v>361</v>
-      </c>
-      <c r="B365" s="15" t="inlineStr">
-        <is>
-          <t>38179</t>
-        </is>
-      </c>
-      <c r="C365" s="12" t="inlineStr">
-        <is>
-          <t>Universidad Anáhuac</t>
-        </is>
-      </c>
-      <c r="D365" s="12" t="inlineStr">
-        <is>
-          <t>Areli Anahi Lazcano Lezama</t>
-        </is>
-      </c>
-      <c r="E365" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F365" s="11" t="n">
-        <v>11</v>
-      </c>
-      <c r="G365" s="13">
-        <f>IFERROR(E365/(E365+F365),0)</f>
-        <v/>
-      </c>
-      <c r="H365" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I365" s="14" t="inlineStr">
-        <is>
-          <t>Priorizar hoy</t>
-        </is>
-      </c>
-    </row>
-    <row r="366" ht="21" customHeight="1">
-      <c r="A366" s="7" t="n">
-        <v>362</v>
-      </c>
-      <c r="B366" s="17" t="inlineStr">
-        <is>
-          <t>38951</t>
-        </is>
-      </c>
-      <c r="C366" s="8" t="inlineStr">
-        <is>
-          <t>Universidad Panamericana</t>
-        </is>
-      </c>
-      <c r="D366" s="8" t="inlineStr">
-        <is>
-          <t>Juan Jesus Zuñiga Flores</t>
-        </is>
-      </c>
-      <c r="E366" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F366" s="7" t="n">
-        <v>11</v>
-      </c>
-      <c r="G366" s="9">
-        <f>IFERROR(E366/(E366+F366),0)</f>
-        <v/>
-      </c>
-      <c r="H366" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I366" s="14" t="inlineStr">
-        <is>
-          <t>Priorizar hoy</t>
-        </is>
-      </c>
-    </row>
-    <row r="367" ht="21" customHeight="1">
-      <c r="A367" s="11" t="n">
-        <v>363</v>
-      </c>
-      <c r="B367" s="15" t="inlineStr">
-        <is>
-          <t>38463</t>
-        </is>
-      </c>
-      <c r="C367" s="12" t="inlineStr">
-        <is>
-          <t>Uruguay</t>
-        </is>
-      </c>
-      <c r="D367" s="12" t="inlineStr">
-        <is>
-          <t>Vacante</t>
-        </is>
-      </c>
-      <c r="E367" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F367" s="11" t="n">
-        <v>11</v>
-      </c>
-      <c r="G367" s="13">
-        <f>IFERROR(E367/(E367+F367),0)</f>
-        <v/>
-      </c>
-      <c r="H367" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I367" s="14" t="inlineStr">
-        <is>
-          <t>Priorizar hoy</t>
-        </is>
-      </c>
-    </row>
-    <row r="368" ht="21" customHeight="1">
-      <c r="A368" s="7" t="n">
-        <v>364</v>
-      </c>
-      <c r="B368" s="17" t="inlineStr">
-        <is>
-          <t>38996</t>
-        </is>
-      </c>
-      <c r="C368" s="8" t="inlineStr">
-        <is>
-          <t>Valle de Aragon</t>
-        </is>
-      </c>
-      <c r="D368" s="8" t="inlineStr">
-        <is>
-          <t>Monica Selene Morales Ibarra</t>
-        </is>
-      </c>
-      <c r="E368" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F368" s="7" t="n">
-        <v>11</v>
-      </c>
-      <c r="G368" s="9">
-        <f>IFERROR(E368/(E368+F368),0)</f>
-        <v/>
-      </c>
-      <c r="H368" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I368" s="14" t="inlineStr">
-        <is>
-          <t>Priorizar hoy</t>
-        </is>
-      </c>
-    </row>
-    <row r="369" ht="21" customHeight="1">
-      <c r="A369" s="11" t="n">
-        <v>365</v>
-      </c>
-      <c r="B369" s="15" t="inlineStr">
-        <is>
-          <t>38404</t>
-        </is>
-      </c>
-      <c r="C369" s="12" t="inlineStr">
-        <is>
-          <t>Varsovia</t>
-        </is>
-      </c>
-      <c r="D369" s="12" t="inlineStr">
-        <is>
-          <t>Guadalupe Ibarra Martínez</t>
-        </is>
-      </c>
-      <c r="E369" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F369" s="11" t="n">
-        <v>11</v>
-      </c>
-      <c r="G369" s="13">
-        <f>IFERROR(E369/(E369+F369),0)</f>
-        <v/>
-      </c>
-      <c r="H369" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I369" s="14" t="inlineStr">
-        <is>
-          <t>Priorizar hoy</t>
-        </is>
-      </c>
-    </row>
-    <row r="370" ht="21" customHeight="1">
-      <c r="A370" s="7" t="n">
-        <v>366</v>
-      </c>
-      <c r="B370" s="17" t="inlineStr">
-        <is>
-          <t>38785</t>
-        </is>
-      </c>
-      <c r="C370" s="8" t="inlineStr">
-        <is>
-          <t>Versalles</t>
-        </is>
-      </c>
-      <c r="D370" s="8" t="inlineStr">
-        <is>
-          <t>Vacante</t>
-        </is>
-      </c>
-      <c r="E370" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F370" s="7" t="n">
-        <v>11</v>
-      </c>
-      <c r="G370" s="9">
-        <f>IFERROR(E370/(E370+F370),0)</f>
-        <v/>
-      </c>
-      <c r="H370" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I370" s="14" t="inlineStr">
-        <is>
-          <t>Priorizar hoy</t>
-        </is>
-      </c>
-    </row>
-    <row r="371" ht="21" customHeight="1">
-      <c r="A371" s="11" t="n">
-        <v>367</v>
-      </c>
-      <c r="B371" s="15" t="inlineStr">
-        <is>
-          <t>38379</t>
-        </is>
-      </c>
-      <c r="C371" s="12" t="inlineStr">
-        <is>
-          <t>Via Acoxpa</t>
-        </is>
-      </c>
-      <c r="D371" s="12" t="inlineStr">
-        <is>
-          <t>Fernando Eduardo Verdugo Saldaña</t>
-        </is>
-      </c>
-      <c r="E371" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F371" s="11" t="n">
-        <v>11</v>
-      </c>
-      <c r="G371" s="13">
-        <f>IFERROR(E371/(E371+F371),0)</f>
-        <v/>
-      </c>
-      <c r="H371" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I371" s="14" t="inlineStr">
-        <is>
-          <t>Priorizar hoy</t>
-        </is>
-      </c>
-    </row>
-    <row r="372" ht="21" customHeight="1">
-      <c r="A372" s="7" t="n">
-        <v>368</v>
-      </c>
-      <c r="B372" s="17" t="inlineStr">
-        <is>
-          <t>38226</t>
-        </is>
-      </c>
-      <c r="C372" s="8" t="inlineStr">
-        <is>
-          <t>Via kiosko 515</t>
-        </is>
-      </c>
-      <c r="D372" s="8" t="inlineStr">
-        <is>
-          <t>Ariana Janet Gutierrez Martinez</t>
-        </is>
-      </c>
-      <c r="E372" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F372" s="7" t="n">
-        <v>11</v>
-      </c>
-      <c r="G372" s="9">
-        <f>IFERROR(E372/(E372+F372),0)</f>
-        <v/>
-      </c>
-      <c r="H372" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I372" s="14" t="inlineStr">
-        <is>
-          <t>Priorizar hoy</t>
-        </is>
-      </c>
-    </row>
-    <row r="373" ht="21" customHeight="1">
-      <c r="A373" s="11" t="n">
-        <v>369</v>
-      </c>
-      <c r="B373" s="15" t="inlineStr">
-        <is>
-          <t>38109</t>
-        </is>
-      </c>
-      <c r="C373" s="12" t="inlineStr">
-        <is>
-          <t>Wtc</t>
-        </is>
-      </c>
-      <c r="D373" s="12" t="inlineStr">
-        <is>
-          <t>Nora Caracas Saldaña</t>
-        </is>
-      </c>
-      <c r="E373" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F373" s="11" t="n">
-        <v>11</v>
-      </c>
-      <c r="G373" s="13">
-        <f>IFERROR(E373/(E373+F373),0)</f>
-        <v/>
-      </c>
-      <c r="H373" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I373" s="14" t="inlineStr">
-        <is>
-          <t>Priorizar hoy</t>
-        </is>
-      </c>
-    </row>
-    <row r="374" ht="21" customHeight="1">
-      <c r="A374" s="7" t="n">
-        <v>370</v>
-      </c>
-      <c r="B374" s="17" t="inlineStr">
-        <is>
-          <t>38613</t>
-        </is>
-      </c>
-      <c r="C374" s="8" t="inlineStr">
-        <is>
-          <t>Xola</t>
-        </is>
-      </c>
-      <c r="D374" s="8" t="inlineStr">
-        <is>
-          <t>Guadalupe Ibarra Martínez</t>
-        </is>
-      </c>
-      <c r="E374" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F374" s="7" t="n">
-        <v>11</v>
-      </c>
-      <c r="G374" s="9">
-        <f>IFERROR(E374/(E374+F374),0)</f>
-        <v/>
-      </c>
-      <c r="H374" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I374" s="14" t="inlineStr">
-        <is>
-          <t>Priorizar hoy</t>
-        </is>
-      </c>
-    </row>
-    <row r="375" ht="21" customHeight="1">
-      <c r="A375" s="11" t="n">
-        <v>371</v>
-      </c>
-      <c r="B375" s="15" t="inlineStr">
-        <is>
-          <t>38477</t>
-        </is>
-      </c>
-      <c r="C375" s="12" t="inlineStr">
-        <is>
-          <t>Zentralia churubusco</t>
-        </is>
-      </c>
-      <c r="D375" s="12" t="inlineStr">
-        <is>
-          <t>Ariana Janet Gutierrez Martinez</t>
-        </is>
-      </c>
-      <c r="E375" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F375" s="11" t="n">
-        <v>11</v>
-      </c>
-      <c r="G375" s="13">
-        <f>IFERROR(E375/(E375+F375),0)</f>
-        <v/>
-      </c>
-      <c r="H375" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I375" s="14" t="inlineStr">
-        <is>
-          <t>Priorizar hoy</t>
-        </is>
-      </c>
-    </row>
-    <row r="376" ht="21" customHeight="1">
-      <c r="A376" s="7" t="n">
-        <v>372</v>
-      </c>
-      <c r="B376" s="17" t="inlineStr">
-        <is>
-          <t>38439</t>
-        </is>
-      </c>
-      <c r="C376" s="8" t="inlineStr">
-        <is>
-          <t>Ángeles Interlomas</t>
-        </is>
-      </c>
-      <c r="D376" s="8" t="inlineStr">
-        <is>
-          <t>Areli Anahi Lazcano Lezama</t>
-        </is>
-      </c>
-      <c r="E376" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F376" s="7" t="n">
-        <v>11</v>
-      </c>
-      <c r="G376" s="9">
-        <f>IFERROR(E376/(E376+F376),0)</f>
-        <v/>
-      </c>
-      <c r="H376" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I376" s="14" t="inlineStr">
-        <is>
-          <t>Priorizar hoy</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A4:I376"/>
+  <autoFilter ref="A4:I361"/>
   <mergeCells count="2">
     <mergeCell ref="A1:I2"/>
     <mergeCell ref="A3:I3"/>
   </mergeCells>
-  <conditionalFormatting sqref="G5:G376">
+  <conditionalFormatting sqref="G5:G361">
     <cfRule type="dataBar" priority="1">
       <dataBar showValue="1">
         <cfvo type="num" val="0"/>
@@ -16665,7 +16032,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Todas las regiones · Corte 03/09/2026 13:49</t>
+          <t>Todas las regiones · Corte 03/09/2026 13:44</t>
         </is>
       </c>
     </row>
@@ -16721,10 +16088,10 @@
         </is>
       </c>
       <c r="C5" s="11" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>337</v>
+        <v>323</v>
       </c>
       <c r="E5" s="13">
         <f>IFERROR(C5/(C5+D5),0)</f>
@@ -16756,10 +16123,10 @@
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D6" s="7" t="n">
-        <v>301</v>
+        <v>287</v>
       </c>
       <c r="E6" s="9">
         <f>IFERROR(C6/(C6+D6),0)</f>
@@ -16791,10 +16158,10 @@
         </is>
       </c>
       <c r="C7" s="11" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>347</v>
+        <v>333</v>
       </c>
       <c r="E7" s="13">
         <f>IFERROR(C7/(C7+D7),0)</f>
@@ -16829,7 +16196,7 @@
         <v>7</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>365</v>
+        <v>350</v>
       </c>
       <c r="E8" s="9">
         <f>IFERROR(C8/(C8+D8),0)</f>
@@ -16864,7 +16231,7 @@
         <v>7</v>
       </c>
       <c r="D9" s="11" t="n">
-        <v>365</v>
+        <v>350</v>
       </c>
       <c r="E9" s="13">
         <f>IFERROR(C9/(C9+D9),0)</f>
@@ -16899,7 +16266,7 @@
         <v>15</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>357</v>
+        <v>342</v>
       </c>
       <c r="E10" s="9">
         <f>IFERROR(C10/(C10+D10),0)</f>
@@ -16934,7 +16301,7 @@
         <v>16</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>356</v>
+        <v>341</v>
       </c>
       <c r="E11" s="13">
         <f>IFERROR(C11/(C11+D11),0)</f>
@@ -16966,10 +16333,10 @@
         </is>
       </c>
       <c r="C12" s="7" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>348</v>
+        <v>334</v>
       </c>
       <c r="E12" s="9">
         <f>IFERROR(C12/(C12+D12),0)</f>
@@ -17004,7 +16371,7 @@
         <v>72</v>
       </c>
       <c r="D13" s="11" t="n">
-        <v>300</v>
+        <v>285</v>
       </c>
       <c r="E13" s="13">
         <f>IFERROR(C13/(C13+D13),0)</f>
@@ -17039,7 +16406,7 @@
         <v>5</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>367</v>
+        <v>352</v>
       </c>
       <c r="E14" s="9">
         <f>IFERROR(C14/(C14+D14),0)</f>
@@ -17071,10 +16438,10 @@
         </is>
       </c>
       <c r="C15" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D15" s="11" t="n">
-        <v>367</v>
+        <v>353</v>
       </c>
       <c r="E15" s="13">
         <f>IFERROR(C15/(C15+D15),0)</f>

--- a/exports/Resumen_Evidencias_OPS.xlsx
+++ b/exports/Resumen_Evidencias_OPS.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tiendas" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Actividades" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Resumen" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Tiendas" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Actividades" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Resumen'!$A$9:$H$37</definedName>
@@ -592,7 +592,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Todas las regiones · Corte 03/09/2026 13:44</t>
+          <t>Todas las regiones · Corte 03/09/2026 13:49</t>
         </is>
       </c>
     </row>
@@ -615,10 +615,10 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>3650</v>
+        <v>3645</v>
       </c>
       <c r="E6" s="5">
         <f>IFERROR(A6/(A6+C6),0)</f>
@@ -714,10 +714,10 @@
         <v>13</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="E11" s="12" t="n">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="F11" s="13">
         <f>IFERROR(D11/(D11+E11),0)</f>
@@ -1650,7 +1650,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Todas las regiones · Corte 03/09/2026 13:44</t>
+          <t>Todas las regiones · Corte 03/09/2026 13:49</t>
         </is>
       </c>
     </row>
@@ -1747,17 +1747,17 @@
       </c>
       <c r="B6" s="17" t="inlineStr">
         <is>
-          <t>38719</t>
+          <t>38695</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>Plaza Fortuna</t>
+          <t>Cetram 4 Caminos</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E6" s="7" t="n">
@@ -1787,37 +1787,37 @@
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>38695</t>
+          <t>38719</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>Cetram 4 Caminos</t>
+          <t>Plaza Fortuna</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E7" s="11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G7" s="13">
         <f>IFERROR(E7/(E7+F7),0)</f>
         <v/>
       </c>
-      <c r="H7" s="10" t="inlineStr">
-        <is>
-          <t>Seguimiento</t>
-        </is>
-      </c>
-      <c r="I7" s="10" t="inlineStr">
-        <is>
-          <t>Dar seguimiento</t>
+      <c r="H7" s="16" t="inlineStr">
+        <is>
+          <t>En meta</t>
+        </is>
+      </c>
+      <c r="I7" s="16" t="inlineStr">
+        <is>
+          <t>Mantener estándar</t>
         </is>
       </c>
     </row>
@@ -2467,17 +2467,17 @@
       </c>
       <c r="B24" s="17" t="inlineStr">
         <is>
-          <t>38606</t>
+          <t>38176</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>TlalnepantlaCarso</t>
+          <t>Periferico Satélite DT</t>
         </is>
       </c>
       <c r="D24" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E24" s="7" t="n">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="B25" s="15" t="inlineStr">
         <is>
-          <t>38374</t>
+          <t>38606</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>Valle Dorado</t>
+          <t>TlalnepantlaCarso</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
@@ -2547,37 +2547,37 @@
       </c>
       <c r="B26" s="17" t="inlineStr">
         <is>
-          <t>38930</t>
+          <t>38374</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>Blvd. Aeropuerto dt</t>
+          <t>Valle Dorado</t>
         </is>
       </c>
       <c r="D26" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E26" s="7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F26" s="7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G26" s="9">
         <f>IFERROR(E26/(E26+F26),0)</f>
         <v/>
       </c>
-      <c r="H26" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I26" s="14" t="inlineStr">
-        <is>
-          <t>Priorizar hoy</t>
+      <c r="H26" s="10" t="inlineStr">
+        <is>
+          <t>Seguimiento</t>
+        </is>
+      </c>
+      <c r="I26" s="10" t="inlineStr">
+        <is>
+          <t>Dar seguimiento</t>
         </is>
       </c>
     </row>
@@ -2587,17 +2587,17 @@
       </c>
       <c r="B27" s="15" t="inlineStr">
         <is>
-          <t>38197</t>
+          <t>38930</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>Echegaray</t>
+          <t>Blvd. Aeropuerto dt</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E27" s="11" t="n">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="B28" s="17" t="inlineStr">
         <is>
-          <t>38995</t>
+          <t>38197</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>Encuentro Oceania II</t>
+          <t>Echegaray</t>
         </is>
       </c>
       <c r="D28" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E28" s="7" t="n">
@@ -2667,17 +2667,17 @@
       </c>
       <c r="B29" s="15" t="inlineStr">
         <is>
-          <t>38230</t>
+          <t>38995</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>ITEMS Edo de Mexico</t>
+          <t>Encuentro Oceania II</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E29" s="11" t="n">
@@ -2707,17 +2707,17 @@
       </c>
       <c r="B30" s="17" t="inlineStr">
         <is>
-          <t>38937</t>
+          <t>38230</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>Parque Tepeyac Piso 1</t>
+          <t>ITEMS Edo de Mexico</t>
         </is>
       </c>
       <c r="D30" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E30" s="7" t="n">
@@ -2747,17 +2747,17 @@
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>38427</t>
+          <t>38937</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>Plaza Satelite</t>
+          <t>Parque Tepeyac Piso 1</t>
         </is>
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E31" s="11" t="n">
@@ -2787,17 +2787,17 @@
       </c>
       <c r="B32" s="17" t="inlineStr">
         <is>
-          <t>38992</t>
+          <t>38427</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>Tapo Puerta Oriente</t>
+          <t>Plaza Satelite</t>
         </is>
       </c>
       <c r="D32" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E32" s="7" t="n">
@@ -2827,21 +2827,21 @@
       </c>
       <c r="B33" s="15" t="inlineStr">
         <is>
-          <t>38604</t>
+          <t>38992</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>Cosmopol</t>
+          <t>Tapo Puerta Oriente</t>
         </is>
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E33" s="11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F33" s="11" t="n">
         <v>7</v>
@@ -2867,17 +2867,17 @@
       </c>
       <c r="B34" s="17" t="inlineStr">
         <is>
-          <t>38770</t>
+          <t>38604</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>Gustavo Baz 29</t>
+          <t>Cosmopol</t>
         </is>
       </c>
       <c r="D34" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E34" s="7" t="n">
@@ -2907,17 +2907,17 @@
       </c>
       <c r="B35" s="15" t="inlineStr">
         <is>
-          <t>38456</t>
+          <t>38770</t>
         </is>
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>Plaza las Flores</t>
+          <t>Gustavo Baz 29</t>
         </is>
       </c>
       <c r="D35" s="12" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E35" s="11" t="n">
@@ -2947,17 +2947,17 @@
       </c>
       <c r="B36" s="17" t="inlineStr">
         <is>
-          <t>43152</t>
+          <t>38456</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>Samara Satélite</t>
+          <t>Plaza las Flores</t>
         </is>
       </c>
       <c r="D36" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E36" s="7" t="n">
@@ -2987,24 +2987,24 @@
       </c>
       <c r="B37" s="15" t="inlineStr">
         <is>
-          <t>43194</t>
+          <t>43152</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>Atana Lindavista</t>
+          <t>Samara Satélite</t>
         </is>
       </c>
       <c r="D37" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E37" s="11" t="n">
         <v>3</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G37" s="13">
         <f>IFERROR(E37/(E37+F37),0)</f>
@@ -3027,17 +3027,17 @@
       </c>
       <c r="B38" s="17" t="inlineStr">
         <is>
-          <t>38529</t>
+          <t>43194</t>
         </is>
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>Bosques de Aragon</t>
+          <t>Atana Lindavista</t>
         </is>
       </c>
       <c r="D38" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E38" s="7" t="n">
@@ -3067,12 +3067,12 @@
       </c>
       <c r="B39" s="15" t="inlineStr">
         <is>
-          <t>38431</t>
+          <t>38529</t>
         </is>
       </c>
       <c r="C39" s="12" t="inlineStr">
         <is>
-          <t>Eduardo Molina</t>
+          <t>Bosques de Aragon</t>
         </is>
       </c>
       <c r="D39" s="12" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="B40" s="17" t="inlineStr">
         <is>
-          <t>38965</t>
+          <t>38431</t>
         </is>
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>Parque Tepeyac Piso 2</t>
+          <t>Eduardo Molina</t>
         </is>
       </c>
       <c r="D40" s="8" t="inlineStr">
@@ -3147,17 +3147,17 @@
       </c>
       <c r="B41" s="15" t="inlineStr">
         <is>
-          <t>38792</t>
+          <t>38965</t>
         </is>
       </c>
       <c r="C41" s="12" t="inlineStr">
         <is>
-          <t>Pasaje Tlanepantla</t>
+          <t>Parque Tepeyac Piso 2</t>
         </is>
       </c>
       <c r="D41" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E41" s="11" t="n">
@@ -3187,17 +3187,17 @@
       </c>
       <c r="B42" s="17" t="inlineStr">
         <is>
-          <t>38924</t>
+          <t>38792</t>
         </is>
       </c>
       <c r="C42" s="8" t="inlineStr">
         <is>
-          <t>Plaza Aeropuerto</t>
+          <t>Pasaje Tlanepantla</t>
         </is>
       </c>
       <c r="D42" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E42" s="7" t="n">
@@ -3227,12 +3227,12 @@
       </c>
       <c r="B43" s="15" t="inlineStr">
         <is>
-          <t>38811</t>
+          <t>38924</t>
         </is>
       </c>
       <c r="C43" s="12" t="inlineStr">
         <is>
-          <t>Plaza Tepeyac</t>
+          <t>Plaza Aeropuerto</t>
         </is>
       </c>
       <c r="D43" s="12" t="inlineStr">
@@ -3267,17 +3267,17 @@
       </c>
       <c r="B44" s="17" t="inlineStr">
         <is>
-          <t>38136</t>
+          <t>38811</t>
         </is>
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t>Punta Norte</t>
+          <t>Plaza Tepeyac</t>
         </is>
       </c>
       <c r="D44" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E44" s="7" t="n">
@@ -3307,17 +3307,17 @@
       </c>
       <c r="B45" s="15" t="inlineStr">
         <is>
-          <t>38651</t>
+          <t>38136</t>
         </is>
       </c>
       <c r="C45" s="12" t="inlineStr">
         <is>
-          <t>Via Vallejo</t>
+          <t>Punta Norte</t>
         </is>
       </c>
       <c r="D45" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E45" s="11" t="n">
@@ -3347,24 +3347,24 @@
       </c>
       <c r="B46" s="17" t="inlineStr">
         <is>
-          <t>38186</t>
+          <t>38651</t>
         </is>
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t>Arboledas</t>
+          <t>Via Vallejo</t>
         </is>
       </c>
       <c r="D46" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E46" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F46" s="7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G46" s="9">
         <f>IFERROR(E46/(E46+F46),0)</f>
@@ -3387,17 +3387,17 @@
       </c>
       <c r="B47" s="15" t="inlineStr">
         <is>
-          <t>43043</t>
+          <t>38186</t>
         </is>
       </c>
       <c r="C47" s="12" t="inlineStr">
         <is>
-          <t>Atizapan</t>
+          <t>Arboledas</t>
         </is>
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E47" s="11" t="n">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="B48" s="17" t="inlineStr">
         <is>
-          <t>38149</t>
+          <t>43043</t>
         </is>
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
-          <t>Bellavista</t>
+          <t>Atizapan</t>
         </is>
       </c>
       <c r="D48" s="8" t="inlineStr">
@@ -3467,17 +3467,17 @@
       </c>
       <c r="B49" s="15" t="inlineStr">
         <is>
-          <t>38527</t>
+          <t>38149</t>
         </is>
       </c>
       <c r="C49" s="12" t="inlineStr">
         <is>
-          <t>Camarones</t>
+          <t>Bellavista</t>
         </is>
       </c>
       <c r="D49" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E49" s="11" t="n">
@@ -3507,12 +3507,12 @@
       </c>
       <c r="B50" s="17" t="inlineStr">
         <is>
-          <t>38837</t>
+          <t>38527</t>
         </is>
       </c>
       <c r="C50" s="8" t="inlineStr">
         <is>
-          <t>Centenario Azcapotzalco</t>
+          <t>Camarones</t>
         </is>
       </c>
       <c r="D50" s="8" t="inlineStr">
@@ -3547,17 +3547,17 @@
       </c>
       <c r="B51" s="15" t="inlineStr">
         <is>
-          <t>38394</t>
+          <t>38837</t>
         </is>
       </c>
       <c r="C51" s="12" t="inlineStr">
         <is>
-          <t>Centro Comercial Lomas Verdes</t>
+          <t>Centenario Azcapotzalco</t>
         </is>
       </c>
       <c r="D51" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E51" s="11" t="n">
@@ -3587,12 +3587,12 @@
       </c>
       <c r="B52" s="17" t="inlineStr">
         <is>
-          <t>38535</t>
+          <t>38394</t>
         </is>
       </c>
       <c r="C52" s="8" t="inlineStr">
         <is>
-          <t>City Center Esmeralda</t>
+          <t>Centro Comercial Lomas Verdes</t>
         </is>
       </c>
       <c r="D52" s="8" t="inlineStr">
@@ -3627,12 +3627,12 @@
       </c>
       <c r="B53" s="15" t="inlineStr">
         <is>
-          <t>38507</t>
+          <t>38535</t>
         </is>
       </c>
       <c r="C53" s="12" t="inlineStr">
         <is>
-          <t>Espacio Vista del Valle</t>
+          <t>City Center Esmeralda</t>
         </is>
       </c>
       <c r="D53" s="12" t="inlineStr">
@@ -3667,12 +3667,12 @@
       </c>
       <c r="B54" s="17" t="inlineStr">
         <is>
-          <t>38363</t>
+          <t>38507</t>
         </is>
       </c>
       <c r="C54" s="8" t="inlineStr">
         <is>
-          <t>Galerias Atizapan</t>
+          <t>Espacio Vista del Valle</t>
         </is>
       </c>
       <c r="D54" s="8" t="inlineStr">
@@ -3707,17 +3707,17 @@
       </c>
       <c r="B55" s="15" t="inlineStr">
         <is>
-          <t>38205</t>
+          <t>38363</t>
         </is>
       </c>
       <c r="C55" s="12" t="inlineStr">
         <is>
-          <t>Lindavista</t>
+          <t>Galerias Atizapan</t>
         </is>
       </c>
       <c r="D55" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E55" s="11" t="n">
@@ -3747,17 +3747,17 @@
       </c>
       <c r="B56" s="17" t="inlineStr">
         <is>
-          <t>38119</t>
+          <t>38205</t>
         </is>
       </c>
       <c r="C56" s="8" t="inlineStr">
         <is>
-          <t>Lomas Verdes</t>
+          <t>Lindavista</t>
         </is>
       </c>
       <c r="D56" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E56" s="7" t="n">
@@ -3787,12 +3787,12 @@
       </c>
       <c r="B57" s="15" t="inlineStr">
         <is>
-          <t>38270</t>
+          <t>38119</t>
         </is>
       </c>
       <c r="C57" s="12" t="inlineStr">
         <is>
-          <t>Lomas Verdes II</t>
+          <t>Lomas Verdes</t>
         </is>
       </c>
       <c r="D57" s="12" t="inlineStr">
@@ -3827,17 +3827,17 @@
       </c>
       <c r="B58" s="17" t="inlineStr">
         <is>
-          <t>38371</t>
+          <t>38270</t>
         </is>
       </c>
       <c r="C58" s="8" t="inlineStr">
         <is>
-          <t>Montevideo DT</t>
+          <t>Lomas Verdes II</t>
         </is>
       </c>
       <c r="D58" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E58" s="7" t="n">
@@ -3867,12 +3867,12 @@
       </c>
       <c r="B59" s="15" t="inlineStr">
         <is>
-          <t>43111</t>
+          <t>38371</t>
         </is>
       </c>
       <c r="C59" s="12" t="inlineStr">
         <is>
-          <t>Montevideo Insurgentes</t>
+          <t>Montevideo DT</t>
         </is>
       </c>
       <c r="D59" s="12" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="B60" s="17" t="inlineStr">
         <is>
-          <t>43195</t>
+          <t>43111</t>
         </is>
       </c>
       <c r="C60" s="8" t="inlineStr">
         <is>
-          <t>Parque Jadin kiosko</t>
+          <t>Montevideo Insurgentes</t>
         </is>
       </c>
       <c r="D60" s="8" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="B61" s="15" t="inlineStr">
         <is>
-          <t>38546</t>
+          <t>43195</t>
         </is>
       </c>
       <c r="C61" s="12" t="inlineStr">
         <is>
-          <t>Patio Claveria</t>
+          <t>Parque Jadin kiosko</t>
         </is>
       </c>
       <c r="D61" s="12" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="B62" s="17" t="inlineStr">
         <is>
-          <t>38677</t>
+          <t>38546</t>
         </is>
       </c>
       <c r="C62" s="8" t="inlineStr">
         <is>
-          <t>Patio la Raza</t>
+          <t>Patio Claveria</t>
         </is>
       </c>
       <c r="D62" s="8" t="inlineStr">
@@ -4027,12 +4027,12 @@
       </c>
       <c r="B63" s="15" t="inlineStr">
         <is>
-          <t>43132</t>
+          <t>38677</t>
         </is>
       </c>
       <c r="C63" s="12" t="inlineStr">
         <is>
-          <t>Plaza Vista Norte</t>
+          <t>Patio la Raza</t>
         </is>
       </c>
       <c r="D63" s="12" t="inlineStr">
@@ -4067,17 +4067,17 @@
       </c>
       <c r="B64" s="17" t="inlineStr">
         <is>
-          <t>38460</t>
+          <t>43132</t>
         </is>
       </c>
       <c r="C64" s="8" t="inlineStr">
         <is>
-          <t>Santa Monica</t>
+          <t>Plaza Vista Norte</t>
         </is>
       </c>
       <c r="D64" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E64" s="7" t="n">
@@ -4107,12 +4107,12 @@
       </c>
       <c r="B65" s="15" t="inlineStr">
         <is>
-          <t>38442</t>
+          <t>38460</t>
         </is>
       </c>
       <c r="C65" s="12" t="inlineStr">
         <is>
-          <t>Sor Juana</t>
+          <t>Santa Monica</t>
         </is>
       </c>
       <c r="D65" s="12" t="inlineStr">
@@ -4147,17 +4147,17 @@
       </c>
       <c r="B66" s="17" t="inlineStr">
         <is>
-          <t>38925</t>
+          <t>38442</t>
         </is>
       </c>
       <c r="C66" s="8" t="inlineStr">
         <is>
-          <t>Star Medica Lomas Verdes</t>
+          <t>Sor Juana</t>
         </is>
       </c>
       <c r="D66" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E66" s="7" t="n">
@@ -4187,17 +4187,17 @@
       </c>
       <c r="B67" s="15" t="inlineStr">
         <is>
-          <t>38411</t>
+          <t>38925</t>
         </is>
       </c>
       <c r="C67" s="12" t="inlineStr">
         <is>
-          <t>Torres Lindavista</t>
+          <t>Star Medica Lomas Verdes</t>
         </is>
       </c>
       <c r="D67" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E67" s="11" t="n">
@@ -4227,17 +4227,17 @@
       </c>
       <c r="B68" s="17" t="inlineStr">
         <is>
-          <t>43130</t>
+          <t>38411</t>
         </is>
       </c>
       <c r="C68" s="8" t="inlineStr">
         <is>
-          <t>Town Center Nicolás Romero</t>
+          <t>Torres Lindavista</t>
         </is>
       </c>
       <c r="D68" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E68" s="7" t="n">
@@ -4267,17 +4267,17 @@
       </c>
       <c r="B69" s="15" t="inlineStr">
         <is>
-          <t>38694</t>
+          <t>43130</t>
         </is>
       </c>
       <c r="C69" s="12" t="inlineStr">
         <is>
-          <t>Villas de la Hacienda</t>
+          <t>Town Center Nicolás Romero</t>
         </is>
       </c>
       <c r="D69" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E69" s="11" t="n">
@@ -4307,17 +4307,17 @@
       </c>
       <c r="B70" s="17" t="inlineStr">
         <is>
-          <t>38115</t>
+          <t>38694</t>
         </is>
       </c>
       <c r="C70" s="8" t="inlineStr">
         <is>
-          <t>Zona Azul</t>
+          <t>Villas de la Hacienda</t>
         </is>
       </c>
       <c r="D70" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E70" s="7" t="n">
@@ -4347,12 +4347,12 @@
       </c>
       <c r="B71" s="15" t="inlineStr">
         <is>
-          <t>38142</t>
+          <t>38115</t>
         </is>
       </c>
       <c r="C71" s="12" t="inlineStr">
         <is>
-          <t>Zona Esmeralda</t>
+          <t>Zona Azul</t>
         </is>
       </c>
       <c r="D71" s="12" t="inlineStr">
@@ -4387,21 +4387,21 @@
       </c>
       <c r="B72" s="17" t="inlineStr">
         <is>
-          <t>38207</t>
+          <t>38142</t>
         </is>
       </c>
       <c r="C72" s="8" t="inlineStr">
         <is>
-          <t>Lindavista II</t>
+          <t>Zona Esmeralda</t>
         </is>
       </c>
       <c r="D72" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E72" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F72" s="7" t="n">
         <v>9</v>
@@ -4427,17 +4427,17 @@
       </c>
       <c r="B73" s="15" t="inlineStr">
         <is>
-          <t>38845</t>
+          <t>38207</t>
         </is>
       </c>
       <c r="C73" s="12" t="inlineStr">
         <is>
-          <t>Mundo E II</t>
+          <t>Lindavista II</t>
         </is>
       </c>
       <c r="D73" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E73" s="11" t="n">
@@ -4467,17 +4467,17 @@
       </c>
       <c r="B74" s="17" t="inlineStr">
         <is>
-          <t>38266</t>
+          <t>38845</t>
         </is>
       </c>
       <c r="C74" s="8" t="inlineStr">
         <is>
-          <t>San Mateo</t>
+          <t>Mundo E II</t>
         </is>
       </c>
       <c r="D74" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E74" s="7" t="n">
@@ -4507,24 +4507,24 @@
       </c>
       <c r="B75" s="15" t="inlineStr">
         <is>
-          <t>38176</t>
+          <t>38266</t>
         </is>
       </c>
       <c r="C75" s="12" t="inlineStr">
         <is>
-          <t>Periferico Satélite DT</t>
+          <t>San Mateo</t>
         </is>
       </c>
       <c r="D75" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E75" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F75" s="11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G75" s="13">
         <f>IFERROR(E75/(E75+F75),0)</f>
@@ -16032,7 +16032,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Todas las regiones · Corte 03/09/2026 13:44</t>
+          <t>Todas las regiones · Corte 03/09/2026 13:49</t>
         </is>
       </c>
     </row>
@@ -16088,10 +16088,10 @@
         </is>
       </c>
       <c r="C5" s="11" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="E5" s="13">
         <f>IFERROR(C5/(C5+D5),0)</f>
@@ -16123,10 +16123,10 @@
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D6" s="7" t="n">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="E6" s="9">
         <f>IFERROR(C6/(C6+D6),0)</f>
@@ -16158,10 +16158,10 @@
         </is>
       </c>
       <c r="C7" s="11" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E7" s="13">
         <f>IFERROR(C7/(C7+D7),0)</f>
@@ -16333,10 +16333,10 @@
         </is>
       </c>
       <c r="C12" s="7" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="E12" s="9">
         <f>IFERROR(C12/(C12+D12),0)</f>
@@ -16438,10 +16438,10 @@
         </is>
       </c>
       <c r="C15" s="11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D15" s="11" t="n">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="E15" s="13">
         <f>IFERROR(C15/(C15+D15),0)</f>

--- a/exports/Resumen_Evidencias_OPS.xlsx
+++ b/exports/Resumen_Evidencias_OPS.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Resumen" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Tiendas" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Actividades" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tiendas" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Actividades" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Resumen'!$A$9:$H$37</definedName>
@@ -592,7 +592,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Todas las regiones · Corte 03/09/2026 13:49</t>
+          <t>Todas las regiones · Corte 03/09/2026 13:44</t>
         </is>
       </c>
     </row>
@@ -615,10 +615,10 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>3645</v>
+        <v>3650</v>
       </c>
       <c r="E6" s="5">
         <f>IFERROR(A6/(A6+C6),0)</f>
@@ -714,10 +714,10 @@
         <v>13</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="E11" s="12" t="n">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="F11" s="13">
         <f>IFERROR(D11/(D11+E11),0)</f>
@@ -1650,7 +1650,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Todas las regiones · Corte 03/09/2026 13:49</t>
+          <t>Todas las regiones · Corte 03/09/2026 13:44</t>
         </is>
       </c>
     </row>
@@ -1747,17 +1747,17 @@
       </c>
       <c r="B6" s="17" t="inlineStr">
         <is>
-          <t>38695</t>
+          <t>38719</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>Cetram 4 Caminos</t>
+          <t>Plaza Fortuna</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E6" s="7" t="n">
@@ -1787,37 +1787,37 @@
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>38719</t>
+          <t>38695</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>Plaza Fortuna</t>
+          <t>Cetram 4 Caminos</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E7" s="11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G7" s="13">
         <f>IFERROR(E7/(E7+F7),0)</f>
         <v/>
       </c>
-      <c r="H7" s="16" t="inlineStr">
-        <is>
-          <t>En meta</t>
-        </is>
-      </c>
-      <c r="I7" s="16" t="inlineStr">
-        <is>
-          <t>Mantener estándar</t>
+      <c r="H7" s="10" t="inlineStr">
+        <is>
+          <t>Seguimiento</t>
+        </is>
+      </c>
+      <c r="I7" s="10" t="inlineStr">
+        <is>
+          <t>Dar seguimiento</t>
         </is>
       </c>
     </row>
@@ -2467,17 +2467,17 @@
       </c>
       <c r="B24" s="17" t="inlineStr">
         <is>
-          <t>38176</t>
+          <t>38606</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>Periferico Satélite DT</t>
+          <t>TlalnepantlaCarso</t>
         </is>
       </c>
       <c r="D24" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E24" s="7" t="n">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="B25" s="15" t="inlineStr">
         <is>
-          <t>38606</t>
+          <t>38374</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>TlalnepantlaCarso</t>
+          <t>Valle Dorado</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
@@ -2547,37 +2547,37 @@
       </c>
       <c r="B26" s="17" t="inlineStr">
         <is>
-          <t>38374</t>
+          <t>38930</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>Valle Dorado</t>
+          <t>Blvd. Aeropuerto dt</t>
         </is>
       </c>
       <c r="D26" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E26" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F26" s="7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G26" s="9">
         <f>IFERROR(E26/(E26+F26),0)</f>
         <v/>
       </c>
-      <c r="H26" s="10" t="inlineStr">
-        <is>
-          <t>Seguimiento</t>
-        </is>
-      </c>
-      <c r="I26" s="10" t="inlineStr">
-        <is>
-          <t>Dar seguimiento</t>
+      <c r="H26" s="14" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="I26" s="14" t="inlineStr">
+        <is>
+          <t>Priorizar hoy</t>
         </is>
       </c>
     </row>
@@ -2587,17 +2587,17 @@
       </c>
       <c r="B27" s="15" t="inlineStr">
         <is>
-          <t>38930</t>
+          <t>38197</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>Blvd. Aeropuerto dt</t>
+          <t>Echegaray</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E27" s="11" t="n">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="B28" s="17" t="inlineStr">
         <is>
-          <t>38197</t>
+          <t>38995</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>Echegaray</t>
+          <t>Encuentro Oceania II</t>
         </is>
       </c>
       <c r="D28" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E28" s="7" t="n">
@@ -2667,17 +2667,17 @@
       </c>
       <c r="B29" s="15" t="inlineStr">
         <is>
-          <t>38995</t>
+          <t>38230</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>Encuentro Oceania II</t>
+          <t>ITEMS Edo de Mexico</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E29" s="11" t="n">
@@ -2707,17 +2707,17 @@
       </c>
       <c r="B30" s="17" t="inlineStr">
         <is>
-          <t>38230</t>
+          <t>38937</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>ITEMS Edo de Mexico</t>
+          <t>Parque Tepeyac Piso 1</t>
         </is>
       </c>
       <c r="D30" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E30" s="7" t="n">
@@ -2747,17 +2747,17 @@
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>38937</t>
+          <t>38427</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>Parque Tepeyac Piso 1</t>
+          <t>Plaza Satelite</t>
         </is>
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E31" s="11" t="n">
@@ -2787,17 +2787,17 @@
       </c>
       <c r="B32" s="17" t="inlineStr">
         <is>
-          <t>38427</t>
+          <t>38992</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>Plaza Satelite</t>
+          <t>Tapo Puerta Oriente</t>
         </is>
       </c>
       <c r="D32" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E32" s="7" t="n">
@@ -2827,21 +2827,21 @@
       </c>
       <c r="B33" s="15" t="inlineStr">
         <is>
-          <t>38992</t>
+          <t>38604</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>Tapo Puerta Oriente</t>
+          <t>Cosmopol</t>
         </is>
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E33" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F33" s="11" t="n">
         <v>7</v>
@@ -2867,17 +2867,17 @@
       </c>
       <c r="B34" s="17" t="inlineStr">
         <is>
-          <t>38604</t>
+          <t>38770</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>Cosmopol</t>
+          <t>Gustavo Baz 29</t>
         </is>
       </c>
       <c r="D34" s="8" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E34" s="7" t="n">
@@ -2907,17 +2907,17 @@
       </c>
       <c r="B35" s="15" t="inlineStr">
         <is>
-          <t>38770</t>
+          <t>38456</t>
         </is>
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>Gustavo Baz 29</t>
+          <t>Plaza las Flores</t>
         </is>
       </c>
       <c r="D35" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E35" s="11" t="n">
@@ -2947,17 +2947,17 @@
       </c>
       <c r="B36" s="17" t="inlineStr">
         <is>
-          <t>38456</t>
+          <t>43152</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>Plaza las Flores</t>
+          <t>Samara Satélite</t>
         </is>
       </c>
       <c r="D36" s="8" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E36" s="7" t="n">
@@ -2987,24 +2987,24 @@
       </c>
       <c r="B37" s="15" t="inlineStr">
         <is>
-          <t>43152</t>
+          <t>43194</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>Samara Satélite</t>
+          <t>Atana Lindavista</t>
         </is>
       </c>
       <c r="D37" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E37" s="11" t="n">
         <v>3</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G37" s="13">
         <f>IFERROR(E37/(E37+F37),0)</f>
@@ -3027,17 +3027,17 @@
       </c>
       <c r="B38" s="17" t="inlineStr">
         <is>
-          <t>43194</t>
+          <t>38529</t>
         </is>
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>Atana Lindavista</t>
+          <t>Bosques de Aragon</t>
         </is>
       </c>
       <c r="D38" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E38" s="7" t="n">
@@ -3067,12 +3067,12 @@
       </c>
       <c r="B39" s="15" t="inlineStr">
         <is>
-          <t>38529</t>
+          <t>38431</t>
         </is>
       </c>
       <c r="C39" s="12" t="inlineStr">
         <is>
-          <t>Bosques de Aragon</t>
+          <t>Eduardo Molina</t>
         </is>
       </c>
       <c r="D39" s="12" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="B40" s="17" t="inlineStr">
         <is>
-          <t>38431</t>
+          <t>38965</t>
         </is>
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>Eduardo Molina</t>
+          <t>Parque Tepeyac Piso 2</t>
         </is>
       </c>
       <c r="D40" s="8" t="inlineStr">
@@ -3147,17 +3147,17 @@
       </c>
       <c r="B41" s="15" t="inlineStr">
         <is>
-          <t>38965</t>
+          <t>38792</t>
         </is>
       </c>
       <c r="C41" s="12" t="inlineStr">
         <is>
-          <t>Parque Tepeyac Piso 2</t>
+          <t>Pasaje Tlanepantla</t>
         </is>
       </c>
       <c r="D41" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E41" s="11" t="n">
@@ -3187,17 +3187,17 @@
       </c>
       <c r="B42" s="17" t="inlineStr">
         <is>
-          <t>38792</t>
+          <t>38924</t>
         </is>
       </c>
       <c r="C42" s="8" t="inlineStr">
         <is>
-          <t>Pasaje Tlanepantla</t>
+          <t>Plaza Aeropuerto</t>
         </is>
       </c>
       <c r="D42" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E42" s="7" t="n">
@@ -3227,12 +3227,12 @@
       </c>
       <c r="B43" s="15" t="inlineStr">
         <is>
-          <t>38924</t>
+          <t>38811</t>
         </is>
       </c>
       <c r="C43" s="12" t="inlineStr">
         <is>
-          <t>Plaza Aeropuerto</t>
+          <t>Plaza Tepeyac</t>
         </is>
       </c>
       <c r="D43" s="12" t="inlineStr">
@@ -3267,17 +3267,17 @@
       </c>
       <c r="B44" s="17" t="inlineStr">
         <is>
-          <t>38811</t>
+          <t>38136</t>
         </is>
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t>Plaza Tepeyac</t>
+          <t>Punta Norte</t>
         </is>
       </c>
       <c r="D44" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E44" s="7" t="n">
@@ -3307,17 +3307,17 @@
       </c>
       <c r="B45" s="15" t="inlineStr">
         <is>
-          <t>38136</t>
+          <t>38651</t>
         </is>
       </c>
       <c r="C45" s="12" t="inlineStr">
         <is>
-          <t>Punta Norte</t>
+          <t>Via Vallejo</t>
         </is>
       </c>
       <c r="D45" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E45" s="11" t="n">
@@ -3347,24 +3347,24 @@
       </c>
       <c r="B46" s="17" t="inlineStr">
         <is>
-          <t>38651</t>
+          <t>38186</t>
         </is>
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t>Via Vallejo</t>
+          <t>Arboledas</t>
         </is>
       </c>
       <c r="D46" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E46" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F46" s="7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G46" s="9">
         <f>IFERROR(E46/(E46+F46),0)</f>
@@ -3387,17 +3387,17 @@
       </c>
       <c r="B47" s="15" t="inlineStr">
         <is>
-          <t>38186</t>
+          <t>43043</t>
         </is>
       </c>
       <c r="C47" s="12" t="inlineStr">
         <is>
-          <t>Arboledas</t>
+          <t>Atizapan</t>
         </is>
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E47" s="11" t="n">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="B48" s="17" t="inlineStr">
         <is>
-          <t>43043</t>
+          <t>38149</t>
         </is>
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
-          <t>Atizapan</t>
+          <t>Bellavista</t>
         </is>
       </c>
       <c r="D48" s="8" t="inlineStr">
@@ -3467,17 +3467,17 @@
       </c>
       <c r="B49" s="15" t="inlineStr">
         <is>
-          <t>38149</t>
+          <t>38527</t>
         </is>
       </c>
       <c r="C49" s="12" t="inlineStr">
         <is>
-          <t>Bellavista</t>
+          <t>Camarones</t>
         </is>
       </c>
       <c r="D49" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E49" s="11" t="n">
@@ -3507,12 +3507,12 @@
       </c>
       <c r="B50" s="17" t="inlineStr">
         <is>
-          <t>38527</t>
+          <t>38837</t>
         </is>
       </c>
       <c r="C50" s="8" t="inlineStr">
         <is>
-          <t>Camarones</t>
+          <t>Centenario Azcapotzalco</t>
         </is>
       </c>
       <c r="D50" s="8" t="inlineStr">
@@ -3547,17 +3547,17 @@
       </c>
       <c r="B51" s="15" t="inlineStr">
         <is>
-          <t>38837</t>
+          <t>38394</t>
         </is>
       </c>
       <c r="C51" s="12" t="inlineStr">
         <is>
-          <t>Centenario Azcapotzalco</t>
+          <t>Centro Comercial Lomas Verdes</t>
         </is>
       </c>
       <c r="D51" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E51" s="11" t="n">
@@ -3587,12 +3587,12 @@
       </c>
       <c r="B52" s="17" t="inlineStr">
         <is>
-          <t>38394</t>
+          <t>38535</t>
         </is>
       </c>
       <c r="C52" s="8" t="inlineStr">
         <is>
-          <t>Centro Comercial Lomas Verdes</t>
+          <t>City Center Esmeralda</t>
         </is>
       </c>
       <c r="D52" s="8" t="inlineStr">
@@ -3627,12 +3627,12 @@
       </c>
       <c r="B53" s="15" t="inlineStr">
         <is>
-          <t>38535</t>
+          <t>38507</t>
         </is>
       </c>
       <c r="C53" s="12" t="inlineStr">
         <is>
-          <t>City Center Esmeralda</t>
+          <t>Espacio Vista del Valle</t>
         </is>
       </c>
       <c r="D53" s="12" t="inlineStr">
@@ -3667,12 +3667,12 @@
       </c>
       <c r="B54" s="17" t="inlineStr">
         <is>
-          <t>38507</t>
+          <t>38363</t>
         </is>
       </c>
       <c r="C54" s="8" t="inlineStr">
         <is>
-          <t>Espacio Vista del Valle</t>
+          <t>Galerias Atizapan</t>
         </is>
       </c>
       <c r="D54" s="8" t="inlineStr">
@@ -3707,17 +3707,17 @@
       </c>
       <c r="B55" s="15" t="inlineStr">
         <is>
-          <t>38363</t>
+          <t>38205</t>
         </is>
       </c>
       <c r="C55" s="12" t="inlineStr">
         <is>
-          <t>Galerias Atizapan</t>
+          <t>Lindavista</t>
         </is>
       </c>
       <c r="D55" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E55" s="11" t="n">
@@ -3747,17 +3747,17 @@
       </c>
       <c r="B56" s="17" t="inlineStr">
         <is>
-          <t>38205</t>
+          <t>38119</t>
         </is>
       </c>
       <c r="C56" s="8" t="inlineStr">
         <is>
-          <t>Lindavista</t>
+          <t>Lomas Verdes</t>
         </is>
       </c>
       <c r="D56" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E56" s="7" t="n">
@@ -3787,12 +3787,12 @@
       </c>
       <c r="B57" s="15" t="inlineStr">
         <is>
-          <t>38119</t>
+          <t>38270</t>
         </is>
       </c>
       <c r="C57" s="12" t="inlineStr">
         <is>
-          <t>Lomas Verdes</t>
+          <t>Lomas Verdes II</t>
         </is>
       </c>
       <c r="D57" s="12" t="inlineStr">
@@ -3827,17 +3827,17 @@
       </c>
       <c r="B58" s="17" t="inlineStr">
         <is>
-          <t>38270</t>
+          <t>38371</t>
         </is>
       </c>
       <c r="C58" s="8" t="inlineStr">
         <is>
-          <t>Lomas Verdes II</t>
+          <t>Montevideo DT</t>
         </is>
       </c>
       <c r="D58" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E58" s="7" t="n">
@@ -3867,12 +3867,12 @@
       </c>
       <c r="B59" s="15" t="inlineStr">
         <is>
-          <t>38371</t>
+          <t>43111</t>
         </is>
       </c>
       <c r="C59" s="12" t="inlineStr">
         <is>
-          <t>Montevideo DT</t>
+          <t>Montevideo Insurgentes</t>
         </is>
       </c>
       <c r="D59" s="12" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="B60" s="17" t="inlineStr">
         <is>
-          <t>43111</t>
+          <t>43195</t>
         </is>
       </c>
       <c r="C60" s="8" t="inlineStr">
         <is>
-          <t>Montevideo Insurgentes</t>
+          <t>Parque Jadin kiosko</t>
         </is>
       </c>
       <c r="D60" s="8" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="B61" s="15" t="inlineStr">
         <is>
-          <t>43195</t>
+          <t>38546</t>
         </is>
       </c>
       <c r="C61" s="12" t="inlineStr">
         <is>
-          <t>Parque Jadin kiosko</t>
+          <t>Patio Claveria</t>
         </is>
       </c>
       <c r="D61" s="12" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="B62" s="17" t="inlineStr">
         <is>
-          <t>38546</t>
+          <t>38677</t>
         </is>
       </c>
       <c r="C62" s="8" t="inlineStr">
         <is>
-          <t>Patio Claveria</t>
+          <t>Patio la Raza</t>
         </is>
       </c>
       <c r="D62" s="8" t="inlineStr">
@@ -4027,12 +4027,12 @@
       </c>
       <c r="B63" s="15" t="inlineStr">
         <is>
-          <t>38677</t>
+          <t>43132</t>
         </is>
       </c>
       <c r="C63" s="12" t="inlineStr">
         <is>
-          <t>Patio la Raza</t>
+          <t>Plaza Vista Norte</t>
         </is>
       </c>
       <c r="D63" s="12" t="inlineStr">
@@ -4067,17 +4067,17 @@
       </c>
       <c r="B64" s="17" t="inlineStr">
         <is>
-          <t>43132</t>
+          <t>38460</t>
         </is>
       </c>
       <c r="C64" s="8" t="inlineStr">
         <is>
-          <t>Plaza Vista Norte</t>
+          <t>Santa Monica</t>
         </is>
       </c>
       <c r="D64" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E64" s="7" t="n">
@@ -4107,12 +4107,12 @@
       </c>
       <c r="B65" s="15" t="inlineStr">
         <is>
-          <t>38460</t>
+          <t>38442</t>
         </is>
       </c>
       <c r="C65" s="12" t="inlineStr">
         <is>
-          <t>Santa Monica</t>
+          <t>Sor Juana</t>
         </is>
       </c>
       <c r="D65" s="12" t="inlineStr">
@@ -4147,17 +4147,17 @@
       </c>
       <c r="B66" s="17" t="inlineStr">
         <is>
-          <t>38442</t>
+          <t>38925</t>
         </is>
       </c>
       <c r="C66" s="8" t="inlineStr">
         <is>
-          <t>Sor Juana</t>
+          <t>Star Medica Lomas Verdes</t>
         </is>
       </c>
       <c r="D66" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E66" s="7" t="n">
@@ -4187,17 +4187,17 @@
       </c>
       <c r="B67" s="15" t="inlineStr">
         <is>
-          <t>38925</t>
+          <t>38411</t>
         </is>
       </c>
       <c r="C67" s="12" t="inlineStr">
         <is>
-          <t>Star Medica Lomas Verdes</t>
+          <t>Torres Lindavista</t>
         </is>
       </c>
       <c r="D67" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E67" s="11" t="n">
@@ -4227,17 +4227,17 @@
       </c>
       <c r="B68" s="17" t="inlineStr">
         <is>
-          <t>38411</t>
+          <t>43130</t>
         </is>
       </c>
       <c r="C68" s="8" t="inlineStr">
         <is>
-          <t>Torres Lindavista</t>
+          <t>Town Center Nicolás Romero</t>
         </is>
       </c>
       <c r="D68" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E68" s="7" t="n">
@@ -4267,17 +4267,17 @@
       </c>
       <c r="B69" s="15" t="inlineStr">
         <is>
-          <t>43130</t>
+          <t>38694</t>
         </is>
       </c>
       <c r="C69" s="12" t="inlineStr">
         <is>
-          <t>Town Center Nicolás Romero</t>
+          <t>Villas de la Hacienda</t>
         </is>
       </c>
       <c r="D69" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E69" s="11" t="n">
@@ -4307,17 +4307,17 @@
       </c>
       <c r="B70" s="17" t="inlineStr">
         <is>
-          <t>38694</t>
+          <t>38115</t>
         </is>
       </c>
       <c r="C70" s="8" t="inlineStr">
         <is>
-          <t>Villas de la Hacienda</t>
+          <t>Zona Azul</t>
         </is>
       </c>
       <c r="D70" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E70" s="7" t="n">
@@ -4347,12 +4347,12 @@
       </c>
       <c r="B71" s="15" t="inlineStr">
         <is>
-          <t>38115</t>
+          <t>38142</t>
         </is>
       </c>
       <c r="C71" s="12" t="inlineStr">
         <is>
-          <t>Zona Azul</t>
+          <t>Zona Esmeralda</t>
         </is>
       </c>
       <c r="D71" s="12" t="inlineStr">
@@ -4387,21 +4387,21 @@
       </c>
       <c r="B72" s="17" t="inlineStr">
         <is>
-          <t>38142</t>
+          <t>38207</t>
         </is>
       </c>
       <c r="C72" s="8" t="inlineStr">
         <is>
-          <t>Zona Esmeralda</t>
+          <t>Lindavista II</t>
         </is>
       </c>
       <c r="D72" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E72" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F72" s="7" t="n">
         <v>9</v>
@@ -4427,17 +4427,17 @@
       </c>
       <c r="B73" s="15" t="inlineStr">
         <is>
-          <t>38207</t>
+          <t>38845</t>
         </is>
       </c>
       <c r="C73" s="12" t="inlineStr">
         <is>
-          <t>Lindavista II</t>
+          <t>Mundo E II</t>
         </is>
       </c>
       <c r="D73" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E73" s="11" t="n">
@@ -4467,17 +4467,17 @@
       </c>
       <c r="B74" s="17" t="inlineStr">
         <is>
-          <t>38845</t>
+          <t>38266</t>
         </is>
       </c>
       <c r="C74" s="8" t="inlineStr">
         <is>
-          <t>Mundo E II</t>
+          <t>San Mateo</t>
         </is>
       </c>
       <c r="D74" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E74" s="7" t="n">
@@ -4507,24 +4507,24 @@
       </c>
       <c r="B75" s="15" t="inlineStr">
         <is>
-          <t>38266</t>
+          <t>38176</t>
         </is>
       </c>
       <c r="C75" s="12" t="inlineStr">
         <is>
-          <t>San Mateo</t>
+          <t>Periferico Satélite DT</t>
         </is>
       </c>
       <c r="D75" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E75" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F75" s="11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G75" s="13">
         <f>IFERROR(E75/(E75+F75),0)</f>
@@ -16032,7 +16032,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Todas las regiones · Corte 03/09/2026 13:49</t>
+          <t>Todas las regiones · Corte 03/09/2026 13:44</t>
         </is>
       </c>
     </row>
@@ -16088,10 +16088,10 @@
         </is>
       </c>
       <c r="C5" s="11" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="E5" s="13">
         <f>IFERROR(C5/(C5+D5),0)</f>
@@ -16123,10 +16123,10 @@
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D6" s="7" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="E6" s="9">
         <f>IFERROR(C6/(C6+D6),0)</f>
@@ -16158,10 +16158,10 @@
         </is>
       </c>
       <c r="C7" s="11" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="E7" s="13">
         <f>IFERROR(C7/(C7+D7),0)</f>
@@ -16333,10 +16333,10 @@
         </is>
       </c>
       <c r="C12" s="7" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="E12" s="9">
         <f>IFERROR(C12/(C12+D12),0)</f>
@@ -16438,10 +16438,10 @@
         </is>
       </c>
       <c r="C15" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D15" s="11" t="n">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="E15" s="13">
         <f>IFERROR(C15/(C15+D15),0)</f>

--- a/exports/Resumen_Evidencias_OPS.xlsx
+++ b/exports/Resumen_Evidencias_OPS.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tiendas" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Actividades" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Resumen" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Tiendas" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Actividades" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Resumen'!$A$9:$H$37</definedName>

--- a/exports/Resumen_Evidencias_OPS.xlsx
+++ b/exports/Resumen_Evidencias_OPS.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Resumen" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Tiendas" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Actividades" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tiendas" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Actividades" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Resumen'!$A$9:$H$37</definedName>
@@ -674,7 +674,7 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>Enrique Cesar</t>
+          <t>Enrique Flores</t>
         </is>
       </c>
       <c r="C10" s="7" t="n">
@@ -707,7 +707,7 @@
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela</t>
+          <t>Yazmin Guadarrama</t>
         </is>
       </c>
       <c r="C11" s="11" t="n">
@@ -773,7 +773,7 @@
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina</t>
+          <t>Nancy Rodriguez</t>
         </is>
       </c>
       <c r="C13" s="11" t="n">
@@ -872,7 +872,7 @@
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>Adriana Alejandra Tanus Buhler</t>
+          <t>Adriana Tanus</t>
         </is>
       </c>
       <c r="C16" s="7" t="n">
@@ -905,7 +905,7 @@
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>Alberto Torrado Aguilar Cauz</t>
+          <t>Alberto Torrado</t>
         </is>
       </c>
       <c r="C17" s="11" t="n">
@@ -938,7 +938,7 @@
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>Andrea Nava Guzman</t>
+          <t>Andrea Nava</t>
         </is>
       </c>
       <c r="C18" s="7" t="n">
@@ -971,7 +971,7 @@
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>Areli Anahi Lazcano Lezama</t>
+          <t>Areli Lazcano</t>
         </is>
       </c>
       <c r="C19" s="11" t="n">
@@ -1004,7 +1004,7 @@
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>Ariana Janet Gutierrez Martinez</t>
+          <t>Ariana Gutierrez</t>
         </is>
       </c>
       <c r="C20" s="7" t="n">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>Cesar Alfonso Castillo Romero</t>
+          <t>Cesar Castillo</t>
         </is>
       </c>
       <c r="C21" s="11" t="n">
@@ -1070,7 +1070,7 @@
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>Daniel Flores Maldonado</t>
+          <t>Daniel Flores</t>
         </is>
       </c>
       <c r="C22" s="7" t="n">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="B23" s="12" t="inlineStr">
         <is>
-          <t>Erika Julieta Contreras Aguilera</t>
+          <t>Erika Contreras</t>
         </is>
       </c>
       <c r="C23" s="11" t="n">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>Fernando Eduardo Verdugo Saldaña</t>
+          <t>Fernando Verdugo</t>
         </is>
       </c>
       <c r="C24" s="7" t="n">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="B25" s="12" t="inlineStr">
         <is>
-          <t>Guadalupe Ibarra Martínez</t>
+          <t>Guadalupe Ibarra</t>
         </is>
       </c>
       <c r="C25" s="11" t="n">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>Hazar Susim Trejo Hernandez</t>
+          <t>Hazar Trejo</t>
         </is>
       </c>
       <c r="C26" s="7" t="n">
@@ -1235,7 +1235,7 @@
       </c>
       <c r="B27" s="12" t="inlineStr">
         <is>
-          <t>Jaqueline Cortes Ayala</t>
+          <t>Jaqueline Cortes</t>
         </is>
       </c>
       <c r="C27" s="11" t="n">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>Jesus Antonio Elguera Flores</t>
+          <t>Jesus Elguera</t>
         </is>
       </c>
       <c r="C28" s="7" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="B29" s="12" t="inlineStr">
         <is>
-          <t>Jose De Jesus Magos Arzaluz</t>
+          <t>Jose Magos</t>
         </is>
       </c>
       <c r="C29" s="11" t="n">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>Juan Jesus Zuñiga Flores</t>
+          <t>Juan Zuñiga</t>
         </is>
       </c>
       <c r="C30" s="7" t="n">
@@ -1367,17 +1367,17 @@
       </c>
       <c r="B31" s="12" t="inlineStr">
         <is>
-          <t>Luis Alberto Quevedo Rodriguez</t>
+          <t>Luis Neri</t>
         </is>
       </c>
       <c r="C31" s="11" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D31" s="11" t="n">
         <v>0</v>
       </c>
       <c r="E31" s="12" t="n">
-        <v>154</v>
+        <v>165</v>
       </c>
       <c r="F31" s="13">
         <f>IFERROR(D31/(D31+E31),0)</f>
@@ -1400,17 +1400,17 @@
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>Luis Manuel Neri Saldaña</t>
+          <t>Luis Quevedo</t>
         </is>
       </c>
       <c r="C32" s="7" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D32" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E32" s="8" t="n">
-        <v>165</v>
+        <v>154</v>
       </c>
       <c r="F32" s="9">
         <f>IFERROR(D32/(D32+E32),0)</f>
@@ -1433,7 +1433,7 @@
       </c>
       <c r="B33" s="12" t="inlineStr">
         <is>
-          <t>Manuel Alejandro Avila Molina</t>
+          <t>Manuel Avila</t>
         </is>
       </c>
       <c r="C33" s="11" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>Maria Anallely Sanchez Garcia</t>
+          <t>Maria Sanchez</t>
         </is>
       </c>
       <c r="C34" s="7" t="n">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="B35" s="12" t="inlineStr">
         <is>
-          <t>Monica Selene Morales Ibarra</t>
+          <t>Monica Morales</t>
         </is>
       </c>
       <c r="C35" s="11" t="n">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>Nora Caracas Saldaña</t>
+          <t>Nora Caracas</t>
         </is>
       </c>
       <c r="C36" s="7" t="n">

--- a/exports/Resumen_Evidencias_OPS.xlsx
+++ b/exports/Resumen_Evidencias_OPS.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Resumen" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Tiendas" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Actividades" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tiendas" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Actividades" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Resumen'!$A$9:$H$37</definedName>
@@ -592,7 +592,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Todas las regiones · Corte 03/09/2026 13:44</t>
+          <t>Todas las regiones · Corte 03/09/2026 20:28</t>
         </is>
       </c>
     </row>
@@ -615,10 +615,10 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>266</v>
+        <v>290</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>3650</v>
+        <v>3626</v>
       </c>
       <c r="E6" s="5">
         <f>IFERROR(A6/(A6+C6),0)</f>
@@ -674,17 +674,17 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>Enrique Flores</t>
+          <t>Yazmin Guadarrama</t>
         </is>
       </c>
       <c r="C10" s="7" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>59</v>
+        <v>85</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="F10" s="9">
         <f>IFERROR(D10/(D10+E10),0)</f>
@@ -707,17 +707,17 @@
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Guadarrama</t>
+          <t>Enrique Flores</t>
         </is>
       </c>
       <c r="C11" s="11" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="E11" s="12" t="n">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="F11" s="13">
         <f>IFERROR(D11/(D11+E11),0)</f>
@@ -747,23 +747,23 @@
         <v>11</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="E12" s="8" t="n">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="F12" s="9">
         <f>IFERROR(D12/(D12+E12),0)</f>
         <v/>
       </c>
-      <c r="G12" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="H12" s="14" t="inlineStr">
-        <is>
-          <t>Priorizar hoy</t>
+      <c r="G12" s="10" t="inlineStr">
+        <is>
+          <t>Seguimiento</t>
+        </is>
+      </c>
+      <c r="H12" s="10" t="inlineStr">
+        <is>
+          <t>Dar seguimiento</t>
         </is>
       </c>
     </row>
@@ -780,10 +780,10 @@
         <v>12</v>
       </c>
       <c r="D13" s="11" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E13" s="12" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F13" s="13">
         <f>IFERROR(D13/(D13+E13),0)</f>
@@ -1650,7 +1650,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Todas las regiones · Corte 03/09/2026 13:44</t>
+          <t>Todas las regiones · Corte 03/09/2026 20:28</t>
         </is>
       </c>
     </row>
@@ -1747,24 +1747,24 @@
       </c>
       <c r="B6" s="17" t="inlineStr">
         <is>
-          <t>38719</t>
+          <t>38117</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>Plaza Fortuna</t>
+          <t>Satelite</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E6" s="7" t="n">
         <v>9</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G6" s="9">
         <f>IFERROR(E6/(E6+F6),0)</f>
@@ -1801,23 +1801,23 @@
         </is>
       </c>
       <c r="E7" s="11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G7" s="13">
         <f>IFERROR(E7/(E7+F7),0)</f>
         <v/>
       </c>
-      <c r="H7" s="10" t="inlineStr">
-        <is>
-          <t>Seguimiento</t>
-        </is>
-      </c>
-      <c r="I7" s="10" t="inlineStr">
-        <is>
-          <t>Dar seguimiento</t>
+      <c r="H7" s="16" t="inlineStr">
+        <is>
+          <t>En meta</t>
+        </is>
+      </c>
+      <c r="I7" s="16" t="inlineStr">
+        <is>
+          <t>Mantener estándar</t>
         </is>
       </c>
     </row>
@@ -1827,12 +1827,12 @@
       </c>
       <c r="B8" s="17" t="inlineStr">
         <is>
-          <t>38458</t>
+          <t>38561</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>El Rosario</t>
+          <t>Parque Toreo</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
@@ -1841,23 +1841,23 @@
         </is>
       </c>
       <c r="E8" s="7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G8" s="9">
         <f>IFERROR(E8/(E8+F8),0)</f>
         <v/>
       </c>
-      <c r="H8" s="10" t="inlineStr">
-        <is>
-          <t>Seguimiento</t>
-        </is>
-      </c>
-      <c r="I8" s="10" t="inlineStr">
-        <is>
-          <t>Dar seguimiento</t>
+      <c r="H8" s="16" t="inlineStr">
+        <is>
+          <t>En meta</t>
+        </is>
+      </c>
+      <c r="I8" s="16" t="inlineStr">
+        <is>
+          <t>Mantener estándar</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>38903</t>
+          <t>38719</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>Encuentro Oceania</t>
+          <t>Plaza Fortuna</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
@@ -1881,23 +1881,23 @@
         </is>
       </c>
       <c r="E9" s="11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G9" s="13">
         <f>IFERROR(E9/(E9+F9),0)</f>
         <v/>
       </c>
-      <c r="H9" s="10" t="inlineStr">
-        <is>
-          <t>Seguimiento</t>
-        </is>
-      </c>
-      <c r="I9" s="10" t="inlineStr">
-        <is>
-          <t>Dar seguimiento</t>
+      <c r="H9" s="16" t="inlineStr">
+        <is>
+          <t>En meta</t>
+        </is>
+      </c>
+      <c r="I9" s="16" t="inlineStr">
+        <is>
+          <t>Mantener estándar</t>
         </is>
       </c>
     </row>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="B10" s="17" t="inlineStr">
         <is>
-          <t>38561</t>
+          <t>38197</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>Parque Toreo</t>
+          <t>Echegaray</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
@@ -1947,12 +1947,12 @@
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>38590</t>
+          <t>38458</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>Parque Toreo II</t>
+          <t>El Rosario</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
@@ -1961,7 +1961,7 @@
         </is>
       </c>
       <c r="E11" s="11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F11" s="11" t="n">
         <v>3</v>
@@ -1987,21 +1987,21 @@
       </c>
       <c r="B12" s="17" t="inlineStr">
         <is>
-          <t>38859</t>
+          <t>38903</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Plaza Satelite II N1</t>
+          <t>Encuentro Oceania</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E12" s="7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F12" s="7" t="n">
         <v>3</v>
@@ -2027,24 +2027,24 @@
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>38368</t>
+          <t>38590</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>Luna Park</t>
+          <t>Parque Toreo II</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E13" s="11" t="n">
         <v>7</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G13" s="13">
         <f>IFERROR(E13/(E13+F13),0)</f>
@@ -2067,24 +2067,24 @@
       </c>
       <c r="B14" s="17" t="inlineStr">
         <is>
-          <t>38674</t>
+          <t>38859</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Mundo E</t>
+          <t>Plaza Satelite II N1</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E14" s="7" t="n">
         <v>7</v>
       </c>
       <c r="F14" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G14" s="9">
         <f>IFERROR(E14/(E14+F14),0)</f>
@@ -2107,12 +2107,12 @@
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>38515</t>
+          <t>38368</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>Patio Ecatepec</t>
+          <t>Luna Park</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
@@ -2147,21 +2147,21 @@
       </c>
       <c r="B16" s="17" t="inlineStr">
         <is>
-          <t>38117</t>
+          <t>38674</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>Satelite</t>
+          <t>Mundo E</t>
         </is>
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E16" s="7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F16" s="7" t="n">
         <v>4</v>
@@ -2187,12 +2187,12 @@
       </c>
       <c r="B17" s="15" t="inlineStr">
         <is>
-          <t>38401</t>
+          <t>38515</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>Coacalco</t>
+          <t>Patio Ecatepec</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
@@ -2201,10 +2201,10 @@
         </is>
       </c>
       <c r="E17" s="11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G17" s="13">
         <f>IFERROR(E17/(E17+F17),0)</f>
@@ -2227,24 +2227,24 @@
       </c>
       <c r="B18" s="17" t="inlineStr">
         <is>
-          <t>38333</t>
+          <t>38475</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>Izcalli Mega</t>
+          <t>Satelite Centro Civico</t>
         </is>
       </c>
       <c r="D18" s="8" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E18" s="7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F18" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G18" s="9">
         <f>IFERROR(E18/(E18+F18),0)</f>
@@ -2267,12 +2267,12 @@
       </c>
       <c r="B19" s="15" t="inlineStr">
         <is>
-          <t>38339</t>
+          <t>38401</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Coacalco</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
@@ -2307,17 +2307,17 @@
       </c>
       <c r="B20" s="17" t="inlineStr">
         <is>
-          <t>38475</t>
+          <t>38333</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>Satelite Centro Civico</t>
+          <t>Izcalli Mega</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E20" s="7" t="n">
@@ -2347,21 +2347,21 @@
       </c>
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t>43193</t>
+          <t>38661</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>Cosmopol N1</t>
+          <t>Jinetes</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E21" s="11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F21" s="11" t="n">
         <v>5</v>
@@ -2387,24 +2387,24 @@
       </c>
       <c r="B22" s="17" t="inlineStr">
         <is>
-          <t>38894</t>
+          <t>38176</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>Galerias Perinorte</t>
+          <t>Periferico Satélite DT</t>
         </is>
       </c>
       <c r="D22" s="8" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E22" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="F22" s="7" t="n">
         <v>5</v>
-      </c>
-      <c r="F22" s="7" t="n">
-        <v>6</v>
       </c>
       <c r="G22" s="9">
         <f>IFERROR(E22/(E22+F22),0)</f>
@@ -2427,24 +2427,24 @@
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>38661</t>
+          <t>38339</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>Jinetes</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E23" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="F23" s="11" t="n">
         <v>5</v>
-      </c>
-      <c r="F23" s="11" t="n">
-        <v>6</v>
       </c>
       <c r="G23" s="13">
         <f>IFERROR(E23/(E23+F23),0)</f>
@@ -2467,24 +2467,24 @@
       </c>
       <c r="B24" s="17" t="inlineStr">
         <is>
-          <t>38606</t>
+          <t>43193</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>TlalnepantlaCarso</t>
+          <t>Cosmopol N1</t>
         </is>
       </c>
       <c r="D24" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E24" s="7" t="n">
         <v>5</v>
       </c>
       <c r="F24" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G24" s="9">
         <f>IFERROR(E24/(E24+F24),0)</f>
@@ -2507,17 +2507,17 @@
       </c>
       <c r="B25" s="15" t="inlineStr">
         <is>
-          <t>38374</t>
+          <t>38894</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>Valle Dorado</t>
+          <t>Galerias Perinorte</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E25" s="11" t="n">
@@ -2547,12 +2547,12 @@
       </c>
       <c r="B26" s="17" t="inlineStr">
         <is>
-          <t>38930</t>
+          <t>38924</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>Blvd. Aeropuerto dt</t>
+          <t>Plaza Aeropuerto</t>
         </is>
       </c>
       <c r="D26" s="8" t="inlineStr">
@@ -2561,23 +2561,23 @@
         </is>
       </c>
       <c r="E26" s="7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F26" s="7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G26" s="9">
         <f>IFERROR(E26/(E26+F26),0)</f>
         <v/>
       </c>
-      <c r="H26" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I26" s="14" t="inlineStr">
-        <is>
-          <t>Priorizar hoy</t>
+      <c r="H26" s="10" t="inlineStr">
+        <is>
+          <t>Seguimiento</t>
+        </is>
+      </c>
+      <c r="I26" s="10" t="inlineStr">
+        <is>
+          <t>Dar seguimiento</t>
         </is>
       </c>
     </row>
@@ -2587,37 +2587,37 @@
       </c>
       <c r="B27" s="15" t="inlineStr">
         <is>
-          <t>38197</t>
+          <t>38606</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>Echegaray</t>
+          <t>TlalnepantlaCarso</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E27" s="11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G27" s="13">
         <f>IFERROR(E27/(E27+F27),0)</f>
         <v/>
       </c>
-      <c r="H27" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I27" s="14" t="inlineStr">
-        <is>
-          <t>Priorizar hoy</t>
+      <c r="H27" s="10" t="inlineStr">
+        <is>
+          <t>Seguimiento</t>
+        </is>
+      </c>
+      <c r="I27" s="10" t="inlineStr">
+        <is>
+          <t>Dar seguimiento</t>
         </is>
       </c>
     </row>
@@ -2627,37 +2627,37 @@
       </c>
       <c r="B28" s="17" t="inlineStr">
         <is>
-          <t>38995</t>
+          <t>38374</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>Encuentro Oceania II</t>
+          <t>Valle Dorado</t>
         </is>
       </c>
       <c r="D28" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E28" s="7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F28" s="7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G28" s="9">
         <f>IFERROR(E28/(E28+F28),0)</f>
         <v/>
       </c>
-      <c r="H28" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I28" s="14" t="inlineStr">
-        <is>
-          <t>Priorizar hoy</t>
+      <c r="H28" s="10" t="inlineStr">
+        <is>
+          <t>Seguimiento</t>
+        </is>
+      </c>
+      <c r="I28" s="10" t="inlineStr">
+        <is>
+          <t>Dar seguimiento</t>
         </is>
       </c>
     </row>
@@ -2667,37 +2667,37 @@
       </c>
       <c r="B29" s="15" t="inlineStr">
         <is>
-          <t>38230</t>
+          <t>38656</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>ITEMS Edo de Mexico</t>
+          <t>Viveros de la Loma</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E29" s="11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G29" s="13">
         <f>IFERROR(E29/(E29+F29),0)</f>
         <v/>
       </c>
-      <c r="H29" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I29" s="14" t="inlineStr">
-        <is>
-          <t>Priorizar hoy</t>
+      <c r="H29" s="10" t="inlineStr">
+        <is>
+          <t>Seguimiento</t>
+        </is>
+      </c>
+      <c r="I29" s="10" t="inlineStr">
+        <is>
+          <t>Dar seguimiento</t>
         </is>
       </c>
     </row>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="B30" s="17" t="inlineStr">
         <is>
-          <t>38937</t>
+          <t>38930</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>Parque Tepeyac Piso 1</t>
+          <t>Blvd. Aeropuerto dt</t>
         </is>
       </c>
       <c r="D30" s="8" t="inlineStr">
@@ -2747,17 +2747,17 @@
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>38427</t>
+          <t>38431</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>Plaza Satelite</t>
+          <t>Eduardo Molina</t>
         </is>
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E31" s="11" t="n">
@@ -2787,12 +2787,12 @@
       </c>
       <c r="B32" s="17" t="inlineStr">
         <is>
-          <t>38992</t>
+          <t>38995</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>Tapo Puerta Oriente</t>
+          <t>Encuentro Oceania II</t>
         </is>
       </c>
       <c r="D32" s="8" t="inlineStr">
@@ -2827,21 +2827,21 @@
       </c>
       <c r="B33" s="15" t="inlineStr">
         <is>
-          <t>38604</t>
+          <t>38230</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>Cosmopol</t>
+          <t>ITEMS Edo de Mexico</t>
         </is>
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E33" s="11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F33" s="11" t="n">
         <v>7</v>
@@ -2867,21 +2867,21 @@
       </c>
       <c r="B34" s="17" t="inlineStr">
         <is>
-          <t>38770</t>
+          <t>38937</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>Gustavo Baz 29</t>
+          <t>Parque Tepeyac Piso 1</t>
         </is>
       </c>
       <c r="D34" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E34" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F34" s="7" t="n">
         <v>7</v>
@@ -2907,21 +2907,21 @@
       </c>
       <c r="B35" s="15" t="inlineStr">
         <is>
-          <t>38456</t>
+          <t>38965</t>
         </is>
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>Plaza las Flores</t>
+          <t>Parque Tepeyac Piso 2</t>
         </is>
       </c>
       <c r="D35" s="12" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E35" s="11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F35" s="11" t="n">
         <v>7</v>
@@ -2947,12 +2947,12 @@
       </c>
       <c r="B36" s="17" t="inlineStr">
         <is>
-          <t>43152</t>
+          <t>38427</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>Samara Satélite</t>
+          <t>Plaza Satelite</t>
         </is>
       </c>
       <c r="D36" s="8" t="inlineStr">
@@ -2961,7 +2961,7 @@
         </is>
       </c>
       <c r="E36" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F36" s="7" t="n">
         <v>7</v>
@@ -2987,24 +2987,24 @@
       </c>
       <c r="B37" s="15" t="inlineStr">
         <is>
-          <t>43194</t>
+          <t>38992</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>Atana Lindavista</t>
+          <t>Tapo Puerta Oriente</t>
         </is>
       </c>
       <c r="D37" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E37" s="11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G37" s="13">
         <f>IFERROR(E37/(E37+F37),0)</f>
@@ -3027,24 +3027,24 @@
       </c>
       <c r="B38" s="17" t="inlineStr">
         <is>
-          <t>38529</t>
+          <t>38604</t>
         </is>
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>Bosques de Aragon</t>
+          <t>Cosmopol</t>
         </is>
       </c>
       <c r="D38" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E38" s="7" t="n">
         <v>3</v>
       </c>
       <c r="F38" s="7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G38" s="9">
         <f>IFERROR(E38/(E38+F38),0)</f>
@@ -3067,24 +3067,24 @@
       </c>
       <c r="B39" s="15" t="inlineStr">
         <is>
-          <t>38431</t>
+          <t>38770</t>
         </is>
       </c>
       <c r="C39" s="12" t="inlineStr">
         <is>
-          <t>Eduardo Molina</t>
+          <t>Gustavo Baz 29</t>
         </is>
       </c>
       <c r="D39" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E39" s="11" t="n">
         <v>3</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G39" s="13">
         <f>IFERROR(E39/(E39+F39),0)</f>
@@ -3107,24 +3107,24 @@
       </c>
       <c r="B40" s="17" t="inlineStr">
         <is>
-          <t>38965</t>
+          <t>38456</t>
         </is>
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>Parque Tepeyac Piso 2</t>
+          <t>Plaza las Flores</t>
         </is>
       </c>
       <c r="D40" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E40" s="7" t="n">
         <v>3</v>
       </c>
       <c r="F40" s="7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G40" s="9">
         <f>IFERROR(E40/(E40+F40),0)</f>
@@ -3147,24 +3147,24 @@
       </c>
       <c r="B41" s="15" t="inlineStr">
         <is>
-          <t>38792</t>
+          <t>43152</t>
         </is>
       </c>
       <c r="C41" s="12" t="inlineStr">
         <is>
-          <t>Pasaje Tlanepantla</t>
+          <t>Samara Satélite</t>
         </is>
       </c>
       <c r="D41" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E41" s="11" t="n">
         <v>3</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G41" s="13">
         <f>IFERROR(E41/(E41+F41),0)</f>
@@ -3187,17 +3187,17 @@
       </c>
       <c r="B42" s="17" t="inlineStr">
         <is>
-          <t>38924</t>
+          <t>43194</t>
         </is>
       </c>
       <c r="C42" s="8" t="inlineStr">
         <is>
-          <t>Plaza Aeropuerto</t>
+          <t>Atana Lindavista</t>
         </is>
       </c>
       <c r="D42" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E42" s="7" t="n">
@@ -3227,12 +3227,12 @@
       </c>
       <c r="B43" s="15" t="inlineStr">
         <is>
-          <t>38811</t>
+          <t>38529</t>
         </is>
       </c>
       <c r="C43" s="12" t="inlineStr">
         <is>
-          <t>Plaza Tepeyac</t>
+          <t>Bosques de Aragon</t>
         </is>
       </c>
       <c r="D43" s="12" t="inlineStr">
@@ -3267,12 +3267,12 @@
       </c>
       <c r="B44" s="17" t="inlineStr">
         <is>
-          <t>38136</t>
+          <t>38792</t>
         </is>
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t>Punta Norte</t>
+          <t>Pasaje Tlanepantla</t>
         </is>
       </c>
       <c r="D44" s="8" t="inlineStr">
@@ -3307,17 +3307,17 @@
       </c>
       <c r="B45" s="15" t="inlineStr">
         <is>
-          <t>38651</t>
+          <t>38811</t>
         </is>
       </c>
       <c r="C45" s="12" t="inlineStr">
         <is>
-          <t>Via Vallejo</t>
+          <t>Plaza Tepeyac</t>
         </is>
       </c>
       <c r="D45" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E45" s="11" t="n">
@@ -3347,12 +3347,12 @@
       </c>
       <c r="B46" s="17" t="inlineStr">
         <is>
-          <t>38186</t>
+          <t>38136</t>
         </is>
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t>Arboledas</t>
+          <t>Punta Norte</t>
         </is>
       </c>
       <c r="D46" s="8" t="inlineStr">
@@ -3361,10 +3361,10 @@
         </is>
       </c>
       <c r="E46" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F46" s="7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G46" s="9">
         <f>IFERROR(E46/(E46+F46),0)</f>
@@ -3387,24 +3387,24 @@
       </c>
       <c r="B47" s="15" t="inlineStr">
         <is>
-          <t>43043</t>
+          <t>38651</t>
         </is>
       </c>
       <c r="C47" s="12" t="inlineStr">
         <is>
-          <t>Atizapan</t>
+          <t>Via Vallejo</t>
         </is>
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E47" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G47" s="13">
         <f>IFERROR(E47/(E47+F47),0)</f>
@@ -3427,17 +3427,17 @@
       </c>
       <c r="B48" s="17" t="inlineStr">
         <is>
-          <t>38149</t>
+          <t>38186</t>
         </is>
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
-          <t>Bellavista</t>
+          <t>Arboledas</t>
         </is>
       </c>
       <c r="D48" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E48" s="7" t="n">
@@ -3467,17 +3467,17 @@
       </c>
       <c r="B49" s="15" t="inlineStr">
         <is>
-          <t>38527</t>
+          <t>43043</t>
         </is>
       </c>
       <c r="C49" s="12" t="inlineStr">
         <is>
-          <t>Camarones</t>
+          <t>Atizapan</t>
         </is>
       </c>
       <c r="D49" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E49" s="11" t="n">
@@ -3507,17 +3507,17 @@
       </c>
       <c r="B50" s="17" t="inlineStr">
         <is>
-          <t>38837</t>
+          <t>38149</t>
         </is>
       </c>
       <c r="C50" s="8" t="inlineStr">
         <is>
-          <t>Centenario Azcapotzalco</t>
+          <t>Bellavista</t>
         </is>
       </c>
       <c r="D50" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E50" s="7" t="n">
@@ -3547,17 +3547,17 @@
       </c>
       <c r="B51" s="15" t="inlineStr">
         <is>
-          <t>38394</t>
+          <t>38527</t>
         </is>
       </c>
       <c r="C51" s="12" t="inlineStr">
         <is>
-          <t>Centro Comercial Lomas Verdes</t>
+          <t>Camarones</t>
         </is>
       </c>
       <c r="D51" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E51" s="11" t="n">
@@ -3587,17 +3587,17 @@
       </c>
       <c r="B52" s="17" t="inlineStr">
         <is>
-          <t>38535</t>
+          <t>38837</t>
         </is>
       </c>
       <c r="C52" s="8" t="inlineStr">
         <is>
-          <t>City Center Esmeralda</t>
+          <t>Centenario Azcapotzalco</t>
         </is>
       </c>
       <c r="D52" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E52" s="7" t="n">
@@ -3627,12 +3627,12 @@
       </c>
       <c r="B53" s="15" t="inlineStr">
         <is>
-          <t>38507</t>
+          <t>38394</t>
         </is>
       </c>
       <c r="C53" s="12" t="inlineStr">
         <is>
-          <t>Espacio Vista del Valle</t>
+          <t>Centro Comercial Lomas Verdes</t>
         </is>
       </c>
       <c r="D53" s="12" t="inlineStr">
@@ -3667,12 +3667,12 @@
       </c>
       <c r="B54" s="17" t="inlineStr">
         <is>
-          <t>38363</t>
+          <t>38535</t>
         </is>
       </c>
       <c r="C54" s="8" t="inlineStr">
         <is>
-          <t>Galerias Atizapan</t>
+          <t>City Center Esmeralda</t>
         </is>
       </c>
       <c r="D54" s="8" t="inlineStr">
@@ -3707,17 +3707,17 @@
       </c>
       <c r="B55" s="15" t="inlineStr">
         <is>
-          <t>38205</t>
+          <t>38507</t>
         </is>
       </c>
       <c r="C55" s="12" t="inlineStr">
         <is>
-          <t>Lindavista</t>
+          <t>Espacio Vista del Valle</t>
         </is>
       </c>
       <c r="D55" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E55" s="11" t="n">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="B56" s="17" t="inlineStr">
         <is>
-          <t>38119</t>
+          <t>38363</t>
         </is>
       </c>
       <c r="C56" s="8" t="inlineStr">
         <is>
-          <t>Lomas Verdes</t>
+          <t>Galerias Atizapan</t>
         </is>
       </c>
       <c r="D56" s="8" t="inlineStr">
@@ -3787,17 +3787,17 @@
       </c>
       <c r="B57" s="15" t="inlineStr">
         <is>
-          <t>38270</t>
+          <t>38205</t>
         </is>
       </c>
       <c r="C57" s="12" t="inlineStr">
         <is>
-          <t>Lomas Verdes II</t>
+          <t>Lindavista</t>
         </is>
       </c>
       <c r="D57" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E57" s="11" t="n">
@@ -3827,17 +3827,17 @@
       </c>
       <c r="B58" s="17" t="inlineStr">
         <is>
-          <t>38371</t>
+          <t>38119</t>
         </is>
       </c>
       <c r="C58" s="8" t="inlineStr">
         <is>
-          <t>Montevideo DT</t>
+          <t>Lomas Verdes</t>
         </is>
       </c>
       <c r="D58" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E58" s="7" t="n">
@@ -3867,17 +3867,17 @@
       </c>
       <c r="B59" s="15" t="inlineStr">
         <is>
-          <t>43111</t>
+          <t>38270</t>
         </is>
       </c>
       <c r="C59" s="12" t="inlineStr">
         <is>
-          <t>Montevideo Insurgentes</t>
+          <t>Lomas Verdes II</t>
         </is>
       </c>
       <c r="D59" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E59" s="11" t="n">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="B60" s="17" t="inlineStr">
         <is>
-          <t>43195</t>
+          <t>38371</t>
         </is>
       </c>
       <c r="C60" s="8" t="inlineStr">
         <is>
-          <t>Parque Jadin kiosko</t>
+          <t>Montevideo DT</t>
         </is>
       </c>
       <c r="D60" s="8" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="B61" s="15" t="inlineStr">
         <is>
-          <t>38546</t>
+          <t>43111</t>
         </is>
       </c>
       <c r="C61" s="12" t="inlineStr">
         <is>
-          <t>Patio Claveria</t>
+          <t>Montevideo Insurgentes</t>
         </is>
       </c>
       <c r="D61" s="12" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="B62" s="17" t="inlineStr">
         <is>
-          <t>38677</t>
+          <t>43195</t>
         </is>
       </c>
       <c r="C62" s="8" t="inlineStr">
         <is>
-          <t>Patio la Raza</t>
+          <t>Parque Jadin kiosko</t>
         </is>
       </c>
       <c r="D62" s="8" t="inlineStr">
@@ -4027,12 +4027,12 @@
       </c>
       <c r="B63" s="15" t="inlineStr">
         <is>
-          <t>43132</t>
+          <t>38546</t>
         </is>
       </c>
       <c r="C63" s="12" t="inlineStr">
         <is>
-          <t>Plaza Vista Norte</t>
+          <t>Patio Claveria</t>
         </is>
       </c>
       <c r="D63" s="12" t="inlineStr">
@@ -4067,17 +4067,17 @@
       </c>
       <c r="B64" s="17" t="inlineStr">
         <is>
-          <t>38460</t>
+          <t>38677</t>
         </is>
       </c>
       <c r="C64" s="8" t="inlineStr">
         <is>
-          <t>Santa Monica</t>
+          <t>Patio la Raza</t>
         </is>
       </c>
       <c r="D64" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E64" s="7" t="n">
@@ -4107,17 +4107,17 @@
       </c>
       <c r="B65" s="15" t="inlineStr">
         <is>
-          <t>38442</t>
+          <t>43132</t>
         </is>
       </c>
       <c r="C65" s="12" t="inlineStr">
         <is>
-          <t>Sor Juana</t>
+          <t>Plaza Vista Norte</t>
         </is>
       </c>
       <c r="D65" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E65" s="11" t="n">
@@ -4147,17 +4147,17 @@
       </c>
       <c r="B66" s="17" t="inlineStr">
         <is>
-          <t>38925</t>
+          <t>38460</t>
         </is>
       </c>
       <c r="C66" s="8" t="inlineStr">
         <is>
-          <t>Star Medica Lomas Verdes</t>
+          <t>Santa Monica</t>
         </is>
       </c>
       <c r="D66" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E66" s="7" t="n">
@@ -4187,17 +4187,17 @@
       </c>
       <c r="B67" s="15" t="inlineStr">
         <is>
-          <t>38411</t>
+          <t>38442</t>
         </is>
       </c>
       <c r="C67" s="12" t="inlineStr">
         <is>
-          <t>Torres Lindavista</t>
+          <t>Sor Juana</t>
         </is>
       </c>
       <c r="D67" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E67" s="11" t="n">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="B68" s="17" t="inlineStr">
         <is>
-          <t>43130</t>
+          <t>38925</t>
         </is>
       </c>
       <c r="C68" s="8" t="inlineStr">
         <is>
-          <t>Town Center Nicolás Romero</t>
+          <t>Star Medica Lomas Verdes</t>
         </is>
       </c>
       <c r="D68" s="8" t="inlineStr">
@@ -4267,17 +4267,17 @@
       </c>
       <c r="B69" s="15" t="inlineStr">
         <is>
-          <t>38694</t>
+          <t>38411</t>
         </is>
       </c>
       <c r="C69" s="12" t="inlineStr">
         <is>
-          <t>Villas de la Hacienda</t>
+          <t>Torres Lindavista</t>
         </is>
       </c>
       <c r="D69" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E69" s="11" t="n">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="B70" s="17" t="inlineStr">
         <is>
-          <t>38115</t>
+          <t>43130</t>
         </is>
       </c>
       <c r="C70" s="8" t="inlineStr">
         <is>
-          <t>Zona Azul</t>
+          <t>Town Center Nicolás Romero</t>
         </is>
       </c>
       <c r="D70" s="8" t="inlineStr">
@@ -4347,17 +4347,17 @@
       </c>
       <c r="B71" s="15" t="inlineStr">
         <is>
-          <t>38142</t>
+          <t>38694</t>
         </is>
       </c>
       <c r="C71" s="12" t="inlineStr">
         <is>
-          <t>Zona Esmeralda</t>
+          <t>Villas de la Hacienda</t>
         </is>
       </c>
       <c r="D71" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E71" s="11" t="n">
@@ -4387,21 +4387,21 @@
       </c>
       <c r="B72" s="17" t="inlineStr">
         <is>
-          <t>38207</t>
+          <t>38115</t>
         </is>
       </c>
       <c r="C72" s="8" t="inlineStr">
         <is>
-          <t>Lindavista II</t>
+          <t>Zona Azul</t>
         </is>
       </c>
       <c r="D72" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E72" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F72" s="7" t="n">
         <v>9</v>
@@ -4427,21 +4427,21 @@
       </c>
       <c r="B73" s="15" t="inlineStr">
         <is>
-          <t>38845</t>
+          <t>38142</t>
         </is>
       </c>
       <c r="C73" s="12" t="inlineStr">
         <is>
-          <t>Mundo E II</t>
+          <t>Zona Esmeralda</t>
         </is>
       </c>
       <c r="D73" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E73" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F73" s="11" t="n">
         <v>9</v>
@@ -4467,17 +4467,17 @@
       </c>
       <c r="B74" s="17" t="inlineStr">
         <is>
-          <t>38266</t>
+          <t>38207</t>
         </is>
       </c>
       <c r="C74" s="8" t="inlineStr">
         <is>
-          <t>San Mateo</t>
+          <t>Lindavista II</t>
         </is>
       </c>
       <c r="D74" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E74" s="7" t="n">
@@ -4507,24 +4507,24 @@
       </c>
       <c r="B75" s="15" t="inlineStr">
         <is>
-          <t>38176</t>
+          <t>38845</t>
         </is>
       </c>
       <c r="C75" s="12" t="inlineStr">
         <is>
-          <t>Periferico Satélite DT</t>
+          <t>Mundo E II</t>
         </is>
       </c>
       <c r="D75" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E75" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F75" s="11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G75" s="13">
         <f>IFERROR(E75/(E75+F75),0)</f>
@@ -4547,24 +4547,24 @@
       </c>
       <c r="B76" s="17" t="inlineStr">
         <is>
-          <t>38656</t>
+          <t>38266</t>
         </is>
       </c>
       <c r="C76" s="8" t="inlineStr">
         <is>
-          <t>Viveros de la Loma</t>
+          <t>San Mateo</t>
         </is>
       </c>
       <c r="D76" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E76" s="7" t="n">
         <v>1</v>
       </c>
       <c r="F76" s="7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G76" s="9">
         <f>IFERROR(E76/(E76+F76),0)</f>
@@ -16032,7 +16032,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Todas las regiones · Corte 03/09/2026 13:44</t>
+          <t>Todas las regiones · Corte 03/09/2026 20:28</t>
         </is>
       </c>
     </row>
@@ -16088,10 +16088,10 @@
         </is>
       </c>
       <c r="C5" s="11" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D5" s="11" t="n">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="E5" s="13">
         <f>IFERROR(C5/(C5+D5),0)</f>
@@ -16123,10 +16123,10 @@
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D6" s="7" t="n">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="E6" s="9">
         <f>IFERROR(C6/(C6+D6),0)</f>
@@ -16158,10 +16158,10 @@
         </is>
       </c>
       <c r="C7" s="11" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="E7" s="13">
         <f>IFERROR(C7/(C7+D7),0)</f>
@@ -16193,10 +16193,10 @@
         </is>
       </c>
       <c r="C8" s="7" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="E8" s="9">
         <f>IFERROR(C8/(C8+D8),0)</f>
@@ -16228,10 +16228,10 @@
         </is>
       </c>
       <c r="C9" s="11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D9" s="11" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="E9" s="13">
         <f>IFERROR(C9/(C9+D9),0)</f>
@@ -16263,10 +16263,10 @@
         </is>
       </c>
       <c r="C10" s="7" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="E10" s="9">
         <f>IFERROR(C10/(C10+D10),0)</f>
@@ -16298,10 +16298,10 @@
         </is>
       </c>
       <c r="C11" s="11" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E11" s="13">
         <f>IFERROR(C11/(C11+D11),0)</f>
@@ -16333,10 +16333,10 @@
         </is>
       </c>
       <c r="C12" s="7" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="E12" s="9">
         <f>IFERROR(C12/(C12+D12),0)</f>
@@ -16403,10 +16403,10 @@
         </is>
       </c>
       <c r="C14" s="7" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="E14" s="9">
         <f>IFERROR(C14/(C14+D14),0)</f>
@@ -16438,10 +16438,10 @@
         </is>
       </c>
       <c r="C15" s="11" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D15" s="11" t="n">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="E15" s="13">
         <f>IFERROR(C15/(C15+D15),0)</f>

--- a/exports/Resumen_Evidencias_OPS.xlsx
+++ b/exports/Resumen_Evidencias_OPS.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Resumen" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Tiendas" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Actividades" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tiendas" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Actividades" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Resumen'!$A$9:$H$37</definedName>

--- a/exports/Resumen_Evidencias_OPS.xlsx
+++ b/exports/Resumen_Evidencias_OPS.xlsx
@@ -592,7 +592,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Todas las regiones · Corte 03/09/2026 20:28</t>
+          <t>Todas las regiones · Corte 04/09/2026 11:51</t>
         </is>
       </c>
     </row>
@@ -615,10 +615,10 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>3626</v>
+        <v>3624</v>
       </c>
       <c r="E6" s="5">
         <f>IFERROR(A6/(A6+C6),0)</f>
@@ -681,10 +681,10 @@
         <v>13</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F10" s="9">
         <f>IFERROR(D10/(D10+E10),0)</f>
@@ -747,10 +747,10 @@
         <v>11</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E12" s="8" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F12" s="9">
         <f>IFERROR(D12/(D12+E12),0)</f>
@@ -1650,7 +1650,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Todas las regiones · Corte 03/09/2026 20:28</t>
+          <t>Todas las regiones · Corte 04/09/2026 11:51</t>
         </is>
       </c>
     </row>
@@ -2467,21 +2467,21 @@
       </c>
       <c r="B24" s="17" t="inlineStr">
         <is>
-          <t>43193</t>
+          <t>38656</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>Cosmopol N1</t>
+          <t>Viveros de la Loma</t>
         </is>
       </c>
       <c r="D24" s="8" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E24" s="7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F24" s="7" t="n">
         <v>5</v>
@@ -2507,12 +2507,12 @@
       </c>
       <c r="B25" s="15" t="inlineStr">
         <is>
-          <t>38894</t>
+          <t>43193</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>Galerias Perinorte</t>
+          <t>Cosmopol N1</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
@@ -2524,7 +2524,7 @@
         <v>5</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G25" s="13">
         <f>IFERROR(E25/(E25+F25),0)</f>
@@ -2547,17 +2547,17 @@
       </c>
       <c r="B26" s="17" t="inlineStr">
         <is>
-          <t>38924</t>
+          <t>38894</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>Plaza Aeropuerto</t>
+          <t>Galerias Perinorte</t>
         </is>
       </c>
       <c r="D26" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E26" s="7" t="n">
@@ -2587,17 +2587,17 @@
       </c>
       <c r="B27" s="15" t="inlineStr">
         <is>
-          <t>38606</t>
+          <t>38924</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>TlalnepantlaCarso</t>
+          <t>Plaza Aeropuerto</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E27" s="11" t="n">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="B28" s="17" t="inlineStr">
         <is>
-          <t>38374</t>
+          <t>38606</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>Valle Dorado</t>
+          <t>TlalnepantlaCarso</t>
         </is>
       </c>
       <c r="D28" s="8" t="inlineStr">
@@ -2667,17 +2667,17 @@
       </c>
       <c r="B29" s="15" t="inlineStr">
         <is>
-          <t>38656</t>
+          <t>38374</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>Viveros de la Loma</t>
+          <t>Valle Dorado</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E29" s="11" t="n">
@@ -2987,12 +2987,12 @@
       </c>
       <c r="B37" s="15" t="inlineStr">
         <is>
-          <t>38992</t>
+          <t>38811</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>Tapo Puerta Oriente</t>
+          <t>Plaza Tepeyac</t>
         </is>
       </c>
       <c r="D37" s="12" t="inlineStr">
@@ -3027,21 +3027,21 @@
       </c>
       <c r="B38" s="17" t="inlineStr">
         <is>
-          <t>38604</t>
+          <t>38992</t>
         </is>
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>Cosmopol</t>
+          <t>Tapo Puerta Oriente</t>
         </is>
       </c>
       <c r="D38" s="8" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E38" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F38" s="7" t="n">
         <v>7</v>
@@ -3067,17 +3067,17 @@
       </c>
       <c r="B39" s="15" t="inlineStr">
         <is>
-          <t>38770</t>
+          <t>38604</t>
         </is>
       </c>
       <c r="C39" s="12" t="inlineStr">
         <is>
-          <t>Gustavo Baz 29</t>
+          <t>Cosmopol</t>
         </is>
       </c>
       <c r="D39" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E39" s="11" t="n">
@@ -3107,17 +3107,17 @@
       </c>
       <c r="B40" s="17" t="inlineStr">
         <is>
-          <t>38456</t>
+          <t>38770</t>
         </is>
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>Plaza las Flores</t>
+          <t>Gustavo Baz 29</t>
         </is>
       </c>
       <c r="D40" s="8" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E40" s="7" t="n">
@@ -3147,17 +3147,17 @@
       </c>
       <c r="B41" s="15" t="inlineStr">
         <is>
-          <t>43152</t>
+          <t>38456</t>
         </is>
       </c>
       <c r="C41" s="12" t="inlineStr">
         <is>
-          <t>Samara Satélite</t>
+          <t>Plaza las Flores</t>
         </is>
       </c>
       <c r="D41" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E41" s="11" t="n">
@@ -3187,24 +3187,24 @@
       </c>
       <c r="B42" s="17" t="inlineStr">
         <is>
-          <t>43194</t>
+          <t>43152</t>
         </is>
       </c>
       <c r="C42" s="8" t="inlineStr">
         <is>
-          <t>Atana Lindavista</t>
+          <t>Samara Satélite</t>
         </is>
       </c>
       <c r="D42" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E42" s="7" t="n">
         <v>3</v>
       </c>
       <c r="F42" s="7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G42" s="9">
         <f>IFERROR(E42/(E42+F42),0)</f>
@@ -3227,17 +3227,17 @@
       </c>
       <c r="B43" s="15" t="inlineStr">
         <is>
-          <t>38529</t>
+          <t>43194</t>
         </is>
       </c>
       <c r="C43" s="12" t="inlineStr">
         <is>
-          <t>Bosques de Aragon</t>
+          <t>Atana Lindavista</t>
         </is>
       </c>
       <c r="D43" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E43" s="11" t="n">
@@ -3267,17 +3267,17 @@
       </c>
       <c r="B44" s="17" t="inlineStr">
         <is>
-          <t>38792</t>
+          <t>38529</t>
         </is>
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t>Pasaje Tlanepantla</t>
+          <t>Bosques de Aragon</t>
         </is>
       </c>
       <c r="D44" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E44" s="7" t="n">
@@ -3307,17 +3307,17 @@
       </c>
       <c r="B45" s="15" t="inlineStr">
         <is>
-          <t>38811</t>
+          <t>38792</t>
         </is>
       </c>
       <c r="C45" s="12" t="inlineStr">
         <is>
-          <t>Plaza Tepeyac</t>
+          <t>Pasaje Tlanepantla</t>
         </is>
       </c>
       <c r="D45" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E45" s="11" t="n">
@@ -16032,7 +16032,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Todas las regiones · Corte 03/09/2026 20:28</t>
+          <t>Todas las regiones · Corte 04/09/2026 11:51</t>
         </is>
       </c>
     </row>
@@ -16158,10 +16158,10 @@
         </is>
       </c>
       <c r="C7" s="11" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="E7" s="13">
         <f>IFERROR(C7/(C7+D7),0)</f>
@@ -16333,10 +16333,10 @@
         </is>
       </c>
       <c r="C12" s="7" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="E12" s="9">
         <f>IFERROR(C12/(C12+D12),0)</f>

--- a/exports/Resumen_Evidencias_OPS.xlsx
+++ b/exports/Resumen_Evidencias_OPS.xlsx
@@ -592,7 +592,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Todas las regiones · Corte 04/09/2026 11:51</t>
+          <t>Todas las regiones · Corte 04/09/2026 13:56</t>
         </is>
       </c>
     </row>
@@ -615,10 +615,10 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>3624</v>
+        <v>3621</v>
       </c>
       <c r="E6" s="5">
         <f>IFERROR(A6/(A6+C6),0)</f>
@@ -681,10 +681,10 @@
         <v>13</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="F10" s="9">
         <f>IFERROR(D10/(D10+E10),0)</f>
@@ -1650,7 +1650,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Todas las regiones · Corte 04/09/2026 11:51</t>
+          <t>Todas las regiones · Corte 04/09/2026 13:56</t>
         </is>
       </c>
     </row>
@@ -1907,12 +1907,12 @@
       </c>
       <c r="B10" s="17" t="inlineStr">
         <is>
-          <t>38197</t>
+          <t>38859</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>Echegaray</t>
+          <t>Plaza Satelite II N1</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
@@ -1924,20 +1924,20 @@
         <v>8</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G10" s="9">
         <f>IFERROR(E10/(E10+F10),0)</f>
         <v/>
       </c>
-      <c r="H10" s="10" t="inlineStr">
-        <is>
-          <t>Seguimiento</t>
-        </is>
-      </c>
-      <c r="I10" s="10" t="inlineStr">
-        <is>
-          <t>Dar seguimiento</t>
+      <c r="H10" s="16" t="inlineStr">
+        <is>
+          <t>En meta</t>
+        </is>
+      </c>
+      <c r="I10" s="16" t="inlineStr">
+        <is>
+          <t>Mantener estándar</t>
         </is>
       </c>
     </row>
@@ -1947,12 +1947,12 @@
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>38458</t>
+          <t>38197</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>El Rosario</t>
+          <t>Echegaray</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
@@ -1987,17 +1987,17 @@
       </c>
       <c r="B12" s="17" t="inlineStr">
         <is>
-          <t>38903</t>
+          <t>38458</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Encuentro Oceania</t>
+          <t>El Rosario</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E12" s="7" t="n">
@@ -2027,21 +2027,21 @@
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>38590</t>
+          <t>38903</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>Parque Toreo II</t>
+          <t>Encuentro Oceania</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E13" s="11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F13" s="11" t="n">
         <v>3</v>
@@ -2067,12 +2067,12 @@
       </c>
       <c r="B14" s="17" t="inlineStr">
         <is>
-          <t>38859</t>
+          <t>38590</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Plaza Satelite II N1</t>
+          <t>Parque Toreo II</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr">
@@ -2547,24 +2547,24 @@
       </c>
       <c r="B26" s="17" t="inlineStr">
         <is>
-          <t>38894</t>
+          <t>43152</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>Galerias Perinorte</t>
+          <t>Samara Satélite</t>
         </is>
       </c>
       <c r="D26" s="8" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E26" s="7" t="n">
         <v>5</v>
       </c>
       <c r="F26" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G26" s="9">
         <f>IFERROR(E26/(E26+F26),0)</f>
@@ -2587,17 +2587,17 @@
       </c>
       <c r="B27" s="15" t="inlineStr">
         <is>
-          <t>38924</t>
+          <t>38894</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>Plaza Aeropuerto</t>
+          <t>Galerias Perinorte</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E27" s="11" t="n">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="B28" s="17" t="inlineStr">
         <is>
-          <t>38606</t>
+          <t>38924</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>TlalnepantlaCarso</t>
+          <t>Plaza Aeropuerto</t>
         </is>
       </c>
       <c r="D28" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E28" s="7" t="n">
@@ -2667,12 +2667,12 @@
       </c>
       <c r="B29" s="15" t="inlineStr">
         <is>
-          <t>38374</t>
+          <t>38606</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>Valle Dorado</t>
+          <t>TlalnepantlaCarso</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr">
@@ -2707,37 +2707,37 @@
       </c>
       <c r="B30" s="17" t="inlineStr">
         <is>
-          <t>38930</t>
+          <t>38374</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>Blvd. Aeropuerto dt</t>
+          <t>Valle Dorado</t>
         </is>
       </c>
       <c r="D30" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E30" s="7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F30" s="7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G30" s="9">
         <f>IFERROR(E30/(E30+F30),0)</f>
         <v/>
       </c>
-      <c r="H30" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I30" s="14" t="inlineStr">
-        <is>
-          <t>Priorizar hoy</t>
+      <c r="H30" s="10" t="inlineStr">
+        <is>
+          <t>Seguimiento</t>
+        </is>
+      </c>
+      <c r="I30" s="10" t="inlineStr">
+        <is>
+          <t>Dar seguimiento</t>
         </is>
       </c>
     </row>
@@ -2747,12 +2747,12 @@
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>38431</t>
+          <t>38930</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>Eduardo Molina</t>
+          <t>Blvd. Aeropuerto dt</t>
         </is>
       </c>
       <c r="D31" s="12" t="inlineStr">
@@ -2787,12 +2787,12 @@
       </c>
       <c r="B32" s="17" t="inlineStr">
         <is>
-          <t>38995</t>
+          <t>38431</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>Encuentro Oceania II</t>
+          <t>Eduardo Molina</t>
         </is>
       </c>
       <c r="D32" s="8" t="inlineStr">
@@ -2827,17 +2827,17 @@
       </c>
       <c r="B33" s="15" t="inlineStr">
         <is>
-          <t>38230</t>
+          <t>38995</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>ITEMS Edo de Mexico</t>
+          <t>Encuentro Oceania II</t>
         </is>
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E33" s="11" t="n">
@@ -2867,17 +2867,17 @@
       </c>
       <c r="B34" s="17" t="inlineStr">
         <is>
-          <t>38937</t>
+          <t>38230</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>Parque Tepeyac Piso 1</t>
+          <t>ITEMS Edo de Mexico</t>
         </is>
       </c>
       <c r="D34" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E34" s="7" t="n">
@@ -2907,12 +2907,12 @@
       </c>
       <c r="B35" s="15" t="inlineStr">
         <is>
-          <t>38965</t>
+          <t>38937</t>
         </is>
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>Parque Tepeyac Piso 2</t>
+          <t>Parque Tepeyac Piso 1</t>
         </is>
       </c>
       <c r="D35" s="12" t="inlineStr">
@@ -2947,17 +2947,17 @@
       </c>
       <c r="B36" s="17" t="inlineStr">
         <is>
-          <t>38427</t>
+          <t>38965</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>Plaza Satelite</t>
+          <t>Parque Tepeyac Piso 2</t>
         </is>
       </c>
       <c r="D36" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E36" s="7" t="n">
@@ -2987,17 +2987,17 @@
       </c>
       <c r="B37" s="15" t="inlineStr">
         <is>
-          <t>38811</t>
+          <t>38427</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>Plaza Tepeyac</t>
+          <t>Plaza Satelite</t>
         </is>
       </c>
       <c r="D37" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E37" s="11" t="n">
@@ -3027,12 +3027,12 @@
       </c>
       <c r="B38" s="17" t="inlineStr">
         <is>
-          <t>38992</t>
+          <t>38811</t>
         </is>
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>Tapo Puerta Oriente</t>
+          <t>Plaza Tepeyac</t>
         </is>
       </c>
       <c r="D38" s="8" t="inlineStr">
@@ -3067,21 +3067,21 @@
       </c>
       <c r="B39" s="15" t="inlineStr">
         <is>
-          <t>38604</t>
+          <t>38992</t>
         </is>
       </c>
       <c r="C39" s="12" t="inlineStr">
         <is>
-          <t>Cosmopol</t>
+          <t>Tapo Puerta Oriente</t>
         </is>
       </c>
       <c r="D39" s="12" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E39" s="11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F39" s="11" t="n">
         <v>7</v>
@@ -3107,17 +3107,17 @@
       </c>
       <c r="B40" s="17" t="inlineStr">
         <is>
-          <t>38770</t>
+          <t>38604</t>
         </is>
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>Gustavo Baz 29</t>
+          <t>Cosmopol</t>
         </is>
       </c>
       <c r="D40" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E40" s="7" t="n">
@@ -3147,17 +3147,17 @@
       </c>
       <c r="B41" s="15" t="inlineStr">
         <is>
-          <t>38456</t>
+          <t>38770</t>
         </is>
       </c>
       <c r="C41" s="12" t="inlineStr">
         <is>
-          <t>Plaza las Flores</t>
+          <t>Gustavo Baz 29</t>
         </is>
       </c>
       <c r="D41" s="12" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E41" s="11" t="n">
@@ -3187,17 +3187,17 @@
       </c>
       <c r="B42" s="17" t="inlineStr">
         <is>
-          <t>43152</t>
+          <t>38456</t>
         </is>
       </c>
       <c r="C42" s="8" t="inlineStr">
         <is>
-          <t>Samara Satélite</t>
+          <t>Plaza las Flores</t>
         </is>
       </c>
       <c r="D42" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E42" s="7" t="n">
@@ -16032,7 +16032,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Todas las regiones · Corte 04/09/2026 11:51</t>
+          <t>Todas las regiones · Corte 04/09/2026 13:56</t>
         </is>
       </c>
     </row>
@@ -16158,10 +16158,10 @@
         </is>
       </c>
       <c r="C7" s="11" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="E7" s="13">
         <f>IFERROR(C7/(C7+D7),0)</f>
@@ -16403,10 +16403,10 @@
         </is>
       </c>
       <c r="C14" s="7" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="E14" s="9">
         <f>IFERROR(C14/(C14+D14),0)</f>

--- a/exports/Resumen_Evidencias_OPS.xlsx
+++ b/exports/Resumen_Evidencias_OPS.xlsx
@@ -592,7 +592,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Todas las regiones · Corte 04/09/2026 13:56</t>
+          <t>Todas las regiones · Corte 04/09/2026 14:02</t>
         </is>
       </c>
     </row>
@@ -615,10 +615,10 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>3621</v>
+        <v>3620</v>
       </c>
       <c r="E6" s="5">
         <f>IFERROR(A6/(A6+C6),0)</f>
@@ -681,10 +681,10 @@
         <v>13</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F10" s="9">
         <f>IFERROR(D10/(D10+E10),0)</f>
@@ -1650,7 +1650,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Todas las regiones · Corte 04/09/2026 13:56</t>
+          <t>Todas las regiones · Corte 04/09/2026 14:02</t>
         </is>
       </c>
     </row>
@@ -1747,12 +1747,12 @@
       </c>
       <c r="B6" s="17" t="inlineStr">
         <is>
-          <t>38117</t>
+          <t>38859</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>Satelite</t>
+          <t>Plaza Satelite II N1</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
@@ -1787,12 +1787,12 @@
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>38695</t>
+          <t>38117</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>Cetram 4 Caminos</t>
+          <t>Satelite</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
@@ -1804,7 +1804,7 @@
         <v>9</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G7" s="13">
         <f>IFERROR(E7/(E7+F7),0)</f>
@@ -1827,12 +1827,12 @@
       </c>
       <c r="B8" s="17" t="inlineStr">
         <is>
-          <t>38561</t>
+          <t>38695</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>Parque Toreo</t>
+          <t>Cetram 4 Caminos</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
@@ -1867,17 +1867,17 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>38719</t>
+          <t>38561</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>Plaza Fortuna</t>
+          <t>Parque Toreo</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E9" s="11" t="n">
@@ -1907,21 +1907,21 @@
       </c>
       <c r="B10" s="17" t="inlineStr">
         <is>
-          <t>38859</t>
+          <t>38719</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>Plaza Satelite II N1</t>
+          <t>Plaza Fortuna</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E10" s="7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F10" s="7" t="n">
         <v>2</v>
@@ -16032,7 +16032,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Todas las regiones · Corte 04/09/2026 13:56</t>
+          <t>Todas las regiones · Corte 04/09/2026 14:02</t>
         </is>
       </c>
     </row>
@@ -16228,10 +16228,10 @@
         </is>
       </c>
       <c r="C9" s="11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D9" s="11" t="n">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="E9" s="13">
         <f>IFERROR(C9/(C9+D9),0)</f>

--- a/exports/Resumen_Evidencias_OPS.xlsx
+++ b/exports/Resumen_Evidencias_OPS.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Resumen" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Tiendas" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Actividades" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tiendas" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Actividades" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Resumen'!$A$9:$H$37</definedName>
@@ -592,7 +592,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Todas las regiones · Corte 04/09/2026 14:02</t>
+          <t>Todas las regiones · Corte 04/09/2026 14:30</t>
         </is>
       </c>
     </row>
@@ -615,10 +615,10 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>3620</v>
+        <v>3619</v>
       </c>
       <c r="E6" s="5">
         <f>IFERROR(A6/(A6+C6),0)</f>
@@ -780,10 +780,10 @@
         <v>12</v>
       </c>
       <c r="D13" s="11" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E13" s="12" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F13" s="13">
         <f>IFERROR(D13/(D13+E13),0)</f>
@@ -1650,7 +1650,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Todas las regiones · Corte 04/09/2026 14:02</t>
+          <t>Todas las regiones · Corte 04/09/2026 14:30</t>
         </is>
       </c>
     </row>
@@ -2467,17 +2467,17 @@
       </c>
       <c r="B24" s="17" t="inlineStr">
         <is>
-          <t>38656</t>
+          <t>38606</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>Viveros de la Loma</t>
+          <t>TlalnepantlaCarso</t>
         </is>
       </c>
       <c r="D24" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E24" s="7" t="n">
@@ -2507,21 +2507,21 @@
       </c>
       <c r="B25" s="15" t="inlineStr">
         <is>
-          <t>43193</t>
+          <t>38656</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>Cosmopol N1</t>
+          <t>Viveros de la Loma</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E25" s="11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F25" s="11" t="n">
         <v>5</v>
@@ -2547,17 +2547,17 @@
       </c>
       <c r="B26" s="17" t="inlineStr">
         <is>
-          <t>43152</t>
+          <t>43193</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>Samara Satélite</t>
+          <t>Cosmopol N1</t>
         </is>
       </c>
       <c r="D26" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E26" s="7" t="n">
@@ -2587,24 +2587,24 @@
       </c>
       <c r="B27" s="15" t="inlineStr">
         <is>
-          <t>38894</t>
+          <t>43152</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>Galerias Perinorte</t>
+          <t>Samara Satélite</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E27" s="11" t="n">
         <v>5</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G27" s="13">
         <f>IFERROR(E27/(E27+F27),0)</f>
@@ -2627,17 +2627,17 @@
       </c>
       <c r="B28" s="17" t="inlineStr">
         <is>
-          <t>38924</t>
+          <t>38894</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>Plaza Aeropuerto</t>
+          <t>Galerias Perinorte</t>
         </is>
       </c>
       <c r="D28" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E28" s="7" t="n">
@@ -2667,17 +2667,17 @@
       </c>
       <c r="B29" s="15" t="inlineStr">
         <is>
-          <t>38606</t>
+          <t>38924</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>TlalnepantlaCarso</t>
+          <t>Plaza Aeropuerto</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E29" s="11" t="n">
@@ -16032,7 +16032,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Todas las regiones · Corte 04/09/2026 14:02</t>
+          <t>Todas las regiones · Corte 04/09/2026 14:30</t>
         </is>
       </c>
     </row>
@@ -16158,10 +16158,10 @@
         </is>
       </c>
       <c r="C7" s="11" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="E7" s="13">
         <f>IFERROR(C7/(C7+D7),0)</f>

--- a/exports/Resumen_Evidencias_OPS.xlsx
+++ b/exports/Resumen_Evidencias_OPS.xlsx
@@ -592,7 +592,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Todas las regiones · Corte 04/09/2026 14:30</t>
+          <t>Todas las regiones · Corte 04/09/2026 14:49</t>
         </is>
       </c>
     </row>
@@ -1650,7 +1650,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Todas las regiones · Corte 04/09/2026 14:30</t>
+          <t>Todas las regiones · Corte 04/09/2026 14:49</t>
         </is>
       </c>
     </row>
@@ -16032,7 +16032,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Todas las regiones · Corte 04/09/2026 14:30</t>
+          <t>Todas las regiones · Corte 04/09/2026 14:49</t>
         </is>
       </c>
     </row>

--- a/exports/Resumen_Evidencias_OPS.xlsx
+++ b/exports/Resumen_Evidencias_OPS.xlsx
@@ -592,7 +592,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Todas las regiones · Corte 04/09/2026 14:49</t>
+          <t>Todas las regiones · Corte 04/09/2026 21:57</t>
         </is>
       </c>
     </row>
@@ -615,10 +615,10 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>297</v>
+        <v>304</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>3619</v>
+        <v>3612</v>
       </c>
       <c r="E6" s="5">
         <f>IFERROR(A6/(A6+C6),0)</f>
@@ -681,10 +681,10 @@
         <v>13</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="F10" s="9">
         <f>IFERROR(D10/(D10+E10),0)</f>
@@ -747,10 +747,10 @@
         <v>11</v>
       </c>
       <c r="D12" s="7" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E12" s="8" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F12" s="9">
         <f>IFERROR(D12/(D12+E12),0)</f>
@@ -1650,7 +1650,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Todas las regiones · Corte 04/09/2026 14:49</t>
+          <t>Todas las regiones · Corte 04/09/2026 21:57</t>
         </is>
       </c>
     </row>
@@ -1947,12 +1947,12 @@
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>38197</t>
+          <t>38770</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>Echegaray</t>
+          <t>Gustavo Baz 29</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
@@ -1964,20 +1964,20 @@
         <v>8</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G11" s="13">
         <f>IFERROR(E11/(E11+F11),0)</f>
         <v/>
       </c>
-      <c r="H11" s="10" t="inlineStr">
-        <is>
-          <t>Seguimiento</t>
-        </is>
-      </c>
-      <c r="I11" s="10" t="inlineStr">
-        <is>
-          <t>Dar seguimiento</t>
+      <c r="H11" s="16" t="inlineStr">
+        <is>
+          <t>En meta</t>
+        </is>
+      </c>
+      <c r="I11" s="16" t="inlineStr">
+        <is>
+          <t>Mantener estándar</t>
         </is>
       </c>
     </row>
@@ -1987,12 +1987,12 @@
       </c>
       <c r="B12" s="17" t="inlineStr">
         <is>
-          <t>38458</t>
+          <t>38197</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>El Rosario</t>
+          <t>Echegaray</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
@@ -2027,17 +2027,17 @@
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>38903</t>
+          <t>38458</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>Encuentro Oceania</t>
+          <t>El Rosario</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E13" s="11" t="n">
@@ -2067,21 +2067,21 @@
       </c>
       <c r="B14" s="17" t="inlineStr">
         <is>
-          <t>38590</t>
+          <t>38903</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Parque Toreo II</t>
+          <t>Encuentro Oceania</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E14" s="7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F14" s="7" t="n">
         <v>3</v>
@@ -2107,24 +2107,24 @@
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>38368</t>
+          <t>38590</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>Luna Park</t>
+          <t>Parque Toreo II</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E15" s="11" t="n">
         <v>7</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G15" s="13">
         <f>IFERROR(E15/(E15+F15),0)</f>
@@ -2147,17 +2147,17 @@
       </c>
       <c r="B16" s="17" t="inlineStr">
         <is>
-          <t>38674</t>
+          <t>38368</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>Mundo E</t>
+          <t>Luna Park</t>
         </is>
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E16" s="7" t="n">
@@ -2187,17 +2187,17 @@
       </c>
       <c r="B17" s="15" t="inlineStr">
         <is>
-          <t>38515</t>
+          <t>38674</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>Patio Ecatepec</t>
+          <t>Mundo E</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E17" s="11" t="n">
@@ -2227,17 +2227,17 @@
       </c>
       <c r="B18" s="17" t="inlineStr">
         <is>
-          <t>38475</t>
+          <t>38515</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>Satelite Centro Civico</t>
+          <t>Patio Ecatepec</t>
         </is>
       </c>
       <c r="D18" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E18" s="7" t="n">
@@ -2267,24 +2267,24 @@
       </c>
       <c r="B19" s="15" t="inlineStr">
         <is>
-          <t>38401</t>
+          <t>38475</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>Coacalco</t>
+          <t>Satelite Centro Civico</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E19" s="11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G19" s="13">
         <f>IFERROR(E19/(E19+F19),0)</f>
@@ -2307,12 +2307,12 @@
       </c>
       <c r="B20" s="17" t="inlineStr">
         <is>
-          <t>38333</t>
+          <t>38401</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>Izcalli Mega</t>
+          <t>Coacalco</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr">
@@ -2347,17 +2347,17 @@
       </c>
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t>38661</t>
+          <t>38333</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>Jinetes</t>
+          <t>Izcalli Mega</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E21" s="11" t="n">
@@ -2387,17 +2387,17 @@
       </c>
       <c r="B22" s="17" t="inlineStr">
         <is>
-          <t>38176</t>
+          <t>38661</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>Periferico Satélite DT</t>
+          <t>Jinetes</t>
         </is>
       </c>
       <c r="D22" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E22" s="7" t="n">
@@ -2427,17 +2427,17 @@
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>38339</t>
+          <t>38176</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Periferico Satélite DT</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E23" s="11" t="n">
@@ -2467,17 +2467,17 @@
       </c>
       <c r="B24" s="17" t="inlineStr">
         <is>
-          <t>38606</t>
+          <t>38339</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>TlalnepantlaCarso</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="D24" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E24" s="7" t="n">
@@ -2507,17 +2507,17 @@
       </c>
       <c r="B25" s="15" t="inlineStr">
         <is>
-          <t>38656</t>
+          <t>38606</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>Viveros de la Loma</t>
+          <t>TlalnepantlaCarso</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E25" s="11" t="n">
@@ -2547,21 +2547,21 @@
       </c>
       <c r="B26" s="17" t="inlineStr">
         <is>
-          <t>43193</t>
+          <t>38656</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>Cosmopol N1</t>
+          <t>Viveros de la Loma</t>
         </is>
       </c>
       <c r="D26" s="8" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E26" s="7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F26" s="7" t="n">
         <v>5</v>
@@ -2587,17 +2587,17 @@
       </c>
       <c r="B27" s="15" t="inlineStr">
         <is>
-          <t>43152</t>
+          <t>43193</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>Samara Satélite</t>
+          <t>Cosmopol N1</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E27" s="11" t="n">
@@ -2627,24 +2627,24 @@
       </c>
       <c r="B28" s="17" t="inlineStr">
         <is>
-          <t>38894</t>
+          <t>43152</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>Galerias Perinorte</t>
+          <t>Samara Satélite</t>
         </is>
       </c>
       <c r="D28" s="8" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E28" s="7" t="n">
         <v>5</v>
       </c>
       <c r="F28" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G28" s="9">
         <f>IFERROR(E28/(E28+F28),0)</f>
@@ -2667,17 +2667,17 @@
       </c>
       <c r="B29" s="15" t="inlineStr">
         <is>
-          <t>38924</t>
+          <t>38894</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>Plaza Aeropuerto</t>
+          <t>Galerias Perinorte</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E29" s="11" t="n">
@@ -2707,17 +2707,17 @@
       </c>
       <c r="B30" s="17" t="inlineStr">
         <is>
-          <t>38374</t>
+          <t>38924</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>Valle Dorado</t>
+          <t>Plaza Aeropuerto</t>
         </is>
       </c>
       <c r="D30" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E30" s="7" t="n">
@@ -2747,37 +2747,37 @@
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>38930</t>
+          <t>38427</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>Blvd. Aeropuerto dt</t>
+          <t>Plaza Satelite</t>
         </is>
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E31" s="11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G31" s="13">
         <f>IFERROR(E31/(E31+F31),0)</f>
         <v/>
       </c>
-      <c r="H31" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I31" s="14" t="inlineStr">
-        <is>
-          <t>Priorizar hoy</t>
+      <c r="H31" s="10" t="inlineStr">
+        <is>
+          <t>Seguimiento</t>
+        </is>
+      </c>
+      <c r="I31" s="10" t="inlineStr">
+        <is>
+          <t>Dar seguimiento</t>
         </is>
       </c>
     </row>
@@ -2787,37 +2787,37 @@
       </c>
       <c r="B32" s="17" t="inlineStr">
         <is>
-          <t>38431</t>
+          <t>38374</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>Eduardo Molina</t>
+          <t>Valle Dorado</t>
         </is>
       </c>
       <c r="D32" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E32" s="7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F32" s="7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G32" s="9">
         <f>IFERROR(E32/(E32+F32),0)</f>
         <v/>
       </c>
-      <c r="H32" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I32" s="14" t="inlineStr">
-        <is>
-          <t>Priorizar hoy</t>
+      <c r="H32" s="10" t="inlineStr">
+        <is>
+          <t>Seguimiento</t>
+        </is>
+      </c>
+      <c r="I32" s="10" t="inlineStr">
+        <is>
+          <t>Dar seguimiento</t>
         </is>
       </c>
     </row>
@@ -2827,12 +2827,12 @@
       </c>
       <c r="B33" s="15" t="inlineStr">
         <is>
-          <t>38995</t>
+          <t>38930</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>Encuentro Oceania II</t>
+          <t>Blvd. Aeropuerto dt</t>
         </is>
       </c>
       <c r="D33" s="12" t="inlineStr">
@@ -2867,17 +2867,17 @@
       </c>
       <c r="B34" s="17" t="inlineStr">
         <is>
-          <t>38230</t>
+          <t>38529</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>ITEMS Edo de Mexico</t>
+          <t>Bosques de Aragon</t>
         </is>
       </c>
       <c r="D34" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E34" s="7" t="n">
@@ -2907,12 +2907,12 @@
       </c>
       <c r="B35" s="15" t="inlineStr">
         <is>
-          <t>38937</t>
+          <t>38431</t>
         </is>
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>Parque Tepeyac Piso 1</t>
+          <t>Eduardo Molina</t>
         </is>
       </c>
       <c r="D35" s="12" t="inlineStr">
@@ -2947,12 +2947,12 @@
       </c>
       <c r="B36" s="17" t="inlineStr">
         <is>
-          <t>38965</t>
+          <t>38995</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>Parque Tepeyac Piso 2</t>
+          <t>Encuentro Oceania II</t>
         </is>
       </c>
       <c r="D36" s="8" t="inlineStr">
@@ -2987,17 +2987,17 @@
       </c>
       <c r="B37" s="15" t="inlineStr">
         <is>
-          <t>38427</t>
+          <t>38230</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>Plaza Satelite</t>
+          <t>ITEMS Edo de Mexico</t>
         </is>
       </c>
       <c r="D37" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E37" s="11" t="n">
@@ -3027,12 +3027,12 @@
       </c>
       <c r="B38" s="17" t="inlineStr">
         <is>
-          <t>38811</t>
+          <t>38937</t>
         </is>
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>Plaza Tepeyac</t>
+          <t>Parque Tepeyac Piso 1</t>
         </is>
       </c>
       <c r="D38" s="8" t="inlineStr">
@@ -3067,12 +3067,12 @@
       </c>
       <c r="B39" s="15" t="inlineStr">
         <is>
-          <t>38992</t>
+          <t>38965</t>
         </is>
       </c>
       <c r="C39" s="12" t="inlineStr">
         <is>
-          <t>Tapo Puerta Oriente</t>
+          <t>Parque Tepeyac Piso 2</t>
         </is>
       </c>
       <c r="D39" s="12" t="inlineStr">
@@ -3107,21 +3107,21 @@
       </c>
       <c r="B40" s="17" t="inlineStr">
         <is>
-          <t>38604</t>
+          <t>38811</t>
         </is>
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>Cosmopol</t>
+          <t>Plaza Tepeyac</t>
         </is>
       </c>
       <c r="D40" s="8" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E40" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F40" s="7" t="n">
         <v>7</v>
@@ -3147,21 +3147,21 @@
       </c>
       <c r="B41" s="15" t="inlineStr">
         <is>
-          <t>38770</t>
+          <t>38992</t>
         </is>
       </c>
       <c r="C41" s="12" t="inlineStr">
         <is>
-          <t>Gustavo Baz 29</t>
+          <t>Tapo Puerta Oriente</t>
         </is>
       </c>
       <c r="D41" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E41" s="11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F41" s="11" t="n">
         <v>7</v>
@@ -3187,12 +3187,12 @@
       </c>
       <c r="B42" s="17" t="inlineStr">
         <is>
-          <t>38456</t>
+          <t>38604</t>
         </is>
       </c>
       <c r="C42" s="8" t="inlineStr">
         <is>
-          <t>Plaza las Flores</t>
+          <t>Cosmopol</t>
         </is>
       </c>
       <c r="D42" s="8" t="inlineStr">
@@ -3227,24 +3227,24 @@
       </c>
       <c r="B43" s="15" t="inlineStr">
         <is>
-          <t>43194</t>
+          <t>38456</t>
         </is>
       </c>
       <c r="C43" s="12" t="inlineStr">
         <is>
-          <t>Atana Lindavista</t>
+          <t>Plaza las Flores</t>
         </is>
       </c>
       <c r="D43" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E43" s="11" t="n">
         <v>3</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G43" s="13">
         <f>IFERROR(E43/(E43+F43),0)</f>
@@ -3267,17 +3267,17 @@
       </c>
       <c r="B44" s="17" t="inlineStr">
         <is>
-          <t>38529</t>
+          <t>43194</t>
         </is>
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t>Bosques de Aragon</t>
+          <t>Atana Lindavista</t>
         </is>
       </c>
       <c r="D44" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E44" s="7" t="n">
@@ -16032,7 +16032,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Todas las regiones · Corte 04/09/2026 14:49</t>
+          <t>Todas las regiones · Corte 04/09/2026 21:57</t>
         </is>
       </c>
     </row>
@@ -16158,10 +16158,10 @@
         </is>
       </c>
       <c r="C7" s="11" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="E7" s="13">
         <f>IFERROR(C7/(C7+D7),0)</f>
@@ -16263,10 +16263,10 @@
         </is>
       </c>
       <c r="C10" s="7" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="E10" s="9">
         <f>IFERROR(C10/(C10+D10),0)</f>
@@ -16298,10 +16298,10 @@
         </is>
       </c>
       <c r="C11" s="11" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="E11" s="13">
         <f>IFERROR(C11/(C11+D11),0)</f>
@@ -16403,10 +16403,10 @@
         </is>
       </c>
       <c r="C14" s="7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E14" s="9">
         <f>IFERROR(C14/(C14+D14),0)</f>
@@ -16438,10 +16438,10 @@
         </is>
       </c>
       <c r="C15" s="11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D15" s="11" t="n">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="E15" s="13">
         <f>IFERROR(C15/(C15+D15),0)</f>

--- a/exports/Resumen_Evidencias_OPS.xlsx
+++ b/exports/Resumen_Evidencias_OPS.xlsx
@@ -592,7 +592,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Todas las regiones · Corte 04/09/2026 21:57</t>
+          <t>Todas las regiones · Corte 05/09/2026 21:12</t>
         </is>
       </c>
     </row>
@@ -615,10 +615,10 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>304</v>
+        <v>327</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>3612</v>
+        <v>3589</v>
       </c>
       <c r="E6" s="5">
         <f>IFERROR(A6/(A6+C6),0)</f>
@@ -674,17 +674,17 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Guadarrama</t>
+          <t>Enrique Flores</t>
         </is>
       </c>
       <c r="C10" s="7" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="F10" s="9">
         <f>IFERROR(D10/(D10+E10),0)</f>
@@ -707,17 +707,17 @@
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>Enrique Flores</t>
+          <t>Yazmin Guadarrama</t>
         </is>
       </c>
       <c r="C11" s="11" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>59</v>
+        <v>97</v>
       </c>
       <c r="E11" s="12" t="n">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="F11" s="13">
         <f>IFERROR(D11/(D11+E11),0)</f>
@@ -813,10 +813,10 @@
         <v>13</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E14" s="8" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F14" s="9">
         <f>IFERROR(D14/(D14+E14),0)</f>
@@ -1650,7 +1650,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Todas las regiones · Corte 04/09/2026 21:57</t>
+          <t>Todas las regiones · Corte 05/09/2026 21:12</t>
         </is>
       </c>
     </row>
@@ -1707,12 +1707,12 @@
       </c>
       <c r="B5" s="15" t="inlineStr">
         <is>
-          <t>38862</t>
+          <t>43193</t>
         </is>
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>San Miguel Izcalli</t>
+          <t>Cosmopol N1</t>
         </is>
       </c>
       <c r="D5" s="12" t="inlineStr">
@@ -1721,7 +1721,7 @@
         </is>
       </c>
       <c r="E5" s="11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F5" s="11" t="n">
         <v>0</v>
@@ -1761,10 +1761,10 @@
         </is>
       </c>
       <c r="E6" s="7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G6" s="9">
         <f>IFERROR(E6/(E6+F6),0)</f>
@@ -1787,24 +1787,24 @@
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>38117</t>
+          <t>38862</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>Satelite</t>
+          <t>San Miguel Izcalli</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E7" s="11" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7" s="13">
         <f>IFERROR(E7/(E7+F7),0)</f>
@@ -1827,24 +1827,24 @@
       </c>
       <c r="B8" s="17" t="inlineStr">
         <is>
-          <t>38695</t>
+          <t>38456</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>Cetram 4 Caminos</t>
+          <t>Plaza las Flores</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E8" s="7" t="n">
         <v>9</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G8" s="9">
         <f>IFERROR(E8/(E8+F8),0)</f>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>38561</t>
+          <t>38117</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>Parque Toreo</t>
+          <t>Satelite</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
@@ -1884,7 +1884,7 @@
         <v>9</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G9" s="13">
         <f>IFERROR(E9/(E9+F9),0)</f>
@@ -1907,17 +1907,17 @@
       </c>
       <c r="B10" s="17" t="inlineStr">
         <is>
-          <t>38719</t>
+          <t>38695</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>Plaza Fortuna</t>
+          <t>Cetram 4 Caminos</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E10" s="7" t="n">
@@ -1947,12 +1947,12 @@
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>38770</t>
+          <t>38561</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>Gustavo Baz 29</t>
+          <t>Parque Toreo</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
@@ -1961,7 +1961,7 @@
         </is>
       </c>
       <c r="E11" s="11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F11" s="11" t="n">
         <v>2</v>
@@ -1987,37 +1987,37 @@
       </c>
       <c r="B12" s="17" t="inlineStr">
         <is>
-          <t>38197</t>
+          <t>38719</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Echegaray</t>
+          <t>Plaza Fortuna</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E12" s="7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F12" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G12" s="9">
         <f>IFERROR(E12/(E12+F12),0)</f>
         <v/>
       </c>
-      <c r="H12" s="10" t="inlineStr">
-        <is>
-          <t>Seguimiento</t>
-        </is>
-      </c>
-      <c r="I12" s="10" t="inlineStr">
-        <is>
-          <t>Dar seguimiento</t>
+      <c r="H12" s="16" t="inlineStr">
+        <is>
+          <t>En meta</t>
+        </is>
+      </c>
+      <c r="I12" s="16" t="inlineStr">
+        <is>
+          <t>Mantener estándar</t>
         </is>
       </c>
     </row>
@@ -2027,37 +2027,37 @@
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>38458</t>
+          <t>38339</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>El Rosario</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E13" s="11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G13" s="13">
         <f>IFERROR(E13/(E13+F13),0)</f>
         <v/>
       </c>
-      <c r="H13" s="10" t="inlineStr">
-        <is>
-          <t>Seguimiento</t>
-        </is>
-      </c>
-      <c r="I13" s="10" t="inlineStr">
-        <is>
-          <t>Dar seguimiento</t>
+      <c r="H13" s="16" t="inlineStr">
+        <is>
+          <t>En meta</t>
+        </is>
+      </c>
+      <c r="I13" s="16" t="inlineStr">
+        <is>
+          <t>Mantener estándar</t>
         </is>
       </c>
     </row>
@@ -2067,37 +2067,37 @@
       </c>
       <c r="B14" s="17" t="inlineStr">
         <is>
-          <t>38903</t>
+          <t>38770</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Encuentro Oceania</t>
+          <t>Gustavo Baz 29</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E14" s="7" t="n">
         <v>8</v>
       </c>
       <c r="F14" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G14" s="9">
         <f>IFERROR(E14/(E14+F14),0)</f>
         <v/>
       </c>
-      <c r="H14" s="10" t="inlineStr">
-        <is>
-          <t>Seguimiento</t>
-        </is>
-      </c>
-      <c r="I14" s="10" t="inlineStr">
-        <is>
-          <t>Dar seguimiento</t>
+      <c r="H14" s="16" t="inlineStr">
+        <is>
+          <t>En meta</t>
+        </is>
+      </c>
+      <c r="I14" s="16" t="inlineStr">
+        <is>
+          <t>Mantener estándar</t>
         </is>
       </c>
     </row>
@@ -2107,21 +2107,21 @@
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>38590</t>
+          <t>38401</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>Parque Toreo II</t>
+          <t>Coacalco</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E15" s="11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F15" s="11" t="n">
         <v>3</v>
@@ -2147,24 +2147,24 @@
       </c>
       <c r="B16" s="17" t="inlineStr">
         <is>
-          <t>38368</t>
+          <t>38197</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>Luna Park</t>
+          <t>Echegaray</t>
         </is>
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E16" s="7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F16" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G16" s="9">
         <f>IFERROR(E16/(E16+F16),0)</f>
@@ -2187,24 +2187,24 @@
       </c>
       <c r="B17" s="15" t="inlineStr">
         <is>
-          <t>38674</t>
+          <t>38458</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>Mundo E</t>
+          <t>El Rosario</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E17" s="11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G17" s="13">
         <f>IFERROR(E17/(E17+F17),0)</f>
@@ -2227,24 +2227,24 @@
       </c>
       <c r="B18" s="17" t="inlineStr">
         <is>
-          <t>38515</t>
+          <t>38903</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>Patio Ecatepec</t>
+          <t>Encuentro Oceania</t>
         </is>
       </c>
       <c r="D18" s="8" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E18" s="7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F18" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G18" s="9">
         <f>IFERROR(E18/(E18+F18),0)</f>
@@ -2267,24 +2267,24 @@
       </c>
       <c r="B19" s="15" t="inlineStr">
         <is>
-          <t>38475</t>
+          <t>38515</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>Satelite Centro Civico</t>
+          <t>Patio Ecatepec</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E19" s="11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G19" s="13">
         <f>IFERROR(E19/(E19+F19),0)</f>
@@ -2307,12 +2307,12 @@
       </c>
       <c r="B20" s="17" t="inlineStr">
         <is>
-          <t>38401</t>
+          <t>38604</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>Coacalco</t>
+          <t>Cosmopol</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr">
@@ -2321,10 +2321,10 @@
         </is>
       </c>
       <c r="E20" s="7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F20" s="7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G20" s="9">
         <f>IFERROR(E20/(E20+F20),0)</f>
@@ -2347,24 +2347,24 @@
       </c>
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t>38333</t>
+          <t>38590</t>
         </is>
       </c>
       <c r="C21" s="12" t="inlineStr">
         <is>
-          <t>Izcalli Mega</t>
+          <t>Parque Toreo II</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E21" s="11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G21" s="13">
         <f>IFERROR(E21/(E21+F21),0)</f>
@@ -2387,24 +2387,24 @@
       </c>
       <c r="B22" s="17" t="inlineStr">
         <is>
-          <t>38661</t>
+          <t>38368</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>Jinetes</t>
+          <t>Luna Park</t>
         </is>
       </c>
       <c r="D22" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E22" s="7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G22" s="9">
         <f>IFERROR(E22/(E22+F22),0)</f>
@@ -2427,24 +2427,24 @@
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>38176</t>
+          <t>38674</t>
         </is>
       </c>
       <c r="C23" s="12" t="inlineStr">
         <is>
-          <t>Periferico Satélite DT</t>
+          <t>Mundo E</t>
         </is>
       </c>
       <c r="D23" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E23" s="11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G23" s="13">
         <f>IFERROR(E23/(E23+F23),0)</f>
@@ -2467,24 +2467,24 @@
       </c>
       <c r="B24" s="17" t="inlineStr">
         <is>
-          <t>38339</t>
+          <t>38475</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Satelite Centro Civico</t>
         </is>
       </c>
       <c r="D24" s="8" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E24" s="7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F24" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G24" s="9">
         <f>IFERROR(E24/(E24+F24),0)</f>
@@ -2507,17 +2507,17 @@
       </c>
       <c r="B25" s="15" t="inlineStr">
         <is>
-          <t>38606</t>
+          <t>38333</t>
         </is>
       </c>
       <c r="C25" s="12" t="inlineStr">
         <is>
-          <t>TlalnepantlaCarso</t>
+          <t>Izcalli Mega</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E25" s="11" t="n">
@@ -2547,17 +2547,17 @@
       </c>
       <c r="B26" s="17" t="inlineStr">
         <is>
-          <t>38656</t>
+          <t>38661</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>Viveros de la Loma</t>
+          <t>Jinetes</t>
         </is>
       </c>
       <c r="D26" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E26" s="7" t="n">
@@ -2587,21 +2587,21 @@
       </c>
       <c r="B27" s="15" t="inlineStr">
         <is>
-          <t>43193</t>
+          <t>38176</t>
         </is>
       </c>
       <c r="C27" s="12" t="inlineStr">
         <is>
-          <t>Cosmopol N1</t>
+          <t>Periferico Satélite DT</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E27" s="11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F27" s="11" t="n">
         <v>5</v>
@@ -2627,21 +2627,21 @@
       </c>
       <c r="B28" s="17" t="inlineStr">
         <is>
-          <t>43152</t>
+          <t>38606</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>Samara Satélite</t>
+          <t>TlalnepantlaCarso</t>
         </is>
       </c>
       <c r="D28" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E28" s="7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F28" s="7" t="n">
         <v>5</v>
@@ -2667,24 +2667,24 @@
       </c>
       <c r="B29" s="15" t="inlineStr">
         <is>
-          <t>38894</t>
+          <t>38656</t>
         </is>
       </c>
       <c r="C29" s="12" t="inlineStr">
         <is>
-          <t>Galerias Perinorte</t>
+          <t>Viveros de la Loma</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E29" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="F29" s="11" t="n">
         <v>5</v>
-      </c>
-      <c r="F29" s="11" t="n">
-        <v>6</v>
       </c>
       <c r="G29" s="13">
         <f>IFERROR(E29/(E29+F29),0)</f>
@@ -2707,24 +2707,24 @@
       </c>
       <c r="B30" s="17" t="inlineStr">
         <is>
-          <t>38924</t>
+          <t>43152</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>Plaza Aeropuerto</t>
+          <t>Samara Satélite</t>
         </is>
       </c>
       <c r="D30" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E30" s="7" t="n">
         <v>5</v>
       </c>
       <c r="F30" s="7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G30" s="9">
         <f>IFERROR(E30/(E30+F30),0)</f>
@@ -2747,17 +2747,17 @@
       </c>
       <c r="B31" s="15" t="inlineStr">
         <is>
-          <t>38427</t>
+          <t>38894</t>
         </is>
       </c>
       <c r="C31" s="12" t="inlineStr">
         <is>
-          <t>Plaza Satelite</t>
+          <t>Galerias Perinorte</t>
         </is>
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E31" s="11" t="n">
@@ -2787,17 +2787,17 @@
       </c>
       <c r="B32" s="17" t="inlineStr">
         <is>
-          <t>38374</t>
+          <t>38924</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>Valle Dorado</t>
+          <t>Plaza Aeropuerto</t>
         </is>
       </c>
       <c r="D32" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E32" s="7" t="n">
@@ -2827,37 +2827,37 @@
       </c>
       <c r="B33" s="15" t="inlineStr">
         <is>
-          <t>38930</t>
+          <t>38427</t>
         </is>
       </c>
       <c r="C33" s="12" t="inlineStr">
         <is>
-          <t>Blvd. Aeropuerto dt</t>
+          <t>Plaza Satelite</t>
         </is>
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E33" s="11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G33" s="13">
         <f>IFERROR(E33/(E33+F33),0)</f>
         <v/>
       </c>
-      <c r="H33" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I33" s="14" t="inlineStr">
-        <is>
-          <t>Priorizar hoy</t>
+      <c r="H33" s="10" t="inlineStr">
+        <is>
+          <t>Seguimiento</t>
+        </is>
+      </c>
+      <c r="I33" s="10" t="inlineStr">
+        <is>
+          <t>Dar seguimiento</t>
         </is>
       </c>
     </row>
@@ -2867,37 +2867,37 @@
       </c>
       <c r="B34" s="17" t="inlineStr">
         <is>
-          <t>38529</t>
+          <t>38374</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>Bosques de Aragon</t>
+          <t>Valle Dorado</t>
         </is>
       </c>
       <c r="D34" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E34" s="7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F34" s="7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G34" s="9">
         <f>IFERROR(E34/(E34+F34),0)</f>
         <v/>
       </c>
-      <c r="H34" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I34" s="14" t="inlineStr">
-        <is>
-          <t>Priorizar hoy</t>
+      <c r="H34" s="10" t="inlineStr">
+        <is>
+          <t>Seguimiento</t>
+        </is>
+      </c>
+      <c r="I34" s="10" t="inlineStr">
+        <is>
+          <t>Dar seguimiento</t>
         </is>
       </c>
     </row>
@@ -2907,12 +2907,12 @@
       </c>
       <c r="B35" s="15" t="inlineStr">
         <is>
-          <t>38431</t>
+          <t>38930</t>
         </is>
       </c>
       <c r="C35" s="12" t="inlineStr">
         <is>
-          <t>Eduardo Molina</t>
+          <t>Blvd. Aeropuerto dt</t>
         </is>
       </c>
       <c r="D35" s="12" t="inlineStr">
@@ -2947,12 +2947,12 @@
       </c>
       <c r="B36" s="17" t="inlineStr">
         <is>
-          <t>38995</t>
+          <t>38529</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>Encuentro Oceania II</t>
+          <t>Bosques de Aragon</t>
         </is>
       </c>
       <c r="D36" s="8" t="inlineStr">
@@ -2987,17 +2987,17 @@
       </c>
       <c r="B37" s="15" t="inlineStr">
         <is>
-          <t>38230</t>
+          <t>38431</t>
         </is>
       </c>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>ITEMS Edo de Mexico</t>
+          <t>Eduardo Molina</t>
         </is>
       </c>
       <c r="D37" s="12" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E37" s="11" t="n">
@@ -3027,12 +3027,12 @@
       </c>
       <c r="B38" s="17" t="inlineStr">
         <is>
-          <t>38937</t>
+          <t>38995</t>
         </is>
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>Parque Tepeyac Piso 1</t>
+          <t>Encuentro Oceania II</t>
         </is>
       </c>
       <c r="D38" s="8" t="inlineStr">
@@ -3067,17 +3067,17 @@
       </c>
       <c r="B39" s="15" t="inlineStr">
         <is>
-          <t>38965</t>
+          <t>38230</t>
         </is>
       </c>
       <c r="C39" s="12" t="inlineStr">
         <is>
-          <t>Parque Tepeyac Piso 2</t>
+          <t>ITEMS Edo de Mexico</t>
         </is>
       </c>
       <c r="D39" s="12" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E39" s="11" t="n">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="B40" s="17" t="inlineStr">
         <is>
-          <t>38811</t>
+          <t>38937</t>
         </is>
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>Plaza Tepeyac</t>
+          <t>Parque Tepeyac Piso 1</t>
         </is>
       </c>
       <c r="D40" s="8" t="inlineStr">
@@ -3147,12 +3147,12 @@
       </c>
       <c r="B41" s="15" t="inlineStr">
         <is>
-          <t>38992</t>
+          <t>38965</t>
         </is>
       </c>
       <c r="C41" s="12" t="inlineStr">
         <is>
-          <t>Tapo Puerta Oriente</t>
+          <t>Parque Tepeyac Piso 2</t>
         </is>
       </c>
       <c r="D41" s="12" t="inlineStr">
@@ -3187,21 +3187,21 @@
       </c>
       <c r="B42" s="17" t="inlineStr">
         <is>
-          <t>38604</t>
+          <t>38811</t>
         </is>
       </c>
       <c r="C42" s="8" t="inlineStr">
         <is>
-          <t>Cosmopol</t>
+          <t>Plaza Tepeyac</t>
         </is>
       </c>
       <c r="D42" s="8" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E42" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F42" s="7" t="n">
         <v>7</v>
@@ -3227,21 +3227,21 @@
       </c>
       <c r="B43" s="15" t="inlineStr">
         <is>
-          <t>38456</t>
+          <t>38992</t>
         </is>
       </c>
       <c r="C43" s="12" t="inlineStr">
         <is>
-          <t>Plaza las Flores</t>
+          <t>Tapo Puerta Oriente</t>
         </is>
       </c>
       <c r="D43" s="12" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E43" s="11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F43" s="11" t="n">
         <v>7</v>
@@ -3347,17 +3347,17 @@
       </c>
       <c r="B46" s="17" t="inlineStr">
         <is>
-          <t>38136</t>
+          <t>38546</t>
         </is>
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t>Punta Norte</t>
+          <t>Patio Claveria</t>
         </is>
       </c>
       <c r="D46" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E46" s="7" t="n">
@@ -3387,17 +3387,17 @@
       </c>
       <c r="B47" s="15" t="inlineStr">
         <is>
-          <t>38651</t>
+          <t>38136</t>
         </is>
       </c>
       <c r="C47" s="12" t="inlineStr">
         <is>
-          <t>Via Vallejo</t>
+          <t>Punta Norte</t>
         </is>
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E47" s="11" t="n">
@@ -3427,24 +3427,24 @@
       </c>
       <c r="B48" s="17" t="inlineStr">
         <is>
-          <t>38186</t>
+          <t>38651</t>
         </is>
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
-          <t>Arboledas</t>
+          <t>Via Vallejo</t>
         </is>
       </c>
       <c r="D48" s="8" t="inlineStr">
         <is>
-          <t>Nancy Carolina Rodriguez Medina</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E48" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F48" s="7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G48" s="9">
         <f>IFERROR(E48/(E48+F48),0)</f>
@@ -3467,17 +3467,17 @@
       </c>
       <c r="B49" s="15" t="inlineStr">
         <is>
-          <t>43043</t>
+          <t>38186</t>
         </is>
       </c>
       <c r="C49" s="12" t="inlineStr">
         <is>
-          <t>Atizapan</t>
+          <t>Arboledas</t>
         </is>
       </c>
       <c r="D49" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Nancy Carolina Rodriguez Medina</t>
         </is>
       </c>
       <c r="E49" s="11" t="n">
@@ -3507,12 +3507,12 @@
       </c>
       <c r="B50" s="17" t="inlineStr">
         <is>
-          <t>38149</t>
+          <t>43043</t>
         </is>
       </c>
       <c r="C50" s="8" t="inlineStr">
         <is>
-          <t>Bellavista</t>
+          <t>Atizapan</t>
         </is>
       </c>
       <c r="D50" s="8" t="inlineStr">
@@ -3547,17 +3547,17 @@
       </c>
       <c r="B51" s="15" t="inlineStr">
         <is>
-          <t>38527</t>
+          <t>38149</t>
         </is>
       </c>
       <c r="C51" s="12" t="inlineStr">
         <is>
-          <t>Camarones</t>
+          <t>Bellavista</t>
         </is>
       </c>
       <c r="D51" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E51" s="11" t="n">
@@ -3587,12 +3587,12 @@
       </c>
       <c r="B52" s="17" t="inlineStr">
         <is>
-          <t>38837</t>
+          <t>38527</t>
         </is>
       </c>
       <c r="C52" s="8" t="inlineStr">
         <is>
-          <t>Centenario Azcapotzalco</t>
+          <t>Camarones</t>
         </is>
       </c>
       <c r="D52" s="8" t="inlineStr">
@@ -3627,17 +3627,17 @@
       </c>
       <c r="B53" s="15" t="inlineStr">
         <is>
-          <t>38394</t>
+          <t>38837</t>
         </is>
       </c>
       <c r="C53" s="12" t="inlineStr">
         <is>
-          <t>Centro Comercial Lomas Verdes</t>
+          <t>Centenario Azcapotzalco</t>
         </is>
       </c>
       <c r="D53" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E53" s="11" t="n">
@@ -3667,12 +3667,12 @@
       </c>
       <c r="B54" s="17" t="inlineStr">
         <is>
-          <t>38535</t>
+          <t>38394</t>
         </is>
       </c>
       <c r="C54" s="8" t="inlineStr">
         <is>
-          <t>City Center Esmeralda</t>
+          <t>Centro Comercial Lomas Verdes</t>
         </is>
       </c>
       <c r="D54" s="8" t="inlineStr">
@@ -3707,12 +3707,12 @@
       </c>
       <c r="B55" s="15" t="inlineStr">
         <is>
-          <t>38507</t>
+          <t>38535</t>
         </is>
       </c>
       <c r="C55" s="12" t="inlineStr">
         <is>
-          <t>Espacio Vista del Valle</t>
+          <t>City Center Esmeralda</t>
         </is>
       </c>
       <c r="D55" s="12" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="B56" s="17" t="inlineStr">
         <is>
-          <t>38363</t>
+          <t>38507</t>
         </is>
       </c>
       <c r="C56" s="8" t="inlineStr">
         <is>
-          <t>Galerias Atizapan</t>
+          <t>Espacio Vista del Valle</t>
         </is>
       </c>
       <c r="D56" s="8" t="inlineStr">
@@ -3787,17 +3787,17 @@
       </c>
       <c r="B57" s="15" t="inlineStr">
         <is>
-          <t>38205</t>
+          <t>38363</t>
         </is>
       </c>
       <c r="C57" s="12" t="inlineStr">
         <is>
-          <t>Lindavista</t>
+          <t>Galerias Atizapan</t>
         </is>
       </c>
       <c r="D57" s="12" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E57" s="11" t="n">
@@ -3827,17 +3827,17 @@
       </c>
       <c r="B58" s="17" t="inlineStr">
         <is>
-          <t>38119</t>
+          <t>38205</t>
         </is>
       </c>
       <c r="C58" s="8" t="inlineStr">
         <is>
-          <t>Lomas Verdes</t>
+          <t>Lindavista</t>
         </is>
       </c>
       <c r="D58" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Haydee Garcia Gonzalez</t>
+          <t>Vanessa Carreño Rios</t>
         </is>
       </c>
       <c r="E58" s="7" t="n">
@@ -3867,12 +3867,12 @@
       </c>
       <c r="B59" s="15" t="inlineStr">
         <is>
-          <t>38270</t>
+          <t>38119</t>
         </is>
       </c>
       <c r="C59" s="12" t="inlineStr">
         <is>
-          <t>Lomas Verdes II</t>
+          <t>Lomas Verdes</t>
         </is>
       </c>
       <c r="D59" s="12" t="inlineStr">
@@ -3907,17 +3907,17 @@
       </c>
       <c r="B60" s="17" t="inlineStr">
         <is>
-          <t>38371</t>
+          <t>38270</t>
         </is>
       </c>
       <c r="C60" s="8" t="inlineStr">
         <is>
-          <t>Montevideo DT</t>
+          <t>Lomas Verdes II</t>
         </is>
       </c>
       <c r="D60" s="8" t="inlineStr">
         <is>
-          <t>Vanessa Carreño Rios</t>
+          <t>Yazmin Haydee Garcia Gonzalez</t>
         </is>
       </c>
       <c r="E60" s="7" t="n">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="B61" s="15" t="inlineStr">
         <is>
-          <t>43111</t>
+          <t>38371</t>
         </is>
       </c>
       <c r="C61" s="12" t="inlineStr">
         <is>
-          <t>Montevideo Insurgentes</t>
+          <t>Montevideo DT</t>
         </is>
       </c>
       <c r="D61" s="12" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="B62" s="17" t="inlineStr">
         <is>
-          <t>43195</t>
+          <t>43111</t>
         </is>
       </c>
       <c r="C62" s="8" t="inlineStr">
         <is>
-          <t>Parque Jadin kiosko</t>
+          <t>Montevideo Insurgentes</t>
         </is>
       </c>
       <c r="D62" s="8" t="inlineStr">
@@ -4027,12 +4027,12 @@
       </c>
       <c r="B63" s="15" t="inlineStr">
         <is>
-          <t>38546</t>
+          <t>43195</t>
         </is>
       </c>
       <c r="C63" s="12" t="inlineStr">
         <is>
-          <t>Patio Claveria</t>
+          <t>Parque Jadin kiosko</t>
         </is>
       </c>
       <c r="D63" s="12" t="inlineStr">
@@ -16032,7 +16032,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Todas las regiones · Corte 04/09/2026 21:57</t>
+          <t>Todas las regiones · Corte 05/09/2026 21:12</t>
         </is>
       </c>
     </row>
@@ -16158,10 +16158,10 @@
         </is>
       </c>
       <c r="C7" s="11" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="E7" s="13">
         <f>IFERROR(C7/(C7+D7),0)</f>
@@ -16193,10 +16193,10 @@
         </is>
       </c>
       <c r="C8" s="7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="E8" s="9">
         <f>IFERROR(C8/(C8+D8),0)</f>
@@ -16228,10 +16228,10 @@
         </is>
       </c>
       <c r="C9" s="11" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D9" s="11" t="n">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="E9" s="13">
         <f>IFERROR(C9/(C9+D9),0)</f>
@@ -16263,10 +16263,10 @@
         </is>
       </c>
       <c r="C10" s="7" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="E10" s="9">
         <f>IFERROR(C10/(C10+D10),0)</f>
@@ -16298,10 +16298,10 @@
         </is>
       </c>
       <c r="C11" s="11" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="E11" s="13">
         <f>IFERROR(C11/(C11+D11),0)</f>
@@ -16403,10 +16403,10 @@
         </is>
       </c>
       <c r="C14" s="7" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="E14" s="9">
         <f>IFERROR(C14/(C14+D14),0)</f>
@@ -16438,10 +16438,10 @@
         </is>
       </c>
       <c r="C15" s="11" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D15" s="11" t="n">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="E15" s="13">
         <f>IFERROR(C15/(C15+D15),0)</f>

--- a/exports/Resumen_Evidencias_OPS.xlsx
+++ b/exports/Resumen_Evidencias_OPS.xlsx
@@ -592,7 +592,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Todas las regiones · Corte 05/09/2026 21:12</t>
+          <t>Todas las regiones · Corte 06/09/2026 16:16</t>
         </is>
       </c>
     </row>
@@ -615,10 +615,10 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>3589</v>
+        <v>3585</v>
       </c>
       <c r="E6" s="5">
         <f>IFERROR(A6/(A6+C6),0)</f>
@@ -681,10 +681,10 @@
         <v>10</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="F10" s="9">
         <f>IFERROR(D10/(D10+E10),0)</f>
@@ -1650,7 +1650,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Todas las regiones · Corte 05/09/2026 21:12</t>
+          <t>Todas las regiones · Corte 06/09/2026 16:16</t>
         </is>
       </c>
     </row>
@@ -1827,12 +1827,12 @@
       </c>
       <c r="B8" s="17" t="inlineStr">
         <is>
-          <t>38456</t>
+          <t>38515</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>Plaza las Flores</t>
+          <t>Patio Ecatepec</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
@@ -1841,7 +1841,7 @@
         </is>
       </c>
       <c r="E8" s="7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F8" s="7" t="n">
         <v>1</v>
@@ -1867,17 +1867,17 @@
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>38117</t>
+          <t>38604</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>Satelite</t>
+          <t>Cosmopol</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E9" s="11" t="n">
@@ -1907,24 +1907,24 @@
       </c>
       <c r="B10" s="17" t="inlineStr">
         <is>
-          <t>38695</t>
+          <t>38456</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>Cetram 4 Caminos</t>
+          <t>Plaza las Flores</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E10" s="7" t="n">
         <v>9</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G10" s="9">
         <f>IFERROR(E10/(E10+F10),0)</f>
@@ -1947,12 +1947,12 @@
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>38561</t>
+          <t>38117</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>Parque Toreo</t>
+          <t>Satelite</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
@@ -1964,7 +1964,7 @@
         <v>9</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G11" s="13">
         <f>IFERROR(E11/(E11+F11),0)</f>
@@ -1987,17 +1987,17 @@
       </c>
       <c r="B12" s="17" t="inlineStr">
         <is>
-          <t>38719</t>
+          <t>38695</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Plaza Fortuna</t>
+          <t>Cetram 4 Caminos</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E12" s="7" t="n">
@@ -2027,17 +2027,17 @@
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>38339</t>
+          <t>38561</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Parque Toreo</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E13" s="11" t="n">
@@ -2067,21 +2067,21 @@
       </c>
       <c r="B14" s="17" t="inlineStr">
         <is>
-          <t>38770</t>
+          <t>38719</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Gustavo Baz 29</t>
+          <t>Plaza Fortuna</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E14" s="7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F14" s="7" t="n">
         <v>2</v>
@@ -2107,12 +2107,12 @@
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>38401</t>
+          <t>38339</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>Coacalco</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
@@ -2121,23 +2121,23 @@
         </is>
       </c>
       <c r="E15" s="11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G15" s="13">
         <f>IFERROR(E15/(E15+F15),0)</f>
         <v/>
       </c>
-      <c r="H15" s="10" t="inlineStr">
-        <is>
-          <t>Seguimiento</t>
-        </is>
-      </c>
-      <c r="I15" s="10" t="inlineStr">
-        <is>
-          <t>Dar seguimiento</t>
+      <c r="H15" s="16" t="inlineStr">
+        <is>
+          <t>En meta</t>
+        </is>
+      </c>
+      <c r="I15" s="16" t="inlineStr">
+        <is>
+          <t>Mantener estándar</t>
         </is>
       </c>
     </row>
@@ -2147,12 +2147,12 @@
       </c>
       <c r="B16" s="17" t="inlineStr">
         <is>
-          <t>38197</t>
+          <t>38770</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>Echegaray</t>
+          <t>Gustavo Baz 29</t>
         </is>
       </c>
       <c r="D16" s="8" t="inlineStr">
@@ -2164,20 +2164,20 @@
         <v>8</v>
       </c>
       <c r="F16" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G16" s="9">
         <f>IFERROR(E16/(E16+F16),0)</f>
         <v/>
       </c>
-      <c r="H16" s="10" t="inlineStr">
-        <is>
-          <t>Seguimiento</t>
-        </is>
-      </c>
-      <c r="I16" s="10" t="inlineStr">
-        <is>
-          <t>Dar seguimiento</t>
+      <c r="H16" s="16" t="inlineStr">
+        <is>
+          <t>En meta</t>
+        </is>
+      </c>
+      <c r="I16" s="16" t="inlineStr">
+        <is>
+          <t>Mantener estándar</t>
         </is>
       </c>
     </row>
@@ -2187,17 +2187,17 @@
       </c>
       <c r="B17" s="15" t="inlineStr">
         <is>
-          <t>38458</t>
+          <t>38401</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>El Rosario</t>
+          <t>Coacalco</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E17" s="11" t="n">
@@ -2227,17 +2227,17 @@
       </c>
       <c r="B18" s="17" t="inlineStr">
         <is>
-          <t>38903</t>
+          <t>38197</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>Encuentro Oceania</t>
+          <t>Echegaray</t>
         </is>
       </c>
       <c r="D18" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E18" s="7" t="n">
@@ -2267,17 +2267,17 @@
       </c>
       <c r="B19" s="15" t="inlineStr">
         <is>
-          <t>38515</t>
+          <t>38458</t>
         </is>
       </c>
       <c r="C19" s="12" t="inlineStr">
         <is>
-          <t>Patio Ecatepec</t>
+          <t>El Rosario</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E19" s="11" t="n">
@@ -2307,21 +2307,21 @@
       </c>
       <c r="B20" s="17" t="inlineStr">
         <is>
-          <t>38604</t>
+          <t>38903</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>Cosmopol</t>
+          <t>Encuentro Oceania</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E20" s="7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F20" s="7" t="n">
         <v>3</v>
@@ -16032,7 +16032,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Todas las regiones · Corte 05/09/2026 21:12</t>
+          <t>Todas las regiones · Corte 06/09/2026 16:16</t>
         </is>
       </c>
     </row>
@@ -16158,10 +16158,10 @@
         </is>
       </c>
       <c r="C7" s="11" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D7" s="11" t="n">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="E7" s="13">
         <f>IFERROR(C7/(C7+D7),0)</f>
@@ -16298,10 +16298,10 @@
         </is>
       </c>
       <c r="C11" s="11" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="E11" s="13">
         <f>IFERROR(C11/(C11+D11),0)</f>
@@ -16403,10 +16403,10 @@
         </is>
       </c>
       <c r="C14" s="7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E14" s="9">
         <f>IFERROR(C14/(C14+D14),0)</f>
@@ -16438,10 +16438,10 @@
         </is>
       </c>
       <c r="C15" s="11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D15" s="11" t="n">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="E15" s="13">
         <f>IFERROR(C15/(C15+D15),0)</f>

--- a/exports/Resumen_Evidencias_OPS.xlsx
+++ b/exports/Resumen_Evidencias_OPS.xlsx
@@ -73,6 +73,12 @@
     <font>
       <name val="Aptos"/>
       <b val="1"/>
+      <color rgb="00116444"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Aptos"/>
+      <b val="1"/>
       <color rgb="0080520C"/>
       <sz val="9"/>
     </font>
@@ -80,12 +86,6 @@
       <name val="Aptos"/>
       <b val="1"/>
       <color rgb="00922F24"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Aptos"/>
-      <b val="1"/>
-      <color rgb="00116444"/>
       <sz val="9"/>
     </font>
   </fonts>
@@ -118,17 +118,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00DAF1E6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00FFF0D5"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F9E6E3"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00DAF1E6"/>
       </patternFill>
     </fill>
   </fills>
@@ -193,11 +193,11 @@
     <xf numFmtId="0" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -592,7 +592,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Todas las regiones · Corte 06/09/2026 16:16</t>
+          <t>Todas las regiones · Corte 06/09/2026 18:41</t>
         </is>
       </c>
     </row>
@@ -615,10 +615,10 @@
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>3585</v>
+        <v>3581</v>
       </c>
       <c r="E6" s="5">
         <f>IFERROR(A6/(A6+C6),0)</f>
@@ -681,10 +681,10 @@
         <v>10</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="F10" s="9">
         <f>IFERROR(D10/(D10+E10),0)</f>
@@ -692,12 +692,12 @@
       </c>
       <c r="G10" s="10" t="inlineStr">
         <is>
-          <t>Seguimiento</t>
+          <t>En meta</t>
         </is>
       </c>
       <c r="H10" s="10" t="inlineStr">
         <is>
-          <t>Dar seguimiento</t>
+          <t>Mantener estándar</t>
         </is>
       </c>
     </row>
@@ -714,21 +714,21 @@
         <v>13</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E11" s="12" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F11" s="13">
         <f>IFERROR(D11/(D11+E11),0)</f>
         <v/>
       </c>
-      <c r="G11" s="10" t="inlineStr">
+      <c r="G11" s="14" t="inlineStr">
         <is>
           <t>Seguimiento</t>
         </is>
       </c>
-      <c r="H11" s="10" t="inlineStr">
+      <c r="H11" s="14" t="inlineStr">
         <is>
           <t>Dar seguimiento</t>
         </is>
@@ -756,12 +756,12 @@
         <f>IFERROR(D12/(D12+E12),0)</f>
         <v/>
       </c>
-      <c r="G12" s="10" t="inlineStr">
+      <c r="G12" s="14" t="inlineStr">
         <is>
           <t>Seguimiento</t>
         </is>
       </c>
-      <c r="H12" s="10" t="inlineStr">
+      <c r="H12" s="14" t="inlineStr">
         <is>
           <t>Dar seguimiento</t>
         </is>
@@ -789,12 +789,12 @@
         <f>IFERROR(D13/(D13+E13),0)</f>
         <v/>
       </c>
-      <c r="G13" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="H13" s="14" t="inlineStr">
+      <c r="G13" s="15" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="H13" s="15" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -822,12 +822,12 @@
         <f>IFERROR(D14/(D14+E14),0)</f>
         <v/>
       </c>
-      <c r="G14" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="H14" s="14" t="inlineStr">
+      <c r="G14" s="15" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="H14" s="15" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -855,12 +855,12 @@
         <f>IFERROR(D15/(D15+E15),0)</f>
         <v/>
       </c>
-      <c r="G15" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="H15" s="14" t="inlineStr">
+      <c r="G15" s="15" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="H15" s="15" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -888,12 +888,12 @@
         <f>IFERROR(D16/(D16+E16),0)</f>
         <v/>
       </c>
-      <c r="G16" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="H16" s="14" t="inlineStr">
+      <c r="G16" s="15" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="H16" s="15" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -921,12 +921,12 @@
         <f>IFERROR(D17/(D17+E17),0)</f>
         <v/>
       </c>
-      <c r="G17" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="H17" s="14" t="inlineStr">
+      <c r="G17" s="15" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="H17" s="15" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -954,12 +954,12 @@
         <f>IFERROR(D18/(D18+E18),0)</f>
         <v/>
       </c>
-      <c r="G18" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="H18" s="14" t="inlineStr">
+      <c r="G18" s="15" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="H18" s="15" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -987,12 +987,12 @@
         <f>IFERROR(D19/(D19+E19),0)</f>
         <v/>
       </c>
-      <c r="G19" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="H19" s="14" t="inlineStr">
+      <c r="G19" s="15" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="H19" s="15" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -1020,12 +1020,12 @@
         <f>IFERROR(D20/(D20+E20),0)</f>
         <v/>
       </c>
-      <c r="G20" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="H20" s="14" t="inlineStr">
+      <c r="G20" s="15" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="H20" s="15" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -1053,12 +1053,12 @@
         <f>IFERROR(D21/(D21+E21),0)</f>
         <v/>
       </c>
-      <c r="G21" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="H21" s="14" t="inlineStr">
+      <c r="G21" s="15" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="H21" s="15" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -1086,12 +1086,12 @@
         <f>IFERROR(D22/(D22+E22),0)</f>
         <v/>
       </c>
-      <c r="G22" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="H22" s="14" t="inlineStr">
+      <c r="G22" s="15" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="H22" s="15" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -1119,12 +1119,12 @@
         <f>IFERROR(D23/(D23+E23),0)</f>
         <v/>
       </c>
-      <c r="G23" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="H23" s="14" t="inlineStr">
+      <c r="G23" s="15" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="H23" s="15" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -1152,12 +1152,12 @@
         <f>IFERROR(D24/(D24+E24),0)</f>
         <v/>
       </c>
-      <c r="G24" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="H24" s="14" t="inlineStr">
+      <c r="G24" s="15" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="H24" s="15" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -1185,12 +1185,12 @@
         <f>IFERROR(D25/(D25+E25),0)</f>
         <v/>
       </c>
-      <c r="G25" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="H25" s="14" t="inlineStr">
+      <c r="G25" s="15" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="H25" s="15" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -1218,12 +1218,12 @@
         <f>IFERROR(D26/(D26+E26),0)</f>
         <v/>
       </c>
-      <c r="G26" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="H26" s="14" t="inlineStr">
+      <c r="G26" s="15" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="H26" s="15" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -1251,12 +1251,12 @@
         <f>IFERROR(D27/(D27+E27),0)</f>
         <v/>
       </c>
-      <c r="G27" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="H27" s="14" t="inlineStr">
+      <c r="G27" s="15" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="H27" s="15" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -1284,12 +1284,12 @@
         <f>IFERROR(D28/(D28+E28),0)</f>
         <v/>
       </c>
-      <c r="G28" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="H28" s="14" t="inlineStr">
+      <c r="G28" s="15" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="H28" s="15" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -1317,12 +1317,12 @@
         <f>IFERROR(D29/(D29+E29),0)</f>
         <v/>
       </c>
-      <c r="G29" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="H29" s="14" t="inlineStr">
+      <c r="G29" s="15" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="H29" s="15" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -1350,12 +1350,12 @@
         <f>IFERROR(D30/(D30+E30),0)</f>
         <v/>
       </c>
-      <c r="G30" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="H30" s="14" t="inlineStr">
+      <c r="G30" s="15" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="H30" s="15" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -1383,12 +1383,12 @@
         <f>IFERROR(D31/(D31+E31),0)</f>
         <v/>
       </c>
-      <c r="G31" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="H31" s="14" t="inlineStr">
+      <c r="G31" s="15" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="H31" s="15" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -1416,12 +1416,12 @@
         <f>IFERROR(D32/(D32+E32),0)</f>
         <v/>
       </c>
-      <c r="G32" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="H32" s="14" t="inlineStr">
+      <c r="G32" s="15" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="H32" s="15" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -1449,12 +1449,12 @@
         <f>IFERROR(D33/(D33+E33),0)</f>
         <v/>
       </c>
-      <c r="G33" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="H33" s="14" t="inlineStr">
+      <c r="G33" s="15" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="H33" s="15" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -1482,12 +1482,12 @@
         <f>IFERROR(D34/(D34+E34),0)</f>
         <v/>
       </c>
-      <c r="G34" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="H34" s="14" t="inlineStr">
+      <c r="G34" s="15" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="H34" s="15" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -1515,12 +1515,12 @@
         <f>IFERROR(D35/(D35+E35),0)</f>
         <v/>
       </c>
-      <c r="G35" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="H35" s="14" t="inlineStr">
+      <c r="G35" s="15" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="H35" s="15" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -1548,12 +1548,12 @@
         <f>IFERROR(D36/(D36+E36),0)</f>
         <v/>
       </c>
-      <c r="G36" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="H36" s="14" t="inlineStr">
+      <c r="G36" s="15" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="H36" s="15" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -1581,12 +1581,12 @@
         <f>IFERROR(D37/(D37+E37),0)</f>
         <v/>
       </c>
-      <c r="G37" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="H37" s="14" t="inlineStr">
+      <c r="G37" s="15" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="H37" s="15" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -1650,7 +1650,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Todas las regiones · Corte 06/09/2026 16:16</t>
+          <t>Todas las regiones · Corte 06/09/2026 18:41</t>
         </is>
       </c>
     </row>
@@ -1705,14 +1705,14 @@
       <c r="A5" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="15" t="inlineStr">
-        <is>
-          <t>43193</t>
+      <c r="B5" s="16" t="inlineStr">
+        <is>
+          <t>38604</t>
         </is>
       </c>
       <c r="C5" s="12" t="inlineStr">
         <is>
-          <t>Cosmopol N1</t>
+          <t>Cosmopol</t>
         </is>
       </c>
       <c r="D5" s="12" t="inlineStr">
@@ -1730,12 +1730,12 @@
         <f>IFERROR(E5/(E5+F5),0)</f>
         <v/>
       </c>
-      <c r="H5" s="16" t="inlineStr">
+      <c r="H5" s="10" t="inlineStr">
         <is>
           <t>En meta</t>
         </is>
       </c>
-      <c r="I5" s="16" t="inlineStr">
+      <c r="I5" s="10" t="inlineStr">
         <is>
           <t>Mantener estándar</t>
         </is>
@@ -1747,17 +1747,17 @@
       </c>
       <c r="B6" s="17" t="inlineStr">
         <is>
-          <t>38859</t>
+          <t>43193</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>Plaza Satelite II N1</t>
+          <t>Cosmopol N1</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E6" s="7" t="n">
@@ -1770,12 +1770,12 @@
         <f>IFERROR(E6/(E6+F6),0)</f>
         <v/>
       </c>
-      <c r="H6" s="16" t="inlineStr">
+      <c r="H6" s="10" t="inlineStr">
         <is>
           <t>En meta</t>
         </is>
       </c>
-      <c r="I6" s="16" t="inlineStr">
+      <c r="I6" s="10" t="inlineStr">
         <is>
           <t>Mantener estándar</t>
         </is>
@@ -1785,14 +1785,14 @@
       <c r="A7" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="15" t="inlineStr">
-        <is>
-          <t>38862</t>
+      <c r="B7" s="16" t="inlineStr">
+        <is>
+          <t>38515</t>
         </is>
       </c>
       <c r="C7" s="12" t="inlineStr">
         <is>
-          <t>San Miguel Izcalli</t>
+          <t>Patio Ecatepec</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
@@ -1810,12 +1810,12 @@
         <f>IFERROR(E7/(E7+F7),0)</f>
         <v/>
       </c>
-      <c r="H7" s="16" t="inlineStr">
+      <c r="H7" s="10" t="inlineStr">
         <is>
           <t>En meta</t>
         </is>
       </c>
-      <c r="I7" s="16" t="inlineStr">
+      <c r="I7" s="10" t="inlineStr">
         <is>
           <t>Mantener estándar</t>
         </is>
@@ -1827,35 +1827,35 @@
       </c>
       <c r="B8" s="17" t="inlineStr">
         <is>
-          <t>38515</t>
+          <t>38859</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>Patio Ecatepec</t>
+          <t>Plaza Satelite II N1</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E8" s="7" t="n">
         <v>10</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G8" s="9">
         <f>IFERROR(E8/(E8+F8),0)</f>
         <v/>
       </c>
-      <c r="H8" s="16" t="inlineStr">
+      <c r="H8" s="10" t="inlineStr">
         <is>
           <t>En meta</t>
         </is>
       </c>
-      <c r="I8" s="16" t="inlineStr">
+      <c r="I8" s="10" t="inlineStr">
         <is>
           <t>Mantener estándar</t>
         </is>
@@ -1865,14 +1865,14 @@
       <c r="A9" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="15" t="inlineStr">
-        <is>
-          <t>38604</t>
+      <c r="B9" s="16" t="inlineStr">
+        <is>
+          <t>38862</t>
         </is>
       </c>
       <c r="C9" s="12" t="inlineStr">
         <is>
-          <t>Cosmopol</t>
+          <t>San Miguel Izcalli</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
@@ -1881,21 +1881,21 @@
         </is>
       </c>
       <c r="E9" s="11" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" s="13">
         <f>IFERROR(E9/(E9+F9),0)</f>
         <v/>
       </c>
-      <c r="H9" s="16" t="inlineStr">
+      <c r="H9" s="10" t="inlineStr">
         <is>
           <t>En meta</t>
         </is>
       </c>
-      <c r="I9" s="16" t="inlineStr">
+      <c r="I9" s="10" t="inlineStr">
         <is>
           <t>Mantener estándar</t>
         </is>
@@ -1907,17 +1907,17 @@
       </c>
       <c r="B10" s="17" t="inlineStr">
         <is>
-          <t>38456</t>
+          <t>38770</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>Plaza las Flores</t>
+          <t>Gustavo Baz 29</t>
         </is>
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E10" s="7" t="n">
@@ -1930,12 +1930,12 @@
         <f>IFERROR(E10/(E10+F10),0)</f>
         <v/>
       </c>
-      <c r="H10" s="16" t="inlineStr">
+      <c r="H10" s="10" t="inlineStr">
         <is>
           <t>En meta</t>
         </is>
       </c>
-      <c r="I10" s="16" t="inlineStr">
+      <c r="I10" s="10" t="inlineStr">
         <is>
           <t>Mantener estándar</t>
         </is>
@@ -1945,19 +1945,19 @@
       <c r="A11" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="15" t="inlineStr">
-        <is>
-          <t>38117</t>
+      <c r="B11" s="16" t="inlineStr">
+        <is>
+          <t>38456</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>Satelite</t>
+          <t>Plaza las Flores</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E11" s="11" t="n">
@@ -1970,12 +1970,12 @@
         <f>IFERROR(E11/(E11+F11),0)</f>
         <v/>
       </c>
-      <c r="H11" s="16" t="inlineStr">
+      <c r="H11" s="10" t="inlineStr">
         <is>
           <t>En meta</t>
         </is>
       </c>
-      <c r="I11" s="16" t="inlineStr">
+      <c r="I11" s="10" t="inlineStr">
         <is>
           <t>Mantener estándar</t>
         </is>
@@ -1987,12 +1987,12 @@
       </c>
       <c r="B12" s="17" t="inlineStr">
         <is>
-          <t>38695</t>
+          <t>38117</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Cetram 4 Caminos</t>
+          <t>Satelite</t>
         </is>
       </c>
       <c r="D12" s="8" t="inlineStr">
@@ -2004,18 +2004,18 @@
         <v>9</v>
       </c>
       <c r="F12" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G12" s="9">
         <f>IFERROR(E12/(E12+F12),0)</f>
         <v/>
       </c>
-      <c r="H12" s="16" t="inlineStr">
+      <c r="H12" s="10" t="inlineStr">
         <is>
           <t>En meta</t>
         </is>
       </c>
-      <c r="I12" s="16" t="inlineStr">
+      <c r="I12" s="10" t="inlineStr">
         <is>
           <t>Mantener estándar</t>
         </is>
@@ -2025,14 +2025,14 @@
       <c r="A13" s="11" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="15" t="inlineStr">
-        <is>
-          <t>38561</t>
+      <c r="B13" s="16" t="inlineStr">
+        <is>
+          <t>38695</t>
         </is>
       </c>
       <c r="C13" s="12" t="inlineStr">
         <is>
-          <t>Parque Toreo</t>
+          <t>Cetram 4 Caminos</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
@@ -2050,12 +2050,12 @@
         <f>IFERROR(E13/(E13+F13),0)</f>
         <v/>
       </c>
-      <c r="H13" s="16" t="inlineStr">
+      <c r="H13" s="10" t="inlineStr">
         <is>
           <t>En meta</t>
         </is>
       </c>
-      <c r="I13" s="16" t="inlineStr">
+      <c r="I13" s="10" t="inlineStr">
         <is>
           <t>Mantener estándar</t>
         </is>
@@ -2067,17 +2067,17 @@
       </c>
       <c r="B14" s="17" t="inlineStr">
         <is>
-          <t>38719</t>
+          <t>38401</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Plaza Fortuna</t>
+          <t>Coacalco</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t>Veronica Garcia Ortega</t>
+          <t>Enrique Cesar Flores</t>
         </is>
       </c>
       <c r="E14" s="7" t="n">
@@ -2090,12 +2090,12 @@
         <f>IFERROR(E14/(E14+F14),0)</f>
         <v/>
       </c>
-      <c r="H14" s="16" t="inlineStr">
+      <c r="H14" s="10" t="inlineStr">
         <is>
           <t>En meta</t>
         </is>
       </c>
-      <c r="I14" s="16" t="inlineStr">
+      <c r="I14" s="10" t="inlineStr">
         <is>
           <t>Mantener estándar</t>
         </is>
@@ -2105,19 +2105,19 @@
       <c r="A15" s="11" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="15" t="inlineStr">
-        <is>
-          <t>38339</t>
+      <c r="B15" s="16" t="inlineStr">
+        <is>
+          <t>38561</t>
         </is>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>San Marcos</t>
+          <t>Parque Toreo</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>Enrique Cesar Flores</t>
+          <t>Yazmin Chabela Guadarrama</t>
         </is>
       </c>
       <c r="E15" s="11" t="n">
@@ -2130,12 +2130,12 @@
         <f>IFERROR(E15/(E15+F15),0)</f>
         <v/>
       </c>
-      <c r="H15" s="16" t="inlineStr">
+      <c r="H15" s="10" t="inlineStr">
         <is>
           <t>En meta</t>
         </is>
       </c>
-      <c r="I15" s="16" t="inlineStr">
+      <c r="I15" s="10" t="inlineStr">
         <is>
           <t>Mantener estándar</t>
         </is>
@@ -2147,21 +2147,21 @@
       </c>
       <c r="B16" s="17" t="inlineStr">
         <is>
-          <t>38770</t>
+          <t>38719</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>Gustavo Baz 29</t>
+          <t>Plaza Fortuna</t>
         </is>
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t>Yazmin Chabela Guadarrama</t>
+          <t>Veronica Garcia Ortega</t>
         </is>
       </c>
       <c r="E16" s="7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F16" s="7" t="n">
         <v>2</v>
@@ -2170,12 +2170,12 @@
         <f>IFERROR(E16/(E16+F16),0)</f>
         <v/>
       </c>
-      <c r="H16" s="16" t="inlineStr">
+      <c r="H16" s="10" t="inlineStr">
         <is>
           <t>En meta</t>
         </is>
       </c>
-      <c r="I16" s="16" t="inlineStr">
+      <c r="I16" s="10" t="inlineStr">
         <is>
           <t>Mantener estándar</t>
         </is>
@@ -2185,14 +2185,14 @@
       <c r="A17" s="11" t="n">
         <v>13</v>
       </c>
-      <c r="B17" s="15" t="inlineStr">
-        <is>
-          <t>38401</t>
+      <c r="B17" s="16" t="inlineStr">
+        <is>
+          <t>38339</t>
         </is>
       </c>
       <c r="C17" s="12" t="inlineStr">
         <is>
-          <t>Coacalco</t>
+          <t>San Marcos</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
@@ -2201,10 +2201,10 @@
         </is>
       </c>
       <c r="E17" s="11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G17" s="13">
         <f>IFERROR(E17/(E17+F17),0)</f>
@@ -2212,12 +2212,12 @@
       </c>
       <c r="H17" s="10" t="inlineStr">
         <is>
-          <t>Seguimiento</t>
+          <t>En meta</t>
         </is>
       </c>
       <c r="I17" s="10" t="inlineStr">
         <is>
-          <t>Dar seguimiento</t>
+          <t>Mantener estándar</t>
         </is>
       </c>
     </row>
@@ -2250,12 +2250,12 @@
         <f>IFERROR(E18/(E18+F18),0)</f>
         <v/>
       </c>
-      <c r="H18" s="10" t="inlineStr">
+      <c r="H18" s="14" t="inlineStr">
         <is>
           <t>Seguimiento</t>
         </is>
       </c>
-      <c r="I18" s="10" t="inlineStr">
+      <c r="I18" s="14" t="inlineStr">
         <is>
           <t>Dar seguimiento</t>
         </is>
@@ -2265,7 +2265,7 @@
       <c r="A19" s="11" t="n">
         <v>15</v>
       </c>
-      <c r="B19" s="15" t="inlineStr">
+      <c r="B19" s="16" t="inlineStr">
         <is>
           <t>38458</t>
         </is>
@@ -2290,12 +2290,12 @@
         <f>IFERROR(E19/(E19+F19),0)</f>
         <v/>
       </c>
-      <c r="H19" s="10" t="inlineStr">
+      <c r="H19" s="14" t="inlineStr">
         <is>
           <t>Seguimiento</t>
         </is>
       </c>
-      <c r="I19" s="10" t="inlineStr">
+      <c r="I19" s="14" t="inlineStr">
         <is>
           <t>Dar seguimiento</t>
         </is>
@@ -2330,12 +2330,12 @@
         <f>IFERROR(E20/(E20+F20),0)</f>
         <v/>
       </c>
-      <c r="H20" s="10" t="inlineStr">
+      <c r="H20" s="14" t="inlineStr">
         <is>
           <t>Seguimiento</t>
         </is>
       </c>
-      <c r="I20" s="10" t="inlineStr">
+      <c r="I20" s="14" t="inlineStr">
         <is>
           <t>Dar seguimiento</t>
         </is>
@@ -2345,7 +2345,7 @@
       <c r="A21" s="11" t="n">
         <v>17</v>
       </c>
-      <c r="B21" s="15" t="inlineStr">
+      <c r="B21" s="16" t="inlineStr">
         <is>
           <t>38590</t>
         </is>
@@ -2370,12 +2370,12 @@
         <f>IFERROR(E21/(E21+F21),0)</f>
         <v/>
       </c>
-      <c r="H21" s="10" t="inlineStr">
+      <c r="H21" s="14" t="inlineStr">
         <is>
           <t>Seguimiento</t>
         </is>
       </c>
-      <c r="I21" s="10" t="inlineStr">
+      <c r="I21" s="14" t="inlineStr">
         <is>
           <t>Dar seguimiento</t>
         </is>
@@ -2410,12 +2410,12 @@
         <f>IFERROR(E22/(E22+F22),0)</f>
         <v/>
       </c>
-      <c r="H22" s="10" t="inlineStr">
+      <c r="H22" s="14" t="inlineStr">
         <is>
           <t>Seguimiento</t>
         </is>
       </c>
-      <c r="I22" s="10" t="inlineStr">
+      <c r="I22" s="14" t="inlineStr">
         <is>
           <t>Dar seguimiento</t>
         </is>
@@ -2425,7 +2425,7 @@
       <c r="A23" s="11" t="n">
         <v>19</v>
       </c>
-      <c r="B23" s="15" t="inlineStr">
+      <c r="B23" s="16" t="inlineStr">
         <is>
           <t>38674</t>
         </is>
@@ -2450,12 +2450,12 @@
         <f>IFERROR(E23/(E23+F23),0)</f>
         <v/>
       </c>
-      <c r="H23" s="10" t="inlineStr">
+      <c r="H23" s="14" t="inlineStr">
         <is>
           <t>Seguimiento</t>
         </is>
       </c>
-      <c r="I23" s="10" t="inlineStr">
+      <c r="I23" s="14" t="inlineStr">
         <is>
           <t>Dar seguimiento</t>
         </is>
@@ -2490,12 +2490,12 @@
         <f>IFERROR(E24/(E24+F24),0)</f>
         <v/>
       </c>
-      <c r="H24" s="10" t="inlineStr">
+      <c r="H24" s="14" t="inlineStr">
         <is>
           <t>Seguimiento</t>
         </is>
       </c>
-      <c r="I24" s="10" t="inlineStr">
+      <c r="I24" s="14" t="inlineStr">
         <is>
           <t>Dar seguimiento</t>
         </is>
@@ -2505,7 +2505,7 @@
       <c r="A25" s="11" t="n">
         <v>21</v>
       </c>
-      <c r="B25" s="15" t="inlineStr">
+      <c r="B25" s="16" t="inlineStr">
         <is>
           <t>38333</t>
         </is>
@@ -2530,12 +2530,12 @@
         <f>IFERROR(E25/(E25+F25),0)</f>
         <v/>
       </c>
-      <c r="H25" s="10" t="inlineStr">
+      <c r="H25" s="14" t="inlineStr">
         <is>
           <t>Seguimiento</t>
         </is>
       </c>
-      <c r="I25" s="10" t="inlineStr">
+      <c r="I25" s="14" t="inlineStr">
         <is>
           <t>Dar seguimiento</t>
         </is>
@@ -2570,12 +2570,12 @@
         <f>IFERROR(E26/(E26+F26),0)</f>
         <v/>
       </c>
-      <c r="H26" s="10" t="inlineStr">
+      <c r="H26" s="14" t="inlineStr">
         <is>
           <t>Seguimiento</t>
         </is>
       </c>
-      <c r="I26" s="10" t="inlineStr">
+      <c r="I26" s="14" t="inlineStr">
         <is>
           <t>Dar seguimiento</t>
         </is>
@@ -2585,7 +2585,7 @@
       <c r="A27" s="11" t="n">
         <v>23</v>
       </c>
-      <c r="B27" s="15" t="inlineStr">
+      <c r="B27" s="16" t="inlineStr">
         <is>
           <t>38176</t>
         </is>
@@ -2610,12 +2610,12 @@
         <f>IFERROR(E27/(E27+F27),0)</f>
         <v/>
       </c>
-      <c r="H27" s="10" t="inlineStr">
+      <c r="H27" s="14" t="inlineStr">
         <is>
           <t>Seguimiento</t>
         </is>
       </c>
-      <c r="I27" s="10" t="inlineStr">
+      <c r="I27" s="14" t="inlineStr">
         <is>
           <t>Dar seguimiento</t>
         </is>
@@ -2650,12 +2650,12 @@
         <f>IFERROR(E28/(E28+F28),0)</f>
         <v/>
       </c>
-      <c r="H28" s="10" t="inlineStr">
+      <c r="H28" s="14" t="inlineStr">
         <is>
           <t>Seguimiento</t>
         </is>
       </c>
-      <c r="I28" s="10" t="inlineStr">
+      <c r="I28" s="14" t="inlineStr">
         <is>
           <t>Dar seguimiento</t>
         </is>
@@ -2665,7 +2665,7 @@
       <c r="A29" s="11" t="n">
         <v>25</v>
       </c>
-      <c r="B29" s="15" t="inlineStr">
+      <c r="B29" s="16" t="inlineStr">
         <is>
           <t>38656</t>
         </is>
@@ -2690,12 +2690,12 @@
         <f>IFERROR(E29/(E29+F29),0)</f>
         <v/>
       </c>
-      <c r="H29" s="10" t="inlineStr">
+      <c r="H29" s="14" t="inlineStr">
         <is>
           <t>Seguimiento</t>
         </is>
       </c>
-      <c r="I29" s="10" t="inlineStr">
+      <c r="I29" s="14" t="inlineStr">
         <is>
           <t>Dar seguimiento</t>
         </is>
@@ -2730,12 +2730,12 @@
         <f>IFERROR(E30/(E30+F30),0)</f>
         <v/>
       </c>
-      <c r="H30" s="10" t="inlineStr">
+      <c r="H30" s="14" t="inlineStr">
         <is>
           <t>Seguimiento</t>
         </is>
       </c>
-      <c r="I30" s="10" t="inlineStr">
+      <c r="I30" s="14" t="inlineStr">
         <is>
           <t>Dar seguimiento</t>
         </is>
@@ -2745,7 +2745,7 @@
       <c r="A31" s="11" t="n">
         <v>27</v>
       </c>
-      <c r="B31" s="15" t="inlineStr">
+      <c r="B31" s="16" t="inlineStr">
         <is>
           <t>38894</t>
         </is>
@@ -2770,12 +2770,12 @@
         <f>IFERROR(E31/(E31+F31),0)</f>
         <v/>
       </c>
-      <c r="H31" s="10" t="inlineStr">
+      <c r="H31" s="14" t="inlineStr">
         <is>
           <t>Seguimiento</t>
         </is>
       </c>
-      <c r="I31" s="10" t="inlineStr">
+      <c r="I31" s="14" t="inlineStr">
         <is>
           <t>Dar seguimiento</t>
         </is>
@@ -2810,12 +2810,12 @@
         <f>IFERROR(E32/(E32+F32),0)</f>
         <v/>
       </c>
-      <c r="H32" s="10" t="inlineStr">
+      <c r="H32" s="14" t="inlineStr">
         <is>
           <t>Seguimiento</t>
         </is>
       </c>
-      <c r="I32" s="10" t="inlineStr">
+      <c r="I32" s="14" t="inlineStr">
         <is>
           <t>Dar seguimiento</t>
         </is>
@@ -2825,7 +2825,7 @@
       <c r="A33" s="11" t="n">
         <v>29</v>
       </c>
-      <c r="B33" s="15" t="inlineStr">
+      <c r="B33" s="16" t="inlineStr">
         <is>
           <t>38427</t>
         </is>
@@ -2850,12 +2850,12 @@
         <f>IFERROR(E33/(E33+F33),0)</f>
         <v/>
       </c>
-      <c r="H33" s="10" t="inlineStr">
+      <c r="H33" s="14" t="inlineStr">
         <is>
           <t>Seguimiento</t>
         </is>
       </c>
-      <c r="I33" s="10" t="inlineStr">
+      <c r="I33" s="14" t="inlineStr">
         <is>
           <t>Dar seguimiento</t>
         </is>
@@ -2890,12 +2890,12 @@
         <f>IFERROR(E34/(E34+F34),0)</f>
         <v/>
       </c>
-      <c r="H34" s="10" t="inlineStr">
+      <c r="H34" s="14" t="inlineStr">
         <is>
           <t>Seguimiento</t>
         </is>
       </c>
-      <c r="I34" s="10" t="inlineStr">
+      <c r="I34" s="14" t="inlineStr">
         <is>
           <t>Dar seguimiento</t>
         </is>
@@ -2905,7 +2905,7 @@
       <c r="A35" s="11" t="n">
         <v>31</v>
       </c>
-      <c r="B35" s="15" t="inlineStr">
+      <c r="B35" s="16" t="inlineStr">
         <is>
           <t>38930</t>
         </is>
@@ -2930,12 +2930,12 @@
         <f>IFERROR(E35/(E35+F35),0)</f>
         <v/>
       </c>
-      <c r="H35" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I35" s="14" t="inlineStr">
+      <c r="H35" s="15" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="I35" s="15" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -2970,12 +2970,12 @@
         <f>IFERROR(E36/(E36+F36),0)</f>
         <v/>
       </c>
-      <c r="H36" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I36" s="14" t="inlineStr">
+      <c r="H36" s="15" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="I36" s="15" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -2985,7 +2985,7 @@
       <c r="A37" s="11" t="n">
         <v>33</v>
       </c>
-      <c r="B37" s="15" t="inlineStr">
+      <c r="B37" s="16" t="inlineStr">
         <is>
           <t>38431</t>
         </is>
@@ -3010,12 +3010,12 @@
         <f>IFERROR(E37/(E37+F37),0)</f>
         <v/>
       </c>
-      <c r="H37" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I37" s="14" t="inlineStr">
+      <c r="H37" s="15" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="I37" s="15" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -3050,12 +3050,12 @@
         <f>IFERROR(E38/(E38+F38),0)</f>
         <v/>
       </c>
-      <c r="H38" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I38" s="14" t="inlineStr">
+      <c r="H38" s="15" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="I38" s="15" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -3065,7 +3065,7 @@
       <c r="A39" s="11" t="n">
         <v>35</v>
       </c>
-      <c r="B39" s="15" t="inlineStr">
+      <c r="B39" s="16" t="inlineStr">
         <is>
           <t>38230</t>
         </is>
@@ -3090,12 +3090,12 @@
         <f>IFERROR(E39/(E39+F39),0)</f>
         <v/>
       </c>
-      <c r="H39" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I39" s="14" t="inlineStr">
+      <c r="H39" s="15" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="I39" s="15" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -3130,12 +3130,12 @@
         <f>IFERROR(E40/(E40+F40),0)</f>
         <v/>
       </c>
-      <c r="H40" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I40" s="14" t="inlineStr">
+      <c r="H40" s="15" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="I40" s="15" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -3145,7 +3145,7 @@
       <c r="A41" s="11" t="n">
         <v>37</v>
       </c>
-      <c r="B41" s="15" t="inlineStr">
+      <c r="B41" s="16" t="inlineStr">
         <is>
           <t>38965</t>
         </is>
@@ -3170,12 +3170,12 @@
         <f>IFERROR(E41/(E41+F41),0)</f>
         <v/>
       </c>
-      <c r="H41" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I41" s="14" t="inlineStr">
+      <c r="H41" s="15" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="I41" s="15" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -3210,12 +3210,12 @@
         <f>IFERROR(E42/(E42+F42),0)</f>
         <v/>
       </c>
-      <c r="H42" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I42" s="14" t="inlineStr">
+      <c r="H42" s="15" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="I42" s="15" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -3225,7 +3225,7 @@
       <c r="A43" s="11" t="n">
         <v>39</v>
       </c>
-      <c r="B43" s="15" t="inlineStr">
+      <c r="B43" s="16" t="inlineStr">
         <is>
           <t>38992</t>
         </is>
@@ -3250,12 +3250,12 @@
         <f>IFERROR(E43/(E43+F43),0)</f>
         <v/>
       </c>
-      <c r="H43" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I43" s="14" t="inlineStr">
+      <c r="H43" s="15" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="I43" s="15" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -3290,12 +3290,12 @@
         <f>IFERROR(E44/(E44+F44),0)</f>
         <v/>
       </c>
-      <c r="H44" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I44" s="14" t="inlineStr">
+      <c r="H44" s="15" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="I44" s="15" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -3305,7 +3305,7 @@
       <c r="A45" s="11" t="n">
         <v>41</v>
       </c>
-      <c r="B45" s="15" t="inlineStr">
+      <c r="B45" s="16" t="inlineStr">
         <is>
           <t>38792</t>
         </is>
@@ -3330,12 +3330,12 @@
         <f>IFERROR(E45/(E45+F45),0)</f>
         <v/>
       </c>
-      <c r="H45" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I45" s="14" t="inlineStr">
+      <c r="H45" s="15" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="I45" s="15" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -3370,12 +3370,12 @@
         <f>IFERROR(E46/(E46+F46),0)</f>
         <v/>
       </c>
-      <c r="H46" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I46" s="14" t="inlineStr">
+      <c r="H46" s="15" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="I46" s="15" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -3385,7 +3385,7 @@
       <c r="A47" s="11" t="n">
         <v>43</v>
       </c>
-      <c r="B47" s="15" t="inlineStr">
+      <c r="B47" s="16" t="inlineStr">
         <is>
           <t>38136</t>
         </is>
@@ -3410,12 +3410,12 @@
         <f>IFERROR(E47/(E47+F47),0)</f>
         <v/>
       </c>
-      <c r="H47" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I47" s="14" t="inlineStr">
+      <c r="H47" s="15" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="I47" s="15" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -3450,12 +3450,12 @@
         <f>IFERROR(E48/(E48+F48),0)</f>
         <v/>
       </c>
-      <c r="H48" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I48" s="14" t="inlineStr">
+      <c r="H48" s="15" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="I48" s="15" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -3465,7 +3465,7 @@
       <c r="A49" s="11" t="n">
         <v>45</v>
       </c>
-      <c r="B49" s="15" t="inlineStr">
+      <c r="B49" s="16" t="inlineStr">
         <is>
           <t>38186</t>
         </is>
@@ -3490,12 +3490,12 @@
         <f>IFERROR(E49/(E49+F49),0)</f>
         <v/>
       </c>
-      <c r="H49" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I49" s="14" t="inlineStr">
+      <c r="H49" s="15" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="I49" s="15" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -3530,12 +3530,12 @@
         <f>IFERROR(E50/(E50+F50),0)</f>
         <v/>
       </c>
-      <c r="H50" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I50" s="14" t="inlineStr">
+      <c r="H50" s="15" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="I50" s="15" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -3545,7 +3545,7 @@
       <c r="A51" s="11" t="n">
         <v>47</v>
       </c>
-      <c r="B51" s="15" t="inlineStr">
+      <c r="B51" s="16" t="inlineStr">
         <is>
           <t>38149</t>
         </is>
@@ -3570,12 +3570,12 @@
         <f>IFERROR(E51/(E51+F51),0)</f>
         <v/>
       </c>
-      <c r="H51" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I51" s="14" t="inlineStr">
+      <c r="H51" s="15" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="I51" s="15" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -3610,12 +3610,12 @@
         <f>IFERROR(E52/(E52+F52),0)</f>
         <v/>
       </c>
-      <c r="H52" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I52" s="14" t="inlineStr">
+      <c r="H52" s="15" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="I52" s="15" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -3625,7 +3625,7 @@
       <c r="A53" s="11" t="n">
         <v>49</v>
       </c>
-      <c r="B53" s="15" t="inlineStr">
+      <c r="B53" s="16" t="inlineStr">
         <is>
           <t>38837</t>
         </is>
@@ -3650,12 +3650,12 @@
         <f>IFERROR(E53/(E53+F53),0)</f>
         <v/>
       </c>
-      <c r="H53" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I53" s="14" t="inlineStr">
+      <c r="H53" s="15" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="I53" s="15" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -3690,12 +3690,12 @@
         <f>IFERROR(E54/(E54+F54),0)</f>
         <v/>
       </c>
-      <c r="H54" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I54" s="14" t="inlineStr">
+      <c r="H54" s="15" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="I54" s="15" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -3705,7 +3705,7 @@
       <c r="A55" s="11" t="n">
         <v>51</v>
       </c>
-      <c r="B55" s="15" t="inlineStr">
+      <c r="B55" s="16" t="inlineStr">
         <is>
           <t>38535</t>
         </is>
@@ -3730,12 +3730,12 @@
         <f>IFERROR(E55/(E55+F55),0)</f>
         <v/>
       </c>
-      <c r="H55" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I55" s="14" t="inlineStr">
+      <c r="H55" s="15" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="I55" s="15" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -3770,12 +3770,12 @@
         <f>IFERROR(E56/(E56+F56),0)</f>
         <v/>
       </c>
-      <c r="H56" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I56" s="14" t="inlineStr">
+      <c r="H56" s="15" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="I56" s="15" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -3785,7 +3785,7 @@
       <c r="A57" s="11" t="n">
         <v>53</v>
       </c>
-      <c r="B57" s="15" t="inlineStr">
+      <c r="B57" s="16" t="inlineStr">
         <is>
           <t>38363</t>
         </is>
@@ -3810,12 +3810,12 @@
         <f>IFERROR(E57/(E57+F57),0)</f>
         <v/>
       </c>
-      <c r="H57" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I57" s="14" t="inlineStr">
+      <c r="H57" s="15" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="I57" s="15" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -3850,12 +3850,12 @@
         <f>IFERROR(E58/(E58+F58),0)</f>
         <v/>
       </c>
-      <c r="H58" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I58" s="14" t="inlineStr">
+      <c r="H58" s="15" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="I58" s="15" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -3865,7 +3865,7 @@
       <c r="A59" s="11" t="n">
         <v>55</v>
       </c>
-      <c r="B59" s="15" t="inlineStr">
+      <c r="B59" s="16" t="inlineStr">
         <is>
           <t>38119</t>
         </is>
@@ -3890,12 +3890,12 @@
         <f>IFERROR(E59/(E59+F59),0)</f>
         <v/>
       </c>
-      <c r="H59" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I59" s="14" t="inlineStr">
+      <c r="H59" s="15" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="I59" s="15" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -3930,12 +3930,12 @@
         <f>IFERROR(E60/(E60+F60),0)</f>
         <v/>
       </c>
-      <c r="H60" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I60" s="14" t="inlineStr">
+      <c r="H60" s="15" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="I60" s="15" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -3945,7 +3945,7 @@
       <c r="A61" s="11" t="n">
         <v>57</v>
       </c>
-      <c r="B61" s="15" t="inlineStr">
+      <c r="B61" s="16" t="inlineStr">
         <is>
           <t>38371</t>
         </is>
@@ -3970,12 +3970,12 @@
         <f>IFERROR(E61/(E61+F61),0)</f>
         <v/>
       </c>
-      <c r="H61" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I61" s="14" t="inlineStr">
+      <c r="H61" s="15" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="I61" s="15" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -4010,12 +4010,12 @@
         <f>IFERROR(E62/(E62+F62),0)</f>
         <v/>
       </c>
-      <c r="H62" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I62" s="14" t="inlineStr">
+      <c r="H62" s="15" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="I62" s="15" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -4025,7 +4025,7 @@
       <c r="A63" s="11" t="n">
         <v>59</v>
       </c>
-      <c r="B63" s="15" t="inlineStr">
+      <c r="B63" s="16" t="inlineStr">
         <is>
           <t>43195</t>
         </is>
@@ -4050,12 +4050,12 @@
         <f>IFERROR(E63/(E63+F63),0)</f>
         <v/>
       </c>
-      <c r="H63" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I63" s="14" t="inlineStr">
+      <c r="H63" s="15" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="I63" s="15" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -4090,12 +4090,12 @@
         <f>IFERROR(E64/(E64+F64),0)</f>
         <v/>
       </c>
-      <c r="H64" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I64" s="14" t="inlineStr">
+      <c r="H64" s="15" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="I64" s="15" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -4105,7 +4105,7 @@
       <c r="A65" s="11" t="n">
         <v>61</v>
       </c>
-      <c r="B65" s="15" t="inlineStr">
+      <c r="B65" s="16" t="inlineStr">
         <is>
           <t>43132</t>
         </is>
@@ -4130,12 +4130,12 @@
         <f>IFERROR(E65/(E65+F65),0)</f>
         <v/>
       </c>
-      <c r="H65" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I65" s="14" t="inlineStr">
+      <c r="H65" s="15" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="I65" s="15" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -4170,12 +4170,12 @@
         <f>IFERROR(E66/(E66+F66),0)</f>
         <v/>
       </c>
-      <c r="H66" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I66" s="14" t="inlineStr">
+      <c r="H66" s="15" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="I66" s="15" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -4185,7 +4185,7 @@
       <c r="A67" s="11" t="n">
         <v>63</v>
       </c>
-      <c r="B67" s="15" t="inlineStr">
+      <c r="B67" s="16" t="inlineStr">
         <is>
           <t>38442</t>
         </is>
@@ -4210,12 +4210,12 @@
         <f>IFERROR(E67/(E67+F67),0)</f>
         <v/>
       </c>
-      <c r="H67" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I67" s="14" t="inlineStr">
+      <c r="H67" s="15" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="I67" s="15" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -4250,12 +4250,12 @@
         <f>IFERROR(E68/(E68+F68),0)</f>
         <v/>
       </c>
-      <c r="H68" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I68" s="14" t="inlineStr">
+      <c r="H68" s="15" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="I68" s="15" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -4265,7 +4265,7 @@
       <c r="A69" s="11" t="n">
         <v>65</v>
       </c>
-      <c r="B69" s="15" t="inlineStr">
+      <c r="B69" s="16" t="inlineStr">
         <is>
           <t>38411</t>
         </is>
@@ -4290,12 +4290,12 @@
         <f>IFERROR(E69/(E69+F69),0)</f>
         <v/>
       </c>
-      <c r="H69" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I69" s="14" t="inlineStr">
+      <c r="H69" s="15" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="I69" s="15" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -4330,12 +4330,12 @@
         <f>IFERROR(E70/(E70+F70),0)</f>
         <v/>
       </c>
-      <c r="H70" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I70" s="14" t="inlineStr">
+      <c r="H70" s="15" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="I70" s="15" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -4345,7 +4345,7 @@
       <c r="A71" s="11" t="n">
         <v>67</v>
       </c>
-      <c r="B71" s="15" t="inlineStr">
+      <c r="B71" s="16" t="inlineStr">
         <is>
           <t>38694</t>
         </is>
@@ -4370,12 +4370,12 @@
         <f>IFERROR(E71/(E71+F71),0)</f>
         <v/>
       </c>
-      <c r="H71" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I71" s="14" t="inlineStr">
+      <c r="H71" s="15" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="I71" s="15" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -4410,12 +4410,12 @@
         <f>IFERROR(E72/(E72+F72),0)</f>
         <v/>
       </c>
-      <c r="H72" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I72" s="14" t="inlineStr">
+      <c r="H72" s="15" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="I72" s="15" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -4425,7 +4425,7 @@
       <c r="A73" s="11" t="n">
         <v>69</v>
       </c>
-      <c r="B73" s="15" t="inlineStr">
+      <c r="B73" s="16" t="inlineStr">
         <is>
           <t>38142</t>
         </is>
@@ -4450,12 +4450,12 @@
         <f>IFERROR(E73/(E73+F73),0)</f>
         <v/>
       </c>
-      <c r="H73" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I73" s="14" t="inlineStr">
+      <c r="H73" s="15" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="I73" s="15" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -4490,12 +4490,12 @@
         <f>IFERROR(E74/(E74+F74),0)</f>
         <v/>
       </c>
-      <c r="H74" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I74" s="14" t="inlineStr">
+      <c r="H74" s="15" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="I74" s="15" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -4505,7 +4505,7 @@
       <c r="A75" s="11" t="n">
         <v>71</v>
       </c>
-      <c r="B75" s="15" t="inlineStr">
+      <c r="B75" s="16" t="inlineStr">
         <is>
           <t>38845</t>
         </is>
@@ -4530,12 +4530,12 @@
         <f>IFERROR(E75/(E75+F75),0)</f>
         <v/>
       </c>
-      <c r="H75" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I75" s="14" t="inlineStr">
+      <c r="H75" s="15" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="I75" s="15" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -4570,12 +4570,12 @@
         <f>IFERROR(E76/(E76+F76),0)</f>
         <v/>
       </c>
-      <c r="H76" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I76" s="14" t="inlineStr">
+      <c r="H76" s="15" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="I76" s="15" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -4585,7 +4585,7 @@
       <c r="A77" s="11" t="n">
         <v>73</v>
       </c>
-      <c r="B77" s="15" t="inlineStr">
+      <c r="B77" s="16" t="inlineStr">
         <is>
           <t>38155</t>
         </is>
@@ -4610,12 +4610,12 @@
         <f>IFERROR(E77/(E77+F77),0)</f>
         <v/>
       </c>
-      <c r="H77" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I77" s="14" t="inlineStr">
+      <c r="H77" s="15" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="I77" s="15" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -4650,12 +4650,12 @@
         <f>IFERROR(E78/(E78+F78),0)</f>
         <v/>
       </c>
-      <c r="H78" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I78" s="14" t="inlineStr">
+      <c r="H78" s="15" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="I78" s="15" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -4665,7 +4665,7 @@
       <c r="A79" s="11" t="n">
         <v>75</v>
       </c>
-      <c r="B79" s="15" t="inlineStr">
+      <c r="B79" s="16" t="inlineStr">
         <is>
           <t>38906</t>
         </is>
@@ -4690,12 +4690,12 @@
         <f>IFERROR(E79/(E79+F79),0)</f>
         <v/>
       </c>
-      <c r="H79" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I79" s="14" t="inlineStr">
+      <c r="H79" s="15" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="I79" s="15" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -4730,12 +4730,12 @@
         <f>IFERROR(E80/(E80+F80),0)</f>
         <v/>
       </c>
-      <c r="H80" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I80" s="14" t="inlineStr">
+      <c r="H80" s="15" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="I80" s="15" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -4745,7 +4745,7 @@
       <c r="A81" s="11" t="n">
         <v>77</v>
       </c>
-      <c r="B81" s="15" t="inlineStr">
+      <c r="B81" s="16" t="inlineStr">
         <is>
           <t>38167</t>
         </is>
@@ -4770,12 +4770,12 @@
         <f>IFERROR(E81/(E81+F81),0)</f>
         <v/>
       </c>
-      <c r="H81" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I81" s="14" t="inlineStr">
+      <c r="H81" s="15" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="I81" s="15" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -4810,12 +4810,12 @@
         <f>IFERROR(E82/(E82+F82),0)</f>
         <v/>
       </c>
-      <c r="H82" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I82" s="14" t="inlineStr">
+      <c r="H82" s="15" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="I82" s="15" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -4825,7 +4825,7 @@
       <c r="A83" s="11" t="n">
         <v>79</v>
       </c>
-      <c r="B83" s="15" t="inlineStr">
+      <c r="B83" s="16" t="inlineStr">
         <is>
           <t>38171</t>
         </is>
@@ -4850,12 +4850,12 @@
         <f>IFERROR(E83/(E83+F83),0)</f>
         <v/>
       </c>
-      <c r="H83" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I83" s="14" t="inlineStr">
+      <c r="H83" s="15" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="I83" s="15" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -4890,12 +4890,12 @@
         <f>IFERROR(E84/(E84+F84),0)</f>
         <v/>
       </c>
-      <c r="H84" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I84" s="14" t="inlineStr">
+      <c r="H84" s="15" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="I84" s="15" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -4905,7 +4905,7 @@
       <c r="A85" s="11" t="n">
         <v>81</v>
       </c>
-      <c r="B85" s="15" t="inlineStr">
+      <c r="B85" s="16" t="inlineStr">
         <is>
           <t>38103</t>
         </is>
@@ -4930,12 +4930,12 @@
         <f>IFERROR(E85/(E85+F85),0)</f>
         <v/>
       </c>
-      <c r="H85" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I85" s="14" t="inlineStr">
+      <c r="H85" s="15" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="I85" s="15" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -4970,12 +4970,12 @@
         <f>IFERROR(E86/(E86+F86),0)</f>
         <v/>
       </c>
-      <c r="H86" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I86" s="14" t="inlineStr">
+      <c r="H86" s="15" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="I86" s="15" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -4985,7 +4985,7 @@
       <c r="A87" s="11" t="n">
         <v>83</v>
       </c>
-      <c r="B87" s="15" t="inlineStr">
+      <c r="B87" s="16" t="inlineStr">
         <is>
           <t>38169</t>
         </is>
@@ -5010,12 +5010,12 @@
         <f>IFERROR(E87/(E87+F87),0)</f>
         <v/>
       </c>
-      <c r="H87" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I87" s="14" t="inlineStr">
+      <c r="H87" s="15" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="I87" s="15" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -5050,12 +5050,12 @@
         <f>IFERROR(E88/(E88+F88),0)</f>
         <v/>
       </c>
-      <c r="H88" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I88" s="14" t="inlineStr">
+      <c r="H88" s="15" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="I88" s="15" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -5065,7 +5065,7 @@
       <c r="A89" s="11" t="n">
         <v>85</v>
       </c>
-      <c r="B89" s="15" t="inlineStr">
+      <c r="B89" s="16" t="inlineStr">
         <is>
           <t>38508</t>
         </is>
@@ -5090,12 +5090,12 @@
         <f>IFERROR(E89/(E89+F89),0)</f>
         <v/>
       </c>
-      <c r="H89" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I89" s="14" t="inlineStr">
+      <c r="H89" s="15" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="I89" s="15" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -5130,12 +5130,12 @@
         <f>IFERROR(E90/(E90+F90),0)</f>
         <v/>
       </c>
-      <c r="H90" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I90" s="14" t="inlineStr">
+      <c r="H90" s="15" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="I90" s="15" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -5145,7 +5145,7 @@
       <c r="A91" s="11" t="n">
         <v>87</v>
       </c>
-      <c r="B91" s="15" t="inlineStr">
+      <c r="B91" s="16" t="inlineStr">
         <is>
           <t>38101</t>
         </is>
@@ -5170,12 +5170,12 @@
         <f>IFERROR(E91/(E91+F91),0)</f>
         <v/>
       </c>
-      <c r="H91" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I91" s="14" t="inlineStr">
+      <c r="H91" s="15" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="I91" s="15" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -5210,12 +5210,12 @@
         <f>IFERROR(E92/(E92+F92),0)</f>
         <v/>
       </c>
-      <c r="H92" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I92" s="14" t="inlineStr">
+      <c r="H92" s="15" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="I92" s="15" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -5225,7 +5225,7 @@
       <c r="A93" s="11" t="n">
         <v>89</v>
       </c>
-      <c r="B93" s="15" t="inlineStr">
+      <c r="B93" s="16" t="inlineStr">
         <is>
           <t>38194</t>
         </is>
@@ -5250,12 +5250,12 @@
         <f>IFERROR(E93/(E93+F93),0)</f>
         <v/>
       </c>
-      <c r="H93" s="14" t="inlineStr">
-        <is>
-          <t>Atención</t>
-        </is>
-      </c>
-      <c r="I93" s="14" t="inlineStr">
+      <c r="H93" s="15" t="inlineStr">
+        <is>
+          <t>Atención</t>
+        </is>
+      </c>
+      <c r="I93" s="15" t="inlineStr">
         <is>
           <t>Priorizar hoy</t>
         </is>
@@ -5290,12 +5290,12 